--- a/SITE MONITORING.xlsx
+++ b/SITE MONITORING.xlsx
@@ -1114,19 +1114,19 @@
       </c>
       <c r="F2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>3767640.1674616369</v>
+        <v>6059382.1473084744</v>
       </c>
       <c r="G2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3378902.3358840779</v>
+        <v>5415574.0184972491</v>
       </c>
       <c r="H2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>400</v>
+        <v>620</v>
       </c>
       <c r="I2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>337</v>
+        <v>379</v>
       </c>
       <c r="J2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="L2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -1146,11 +1146,11 @@
       </c>
       <c r="N2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O2">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="P2">
         <v>3</v>
@@ -1174,19 +1174,19 @@
       </c>
       <c r="F3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4755985.7453720355</v>
+        <v>7288506.4151363429</v>
       </c>
       <c r="G3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4198139.0504805734</v>
+        <v>6653085.5256644776</v>
       </c>
       <c r="H3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>547</v>
+        <v>614</v>
       </c>
       <c r="I3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>610</v>
+        <v>497</v>
       </c>
       <c r="J3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1206,11 +1206,11 @@
       </c>
       <c r="N3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="O3">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="P3">
         <v>2</v>
@@ -1234,23 +1234,23 @@
       </c>
       <c r="F4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4115736.9093229892</v>
+        <v>6371310.9355353834</v>
       </c>
       <c r="G4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4831243.1255528908</v>
+        <v>6613502.6668428723</v>
       </c>
       <c r="H4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>566</v>
+        <v>667</v>
       </c>
       <c r="I4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>42</v>
+        <v>745</v>
       </c>
       <c r="J4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -1258,19 +1258,19 @@
       </c>
       <c r="L4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="O4">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="P4">
         <v>4</v>
@@ -1294,27 +1294,27 @@
       </c>
       <c r="F5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9315606.1279473379</v>
+        <v>14068595.525211383</v>
       </c>
       <c r="G5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8927501.3209277317</v>
+        <v>13913394.68100726</v>
       </c>
       <c r="H5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>989</v>
+        <v>760</v>
       </c>
       <c r="I5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1033</v>
+        <v>998</v>
       </c>
       <c r="J5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -1322,15 +1322,15 @@
       </c>
       <c r="M5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1203</v>
+        <v>1197</v>
       </c>
       <c r="O5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1218</v>
+        <v>1207</v>
       </c>
       <c r="P5">
         <v>3</v>
@@ -1354,19 +1354,19 @@
       </c>
       <c r="F6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>3622509.6095191082</v>
+        <v>5121540.0843401868</v>
       </c>
       <c r="G6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3433165.5757586341</v>
+        <v>5839432.1316437609</v>
       </c>
       <c r="H6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="I6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>353</v>
+        <v>419</v>
       </c>
       <c r="J6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1386,11 +1386,11 @@
       </c>
       <c r="N6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O6">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="P6">
         <v>3</v>
@@ -1414,19 +1414,19 @@
       </c>
       <c r="F7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>3453641.8844623081</v>
+        <v>5394052.5405044062</v>
       </c>
       <c r="G7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3315695.6946051032</v>
+        <v>5345165.618633477</v>
       </c>
       <c r="H7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>345</v>
+        <v>431</v>
       </c>
       <c r="I7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>318</v>
+        <v>301</v>
       </c>
       <c r="J7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="L7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -1446,11 +1446,11 @@
       </c>
       <c r="N7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="O7">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="P7">
         <v>2</v>
@@ -1474,23 +1474,23 @@
       </c>
       <c r="F8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4149554.9330451461</v>
+        <v>6272003.9840085637</v>
       </c>
       <c r="G8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3763040.3506287369</v>
+        <v>5990321.0092403321</v>
       </c>
       <c r="H8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>515</v>
+        <v>1167</v>
       </c>
       <c r="I8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>558</v>
+        <v>483</v>
       </c>
       <c r="J8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -1506,11 +1506,11 @@
       </c>
       <c r="N8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>592</v>
+        <v>608</v>
       </c>
       <c r="O8">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="P8">
         <v>9</v>
@@ -1534,19 +1534,19 @@
       </c>
       <c r="F9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>1692945.1848517051</v>
+        <v>2610227.0540075419</v>
       </c>
       <c r="G9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>1873870.2528251619</v>
+        <v>2744967.7764228848</v>
       </c>
       <c r="H9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="I9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="J9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="O9">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="P9">
         <v>1</v>
@@ -1594,19 +1594,19 @@
       </c>
       <c r="F10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>1943111.7270830791</v>
+        <v>2761713.1927333758</v>
       </c>
       <c r="G10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22.486592934000001</v>
+        <v>267968.35746859002</v>
       </c>
       <c r="H10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>159</v>
+        <v>196</v>
       </c>
       <c r="I10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1626,11 +1626,11 @@
       </c>
       <c r="N10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="O10">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="P10">
         <v>1</v>
@@ -1654,19 +1654,19 @@
       </c>
       <c r="F11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>2925789.0628380021</v>
+        <v>4379782.4858754724</v>
       </c>
       <c r="G11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3816371.4646472102</v>
+        <v>5948859.3354461109</v>
       </c>
       <c r="H11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>326</v>
+        <v>363</v>
       </c>
       <c r="I11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>487</v>
+        <v>542</v>
       </c>
       <c r="J11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1686,11 +1686,11 @@
       </c>
       <c r="N11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="O11">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="P11">
         <v>4</v>
@@ -1714,19 +1714,19 @@
       </c>
       <c r="F12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>1301883.6042596891</v>
+        <v>1995774.4805199029</v>
       </c>
       <c r="G12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>1720402.2001648659</v>
+        <v>2625962.4150365731</v>
       </c>
       <c r="H12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>257</v>
+        <v>212</v>
       </c>
       <c r="I12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>277</v>
+        <v>578</v>
       </c>
       <c r="J12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="N12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="O12">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -1774,19 +1774,19 @@
       </c>
       <c r="F13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>1833456.113912377</v>
+        <v>2676274.3626946318</v>
       </c>
       <c r="G13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>1807666.7458902949</v>
+        <v>2935154.1349404189</v>
       </c>
       <c r="H13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="I13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="J13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="K13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="N13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="O13">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -1834,27 +1834,27 @@
       </c>
       <c r="F14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6732074.4633739255</v>
+        <v>7510668.6871368838</v>
       </c>
       <c r="G14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5812917.9415709646</v>
+        <v>8711554.6449297052</v>
       </c>
       <c r="H14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>905</v>
+        <v>121</v>
       </c>
       <c r="I14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>161</v>
+        <v>802</v>
       </c>
       <c r="J14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -1866,11 +1866,11 @@
       </c>
       <c r="N14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1471</v>
+        <v>1454</v>
       </c>
       <c r="O14">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1442</v>
+        <v>1427</v>
       </c>
       <c r="P14">
         <v>2</v>
@@ -1894,19 +1894,19 @@
       </c>
       <c r="F15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10956297.987773804</v>
+        <v>18218164.868068825</v>
       </c>
       <c r="G15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12242361.641453536</v>
+        <v>19264893.816357184</v>
       </c>
       <c r="H15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>937</v>
+        <v>1045</v>
       </c>
       <c r="I15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>948</v>
+        <v>881</v>
       </c>
       <c r="J15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="K15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -1926,11 +1926,11 @@
       </c>
       <c r="N15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1277</v>
+        <v>1282</v>
       </c>
       <c r="O15">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1233</v>
+        <v>1240</v>
       </c>
       <c r="P15">
         <v>4</v>
@@ -1954,23 +1954,23 @@
       </c>
       <c r="F16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7253821.6632021237</v>
+        <v>11271211.941410139</v>
       </c>
       <c r="G16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7452158.4424874652</v>
+        <v>11477126.439976607</v>
       </c>
       <c r="H16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="I16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>982</v>
+        <v>939</v>
       </c>
       <c r="J16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="L16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -1986,11 +1986,11 @@
       </c>
       <c r="N16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="O16">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="P16">
         <v>3</v>
@@ -2014,19 +2014,19 @@
       </c>
       <c r="F17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7626729.4082962554</v>
+        <v>12072562.882114958</v>
       </c>
       <c r="G17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4874478.6350986613</v>
+        <v>7647194.0438168291</v>
       </c>
       <c r="H17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>639</v>
+        <v>678</v>
       </c>
       <c r="I17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>746</v>
+        <v>696</v>
       </c>
       <c r="J17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="K17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2042,15 +2042,15 @@
       </c>
       <c r="M17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>933</v>
+        <v>950</v>
       </c>
       <c r="O17">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="P17">
         <v>4</v>
@@ -2074,43 +2074,43 @@
       </c>
       <c r="F18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24966540.321500681</v>
+        <v>39301193.021534018</v>
       </c>
       <c r="G18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>26628976.073495127</v>
+        <v>43058855.414458841</v>
       </c>
       <c r="H18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2054</v>
+        <v>2028</v>
       </c>
       <c r="I18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2946</v>
+        <v>2890</v>
       </c>
       <c r="J18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>108</v>
+        <v>167</v>
       </c>
       <c r="N18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2897</v>
+        <v>2819</v>
       </c>
       <c r="O18">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2936</v>
+        <v>2980</v>
       </c>
       <c r="P18">
         <v>5</v>
@@ -2134,23 +2134,23 @@
       </c>
       <c r="F19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13428745.928681612</v>
+        <v>21548491.261211187</v>
       </c>
       <c r="G19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8060394.6620687013</v>
+        <v>8067116.426811154</v>
       </c>
       <c r="H19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1217</v>
+        <v>1139</v>
       </c>
       <c r="I19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -2166,11 +2166,11 @@
       </c>
       <c r="N19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="O19">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1396</v>
+        <v>1375</v>
       </c>
       <c r="P19">
         <v>1</v>
@@ -2194,19 +2194,19 @@
       </c>
       <c r="F20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>25647463.855537627</v>
+        <v>41412282.042329848</v>
       </c>
       <c r="G20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>26874093.702797864</v>
+        <v>42204564.094008639</v>
       </c>
       <c r="H20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2331</v>
+        <v>2306</v>
       </c>
       <c r="I20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2234</v>
+        <v>2202</v>
       </c>
       <c r="J20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2218,19 +2218,19 @@
       </c>
       <c r="L20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2979</v>
+        <v>2982</v>
       </c>
       <c r="O20">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2969</v>
+        <v>2961</v>
       </c>
       <c r="P20">
         <v>8</v>
@@ -2254,19 +2254,19 @@
       </c>
       <c r="F21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>3763683.5108333109</v>
+        <v>6074404.571538738</v>
       </c>
       <c r="G21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4235172.3475251095</v>
+        <v>6415129.7986748964</v>
       </c>
       <c r="H21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>506</v>
+        <v>480</v>
       </c>
       <c r="I21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>639</v>
+        <v>534</v>
       </c>
       <c r="J21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2282,15 +2282,15 @@
       </c>
       <c r="M21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>567</v>
+        <v>554</v>
       </c>
       <c r="O21">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="P21">
         <v>1</v>
@@ -2314,19 +2314,19 @@
       </c>
       <c r="F22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11288354.412634833</v>
+        <v>17223155.15647522</v>
       </c>
       <c r="G22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10789611.241360519</v>
+        <v>17223861.127960525</v>
       </c>
       <c r="H22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1303</v>
+        <v>1286</v>
       </c>
       <c r="I22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1346</v>
+        <v>1282</v>
       </c>
       <c r="J22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="L22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -2346,11 +2346,11 @@
       </c>
       <c r="N22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1690</v>
+        <v>1702</v>
       </c>
       <c r="O22">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1750</v>
+        <v>1731</v>
       </c>
       <c r="P22">
         <v>8</v>
@@ -2374,23 +2374,23 @@
       </c>
       <c r="F23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4860126.4765750067</v>
+        <v>7606090.3029235201</v>
       </c>
       <c r="G23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4592984.7088493519</v>
+        <v>6991287.7517503034</v>
       </c>
       <c r="H23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>805</v>
+        <v>762</v>
       </c>
       <c r="I23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>740</v>
+        <v>792</v>
       </c>
       <c r="J23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -2398,19 +2398,19 @@
       </c>
       <c r="L23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="O23">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="P23">
         <v>1</v>
@@ -2434,19 +2434,19 @@
       </c>
       <c r="F24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5093364.8741606213</v>
+        <v>7771830.7785125766</v>
       </c>
       <c r="G24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5765124.8283889508</v>
+        <v>8945717.278125396</v>
       </c>
       <c r="H24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>585</v>
+        <v>846</v>
       </c>
       <c r="I24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>846</v>
+        <v>731</v>
       </c>
       <c r="J24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="K24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2462,15 +2462,15 @@
       </c>
       <c r="M24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>911</v>
+        <v>902</v>
       </c>
       <c r="O24">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="P24">
         <v>3</v>
@@ -2494,19 +2494,19 @@
       </c>
       <c r="F25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>1440236.1312589699</v>
+        <v>2280396.1807618379</v>
       </c>
       <c r="G25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>1329183.5474891129</v>
+        <v>1898558.2643888111</v>
       </c>
       <c r="H25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="I25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>170</v>
+        <v>2554</v>
       </c>
       <c r="J25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="K25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2526,11 +2526,11 @@
       </c>
       <c r="N25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="O25">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="P25">
         <v>1</v>
@@ -2554,19 +2554,19 @@
       </c>
       <c r="F26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12593024.586868605</v>
+        <v>20642472.561316367</v>
       </c>
       <c r="G26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10525091.880569469</v>
+        <v>16597899.852037497</v>
       </c>
       <c r="H26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1689</v>
+        <v>1477</v>
       </c>
       <c r="I26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1315</v>
+        <v>1372</v>
       </c>
       <c r="J26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2582,15 +2582,15 @@
       </c>
       <c r="M26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1641</v>
+        <v>1654</v>
       </c>
       <c r="O26">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1629</v>
+        <v>1653</v>
       </c>
       <c r="P26">
         <v>1</v>
@@ -2614,19 +2614,19 @@
       </c>
       <c r="F27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9319399.3098883685</v>
+        <v>12615973.394648995</v>
       </c>
       <c r="G27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7945438.205796659</v>
+        <v>12917264.245188372</v>
       </c>
       <c r="H27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>592</v>
+        <v>677</v>
       </c>
       <c r="I27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>624</v>
+        <v>816</v>
       </c>
       <c r="J27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="L27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -2646,11 +2646,11 @@
       </c>
       <c r="N27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>863</v>
+        <v>873</v>
       </c>
       <c r="O27">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="P27">
         <v>1</v>
@@ -2674,19 +2674,19 @@
       </c>
       <c r="F28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9229408.5964249745</v>
+        <v>14123223.678253656</v>
       </c>
       <c r="G28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7682265.5208570464</v>
+        <v>12597981.049125759</v>
       </c>
       <c r="H28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>908</v>
+        <v>762</v>
       </c>
       <c r="I28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>716</v>
+        <v>827</v>
       </c>
       <c r="J28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="O28">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1058</v>
+        <v>1065</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -2734,19 +2734,19 @@
       </c>
       <c r="F29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11544143.05306543</v>
+        <v>17457947.394665383</v>
       </c>
       <c r="G29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11432953.513380121</v>
+        <v>17664552.96019372</v>
       </c>
       <c r="H29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>875</v>
+        <v>908</v>
       </c>
       <c r="I29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>928</v>
+        <v>879</v>
       </c>
       <c r="J29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2762,15 +2762,15 @@
       </c>
       <c r="M29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1115</v>
+        <v>1105</v>
       </c>
       <c r="O29">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1106</v>
+        <v>1111</v>
       </c>
       <c r="P29">
         <v>1</v>
@@ -2794,19 +2794,19 @@
       </c>
       <c r="F30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17016188.039597787</v>
+        <v>26720855.442626528</v>
       </c>
       <c r="G30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16052372.710008221</v>
+        <v>24955672.140388235</v>
       </c>
       <c r="H30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1093</v>
+        <v>1152</v>
       </c>
       <c r="I30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1132</v>
+        <v>1077</v>
       </c>
       <c r="J30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2822,15 +2822,15 @@
       </c>
       <c r="M30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1479</v>
+        <v>1488</v>
       </c>
       <c r="O30">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="P30">
         <v>4</v>
@@ -2854,19 +2854,19 @@
       </c>
       <c r="F31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6712460.6493473453</v>
+        <v>9677957.3193788044</v>
       </c>
       <c r="G31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6447003.3071393995</v>
+        <v>10225048.001245813</v>
       </c>
       <c r="H31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>516</v>
+        <v>487</v>
       </c>
       <c r="I31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>562</v>
+        <v>532</v>
       </c>
       <c r="J31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2886,11 +2886,11 @@
       </c>
       <c r="N31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>690</v>
+        <v>701</v>
       </c>
       <c r="O31">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>689</v>
+        <v>680</v>
       </c>
       <c r="P31">
         <v>3</v>
@@ -2914,27 +2914,27 @@
       </c>
       <c r="F32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20118854.236279029</v>
+        <v>31206440.608555064</v>
       </c>
       <c r="G32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19838539.705524493</v>
+        <v>31195786.901903056</v>
       </c>
       <c r="H32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1616</v>
+        <v>1734</v>
       </c>
       <c r="I32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1556</v>
+        <v>1550</v>
       </c>
       <c r="J32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2942,15 +2942,15 @@
       </c>
       <c r="M32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1975</v>
+        <v>1967</v>
       </c>
       <c r="O32">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1945</v>
+        <v>1937</v>
       </c>
       <c r="P32">
         <v>5</v>
@@ -2974,19 +2974,19 @@
       </c>
       <c r="F33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7210121.5178656941</v>
+        <v>11118207.377145017</v>
       </c>
       <c r="G33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6647967.3857165854</v>
+        <v>10306463.021471065</v>
       </c>
       <c r="H33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>636</v>
+        <v>703</v>
       </c>
       <c r="I33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>666</v>
+        <v>645</v>
       </c>
       <c r="J33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3006,11 +3006,11 @@
       </c>
       <c r="N33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>828</v>
+        <v>839</v>
       </c>
       <c r="O33">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="P33">
         <v>3</v>
@@ -3034,19 +3034,19 @@
       </c>
       <c r="F34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6619601.4259460308</v>
+        <v>9306095.0251620207</v>
       </c>
       <c r="G34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6273615.4145639166</v>
+        <v>9952856.9297330845</v>
       </c>
       <c r="H34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>529</v>
+        <v>418</v>
       </c>
       <c r="I34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>544</v>
+        <v>525</v>
       </c>
       <c r="J34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3066,11 +3066,11 @@
       </c>
       <c r="N34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="O34">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="P34">
         <v>4</v>
@@ -3094,23 +3094,23 @@
       </c>
       <c r="F35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10611923.670867007</v>
+        <v>16122199.413593575</v>
       </c>
       <c r="G35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9719179.3084224835</v>
+        <v>15241628.231743544</v>
       </c>
       <c r="H35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>859</v>
+        <v>798</v>
       </c>
       <c r="I35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>867</v>
+        <v>852</v>
       </c>
       <c r="J35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="L35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3126,11 +3126,11 @@
       </c>
       <c r="N35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1137</v>
+        <v>1131</v>
       </c>
       <c r="O35">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1176</v>
+        <v>1171</v>
       </c>
       <c r="P35">
         <v>13</v>
@@ -3154,19 +3154,19 @@
       </c>
       <c r="F36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9597528.5100794509</v>
+        <v>15445962.516069006</v>
       </c>
       <c r="G36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8790994.6551055964</v>
+        <v>13827542.353898088</v>
       </c>
       <c r="H36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>782</v>
+        <v>959</v>
       </c>
       <c r="I36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>793</v>
+        <v>829</v>
       </c>
       <c r="J36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3178,19 +3178,19 @@
       </c>
       <c r="L36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="N36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1233</v>
+        <v>1200</v>
       </c>
       <c r="O36">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1337</v>
+        <v>1390</v>
       </c>
       <c r="P36">
         <v>4</v>
@@ -3214,23 +3214,23 @@
       </c>
       <c r="F37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15688734.510597564</v>
+        <v>24434713.31977386</v>
       </c>
       <c r="G37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16041935.121685091</v>
+        <v>25291639.249637514</v>
       </c>
       <c r="H37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="I37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1477</v>
+        <v>1498</v>
       </c>
       <c r="J37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -3238,19 +3238,19 @@
       </c>
       <c r="L37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="N37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1882</v>
+        <v>1844</v>
       </c>
       <c r="O37">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2544</v>
+        <v>2522</v>
       </c>
       <c r="P37">
         <v>16</v>
@@ -3274,19 +3274,19 @@
       </c>
       <c r="F38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6470067.6283398336</v>
+        <v>10078150.216247274</v>
       </c>
       <c r="G38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5775032.9829335511</v>
+        <v>9191077.4228783716</v>
       </c>
       <c r="H38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>483</v>
+        <v>462</v>
       </c>
       <c r="I38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>456</v>
+        <v>412</v>
       </c>
       <c r="J38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="L38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3306,11 +3306,11 @@
       </c>
       <c r="N38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="O38">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>611</v>
+        <v>623</v>
       </c>
       <c r="P38">
         <v>3</v>
@@ -3334,43 +3334,43 @@
       </c>
       <c r="F39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17509860.42114738</v>
+        <v>27864970.025229905</v>
       </c>
       <c r="G39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19803000.926697183</v>
+        <v>31007988.562648121</v>
       </c>
       <c r="H39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1802</v>
+        <v>1778</v>
       </c>
       <c r="I39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2006</v>
+        <v>1826</v>
       </c>
       <c r="J39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1968</v>
+        <v>1945</v>
       </c>
       <c r="O39">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2066</v>
+        <v>2057</v>
       </c>
       <c r="P39">
         <v>4</v>
@@ -3394,19 +3394,19 @@
       </c>
       <c r="F40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12266555.037886323</v>
+        <v>19342823.481627457</v>
       </c>
       <c r="G40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12542230.531580009</v>
+        <v>19825792.805345695</v>
       </c>
       <c r="H40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>748</v>
+        <v>731</v>
       </c>
       <c r="I40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>782</v>
+        <v>753</v>
       </c>
       <c r="J40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3422,15 +3422,15 @@
       </c>
       <c r="M40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>859</v>
+        <v>869</v>
       </c>
       <c r="O40">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="P40">
         <v>3</v>
@@ -3454,23 +3454,23 @@
       </c>
       <c r="F41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11423518.706303084</v>
+        <v>17597530.510886051</v>
       </c>
       <c r="G41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5556095.8800142836</v>
+        <v>8542291.4264150988</v>
       </c>
       <c r="H41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>893</v>
+        <v>939</v>
       </c>
       <c r="I41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>462</v>
+        <v>918</v>
       </c>
       <c r="J41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -3486,11 +3486,11 @@
       </c>
       <c r="N41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="O41">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1105</v>
+        <v>1087</v>
       </c>
       <c r="P41">
         <v>4</v>
@@ -3514,19 +3514,19 @@
       </c>
       <c r="F42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10758260.689446844</v>
+        <v>16323094.491309352</v>
       </c>
       <c r="G42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9777702.0178567767</v>
+        <v>15660058.036465179</v>
       </c>
       <c r="H42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>629</v>
+        <v>608</v>
       </c>
       <c r="I42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>663</v>
+        <v>597</v>
       </c>
       <c r="J42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3542,15 +3542,15 @@
       </c>
       <c r="M42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="O42">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>827</v>
+        <v>819</v>
       </c>
       <c r="P42">
         <v>2</v>
@@ -3574,19 +3574,19 @@
       </c>
       <c r="F43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5798980.5858204048</v>
+        <v>9307002.4168394431</v>
       </c>
       <c r="G43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6684286.8881617002</v>
+        <v>9999788.4775667209</v>
       </c>
       <c r="H43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>528</v>
+        <v>547</v>
       </c>
       <c r="I43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>584</v>
+        <v>715</v>
       </c>
       <c r="J43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="M43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="O43">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="P43">
         <v>2</v>
@@ -3634,19 +3634,19 @@
       </c>
       <c r="F44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5562478.9097076738</v>
+        <v>9148288.1945246682</v>
       </c>
       <c r="G44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5538977.3383655511</v>
+        <v>8607899.5225225668</v>
       </c>
       <c r="H44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>705</v>
+        <v>682</v>
       </c>
       <c r="I44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>712</v>
+        <v>696</v>
       </c>
       <c r="J44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3666,11 +3666,11 @@
       </c>
       <c r="N44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="O44">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="P44">
         <v>3</v>
@@ -3694,19 +3694,19 @@
       </c>
       <c r="F45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21737480.949146856</v>
+        <v>33294714.610988211</v>
       </c>
       <c r="G45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17668408.580657668</v>
+        <v>27457832.858950939</v>
       </c>
       <c r="H45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1454</v>
+        <v>1209</v>
       </c>
       <c r="I45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1120</v>
+        <v>1154</v>
       </c>
       <c r="J45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3726,11 +3726,11 @@
       </c>
       <c r="N45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="O45">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="P45">
         <v>4</v>
@@ -3754,19 +3754,19 @@
       </c>
       <c r="F46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9251292.3983292542</v>
+        <v>14593080.011471108</v>
       </c>
       <c r="G46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8311758.9493374256</v>
+        <v>13251593.852497272</v>
       </c>
       <c r="H46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>932</v>
+        <v>925</v>
       </c>
       <c r="I46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>933</v>
+        <v>887</v>
       </c>
       <c r="J46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3782,15 +3782,15 @@
       </c>
       <c r="M46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="O46">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>901</v>
+        <v>917</v>
       </c>
       <c r="P46">
         <v>4</v>
@@ -3814,19 +3814,19 @@
       </c>
       <c r="F47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11821046.27861462</v>
+        <v>18552025.445382949</v>
       </c>
       <c r="G47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14882247.462702388</v>
+        <v>23392753.696536377</v>
       </c>
       <c r="H47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1109</v>
+        <v>946</v>
       </c>
       <c r="I47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1042</v>
+        <v>958</v>
       </c>
       <c r="J47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3842,15 +3842,15 @@
       </c>
       <c r="M47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1319</v>
+        <v>1312</v>
       </c>
       <c r="O47">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1347</v>
+        <v>1362</v>
       </c>
       <c r="P47">
         <v>6</v>
@@ -3874,23 +3874,23 @@
       </c>
       <c r="F48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5591648.4348684251</v>
+        <v>9531210.9429570977</v>
       </c>
       <c r="G48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7909758.2747908533</v>
+        <v>12215200.861652251</v>
       </c>
       <c r="H48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>5</v>
+        <v>369</v>
       </c>
       <c r="I48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>392</v>
+        <v>371</v>
       </c>
       <c r="J48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -3906,11 +3906,11 @@
       </c>
       <c r="N48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="O48">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="P48">
         <v>1</v>
@@ -3934,23 +3934,23 @@
       </c>
       <c r="F49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7608363.9352213563</v>
+        <v>11573023.120887872</v>
       </c>
       <c r="G49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5763787.7664615251</v>
+        <v>8993502.2004245669</v>
       </c>
       <c r="H49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>541</v>
+        <v>325</v>
       </c>
       <c r="I49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="J49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="N49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O49">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -3994,19 +3994,19 @@
       </c>
       <c r="F50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6128628.9357606936</v>
+        <v>9065219.3768147286</v>
       </c>
       <c r="G50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4932361.0217840318</v>
+        <v>7672695.2189010149</v>
       </c>
       <c r="H50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>879</v>
+        <v>339</v>
       </c>
       <c r="I50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="J50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4018,19 +4018,19 @@
       </c>
       <c r="L50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="O50">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="P50">
         <v>4</v>
@@ -4054,23 +4054,23 @@
       </c>
       <c r="F51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12661711.662759928</v>
+        <v>19252439.405621711</v>
       </c>
       <c r="G51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11307100.037220374</v>
+        <v>18272372.933828708</v>
       </c>
       <c r="H51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>932</v>
+        <v>902</v>
       </c>
       <c r="I51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1111</v>
+        <v>921</v>
       </c>
       <c r="J51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -4086,11 +4086,11 @@
       </c>
       <c r="N51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1130</v>
+        <v>1135</v>
       </c>
       <c r="O51">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1112</v>
+        <v>1100</v>
       </c>
       <c r="P51">
         <v>5</v>
@@ -4114,23 +4114,23 @@
       </c>
       <c r="F52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13626568.667371128</v>
+        <v>20212422.982229233</v>
       </c>
       <c r="G52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8397528.3064261712</v>
+        <v>15381123.373330694</v>
       </c>
       <c r="H52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>876</v>
+        <v>820</v>
       </c>
       <c r="I52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>695</v>
+        <v>976</v>
       </c>
       <c r="J52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="L52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4146,11 +4146,11 @@
       </c>
       <c r="N52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>966</v>
+        <v>958</v>
       </c>
       <c r="O52">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>954</v>
+        <v>966</v>
       </c>
       <c r="P52">
         <v>4</v>
@@ -4174,23 +4174,23 @@
       </c>
       <c r="F53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16713879.377090869</v>
+        <v>27521319.010392979</v>
       </c>
       <c r="G53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22573183.750718944</v>
+        <v>34698100.647447377</v>
       </c>
       <c r="H53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1640</v>
+        <v>1619</v>
       </c>
       <c r="I53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1558</v>
+        <v>1483</v>
       </c>
       <c r="J53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="L53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="M53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4206,11 +4206,11 @@
       </c>
       <c r="N53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2212</v>
+        <v>2240</v>
       </c>
       <c r="O53">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2037</v>
+        <v>2055</v>
       </c>
       <c r="P53">
         <v>8</v>
@@ -4234,19 +4234,19 @@
       </c>
       <c r="F54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6379712.6169025553</v>
+        <v>9434418.3837709222</v>
       </c>
       <c r="G54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4781920.9490648406</v>
+        <v>7707113.4334032862</v>
       </c>
       <c r="H54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>532</v>
+        <v>513</v>
       </c>
       <c r="I54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="J54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4266,11 +4266,11 @@
       </c>
       <c r="N54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="O54">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="P54">
         <v>2</v>
@@ -4294,19 +4294,19 @@
       </c>
       <c r="F55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8991956.9474403877</v>
+        <v>13858244.856042204</v>
       </c>
       <c r="G55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8349086.2784085236</v>
+        <v>13874918.72588186</v>
       </c>
       <c r="H55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>658</v>
+        <v>742</v>
       </c>
       <c r="I55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>683</v>
+        <v>761</v>
       </c>
       <c r="J55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4318,19 +4318,19 @@
       </c>
       <c r="L55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="O55">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="P55">
         <v>6</v>
@@ -4354,19 +4354,19 @@
       </c>
       <c r="F56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7657816.4317125622</v>
+        <v>11626890.823241539</v>
       </c>
       <c r="G56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5833873.0823586648</v>
+        <v>8580104.8251491878</v>
       </c>
       <c r="H56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>774</v>
+        <v>622</v>
       </c>
       <c r="I56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>612</v>
+        <v>691</v>
       </c>
       <c r="J56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4382,15 +4382,15 @@
       </c>
       <c r="M56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="O56">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>756</v>
+        <v>747</v>
       </c>
       <c r="P56">
         <v>3</v>
@@ -4414,19 +4414,19 @@
       </c>
       <c r="F57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11863483.749333108</v>
+        <v>18581393.752516262</v>
       </c>
       <c r="G57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11507491.265354032</v>
+        <v>18789590.991508801</v>
       </c>
       <c r="H57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1121</v>
+        <v>1203</v>
       </c>
       <c r="I57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1017</v>
+        <v>928</v>
       </c>
       <c r="J57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4438,19 +4438,19 @@
       </c>
       <c r="L57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="O57">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1100</v>
+        <v>1106</v>
       </c>
       <c r="P57">
         <v>3</v>
@@ -4474,19 +4474,19 @@
       </c>
       <c r="F58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15321494.302633652</v>
+        <v>24051078.007695895</v>
       </c>
       <c r="G58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13532937.95509661</v>
+        <v>22594833.46428778</v>
       </c>
       <c r="H58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1447</v>
+        <v>1415</v>
       </c>
       <c r="I58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1450</v>
+        <v>1341</v>
       </c>
       <c r="J58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="L58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4506,11 +4506,11 @@
       </c>
       <c r="N58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1341</v>
+        <v>1321</v>
       </c>
       <c r="O58">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1358</v>
+        <v>1387</v>
       </c>
       <c r="P58">
         <v>4</v>
@@ -4534,19 +4534,19 @@
       </c>
       <c r="F59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8058811.266136542</v>
+        <v>12751076.307971718</v>
       </c>
       <c r="G59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8013162.8275077576</v>
+        <v>12643538.853697417</v>
       </c>
       <c r="H59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>731</v>
+        <v>715</v>
       </c>
       <c r="I59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="J59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4558,19 +4558,19 @@
       </c>
       <c r="L59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="O59">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="P59">
         <v>3</v>
@@ -4594,19 +4594,19 @@
       </c>
       <c r="F60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9269260.5100010578</v>
+        <v>14810216.222912636</v>
       </c>
       <c r="G60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8893470.3084834833</v>
+        <v>14171503.656152204</v>
       </c>
       <c r="H60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>468</v>
+        <v>502</v>
       </c>
       <c r="I60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="J60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4618,11 +4618,11 @@
       </c>
       <c r="L60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="O60">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="P60">
         <v>8</v>
@@ -4654,23 +4654,23 @@
       </c>
       <c r="F61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18229398.001991931</v>
+        <v>32404512.52197903</v>
       </c>
       <c r="G61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>28428132.615541138</v>
+        <v>45501282.296908557</v>
       </c>
       <c r="H61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1622</v>
+        <v>1606</v>
       </c>
       <c r="I61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1646</v>
+        <v>1907</v>
       </c>
       <c r="J61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="L61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4686,11 +4686,11 @@
       </c>
       <c r="N61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2017</v>
+        <v>2029</v>
       </c>
       <c r="O61">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2011</v>
+        <v>2002</v>
       </c>
       <c r="P61">
         <v>10</v>
@@ -4714,23 +4714,23 @@
       </c>
       <c r="F62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>22361324.738696799</v>
+        <v>33665873.670948178</v>
       </c>
       <c r="G62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19014835.241792019</v>
+        <v>31666643.56758967</v>
       </c>
       <c r="H62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1171</v>
+        <v>1130</v>
       </c>
       <c r="I62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1188</v>
+        <v>1135</v>
       </c>
       <c r="J62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -4738,19 +4738,19 @@
       </c>
       <c r="L62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1611</v>
+        <v>1616</v>
       </c>
       <c r="O62">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1569</v>
+        <v>1572</v>
       </c>
       <c r="P62">
         <v>9</v>
@@ -4774,23 +4774,23 @@
       </c>
       <c r="F63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14473423.450396292</v>
+        <v>21955038.147735532</v>
       </c>
       <c r="G63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13488920.19425902</v>
+        <v>21711289.52854608</v>
       </c>
       <c r="H63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>662</v>
+        <v>726</v>
       </c>
       <c r="I63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>767</v>
+        <v>701</v>
       </c>
       <c r="J63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -4798,19 +4798,19 @@
       </c>
       <c r="L63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O63">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>870</v>
+        <v>889</v>
       </c>
       <c r="P63">
         <v>4</v>
@@ -4834,19 +4834,19 @@
       </c>
       <c r="F64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20091572.499213256</v>
+        <v>31196971.177899417</v>
       </c>
       <c r="G64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21020869.711768493</v>
+        <v>32860185.916051608</v>
       </c>
       <c r="H64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1338</v>
+        <v>1290</v>
       </c>
       <c r="I64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1307</v>
+        <v>1462</v>
       </c>
       <c r="J64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4858,19 +4858,19 @@
       </c>
       <c r="L64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="N64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1899</v>
+        <v>1879</v>
       </c>
       <c r="O64">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2133</v>
+        <v>2097</v>
       </c>
       <c r="P64">
         <v>9</v>
@@ -4894,19 +4894,19 @@
       </c>
       <c r="F65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>1561428.480501238</v>
+        <v>2292405.9875394548</v>
       </c>
       <c r="G65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>2.0709595030000001</v>
+        <v>375644.44752447098</v>
       </c>
       <c r="H65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>254</v>
+        <v>212</v>
       </c>
       <c r="I65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2</v>
+        <v>256</v>
       </c>
       <c r="J65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4926,11 +4926,11 @@
       </c>
       <c r="N65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="O65">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="P65">
         <v>3</v>
@@ -4954,19 +4954,19 @@
       </c>
       <c r="F66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16733881.714438308</v>
+        <v>25616759.463998247</v>
       </c>
       <c r="G66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14199763.569661347</v>
+        <v>23897425.779863752</v>
       </c>
       <c r="H66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1664</v>
+        <v>1689</v>
       </c>
       <c r="I66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1836</v>
+        <v>1868</v>
       </c>
       <c r="J66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4974,23 +4974,23 @@
       </c>
       <c r="K66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1739</v>
+        <v>1745</v>
       </c>
       <c r="O66">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1666</v>
+        <v>1672</v>
       </c>
       <c r="P66">
         <v>6</v>
@@ -5014,19 +5014,19 @@
       </c>
       <c r="F67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6260256.2300493997</v>
+        <v>9992649.6044265609</v>
       </c>
       <c r="G67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7314365.6052390682</v>
+        <v>11330814.204616746</v>
       </c>
       <c r="H67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>548</v>
+        <v>603</v>
       </c>
       <c r="I67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>776</v>
+        <v>603</v>
       </c>
       <c r="J67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="L67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5046,11 +5046,11 @@
       </c>
       <c r="N67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="O67">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>698</v>
+        <v>717</v>
       </c>
       <c r="P67">
         <v>3</v>
@@ -5074,19 +5074,19 @@
       </c>
       <c r="F68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10563149.67928694</v>
+        <v>17067513.194088787</v>
       </c>
       <c r="G68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10158060.965133499</v>
+        <v>15742610.95808477</v>
       </c>
       <c r="H68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>957</v>
+        <v>1182</v>
       </c>
       <c r="I68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>903</v>
+        <v>844</v>
       </c>
       <c r="J68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5098,19 +5098,19 @@
       </c>
       <c r="L68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1396</v>
+        <v>1358</v>
       </c>
       <c r="O68">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1384</v>
+        <v>1370</v>
       </c>
       <c r="P68">
         <v>3</v>
@@ -5134,23 +5134,23 @@
       </c>
       <c r="F69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4879934.5253025386</v>
+        <v>8171514.3711125841</v>
       </c>
       <c r="G69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8403983.9138157759</v>
+        <v>11909259.237161091</v>
       </c>
       <c r="H69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1403</v>
+        <v>1789</v>
       </c>
       <c r="I69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1792</v>
+        <v>1226</v>
       </c>
       <c r="J69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -5166,11 +5166,11 @@
       </c>
       <c r="N69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1412</v>
+        <v>1403</v>
       </c>
       <c r="O69">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1306</v>
+        <v>1303</v>
       </c>
       <c r="P69">
         <v>4</v>
@@ -5194,27 +5194,27 @@
       </c>
       <c r="F70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17404206.181409512</v>
+        <v>28308720.802652378</v>
       </c>
       <c r="G70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19248935.953068849</v>
+        <v>29124730.546930134</v>
       </c>
       <c r="H70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1271</v>
+        <v>1215</v>
       </c>
       <c r="I70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1232</v>
+        <v>1158</v>
       </c>
       <c r="J70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -5222,15 +5222,15 @@
       </c>
       <c r="M70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1719</v>
+        <v>1743</v>
       </c>
       <c r="O70">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1743</v>
+        <v>1728</v>
       </c>
       <c r="P70">
         <v>4</v>
@@ -5254,23 +5254,23 @@
       </c>
       <c r="F71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4029401.0109289791</v>
+        <v>6354765.22670455</v>
       </c>
       <c r="G71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3683325.4120055642</v>
+        <v>5975962.6817722982</v>
       </c>
       <c r="H71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>554</v>
+        <v>511</v>
       </c>
       <c r="I71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="J71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -5282,15 +5282,15 @@
       </c>
       <c r="M71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="O71">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="P71">
         <v>2</v>
@@ -5314,27 +5314,27 @@
       </c>
       <c r="F72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6554960.5533400709</v>
+        <v>9989788.20540924</v>
       </c>
       <c r="G72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5391451.010178484</v>
+        <v>8967153.6823930759</v>
       </c>
       <c r="H72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>805</v>
+        <v>813</v>
       </c>
       <c r="I72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>820</v>
+        <v>920</v>
       </c>
       <c r="J72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -5346,11 +5346,11 @@
       </c>
       <c r="N72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>909</v>
+        <v>897</v>
       </c>
       <c r="O72">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="P72">
         <v>3</v>
@@ -5374,19 +5374,19 @@
       </c>
       <c r="F73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>2689264.6686447202</v>
+        <v>5514504.1095447363</v>
       </c>
       <c r="G73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5569919.9248531396</v>
+        <v>8838437.0925082453</v>
       </c>
       <c r="H73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>564</v>
+        <v>513</v>
       </c>
       <c r="I73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="J73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5406,11 +5406,11 @@
       </c>
       <c r="N73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>679</v>
+        <v>688</v>
       </c>
       <c r="O73">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="P73">
         <v>7</v>
@@ -5434,23 +5434,23 @@
       </c>
       <c r="F74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4337037.0864686901</v>
+        <v>6750615.9754769709</v>
       </c>
       <c r="G74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4940735.7756936448</v>
+        <v>7890411.4936368279</v>
       </c>
       <c r="H74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>906</v>
+        <v>924</v>
       </c>
       <c r="I74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1265</v>
+        <v>698</v>
       </c>
       <c r="J74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="L74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5466,11 +5466,11 @@
       </c>
       <c r="N74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="O74">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="P74">
         <v>2</v>
@@ -5494,23 +5494,23 @@
       </c>
       <c r="F75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5003494.0996635016</v>
+        <v>7653920.359339037</v>
       </c>
       <c r="G75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5325255.3244800083</v>
+        <v>8390126.8830564395</v>
       </c>
       <c r="H75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>387</v>
+        <v>355</v>
       </c>
       <c r="I75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="J75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="L75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5526,11 +5526,11 @@
       </c>
       <c r="N75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="O75">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="P75">
         <v>1</v>
@@ -5554,23 +5554,23 @@
       </c>
       <c r="F76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14599105.463165892</v>
+        <v>21521164.578006919</v>
       </c>
       <c r="G76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13331666.494566012</v>
+        <v>20746372.803316668</v>
       </c>
       <c r="H76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>834</v>
+        <v>691</v>
       </c>
       <c r="I76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>730</v>
+        <v>672</v>
       </c>
       <c r="J76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -5578,19 +5578,19 @@
       </c>
       <c r="L76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="O76">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>969</v>
+        <v>955</v>
       </c>
       <c r="P76">
         <v>4</v>
@@ -5614,19 +5614,19 @@
       </c>
       <c r="F77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8574263.9764997829</v>
+        <v>13363157.032803241</v>
       </c>
       <c r="G77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8108231.6625237344</v>
+        <v>13054902.089641485</v>
       </c>
       <c r="H77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>761</v>
+        <v>814</v>
       </c>
       <c r="I77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>711</v>
+        <v>741</v>
       </c>
       <c r="J77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5642,15 +5642,15 @@
       </c>
       <c r="M77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="O77">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="P77">
         <v>2</v>
@@ -5674,15 +5674,15 @@
       </c>
       <c r="F78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6657424.7365432037</v>
+        <v>10535619.815227035</v>
       </c>
       <c r="G78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7256682.7153262254</v>
+        <v>11489184.409651188</v>
       </c>
       <c r="H78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>939</v>
+        <v>863</v>
       </c>
       <c r="I78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="K78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -5706,11 +5706,11 @@
       </c>
       <c r="N78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>907</v>
+        <v>922</v>
       </c>
       <c r="O78">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>960</v>
+        <v>972</v>
       </c>
       <c r="P78">
         <v>3</v>
@@ -5734,19 +5734,19 @@
       </c>
       <c r="F79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7511852.493724742</v>
+        <v>12029136.598088751</v>
       </c>
       <c r="G79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4702680.6416437216</v>
+        <v>8436359.6429892965</v>
       </c>
       <c r="H79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>842</v>
+        <v>816</v>
       </c>
       <c r="I79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>20</v>
+        <v>688</v>
       </c>
       <c r="J79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5758,19 +5758,19 @@
       </c>
       <c r="L79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1021</v>
+        <v>1012</v>
       </c>
       <c r="O79">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>997</v>
+        <v>1006</v>
       </c>
       <c r="P79">
         <v>3</v>
@@ -5794,19 +5794,19 @@
       </c>
       <c r="F80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7143614.790428766</v>
+        <v>12058816.101821585</v>
       </c>
       <c r="G80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7522930.9770057639</v>
+        <v>12570353.635213269</v>
       </c>
       <c r="H80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>697</v>
+        <v>723</v>
       </c>
       <c r="I80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>742</v>
+        <v>831</v>
       </c>
       <c r="J80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5822,15 +5822,15 @@
       </c>
       <c r="M80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="O80">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>730</v>
+        <v>744</v>
       </c>
       <c r="P80">
         <v>3</v>
@@ -5854,19 +5854,19 @@
       </c>
       <c r="F81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4147371.3965030778</v>
+        <v>6345447.8126080902</v>
       </c>
       <c r="G81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4156463.0287198988</v>
+        <v>6485541.9481432578</v>
       </c>
       <c r="H81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>609</v>
+        <v>686</v>
       </c>
       <c r="I81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>764</v>
+        <v>575</v>
       </c>
       <c r="J81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5886,11 +5886,11 @@
       </c>
       <c r="N81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="O81">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="P81">
         <v>1</v>
@@ -5914,19 +5914,19 @@
       </c>
       <c r="F82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15155946.089206984</v>
+        <v>24330358.382188115</v>
       </c>
       <c r="G82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15539415.573069196</v>
+        <v>24951429.425259337</v>
       </c>
       <c r="H82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1330</v>
+        <v>1262</v>
       </c>
       <c r="I82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1218</v>
+        <v>1231</v>
       </c>
       <c r="J82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="L82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5946,11 +5946,11 @@
       </c>
       <c r="N82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="O82">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1728</v>
+        <v>1749</v>
       </c>
       <c r="P82">
         <v>1</v>
@@ -5974,19 +5974,19 @@
       </c>
       <c r="F83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4716414.244273073</v>
+        <v>6599894.3574415911</v>
       </c>
       <c r="G83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3439065.9601564072</v>
+        <v>5256040.7605468342</v>
       </c>
       <c r="H83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>755</v>
+        <v>631</v>
       </c>
       <c r="I83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>862</v>
+        <v>668</v>
       </c>
       <c r="J83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6006,11 +6006,11 @@
       </c>
       <c r="N83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>688</v>
+        <v>664</v>
       </c>
       <c r="O83">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="P83">
         <v>2</v>
@@ -6034,19 +6034,19 @@
       </c>
       <c r="F84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8023492.5817246111</v>
+        <v>11603173.468591984</v>
       </c>
       <c r="G84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7587961.4134114794</v>
+        <v>12085662.536187533</v>
       </c>
       <c r="H84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>570</v>
+        <v>494</v>
       </c>
       <c r="I84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="J84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="L84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -6066,11 +6066,11 @@
       </c>
       <c r="N84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>629</v>
+        <v>616</v>
       </c>
       <c r="O84">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>601</v>
+        <v>620</v>
       </c>
       <c r="P84">
         <v>7</v>
@@ -6094,19 +6094,19 @@
       </c>
       <c r="F85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>2442094.5526837292</v>
+        <v>3559231.8746322528</v>
       </c>
       <c r="G85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>2185891.8143150499</v>
+        <v>3096779.6955845412</v>
       </c>
       <c r="H85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>445</v>
+        <v>304</v>
       </c>
       <c r="I85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6122,15 +6122,15 @@
       </c>
       <c r="M85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="O85">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="P85">
         <v>2</v>
@@ -6163,43 +6163,43 @@
       <c r="A3" s="11"/>
       <c r="B3" s="11">
         <f t="shared" ref="B3:K3" si="0">SUBTOTAL(9,B6:B90)</f>
-        <v>84161</v>
+        <v>83982</v>
       </c>
       <c r="C3" s="11">
         <f t="shared" si="0"/>
-        <v>336</v>
+        <v>408</v>
       </c>
       <c r="D3" s="11">
         <f t="shared" si="0"/>
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E3" s="11">
         <f t="shared" si="0"/>
-        <v>70915</v>
+        <v>70176</v>
       </c>
       <c r="F3" s="11">
         <f t="shared" si="0"/>
-        <v>782491558.51555836</v>
+        <v>1219019592.7645988</v>
       </c>
       <c r="G3" s="11">
         <f t="shared" si="0"/>
-        <v>84583</v>
+        <v>84684</v>
       </c>
       <c r="H3" s="11">
         <f t="shared" si="0"/>
-        <v>385</v>
+        <v>622</v>
       </c>
       <c r="I3" s="11">
         <f t="shared" si="0"/>
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="J3" s="11">
         <f t="shared" si="0"/>
-        <v>68595</v>
+        <v>71951</v>
       </c>
       <c r="K3" s="11">
         <f t="shared" si="0"/>
-        <v>758337594.71692479</v>
+        <v>1196500500.4514337</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -6258,23 +6258,23 @@
       <c r="A6" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="B6" s="1">
-        <v>413</v>
-      </c>
-      <c r="C6" s="1">
-        <v>2</v>
-      </c>
-      <c r="D6" s="1">
-        <v>2</v>
-      </c>
-      <c r="E6" s="1">
-        <v>400</v>
+      <c r="B6" s="10">
+        <v>414</v>
+      </c>
+      <c r="C6" s="10">
+        <v>3</v>
+      </c>
+      <c r="D6" s="10">
+        <v>2</v>
+      </c>
+      <c r="E6" s="10">
+        <v>620</v>
       </c>
       <c r="F6" s="10">
-        <v>3767640.1674616369</v>
+        <v>6059382.1473084744</v>
       </c>
       <c r="G6" s="10">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="H6" s="10">
         <v>0</v>
@@ -6283,33 +6283,33 @@
         <v>2</v>
       </c>
       <c r="J6" s="10">
-        <v>337</v>
+        <v>379</v>
       </c>
       <c r="K6" s="10">
-        <v>3378902.3358840779</v>
+        <v>5415574.0184972491</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="B7" s="1">
-        <v>691</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1</v>
-      </c>
-      <c r="D7" s="1">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1">
-        <v>547</v>
+      <c r="B7" s="10">
+        <v>686</v>
+      </c>
+      <c r="C7" s="10">
+        <v>1</v>
+      </c>
+      <c r="D7" s="10">
+        <v>1</v>
+      </c>
+      <c r="E7" s="10">
+        <v>614</v>
       </c>
       <c r="F7" s="10">
-        <v>4755985.7453720355</v>
+        <v>7288506.4151363429</v>
       </c>
       <c r="G7" s="10">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="H7" s="10">
         <v>1</v>
@@ -6318,103 +6318,103 @@
         <v>2</v>
       </c>
       <c r="J7" s="10">
-        <v>610</v>
+        <v>497</v>
       </c>
       <c r="K7" s="10">
-        <v>4198139.0504805734</v>
+        <v>6653085.5256644776</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B8" s="1">
-        <v>690</v>
-      </c>
-      <c r="C8" s="1">
-        <v>1</v>
-      </c>
-      <c r="D8" s="1">
+      <c r="B8" s="10">
+        <v>686</v>
+      </c>
+      <c r="C8" s="10">
+        <v>2</v>
+      </c>
+      <c r="D8" s="10">
+        <v>2</v>
+      </c>
+      <c r="E8" s="10">
+        <v>667</v>
+      </c>
+      <c r="F8" s="10">
+        <v>6371310.9355353834</v>
+      </c>
+      <c r="G8" s="10">
+        <v>734</v>
+      </c>
+      <c r="H8" s="10">
         <v>3</v>
       </c>
-      <c r="E8" s="1">
-        <v>566</v>
-      </c>
-      <c r="F8" s="10">
-        <v>4115736.9093229892</v>
-      </c>
-      <c r="G8" s="10">
-        <v>732</v>
-      </c>
-      <c r="H8" s="10">
-        <v>2</v>
-      </c>
       <c r="I8" s="10">
         <v>1</v>
       </c>
       <c r="J8" s="10">
-        <v>42</v>
+        <v>745</v>
       </c>
       <c r="K8" s="10">
-        <v>4831243.1255528908</v>
+        <v>6613502.6668428723</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="B9" s="1">
-        <v>1203</v>
-      </c>
-      <c r="C9" s="1">
-        <v>2</v>
-      </c>
-      <c r="D9" s="1">
+      <c r="B9" s="10">
+        <v>1197</v>
+      </c>
+      <c r="C9" s="10">
+        <v>2</v>
+      </c>
+      <c r="D9" s="10">
+        <v>2</v>
+      </c>
+      <c r="E9" s="10">
+        <v>760</v>
+      </c>
+      <c r="F9" s="10">
+        <v>14068595.525211383</v>
+      </c>
+      <c r="G9" s="10">
+        <v>1207</v>
+      </c>
+      <c r="H9" s="10">
+        <v>2</v>
+      </c>
+      <c r="I9" s="10">
         <v>3</v>
       </c>
-      <c r="E9" s="1">
-        <v>989</v>
-      </c>
-      <c r="F9" s="10">
-        <v>9315606.1279473379</v>
-      </c>
-      <c r="G9" s="10">
-        <v>1218</v>
-      </c>
-      <c r="H9" s="10">
-        <v>1</v>
-      </c>
-      <c r="I9" s="10">
-        <v>4</v>
-      </c>
       <c r="J9" s="10">
-        <v>1033</v>
+        <v>998</v>
       </c>
       <c r="K9" s="10">
-        <v>8927501.3209277317</v>
+        <v>13913394.68100726</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="B10" s="1">
-        <v>395</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1</v>
-      </c>
-      <c r="D10" s="1">
-        <v>0</v>
-      </c>
-      <c r="E10" s="1">
-        <v>320</v>
+      <c r="B10" s="10">
+        <v>394</v>
+      </c>
+      <c r="C10" s="10">
+        <v>1</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0</v>
+      </c>
+      <c r="E10" s="10">
+        <v>315</v>
       </c>
       <c r="F10" s="10">
-        <v>3622509.6095191082</v>
+        <v>5121540.0843401868</v>
       </c>
       <c r="G10" s="10">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="H10" s="10">
         <v>1</v>
@@ -6423,33 +6423,33 @@
         <v>1</v>
       </c>
       <c r="J10" s="10">
-        <v>353</v>
+        <v>419</v>
       </c>
       <c r="K10" s="10">
-        <v>3433165.5757586341</v>
+        <v>5839432.1316437609</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B11" s="1">
-        <v>368</v>
-      </c>
-      <c r="C11" s="1">
-        <v>1</v>
-      </c>
-      <c r="D11" s="1">
-        <v>2</v>
-      </c>
-      <c r="E11" s="1">
-        <v>345</v>
+      <c r="B11" s="10">
+        <v>374</v>
+      </c>
+      <c r="C11" s="10">
+        <v>2</v>
+      </c>
+      <c r="D11" s="10">
+        <v>2</v>
+      </c>
+      <c r="E11" s="10">
+        <v>431</v>
       </c>
       <c r="F11" s="10">
-        <v>3453641.8844623081</v>
+        <v>5394052.5405044062</v>
       </c>
       <c r="G11" s="10">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="H11" s="10">
         <v>2</v>
@@ -6458,33 +6458,33 @@
         <v>2</v>
       </c>
       <c r="J11" s="10">
-        <v>318</v>
+        <v>301</v>
       </c>
       <c r="K11" s="10">
-        <v>3315695.6946051032</v>
+        <v>5345165.618633477</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="10">
+        <v>608</v>
+      </c>
+      <c r="C12" s="10">
+        <v>0</v>
+      </c>
+      <c r="D12" s="10">
+        <v>1</v>
+      </c>
+      <c r="E12" s="10">
+        <v>1167</v>
+      </c>
+      <c r="F12" s="10">
+        <v>6272003.9840085637</v>
+      </c>
+      <c r="G12" s="10">
         <v>592</v>
-      </c>
-      <c r="C12" s="1">
-        <v>0</v>
-      </c>
-      <c r="D12" s="1">
-        <v>0</v>
-      </c>
-      <c r="E12" s="1">
-        <v>515</v>
-      </c>
-      <c r="F12" s="10">
-        <v>4149554.9330451461</v>
-      </c>
-      <c r="G12" s="10">
-        <v>596</v>
       </c>
       <c r="H12" s="10">
         <v>0</v>
@@ -6493,33 +6493,33 @@
         <v>5</v>
       </c>
       <c r="J12" s="10">
-        <v>558</v>
+        <v>483</v>
       </c>
       <c r="K12" s="10">
-        <v>3763040.3506287369</v>
+        <v>5990321.0092403321</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="10">
         <v>162</v>
       </c>
-      <c r="C13" s="1">
-        <v>0</v>
-      </c>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1">
-        <v>124</v>
+      <c r="C13" s="10">
+        <v>0</v>
+      </c>
+      <c r="D13" s="10">
+        <v>1</v>
+      </c>
+      <c r="E13" s="10">
+        <v>138</v>
       </c>
       <c r="F13" s="10">
-        <v>1692945.1848517051</v>
+        <v>2610227.0540075419</v>
       </c>
       <c r="G13" s="10">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H13" s="10">
         <v>0</v>
@@ -6528,33 +6528,33 @@
         <v>0</v>
       </c>
       <c r="J13" s="10">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="K13" s="10">
-        <v>1873870.2528251619</v>
+        <v>2744967.7764228848</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="B14" s="1">
-        <v>201</v>
-      </c>
-      <c r="C14" s="1">
-        <v>1</v>
-      </c>
-      <c r="D14" s="1">
-        <v>0</v>
-      </c>
-      <c r="E14" s="1">
-        <v>159</v>
+      <c r="B14" s="10">
+        <v>197</v>
+      </c>
+      <c r="C14" s="10">
+        <v>1</v>
+      </c>
+      <c r="D14" s="10">
+        <v>0</v>
+      </c>
+      <c r="E14" s="10">
+        <v>196</v>
       </c>
       <c r="F14" s="10">
-        <v>1943111.7270830791</v>
+        <v>2761713.1927333758</v>
       </c>
       <c r="G14" s="10">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H14" s="10">
         <v>0</v>
@@ -6563,33 +6563,33 @@
         <v>1</v>
       </c>
       <c r="J14" s="10">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K14" s="10">
-        <v>22.486592934000001</v>
+        <v>267968.35746859002</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="B15" s="1">
-        <v>353</v>
-      </c>
-      <c r="C15" s="1">
-        <v>0</v>
-      </c>
-      <c r="D15" s="1">
-        <v>0</v>
-      </c>
-      <c r="E15" s="1">
-        <v>326</v>
+      <c r="B15" s="10">
+        <v>349</v>
+      </c>
+      <c r="C15" s="10">
+        <v>0</v>
+      </c>
+      <c r="D15" s="10">
+        <v>0</v>
+      </c>
+      <c r="E15" s="10">
+        <v>363</v>
       </c>
       <c r="F15" s="10">
-        <v>2925789.0628380021</v>
+        <v>4379782.4858754724</v>
       </c>
       <c r="G15" s="10">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="H15" s="10">
         <v>1</v>
@@ -6598,30 +6598,30 @@
         <v>1</v>
       </c>
       <c r="J15" s="10">
-        <v>487</v>
+        <v>542</v>
       </c>
       <c r="K15" s="10">
-        <v>3816371.4646472102</v>
+        <v>5948859.3354461109</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="B16" s="1">
-        <v>216</v>
-      </c>
-      <c r="C16" s="1">
-        <v>0</v>
-      </c>
-      <c r="D16" s="1">
-        <v>1</v>
-      </c>
-      <c r="E16" s="1">
-        <v>257</v>
+      <c r="B16" s="10">
+        <v>208</v>
+      </c>
+      <c r="C16" s="10">
+        <v>0</v>
+      </c>
+      <c r="D16" s="10">
+        <v>1</v>
+      </c>
+      <c r="E16" s="10">
+        <v>212</v>
       </c>
       <c r="F16" s="10">
-        <v>1301883.6042596891</v>
+        <v>1995774.4805199029</v>
       </c>
       <c r="G16" s="10">
         <v>198</v>
@@ -6633,30 +6633,30 @@
         <v>2</v>
       </c>
       <c r="J16" s="10">
-        <v>277</v>
+        <v>578</v>
       </c>
       <c r="K16" s="10">
-        <v>1720402.2001648659</v>
+        <v>2625962.4150365731</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="B17" s="1">
-        <v>262</v>
-      </c>
-      <c r="C17" s="1">
+      <c r="B17" s="10">
+        <v>253</v>
+      </c>
+      <c r="C17" s="10">
         <v>5</v>
       </c>
-      <c r="D17" s="1">
-        <v>0</v>
-      </c>
-      <c r="E17" s="1">
-        <v>226</v>
+      <c r="D17" s="10">
+        <v>0</v>
+      </c>
+      <c r="E17" s="10">
+        <v>208</v>
       </c>
       <c r="F17" s="10">
-        <v>1833456.113912377</v>
+        <v>2676274.3626946318</v>
       </c>
       <c r="G17" s="10">
         <v>241</v>
@@ -6665,106 +6665,106 @@
         <v>0</v>
       </c>
       <c r="I17" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="10">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="K17" s="10">
-        <v>1807666.7458902949</v>
+        <v>2935154.1349404189</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="1">
-        <v>1471</v>
-      </c>
-      <c r="C18" s="1">
-        <v>0</v>
-      </c>
-      <c r="D18" s="1">
+      <c r="B18" s="10">
+        <v>1454</v>
+      </c>
+      <c r="C18" s="10">
+        <v>0</v>
+      </c>
+      <c r="D18" s="10">
+        <v>2</v>
+      </c>
+      <c r="E18" s="10">
+        <v>121</v>
+      </c>
+      <c r="F18" s="10">
+        <v>7510668.6871368838</v>
+      </c>
+      <c r="G18" s="10">
+        <v>1427</v>
+      </c>
+      <c r="H18" s="10">
+        <v>2</v>
+      </c>
+      <c r="I18" s="10">
         <v>3</v>
       </c>
-      <c r="E18" s="1">
-        <v>905</v>
-      </c>
-      <c r="F18" s="10">
-        <v>6732074.4633739255</v>
-      </c>
-      <c r="G18" s="10">
-        <v>1442</v>
-      </c>
-      <c r="H18" s="10">
-        <v>2</v>
-      </c>
-      <c r="I18" s="10">
-        <v>2</v>
-      </c>
       <c r="J18" s="10">
-        <v>161</v>
+        <v>802</v>
       </c>
       <c r="K18" s="10">
-        <v>5812917.9415709646</v>
+        <v>8711554.6449297052</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="1">
-        <v>1277</v>
-      </c>
-      <c r="C19" s="1">
-        <v>0</v>
-      </c>
-      <c r="D19" s="1">
-        <v>2</v>
-      </c>
-      <c r="E19" s="1">
-        <v>937</v>
+      <c r="B19" s="10">
+        <v>1282</v>
+      </c>
+      <c r="C19" s="10">
+        <v>0</v>
+      </c>
+      <c r="D19" s="10">
+        <v>2</v>
+      </c>
+      <c r="E19" s="10">
+        <v>1045</v>
       </c>
       <c r="F19" s="10">
-        <v>10956297.987773804</v>
+        <v>18218164.868068825</v>
       </c>
       <c r="G19" s="10">
-        <v>1233</v>
+        <v>1240</v>
       </c>
       <c r="H19" s="10">
         <v>1</v>
       </c>
       <c r="I19" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J19" s="10">
-        <v>948</v>
+        <v>881</v>
       </c>
       <c r="K19" s="10">
-        <v>12242361.641453536</v>
+        <v>19264893.816357184</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="1">
-        <v>1030</v>
-      </c>
-      <c r="C20" s="1">
-        <v>0</v>
-      </c>
-      <c r="D20" s="1">
-        <v>4</v>
-      </c>
-      <c r="E20" s="1">
-        <v>911</v>
+      <c r="B20" s="10">
+        <v>1031</v>
+      </c>
+      <c r="C20" s="10">
+        <v>1</v>
+      </c>
+      <c r="D20" s="10">
+        <v>3</v>
+      </c>
+      <c r="E20" s="10">
+        <v>920</v>
       </c>
       <c r="F20" s="10">
-        <v>7253821.6632021237</v>
+        <v>11271211.941410139</v>
       </c>
       <c r="G20" s="10">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="H20" s="10">
         <v>1</v>
@@ -6773,103 +6773,103 @@
         <v>5</v>
       </c>
       <c r="J20" s="10">
-        <v>982</v>
+        <v>939</v>
       </c>
       <c r="K20" s="10">
-        <v>7452158.4424874652</v>
+        <v>11477126.439976607</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="1">
-        <v>933</v>
-      </c>
-      <c r="C21" s="1">
-        <v>0</v>
-      </c>
-      <c r="D21" s="1">
-        <v>2</v>
-      </c>
-      <c r="E21" s="1">
-        <v>639</v>
+      <c r="B21" s="10">
+        <v>950</v>
+      </c>
+      <c r="C21" s="10">
+        <v>0</v>
+      </c>
+      <c r="D21" s="10">
+        <v>2</v>
+      </c>
+      <c r="E21" s="10">
+        <v>678</v>
       </c>
       <c r="F21" s="10">
-        <v>7626729.4082962554</v>
+        <v>12072562.882114958</v>
       </c>
       <c r="G21" s="10">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="H21" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J21" s="10">
-        <v>746</v>
+        <v>696</v>
       </c>
       <c r="K21" s="10">
-        <v>4874478.6350986613</v>
+        <v>7647194.0438168291</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B22" s="1">
-        <v>2897</v>
-      </c>
-      <c r="C22" s="1">
-        <v>107</v>
-      </c>
-      <c r="D22" s="1">
-        <v>11</v>
-      </c>
-      <c r="E22" s="1">
-        <v>2054</v>
+      <c r="B22" s="10">
+        <v>2819</v>
+      </c>
+      <c r="C22" s="10">
+        <v>111</v>
+      </c>
+      <c r="D22" s="10">
+        <v>10</v>
+      </c>
+      <c r="E22" s="10">
+        <v>2028</v>
       </c>
       <c r="F22" s="10">
-        <v>24966540.321500681</v>
+        <v>39301193.021534018</v>
       </c>
       <c r="G22" s="10">
-        <v>2936</v>
+        <v>2980</v>
       </c>
       <c r="H22" s="10">
-        <v>108</v>
+        <v>167</v>
       </c>
       <c r="I22" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J22" s="10">
-        <v>2946</v>
+        <v>2890</v>
       </c>
       <c r="K22" s="10">
-        <v>26628976.073495127</v>
+        <v>43058855.414458841</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="1">
-        <v>1447</v>
-      </c>
-      <c r="C23" s="1">
-        <v>0</v>
-      </c>
-      <c r="D23" s="1">
-        <v>3</v>
-      </c>
-      <c r="E23" s="1">
-        <v>1217</v>
+      <c r="B23" s="10">
+        <v>1449</v>
+      </c>
+      <c r="C23" s="10">
+        <v>0</v>
+      </c>
+      <c r="D23" s="10">
+        <v>2</v>
+      </c>
+      <c r="E23" s="10">
+        <v>1139</v>
       </c>
       <c r="F23" s="10">
-        <v>13428745.928681612</v>
+        <v>21548491.261211187</v>
       </c>
       <c r="G23" s="10">
-        <v>1396</v>
+        <v>1375</v>
       </c>
       <c r="H23" s="10">
         <v>2</v>
@@ -6878,103 +6878,103 @@
         <v>1</v>
       </c>
       <c r="J23" s="10">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="K23" s="10">
-        <v>8060394.6620687013</v>
+        <v>8067116.426811154</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B24" s="1">
-        <v>2979</v>
-      </c>
-      <c r="C24" s="1">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1">
+      <c r="B24" s="10">
+        <v>2982</v>
+      </c>
+      <c r="C24" s="10">
+        <v>6</v>
+      </c>
+      <c r="D24" s="10">
         <v>12</v>
       </c>
-      <c r="E24" s="1">
-        <v>2331</v>
+      <c r="E24" s="10">
+        <v>2306</v>
       </c>
       <c r="F24" s="10">
-        <v>25647463.855537627</v>
+        <v>41412282.042329848</v>
       </c>
       <c r="G24" s="10">
-        <v>2969</v>
+        <v>2961</v>
       </c>
       <c r="H24" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I24" s="10">
         <v>10</v>
       </c>
       <c r="J24" s="10">
-        <v>2234</v>
+        <v>2202</v>
       </c>
       <c r="K24" s="10">
-        <v>26874093.702797864</v>
+        <v>42204564.094008639</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B25" s="1">
-        <v>567</v>
-      </c>
-      <c r="C25" s="1">
+      <c r="B25" s="10">
+        <v>554</v>
+      </c>
+      <c r="C25" s="10">
         <v>3</v>
       </c>
-      <c r="D25" s="1">
-        <v>1</v>
-      </c>
-      <c r="E25" s="1">
-        <v>506</v>
+      <c r="D25" s="10">
+        <v>1</v>
+      </c>
+      <c r="E25" s="10">
+        <v>480</v>
       </c>
       <c r="F25" s="10">
-        <v>3763683.5108333109</v>
+        <v>6074404.571538738</v>
       </c>
       <c r="G25" s="10">
+        <v>532</v>
+      </c>
+      <c r="H25" s="10">
+        <v>4</v>
+      </c>
+      <c r="I25" s="10">
+        <v>1</v>
+      </c>
+      <c r="J25" s="10">
         <v>534</v>
       </c>
-      <c r="H25" s="10">
-        <v>1</v>
-      </c>
-      <c r="I25" s="10">
-        <v>1</v>
-      </c>
-      <c r="J25" s="10">
-        <v>639</v>
-      </c>
       <c r="K25" s="10">
-        <v>4235172.3475251095</v>
+        <v>6415129.7986748964</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="B26" s="1">
-        <v>1690</v>
-      </c>
-      <c r="C26" s="1">
-        <v>4</v>
-      </c>
-      <c r="D26" s="1">
-        <v>1</v>
-      </c>
-      <c r="E26" s="1">
-        <v>1303</v>
+      <c r="B26" s="10">
+        <v>1702</v>
+      </c>
+      <c r="C26" s="10">
+        <v>6</v>
+      </c>
+      <c r="D26" s="10">
+        <v>1</v>
+      </c>
+      <c r="E26" s="10">
+        <v>1286</v>
       </c>
       <c r="F26" s="10">
-        <v>11288354.412634833</v>
+        <v>17223155.15647522</v>
       </c>
       <c r="G26" s="10">
-        <v>1750</v>
+        <v>1731</v>
       </c>
       <c r="H26" s="10">
         <v>7</v>
@@ -6983,173 +6983,173 @@
         <v>1</v>
       </c>
       <c r="J26" s="10">
-        <v>1346</v>
+        <v>1282</v>
       </c>
       <c r="K26" s="10">
-        <v>10789611.241360519</v>
+        <v>17223861.127960525</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="B27" s="1">
-        <v>868</v>
-      </c>
-      <c r="C27" s="1">
-        <v>2</v>
-      </c>
-      <c r="D27" s="1">
-        <v>0</v>
-      </c>
-      <c r="E27" s="1">
-        <v>805</v>
+      <c r="B27" s="10">
+        <v>870</v>
+      </c>
+      <c r="C27" s="10">
+        <v>4</v>
+      </c>
+      <c r="D27" s="10">
+        <v>1</v>
+      </c>
+      <c r="E27" s="10">
+        <v>762</v>
       </c>
       <c r="F27" s="10">
-        <v>4860126.4765750067</v>
+        <v>7606090.3029235201</v>
       </c>
       <c r="G27" s="10">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="H27" s="10">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I27" s="10">
         <v>1</v>
       </c>
       <c r="J27" s="10">
-        <v>740</v>
+        <v>792</v>
       </c>
       <c r="K27" s="10">
-        <v>4592984.7088493519</v>
+        <v>6991287.7517503034</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="1">
-        <v>911</v>
-      </c>
-      <c r="C28" s="1">
-        <v>1</v>
-      </c>
-      <c r="D28" s="1">
-        <v>1</v>
-      </c>
-      <c r="E28" s="1">
-        <v>585</v>
+      <c r="B28" s="10">
+        <v>902</v>
+      </c>
+      <c r="C28" s="10">
+        <v>1</v>
+      </c>
+      <c r="D28" s="10">
+        <v>1</v>
+      </c>
+      <c r="E28" s="10">
+        <v>846</v>
       </c>
       <c r="F28" s="10">
-        <v>5093364.8741606213</v>
+        <v>7771830.7785125766</v>
       </c>
       <c r="G28" s="10">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="H28" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I28" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" s="10">
-        <v>846</v>
+        <v>731</v>
       </c>
       <c r="K28" s="10">
-        <v>5765124.8283889508</v>
+        <v>8945717.278125396</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="10">
+        <v>237</v>
+      </c>
+      <c r="C29" s="10">
+        <v>1</v>
+      </c>
+      <c r="D29" s="10">
+        <v>0</v>
+      </c>
+      <c r="E29" s="10">
+        <v>176</v>
+      </c>
+      <c r="F29" s="10">
+        <v>2280396.1807618379</v>
+      </c>
+      <c r="G29" s="10">
         <v>232</v>
       </c>
-      <c r="C29" s="1">
-        <v>1</v>
-      </c>
-      <c r="D29" s="1">
-        <v>0</v>
-      </c>
-      <c r="E29" s="1">
-        <v>197</v>
-      </c>
-      <c r="F29" s="10">
-        <v>1440236.1312589699</v>
-      </c>
-      <c r="G29" s="10">
-        <v>235</v>
-      </c>
       <c r="H29" s="10">
         <v>1</v>
       </c>
       <c r="I29" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J29" s="10">
-        <v>170</v>
+        <v>2554</v>
       </c>
       <c r="K29" s="10">
-        <v>1329183.5474891129</v>
+        <v>1898558.2643888111</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B30" s="1">
-        <v>1641</v>
-      </c>
-      <c r="C30" s="1">
-        <v>1</v>
-      </c>
-      <c r="D30" s="1">
+      <c r="B30" s="10">
+        <v>1654</v>
+      </c>
+      <c r="C30" s="10">
+        <v>1</v>
+      </c>
+      <c r="D30" s="10">
         <v>5</v>
       </c>
-      <c r="E30" s="1">
-        <v>1689</v>
+      <c r="E30" s="10">
+        <v>1477</v>
       </c>
       <c r="F30" s="10">
-        <v>12593024.586868605</v>
+        <v>20642472.561316367</v>
       </c>
       <c r="G30" s="10">
-        <v>1629</v>
+        <v>1653</v>
       </c>
       <c r="H30" s="10">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I30" s="10">
         <v>6</v>
       </c>
       <c r="J30" s="10">
-        <v>1315</v>
+        <v>1372</v>
       </c>
       <c r="K30" s="10">
-        <v>10525091.880569469</v>
+        <v>16597899.852037497</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B31" s="1">
-        <v>863</v>
-      </c>
-      <c r="C31" s="1">
-        <v>0</v>
-      </c>
-      <c r="D31" s="1">
-        <v>1</v>
-      </c>
-      <c r="E31" s="1">
-        <v>592</v>
+      <c r="B31" s="10">
+        <v>873</v>
+      </c>
+      <c r="C31" s="10">
+        <v>1</v>
+      </c>
+      <c r="D31" s="10">
+        <v>1</v>
+      </c>
+      <c r="E31" s="10">
+        <v>677</v>
       </c>
       <c r="F31" s="10">
-        <v>9319399.3098883685</v>
+        <v>12615973.394648995</v>
       </c>
       <c r="G31" s="10">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="H31" s="10">
         <v>0</v>
@@ -7158,33 +7158,33 @@
         <v>1</v>
       </c>
       <c r="J31" s="10">
-        <v>624</v>
+        <v>816</v>
       </c>
       <c r="K31" s="10">
-        <v>7945438.205796659</v>
+        <v>12917264.245188372</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="10">
         <v>1136</v>
       </c>
-      <c r="C32" s="1">
-        <v>0</v>
-      </c>
-      <c r="D32" s="1">
-        <v>1</v>
-      </c>
-      <c r="E32" s="1">
-        <v>908</v>
+      <c r="C32" s="10">
+        <v>0</v>
+      </c>
+      <c r="D32" s="10">
+        <v>1</v>
+      </c>
+      <c r="E32" s="10">
+        <v>762</v>
       </c>
       <c r="F32" s="10">
-        <v>9229408.5964249745</v>
+        <v>14123223.678253656</v>
       </c>
       <c r="G32" s="10">
-        <v>1058</v>
+        <v>1065</v>
       </c>
       <c r="H32" s="10">
         <v>1</v>
@@ -7193,103 +7193,103 @@
         <v>1</v>
       </c>
       <c r="J32" s="10">
-        <v>716</v>
+        <v>827</v>
       </c>
       <c r="K32" s="10">
-        <v>7682265.5208570464</v>
+        <v>12597981.049125759</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="B33" s="1">
-        <v>1115</v>
-      </c>
-      <c r="C33" s="1">
-        <v>0</v>
-      </c>
-      <c r="D33" s="1">
+      <c r="B33" s="10">
+        <v>1105</v>
+      </c>
+      <c r="C33" s="10">
+        <v>0</v>
+      </c>
+      <c r="D33" s="10">
         <v>3</v>
       </c>
-      <c r="E33" s="1">
-        <v>875</v>
+      <c r="E33" s="10">
+        <v>908</v>
       </c>
       <c r="F33" s="10">
-        <v>11544143.05306543</v>
+        <v>17457947.394665383</v>
       </c>
       <c r="G33" s="10">
-        <v>1106</v>
+        <v>1111</v>
       </c>
       <c r="H33" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I33" s="10">
         <v>2</v>
       </c>
       <c r="J33" s="10">
-        <v>928</v>
+        <v>879</v>
       </c>
       <c r="K33" s="10">
-        <v>11432953.513380121</v>
+        <v>17664552.96019372</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B34" s="1">
-        <v>1479</v>
-      </c>
-      <c r="C34" s="1">
-        <v>0</v>
-      </c>
-      <c r="D34" s="1">
+      <c r="B34" s="10">
+        <v>1488</v>
+      </c>
+      <c r="C34" s="10">
+        <v>0</v>
+      </c>
+      <c r="D34" s="10">
         <v>5</v>
       </c>
-      <c r="E34" s="1">
-        <v>1093</v>
+      <c r="E34" s="10">
+        <v>1152</v>
       </c>
       <c r="F34" s="10">
-        <v>17016188.039597787</v>
+        <v>26720855.442626528</v>
       </c>
       <c r="G34" s="10">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H34" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" s="10">
         <v>5</v>
       </c>
       <c r="J34" s="10">
-        <v>1132</v>
+        <v>1077</v>
       </c>
       <c r="K34" s="10">
-        <v>16052372.710008221</v>
+        <v>24955672.140388235</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B35" s="1">
-        <v>690</v>
-      </c>
-      <c r="C35" s="1">
-        <v>0</v>
-      </c>
-      <c r="D35" s="1">
-        <v>2</v>
-      </c>
-      <c r="E35" s="1">
-        <v>516</v>
+      <c r="B35" s="10">
+        <v>701</v>
+      </c>
+      <c r="C35" s="10">
+        <v>0</v>
+      </c>
+      <c r="D35" s="10">
+        <v>2</v>
+      </c>
+      <c r="E35" s="10">
+        <v>487</v>
       </c>
       <c r="F35" s="10">
-        <v>6712460.6493473453</v>
+        <v>9677957.3193788044</v>
       </c>
       <c r="G35" s="10">
-        <v>689</v>
+        <v>680</v>
       </c>
       <c r="H35" s="10">
         <v>0</v>
@@ -7298,68 +7298,68 @@
         <v>5</v>
       </c>
       <c r="J35" s="10">
-        <v>562</v>
+        <v>532</v>
       </c>
       <c r="K35" s="10">
-        <v>6447003.3071393995</v>
+        <v>10225048.001245813</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="1">
-        <v>1975</v>
-      </c>
-      <c r="C36" s="1">
-        <v>0</v>
-      </c>
-      <c r="D36" s="1">
-        <v>12</v>
-      </c>
-      <c r="E36" s="1">
-        <v>1616</v>
+      <c r="B36" s="10">
+        <v>1967</v>
+      </c>
+      <c r="C36" s="10">
+        <v>0</v>
+      </c>
+      <c r="D36" s="10">
+        <v>10</v>
+      </c>
+      <c r="E36" s="10">
+        <v>1734</v>
       </c>
       <c r="F36" s="10">
-        <v>20118854.236279029</v>
+        <v>31206440.608555064</v>
       </c>
       <c r="G36" s="10">
-        <v>1945</v>
+        <v>1937</v>
       </c>
       <c r="H36" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I36" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J36" s="10">
-        <v>1556</v>
+        <v>1550</v>
       </c>
       <c r="K36" s="10">
-        <v>19838539.705524493</v>
+        <v>31195786.901903056</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="B37" s="1">
-        <v>828</v>
-      </c>
-      <c r="C37" s="1">
-        <v>1</v>
-      </c>
-      <c r="D37" s="1">
-        <v>2</v>
-      </c>
-      <c r="E37" s="1">
-        <v>636</v>
+      <c r="B37" s="10">
+        <v>839</v>
+      </c>
+      <c r="C37" s="10">
+        <v>1</v>
+      </c>
+      <c r="D37" s="10">
+        <v>2</v>
+      </c>
+      <c r="E37" s="10">
+        <v>703</v>
       </c>
       <c r="F37" s="10">
-        <v>7210121.5178656941</v>
+        <v>11118207.377145017</v>
       </c>
       <c r="G37" s="10">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="H37" s="10">
         <v>1</v>
@@ -7368,33 +7368,33 @@
         <v>2</v>
       </c>
       <c r="J37" s="10">
-        <v>666</v>
+        <v>645</v>
       </c>
       <c r="K37" s="10">
-        <v>6647967.3857165854</v>
+        <v>10306463.021471065</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="B38" s="1">
-        <v>705</v>
-      </c>
-      <c r="C38" s="1">
-        <v>0</v>
-      </c>
-      <c r="D38" s="1">
-        <v>1</v>
-      </c>
-      <c r="E38" s="1">
-        <v>529</v>
+      <c r="B38" s="10">
+        <v>698</v>
+      </c>
+      <c r="C38" s="10">
+        <v>0</v>
+      </c>
+      <c r="D38" s="10">
+        <v>1</v>
+      </c>
+      <c r="E38" s="10">
+        <v>418</v>
       </c>
       <c r="F38" s="10">
-        <v>6619601.4259460308</v>
+        <v>9306095.0251620207</v>
       </c>
       <c r="G38" s="10">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="H38" s="10">
         <v>0</v>
@@ -7403,33 +7403,33 @@
         <v>1</v>
       </c>
       <c r="J38" s="10">
-        <v>544</v>
+        <v>525</v>
       </c>
       <c r="K38" s="10">
-        <v>6273615.4145639166</v>
+        <v>9952856.9297330845</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="B39" s="1">
-        <v>1137</v>
-      </c>
-      <c r="C39" s="1">
-        <v>1</v>
-      </c>
-      <c r="D39" s="1">
-        <v>2</v>
-      </c>
-      <c r="E39" s="1">
-        <v>859</v>
+      <c r="B39" s="10">
+        <v>1131</v>
+      </c>
+      <c r="C39" s="10">
+        <v>3</v>
+      </c>
+      <c r="D39" s="10">
+        <v>3</v>
+      </c>
+      <c r="E39" s="10">
+        <v>798</v>
       </c>
       <c r="F39" s="10">
-        <v>10611923.670867007</v>
+        <v>16122199.413593575</v>
       </c>
       <c r="G39" s="10">
-        <v>1176</v>
+        <v>1171</v>
       </c>
       <c r="H39" s="10">
         <v>5</v>
@@ -7438,103 +7438,103 @@
         <v>1</v>
       </c>
       <c r="J39" s="10">
-        <v>867</v>
+        <v>852</v>
       </c>
       <c r="K39" s="10">
-        <v>9719179.3084224835</v>
+        <v>15241628.231743544</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B40" s="1">
-        <v>1233</v>
-      </c>
-      <c r="C40" s="1">
-        <v>34</v>
-      </c>
-      <c r="D40" s="1">
-        <v>1</v>
-      </c>
-      <c r="E40" s="1">
-        <v>782</v>
+      <c r="B40" s="10">
+        <v>1200</v>
+      </c>
+      <c r="C40" s="10">
+        <v>36</v>
+      </c>
+      <c r="D40" s="10">
+        <v>1</v>
+      </c>
+      <c r="E40" s="10">
+        <v>959</v>
       </c>
       <c r="F40" s="10">
-        <v>9597528.5100794509</v>
+        <v>15445962.516069006</v>
       </c>
       <c r="G40" s="10">
-        <v>1337</v>
+        <v>1390</v>
       </c>
       <c r="H40" s="10">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="I40" s="10">
         <v>1</v>
       </c>
       <c r="J40" s="10">
-        <v>793</v>
+        <v>829</v>
       </c>
       <c r="K40" s="10">
-        <v>8790994.6551055964</v>
+        <v>13827542.353898088</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="B41" s="1">
-        <v>1882</v>
-      </c>
-      <c r="C41" s="1">
-        <v>36</v>
-      </c>
-      <c r="D41" s="1">
-        <v>3</v>
-      </c>
-      <c r="E41" s="1">
-        <v>1409</v>
+      <c r="B41" s="10">
+        <v>1844</v>
+      </c>
+      <c r="C41" s="10">
+        <v>40</v>
+      </c>
+      <c r="D41" s="10">
+        <v>4</v>
+      </c>
+      <c r="E41" s="10">
+        <v>1411</v>
       </c>
       <c r="F41" s="10">
-        <v>15688734.510597564</v>
+        <v>24434713.31977386</v>
       </c>
       <c r="G41" s="10">
-        <v>2544</v>
+        <v>2522</v>
       </c>
       <c r="H41" s="10">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="I41" s="10">
         <v>5</v>
       </c>
       <c r="J41" s="10">
-        <v>1477</v>
+        <v>1498</v>
       </c>
       <c r="K41" s="10">
-        <v>16041935.121685091</v>
+        <v>25291639.249637514</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B42" s="1">
-        <v>627</v>
-      </c>
-      <c r="C42" s="1">
-        <v>1</v>
-      </c>
-      <c r="D42" s="1">
+      <c r="B42" s="10">
+        <v>625</v>
+      </c>
+      <c r="C42" s="10">
+        <v>2</v>
+      </c>
+      <c r="D42" s="10">
         <v>6</v>
       </c>
-      <c r="E42" s="1">
-        <v>483</v>
+      <c r="E42" s="10">
+        <v>462</v>
       </c>
       <c r="F42" s="10">
-        <v>6470067.6283398336</v>
+        <v>10078150.216247274</v>
       </c>
       <c r="G42" s="10">
-        <v>611</v>
+        <v>623</v>
       </c>
       <c r="H42" s="10">
         <v>0</v>
@@ -7543,103 +7543,103 @@
         <v>6</v>
       </c>
       <c r="J42" s="10">
-        <v>456</v>
+        <v>412</v>
       </c>
       <c r="K42" s="10">
-        <v>5775032.9829335511</v>
+        <v>9191077.4228783716</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B43" s="1">
-        <v>1968</v>
-      </c>
-      <c r="C43" s="1">
-        <v>1</v>
-      </c>
-      <c r="D43" s="1">
-        <v>7</v>
-      </c>
-      <c r="E43" s="1">
-        <v>1802</v>
+      <c r="B43" s="10">
+        <v>1945</v>
+      </c>
+      <c r="C43" s="10">
+        <v>2</v>
+      </c>
+      <c r="D43" s="10">
+        <v>6</v>
+      </c>
+      <c r="E43" s="10">
+        <v>1778</v>
       </c>
       <c r="F43" s="10">
-        <v>17509860.42114738</v>
+        <v>27864970.025229905</v>
       </c>
       <c r="G43" s="10">
-        <v>2066</v>
+        <v>2057</v>
       </c>
       <c r="H43" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J43" s="10">
-        <v>2006</v>
+        <v>1826</v>
       </c>
       <c r="K43" s="10">
-        <v>19803000.926697183</v>
+        <v>31007988.562648121</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="1">
-        <v>859</v>
-      </c>
-      <c r="C44" s="1">
+      <c r="B44" s="10">
+        <v>869</v>
+      </c>
+      <c r="C44" s="10">
         <v>3</v>
       </c>
-      <c r="D44" s="1">
-        <v>4</v>
-      </c>
-      <c r="E44" s="1">
-        <v>748</v>
+      <c r="D44" s="10">
+        <v>4</v>
+      </c>
+      <c r="E44" s="10">
+        <v>731</v>
       </c>
       <c r="F44" s="10">
-        <v>12266555.037886323</v>
+        <v>19342823.481627457</v>
       </c>
       <c r="G44" s="10">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H44" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44" s="10">
         <v>2</v>
       </c>
       <c r="J44" s="10">
-        <v>782</v>
+        <v>753</v>
       </c>
       <c r="K44" s="10">
-        <v>12542230.531580009</v>
+        <v>19825792.805345695</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B45" s="1">
-        <v>1142</v>
-      </c>
-      <c r="C45" s="1">
-        <v>0</v>
-      </c>
-      <c r="D45" s="1">
-        <v>4</v>
-      </c>
-      <c r="E45" s="1">
-        <v>893</v>
+      <c r="B45" s="10">
+        <v>1146</v>
+      </c>
+      <c r="C45" s="10">
+        <v>0</v>
+      </c>
+      <c r="D45" s="10">
+        <v>3</v>
+      </c>
+      <c r="E45" s="10">
+        <v>939</v>
       </c>
       <c r="F45" s="10">
-        <v>11423518.706303084</v>
+        <v>17597530.510886051</v>
       </c>
       <c r="G45" s="10">
-        <v>1105</v>
+        <v>1087</v>
       </c>
       <c r="H45" s="10">
         <v>0</v>
@@ -7648,103 +7648,103 @@
         <v>3</v>
       </c>
       <c r="J45" s="10">
-        <v>462</v>
+        <v>918</v>
       </c>
       <c r="K45" s="10">
-        <v>5556095.8800142836</v>
+        <v>8542291.4264150988</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="1">
-        <v>846</v>
-      </c>
-      <c r="C46" s="1">
-        <v>0</v>
-      </c>
-      <c r="D46" s="1">
+      <c r="B46" s="10">
+        <v>849</v>
+      </c>
+      <c r="C46" s="10">
+        <v>0</v>
+      </c>
+      <c r="D46" s="10">
         <v>5</v>
       </c>
-      <c r="E46" s="1">
-        <v>629</v>
+      <c r="E46" s="10">
+        <v>608</v>
       </c>
       <c r="F46" s="10">
-        <v>10758260.689446844</v>
+        <v>16323094.491309352</v>
       </c>
       <c r="G46" s="10">
-        <v>827</v>
+        <v>819</v>
       </c>
       <c r="H46" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" s="10">
         <v>4</v>
       </c>
       <c r="J46" s="10">
-        <v>663</v>
+        <v>597</v>
       </c>
       <c r="K46" s="10">
-        <v>9777702.0178567767</v>
+        <v>15660058.036465179</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B47" s="10">
         <v>661</v>
       </c>
-      <c r="C47" s="1">
-        <v>0</v>
-      </c>
-      <c r="D47" s="1">
+      <c r="C47" s="10">
+        <v>0</v>
+      </c>
+      <c r="D47" s="10">
         <v>10</v>
       </c>
-      <c r="E47" s="1">
-        <v>528</v>
+      <c r="E47" s="10">
+        <v>547</v>
       </c>
       <c r="F47" s="10">
-        <v>5798980.5858204048</v>
+        <v>9307002.4168394431</v>
       </c>
       <c r="G47" s="10">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H47" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" s="10">
         <v>10</v>
       </c>
       <c r="J47" s="10">
-        <v>584</v>
+        <v>715</v>
       </c>
       <c r="K47" s="10">
-        <v>6684286.8881617002</v>
+        <v>9999788.4775667209</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="B48" s="1">
-        <v>690</v>
-      </c>
-      <c r="C48" s="1">
-        <v>1</v>
-      </c>
-      <c r="D48" s="1">
-        <v>1</v>
-      </c>
-      <c r="E48" s="1">
-        <v>705</v>
+      <c r="B48" s="10">
+        <v>691</v>
+      </c>
+      <c r="C48" s="10">
+        <v>1</v>
+      </c>
+      <c r="D48" s="10">
+        <v>1</v>
+      </c>
+      <c r="E48" s="10">
+        <v>682</v>
       </c>
       <c r="F48" s="10">
-        <v>5562478.9097076738</v>
+        <v>9148288.1945246682</v>
       </c>
       <c r="G48" s="10">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="H48" s="10">
         <v>0</v>
@@ -7753,33 +7753,33 @@
         <v>3</v>
       </c>
       <c r="J48" s="10">
-        <v>712</v>
+        <v>696</v>
       </c>
       <c r="K48" s="10">
-        <v>5538977.3383655511</v>
+        <v>8607899.5225225668</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B49" s="1">
-        <v>1279</v>
-      </c>
-      <c r="C49" s="1">
+      <c r="B49" s="10">
+        <v>1276</v>
+      </c>
+      <c r="C49" s="10">
         <v>5</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D49" s="10">
         <v>7</v>
       </c>
-      <c r="E49" s="1">
-        <v>1454</v>
+      <c r="E49" s="10">
+        <v>1209</v>
       </c>
       <c r="F49" s="10">
-        <v>21737480.949146856</v>
+        <v>33294714.610988211</v>
       </c>
       <c r="G49" s="10">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="H49" s="10">
         <v>0</v>
@@ -7788,138 +7788,138 @@
         <v>4</v>
       </c>
       <c r="J49" s="10">
-        <v>1120</v>
+        <v>1154</v>
       </c>
       <c r="K49" s="10">
-        <v>17668408.580657668</v>
+        <v>27457832.858950939</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="B50" s="1">
-        <v>431</v>
-      </c>
-      <c r="C50" s="1">
-        <v>0</v>
-      </c>
-      <c r="D50" s="1">
-        <v>2</v>
-      </c>
-      <c r="E50" s="1">
-        <v>472</v>
+      <c r="B50" s="10">
+        <v>426</v>
+      </c>
+      <c r="C50" s="10">
+        <v>0</v>
+      </c>
+      <c r="D50" s="10">
+        <v>2</v>
+      </c>
+      <c r="E50" s="10">
+        <v>457</v>
       </c>
       <c r="F50" s="10">
-        <v>3677678.6177664129</v>
+        <v>5605744.3736915821</v>
       </c>
       <c r="G50" s="10">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H50" s="10">
         <v>0</v>
       </c>
       <c r="I50" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J50" s="10">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="K50" s="10">
-        <v>2861808.6604427658</v>
+        <v>4640637.6320960438</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B51" s="1">
-        <v>867</v>
-      </c>
-      <c r="C51" s="1">
-        <v>0</v>
-      </c>
-      <c r="D51" s="1">
-        <v>4</v>
-      </c>
-      <c r="E51" s="1">
-        <v>932</v>
+      <c r="B51" s="10">
+        <v>866</v>
+      </c>
+      <c r="C51" s="10">
+        <v>0</v>
+      </c>
+      <c r="D51" s="10">
+        <v>4</v>
+      </c>
+      <c r="E51" s="10">
+        <v>925</v>
       </c>
       <c r="F51" s="10">
-        <v>9251292.3983292542</v>
+        <v>14593080.011471108</v>
       </c>
       <c r="G51" s="10">
-        <v>901</v>
+        <v>917</v>
       </c>
       <c r="H51" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I51" s="10">
         <v>5</v>
       </c>
       <c r="J51" s="10">
-        <v>933</v>
+        <v>887</v>
       </c>
       <c r="K51" s="10">
-        <v>8311758.9493374256</v>
+        <v>13251593.852497272</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B52" s="1">
-        <v>1319</v>
-      </c>
-      <c r="C52" s="1">
-        <v>1</v>
-      </c>
-      <c r="D52" s="1">
+      <c r="B52" s="10">
+        <v>1312</v>
+      </c>
+      <c r="C52" s="10">
+        <v>1</v>
+      </c>
+      <c r="D52" s="10">
         <v>12</v>
       </c>
-      <c r="E52" s="1">
-        <v>1109</v>
+      <c r="E52" s="10">
+        <v>946</v>
       </c>
       <c r="F52" s="10">
-        <v>11821046.27861462</v>
+        <v>18552025.445382949</v>
       </c>
       <c r="G52" s="10">
-        <v>1347</v>
+        <v>1362</v>
       </c>
       <c r="H52" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I52" s="10">
         <v>12</v>
       </c>
       <c r="J52" s="10">
-        <v>1042</v>
+        <v>958</v>
       </c>
       <c r="K52" s="10">
-        <v>14882247.462702388</v>
+        <v>23392753.696536377</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B53" s="1">
-        <v>479</v>
-      </c>
-      <c r="C53" s="1">
-        <v>0</v>
-      </c>
-      <c r="D53" s="1">
-        <v>4</v>
-      </c>
-      <c r="E53" s="1">
+      <c r="B53" s="10">
+        <v>485</v>
+      </c>
+      <c r="C53" s="10">
+        <v>0</v>
+      </c>
+      <c r="D53" s="10">
         <v>5</v>
       </c>
+      <c r="E53" s="10">
+        <v>369</v>
+      </c>
       <c r="F53" s="10">
-        <v>5591648.4348684251</v>
+        <v>9531210.9429570977</v>
       </c>
       <c r="G53" s="10">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="H53" s="10">
         <v>0</v>
@@ -7928,30 +7928,30 @@
         <v>6</v>
       </c>
       <c r="J53" s="10">
-        <v>392</v>
+        <v>371</v>
       </c>
       <c r="K53" s="10">
-        <v>7909758.2747908533</v>
+        <v>12215200.861652251</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B54" s="1">
-        <v>444</v>
-      </c>
-      <c r="C54" s="1">
-        <v>0</v>
-      </c>
-      <c r="D54" s="1">
-        <v>9</v>
-      </c>
-      <c r="E54" s="1">
-        <v>541</v>
+      <c r="B54" s="10">
+        <v>445</v>
+      </c>
+      <c r="C54" s="10">
+        <v>0</v>
+      </c>
+      <c r="D54" s="10">
+        <v>7</v>
+      </c>
+      <c r="E54" s="10">
+        <v>325</v>
       </c>
       <c r="F54" s="10">
-        <v>7608363.9352213563</v>
+        <v>11573023.120887872</v>
       </c>
       <c r="G54" s="10">
         <v>455</v>
@@ -7963,68 +7963,68 @@
         <v>4</v>
       </c>
       <c r="J54" s="10">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="K54" s="10">
-        <v>5763787.7664615251</v>
+        <v>8993502.2004245669</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B55" s="1">
-        <v>423</v>
-      </c>
-      <c r="C55" s="1">
-        <v>3</v>
-      </c>
-      <c r="D55" s="1">
-        <v>2</v>
-      </c>
-      <c r="E55" s="1">
-        <v>879</v>
+      <c r="B55" s="10">
+        <v>422</v>
+      </c>
+      <c r="C55" s="10">
+        <v>8</v>
+      </c>
+      <c r="D55" s="10">
+        <v>2</v>
+      </c>
+      <c r="E55" s="10">
+        <v>339</v>
       </c>
       <c r="F55" s="10">
-        <v>6128628.9357606936</v>
+        <v>9065219.3768147286</v>
       </c>
       <c r="G55" s="10">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="H55" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" s="10">
         <v>3</v>
       </c>
       <c r="J55" s="10">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="K55" s="10">
-        <v>4932361.0217840318</v>
+        <v>7672695.2189010149</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="B56" s="1">
-        <v>1130</v>
-      </c>
-      <c r="C56" s="1">
-        <v>0</v>
-      </c>
-      <c r="D56" s="1">
-        <v>0</v>
-      </c>
-      <c r="E56" s="1">
-        <v>932</v>
+      <c r="B56" s="10">
+        <v>1135</v>
+      </c>
+      <c r="C56" s="10">
+        <v>0</v>
+      </c>
+      <c r="D56" s="10">
+        <v>1</v>
+      </c>
+      <c r="E56" s="10">
+        <v>902</v>
       </c>
       <c r="F56" s="10">
-        <v>12661711.662759928</v>
+        <v>19252439.405621711</v>
       </c>
       <c r="G56" s="10">
-        <v>1112</v>
+        <v>1100</v>
       </c>
       <c r="H56" s="10">
         <v>0</v>
@@ -8033,34 +8033,34 @@
         <v>0</v>
       </c>
       <c r="J56" s="10">
-        <v>1111</v>
+        <v>921</v>
       </c>
       <c r="K56" s="10">
-        <v>11307100.037220374</v>
+        <v>18272372.933828708</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="B57" s="1">
+      <c r="B57" s="10">
+        <v>958</v>
+      </c>
+      <c r="C57" s="10">
+        <v>6</v>
+      </c>
+      <c r="D57" s="10">
+        <v>3</v>
+      </c>
+      <c r="E57" s="10">
+        <v>820</v>
+      </c>
+      <c r="F57" s="10">
+        <v>20212422.982229233</v>
+      </c>
+      <c r="G57" s="10">
         <v>966</v>
       </c>
-      <c r="C57" s="1">
-        <v>4</v>
-      </c>
-      <c r="D57" s="1">
-        <v>4</v>
-      </c>
-      <c r="E57" s="1">
-        <v>876</v>
-      </c>
-      <c r="F57" s="10">
-        <v>13626568.667371128</v>
-      </c>
-      <c r="G57" s="10">
-        <v>954</v>
-      </c>
       <c r="H57" s="10">
         <v>1</v>
       </c>
@@ -8068,33 +8068,33 @@
         <v>1</v>
       </c>
       <c r="J57" s="10">
-        <v>695</v>
+        <v>976</v>
       </c>
       <c r="K57" s="10">
-        <v>8397528.3064261712</v>
+        <v>15381123.373330694</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="B58" s="1">
-        <v>2212</v>
-      </c>
-      <c r="C58" s="1">
-        <v>14</v>
-      </c>
-      <c r="D58" s="1">
-        <v>6</v>
-      </c>
-      <c r="E58" s="1">
-        <v>1640</v>
+      <c r="B58" s="10">
+        <v>2240</v>
+      </c>
+      <c r="C58" s="10">
+        <v>30</v>
+      </c>
+      <c r="D58" s="10">
+        <v>7</v>
+      </c>
+      <c r="E58" s="10">
+        <v>1619</v>
       </c>
       <c r="F58" s="10">
-        <v>16713879.377090869</v>
+        <v>27521319.010392979</v>
       </c>
       <c r="G58" s="10">
-        <v>2037</v>
+        <v>2055</v>
       </c>
       <c r="H58" s="10">
         <v>5</v>
@@ -8103,33 +8103,33 @@
         <v>8</v>
       </c>
       <c r="J58" s="10">
-        <v>1558</v>
+        <v>1483</v>
       </c>
       <c r="K58" s="10">
-        <v>22573183.750718944</v>
+        <v>34698100.647447377</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B59" s="1">
-        <v>678</v>
-      </c>
-      <c r="C59" s="1">
-        <v>0</v>
-      </c>
-      <c r="D59" s="1">
-        <v>0</v>
-      </c>
-      <c r="E59" s="1">
-        <v>532</v>
+      <c r="B59" s="10">
+        <v>679</v>
+      </c>
+      <c r="C59" s="10">
+        <v>0</v>
+      </c>
+      <c r="D59" s="10">
+        <v>0</v>
+      </c>
+      <c r="E59" s="10">
+        <v>513</v>
       </c>
       <c r="F59" s="10">
-        <v>6379712.6169025553</v>
+        <v>9434418.3837709222</v>
       </c>
       <c r="G59" s="10">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="H59" s="10">
         <v>0</v>
@@ -8138,243 +8138,243 @@
         <v>0</v>
       </c>
       <c r="J59" s="10">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="K59" s="10">
-        <v>4781920.9490648406</v>
+        <v>7707113.4334032862</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B60" s="1">
-        <v>860</v>
-      </c>
-      <c r="C60" s="1">
-        <v>1</v>
-      </c>
-      <c r="D60" s="1">
+      <c r="B60" s="10">
+        <v>866</v>
+      </c>
+      <c r="C60" s="10">
+        <v>2</v>
+      </c>
+      <c r="D60" s="10">
         <v>5</v>
       </c>
-      <c r="E60" s="1">
-        <v>658</v>
+      <c r="E60" s="10">
+        <v>742</v>
       </c>
       <c r="F60" s="10">
-        <v>8991956.9474403877</v>
+        <v>13858244.856042204</v>
       </c>
       <c r="G60" s="10">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H60" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I60" s="10">
         <v>5</v>
       </c>
       <c r="J60" s="10">
-        <v>683</v>
+        <v>761</v>
       </c>
       <c r="K60" s="10">
-        <v>8349086.2784085236</v>
+        <v>13874918.72588186</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="B61" s="1">
-        <v>788</v>
-      </c>
-      <c r="C61" s="1">
-        <v>0</v>
-      </c>
-      <c r="D61" s="1">
-        <v>1</v>
-      </c>
-      <c r="E61" s="1">
-        <v>774</v>
+      <c r="B61" s="10">
+        <v>789</v>
+      </c>
+      <c r="C61" s="10">
+        <v>0</v>
+      </c>
+      <c r="D61" s="10">
+        <v>1</v>
+      </c>
+      <c r="E61" s="10">
+        <v>622</v>
       </c>
       <c r="F61" s="10">
-        <v>7657816.4317125622</v>
+        <v>11626890.823241539</v>
       </c>
       <c r="G61" s="10">
-        <v>756</v>
+        <v>747</v>
       </c>
       <c r="H61" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I61" s="10">
         <v>1</v>
       </c>
       <c r="J61" s="10">
-        <v>612</v>
+        <v>691</v>
       </c>
       <c r="K61" s="10">
-        <v>5833873.0823586648</v>
+        <v>8580104.8251491878</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="B62" s="1">
-        <v>1067</v>
-      </c>
-      <c r="C62" s="1">
-        <v>1</v>
-      </c>
-      <c r="D62" s="1">
-        <v>0</v>
-      </c>
-      <c r="E62" s="1">
-        <v>1121</v>
+      <c r="B62" s="10">
+        <v>1071</v>
+      </c>
+      <c r="C62" s="10">
+        <v>2</v>
+      </c>
+      <c r="D62" s="10">
+        <v>0</v>
+      </c>
+      <c r="E62" s="10">
+        <v>1203</v>
       </c>
       <c r="F62" s="10">
-        <v>11863483.749333108</v>
+        <v>18581393.752516262</v>
       </c>
       <c r="G62" s="10">
-        <v>1100</v>
+        <v>1106</v>
       </c>
       <c r="H62" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I62" s="10">
         <v>0</v>
       </c>
       <c r="J62" s="10">
-        <v>1017</v>
+        <v>928</v>
       </c>
       <c r="K62" s="10">
-        <v>11507491.265354032</v>
+        <v>18789590.991508801</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="B63" s="1">
+      <c r="B63" s="10">
+        <v>1321</v>
+      </c>
+      <c r="C63" s="10">
+        <v>4</v>
+      </c>
+      <c r="D63" s="10">
+        <v>4</v>
+      </c>
+      <c r="E63" s="10">
+        <v>1415</v>
+      </c>
+      <c r="F63" s="10">
+        <v>24051078.007695895</v>
+      </c>
+      <c r="G63" s="10">
+        <v>1387</v>
+      </c>
+      <c r="H63" s="10">
+        <v>1</v>
+      </c>
+      <c r="I63" s="10">
+        <v>4</v>
+      </c>
+      <c r="J63" s="10">
         <v>1341</v>
       </c>
-      <c r="C63" s="1">
-        <v>3</v>
-      </c>
-      <c r="D63" s="1">
-        <v>4</v>
-      </c>
-      <c r="E63" s="1">
-        <v>1447</v>
-      </c>
-      <c r="F63" s="10">
-        <v>15321494.302633652</v>
-      </c>
-      <c r="G63" s="10">
-        <v>1358</v>
-      </c>
-      <c r="H63" s="10">
-        <v>1</v>
-      </c>
-      <c r="I63" s="10">
-        <v>4</v>
-      </c>
-      <c r="J63" s="10">
-        <v>1450</v>
-      </c>
       <c r="K63" s="10">
-        <v>13532937.95509661</v>
+        <v>22594833.46428778</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="B64" s="1">
-        <v>792</v>
-      </c>
-      <c r="C64" s="1">
-        <v>1</v>
-      </c>
-      <c r="D64" s="1">
+      <c r="B64" s="10">
+        <v>788</v>
+      </c>
+      <c r="C64" s="10">
+        <v>3</v>
+      </c>
+      <c r="D64" s="10">
         <v>5</v>
       </c>
-      <c r="E64" s="1">
-        <v>731</v>
+      <c r="E64" s="10">
+        <v>715</v>
       </c>
       <c r="F64" s="10">
-        <v>8058811.266136542</v>
+        <v>12751076.307971718</v>
       </c>
       <c r="G64" s="10">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="H64" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" s="10">
         <v>3</v>
       </c>
       <c r="J64" s="10">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="K64" s="10">
-        <v>8013162.8275077576</v>
+        <v>12643538.853697417</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="B65" s="1">
+      <c r="B65" s="10">
         <v>701</v>
       </c>
-      <c r="C65" s="1">
-        <v>1</v>
-      </c>
-      <c r="D65" s="1">
+      <c r="C65" s="10">
+        <v>2</v>
+      </c>
+      <c r="D65" s="10">
         <v>5</v>
       </c>
-      <c r="E65" s="1">
-        <v>468</v>
+      <c r="E65" s="10">
+        <v>502</v>
       </c>
       <c r="F65" s="10">
-        <v>9269260.5100010578</v>
+        <v>14810216.222912636</v>
       </c>
       <c r="G65" s="10">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="H65" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I65" s="10">
         <v>5</v>
       </c>
       <c r="J65" s="10">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="K65" s="10">
-        <v>8893470.3084834833</v>
+        <v>14171503.656152204</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B66" s="1">
-        <v>2017</v>
-      </c>
-      <c r="C66" s="1">
-        <v>0</v>
-      </c>
-      <c r="D66" s="1">
-        <v>8</v>
-      </c>
-      <c r="E66" s="1">
-        <v>1622</v>
+      <c r="B66" s="10">
+        <v>2029</v>
+      </c>
+      <c r="C66" s="10">
+        <v>2</v>
+      </c>
+      <c r="D66" s="10">
+        <v>9</v>
+      </c>
+      <c r="E66" s="10">
+        <v>1606</v>
       </c>
       <c r="F66" s="10">
-        <v>18229398.001991931</v>
+        <v>32404512.52197903</v>
       </c>
       <c r="G66" s="10">
-        <v>2011</v>
+        <v>2002</v>
       </c>
       <c r="H66" s="10">
         <v>2</v>
@@ -8383,138 +8383,138 @@
         <v>11</v>
       </c>
       <c r="J66" s="10">
-        <v>1646</v>
+        <v>1907</v>
       </c>
       <c r="K66" s="10">
-        <v>28428132.615541138</v>
+        <v>45501282.296908557</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B67" s="1">
-        <v>1611</v>
-      </c>
-      <c r="C67" s="1">
-        <v>9</v>
-      </c>
-      <c r="D67" s="1">
-        <v>7</v>
-      </c>
-      <c r="E67" s="1">
-        <v>1171</v>
+      <c r="B67" s="10">
+        <v>1616</v>
+      </c>
+      <c r="C67" s="10">
+        <v>10</v>
+      </c>
+      <c r="D67" s="10">
+        <v>8</v>
+      </c>
+      <c r="E67" s="10">
+        <v>1130</v>
       </c>
       <c r="F67" s="10">
-        <v>22361324.738696799</v>
+        <v>33665873.670948178</v>
       </c>
       <c r="G67" s="10">
-        <v>1569</v>
+        <v>1572</v>
       </c>
       <c r="H67" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I67" s="10">
         <v>6</v>
       </c>
       <c r="J67" s="10">
-        <v>1188</v>
+        <v>1135</v>
       </c>
       <c r="K67" s="10">
-        <v>19014835.241792019</v>
+        <v>31666643.56758967</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B68" s="1">
-        <v>857</v>
-      </c>
-      <c r="C68" s="1">
-        <v>0</v>
-      </c>
-      <c r="D68" s="1">
-        <v>0</v>
-      </c>
-      <c r="E68" s="1">
-        <v>662</v>
+      <c r="B68" s="10">
+        <v>856</v>
+      </c>
+      <c r="C68" s="10">
+        <v>1</v>
+      </c>
+      <c r="D68" s="10">
+        <v>1</v>
+      </c>
+      <c r="E68" s="10">
+        <v>726</v>
       </c>
       <c r="F68" s="10">
-        <v>14473423.450396292</v>
+        <v>21955038.147735532</v>
       </c>
       <c r="G68" s="10">
-        <v>870</v>
+        <v>889</v>
       </c>
       <c r="H68" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I68" s="10">
         <v>1</v>
       </c>
       <c r="J68" s="10">
-        <v>767</v>
+        <v>701</v>
       </c>
       <c r="K68" s="10">
-        <v>13488920.19425902</v>
+        <v>21711289.52854608</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B69" s="1">
-        <v>1899</v>
-      </c>
-      <c r="C69" s="1">
-        <v>35</v>
-      </c>
-      <c r="D69" s="1">
+      <c r="B69" s="10">
+        <v>1879</v>
+      </c>
+      <c r="C69" s="10">
+        <v>36</v>
+      </c>
+      <c r="D69" s="10">
         <v>13</v>
       </c>
-      <c r="E69" s="1">
-        <v>1338</v>
+      <c r="E69" s="10">
+        <v>1290</v>
       </c>
       <c r="F69" s="10">
-        <v>20091572.499213256</v>
+        <v>31196971.177899417</v>
       </c>
       <c r="G69" s="10">
-        <v>2133</v>
+        <v>2097</v>
       </c>
       <c r="H69" s="10">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I69" s="10">
         <v>12</v>
       </c>
       <c r="J69" s="10">
-        <v>1307</v>
+        <v>1462</v>
       </c>
       <c r="K69" s="10">
-        <v>21020869.711768493</v>
+        <v>32860185.916051608</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A70" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="B70" s="1">
-        <v>270</v>
-      </c>
-      <c r="C70" s="1">
-        <v>0</v>
-      </c>
-      <c r="D70" s="1">
-        <v>1</v>
-      </c>
-      <c r="E70" s="1">
-        <v>254</v>
+      <c r="B70" s="10">
+        <v>267</v>
+      </c>
+      <c r="C70" s="10">
+        <v>0</v>
+      </c>
+      <c r="D70" s="10">
+        <v>1</v>
+      </c>
+      <c r="E70" s="10">
+        <v>212</v>
       </c>
       <c r="F70" s="10">
-        <v>1561428.480501238</v>
+        <v>2292405.9875394548</v>
       </c>
       <c r="G70" s="10">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="H70" s="10">
         <v>0</v>
@@ -8523,68 +8523,68 @@
         <v>0</v>
       </c>
       <c r="J70" s="10">
-        <v>2</v>
+        <v>256</v>
       </c>
       <c r="K70" s="10">
-        <v>2.0709595030000001</v>
+        <v>375644.44752447098</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B71" s="1">
-        <v>1739</v>
-      </c>
-      <c r="C71" s="1">
-        <v>0</v>
-      </c>
-      <c r="D71" s="1">
+      <c r="B71" s="10">
+        <v>1745</v>
+      </c>
+      <c r="C71" s="10">
+        <v>2</v>
+      </c>
+      <c r="D71" s="10">
         <v>7</v>
       </c>
-      <c r="E71" s="1">
-        <v>1664</v>
+      <c r="E71" s="10">
+        <v>1689</v>
       </c>
       <c r="F71" s="10">
-        <v>16733881.714438308</v>
+        <v>25616759.463998247</v>
       </c>
       <c r="G71" s="10">
-        <v>1666</v>
+        <v>1672</v>
       </c>
       <c r="H71" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I71" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J71" s="10">
-        <v>1836</v>
+        <v>1868</v>
       </c>
       <c r="K71" s="10">
-        <v>14199763.569661347</v>
+        <v>23897425.779863752</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B72" s="1">
-        <v>653</v>
-      </c>
-      <c r="C72" s="1">
-        <v>0</v>
-      </c>
-      <c r="D72" s="1">
-        <v>2</v>
-      </c>
-      <c r="E72" s="1">
-        <v>548</v>
+      <c r="B72" s="10">
+        <v>661</v>
+      </c>
+      <c r="C72" s="10">
+        <v>1</v>
+      </c>
+      <c r="D72" s="10">
+        <v>2</v>
+      </c>
+      <c r="E72" s="10">
+        <v>603</v>
       </c>
       <c r="F72" s="10">
-        <v>6260256.2300493997</v>
+        <v>9992649.6044265609</v>
       </c>
       <c r="G72" s="10">
-        <v>698</v>
+        <v>717</v>
       </c>
       <c r="H72" s="10">
         <v>1</v>
@@ -8593,68 +8593,68 @@
         <v>3</v>
       </c>
       <c r="J72" s="10">
-        <v>776</v>
+        <v>603</v>
       </c>
       <c r="K72" s="10">
-        <v>7314365.6052390682</v>
+        <v>11330814.204616746</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="B73" s="1">
-        <v>1396</v>
-      </c>
-      <c r="C73" s="1">
+      <c r="B73" s="10">
+        <v>1358</v>
+      </c>
+      <c r="C73" s="10">
+        <v>20</v>
+      </c>
+      <c r="D73" s="10">
+        <v>5</v>
+      </c>
+      <c r="E73" s="10">
+        <v>1182</v>
+      </c>
+      <c r="F73" s="10">
+        <v>17067513.194088787</v>
+      </c>
+      <c r="G73" s="10">
+        <v>1370</v>
+      </c>
+      <c r="H73" s="10">
         <v>19</v>
       </c>
-      <c r="D73" s="1">
-        <v>5</v>
-      </c>
-      <c r="E73" s="1">
-        <v>957</v>
-      </c>
-      <c r="F73" s="10">
-        <v>10563149.67928694</v>
-      </c>
-      <c r="G73" s="10">
-        <v>1384</v>
-      </c>
-      <c r="H73" s="10">
-        <v>18</v>
-      </c>
       <c r="I73" s="10">
         <v>4</v>
       </c>
       <c r="J73" s="10">
-        <v>903</v>
+        <v>844</v>
       </c>
       <c r="K73" s="10">
-        <v>10158060.965133499</v>
+        <v>15742610.95808477</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B74" s="1">
-        <v>1412</v>
-      </c>
-      <c r="C74" s="1">
+      <c r="B74" s="10">
+        <v>1403</v>
+      </c>
+      <c r="C74" s="10">
         <v>3</v>
       </c>
-      <c r="D74" s="1">
-        <v>4</v>
-      </c>
-      <c r="E74" s="1">
-        <v>1403</v>
+      <c r="D74" s="10">
+        <v>5</v>
+      </c>
+      <c r="E74" s="10">
+        <v>1789</v>
       </c>
       <c r="F74" s="10">
-        <v>4879934.5253025386</v>
+        <v>8171514.3711125841</v>
       </c>
       <c r="G74" s="10">
-        <v>1306</v>
+        <v>1303</v>
       </c>
       <c r="H74" s="10">
         <v>1</v>
@@ -8663,138 +8663,138 @@
         <v>5</v>
       </c>
       <c r="J74" s="10">
-        <v>1792</v>
+        <v>1226</v>
       </c>
       <c r="K74" s="10">
-        <v>8403983.9138157759</v>
+        <v>11909259.237161091</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B75" s="1">
-        <v>1719</v>
-      </c>
-      <c r="C75" s="1">
-        <v>2</v>
-      </c>
-      <c r="D75" s="1">
+      <c r="B75" s="10">
+        <v>1743</v>
+      </c>
+      <c r="C75" s="10">
+        <v>2</v>
+      </c>
+      <c r="D75" s="10">
+        <v>5</v>
+      </c>
+      <c r="E75" s="10">
+        <v>1215</v>
+      </c>
+      <c r="F75" s="10">
+        <v>28308720.802652378</v>
+      </c>
+      <c r="G75" s="10">
+        <v>1728</v>
+      </c>
+      <c r="H75" s="10">
         <v>6</v>
       </c>
-      <c r="E75" s="1">
-        <v>1271</v>
-      </c>
-      <c r="F75" s="10">
-        <v>17404206.181409512</v>
-      </c>
-      <c r="G75" s="10">
-        <v>1743</v>
-      </c>
-      <c r="H75" s="10">
-        <v>2</v>
-      </c>
       <c r="I75" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J75" s="10">
-        <v>1232</v>
+        <v>1158</v>
       </c>
       <c r="K75" s="10">
-        <v>19248935.953068849</v>
+        <v>29124730.546930134</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="B76" s="1">
-        <v>488</v>
-      </c>
-      <c r="C76" s="1">
-        <v>1</v>
-      </c>
-      <c r="D76" s="1">
-        <v>2</v>
-      </c>
-      <c r="E76" s="1">
-        <v>554</v>
+      <c r="B76" s="10">
+        <v>487</v>
+      </c>
+      <c r="C76" s="10">
+        <v>1</v>
+      </c>
+      <c r="D76" s="10">
+        <v>3</v>
+      </c>
+      <c r="E76" s="10">
+        <v>511</v>
       </c>
       <c r="F76" s="10">
-        <v>4029401.0109289791</v>
+        <v>6354765.22670455</v>
       </c>
       <c r="G76" s="10">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="H76" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I76" s="10">
         <v>1</v>
       </c>
       <c r="J76" s="10">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="K76" s="10">
-        <v>3683325.4120055642</v>
+        <v>5975962.6817722982</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A77" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="B77" s="1">
-        <v>909</v>
-      </c>
-      <c r="C77" s="1">
-        <v>1</v>
-      </c>
-      <c r="D77" s="1">
-        <v>0</v>
-      </c>
-      <c r="E77" s="1">
-        <v>805</v>
+      <c r="B77" s="10">
+        <v>897</v>
+      </c>
+      <c r="C77" s="10">
+        <v>1</v>
+      </c>
+      <c r="D77" s="10">
+        <v>1</v>
+      </c>
+      <c r="E77" s="10">
+        <v>813</v>
       </c>
       <c r="F77" s="10">
-        <v>6554960.5533400709</v>
+        <v>9989788.20540924</v>
       </c>
       <c r="G77" s="10">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H77" s="10">
         <v>2</v>
       </c>
       <c r="I77" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" s="10">
-        <v>820</v>
+        <v>920</v>
       </c>
       <c r="K77" s="10">
-        <v>5391451.010178484</v>
+        <v>8967153.6823930759</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A78" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B78" s="1">
-        <v>679</v>
-      </c>
-      <c r="C78" s="1">
-        <v>0</v>
-      </c>
-      <c r="D78" s="1">
-        <v>4</v>
-      </c>
-      <c r="E78" s="1">
-        <v>564</v>
+      <c r="B78" s="10">
+        <v>688</v>
+      </c>
+      <c r="C78" s="10">
+        <v>0</v>
+      </c>
+      <c r="D78" s="10">
+        <v>4</v>
+      </c>
+      <c r="E78" s="10">
+        <v>513</v>
       </c>
       <c r="F78" s="10">
-        <v>2689264.6686447202</v>
+        <v>5514504.1095447363</v>
       </c>
       <c r="G78" s="10">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="H78" s="10">
         <v>0</v>
@@ -8803,33 +8803,33 @@
         <v>3</v>
       </c>
       <c r="J78" s="10">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="K78" s="10">
-        <v>5569919.9248531396</v>
+        <v>8838437.0925082453</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A79" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="B79" s="1">
+      <c r="B79" s="10">
+        <v>584</v>
+      </c>
+      <c r="C79" s="10">
+        <v>1</v>
+      </c>
+      <c r="D79" s="10">
+        <v>1</v>
+      </c>
+      <c r="E79" s="10">
+        <v>924</v>
+      </c>
+      <c r="F79" s="10">
+        <v>6750615.9754769709</v>
+      </c>
+      <c r="G79" s="10">
         <v>587</v>
-      </c>
-      <c r="C79" s="1">
-        <v>0</v>
-      </c>
-      <c r="D79" s="1">
-        <v>2</v>
-      </c>
-      <c r="E79" s="1">
-        <v>906</v>
-      </c>
-      <c r="F79" s="10">
-        <v>4337037.0864686901</v>
-      </c>
-      <c r="G79" s="10">
-        <v>585</v>
       </c>
       <c r="H79" s="10">
         <v>3</v>
@@ -8838,33 +8838,33 @@
         <v>1</v>
       </c>
       <c r="J79" s="10">
-        <v>1265</v>
+        <v>698</v>
       </c>
       <c r="K79" s="10">
-        <v>4940735.7756936448</v>
+        <v>7890411.4936368279</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A80" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B80" s="1">
-        <v>446</v>
-      </c>
-      <c r="C80" s="1">
-        <v>1</v>
-      </c>
-      <c r="D80" s="1">
-        <v>4</v>
-      </c>
-      <c r="E80" s="1">
-        <v>387</v>
+      <c r="B80" s="10">
+        <v>449</v>
+      </c>
+      <c r="C80" s="10">
+        <v>2</v>
+      </c>
+      <c r="D80" s="10">
+        <v>5</v>
+      </c>
+      <c r="E80" s="10">
+        <v>355</v>
       </c>
       <c r="F80" s="10">
-        <v>5003494.0996635016</v>
+        <v>7653920.359339037</v>
       </c>
       <c r="G80" s="10">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="H80" s="10">
         <v>0</v>
@@ -8873,243 +8873,243 @@
         <v>7</v>
       </c>
       <c r="J80" s="10">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="K80" s="10">
-        <v>5325255.3244800083</v>
+        <v>8390126.8830564395</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A81" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B81" s="1">
-        <v>968</v>
-      </c>
-      <c r="C81" s="1">
-        <v>0</v>
-      </c>
-      <c r="D81" s="1">
-        <v>5</v>
-      </c>
-      <c r="E81" s="1">
-        <v>834</v>
+      <c r="B81" s="10">
+        <v>971</v>
+      </c>
+      <c r="C81" s="10">
+        <v>1</v>
+      </c>
+      <c r="D81" s="10">
+        <v>4</v>
+      </c>
+      <c r="E81" s="10">
+        <v>691</v>
       </c>
       <c r="F81" s="10">
-        <v>14599105.463165892</v>
+        <v>21521164.578006919</v>
       </c>
       <c r="G81" s="10">
-        <v>969</v>
+        <v>955</v>
       </c>
       <c r="H81" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I81" s="10">
         <v>3</v>
       </c>
       <c r="J81" s="10">
-        <v>730</v>
+        <v>672</v>
       </c>
       <c r="K81" s="10">
-        <v>13331666.494566012</v>
+        <v>20746372.803316668</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A82" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B82" s="1">
-        <v>789</v>
-      </c>
-      <c r="C82" s="1">
-        <v>1</v>
-      </c>
-      <c r="D82" s="1">
+      <c r="B82" s="10">
+        <v>792</v>
+      </c>
+      <c r="C82" s="10">
+        <v>1</v>
+      </c>
+      <c r="D82" s="10">
         <v>10</v>
       </c>
-      <c r="E82" s="1">
-        <v>761</v>
+      <c r="E82" s="10">
+        <v>814</v>
       </c>
       <c r="F82" s="10">
-        <v>8574263.9764997829</v>
+        <v>13363157.032803241</v>
       </c>
       <c r="G82" s="10">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="H82" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I82" s="10">
         <v>10</v>
       </c>
       <c r="J82" s="10">
-        <v>711</v>
+        <v>741</v>
       </c>
       <c r="K82" s="10">
-        <v>8108231.6625237344</v>
+        <v>13054902.089641485</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A83" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B83" s="1">
-        <v>907</v>
-      </c>
-      <c r="C83" s="1">
-        <v>0</v>
-      </c>
-      <c r="D83" s="1">
-        <v>2</v>
-      </c>
-      <c r="E83" s="1">
-        <v>939</v>
+      <c r="B83" s="10">
+        <v>922</v>
+      </c>
+      <c r="C83" s="10">
+        <v>0</v>
+      </c>
+      <c r="D83" s="10">
+        <v>2</v>
+      </c>
+      <c r="E83" s="10">
+        <v>863</v>
       </c>
       <c r="F83" s="10">
-        <v>6657424.7365432037</v>
+        <v>10535619.815227035</v>
       </c>
       <c r="G83" s="10">
-        <v>960</v>
+        <v>972</v>
       </c>
       <c r="H83" s="10">
         <v>1</v>
       </c>
       <c r="I83" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J83" s="10">
         <v>1215</v>
       </c>
       <c r="K83" s="10">
-        <v>7256682.7153262254</v>
+        <v>11489184.409651188</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A84" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B84" s="1">
-        <v>1021</v>
-      </c>
-      <c r="C84" s="1">
-        <v>1</v>
-      </c>
-      <c r="D84" s="1">
-        <v>4</v>
-      </c>
-      <c r="E84" s="1">
-        <v>842</v>
+      <c r="B84" s="10">
+        <v>1012</v>
+      </c>
+      <c r="C84" s="10">
+        <v>3</v>
+      </c>
+      <c r="D84" s="10">
+        <v>4</v>
+      </c>
+      <c r="E84" s="10">
+        <v>816</v>
       </c>
       <c r="F84" s="10">
-        <v>7511852.493724742</v>
+        <v>12029136.598088751</v>
       </c>
       <c r="G84" s="10">
-        <v>997</v>
+        <v>1006</v>
       </c>
       <c r="H84" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I84" s="10">
         <v>4</v>
       </c>
       <c r="J84" s="10">
-        <v>20</v>
+        <v>688</v>
       </c>
       <c r="K84" s="10">
-        <v>4702680.6416437216</v>
+        <v>8436359.6429892965</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A85" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B85" s="1">
-        <v>734</v>
-      </c>
-      <c r="C85" s="1">
-        <v>1</v>
-      </c>
-      <c r="D85" s="1">
+      <c r="B85" s="10">
+        <v>739</v>
+      </c>
+      <c r="C85" s="10">
+        <v>1</v>
+      </c>
+      <c r="D85" s="10">
         <v>5</v>
       </c>
-      <c r="E85" s="1">
-        <v>697</v>
+      <c r="E85" s="10">
+        <v>723</v>
       </c>
       <c r="F85" s="10">
-        <v>7143614.790428766</v>
+        <v>12058816.101821585</v>
       </c>
       <c r="G85" s="10">
-        <v>730</v>
+        <v>744</v>
       </c>
       <c r="H85" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85" s="10">
         <v>6</v>
       </c>
       <c r="J85" s="10">
-        <v>742</v>
+        <v>831</v>
       </c>
       <c r="K85" s="10">
-        <v>7522930.9770057639</v>
+        <v>12570353.635213269</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A86" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="B86" s="1">
+      <c r="B86" s="10">
+        <v>570</v>
+      </c>
+      <c r="C86" s="10">
+        <v>1</v>
+      </c>
+      <c r="D86" s="10">
+        <v>1</v>
+      </c>
+      <c r="E86" s="10">
+        <v>686</v>
+      </c>
+      <c r="F86" s="10">
+        <v>6345447.8126080902</v>
+      </c>
+      <c r="G86" s="10">
+        <v>570</v>
+      </c>
+      <c r="H86" s="10">
+        <v>0</v>
+      </c>
+      <c r="I86" s="10">
+        <v>1</v>
+      </c>
+      <c r="J86" s="10">
         <v>575</v>
       </c>
-      <c r="C86" s="1">
-        <v>1</v>
-      </c>
-      <c r="D86" s="1">
-        <v>1</v>
-      </c>
-      <c r="E86" s="1">
-        <v>609</v>
-      </c>
-      <c r="F86" s="10">
-        <v>4147371.3965030778</v>
-      </c>
-      <c r="G86" s="10">
-        <v>579</v>
-      </c>
-      <c r="H86" s="10">
-        <v>0</v>
-      </c>
-      <c r="I86" s="10">
-        <v>1</v>
-      </c>
-      <c r="J86" s="10">
-        <v>764</v>
-      </c>
       <c r="K86" s="10">
-        <v>4156463.0287198988</v>
+        <v>6485541.9481432578</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A87" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="B87" s="1">
-        <v>1709</v>
-      </c>
-      <c r="C87" s="1">
-        <v>1</v>
-      </c>
-      <c r="D87" s="1">
+      <c r="B87" s="10">
+        <v>1710</v>
+      </c>
+      <c r="C87" s="10">
+        <v>3</v>
+      </c>
+      <c r="D87" s="10">
         <v>10</v>
       </c>
-      <c r="E87" s="1">
-        <v>1330</v>
+      <c r="E87" s="10">
+        <v>1262</v>
       </c>
       <c r="F87" s="10">
-        <v>15155946.089206984</v>
+        <v>24330358.382188115</v>
       </c>
       <c r="G87" s="10">
-        <v>1728</v>
+        <v>1749</v>
       </c>
       <c r="H87" s="10">
         <v>0</v>
@@ -9118,33 +9118,33 @@
         <v>10</v>
       </c>
       <c r="J87" s="10">
-        <v>1218</v>
+        <v>1231</v>
       </c>
       <c r="K87" s="10">
-        <v>15539415.573069196</v>
+        <v>24951429.425259337</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A88" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B88" s="1">
-        <v>688</v>
-      </c>
-      <c r="C88" s="1">
-        <v>2</v>
-      </c>
-      <c r="D88" s="1">
+      <c r="B88" s="10">
+        <v>664</v>
+      </c>
+      <c r="C88" s="10">
+        <v>2</v>
+      </c>
+      <c r="D88" s="10">
         <v>3</v>
       </c>
-      <c r="E88" s="1">
-        <v>755</v>
+      <c r="E88" s="10">
+        <v>631</v>
       </c>
       <c r="F88" s="10">
-        <v>4716414.244273073</v>
+        <v>6599894.3574415911</v>
       </c>
       <c r="G88" s="10">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="H88" s="10">
         <v>0</v>
@@ -9153,33 +9153,33 @@
         <v>3</v>
       </c>
       <c r="J88" s="10">
-        <v>862</v>
+        <v>668</v>
       </c>
       <c r="K88" s="10">
-        <v>3439065.9601564072</v>
+        <v>5256040.7605468342</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A89" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="B89" s="1">
-        <v>629</v>
-      </c>
-      <c r="C89" s="1">
-        <v>9</v>
-      </c>
-      <c r="D89" s="1">
+      <c r="B89" s="10">
+        <v>616</v>
+      </c>
+      <c r="C89" s="10">
+        <v>10</v>
+      </c>
+      <c r="D89" s="10">
         <v>6</v>
       </c>
-      <c r="E89" s="1">
-        <v>570</v>
+      <c r="E89" s="10">
+        <v>494</v>
       </c>
       <c r="F89" s="10">
-        <v>8023492.5817246111</v>
+        <v>11603173.468591984</v>
       </c>
       <c r="G89" s="10">
-        <v>601</v>
+        <v>620</v>
       </c>
       <c r="H89" s="10">
         <v>3</v>
@@ -9188,45 +9188,45 @@
         <v>7</v>
       </c>
       <c r="J89" s="10">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="K89" s="10">
-        <v>7587961.4134114794</v>
+        <v>12085662.536187533</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A90" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B90" s="1">
-        <v>357</v>
-      </c>
-      <c r="C90" s="1">
-        <v>1</v>
-      </c>
-      <c r="D90" s="1">
-        <v>0</v>
-      </c>
-      <c r="E90" s="1">
-        <v>445</v>
+      <c r="B90" s="10">
+        <v>362</v>
+      </c>
+      <c r="C90" s="10">
+        <v>1</v>
+      </c>
+      <c r="D90" s="10">
+        <v>0</v>
+      </c>
+      <c r="E90" s="10">
+        <v>304</v>
       </c>
       <c r="F90" s="10">
-        <v>2442094.5526837292</v>
+        <v>3559231.8746322528</v>
       </c>
       <c r="G90" s="10">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="H90" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90" s="10">
         <v>0</v>
       </c>
       <c r="J90" s="10">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="K90" s="10">
-        <v>2185891.8143150499</v>
+        <v>3096779.6955845412</v>
       </c>
     </row>
   </sheetData>

--- a/SITE MONITORING.xlsx
+++ b/SITE MONITORING.xlsx
@@ -1114,19 +1114,19 @@
       </c>
       <c r="F2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6059382.1473084744</v>
+        <v>6721217.3677318636</v>
       </c>
       <c r="G2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5415574.0184972491</v>
+        <v>6152818.0823086826</v>
       </c>
       <c r="H2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>620</v>
+        <v>331</v>
       </c>
       <c r="I2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>379</v>
+        <v>336</v>
       </c>
       <c r="J2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1146,11 +1146,11 @@
       </c>
       <c r="N2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="O2">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="P2">
         <v>3</v>
@@ -1174,19 +1174,19 @@
       </c>
       <c r="F3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7288506.4151363429</v>
+        <v>8156654.6793239554</v>
       </c>
       <c r="G3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6653085.5256644776</v>
+        <v>7429191.778023608</v>
       </c>
       <c r="H3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>614</v>
+        <v>577</v>
       </c>
       <c r="I3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="J3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1206,11 +1206,11 @@
       </c>
       <c r="N3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>686</v>
+        <v>675</v>
       </c>
       <c r="O3">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="P3">
         <v>2</v>
@@ -1234,19 +1234,19 @@
       </c>
       <c r="F4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6371310.9355353834</v>
+        <v>7399552.3442232348</v>
       </c>
       <c r="G4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6613502.6668428723</v>
+        <v>7950360.3691030573</v>
       </c>
       <c r="H4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>667</v>
+        <v>697</v>
       </c>
       <c r="I4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>745</v>
+        <v>703</v>
       </c>
       <c r="J4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1262,11 +1262,11 @@
       </c>
       <c r="M4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="O4">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -1294,19 +1294,19 @@
       </c>
       <c r="F5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14068595.525211383</v>
+        <v>15552827.417094398</v>
       </c>
       <c r="G5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13913394.68100726</v>
+        <v>15725446.023067832</v>
       </c>
       <c r="H5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>760</v>
+        <v>980</v>
       </c>
       <c r="I5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>998</v>
+        <v>1029</v>
       </c>
       <c r="J5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1326,11 +1326,11 @@
       </c>
       <c r="N5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1197</v>
+        <v>1200</v>
       </c>
       <c r="O5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="P5">
         <v>3</v>
@@ -1354,19 +1354,19 @@
       </c>
       <c r="F6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5121540.0843401868</v>
+        <v>5858964.4469372071</v>
       </c>
       <c r="G6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5839432.1316437609</v>
+        <v>6781752.4824333154</v>
       </c>
       <c r="H6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>315</v>
+        <v>337</v>
       </c>
       <c r="I6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>419</v>
+        <v>356</v>
       </c>
       <c r="J6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1386,11 +1386,11 @@
       </c>
       <c r="N6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="O6">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="P6">
         <v>3</v>
@@ -1414,19 +1414,19 @@
       </c>
       <c r="F7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5394052.5405044062</v>
+        <v>5921570.4369004704</v>
       </c>
       <c r="G7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5345165.618633477</v>
+        <v>5992231.4276800314</v>
       </c>
       <c r="H7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>431</v>
+        <v>356</v>
       </c>
       <c r="I7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="J7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1446,11 +1446,11 @@
       </c>
       <c r="N7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="O7">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P7">
         <v>2</v>
@@ -1474,19 +1474,19 @@
       </c>
       <c r="F8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6272003.9840085637</v>
+        <v>6799052.3254508786</v>
       </c>
       <c r="G8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5990321.0092403321</v>
+        <v>6874438.380801552</v>
       </c>
       <c r="H8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1167</v>
+        <v>525</v>
       </c>
       <c r="I8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>483</v>
+        <v>512</v>
       </c>
       <c r="J8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="K8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -1506,11 +1506,11 @@
       </c>
       <c r="N8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="O8">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="P8">
         <v>9</v>
@@ -1534,19 +1534,19 @@
       </c>
       <c r="F9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>2610227.0540075419</v>
+        <v>2979868.2358265291</v>
       </c>
       <c r="G9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>2744967.7764228848</v>
+        <v>3098186.935847898</v>
       </c>
       <c r="H9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>138</v>
+        <v>172</v>
       </c>
       <c r="I9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="K9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -1566,11 +1566,11 @@
       </c>
       <c r="N9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="O9">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="P9">
         <v>1</v>
@@ -1594,19 +1594,19 @@
       </c>
       <c r="F10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>2761713.1927333758</v>
+        <v>3006238.1098317681</v>
       </c>
       <c r="G10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>267968.35746859002</v>
+        <v>268270.17518669402</v>
       </c>
       <c r="H10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="I10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1626,11 +1626,11 @@
       </c>
       <c r="N10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="O10">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="P10">
         <v>1</v>
@@ -1654,19 +1654,19 @@
       </c>
       <c r="F11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4379782.4858754724</v>
+        <v>4782564.6090684468</v>
       </c>
       <c r="G11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5948859.3354461109</v>
+        <v>6812954.8209106149</v>
       </c>
       <c r="H11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>363</v>
+        <v>286</v>
       </c>
       <c r="I11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>542</v>
+        <v>509</v>
       </c>
       <c r="J11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1686,11 +1686,11 @@
       </c>
       <c r="N11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="O11">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="P11">
         <v>4</v>
@@ -1714,19 +1714,19 @@
       </c>
       <c r="F12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>1995774.4805199029</v>
+        <v>2250565.6269620662</v>
       </c>
       <c r="G12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>2625962.4150365731</v>
+        <v>2959702.482844451</v>
       </c>
       <c r="H12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>212</v>
+        <v>321</v>
       </c>
       <c r="I12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>578</v>
+        <v>273</v>
       </c>
       <c r="J12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1746,11 +1746,11 @@
       </c>
       <c r="N12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="O12">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="P12">
         <v>3</v>
@@ -1774,19 +1774,19 @@
       </c>
       <c r="F13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>2676274.3626946318</v>
+        <v>3008058.056240594</v>
       </c>
       <c r="G13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>2935154.1349404189</v>
+        <v>3318437.6932629938</v>
       </c>
       <c r="H13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="I13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>244</v>
+        <v>219</v>
       </c>
       <c r="J13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="L13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -1806,11 +1806,11 @@
       </c>
       <c r="N13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O13">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="P13">
         <v>5</v>
@@ -1834,19 +1834,19 @@
       </c>
       <c r="F14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7510668.6871368838</v>
+        <v>7512189.1632019328</v>
       </c>
       <c r="G14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8711554.6449297052</v>
+        <v>9987199.9195197597</v>
       </c>
       <c r="H14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>121</v>
+        <v>48</v>
       </c>
       <c r="I14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>802</v>
+        <v>867</v>
       </c>
       <c r="J14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1866,11 +1866,11 @@
       </c>
       <c r="N14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1454</v>
+        <v>1445</v>
       </c>
       <c r="O14">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="P14">
         <v>2</v>
@@ -1894,19 +1894,19 @@
       </c>
       <c r="F15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18218164.868068825</v>
+        <v>21031434.832303733</v>
       </c>
       <c r="G15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19264893.816357184</v>
+        <v>21848454.097331937</v>
       </c>
       <c r="H15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1045</v>
+        <v>1281</v>
       </c>
       <c r="I15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>881</v>
+        <v>896</v>
       </c>
       <c r="J15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="K15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -1926,11 +1926,11 @@
       </c>
       <c r="N15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="O15">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1240</v>
+        <v>1234</v>
       </c>
       <c r="P15">
         <v>4</v>
@@ -1954,19 +1954,19 @@
       </c>
       <c r="F16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11271211.941410139</v>
+        <v>12464962.956552835</v>
       </c>
       <c r="G16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11477126.439976607</v>
+        <v>12945342.206328144</v>
       </c>
       <c r="H16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>920</v>
+        <v>909</v>
       </c>
       <c r="I16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="J16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1982,15 +1982,15 @@
       </c>
       <c r="M16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="O16">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="P16">
         <v>3</v>
@@ -2014,19 +2014,19 @@
       </c>
       <c r="F17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12072562.882114958</v>
+        <v>13216752.071126426</v>
       </c>
       <c r="G17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7647194.0438168291</v>
+        <v>8571431.2894174531</v>
       </c>
       <c r="H17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>678</v>
+        <v>636</v>
       </c>
       <c r="I17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>696</v>
+        <v>726</v>
       </c>
       <c r="J17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="K17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2046,11 +2046,11 @@
       </c>
       <c r="N17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="O17">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="P17">
         <v>4</v>
@@ -2074,19 +2074,19 @@
       </c>
       <c r="F18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>39301193.021534018</v>
+        <v>43765663.42008768</v>
       </c>
       <c r="G18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>43058855.414458841</v>
+        <v>49075557.599973261</v>
       </c>
       <c r="H18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2028</v>
+        <v>2035</v>
       </c>
       <c r="I18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2890</v>
+        <v>2900</v>
       </c>
       <c r="J18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2098,19 +2098,19 @@
       </c>
       <c r="L18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2819</v>
+        <v>2802</v>
       </c>
       <c r="O18">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2980</v>
+        <v>2942</v>
       </c>
       <c r="P18">
         <v>5</v>
@@ -2134,11 +2134,11 @@
       </c>
       <c r="F19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21548491.261211187</v>
+        <v>24021205.021760464</v>
       </c>
       <c r="G19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8067116.426811154</v>
+        <v>8067116.1734909713</v>
       </c>
       <c r="H19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="I19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2166,11 +2166,11 @@
       </c>
       <c r="N19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="O19">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1375</v>
+        <v>1367</v>
       </c>
       <c r="P19">
         <v>1</v>
@@ -2194,19 +2194,19 @@
       </c>
       <c r="F20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>41412282.042329848</v>
+        <v>46803671.881852701</v>
       </c>
       <c r="G20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>42204564.094008639</v>
+        <v>47738508.937325202</v>
       </c>
       <c r="H20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2306</v>
+        <v>2383</v>
       </c>
       <c r="I20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2202</v>
+        <v>2214</v>
       </c>
       <c r="J20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2218,19 +2218,19 @@
       </c>
       <c r="L20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2982</v>
+        <v>2984</v>
       </c>
       <c r="O20">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2961</v>
+        <v>2962</v>
       </c>
       <c r="P20">
         <v>8</v>
@@ -2254,19 +2254,19 @@
       </c>
       <c r="F21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6074404.571538738</v>
+        <v>6796338.2171994355</v>
       </c>
       <c r="G21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6415129.7986748964</v>
+        <v>7122002.4557506125</v>
       </c>
       <c r="H21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>480</v>
+        <v>463</v>
       </c>
       <c r="I21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>534</v>
+        <v>515</v>
       </c>
       <c r="J21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2286,11 +2286,11 @@
       </c>
       <c r="N21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="O21">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P21">
         <v>1</v>
@@ -2314,19 +2314,19 @@
       </c>
       <c r="F22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17223155.15647522</v>
+        <v>18988796.478382163</v>
       </c>
       <c r="G22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17223861.127960525</v>
+        <v>19306182.14601028</v>
       </c>
       <c r="H22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1286</v>
+        <v>1251</v>
       </c>
       <c r="I22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1282</v>
+        <v>1334</v>
       </c>
       <c r="J22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="K22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2342,15 +2342,15 @@
       </c>
       <c r="M22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1702</v>
+        <v>1709</v>
       </c>
       <c r="O22">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="P22">
         <v>8</v>
@@ -2374,19 +2374,19 @@
       </c>
       <c r="F23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7606090.3029235201</v>
+        <v>8482004.1993926615</v>
       </c>
       <c r="G23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6991287.7517503034</v>
+        <v>7846298.3074562633</v>
       </c>
       <c r="H23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>762</v>
+        <v>826</v>
       </c>
       <c r="I23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>792</v>
+        <v>766</v>
       </c>
       <c r="J23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="N23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="O23">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -2434,19 +2434,19 @@
       </c>
       <c r="F24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7771830.7785125766</v>
+        <v>8755237.1310375761</v>
       </c>
       <c r="G24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8945717.278125396</v>
+        <v>9960916.6373697724</v>
       </c>
       <c r="H24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>846</v>
+        <v>570</v>
       </c>
       <c r="I24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>731</v>
+        <v>757</v>
       </c>
       <c r="J24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="N24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>902</v>
+        <v>896</v>
       </c>
       <c r="O24">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -2494,19 +2494,19 @@
       </c>
       <c r="F25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>2280396.1807618379</v>
+        <v>2560118.3425952001</v>
       </c>
       <c r="G25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>1898558.2643888111</v>
+        <v>2055834.390430477</v>
       </c>
       <c r="H25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="I25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2554</v>
+        <v>146</v>
       </c>
       <c r="J25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="K25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2526,11 +2526,11 @@
       </c>
       <c r="N25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="O25">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="P25">
         <v>1</v>
@@ -2554,19 +2554,19 @@
       </c>
       <c r="F26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20642472.561316367</v>
+        <v>22718777.941925272</v>
       </c>
       <c r="G26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16597899.852037497</v>
+        <v>18674864.213929038</v>
       </c>
       <c r="H26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1477</v>
+        <v>1514</v>
       </c>
       <c r="I26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1372</v>
+        <v>1398</v>
       </c>
       <c r="J26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2586,11 +2586,11 @@
       </c>
       <c r="N26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1654</v>
+        <v>1663</v>
       </c>
       <c r="O26">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1653</v>
+        <v>1661</v>
       </c>
       <c r="P26">
         <v>1</v>
@@ -2614,19 +2614,19 @@
       </c>
       <c r="F27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12615973.394648995</v>
+        <v>14153077.91888571</v>
       </c>
       <c r="G27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12917264.245188372</v>
+        <v>14551107.043437852</v>
       </c>
       <c r="H27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>677</v>
+        <v>648</v>
       </c>
       <c r="I27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>816</v>
+        <v>617</v>
       </c>
       <c r="J27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2642,15 +2642,15 @@
       </c>
       <c r="M27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="O27">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>874</v>
+        <v>863</v>
       </c>
       <c r="P27">
         <v>1</v>
@@ -2674,19 +2674,19 @@
       </c>
       <c r="F28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14123223.678253656</v>
+        <v>15725447.580771975</v>
       </c>
       <c r="G28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12597981.049125759</v>
+        <v>14437291.715968899</v>
       </c>
       <c r="H28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>762</v>
+        <v>733</v>
       </c>
       <c r="I28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2706,11 +2706,11 @@
       </c>
       <c r="N28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="O28">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -2734,19 +2734,19 @@
       </c>
       <c r="F29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17457947.394665383</v>
+        <v>19703437.006434254</v>
       </c>
       <c r="G29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17664552.96019372</v>
+        <v>20056812.599486277</v>
       </c>
       <c r="H29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>908</v>
+        <v>967</v>
       </c>
       <c r="I29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>879</v>
+        <v>864</v>
       </c>
       <c r="J29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2766,11 +2766,11 @@
       </c>
       <c r="N29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1105</v>
+        <v>1111</v>
       </c>
       <c r="O29">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1111</v>
+        <v>1116</v>
       </c>
       <c r="P29">
         <v>1</v>
@@ -2794,19 +2794,19 @@
       </c>
       <c r="F30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>26720855.442626528</v>
+        <v>29722501.854668796</v>
       </c>
       <c r="G30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>24955672.140388235</v>
+        <v>28294835.68957008</v>
       </c>
       <c r="H30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1152</v>
+        <v>1178</v>
       </c>
       <c r="I30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1077</v>
+        <v>1146</v>
       </c>
       <c r="J30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2822,15 +2822,15 @@
       </c>
       <c r="M30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="O30">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1472</v>
+        <v>1478</v>
       </c>
       <c r="P30">
         <v>4</v>
@@ -2854,19 +2854,19 @@
       </c>
       <c r="F31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9677957.3193788044</v>
+        <v>10980480.649050532</v>
       </c>
       <c r="G31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10225048.001245813</v>
+        <v>11557874.043439522</v>
       </c>
       <c r="H31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>487</v>
+        <v>528</v>
       </c>
       <c r="I31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="J31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2886,11 +2886,11 @@
       </c>
       <c r="N31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="O31">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="P31">
         <v>3</v>
@@ -2914,19 +2914,19 @@
       </c>
       <c r="F32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>31206440.608555064</v>
+        <v>35060631.354011633</v>
       </c>
       <c r="G32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>31195786.901903056</v>
+        <v>35288715.200185522</v>
       </c>
       <c r="H32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1734</v>
+        <v>1770</v>
       </c>
       <c r="I32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1550</v>
+        <v>1579</v>
       </c>
       <c r="J32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2942,11 +2942,11 @@
       </c>
       <c r="M32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="O32">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -2974,19 +2974,19 @@
       </c>
       <c r="F33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11118207.377145017</v>
+        <v>12333157.928200064</v>
       </c>
       <c r="G33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10306463.021471065</v>
+        <v>11529791.435436616</v>
       </c>
       <c r="H33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>703</v>
+        <v>674</v>
       </c>
       <c r="I33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>645</v>
+        <v>696</v>
       </c>
       <c r="J33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="L33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3006,11 +3006,11 @@
       </c>
       <c r="N33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="O33">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="P33">
         <v>3</v>
@@ -3034,19 +3034,19 @@
       </c>
       <c r="F34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9306095.0251620207</v>
+        <v>10103964.004989509</v>
       </c>
       <c r="G34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9952856.9297330845</v>
+        <v>11112334.557640174</v>
       </c>
       <c r="H34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>418</v>
+        <v>459</v>
       </c>
       <c r="I34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>525</v>
+        <v>557</v>
       </c>
       <c r="J34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3066,11 +3066,11 @@
       </c>
       <c r="N34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="O34">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>718</v>
+        <v>732</v>
       </c>
       <c r="P34">
         <v>4</v>
@@ -3094,19 +3094,19 @@
       </c>
       <c r="F35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16122199.413593575</v>
+        <v>17854652.580006875</v>
       </c>
       <c r="G35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15241628.231743544</v>
+        <v>17193856.285997957</v>
       </c>
       <c r="H35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>798</v>
+        <v>872</v>
       </c>
       <c r="I35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>852</v>
+        <v>836</v>
       </c>
       <c r="J35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3118,19 +3118,19 @@
       </c>
       <c r="L35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1131</v>
+        <v>1122</v>
       </c>
       <c r="O35">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1171</v>
+        <v>1176</v>
       </c>
       <c r="P35">
         <v>13</v>
@@ -3154,19 +3154,19 @@
       </c>
       <c r="F36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15445962.516069006</v>
+        <v>17212785.665607128</v>
       </c>
       <c r="G36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13827542.353898088</v>
+        <v>15645497.955338975</v>
       </c>
       <c r="H36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>959</v>
+        <v>869</v>
       </c>
       <c r="I36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>829</v>
+        <v>769</v>
       </c>
       <c r="J36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3186,11 +3186,11 @@
       </c>
       <c r="N36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1200</v>
+        <v>1183</v>
       </c>
       <c r="O36">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1390</v>
+        <v>1365</v>
       </c>
       <c r="P36">
         <v>4</v>
@@ -3214,19 +3214,19 @@
       </c>
       <c r="F37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24434713.31977386</v>
+        <v>27010112.979283512</v>
       </c>
       <c r="G37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>25291639.249637514</v>
+        <v>28638765.273579638</v>
       </c>
       <c r="H37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1411</v>
+        <v>1382</v>
       </c>
       <c r="I37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1498</v>
+        <v>1439</v>
       </c>
       <c r="J37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="L37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3246,11 +3246,11 @@
       </c>
       <c r="N37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1844</v>
+        <v>1840</v>
       </c>
       <c r="O37">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2522</v>
+        <v>2469</v>
       </c>
       <c r="P37">
         <v>16</v>
@@ -3274,19 +3274,19 @@
       </c>
       <c r="F38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10078150.216247274</v>
+        <v>11241543.166229179</v>
       </c>
       <c r="G38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9191077.4228783716</v>
+        <v>10344833.566559069</v>
       </c>
       <c r="H38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="I38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>412</v>
+        <v>466</v>
       </c>
       <c r="J38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3306,11 +3306,11 @@
       </c>
       <c r="N38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="O38">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="P38">
         <v>3</v>
@@ -3334,19 +3334,19 @@
       </c>
       <c r="F39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>27864970.025229905</v>
+        <v>30939701.804248367</v>
       </c>
       <c r="G39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>31007988.562648121</v>
+        <v>34562600.775030553</v>
       </c>
       <c r="H39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1778</v>
+        <v>1917</v>
       </c>
       <c r="I39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1826</v>
+        <v>1934</v>
       </c>
       <c r="J39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3366,11 +3366,11 @@
       </c>
       <c r="N39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="O39">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2057</v>
+        <v>2049</v>
       </c>
       <c r="P39">
         <v>4</v>
@@ -3394,19 +3394,19 @@
       </c>
       <c r="F40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19342823.481627457</v>
+        <v>21592902.705368832</v>
       </c>
       <c r="G40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19825792.805345695</v>
+        <v>22304769.355051536</v>
       </c>
       <c r="H40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>731</v>
+        <v>743</v>
       </c>
       <c r="I40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>753</v>
+        <v>797</v>
       </c>
       <c r="J40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3426,11 +3426,11 @@
       </c>
       <c r="N40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="O40">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="P40">
         <v>3</v>
@@ -3454,19 +3454,19 @@
       </c>
       <c r="F41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17597530.510886051</v>
+        <v>19361417.568360262</v>
       </c>
       <c r="G41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8542291.4264150988</v>
+        <v>10411236.41967774</v>
       </c>
       <c r="H41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="I41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>918</v>
+        <v>925</v>
       </c>
       <c r="J41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3486,11 +3486,11 @@
       </c>
       <c r="N41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1146</v>
+        <v>1154</v>
       </c>
       <c r="O41">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="P41">
         <v>4</v>
@@ -3514,19 +3514,19 @@
       </c>
       <c r="F42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16323094.491309352</v>
+        <v>18232693.534131359</v>
       </c>
       <c r="G42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15660058.036465179</v>
+        <v>17755224.245391376</v>
       </c>
       <c r="H42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>608</v>
+        <v>630</v>
       </c>
       <c r="I42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>597</v>
+        <v>645</v>
       </c>
       <c r="J42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3542,11 +3542,11 @@
       </c>
       <c r="M42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="O42">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -3574,19 +3574,19 @@
       </c>
       <c r="F43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9307002.4168394431</v>
+        <v>10453278.752228426</v>
       </c>
       <c r="G43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9999788.4775667209</v>
+        <v>11363931.519229412</v>
       </c>
       <c r="H43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>547</v>
+        <v>600</v>
       </c>
       <c r="I43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="J43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3606,11 +3606,11 @@
       </c>
       <c r="N43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="O43">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="P43">
         <v>2</v>
@@ -3634,19 +3634,19 @@
       </c>
       <c r="F44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9148288.1945246682</v>
+        <v>10321050.736769276</v>
       </c>
       <c r="G44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8607899.5225225668</v>
+        <v>9780767.8360642996</v>
       </c>
       <c r="H44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>682</v>
+        <v>743</v>
       </c>
       <c r="I44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>696</v>
+        <v>744</v>
       </c>
       <c r="J44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="K44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -3666,11 +3666,11 @@
       </c>
       <c r="N44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="O44">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="P44">
         <v>3</v>
@@ -3694,19 +3694,19 @@
       </c>
       <c r="F45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>33294714.610988211</v>
+        <v>36614471.61384137</v>
       </c>
       <c r="G45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>27457832.858950939</v>
+        <v>30732060.500332795</v>
       </c>
       <c r="H45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1209</v>
+        <v>1018</v>
       </c>
       <c r="I45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1154</v>
+        <v>1127</v>
       </c>
       <c r="J45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="L45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3726,11 +3726,11 @@
       </c>
       <c r="N45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1276</v>
+        <v>1281</v>
       </c>
       <c r="O45">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="P45">
         <v>4</v>
@@ -3754,19 +3754,19 @@
       </c>
       <c r="F46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14593080.011471108</v>
+        <v>16076235.359384179</v>
       </c>
       <c r="G46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13251593.852497272</v>
+        <v>14733574.789885193</v>
       </c>
       <c r="H46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>925</v>
+        <v>882</v>
       </c>
       <c r="I46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>887</v>
+        <v>3212</v>
       </c>
       <c r="J46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3774,7 +3774,7 @@
       </c>
       <c r="K46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -3786,11 +3786,11 @@
       </c>
       <c r="N46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="O46">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="P46">
         <v>4</v>
@@ -3814,19 +3814,19 @@
       </c>
       <c r="F47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18552025.445382949</v>
+        <v>20734256.805620253</v>
       </c>
       <c r="G47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23392753.696536377</v>
+        <v>26407949.501988936</v>
       </c>
       <c r="H47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>946</v>
+        <v>1001</v>
       </c>
       <c r="I47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>958</v>
+        <v>1033</v>
       </c>
       <c r="J47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="L47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3846,11 +3846,11 @@
       </c>
       <c r="N47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="O47">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="P47">
         <v>6</v>
@@ -3874,19 +3874,19 @@
       </c>
       <c r="F48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9531210.9429570977</v>
+        <v>10925987.34804726</v>
       </c>
       <c r="G48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12215200.861652251</v>
+        <v>13673852.473286686</v>
       </c>
       <c r="H48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>369</v>
+        <v>392</v>
       </c>
       <c r="I48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="J48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3906,11 +3906,11 @@
       </c>
       <c r="N48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="O48">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="P48">
         <v>1</v>
@@ -3934,19 +3934,19 @@
       </c>
       <c r="F49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11573023.120887872</v>
+        <v>12764477.259903496</v>
       </c>
       <c r="G49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8993502.2004245669</v>
+        <v>10116058.890716156</v>
       </c>
       <c r="H49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>325</v>
+        <v>383</v>
       </c>
       <c r="I49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="J49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="O49">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="P49">
         <v>5</v>
@@ -3994,15 +3994,15 @@
       </c>
       <c r="F50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9065219.3768147286</v>
+        <v>9941003.7667885516</v>
       </c>
       <c r="G50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7672695.2189010149</v>
+        <v>8825567.6649791468</v>
       </c>
       <c r="H50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="I50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="L50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4026,11 +4026,11 @@
       </c>
       <c r="N50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O50">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="P50">
         <v>4</v>
@@ -4054,19 +4054,19 @@
       </c>
       <c r="F51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19252439.405621711</v>
+        <v>21509029.915585216</v>
       </c>
       <c r="G51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18272372.933828708</v>
+        <v>20653643.392732065</v>
       </c>
       <c r="H51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>902</v>
+        <v>969</v>
       </c>
       <c r="I51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="J51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4082,15 +4082,15 @@
       </c>
       <c r="M51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="O51">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="P51">
         <v>5</v>
@@ -4114,19 +4114,19 @@
       </c>
       <c r="F52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20212422.982229233</v>
+        <v>22333476.918126777</v>
       </c>
       <c r="G52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15381123.373330694</v>
+        <v>18249780.65836753</v>
       </c>
       <c r="H52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>820</v>
+        <v>1005</v>
       </c>
       <c r="I52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>976</v>
+        <v>891</v>
       </c>
       <c r="J52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4142,15 +4142,15 @@
       </c>
       <c r="M52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="O52">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="P52">
         <v>4</v>
@@ -4174,19 +4174,19 @@
       </c>
       <c r="F53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>27521319.010392979</v>
+        <v>30720766.019070383</v>
       </c>
       <c r="G53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>34698100.647447377</v>
+        <v>39207641.101986013</v>
       </c>
       <c r="H53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1619</v>
+        <v>1427</v>
       </c>
       <c r="I53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1483</v>
+        <v>1631</v>
       </c>
       <c r="J53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4202,15 +4202,15 @@
       </c>
       <c r="M53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2240</v>
+        <v>2229</v>
       </c>
       <c r="O53">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2055</v>
+        <v>2075</v>
       </c>
       <c r="P53">
         <v>8</v>
@@ -4234,19 +4234,19 @@
       </c>
       <c r="F54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9434418.3837709222</v>
+        <v>10654324.550770273</v>
       </c>
       <c r="G54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7707113.4334032862</v>
+        <v>8875675.9081516638</v>
       </c>
       <c r="H54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>513</v>
+        <v>554</v>
       </c>
       <c r="I54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="J54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4266,11 +4266,11 @@
       </c>
       <c r="N54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="O54">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>672</v>
+        <v>681</v>
       </c>
       <c r="P54">
         <v>2</v>
@@ -4294,19 +4294,19 @@
       </c>
       <c r="F55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13858244.856042204</v>
+        <v>15305923.087041697</v>
       </c>
       <c r="G55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13874918.72588186</v>
+        <v>15926711.477734976</v>
       </c>
       <c r="H55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>742</v>
+        <v>652</v>
       </c>
       <c r="I55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="J55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4322,15 +4322,15 @@
       </c>
       <c r="M55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="O55">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="P55">
         <v>6</v>
@@ -4354,19 +4354,19 @@
       </c>
       <c r="F56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11626890.823241539</v>
+        <v>12874140.232146041</v>
       </c>
       <c r="G56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8580104.8251491878</v>
+        <v>9823421.513111636</v>
       </c>
       <c r="H56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>622</v>
+        <v>594</v>
       </c>
       <c r="I56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>691</v>
+        <v>639</v>
       </c>
       <c r="J56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="O56">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="P56">
         <v>3</v>
@@ -4414,23 +4414,23 @@
       </c>
       <c r="F57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18581393.752516262</v>
+        <v>21103865.275950637</v>
       </c>
       <c r="G57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18789590.991508801</v>
+        <v>21418755.666532356</v>
       </c>
       <c r="H57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1203</v>
+        <v>1199</v>
       </c>
       <c r="I57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>928</v>
+        <v>999</v>
       </c>
       <c r="J57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -4446,11 +4446,11 @@
       </c>
       <c r="N57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="O57">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="P57">
         <v>3</v>
@@ -4474,19 +4474,19 @@
       </c>
       <c r="F58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24051078.007695895</v>
+        <v>27064315.72966738</v>
       </c>
       <c r="G58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22594833.46428778</v>
+        <v>25056798.087375559</v>
       </c>
       <c r="H58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1415</v>
+        <v>1500</v>
       </c>
       <c r="I58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1341</v>
+        <v>1429</v>
       </c>
       <c r="J58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4506,11 +4506,11 @@
       </c>
       <c r="N58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1321</v>
+        <v>1327</v>
       </c>
       <c r="O58">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1387</v>
+        <v>1399</v>
       </c>
       <c r="P58">
         <v>4</v>
@@ -4534,19 +4534,19 @@
       </c>
       <c r="F59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12751076.307971718</v>
+        <v>14085926.081406619</v>
       </c>
       <c r="G59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12643538.853697417</v>
+        <v>14375514.953195609</v>
       </c>
       <c r="H59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>715</v>
+        <v>732</v>
       </c>
       <c r="I59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="J59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="L59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4566,11 +4566,11 @@
       </c>
       <c r="N59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="O59">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="P59">
         <v>3</v>
@@ -4594,19 +4594,19 @@
       </c>
       <c r="F60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14810216.222912636</v>
+        <v>16366940.385502718</v>
       </c>
       <c r="G60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14171503.656152204</v>
+        <v>15961705.359798137</v>
       </c>
       <c r="H60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>502</v>
+        <v>440</v>
       </c>
       <c r="I60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>440</v>
+        <v>478</v>
       </c>
       <c r="J60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4618,19 +4618,19 @@
       </c>
       <c r="L60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="O60">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="P60">
         <v>8</v>
@@ -4654,19 +4654,19 @@
       </c>
       <c r="F61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>32404512.52197903</v>
+        <v>37059990.447955251</v>
       </c>
       <c r="G61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>45501282.296908557</v>
+        <v>51313919.349024072</v>
       </c>
       <c r="H61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1606</v>
+        <v>1596</v>
       </c>
       <c r="I61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1907</v>
+        <v>1633</v>
       </c>
       <c r="J61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="L61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4686,11 +4686,11 @@
       </c>
       <c r="N61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2029</v>
+        <v>2025</v>
       </c>
       <c r="O61">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="P61">
         <v>10</v>
@@ -4714,19 +4714,19 @@
       </c>
       <c r="F62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>33665873.670948178</v>
+        <v>37740310.665981181</v>
       </c>
       <c r="G62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>31666643.56758967</v>
+        <v>36316046.751808286</v>
       </c>
       <c r="H62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1130</v>
+        <v>1140</v>
       </c>
       <c r="I62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1135</v>
+        <v>1195</v>
       </c>
       <c r="J62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4738,19 +4738,19 @@
       </c>
       <c r="L62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1616</v>
+        <v>1622</v>
       </c>
       <c r="O62">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1572</v>
+        <v>1581</v>
       </c>
       <c r="P62">
         <v>9</v>
@@ -4774,19 +4774,19 @@
       </c>
       <c r="F63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21955038.147735532</v>
+        <v>24540614.424710989</v>
       </c>
       <c r="G63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21711289.52854608</v>
+        <v>24557087.2031748</v>
       </c>
       <c r="H63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="I63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>701</v>
+        <v>743</v>
       </c>
       <c r="J63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4806,11 +4806,11 @@
       </c>
       <c r="N63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="O63">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="P63">
         <v>4</v>
@@ -4834,19 +4834,19 @@
       </c>
       <c r="F64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>31196971.177899417</v>
+        <v>34664074.752712265</v>
       </c>
       <c r="G64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>32860185.916051608</v>
+        <v>36884990.167373955</v>
       </c>
       <c r="H64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1290</v>
+        <v>1336</v>
       </c>
       <c r="I64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1462</v>
+        <v>1387</v>
       </c>
       <c r="J64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4858,19 +4858,19 @@
       </c>
       <c r="L64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="N64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1879</v>
+        <v>1875</v>
       </c>
       <c r="O64">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2097</v>
+        <v>2104</v>
       </c>
       <c r="P64">
         <v>9</v>
@@ -4894,19 +4894,19 @@
       </c>
       <c r="F65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>2292405.9875394548</v>
+        <v>2621075.0989817032</v>
       </c>
       <c r="G65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>375644.44752447098</v>
+        <v>629491.53686487197</v>
       </c>
       <c r="H65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>212</v>
+        <v>293</v>
       </c>
       <c r="I65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="J65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4926,11 +4926,11 @@
       </c>
       <c r="N65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O65">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="P65">
         <v>3</v>
@@ -4954,19 +4954,19 @@
       </c>
       <c r="F66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>25616759.463998247</v>
+        <v>28226150.449650105</v>
       </c>
       <c r="G66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23897425.779863752</v>
+        <v>26876970.800084837</v>
       </c>
       <c r="H66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1689</v>
+        <v>1771</v>
       </c>
       <c r="I66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1868</v>
+        <v>1623</v>
       </c>
       <c r="J66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4986,11 +4986,11 @@
       </c>
       <c r="N66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1745</v>
+        <v>1751</v>
       </c>
       <c r="O66">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1672</v>
+        <v>1674</v>
       </c>
       <c r="P66">
         <v>6</v>
@@ -5014,19 +5014,19 @@
       </c>
       <c r="F67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9992649.6044265609</v>
+        <v>11149314.029646087</v>
       </c>
       <c r="G67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11330814.204616746</v>
+        <v>12473177.909479629</v>
       </c>
       <c r="H67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>603</v>
+        <v>553</v>
       </c>
       <c r="I67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>603</v>
+        <v>582</v>
       </c>
       <c r="J67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5046,11 +5046,11 @@
       </c>
       <c r="N67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="O67">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="P67">
         <v>3</v>
@@ -5074,19 +5074,19 @@
       </c>
       <c r="F68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17067513.194088787</v>
+        <v>18811212.930350754</v>
       </c>
       <c r="G68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15742610.95808477</v>
+        <v>17738676.445421282</v>
       </c>
       <c r="H68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1182</v>
+        <v>899</v>
       </c>
       <c r="I68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>844</v>
+        <v>946</v>
       </c>
       <c r="J68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5106,11 +5106,11 @@
       </c>
       <c r="N68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="O68">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1370</v>
+        <v>1365</v>
       </c>
       <c r="P68">
         <v>3</v>
@@ -5134,19 +5134,19 @@
       </c>
       <c r="F69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8171514.3711125841</v>
+        <v>9657810.5725929085</v>
       </c>
       <c r="G69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11909259.237161091</v>
+        <v>12929426.00816833</v>
       </c>
       <c r="H69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1789</v>
+        <v>1784</v>
       </c>
       <c r="I69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1226</v>
+        <v>1218</v>
       </c>
       <c r="J69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5166,11 +5166,11 @@
       </c>
       <c r="N69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="O69">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1303</v>
+        <v>1296</v>
       </c>
       <c r="P69">
         <v>4</v>
@@ -5194,19 +5194,19 @@
       </c>
       <c r="F70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>28308720.802652378</v>
+        <v>31676139.724773306</v>
       </c>
       <c r="G70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>29124730.546930134</v>
+        <v>32852093.120552234</v>
       </c>
       <c r="H70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1215</v>
+        <v>1261</v>
       </c>
       <c r="I70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1158</v>
+        <v>1175</v>
       </c>
       <c r="J70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="L70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="N70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1743</v>
+        <v>1748</v>
       </c>
       <c r="O70">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -5254,23 +5254,23 @@
       </c>
       <c r="F71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6354765.22670455</v>
+        <v>7069736.1221274221</v>
       </c>
       <c r="G71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5975962.6817722982</v>
+        <v>6760049.5165477693</v>
       </c>
       <c r="H71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>511</v>
+        <v>563</v>
       </c>
       <c r="I71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>501</v>
+        <v>473</v>
       </c>
       <c r="J71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -5286,11 +5286,11 @@
       </c>
       <c r="N71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="O71">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="P71">
         <v>2</v>
@@ -5314,19 +5314,19 @@
       </c>
       <c r="F72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9989788.20540924</v>
+        <v>11067997.809093548</v>
       </c>
       <c r="G72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8967153.6823930759</v>
+        <v>10338062.634815617</v>
       </c>
       <c r="H72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>813</v>
+        <v>825</v>
       </c>
       <c r="I72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>920</v>
+        <v>879</v>
       </c>
       <c r="J72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5346,11 +5346,11 @@
       </c>
       <c r="N72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>897</v>
+        <v>891</v>
       </c>
       <c r="O72">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="P72">
         <v>3</v>
@@ -5374,19 +5374,19 @@
       </c>
       <c r="F73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5514504.1095447363</v>
+        <v>6646183.4289873363</v>
       </c>
       <c r="G73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8838437.0925082453</v>
+        <v>10027767.237602197</v>
       </c>
       <c r="H73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>513</v>
+        <v>497</v>
       </c>
       <c r="I73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>467</v>
+        <v>437</v>
       </c>
       <c r="J73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5406,11 +5406,11 @@
       </c>
       <c r="N73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="O73">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="P73">
         <v>7</v>
@@ -5434,19 +5434,19 @@
       </c>
       <c r="F74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6750615.9754769709</v>
+        <v>7438912.9088206459</v>
       </c>
       <c r="G74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7890411.4936368279</v>
+        <v>8685443.1066132579</v>
       </c>
       <c r="H74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>924</v>
+        <v>759</v>
       </c>
       <c r="I74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>698</v>
+        <v>710</v>
       </c>
       <c r="J74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5462,15 +5462,15 @@
       </c>
       <c r="M74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="O74">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="P74">
         <v>2</v>
@@ -5494,19 +5494,19 @@
       </c>
       <c r="F75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7653920.359339037</v>
+        <v>8497870.0991402362</v>
       </c>
       <c r="G75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8390126.8830564395</v>
+        <v>9304320.9951788951</v>
       </c>
       <c r="H75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>355</v>
+        <v>391</v>
       </c>
       <c r="I75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="J75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5526,11 +5526,11 @@
       </c>
       <c r="N75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="O75">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="P75">
         <v>1</v>
@@ -5554,19 +5554,19 @@
       </c>
       <c r="F76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21521164.578006919</v>
+        <v>23923392.832980826</v>
       </c>
       <c r="G76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20746372.803316668</v>
+        <v>23499947.38004652</v>
       </c>
       <c r="H76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>691</v>
+        <v>725</v>
       </c>
       <c r="I76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>672</v>
+        <v>747</v>
       </c>
       <c r="J76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5586,11 +5586,11 @@
       </c>
       <c r="N76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="O76">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="P76">
         <v>4</v>
@@ -5614,23 +5614,23 @@
       </c>
       <c r="F77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13363157.032803241</v>
+        <v>14714128.498747272</v>
       </c>
       <c r="G77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13054902.089641485</v>
+        <v>14617965.617096372</v>
       </c>
       <c r="H77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>814</v>
+        <v>673</v>
       </c>
       <c r="I77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="J77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -5646,11 +5646,11 @@
       </c>
       <c r="N77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="O77">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="P77">
         <v>2</v>
@@ -5674,19 +5674,19 @@
       </c>
       <c r="F78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10535619.815227035</v>
+        <v>11668411.154587179</v>
       </c>
       <c r="G78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11489184.409651188</v>
+        <v>12972567.696969476</v>
       </c>
       <c r="H78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>863</v>
+        <v>1067</v>
       </c>
       <c r="I78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1215</v>
+        <v>1182</v>
       </c>
       <c r="J78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5706,11 +5706,11 @@
       </c>
       <c r="N78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>922</v>
+        <v>931</v>
       </c>
       <c r="O78">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="P78">
         <v>3</v>
@@ -5734,19 +5734,19 @@
       </c>
       <c r="F79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12029136.598088751</v>
+        <v>13451041.548536345</v>
       </c>
       <c r="G79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8436359.6429892965</v>
+        <v>10024481.605834993</v>
       </c>
       <c r="H79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>816</v>
+        <v>804</v>
       </c>
       <c r="I79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>688</v>
+        <v>844</v>
       </c>
       <c r="J79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5766,11 +5766,11 @@
       </c>
       <c r="N79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="O79">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="P79">
         <v>3</v>
@@ -5794,19 +5794,19 @@
       </c>
       <c r="F80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12058816.101821585</v>
+        <v>13549867.950274644</v>
       </c>
       <c r="G80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12570353.635213269</v>
+        <v>14559640.370847676</v>
       </c>
       <c r="H80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>723</v>
+        <v>645</v>
       </c>
       <c r="I80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>831</v>
+        <v>756</v>
       </c>
       <c r="J80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5818,19 +5818,19 @@
       </c>
       <c r="L80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="O80">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="P80">
         <v>3</v>
@@ -5854,19 +5854,19 @@
       </c>
       <c r="F81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6345447.8126080902</v>
+        <v>6882758.8965735016</v>
       </c>
       <c r="G81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6485541.9481432578</v>
+        <v>7315762.4698836477</v>
       </c>
       <c r="H81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>686</v>
+        <v>588</v>
       </c>
       <c r="I81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>575</v>
+        <v>599</v>
       </c>
       <c r="J81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5882,15 +5882,15 @@
       </c>
       <c r="M81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="O81">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="P81">
         <v>1</v>
@@ -5914,19 +5914,19 @@
       </c>
       <c r="F82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24330358.382188115</v>
+        <v>26079892.628516715</v>
       </c>
       <c r="G82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>24951429.425259337</v>
+        <v>28525506.244806383</v>
       </c>
       <c r="H82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1262</v>
+        <v>1202</v>
       </c>
       <c r="I82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1231</v>
+        <v>1277</v>
       </c>
       <c r="J82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="L82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5946,11 +5946,11 @@
       </c>
       <c r="N82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1710</v>
+        <v>1712</v>
       </c>
       <c r="O82">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="P82">
         <v>1</v>
@@ -5974,19 +5974,19 @@
       </c>
       <c r="F83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6599894.3574415911</v>
+        <v>7165191.5008343831</v>
       </c>
       <c r="G83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5256040.7605468342</v>
+        <v>5946913.5955582066</v>
       </c>
       <c r="H83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>631</v>
+        <v>687</v>
       </c>
       <c r="I83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>668</v>
+        <v>692</v>
       </c>
       <c r="J83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6006,11 +6006,11 @@
       </c>
       <c r="N83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="O83">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>588</v>
+        <v>572</v>
       </c>
       <c r="P83">
         <v>2</v>
@@ -6034,19 +6034,19 @@
       </c>
       <c r="F84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11603173.468591984</v>
+        <v>12970475.295201844</v>
       </c>
       <c r="G84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12085662.536187533</v>
+        <v>13699798.317924472</v>
       </c>
       <c r="H84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>494</v>
+        <v>582</v>
       </c>
       <c r="I84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>590</v>
+        <v>548</v>
       </c>
       <c r="J84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6066,11 +6066,11 @@
       </c>
       <c r="N84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="O84">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>620</v>
+        <v>634</v>
       </c>
       <c r="P84">
         <v>7</v>
@@ -6094,23 +6094,23 @@
       </c>
       <c r="F85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>3559231.8746322528</v>
+        <v>3870008.7806480499</v>
       </c>
       <c r="G85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3096779.6955845412</v>
+        <v>3450645.4612574582</v>
       </c>
       <c r="H85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>304</v>
+        <v>279</v>
       </c>
       <c r="I85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="J85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -6126,11 +6126,11 @@
       </c>
       <c r="N85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="O85">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="P85">
         <v>2</v>
@@ -6163,11 +6163,11 @@
       <c r="A3" s="11"/>
       <c r="B3" s="11">
         <f t="shared" ref="B3:K3" si="0">SUBTOTAL(9,B6:B90)</f>
-        <v>83982</v>
+        <v>83966</v>
       </c>
       <c r="C3" s="11">
         <f t="shared" si="0"/>
-        <v>408</v>
+        <v>432</v>
       </c>
       <c r="D3" s="11">
         <f t="shared" si="0"/>
@@ -6175,19 +6175,19 @@
       </c>
       <c r="E3" s="11">
         <f t="shared" si="0"/>
-        <v>70176</v>
+        <v>69512</v>
       </c>
       <c r="F3" s="11">
         <f t="shared" si="0"/>
-        <v>1219019592.7645988</v>
+        <v>1358024381.1515994</v>
       </c>
       <c r="G3" s="11">
         <f t="shared" si="0"/>
-        <v>84684</v>
+        <v>84646</v>
       </c>
       <c r="H3" s="11">
         <f t="shared" si="0"/>
-        <v>622</v>
+        <v>649</v>
       </c>
       <c r="I3" s="11">
         <f t="shared" si="0"/>
@@ -6195,11 +6195,11 @@
       </c>
       <c r="J3" s="11">
         <f t="shared" si="0"/>
-        <v>71951</v>
+        <v>71621</v>
       </c>
       <c r="K3" s="11">
         <f t="shared" si="0"/>
-        <v>1196500500.4514337</v>
+        <v>1352856501.8340027</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -6259,7 +6259,7 @@
         <v>117</v>
       </c>
       <c r="B6" s="10">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C6" s="10">
         <v>3</v>
@@ -6268,13 +6268,13 @@
         <v>2</v>
       </c>
       <c r="E6" s="10">
-        <v>620</v>
+        <v>331</v>
       </c>
       <c r="F6" s="10">
-        <v>6059382.1473084744</v>
+        <v>6721217.3677318636</v>
       </c>
       <c r="G6" s="10">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="H6" s="10">
         <v>0</v>
@@ -6283,10 +6283,10 @@
         <v>2</v>
       </c>
       <c r="J6" s="10">
-        <v>379</v>
+        <v>336</v>
       </c>
       <c r="K6" s="10">
-        <v>5415574.0184972491</v>
+        <v>6152818.0823086826</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
@@ -6294,7 +6294,7 @@
         <v>127</v>
       </c>
       <c r="B7" s="10">
-        <v>686</v>
+        <v>675</v>
       </c>
       <c r="C7" s="10">
         <v>1</v>
@@ -6303,13 +6303,13 @@
         <v>1</v>
       </c>
       <c r="E7" s="10">
-        <v>614</v>
+        <v>577</v>
       </c>
       <c r="F7" s="10">
-        <v>7288506.4151363429</v>
+        <v>8156654.6793239554</v>
       </c>
       <c r="G7" s="10">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H7" s="10">
         <v>1</v>
@@ -6318,10 +6318,10 @@
         <v>2</v>
       </c>
       <c r="J7" s="10">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="K7" s="10">
-        <v>6653085.5256644776</v>
+        <v>7429191.778023608</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
@@ -6329,7 +6329,7 @@
         <v>119</v>
       </c>
       <c r="B8" s="10">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C8" s="10">
         <v>2</v>
@@ -6338,25 +6338,25 @@
         <v>2</v>
       </c>
       <c r="E8" s="10">
-        <v>667</v>
+        <v>697</v>
       </c>
       <c r="F8" s="10">
-        <v>6371310.9355353834</v>
+        <v>7399552.3442232348</v>
       </c>
       <c r="G8" s="10">
         <v>734</v>
       </c>
       <c r="H8" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8" s="10">
         <v>1</v>
       </c>
       <c r="J8" s="10">
-        <v>745</v>
+        <v>703</v>
       </c>
       <c r="K8" s="10">
-        <v>6613502.6668428723</v>
+        <v>7950360.3691030573</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
@@ -6364,7 +6364,7 @@
         <v>121</v>
       </c>
       <c r="B9" s="10">
-        <v>1197</v>
+        <v>1200</v>
       </c>
       <c r="C9" s="10">
         <v>2</v>
@@ -6373,13 +6373,13 @@
         <v>2</v>
       </c>
       <c r="E9" s="10">
-        <v>760</v>
+        <v>980</v>
       </c>
       <c r="F9" s="10">
-        <v>14068595.525211383</v>
+        <v>15552827.417094398</v>
       </c>
       <c r="G9" s="10">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="H9" s="10">
         <v>2</v>
@@ -6388,10 +6388,10 @@
         <v>3</v>
       </c>
       <c r="J9" s="10">
-        <v>998</v>
+        <v>1029</v>
       </c>
       <c r="K9" s="10">
-        <v>13913394.68100726</v>
+        <v>15725446.023067832</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
@@ -6399,7 +6399,7 @@
         <v>123</v>
       </c>
       <c r="B10" s="10">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="C10" s="10">
         <v>1</v>
@@ -6408,13 +6408,13 @@
         <v>0</v>
       </c>
       <c r="E10" s="10">
-        <v>315</v>
+        <v>337</v>
       </c>
       <c r="F10" s="10">
-        <v>5121540.0843401868</v>
+        <v>5858964.4469372071</v>
       </c>
       <c r="G10" s="10">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H10" s="10">
         <v>1</v>
@@ -6423,10 +6423,10 @@
         <v>1</v>
       </c>
       <c r="J10" s="10">
-        <v>419</v>
+        <v>356</v>
       </c>
       <c r="K10" s="10">
-        <v>5839432.1316437609</v>
+        <v>6781752.4824333154</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
@@ -6434,7 +6434,7 @@
         <v>125</v>
       </c>
       <c r="B11" s="10">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C11" s="10">
         <v>2</v>
@@ -6443,13 +6443,13 @@
         <v>2</v>
       </c>
       <c r="E11" s="10">
-        <v>431</v>
+        <v>356</v>
       </c>
       <c r="F11" s="10">
-        <v>5394052.5405044062</v>
+        <v>5921570.4369004704</v>
       </c>
       <c r="G11" s="10">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H11" s="10">
         <v>2</v>
@@ -6458,10 +6458,10 @@
         <v>2</v>
       </c>
       <c r="J11" s="10">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="K11" s="10">
-        <v>5345165.618633477</v>
+        <v>5992231.4276800314</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -6469,7 +6469,7 @@
         <v>131</v>
       </c>
       <c r="B12" s="10">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C12" s="10">
         <v>0</v>
@@ -6478,25 +6478,25 @@
         <v>1</v>
       </c>
       <c r="E12" s="10">
-        <v>1167</v>
+        <v>525</v>
       </c>
       <c r="F12" s="10">
-        <v>6272003.9840085637</v>
+        <v>6799052.3254508786</v>
       </c>
       <c r="G12" s="10">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H12" s="10">
         <v>0</v>
       </c>
       <c r="I12" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J12" s="10">
-        <v>483</v>
+        <v>512</v>
       </c>
       <c r="K12" s="10">
-        <v>5990321.0092403321</v>
+        <v>6874438.380801552</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
@@ -6504,7 +6504,7 @@
         <v>133</v>
       </c>
       <c r="B13" s="10">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C13" s="10">
         <v>0</v>
@@ -6513,25 +6513,25 @@
         <v>1</v>
       </c>
       <c r="E13" s="10">
-        <v>138</v>
+        <v>172</v>
       </c>
       <c r="F13" s="10">
-        <v>2610227.0540075419</v>
+        <v>2979868.2358265291</v>
       </c>
       <c r="G13" s="10">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="H13" s="10">
         <v>0</v>
       </c>
       <c r="I13" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="10">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="K13" s="10">
-        <v>2744967.7764228848</v>
+        <v>3098186.935847898</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
@@ -6539,7 +6539,7 @@
         <v>141</v>
       </c>
       <c r="B14" s="10">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C14" s="10">
         <v>1</v>
@@ -6548,13 +6548,13 @@
         <v>0</v>
       </c>
       <c r="E14" s="10">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="F14" s="10">
-        <v>2761713.1927333758</v>
+        <v>3006238.1098317681</v>
       </c>
       <c r="G14" s="10">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="H14" s="10">
         <v>0</v>
@@ -6563,10 +6563,10 @@
         <v>1</v>
       </c>
       <c r="J14" s="10">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K14" s="10">
-        <v>267968.35746859002</v>
+        <v>268270.17518669402</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
@@ -6574,7 +6574,7 @@
         <v>135</v>
       </c>
       <c r="B15" s="10">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C15" s="10">
         <v>0</v>
@@ -6583,13 +6583,13 @@
         <v>0</v>
       </c>
       <c r="E15" s="10">
-        <v>363</v>
+        <v>286</v>
       </c>
       <c r="F15" s="10">
-        <v>4379782.4858754724</v>
+        <v>4782564.6090684468</v>
       </c>
       <c r="G15" s="10">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="H15" s="10">
         <v>1</v>
@@ -6598,10 +6598,10 @@
         <v>1</v>
       </c>
       <c r="J15" s="10">
-        <v>542</v>
+        <v>509</v>
       </c>
       <c r="K15" s="10">
-        <v>5948859.3354461109</v>
+        <v>6812954.8209106149</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
@@ -6609,7 +6609,7 @@
         <v>143</v>
       </c>
       <c r="B16" s="10">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C16" s="10">
         <v>0</v>
@@ -6618,13 +6618,13 @@
         <v>1</v>
       </c>
       <c r="E16" s="10">
-        <v>212</v>
+        <v>321</v>
       </c>
       <c r="F16" s="10">
-        <v>1995774.4805199029</v>
+        <v>2250565.6269620662</v>
       </c>
       <c r="G16" s="10">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H16" s="10">
         <v>0</v>
@@ -6633,10 +6633,10 @@
         <v>2</v>
       </c>
       <c r="J16" s="10">
-        <v>578</v>
+        <v>273</v>
       </c>
       <c r="K16" s="10">
-        <v>2625962.4150365731</v>
+        <v>2959702.482844451</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -6644,22 +6644,22 @@
         <v>145</v>
       </c>
       <c r="B17" s="10">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C17" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" s="10">
         <v>0</v>
       </c>
       <c r="E17" s="10">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="F17" s="10">
-        <v>2676274.3626946318</v>
+        <v>3008058.056240594</v>
       </c>
       <c r="G17" s="10">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H17" s="10">
         <v>0</v>
@@ -6668,10 +6668,10 @@
         <v>1</v>
       </c>
       <c r="J17" s="10">
-        <v>244</v>
+        <v>219</v>
       </c>
       <c r="K17" s="10">
-        <v>2935154.1349404189</v>
+        <v>3318437.6932629938</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
@@ -6679,7 +6679,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="10">
-        <v>1454</v>
+        <v>1445</v>
       </c>
       <c r="C18" s="10">
         <v>0</v>
@@ -6688,13 +6688,13 @@
         <v>2</v>
       </c>
       <c r="E18" s="10">
-        <v>121</v>
+        <v>48</v>
       </c>
       <c r="F18" s="10">
-        <v>7510668.6871368838</v>
+        <v>7512189.1632019328</v>
       </c>
       <c r="G18" s="10">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H18" s="10">
         <v>2</v>
@@ -6703,10 +6703,10 @@
         <v>3</v>
       </c>
       <c r="J18" s="10">
-        <v>802</v>
+        <v>867</v>
       </c>
       <c r="K18" s="10">
-        <v>8711554.6449297052</v>
+        <v>9987199.9195197597</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
@@ -6714,7 +6714,7 @@
         <v>45</v>
       </c>
       <c r="B19" s="10">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="C19" s="10">
         <v>0</v>
@@ -6723,25 +6723,25 @@
         <v>2</v>
       </c>
       <c r="E19" s="10">
-        <v>1045</v>
+        <v>1281</v>
       </c>
       <c r="F19" s="10">
-        <v>18218164.868068825</v>
+        <v>21031434.832303733</v>
       </c>
       <c r="G19" s="10">
-        <v>1240</v>
+        <v>1234</v>
       </c>
       <c r="H19" s="10">
         <v>1</v>
       </c>
       <c r="I19" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J19" s="10">
-        <v>881</v>
+        <v>896</v>
       </c>
       <c r="K19" s="10">
-        <v>19264893.816357184</v>
+        <v>21848454.097331937</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
@@ -6749,7 +6749,7 @@
         <v>47</v>
       </c>
       <c r="B20" s="10">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="C20" s="10">
         <v>1</v>
@@ -6758,25 +6758,25 @@
         <v>3</v>
       </c>
       <c r="E20" s="10">
-        <v>920</v>
+        <v>909</v>
       </c>
       <c r="F20" s="10">
-        <v>11271211.941410139</v>
+        <v>12464962.956552835</v>
       </c>
       <c r="G20" s="10">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="H20" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" s="10">
         <v>5</v>
       </c>
       <c r="J20" s="10">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="K20" s="10">
-        <v>11477126.439976607</v>
+        <v>12945342.206328144</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
@@ -6784,7 +6784,7 @@
         <v>49</v>
       </c>
       <c r="B21" s="10">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="C21" s="10">
         <v>0</v>
@@ -6793,25 +6793,25 @@
         <v>2</v>
       </c>
       <c r="E21" s="10">
-        <v>678</v>
+        <v>636</v>
       </c>
       <c r="F21" s="10">
-        <v>12072562.882114958</v>
+        <v>13216752.071126426</v>
       </c>
       <c r="G21" s="10">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="H21" s="10">
         <v>3</v>
       </c>
       <c r="I21" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J21" s="10">
-        <v>696</v>
+        <v>726</v>
       </c>
       <c r="K21" s="10">
-        <v>7647194.0438168291</v>
+        <v>8571431.2894174531</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
@@ -6819,34 +6819,34 @@
         <v>51</v>
       </c>
       <c r="B22" s="10">
-        <v>2819</v>
+        <v>2802</v>
       </c>
       <c r="C22" s="10">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D22" s="10">
         <v>10</v>
       </c>
       <c r="E22" s="10">
-        <v>2028</v>
+        <v>2035</v>
       </c>
       <c r="F22" s="10">
-        <v>39301193.021534018</v>
+        <v>43765663.42008768</v>
       </c>
       <c r="G22" s="10">
-        <v>2980</v>
+        <v>2942</v>
       </c>
       <c r="H22" s="10">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I22" s="10">
         <v>10</v>
       </c>
       <c r="J22" s="10">
-        <v>2890</v>
+        <v>2900</v>
       </c>
       <c r="K22" s="10">
-        <v>43058855.414458841</v>
+        <v>49075557.599973261</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
@@ -6854,7 +6854,7 @@
         <v>53</v>
       </c>
       <c r="B23" s="10">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="C23" s="10">
         <v>0</v>
@@ -6866,10 +6866,10 @@
         <v>1139</v>
       </c>
       <c r="F23" s="10">
-        <v>21548491.261211187</v>
+        <v>24021205.021760464</v>
       </c>
       <c r="G23" s="10">
-        <v>1375</v>
+        <v>1367</v>
       </c>
       <c r="H23" s="10">
         <v>2</v>
@@ -6878,10 +6878,10 @@
         <v>1</v>
       </c>
       <c r="J23" s="10">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K23" s="10">
-        <v>8067116.426811154</v>
+        <v>8067116.1734909713</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
@@ -6889,34 +6889,34 @@
         <v>55</v>
       </c>
       <c r="B24" s="10">
-        <v>2982</v>
+        <v>2984</v>
       </c>
       <c r="C24" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D24" s="10">
         <v>12</v>
       </c>
       <c r="E24" s="10">
-        <v>2306</v>
+        <v>2383</v>
       </c>
       <c r="F24" s="10">
-        <v>41412282.042329848</v>
+        <v>46803671.881852701</v>
       </c>
       <c r="G24" s="10">
-        <v>2961</v>
+        <v>2962</v>
       </c>
       <c r="H24" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I24" s="10">
         <v>10</v>
       </c>
       <c r="J24" s="10">
-        <v>2202</v>
+        <v>2214</v>
       </c>
       <c r="K24" s="10">
-        <v>42204564.094008639</v>
+        <v>47738508.937325202</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
@@ -6924,7 +6924,7 @@
         <v>67</v>
       </c>
       <c r="B25" s="10">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="C25" s="10">
         <v>3</v>
@@ -6933,13 +6933,13 @@
         <v>1</v>
       </c>
       <c r="E25" s="10">
-        <v>480</v>
+        <v>463</v>
       </c>
       <c r="F25" s="10">
-        <v>6074404.571538738</v>
+        <v>6796338.2171994355</v>
       </c>
       <c r="G25" s="10">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H25" s="10">
         <v>4</v>
@@ -6948,10 +6948,10 @@
         <v>1</v>
       </c>
       <c r="J25" s="10">
-        <v>534</v>
+        <v>515</v>
       </c>
       <c r="K25" s="10">
-        <v>6415129.7986748964</v>
+        <v>7122002.4557506125</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
@@ -6959,7 +6959,7 @@
         <v>74</v>
       </c>
       <c r="B26" s="10">
-        <v>1702</v>
+        <v>1709</v>
       </c>
       <c r="C26" s="10">
         <v>6</v>
@@ -6968,25 +6968,25 @@
         <v>1</v>
       </c>
       <c r="E26" s="10">
-        <v>1286</v>
+        <v>1251</v>
       </c>
       <c r="F26" s="10">
-        <v>17223155.15647522</v>
+        <v>18988796.478382163</v>
       </c>
       <c r="G26" s="10">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="H26" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I26" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26" s="10">
-        <v>1282</v>
+        <v>1334</v>
       </c>
       <c r="K26" s="10">
-        <v>17223861.127960525</v>
+        <v>19306182.14601028</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
@@ -6994,7 +6994,7 @@
         <v>70</v>
       </c>
       <c r="B27" s="10">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="C27" s="10">
         <v>4</v>
@@ -7003,10 +7003,10 @@
         <v>1</v>
       </c>
       <c r="E27" s="10">
-        <v>762</v>
+        <v>826</v>
       </c>
       <c r="F27" s="10">
-        <v>7606090.3029235201</v>
+        <v>8482004.1993926615</v>
       </c>
       <c r="G27" s="10">
         <v>886</v>
@@ -7018,10 +7018,10 @@
         <v>1</v>
       </c>
       <c r="J27" s="10">
-        <v>792</v>
+        <v>766</v>
       </c>
       <c r="K27" s="10">
-        <v>6991287.7517503034</v>
+        <v>7846298.3074562633</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
@@ -7029,7 +7029,7 @@
         <v>72</v>
       </c>
       <c r="B28" s="10">
-        <v>902</v>
+        <v>896</v>
       </c>
       <c r="C28" s="10">
         <v>1</v>
@@ -7038,10 +7038,10 @@
         <v>1</v>
       </c>
       <c r="E28" s="10">
-        <v>846</v>
+        <v>570</v>
       </c>
       <c r="F28" s="10">
-        <v>7771830.7785125766</v>
+        <v>8755237.1310375761</v>
       </c>
       <c r="G28" s="10">
         <v>880</v>
@@ -7053,10 +7053,10 @@
         <v>1</v>
       </c>
       <c r="J28" s="10">
-        <v>731</v>
+        <v>757</v>
       </c>
       <c r="K28" s="10">
-        <v>8945717.278125396</v>
+        <v>9960916.6373697724</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
@@ -7064,7 +7064,7 @@
         <v>79</v>
       </c>
       <c r="B29" s="10">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C29" s="10">
         <v>1</v>
@@ -7073,25 +7073,25 @@
         <v>0</v>
       </c>
       <c r="E29" s="10">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="F29" s="10">
-        <v>2280396.1807618379</v>
+        <v>2560118.3425952001</v>
       </c>
       <c r="G29" s="10">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="H29" s="10">
         <v>1</v>
       </c>
       <c r="I29" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J29" s="10">
-        <v>2554</v>
+        <v>146</v>
       </c>
       <c r="K29" s="10">
-        <v>1898558.2643888111</v>
+        <v>2055834.390430477</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
@@ -7099,7 +7099,7 @@
         <v>109</v>
       </c>
       <c r="B30" s="10">
-        <v>1654</v>
+        <v>1663</v>
       </c>
       <c r="C30" s="10">
         <v>1</v>
@@ -7108,13 +7108,13 @@
         <v>5</v>
       </c>
       <c r="E30" s="10">
-        <v>1477</v>
+        <v>1514</v>
       </c>
       <c r="F30" s="10">
-        <v>20642472.561316367</v>
+        <v>22718777.941925272</v>
       </c>
       <c r="G30" s="10">
-        <v>1653</v>
+        <v>1661</v>
       </c>
       <c r="H30" s="10">
         <v>9</v>
@@ -7123,10 +7123,10 @@
         <v>6</v>
       </c>
       <c r="J30" s="10">
-        <v>1372</v>
+        <v>1398</v>
       </c>
       <c r="K30" s="10">
-        <v>16597899.852037497</v>
+        <v>18674864.213929038</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
@@ -7134,7 +7134,7 @@
         <v>111</v>
       </c>
       <c r="B31" s="10">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="C31" s="10">
         <v>1</v>
@@ -7143,25 +7143,25 @@
         <v>1</v>
       </c>
       <c r="E31" s="10">
-        <v>677</v>
+        <v>648</v>
       </c>
       <c r="F31" s="10">
-        <v>12615973.394648995</v>
+        <v>14153077.91888571</v>
       </c>
       <c r="G31" s="10">
-        <v>874</v>
+        <v>863</v>
       </c>
       <c r="H31" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" s="10">
         <v>1</v>
       </c>
       <c r="J31" s="10">
-        <v>816</v>
+        <v>617</v>
       </c>
       <c r="K31" s="10">
-        <v>12917264.245188372</v>
+        <v>14551107.043437852</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
@@ -7169,7 +7169,7 @@
         <v>113</v>
       </c>
       <c r="B32" s="10">
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="C32" s="10">
         <v>0</v>
@@ -7178,13 +7178,13 @@
         <v>1</v>
       </c>
       <c r="E32" s="10">
-        <v>762</v>
+        <v>733</v>
       </c>
       <c r="F32" s="10">
-        <v>14123223.678253656</v>
+        <v>15725447.580771975</v>
       </c>
       <c r="G32" s="10">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H32" s="10">
         <v>1</v>
@@ -7193,10 +7193,10 @@
         <v>1</v>
       </c>
       <c r="J32" s="10">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="K32" s="10">
-        <v>12597981.049125759</v>
+        <v>14437291.715968899</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
@@ -7204,7 +7204,7 @@
         <v>115</v>
       </c>
       <c r="B33" s="10">
-        <v>1105</v>
+        <v>1111</v>
       </c>
       <c r="C33" s="10">
         <v>0</v>
@@ -7213,13 +7213,13 @@
         <v>3</v>
       </c>
       <c r="E33" s="10">
-        <v>908</v>
+        <v>967</v>
       </c>
       <c r="F33" s="10">
-        <v>17457947.394665383</v>
+        <v>19703437.006434254</v>
       </c>
       <c r="G33" s="10">
-        <v>1111</v>
+        <v>1116</v>
       </c>
       <c r="H33" s="10">
         <v>2</v>
@@ -7228,10 +7228,10 @@
         <v>2</v>
       </c>
       <c r="J33" s="10">
-        <v>879</v>
+        <v>864</v>
       </c>
       <c r="K33" s="10">
-        <v>17664552.96019372</v>
+        <v>20056812.599486277</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
@@ -7239,7 +7239,7 @@
         <v>16</v>
       </c>
       <c r="B34" s="10">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="C34" s="10">
         <v>0</v>
@@ -7248,25 +7248,25 @@
         <v>5</v>
       </c>
       <c r="E34" s="10">
-        <v>1152</v>
+        <v>1178</v>
       </c>
       <c r="F34" s="10">
-        <v>26720855.442626528</v>
+        <v>29722501.854668796</v>
       </c>
       <c r="G34" s="10">
-        <v>1472</v>
+        <v>1478</v>
       </c>
       <c r="H34" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I34" s="10">
         <v>5</v>
       </c>
       <c r="J34" s="10">
-        <v>1077</v>
+        <v>1146</v>
       </c>
       <c r="K34" s="10">
-        <v>24955672.140388235</v>
+        <v>28294835.68957008</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
@@ -7274,7 +7274,7 @@
         <v>18</v>
       </c>
       <c r="B35" s="10">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C35" s="10">
         <v>0</v>
@@ -7283,13 +7283,13 @@
         <v>2</v>
       </c>
       <c r="E35" s="10">
-        <v>487</v>
+        <v>528</v>
       </c>
       <c r="F35" s="10">
-        <v>9677957.3193788044</v>
+        <v>10980480.649050532</v>
       </c>
       <c r="G35" s="10">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="H35" s="10">
         <v>0</v>
@@ -7298,10 +7298,10 @@
         <v>5</v>
       </c>
       <c r="J35" s="10">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="K35" s="10">
-        <v>10225048.001245813</v>
+        <v>11557874.043439522</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
@@ -7309,7 +7309,7 @@
         <v>43</v>
       </c>
       <c r="B36" s="10">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="C36" s="10">
         <v>0</v>
@@ -7318,25 +7318,25 @@
         <v>10</v>
       </c>
       <c r="E36" s="10">
-        <v>1734</v>
+        <v>1770</v>
       </c>
       <c r="F36" s="10">
-        <v>31206440.608555064</v>
+        <v>35060631.354011633</v>
       </c>
       <c r="G36" s="10">
         <v>1937</v>
       </c>
       <c r="H36" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I36" s="10">
         <v>11</v>
       </c>
       <c r="J36" s="10">
-        <v>1550</v>
+        <v>1579</v>
       </c>
       <c r="K36" s="10">
-        <v>31195786.901903056</v>
+        <v>35288715.200185522</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
@@ -7344,23 +7344,23 @@
         <v>152</v>
       </c>
       <c r="B37" s="10">
+        <v>845</v>
+      </c>
+      <c r="C37" s="10">
+        <v>2</v>
+      </c>
+      <c r="D37" s="10">
+        <v>2</v>
+      </c>
+      <c r="E37" s="10">
+        <v>674</v>
+      </c>
+      <c r="F37" s="10">
+        <v>12333157.928200064</v>
+      </c>
+      <c r="G37" s="10">
         <v>839</v>
       </c>
-      <c r="C37" s="10">
-        <v>1</v>
-      </c>
-      <c r="D37" s="10">
-        <v>2</v>
-      </c>
-      <c r="E37" s="10">
-        <v>703</v>
-      </c>
-      <c r="F37" s="10">
-        <v>11118207.377145017</v>
-      </c>
-      <c r="G37" s="10">
-        <v>843</v>
-      </c>
       <c r="H37" s="10">
         <v>1</v>
       </c>
@@ -7368,10 +7368,10 @@
         <v>2</v>
       </c>
       <c r="J37" s="10">
-        <v>645</v>
+        <v>696</v>
       </c>
       <c r="K37" s="10">
-        <v>10306463.021471065</v>
+        <v>11529791.435436616</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
@@ -7379,7 +7379,7 @@
         <v>149</v>
       </c>
       <c r="B38" s="10">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C38" s="10">
         <v>0</v>
@@ -7388,13 +7388,13 @@
         <v>1</v>
       </c>
       <c r="E38" s="10">
-        <v>418</v>
+        <v>459</v>
       </c>
       <c r="F38" s="10">
-        <v>9306095.0251620207</v>
+        <v>10103964.004989509</v>
       </c>
       <c r="G38" s="10">
-        <v>718</v>
+        <v>732</v>
       </c>
       <c r="H38" s="10">
         <v>0</v>
@@ -7403,10 +7403,10 @@
         <v>1</v>
       </c>
       <c r="J38" s="10">
-        <v>525</v>
+        <v>557</v>
       </c>
       <c r="K38" s="10">
-        <v>9952856.9297330845</v>
+        <v>11112334.557640174</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
@@ -7414,34 +7414,34 @@
         <v>154</v>
       </c>
       <c r="B39" s="10">
-        <v>1131</v>
+        <v>1122</v>
       </c>
       <c r="C39" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D39" s="10">
         <v>3</v>
       </c>
       <c r="E39" s="10">
-        <v>798</v>
+        <v>872</v>
       </c>
       <c r="F39" s="10">
-        <v>16122199.413593575</v>
+        <v>17854652.580006875</v>
       </c>
       <c r="G39" s="10">
-        <v>1171</v>
+        <v>1176</v>
       </c>
       <c r="H39" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I39" s="10">
         <v>1</v>
       </c>
       <c r="J39" s="10">
-        <v>852</v>
+        <v>836</v>
       </c>
       <c r="K39" s="10">
-        <v>15241628.231743544</v>
+        <v>17193856.285997957</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
@@ -7449,7 +7449,7 @@
         <v>2</v>
       </c>
       <c r="B40" s="10">
-        <v>1200</v>
+        <v>1183</v>
       </c>
       <c r="C40" s="10">
         <v>36</v>
@@ -7458,13 +7458,13 @@
         <v>1</v>
       </c>
       <c r="E40" s="10">
-        <v>959</v>
+        <v>869</v>
       </c>
       <c r="F40" s="10">
-        <v>15445962.516069006</v>
+        <v>17212785.665607128</v>
       </c>
       <c r="G40" s="10">
-        <v>1390</v>
+        <v>1365</v>
       </c>
       <c r="H40" s="10">
         <v>120</v>
@@ -7473,10 +7473,10 @@
         <v>1</v>
       </c>
       <c r="J40" s="10">
-        <v>829</v>
+        <v>769</v>
       </c>
       <c r="K40" s="10">
-        <v>13827542.353898088</v>
+        <v>15645497.955338975</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
@@ -7484,22 +7484,22 @@
         <v>156</v>
       </c>
       <c r="B41" s="10">
-        <v>1844</v>
+        <v>1840</v>
       </c>
       <c r="C41" s="10">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D41" s="10">
         <v>4</v>
       </c>
       <c r="E41" s="10">
-        <v>1411</v>
+        <v>1382</v>
       </c>
       <c r="F41" s="10">
-        <v>24434713.31977386</v>
+        <v>27010112.979283512</v>
       </c>
       <c r="G41" s="10">
-        <v>2522</v>
+        <v>2469</v>
       </c>
       <c r="H41" s="10">
         <v>68</v>
@@ -7508,10 +7508,10 @@
         <v>5</v>
       </c>
       <c r="J41" s="10">
-        <v>1498</v>
+        <v>1439</v>
       </c>
       <c r="K41" s="10">
-        <v>25291639.249637514</v>
+        <v>28638765.273579638</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
@@ -7519,7 +7519,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="10">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C42" s="10">
         <v>2</v>
@@ -7528,13 +7528,13 @@
         <v>6</v>
       </c>
       <c r="E42" s="10">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F42" s="10">
-        <v>10078150.216247274</v>
+        <v>11241543.166229179</v>
       </c>
       <c r="G42" s="10">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H42" s="10">
         <v>0</v>
@@ -7543,10 +7543,10 @@
         <v>6</v>
       </c>
       <c r="J42" s="10">
-        <v>412</v>
+        <v>466</v>
       </c>
       <c r="K42" s="10">
-        <v>9191077.4228783716</v>
+        <v>10344833.566559069</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
@@ -7554,7 +7554,7 @@
         <v>8</v>
       </c>
       <c r="B43" s="10">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="C43" s="10">
         <v>2</v>
@@ -7563,13 +7563,13 @@
         <v>6</v>
       </c>
       <c r="E43" s="10">
-        <v>1778</v>
+        <v>1917</v>
       </c>
       <c r="F43" s="10">
-        <v>27864970.025229905</v>
+        <v>30939701.804248367</v>
       </c>
       <c r="G43" s="10">
-        <v>2057</v>
+        <v>2049</v>
       </c>
       <c r="H43" s="10">
         <v>2</v>
@@ -7578,10 +7578,10 @@
         <v>6</v>
       </c>
       <c r="J43" s="10">
-        <v>1826</v>
+        <v>1934</v>
       </c>
       <c r="K43" s="10">
-        <v>31007988.562648121</v>
+        <v>34562600.775030553</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.35">
@@ -7589,7 +7589,7 @@
         <v>39</v>
       </c>
       <c r="B44" s="10">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="C44" s="10">
         <v>3</v>
@@ -7598,13 +7598,13 @@
         <v>4</v>
       </c>
       <c r="E44" s="10">
-        <v>731</v>
+        <v>743</v>
       </c>
       <c r="F44" s="10">
-        <v>19342823.481627457</v>
+        <v>21592902.705368832</v>
       </c>
       <c r="G44" s="10">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="H44" s="10">
         <v>2</v>
@@ -7613,10 +7613,10 @@
         <v>2</v>
       </c>
       <c r="J44" s="10">
-        <v>753</v>
+        <v>797</v>
       </c>
       <c r="K44" s="10">
-        <v>19825792.805345695</v>
+        <v>22304769.355051536</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.35">
@@ -7624,7 +7624,7 @@
         <v>6</v>
       </c>
       <c r="B45" s="10">
-        <v>1146</v>
+        <v>1154</v>
       </c>
       <c r="C45" s="10">
         <v>0</v>
@@ -7633,13 +7633,13 @@
         <v>3</v>
       </c>
       <c r="E45" s="10">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="F45" s="10">
-        <v>17597530.510886051</v>
+        <v>19361417.568360262</v>
       </c>
       <c r="G45" s="10">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="H45" s="10">
         <v>0</v>
@@ -7648,10 +7648,10 @@
         <v>3</v>
       </c>
       <c r="J45" s="10">
-        <v>918</v>
+        <v>925</v>
       </c>
       <c r="K45" s="10">
-        <v>8542291.4264150988</v>
+        <v>10411236.41967774</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
@@ -7659,7 +7659,7 @@
         <v>41</v>
       </c>
       <c r="B46" s="10">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="C46" s="10">
         <v>0</v>
@@ -7668,25 +7668,25 @@
         <v>5</v>
       </c>
       <c r="E46" s="10">
-        <v>608</v>
+        <v>630</v>
       </c>
       <c r="F46" s="10">
-        <v>16323094.491309352</v>
+        <v>18232693.534131359</v>
       </c>
       <c r="G46" s="10">
         <v>819</v>
       </c>
       <c r="H46" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I46" s="10">
         <v>4</v>
       </c>
       <c r="J46" s="10">
-        <v>597</v>
+        <v>645</v>
       </c>
       <c r="K46" s="10">
-        <v>15660058.036465179</v>
+        <v>17755224.245391376</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.35">
@@ -7694,7 +7694,7 @@
         <v>158</v>
       </c>
       <c r="B47" s="10">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C47" s="10">
         <v>0</v>
@@ -7703,13 +7703,13 @@
         <v>10</v>
       </c>
       <c r="E47" s="10">
-        <v>547</v>
+        <v>600</v>
       </c>
       <c r="F47" s="10">
-        <v>9307002.4168394431</v>
+        <v>10453278.752228426</v>
       </c>
       <c r="G47" s="10">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="H47" s="10">
         <v>1</v>
@@ -7718,10 +7718,10 @@
         <v>10</v>
       </c>
       <c r="J47" s="10">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="K47" s="10">
-        <v>9999788.4775667209</v>
+        <v>11363931.519229412</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.35">
@@ -7729,7 +7729,7 @@
         <v>160</v>
       </c>
       <c r="B48" s="10">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C48" s="10">
         <v>1</v>
@@ -7738,25 +7738,25 @@
         <v>1</v>
       </c>
       <c r="E48" s="10">
-        <v>682</v>
+        <v>743</v>
       </c>
       <c r="F48" s="10">
-        <v>9148288.1945246682</v>
+        <v>10321050.736769276</v>
       </c>
       <c r="G48" s="10">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H48" s="10">
         <v>0</v>
       </c>
       <c r="I48" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J48" s="10">
-        <v>696</v>
+        <v>744</v>
       </c>
       <c r="K48" s="10">
-        <v>8607899.5225225668</v>
+        <v>9780767.8360642996</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
@@ -7764,22 +7764,22 @@
         <v>83</v>
       </c>
       <c r="B49" s="10">
-        <v>1276</v>
+        <v>1281</v>
       </c>
       <c r="C49" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D49" s="10">
         <v>7</v>
       </c>
       <c r="E49" s="10">
-        <v>1209</v>
+        <v>1018</v>
       </c>
       <c r="F49" s="10">
-        <v>33294714.610988211</v>
+        <v>36614471.61384137</v>
       </c>
       <c r="G49" s="10">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="H49" s="10">
         <v>0</v>
@@ -7788,10 +7788,10 @@
         <v>4</v>
       </c>
       <c r="J49" s="10">
-        <v>1154</v>
+        <v>1127</v>
       </c>
       <c r="K49" s="10">
-        <v>27457832.858950939</v>
+        <v>30732060.500332795</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
@@ -7799,7 +7799,7 @@
         <v>202</v>
       </c>
       <c r="B50" s="10">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C50" s="10">
         <v>0</v>
@@ -7808,13 +7808,13 @@
         <v>2</v>
       </c>
       <c r="E50" s="10">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="F50" s="10">
-        <v>5605744.3736915821</v>
+        <v>6249555.1480661668</v>
       </c>
       <c r="G50" s="10">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="H50" s="10">
         <v>0</v>
@@ -7823,10 +7823,10 @@
         <v>1</v>
       </c>
       <c r="J50" s="10">
-        <v>465</v>
+        <v>429</v>
       </c>
       <c r="K50" s="10">
-        <v>4640637.6320960438</v>
+        <v>5123293.8080037152</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
@@ -7834,7 +7834,7 @@
         <v>31</v>
       </c>
       <c r="B51" s="10">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="C51" s="10">
         <v>0</v>
@@ -7843,25 +7843,25 @@
         <v>4</v>
       </c>
       <c r="E51" s="10">
-        <v>925</v>
+        <v>882</v>
       </c>
       <c r="F51" s="10">
-        <v>14593080.011471108</v>
+        <v>16076235.359384179</v>
       </c>
       <c r="G51" s="10">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="H51" s="10">
         <v>2</v>
       </c>
       <c r="I51" s="10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J51" s="10">
-        <v>887</v>
+        <v>3212</v>
       </c>
       <c r="K51" s="10">
-        <v>13251593.852497272</v>
+        <v>14733574.789885193</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
@@ -7869,22 +7869,22 @@
         <v>33</v>
       </c>
       <c r="B52" s="10">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="C52" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D52" s="10">
         <v>12</v>
       </c>
       <c r="E52" s="10">
-        <v>946</v>
+        <v>1001</v>
       </c>
       <c r="F52" s="10">
-        <v>18552025.445382949</v>
+        <v>20734256.805620253</v>
       </c>
       <c r="G52" s="10">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="H52" s="10">
         <v>3</v>
@@ -7893,10 +7893,10 @@
         <v>12</v>
       </c>
       <c r="J52" s="10">
-        <v>958</v>
+        <v>1033</v>
       </c>
       <c r="K52" s="10">
-        <v>23392753.696536377</v>
+        <v>26407949.501988936</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.35">
@@ -7904,7 +7904,7 @@
         <v>85</v>
       </c>
       <c r="B53" s="10">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C53" s="10">
         <v>0</v>
@@ -7913,13 +7913,13 @@
         <v>5</v>
       </c>
       <c r="E53" s="10">
-        <v>369</v>
+        <v>392</v>
       </c>
       <c r="F53" s="10">
-        <v>9531210.9429570977</v>
+        <v>10925987.34804726</v>
       </c>
       <c r="G53" s="10">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H53" s="10">
         <v>0</v>
@@ -7928,10 +7928,10 @@
         <v>6</v>
       </c>
       <c r="J53" s="10">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K53" s="10">
-        <v>12215200.861652251</v>
+        <v>13673852.473286686</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.35">
@@ -7948,13 +7948,13 @@
         <v>7</v>
       </c>
       <c r="E54" s="10">
-        <v>325</v>
+        <v>383</v>
       </c>
       <c r="F54" s="10">
-        <v>11573023.120887872</v>
+        <v>12764477.259903496</v>
       </c>
       <c r="G54" s="10">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H54" s="10">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>4</v>
       </c>
       <c r="J54" s="10">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="K54" s="10">
-        <v>8993502.2004245669</v>
+        <v>10116058.890716156</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.35">
@@ -7974,22 +7974,22 @@
         <v>87</v>
       </c>
       <c r="B55" s="10">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C55" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D55" s="10">
         <v>2</v>
       </c>
       <c r="E55" s="10">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="F55" s="10">
-        <v>9065219.3768147286</v>
+        <v>9941003.7667885516</v>
       </c>
       <c r="G55" s="10">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H55" s="10">
         <v>1</v>
@@ -8001,7 +8001,7 @@
         <v>346</v>
       </c>
       <c r="K55" s="10">
-        <v>7672695.2189010149</v>
+        <v>8825567.6649791468</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.35">
@@ -8009,7 +8009,7 @@
         <v>166</v>
       </c>
       <c r="B56" s="10">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="C56" s="10">
         <v>0</v>
@@ -8018,25 +8018,25 @@
         <v>1</v>
       </c>
       <c r="E56" s="10">
-        <v>902</v>
+        <v>969</v>
       </c>
       <c r="F56" s="10">
-        <v>19252439.405621711</v>
+        <v>21509029.915585216</v>
       </c>
       <c r="G56" s="10">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H56" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" s="10">
         <v>0</v>
       </c>
       <c r="J56" s="10">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="K56" s="10">
-        <v>18272372.933828708</v>
+        <v>20653643.392732065</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
@@ -8044,7 +8044,7 @@
         <v>93</v>
       </c>
       <c r="B57" s="10">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="C57" s="10">
         <v>6</v>
@@ -8053,25 +8053,25 @@
         <v>3</v>
       </c>
       <c r="E57" s="10">
-        <v>820</v>
+        <v>1005</v>
       </c>
       <c r="F57" s="10">
-        <v>20212422.982229233</v>
+        <v>22333476.918126777</v>
       </c>
       <c r="G57" s="10">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="H57" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I57" s="10">
         <v>1</v>
       </c>
       <c r="J57" s="10">
-        <v>976</v>
+        <v>891</v>
       </c>
       <c r="K57" s="10">
-        <v>15381123.373330694</v>
+        <v>18249780.65836753</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.35">
@@ -8079,7 +8079,7 @@
         <v>95</v>
       </c>
       <c r="B58" s="10">
-        <v>2240</v>
+        <v>2229</v>
       </c>
       <c r="C58" s="10">
         <v>30</v>
@@ -8088,25 +8088,25 @@
         <v>7</v>
       </c>
       <c r="E58" s="10">
-        <v>1619</v>
+        <v>1427</v>
       </c>
       <c r="F58" s="10">
-        <v>27521319.010392979</v>
+        <v>30720766.019070383</v>
       </c>
       <c r="G58" s="10">
-        <v>2055</v>
+        <v>2075</v>
       </c>
       <c r="H58" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I58" s="10">
         <v>8</v>
       </c>
       <c r="J58" s="10">
-        <v>1483</v>
+        <v>1631</v>
       </c>
       <c r="K58" s="10">
-        <v>34698100.647447377</v>
+        <v>39207641.101986013</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.35">
@@ -8114,7 +8114,7 @@
         <v>174</v>
       </c>
       <c r="B59" s="10">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="C59" s="10">
         <v>0</v>
@@ -8123,13 +8123,13 @@
         <v>0</v>
       </c>
       <c r="E59" s="10">
-        <v>513</v>
+        <v>554</v>
       </c>
       <c r="F59" s="10">
-        <v>9434418.3837709222</v>
+        <v>10654324.550770273</v>
       </c>
       <c r="G59" s="10">
-        <v>672</v>
+        <v>681</v>
       </c>
       <c r="H59" s="10">
         <v>0</v>
@@ -8138,10 +8138,10 @@
         <v>0</v>
       </c>
       <c r="J59" s="10">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="K59" s="10">
-        <v>7707113.4334032862</v>
+        <v>8875675.9081516638</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.35">
@@ -8149,7 +8149,7 @@
         <v>99</v>
       </c>
       <c r="B60" s="10">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="C60" s="10">
         <v>2</v>
@@ -8158,25 +8158,25 @@
         <v>5</v>
       </c>
       <c r="E60" s="10">
-        <v>742</v>
+        <v>652</v>
       </c>
       <c r="F60" s="10">
-        <v>13858244.856042204</v>
+        <v>15305923.087041697</v>
       </c>
       <c r="G60" s="10">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H60" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I60" s="10">
         <v>5</v>
       </c>
       <c r="J60" s="10">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="K60" s="10">
-        <v>13874918.72588186</v>
+        <v>15926711.477734976</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.35">
@@ -8193,13 +8193,13 @@
         <v>1</v>
       </c>
       <c r="E61" s="10">
-        <v>622</v>
+        <v>594</v>
       </c>
       <c r="F61" s="10">
-        <v>11626890.823241539</v>
+        <v>12874140.232146041</v>
       </c>
       <c r="G61" s="10">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="H61" s="10">
         <v>2</v>
@@ -8208,10 +8208,10 @@
         <v>1</v>
       </c>
       <c r="J61" s="10">
-        <v>691</v>
+        <v>639</v>
       </c>
       <c r="K61" s="10">
-        <v>8580104.8251491878</v>
+        <v>9823421.513111636</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.35">
@@ -8219,22 +8219,22 @@
         <v>168</v>
       </c>
       <c r="B62" s="10">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="C62" s="10">
         <v>2</v>
       </c>
       <c r="D62" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" s="10">
-        <v>1203</v>
+        <v>1199</v>
       </c>
       <c r="F62" s="10">
-        <v>18581393.752516262</v>
+        <v>21103865.275950637</v>
       </c>
       <c r="G62" s="10">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="H62" s="10">
         <v>4</v>
@@ -8243,10 +8243,10 @@
         <v>0</v>
       </c>
       <c r="J62" s="10">
-        <v>928</v>
+        <v>999</v>
       </c>
       <c r="K62" s="10">
-        <v>18789590.991508801</v>
+        <v>21418755.666532356</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.35">
@@ -8254,7 +8254,7 @@
         <v>101</v>
       </c>
       <c r="B63" s="10">
-        <v>1321</v>
+        <v>1327</v>
       </c>
       <c r="C63" s="10">
         <v>4</v>
@@ -8263,13 +8263,13 @@
         <v>4</v>
       </c>
       <c r="E63" s="10">
-        <v>1415</v>
+        <v>1500</v>
       </c>
       <c r="F63" s="10">
-        <v>24051078.007695895</v>
+        <v>27064315.72966738</v>
       </c>
       <c r="G63" s="10">
-        <v>1387</v>
+        <v>1399</v>
       </c>
       <c r="H63" s="10">
         <v>1</v>
@@ -8278,10 +8278,10 @@
         <v>4</v>
       </c>
       <c r="J63" s="10">
-        <v>1341</v>
+        <v>1429</v>
       </c>
       <c r="K63" s="10">
-        <v>22594833.46428778</v>
+        <v>25056798.087375559</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.35">
@@ -8289,22 +8289,22 @@
         <v>103</v>
       </c>
       <c r="B64" s="10">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="C64" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D64" s="10">
         <v>5</v>
       </c>
       <c r="E64" s="10">
-        <v>715</v>
+        <v>732</v>
       </c>
       <c r="F64" s="10">
-        <v>12751076.307971718</v>
+        <v>14085926.081406619</v>
       </c>
       <c r="G64" s="10">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="H64" s="10">
         <v>1</v>
@@ -8313,10 +8313,10 @@
         <v>3</v>
       </c>
       <c r="J64" s="10">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="K64" s="10">
-        <v>12643538.853697417</v>
+        <v>14375514.953195609</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.35">
@@ -8324,34 +8324,34 @@
         <v>105</v>
       </c>
       <c r="B65" s="10">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="C65" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D65" s="10">
         <v>5</v>
       </c>
       <c r="E65" s="10">
-        <v>502</v>
+        <v>440</v>
       </c>
       <c r="F65" s="10">
-        <v>14810216.222912636</v>
+        <v>16366940.385502718</v>
       </c>
       <c r="G65" s="10">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="H65" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I65" s="10">
         <v>5</v>
       </c>
       <c r="J65" s="10">
-        <v>440</v>
+        <v>478</v>
       </c>
       <c r="K65" s="10">
-        <v>14171503.656152204</v>
+        <v>15961705.359798137</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.35">
@@ -8359,22 +8359,22 @@
         <v>24</v>
       </c>
       <c r="B66" s="10">
-        <v>2029</v>
+        <v>2025</v>
       </c>
       <c r="C66" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D66" s="10">
         <v>9</v>
       </c>
       <c r="E66" s="10">
-        <v>1606</v>
+        <v>1596</v>
       </c>
       <c r="F66" s="10">
-        <v>32404512.52197903</v>
+        <v>37059990.447955251</v>
       </c>
       <c r="G66" s="10">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="H66" s="10">
         <v>2</v>
@@ -8383,10 +8383,10 @@
         <v>11</v>
       </c>
       <c r="J66" s="10">
-        <v>1907</v>
+        <v>1633</v>
       </c>
       <c r="K66" s="10">
-        <v>45501282.296908557</v>
+        <v>51313919.349024072</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.35">
@@ -8394,34 +8394,34 @@
         <v>27</v>
       </c>
       <c r="B67" s="10">
-        <v>1616</v>
+        <v>1622</v>
       </c>
       <c r="C67" s="10">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D67" s="10">
         <v>8</v>
       </c>
       <c r="E67" s="10">
-        <v>1130</v>
+        <v>1140</v>
       </c>
       <c r="F67" s="10">
-        <v>33665873.670948178</v>
+        <v>37740310.665981181</v>
       </c>
       <c r="G67" s="10">
-        <v>1572</v>
+        <v>1581</v>
       </c>
       <c r="H67" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I67" s="10">
         <v>6</v>
       </c>
       <c r="J67" s="10">
-        <v>1135</v>
+        <v>1195</v>
       </c>
       <c r="K67" s="10">
-        <v>31666643.56758967</v>
+        <v>36316046.751808286</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.35">
@@ -8429,7 +8429,7 @@
         <v>29</v>
       </c>
       <c r="B68" s="10">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C68" s="10">
         <v>1</v>
@@ -8438,13 +8438,13 @@
         <v>1</v>
       </c>
       <c r="E68" s="10">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="F68" s="10">
-        <v>21955038.147735532</v>
+        <v>24540614.424710989</v>
       </c>
       <c r="G68" s="10">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="H68" s="10">
         <v>3</v>
@@ -8453,10 +8453,10 @@
         <v>1</v>
       </c>
       <c r="J68" s="10">
-        <v>701</v>
+        <v>743</v>
       </c>
       <c r="K68" s="10">
-        <v>21711289.52854608</v>
+        <v>24557087.2031748</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.35">
@@ -8464,34 +8464,34 @@
         <v>57</v>
       </c>
       <c r="B69" s="10">
-        <v>1879</v>
+        <v>1875</v>
       </c>
       <c r="C69" s="10">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D69" s="10">
         <v>13</v>
       </c>
       <c r="E69" s="10">
-        <v>1290</v>
+        <v>1336</v>
       </c>
       <c r="F69" s="10">
-        <v>31196971.177899417</v>
+        <v>34664074.752712265</v>
       </c>
       <c r="G69" s="10">
-        <v>2097</v>
+        <v>2104</v>
       </c>
       <c r="H69" s="10">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="I69" s="10">
         <v>12</v>
       </c>
       <c r="J69" s="10">
-        <v>1462</v>
+        <v>1387</v>
       </c>
       <c r="K69" s="10">
-        <v>32860185.916051608</v>
+        <v>36884990.167373955</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.35">
@@ -8499,7 +8499,7 @@
         <v>137</v>
       </c>
       <c r="B70" s="10">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C70" s="10">
         <v>0</v>
@@ -8508,13 +8508,13 @@
         <v>1</v>
       </c>
       <c r="E70" s="10">
-        <v>212</v>
+        <v>293</v>
       </c>
       <c r="F70" s="10">
-        <v>2292405.9875394548</v>
+        <v>2621075.0989817032</v>
       </c>
       <c r="G70" s="10">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H70" s="10">
         <v>0</v>
@@ -8523,10 +8523,10 @@
         <v>0</v>
       </c>
       <c r="J70" s="10">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K70" s="10">
-        <v>375644.44752447098</v>
+        <v>629491.53686487197</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.35">
@@ -8534,7 +8534,7 @@
         <v>10</v>
       </c>
       <c r="B71" s="10">
-        <v>1745</v>
+        <v>1751</v>
       </c>
       <c r="C71" s="10">
         <v>2</v>
@@ -8543,13 +8543,13 @@
         <v>7</v>
       </c>
       <c r="E71" s="10">
-        <v>1689</v>
+        <v>1771</v>
       </c>
       <c r="F71" s="10">
-        <v>25616759.463998247</v>
+        <v>28226150.449650105</v>
       </c>
       <c r="G71" s="10">
-        <v>1672</v>
+        <v>1674</v>
       </c>
       <c r="H71" s="10">
         <v>4</v>
@@ -8558,10 +8558,10 @@
         <v>5</v>
       </c>
       <c r="J71" s="10">
-        <v>1868</v>
+        <v>1623</v>
       </c>
       <c r="K71" s="10">
-        <v>23897425.779863752</v>
+        <v>26876970.800084837</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.35">
@@ -8569,7 +8569,7 @@
         <v>12</v>
       </c>
       <c r="B72" s="10">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="C72" s="10">
         <v>1</v>
@@ -8578,13 +8578,13 @@
         <v>2</v>
       </c>
       <c r="E72" s="10">
-        <v>603</v>
+        <v>553</v>
       </c>
       <c r="F72" s="10">
-        <v>9992649.6044265609</v>
+        <v>11149314.029646087</v>
       </c>
       <c r="G72" s="10">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="H72" s="10">
         <v>1</v>
@@ -8593,10 +8593,10 @@
         <v>3</v>
       </c>
       <c r="J72" s="10">
-        <v>603</v>
+        <v>582</v>
       </c>
       <c r="K72" s="10">
-        <v>11330814.204616746</v>
+        <v>12473177.909479629</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.35">
@@ -8604,7 +8604,7 @@
         <v>162</v>
       </c>
       <c r="B73" s="10">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="C73" s="10">
         <v>20</v>
@@ -8613,13 +8613,13 @@
         <v>5</v>
       </c>
       <c r="E73" s="10">
-        <v>1182</v>
+        <v>899</v>
       </c>
       <c r="F73" s="10">
-        <v>17067513.194088787</v>
+        <v>18811212.930350754</v>
       </c>
       <c r="G73" s="10">
-        <v>1370</v>
+        <v>1365</v>
       </c>
       <c r="H73" s="10">
         <v>19</v>
@@ -8628,10 +8628,10 @@
         <v>4</v>
       </c>
       <c r="J73" s="10">
-        <v>844</v>
+        <v>946</v>
       </c>
       <c r="K73" s="10">
-        <v>15742610.95808477</v>
+        <v>17738676.445421282</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.35">
@@ -8639,7 +8639,7 @@
         <v>63</v>
       </c>
       <c r="B74" s="10">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="C74" s="10">
         <v>3</v>
@@ -8648,13 +8648,13 @@
         <v>5</v>
       </c>
       <c r="E74" s="10">
-        <v>1789</v>
+        <v>1784</v>
       </c>
       <c r="F74" s="10">
-        <v>8171514.3711125841</v>
+        <v>9657810.5725929085</v>
       </c>
       <c r="G74" s="10">
-        <v>1303</v>
+        <v>1296</v>
       </c>
       <c r="H74" s="10">
         <v>1</v>
@@ -8663,10 +8663,10 @@
         <v>5</v>
       </c>
       <c r="J74" s="10">
-        <v>1226</v>
+        <v>1218</v>
       </c>
       <c r="K74" s="10">
-        <v>11909259.237161091</v>
+        <v>12929426.00816833</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.35">
@@ -8674,19 +8674,19 @@
         <v>59</v>
       </c>
       <c r="B75" s="10">
-        <v>1743</v>
+        <v>1748</v>
       </c>
       <c r="C75" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D75" s="10">
         <v>5</v>
       </c>
       <c r="E75" s="10">
-        <v>1215</v>
+        <v>1261</v>
       </c>
       <c r="F75" s="10">
-        <v>28308720.802652378</v>
+        <v>31676139.724773306</v>
       </c>
       <c r="G75" s="10">
         <v>1728</v>
@@ -8698,10 +8698,10 @@
         <v>4</v>
       </c>
       <c r="J75" s="10">
-        <v>1158</v>
+        <v>1175</v>
       </c>
       <c r="K75" s="10">
-        <v>29124730.546930134</v>
+        <v>32852093.120552234</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.35">
@@ -8709,22 +8709,22 @@
         <v>139</v>
       </c>
       <c r="B76" s="10">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C76" s="10">
         <v>1</v>
       </c>
       <c r="D76" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E76" s="10">
-        <v>511</v>
+        <v>563</v>
       </c>
       <c r="F76" s="10">
-        <v>6354765.22670455</v>
+        <v>7069736.1221274221</v>
       </c>
       <c r="G76" s="10">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="H76" s="10">
         <v>2</v>
@@ -8733,10 +8733,10 @@
         <v>1</v>
       </c>
       <c r="J76" s="10">
-        <v>501</v>
+        <v>473</v>
       </c>
       <c r="K76" s="10">
-        <v>5975962.6817722982</v>
+        <v>6760049.5165477693</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.35">
@@ -8744,7 +8744,7 @@
         <v>170</v>
       </c>
       <c r="B77" s="10">
-        <v>897</v>
+        <v>891</v>
       </c>
       <c r="C77" s="10">
         <v>1</v>
@@ -8753,13 +8753,13 @@
         <v>1</v>
       </c>
       <c r="E77" s="10">
-        <v>813</v>
+        <v>825</v>
       </c>
       <c r="F77" s="10">
-        <v>9989788.20540924</v>
+        <v>11067997.809093548</v>
       </c>
       <c r="G77" s="10">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="H77" s="10">
         <v>2</v>
@@ -8768,10 +8768,10 @@
         <v>1</v>
       </c>
       <c r="J77" s="10">
-        <v>920</v>
+        <v>879</v>
       </c>
       <c r="K77" s="10">
-        <v>8967153.6823930759</v>
+        <v>10338062.634815617</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.35">
@@ -8779,7 +8779,7 @@
         <v>61</v>
       </c>
       <c r="B78" s="10">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C78" s="10">
         <v>0</v>
@@ -8788,13 +8788,13 @@
         <v>4</v>
       </c>
       <c r="E78" s="10">
-        <v>513</v>
+        <v>497</v>
       </c>
       <c r="F78" s="10">
-        <v>5514504.1095447363</v>
+        <v>6646183.4289873363</v>
       </c>
       <c r="G78" s="10">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="H78" s="10">
         <v>0</v>
@@ -8803,10 +8803,10 @@
         <v>3</v>
       </c>
       <c r="J78" s="10">
-        <v>467</v>
+        <v>437</v>
       </c>
       <c r="K78" s="10">
-        <v>8838437.0925082453</v>
+        <v>10027767.237602197</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.35">
@@ -8814,7 +8814,7 @@
         <v>129</v>
       </c>
       <c r="B79" s="10">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="C79" s="10">
         <v>1</v>
@@ -8823,25 +8823,25 @@
         <v>1</v>
       </c>
       <c r="E79" s="10">
-        <v>924</v>
+        <v>759</v>
       </c>
       <c r="F79" s="10">
-        <v>6750615.9754769709</v>
+        <v>7438912.9088206459</v>
       </c>
       <c r="G79" s="10">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="H79" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I79" s="10">
         <v>1</v>
       </c>
       <c r="J79" s="10">
-        <v>698</v>
+        <v>710</v>
       </c>
       <c r="K79" s="10">
-        <v>7890411.4936368279</v>
+        <v>8685443.1066132579</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.35">
@@ -8849,7 +8849,7 @@
         <v>35</v>
       </c>
       <c r="B80" s="10">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C80" s="10">
         <v>2</v>
@@ -8858,13 +8858,13 @@
         <v>5</v>
       </c>
       <c r="E80" s="10">
-        <v>355</v>
+        <v>391</v>
       </c>
       <c r="F80" s="10">
-        <v>7653920.359339037</v>
+        <v>8497870.0991402362</v>
       </c>
       <c r="G80" s="10">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="H80" s="10">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>7</v>
       </c>
       <c r="J80" s="10">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="K80" s="10">
-        <v>8390126.8830564395</v>
+        <v>9304320.9951788951</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.35">
@@ -8884,7 +8884,7 @@
         <v>107</v>
       </c>
       <c r="B81" s="10">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="C81" s="10">
         <v>1</v>
@@ -8893,13 +8893,13 @@
         <v>4</v>
       </c>
       <c r="E81" s="10">
-        <v>691</v>
+        <v>725</v>
       </c>
       <c r="F81" s="10">
-        <v>21521164.578006919</v>
+        <v>23923392.832980826</v>
       </c>
       <c r="G81" s="10">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="H81" s="10">
         <v>4</v>
@@ -8908,10 +8908,10 @@
         <v>3</v>
       </c>
       <c r="J81" s="10">
-        <v>672</v>
+        <v>747</v>
       </c>
       <c r="K81" s="10">
-        <v>20746372.803316668</v>
+        <v>23499947.38004652</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.35">
@@ -8919,22 +8919,22 @@
         <v>37</v>
       </c>
       <c r="B82" s="10">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="C82" s="10">
         <v>1</v>
       </c>
       <c r="D82" s="10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E82" s="10">
-        <v>814</v>
+        <v>673</v>
       </c>
       <c r="F82" s="10">
-        <v>13363157.032803241</v>
+        <v>14714128.498747272</v>
       </c>
       <c r="G82" s="10">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="H82" s="10">
         <v>2</v>
@@ -8943,10 +8943,10 @@
         <v>10</v>
       </c>
       <c r="J82" s="10">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="K82" s="10">
-        <v>13054902.089641485</v>
+        <v>14617965.617096372</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.35">
@@ -8954,7 +8954,7 @@
         <v>76</v>
       </c>
       <c r="B83" s="10">
-        <v>922</v>
+        <v>931</v>
       </c>
       <c r="C83" s="10">
         <v>0</v>
@@ -8963,13 +8963,13 @@
         <v>2</v>
       </c>
       <c r="E83" s="10">
-        <v>863</v>
+        <v>1067</v>
       </c>
       <c r="F83" s="10">
-        <v>10535619.815227035</v>
+        <v>11668411.154587179</v>
       </c>
       <c r="G83" s="10">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H83" s="10">
         <v>1</v>
@@ -8978,10 +8978,10 @@
         <v>2</v>
       </c>
       <c r="J83" s="10">
-        <v>1215</v>
+        <v>1182</v>
       </c>
       <c r="K83" s="10">
-        <v>11489184.409651188</v>
+        <v>12972567.696969476</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.35">
@@ -8989,7 +8989,7 @@
         <v>65</v>
       </c>
       <c r="B84" s="10">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="C84" s="10">
         <v>3</v>
@@ -8998,13 +8998,13 @@
         <v>4</v>
       </c>
       <c r="E84" s="10">
-        <v>816</v>
+        <v>804</v>
       </c>
       <c r="F84" s="10">
-        <v>12029136.598088751</v>
+        <v>13451041.548536345</v>
       </c>
       <c r="G84" s="10">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H84" s="10">
         <v>1</v>
@@ -9013,10 +9013,10 @@
         <v>4</v>
       </c>
       <c r="J84" s="10">
-        <v>688</v>
+        <v>844</v>
       </c>
       <c r="K84" s="10">
-        <v>8436359.6429892965</v>
+        <v>10024481.605834993</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.35">
@@ -9024,34 +9024,34 @@
         <v>89</v>
       </c>
       <c r="B85" s="10">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="C85" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D85" s="10">
         <v>5</v>
       </c>
       <c r="E85" s="10">
-        <v>723</v>
+        <v>645</v>
       </c>
       <c r="F85" s="10">
-        <v>12058816.101821585</v>
+        <v>13549867.950274644</v>
       </c>
       <c r="G85" s="10">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H85" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I85" s="10">
         <v>6</v>
       </c>
       <c r="J85" s="10">
-        <v>831</v>
+        <v>756</v>
       </c>
       <c r="K85" s="10">
-        <v>12570353.635213269</v>
+        <v>14559640.370847676</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.35">
@@ -9059,7 +9059,7 @@
         <v>147</v>
       </c>
       <c r="B86" s="10">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C86" s="10">
         <v>1</v>
@@ -9068,25 +9068,25 @@
         <v>1</v>
       </c>
       <c r="E86" s="10">
-        <v>686</v>
+        <v>588</v>
       </c>
       <c r="F86" s="10">
-        <v>6345447.8126080902</v>
+        <v>6882758.8965735016</v>
       </c>
       <c r="G86" s="10">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="H86" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I86" s="10">
         <v>1</v>
       </c>
       <c r="J86" s="10">
-        <v>575</v>
+        <v>599</v>
       </c>
       <c r="K86" s="10">
-        <v>6485541.9481432578</v>
+        <v>7315762.4698836477</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.35">
@@ -9094,22 +9094,22 @@
         <v>164</v>
       </c>
       <c r="B87" s="10">
-        <v>1710</v>
+        <v>1712</v>
       </c>
       <c r="C87" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D87" s="10">
         <v>10</v>
       </c>
       <c r="E87" s="10">
-        <v>1262</v>
+        <v>1202</v>
       </c>
       <c r="F87" s="10">
-        <v>24330358.382188115</v>
+        <v>26079892.628516715</v>
       </c>
       <c r="G87" s="10">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="H87" s="10">
         <v>0</v>
@@ -9118,10 +9118,10 @@
         <v>10</v>
       </c>
       <c r="J87" s="10">
-        <v>1231</v>
+        <v>1277</v>
       </c>
       <c r="K87" s="10">
-        <v>24951429.425259337</v>
+        <v>28525506.244806383</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.35">
@@ -9129,7 +9129,7 @@
         <v>91</v>
       </c>
       <c r="B88" s="10">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="C88" s="10">
         <v>2</v>
@@ -9138,13 +9138,13 @@
         <v>3</v>
       </c>
       <c r="E88" s="10">
-        <v>631</v>
+        <v>687</v>
       </c>
       <c r="F88" s="10">
-        <v>6599894.3574415911</v>
+        <v>7165191.5008343831</v>
       </c>
       <c r="G88" s="10">
-        <v>588</v>
+        <v>572</v>
       </c>
       <c r="H88" s="10">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>3</v>
       </c>
       <c r="J88" s="10">
-        <v>668</v>
+        <v>692</v>
       </c>
       <c r="K88" s="10">
-        <v>5256040.7605468342</v>
+        <v>5946913.5955582066</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.35">
@@ -9164,7 +9164,7 @@
         <v>97</v>
       </c>
       <c r="B89" s="10">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="C89" s="10">
         <v>10</v>
@@ -9173,13 +9173,13 @@
         <v>6</v>
       </c>
       <c r="E89" s="10">
-        <v>494</v>
+        <v>582</v>
       </c>
       <c r="F89" s="10">
-        <v>11603173.468591984</v>
+        <v>12970475.295201844</v>
       </c>
       <c r="G89" s="10">
-        <v>620</v>
+        <v>634</v>
       </c>
       <c r="H89" s="10">
         <v>3</v>
@@ -9188,10 +9188,10 @@
         <v>7</v>
       </c>
       <c r="J89" s="10">
-        <v>590</v>
+        <v>548</v>
       </c>
       <c r="K89" s="10">
-        <v>12085662.536187533</v>
+        <v>13699798.317924472</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.35">
@@ -9199,22 +9199,22 @@
         <v>78</v>
       </c>
       <c r="B90" s="10">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C90" s="10">
         <v>1</v>
       </c>
       <c r="D90" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E90" s="10">
-        <v>304</v>
+        <v>279</v>
       </c>
       <c r="F90" s="10">
-        <v>3559231.8746322528</v>
+        <v>3870008.7806480499</v>
       </c>
       <c r="G90" s="10">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="H90" s="10">
         <v>1</v>
@@ -9223,10 +9223,10 @@
         <v>0</v>
       </c>
       <c r="J90" s="10">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="K90" s="10">
-        <v>3096779.6955845412</v>
+        <v>3450645.4612574582</v>
       </c>
     </row>
   </sheetData>

--- a/SITE MONITORING.xlsx
+++ b/SITE MONITORING.xlsx
@@ -1114,19 +1114,19 @@
       </c>
       <c r="F2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6721217.3677318636</v>
+        <v>7403766.379118205</v>
       </c>
       <c r="G2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6152818.0823086826</v>
+        <v>6772587.9741216879</v>
       </c>
       <c r="H2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="I2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="J2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1146,11 +1146,11 @@
       </c>
       <c r="N2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O2">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="P2">
         <v>3</v>
@@ -1174,19 +1174,19 @@
       </c>
       <c r="F3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8156654.6793239554</v>
+        <v>9081858.2921876088</v>
       </c>
       <c r="G3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7429191.778023608</v>
+        <v>8061375.9813275402</v>
       </c>
       <c r="H3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>577</v>
+        <v>610</v>
       </c>
       <c r="I3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="J3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="O3">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="P3">
         <v>2</v>
@@ -1234,19 +1234,19 @@
       </c>
       <c r="F4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7399552.3442232348</v>
+        <v>8472343.6507805083</v>
       </c>
       <c r="G4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7950360.3691030573</v>
+        <v>9235547.2123001292</v>
       </c>
       <c r="H4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="I4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="J4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1262,15 +1262,15 @@
       </c>
       <c r="M4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="O4">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="P4">
         <v>4</v>
@@ -1294,19 +1294,19 @@
       </c>
       <c r="F5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15552827.417094398</v>
+        <v>17086090.225409012</v>
       </c>
       <c r="G5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15725446.023067832</v>
+        <v>17268876.652935285</v>
       </c>
       <c r="H5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>980</v>
+        <v>944</v>
       </c>
       <c r="I5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1029</v>
+        <v>992</v>
       </c>
       <c r="J5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1326,11 +1326,11 @@
       </c>
       <c r="N5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="O5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="P5">
         <v>3</v>
@@ -1354,19 +1354,19 @@
       </c>
       <c r="F6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5858964.4469372071</v>
+        <v>6579428.4202598128</v>
       </c>
       <c r="G6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6781752.4824333154</v>
+        <v>7621380.8444610247</v>
       </c>
       <c r="H6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="I6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="J6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1386,11 +1386,11 @@
       </c>
       <c r="N6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="O6">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="P6">
         <v>3</v>
@@ -1414,19 +1414,19 @@
       </c>
       <c r="F7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5921570.4369004704</v>
+        <v>6507233.0071156528</v>
       </c>
       <c r="G7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5992231.4276800314</v>
+        <v>6557460.7367064152</v>
       </c>
       <c r="H7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="J7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1446,11 +1446,11 @@
       </c>
       <c r="N7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O7">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="P7">
         <v>2</v>
@@ -1474,19 +1474,19 @@
       </c>
       <c r="F8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6799052.3254508786</v>
+        <v>7502762.8835716713</v>
       </c>
       <c r="G8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6874438.380801552</v>
+        <v>7573764.9543150803</v>
       </c>
       <c r="H8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>525</v>
+        <v>483</v>
       </c>
       <c r="I8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>512</v>
+        <v>490</v>
       </c>
       <c r="J8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1502,15 +1502,15 @@
       </c>
       <c r="M8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="O8">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="P8">
         <v>9</v>
@@ -1534,19 +1534,19 @@
       </c>
       <c r="F9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>2979868.2358265291</v>
+        <v>3333683.0118716359</v>
       </c>
       <c r="G9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3098186.935847898</v>
+        <v>3412858.6587270629</v>
       </c>
       <c r="H9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="I9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="J9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="N9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="O9">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -1594,19 +1594,19 @@
       </c>
       <c r="F10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>3006238.1098317681</v>
+        <v>3327945.8076576372</v>
       </c>
       <c r="G10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>268270.17518669402</v>
+        <v>356764.62464087899</v>
       </c>
       <c r="H10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="I10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1</v>
+        <v>136</v>
       </c>
       <c r="J10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1626,11 +1626,11 @@
       </c>
       <c r="N10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O10">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P10">
         <v>1</v>
@@ -1654,19 +1654,19 @@
       </c>
       <c r="F11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4782564.6090684468</v>
+        <v>5285015.9714740682</v>
       </c>
       <c r="G11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6812954.8209106149</v>
+        <v>7406718.8965042289</v>
       </c>
       <c r="H11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>286</v>
+        <v>369</v>
       </c>
       <c r="I11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>509</v>
+        <v>379</v>
       </c>
       <c r="J11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="O11">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="P11">
         <v>4</v>
@@ -1714,19 +1714,19 @@
       </c>
       <c r="F12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>2250565.6269620662</v>
+        <v>2493060.9630141081</v>
       </c>
       <c r="G12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>2959702.482844451</v>
+        <v>3295803.4780012751</v>
       </c>
       <c r="H12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>321</v>
+        <v>252</v>
       </c>
       <c r="I12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="J12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1746,11 +1746,11 @@
       </c>
       <c r="N12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="O12">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="P12">
         <v>3</v>
@@ -1774,19 +1774,19 @@
       </c>
       <c r="F13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>3008058.056240594</v>
+        <v>3339864.9400243089</v>
       </c>
       <c r="G13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3318437.6932629938</v>
+        <v>3668103.6269933642</v>
       </c>
       <c r="H13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="I13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="J13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="L13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -1806,11 +1806,11 @@
       </c>
       <c r="N13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="O13">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="P13">
         <v>5</v>
@@ -1834,19 +1834,19 @@
       </c>
       <c r="F14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7512189.1632019328</v>
+        <v>7512201.2733524209</v>
       </c>
       <c r="G14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9987199.9195197597</v>
+        <v>11435917.552780986</v>
       </c>
       <c r="H14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="I14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>867</v>
+        <v>1100</v>
       </c>
       <c r="J14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1866,11 +1866,11 @@
       </c>
       <c r="N14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1445</v>
+        <v>1433</v>
       </c>
       <c r="O14">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1426</v>
+        <v>1430</v>
       </c>
       <c r="P14">
         <v>2</v>
@@ -1894,19 +1894,19 @@
       </c>
       <c r="F15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21031434.832303733</v>
+        <v>23900483.28657113</v>
       </c>
       <c r="G15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21848454.097331937</v>
+        <v>24163229.470245697</v>
       </c>
       <c r="H15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1281</v>
+        <v>1090</v>
       </c>
       <c r="I15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>896</v>
+        <v>888</v>
       </c>
       <c r="J15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1926,11 +1926,11 @@
       </c>
       <c r="N15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="O15">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="P15">
         <v>4</v>
@@ -1954,19 +1954,19 @@
       </c>
       <c r="F16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12464962.956552835</v>
+        <v>13687331.401381763</v>
       </c>
       <c r="G16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12945342.206328144</v>
+        <v>14290505.340465739</v>
       </c>
       <c r="H16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>909</v>
+        <v>882</v>
       </c>
       <c r="I16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>943</v>
+        <v>1346</v>
       </c>
       <c r="J16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1986,11 +1986,11 @@
       </c>
       <c r="N16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="O16">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="P16">
         <v>3</v>
@@ -2014,19 +2014,19 @@
       </c>
       <c r="F17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13216752.071126426</v>
+        <v>14508159.402924469</v>
       </c>
       <c r="G17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8571431.2894174531</v>
+        <v>9683317.7825561687</v>
       </c>
       <c r="H17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>636</v>
+        <v>697</v>
       </c>
       <c r="I17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>726</v>
+        <v>801</v>
       </c>
       <c r="J17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2046,11 +2046,11 @@
       </c>
       <c r="N17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="O17">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="P17">
         <v>4</v>
@@ -2074,19 +2074,19 @@
       </c>
       <c r="F18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>43765663.42008768</v>
+        <v>48234189.966538787</v>
       </c>
       <c r="G18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>49075557.599973261</v>
+        <v>54021728.128000915</v>
       </c>
       <c r="H18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2035</v>
+        <v>1885</v>
       </c>
       <c r="I18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2900</v>
+        <v>2175</v>
       </c>
       <c r="J18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2098,19 +2098,19 @@
       </c>
       <c r="L18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="M18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="N18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2802</v>
+        <v>2790</v>
       </c>
       <c r="O18">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2942</v>
+        <v>2915</v>
       </c>
       <c r="P18">
         <v>5</v>
@@ -2134,19 +2134,19 @@
       </c>
       <c r="F19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24021205.021760464</v>
+        <v>26648723.196364921</v>
       </c>
       <c r="G19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8067116.1734909713</v>
+        <v>9209407.9122159164</v>
       </c>
       <c r="H19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1139</v>
+        <v>1183</v>
       </c>
       <c r="I19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>9</v>
+        <v>1206</v>
       </c>
       <c r="J19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="M19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="O19">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1367</v>
+        <v>1370</v>
       </c>
       <c r="P19">
         <v>1</v>
@@ -2194,19 +2194,19 @@
       </c>
       <c r="F20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>46803671.881852701</v>
+        <v>52087375.427271821</v>
       </c>
       <c r="G20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>47738508.937325202</v>
+        <v>52488658.529909022</v>
       </c>
       <c r="H20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2383</v>
+        <v>2404</v>
       </c>
       <c r="I20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2214</v>
+        <v>2213</v>
       </c>
       <c r="J20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2218,19 +2218,19 @@
       </c>
       <c r="L20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="N20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2984</v>
+        <v>2996</v>
       </c>
       <c r="O20">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2962</v>
+        <v>2968</v>
       </c>
       <c r="P20">
         <v>8</v>
@@ -2254,19 +2254,19 @@
       </c>
       <c r="F21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6796338.2171994355</v>
+        <v>7489624.1028591068</v>
       </c>
       <c r="G21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7122002.4557506125</v>
+        <v>8131500.9638309013</v>
       </c>
       <c r="H21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>463</v>
+        <v>527</v>
       </c>
       <c r="I21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>515</v>
+        <v>901</v>
       </c>
       <c r="J21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2286,11 +2286,11 @@
       </c>
       <c r="N21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="O21">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="P21">
         <v>1</v>
@@ -2314,19 +2314,19 @@
       </c>
       <c r="F22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18988796.478382163</v>
+        <v>21050766.076841544</v>
       </c>
       <c r="G22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19306182.14601028</v>
+        <v>21530945.293318376</v>
       </c>
       <c r="H22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="I22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1334</v>
+        <v>1375</v>
       </c>
       <c r="J22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2342,15 +2342,15 @@
       </c>
       <c r="M22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1709</v>
+        <v>1713</v>
       </c>
       <c r="O22">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1732</v>
+        <v>1729</v>
       </c>
       <c r="P22">
         <v>8</v>
@@ -2374,19 +2374,19 @@
       </c>
       <c r="F23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8482004.1993926615</v>
+        <v>9392854.7496682443</v>
       </c>
       <c r="G23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7846298.3074562633</v>
+        <v>8641800.9232224785</v>
       </c>
       <c r="H23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>826</v>
+        <v>773</v>
       </c>
       <c r="I23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>766</v>
+        <v>755</v>
       </c>
       <c r="J23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2406,11 +2406,11 @@
       </c>
       <c r="N23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="O23">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="P23">
         <v>1</v>
@@ -2434,19 +2434,19 @@
       </c>
       <c r="F24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8755237.1310375761</v>
+        <v>9579970.5974776149</v>
       </c>
       <c r="G24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9960916.6373697724</v>
+        <v>11009560.832062732</v>
       </c>
       <c r="H24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>570</v>
+        <v>756</v>
       </c>
       <c r="I24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>757</v>
+        <v>723</v>
       </c>
       <c r="J24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2462,15 +2462,15 @@
       </c>
       <c r="M24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="O24">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="P24">
         <v>3</v>
@@ -2494,19 +2494,19 @@
       </c>
       <c r="F25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>2560118.3425952001</v>
+        <v>2855776.6463130671</v>
       </c>
       <c r="G25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>2055834.390430477</v>
+        <v>2269431.611853485</v>
       </c>
       <c r="H25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="I25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>146</v>
+        <v>197</v>
       </c>
       <c r="J25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2526,11 +2526,11 @@
       </c>
       <c r="N25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="O25">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="P25">
         <v>1</v>
@@ -2554,19 +2554,19 @@
       </c>
       <c r="F26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>22718777.941925272</v>
+        <v>24822617.942399263</v>
       </c>
       <c r="G26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18674864.213929038</v>
+        <v>20667503.031828664</v>
       </c>
       <c r="H26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1514</v>
+        <v>1464</v>
       </c>
       <c r="I26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1398</v>
+        <v>1347</v>
       </c>
       <c r="J26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2586,11 +2586,11 @@
       </c>
       <c r="N26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1663</v>
+        <v>1668</v>
       </c>
       <c r="O26">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1661</v>
+        <v>1667</v>
       </c>
       <c r="P26">
         <v>1</v>
@@ -2614,19 +2614,19 @@
       </c>
       <c r="F27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14153077.91888571</v>
+        <v>15651652.677112721</v>
       </c>
       <c r="G27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14551107.043437852</v>
+        <v>16374105.086462455</v>
       </c>
       <c r="H27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>648</v>
+        <v>606</v>
       </c>
       <c r="I27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>617</v>
+        <v>629</v>
       </c>
       <c r="J27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2646,11 +2646,11 @@
       </c>
       <c r="N27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="O27">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="P27">
         <v>1</v>
@@ -2674,19 +2674,19 @@
       </c>
       <c r="F28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15725447.580771975</v>
+        <v>17399020.220064308</v>
       </c>
       <c r="G28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14437291.715968899</v>
+        <v>16060768.424630741</v>
       </c>
       <c r="H28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>733</v>
+        <v>558</v>
       </c>
       <c r="I28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>826</v>
+        <v>836</v>
       </c>
       <c r="J28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2706,11 +2706,11 @@
       </c>
       <c r="N28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="O28">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -2734,19 +2734,19 @@
       </c>
       <c r="F29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19703437.006434254</v>
+        <v>21903595.915449053</v>
       </c>
       <c r="G29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20056812.599486277</v>
+        <v>22045259.973748617</v>
       </c>
       <c r="H29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>967</v>
+        <v>1039</v>
       </c>
       <c r="I29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="J29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2766,11 +2766,11 @@
       </c>
       <c r="N29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="O29">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1116</v>
+        <v>1109</v>
       </c>
       <c r="P29">
         <v>1</v>
@@ -2794,19 +2794,19 @@
       </c>
       <c r="F30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>29722501.854668796</v>
+        <v>33172620.572869904</v>
       </c>
       <c r="G30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>28294835.68957008</v>
+        <v>31324284.763955772</v>
       </c>
       <c r="H30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1178</v>
+        <v>1173</v>
       </c>
       <c r="I30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1146</v>
+        <v>1181</v>
       </c>
       <c r="J30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="L30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -2826,11 +2826,11 @@
       </c>
       <c r="N30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1487</v>
+        <v>1497</v>
       </c>
       <c r="O30">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1478</v>
+        <v>1468</v>
       </c>
       <c r="P30">
         <v>4</v>
@@ -2854,19 +2854,19 @@
       </c>
       <c r="F31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10980480.649050532</v>
+        <v>12052276.283295762</v>
       </c>
       <c r="G31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11557874.043439522</v>
+        <v>12818085.34321888</v>
       </c>
       <c r="H31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>528</v>
+        <v>448</v>
       </c>
       <c r="I31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>528</v>
+        <v>554</v>
       </c>
       <c r="J31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="O31">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="P31">
         <v>3</v>
@@ -2914,19 +2914,19 @@
       </c>
       <c r="F32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>35060631.354011633</v>
+        <v>38950361.986051217</v>
       </c>
       <c r="G32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>35288715.200185522</v>
+        <v>39218450.568227202</v>
       </c>
       <c r="H32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1770</v>
+        <v>1575</v>
       </c>
       <c r="I32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="J32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2946,11 +2946,11 @@
       </c>
       <c r="N32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="O32">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="P32">
         <v>5</v>
@@ -2974,23 +2974,23 @@
       </c>
       <c r="F33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12333157.928200064</v>
+        <v>13641140.097482843</v>
       </c>
       <c r="G33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11529791.435436616</v>
+        <v>12702349.062420461</v>
       </c>
       <c r="H33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>674</v>
+        <v>660</v>
       </c>
       <c r="I33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>696</v>
+        <v>747</v>
       </c>
       <c r="J33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -3006,11 +3006,11 @@
       </c>
       <c r="N33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="O33">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="P33">
         <v>3</v>
@@ -3034,19 +3034,19 @@
       </c>
       <c r="F34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10103964.004989509</v>
+        <v>11020053.945719752</v>
       </c>
       <c r="G34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11112334.557640174</v>
+        <v>12313396.90175152</v>
       </c>
       <c r="H34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>459</v>
+        <v>422</v>
       </c>
       <c r="I34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>557</v>
+        <v>580</v>
       </c>
       <c r="J34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3066,11 +3066,11 @@
       </c>
       <c r="N34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="O34">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="P34">
         <v>4</v>
@@ -3094,19 +3094,19 @@
       </c>
       <c r="F35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17854652.580006875</v>
+        <v>19655782.859162141</v>
       </c>
       <c r="G35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17193856.285997957</v>
+        <v>19043186.757094968</v>
       </c>
       <c r="H35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>872</v>
+        <v>815</v>
       </c>
       <c r="I35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>836</v>
+        <v>793</v>
       </c>
       <c r="J35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3118,19 +3118,19 @@
       </c>
       <c r="L35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1122</v>
+        <v>1113</v>
       </c>
       <c r="O35">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="P35">
         <v>13</v>
@@ -3154,19 +3154,19 @@
       </c>
       <c r="F36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17212785.665607128</v>
+        <v>19180872.019964613</v>
       </c>
       <c r="G36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15645497.955338975</v>
+        <v>17431602.978954356</v>
       </c>
       <c r="H36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>869</v>
+        <v>823</v>
       </c>
       <c r="I36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>769</v>
+        <v>779</v>
       </c>
       <c r="J36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="L36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3186,11 +3186,11 @@
       </c>
       <c r="N36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1183</v>
+        <v>1173</v>
       </c>
       <c r="O36">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1365</v>
+        <v>1351</v>
       </c>
       <c r="P36">
         <v>4</v>
@@ -3214,19 +3214,19 @@
       </c>
       <c r="F37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>27010112.979283512</v>
+        <v>29876677.049243852</v>
       </c>
       <c r="G37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>28638765.273579638</v>
+        <v>31725346.660909802</v>
       </c>
       <c r="H37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1382</v>
+        <v>1425</v>
       </c>
       <c r="I37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="J37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3238,19 +3238,19 @@
       </c>
       <c r="L37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1840</v>
+        <v>1834</v>
       </c>
       <c r="O37">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2469</v>
+        <v>2445</v>
       </c>
       <c r="P37">
         <v>16</v>
@@ -3274,19 +3274,19 @@
       </c>
       <c r="F38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11241543.166229179</v>
+        <v>12462518.939564969</v>
       </c>
       <c r="G38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10344833.566559069</v>
+        <v>11421939.055878559</v>
       </c>
       <c r="H38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="I38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="J38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3306,11 +3306,11 @@
       </c>
       <c r="N38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="O38">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="P38">
         <v>3</v>
@@ -3334,19 +3334,19 @@
       </c>
       <c r="F39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>30939701.804248367</v>
+        <v>34603754.857470505</v>
       </c>
       <c r="G39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>34562600.775030553</v>
+        <v>38251004.015172802</v>
       </c>
       <c r="H39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1917</v>
+        <v>2011</v>
       </c>
       <c r="I39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1934</v>
+        <v>1970</v>
       </c>
       <c r="J39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3366,11 +3366,11 @@
       </c>
       <c r="N39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1946</v>
+        <v>1943</v>
       </c>
       <c r="O39">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2049</v>
+        <v>2054</v>
       </c>
       <c r="P39">
         <v>4</v>
@@ -3394,19 +3394,19 @@
       </c>
       <c r="F40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21592902.705368832</v>
+        <v>23998515.44422197</v>
       </c>
       <c r="G40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22304769.355051536</v>
+        <v>24688120.726337377</v>
       </c>
       <c r="H40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="I40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>797</v>
+        <v>772</v>
       </c>
       <c r="J40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3422,15 +3422,15 @@
       </c>
       <c r="M40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="O40">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="P40">
         <v>3</v>
@@ -3454,19 +3454,19 @@
       </c>
       <c r="F41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19361417.568360262</v>
+        <v>21126962.544779114</v>
       </c>
       <c r="G41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10411236.41967774</v>
+        <v>12296140.818591988</v>
       </c>
       <c r="H41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>934</v>
+        <v>909</v>
       </c>
       <c r="I41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>925</v>
+        <v>936</v>
       </c>
       <c r="J41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3486,11 +3486,11 @@
       </c>
       <c r="N41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1154</v>
+        <v>1143</v>
       </c>
       <c r="O41">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="P41">
         <v>4</v>
@@ -3514,19 +3514,19 @@
       </c>
       <c r="F42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18232693.534131359</v>
+        <v>20292399.117647201</v>
       </c>
       <c r="G42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17755224.245391376</v>
+        <v>19732293.398156039</v>
       </c>
       <c r="H42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>630</v>
+        <v>615</v>
       </c>
       <c r="I42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>645</v>
+        <v>668</v>
       </c>
       <c r="J42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3546,11 +3546,11 @@
       </c>
       <c r="N42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="O42">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="P42">
         <v>2</v>
@@ -3574,19 +3574,19 @@
       </c>
       <c r="F43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10453278.752228426</v>
+        <v>11675592.217419149</v>
       </c>
       <c r="G43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11363931.519229412</v>
+        <v>12617432.245743323</v>
       </c>
       <c r="H43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>600</v>
+        <v>655</v>
       </c>
       <c r="I43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>708</v>
+        <v>566</v>
       </c>
       <c r="J43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3602,15 +3602,15 @@
       </c>
       <c r="M43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="O43">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="P43">
         <v>2</v>
@@ -3634,19 +3634,19 @@
       </c>
       <c r="F44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10321050.736769276</v>
+        <v>11469697.687318595</v>
       </c>
       <c r="G44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9780767.8360642996</v>
+        <v>10927877.013120186</v>
       </c>
       <c r="H44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>743</v>
+        <v>711</v>
       </c>
       <c r="I44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>744</v>
+        <v>701</v>
       </c>
       <c r="J44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3666,11 +3666,11 @@
       </c>
       <c r="N44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="O44">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="P44">
         <v>3</v>
@@ -3694,23 +3694,23 @@
       </c>
       <c r="F45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>36614471.61384137</v>
+        <v>39658020.754120097</v>
       </c>
       <c r="G45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>30732060.500332795</v>
+        <v>33970655.650308527</v>
       </c>
       <c r="H45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1018</v>
+        <v>1068</v>
       </c>
       <c r="I45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1127</v>
+        <v>1072</v>
       </c>
       <c r="J45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="O45">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="P45">
         <v>4</v>
@@ -3754,19 +3754,19 @@
       </c>
       <c r="F46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16076235.359384179</v>
+        <v>17566001.730502713</v>
       </c>
       <c r="G46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14733574.789885193</v>
+        <v>16286567.597074073</v>
       </c>
       <c r="H46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>882</v>
+        <v>906</v>
       </c>
       <c r="I46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>3212</v>
+        <v>923</v>
       </c>
       <c r="J46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3774,7 +3774,7 @@
       </c>
       <c r="K46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -3786,11 +3786,11 @@
       </c>
       <c r="N46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="O46">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="P46">
         <v>4</v>
@@ -3814,19 +3814,19 @@
       </c>
       <c r="F47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20734256.805620253</v>
+        <v>23215427.489808504</v>
       </c>
       <c r="G47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>26407949.501988936</v>
+        <v>29152507.694931164</v>
       </c>
       <c r="H47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1001</v>
+        <v>959</v>
       </c>
       <c r="I47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1033</v>
+        <v>1017</v>
       </c>
       <c r="J47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="L47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3846,11 +3846,11 @@
       </c>
       <c r="N47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="O47">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1363</v>
+        <v>1354</v>
       </c>
       <c r="P47">
         <v>6</v>
@@ -3874,19 +3874,19 @@
       </c>
       <c r="F48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10925987.34804726</v>
+        <v>12332994.762099404</v>
       </c>
       <c r="G48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13673852.473286686</v>
+        <v>15040340.008889956</v>
       </c>
       <c r="H48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>392</v>
+        <v>363</v>
       </c>
       <c r="I48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="J48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3902,11 +3902,11 @@
       </c>
       <c r="M48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O48">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -3934,19 +3934,19 @@
       </c>
       <c r="F49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12764477.259903496</v>
+        <v>14070540.257583896</v>
       </c>
       <c r="G49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10116058.890716156</v>
+        <v>11090723.62741236</v>
       </c>
       <c r="H49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>383</v>
+        <v>322</v>
       </c>
       <c r="I49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="J49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="O49">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="P49">
         <v>5</v>
@@ -3994,19 +3994,19 @@
       </c>
       <c r="F50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9941003.7667885516</v>
+        <v>10956552.874769645</v>
       </c>
       <c r="G50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8825567.6649791468</v>
+        <v>9670437.9324168526</v>
       </c>
       <c r="H50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>327</v>
+        <v>358</v>
       </c>
       <c r="I50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>346</v>
+        <v>2787</v>
       </c>
       <c r="J50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="K50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="O50">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P50">
         <v>4</v>
@@ -4054,19 +4054,19 @@
       </c>
       <c r="F51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21509029.915585216</v>
+        <v>24000525.631255325</v>
       </c>
       <c r="G51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20653643.392732065</v>
+        <v>22657317.560193349</v>
       </c>
       <c r="H51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>969</v>
+        <v>958</v>
       </c>
       <c r="I51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>931</v>
+        <v>964</v>
       </c>
       <c r="J51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4082,11 +4082,11 @@
       </c>
       <c r="M51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="O51">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -4114,19 +4114,19 @@
       </c>
       <c r="F52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>22333476.918126777</v>
+        <v>24952414.545414973</v>
       </c>
       <c r="G52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18249780.65836753</v>
+        <v>20747156.830999862</v>
       </c>
       <c r="H52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1005</v>
+        <v>989</v>
       </c>
       <c r="I52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>891</v>
+        <v>937</v>
       </c>
       <c r="J52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="M52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="O52">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>973</v>
+        <v>982</v>
       </c>
       <c r="P52">
         <v>4</v>
@@ -4174,19 +4174,19 @@
       </c>
       <c r="F53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>30720766.019070383</v>
+        <v>32989159.026679937</v>
       </c>
       <c r="G53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>39207641.101986013</v>
+        <v>42923506.72697591</v>
       </c>
       <c r="H53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1427</v>
+        <v>1476</v>
       </c>
       <c r="I53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1631</v>
+        <v>1639</v>
       </c>
       <c r="J53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="L53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4206,11 +4206,11 @@
       </c>
       <c r="N53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2229</v>
+        <v>2236</v>
       </c>
       <c r="O53">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2075</v>
+        <v>2068</v>
       </c>
       <c r="P53">
         <v>8</v>
@@ -4234,19 +4234,19 @@
       </c>
       <c r="F54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10654324.550770273</v>
+        <v>11837990.619278032</v>
       </c>
       <c r="G54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8875675.9081516638</v>
+        <v>10041405.614067961</v>
       </c>
       <c r="H54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>554</v>
+        <v>580</v>
       </c>
       <c r="I54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>520</v>
+        <v>567</v>
       </c>
       <c r="J54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4258,19 +4258,19 @@
       </c>
       <c r="L54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="O54">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="P54">
         <v>2</v>
@@ -4294,19 +4294,19 @@
       </c>
       <c r="F55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15305923.087041697</v>
+        <v>17085232.849608403</v>
       </c>
       <c r="G55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15926711.477734976</v>
+        <v>17707083.120192073</v>
       </c>
       <c r="H55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>652</v>
+        <v>684</v>
       </c>
       <c r="I55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>758</v>
+        <v>733</v>
       </c>
       <c r="J55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4326,11 +4326,11 @@
       </c>
       <c r="N55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="O55">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="P55">
         <v>6</v>
@@ -4354,19 +4354,19 @@
       </c>
       <c r="F56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12874140.232146041</v>
+        <v>14228080.103506284</v>
       </c>
       <c r="G56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9823421.513111636</v>
+        <v>10974111.643722907</v>
       </c>
       <c r="H56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>594</v>
+        <v>686</v>
       </c>
       <c r="I56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="J56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="M56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="O56">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="P56">
         <v>3</v>
@@ -4414,19 +4414,19 @@
       </c>
       <c r="F57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21103865.275950637</v>
+        <v>23707410.117147829</v>
       </c>
       <c r="G57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21418755.666532356</v>
+        <v>23768120.633329134</v>
       </c>
       <c r="H57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1199</v>
+        <v>1072</v>
       </c>
       <c r="I57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>999</v>
+        <v>984</v>
       </c>
       <c r="J57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4438,19 +4438,19 @@
       </c>
       <c r="L57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="O57">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="P57">
         <v>3</v>
@@ -4474,19 +4474,19 @@
       </c>
       <c r="F58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>27064315.72966738</v>
+        <v>29468066.465633627</v>
       </c>
       <c r="G58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>25056798.087375559</v>
+        <v>28107742.326862235</v>
       </c>
       <c r="H58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1500</v>
+        <v>1443</v>
       </c>
       <c r="I58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1429</v>
+        <v>1477</v>
       </c>
       <c r="J58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="L58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4506,11 +4506,11 @@
       </c>
       <c r="N58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1327</v>
+        <v>1334</v>
       </c>
       <c r="O58">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1399</v>
+        <v>1408</v>
       </c>
       <c r="P58">
         <v>4</v>
@@ -4534,19 +4534,19 @@
       </c>
       <c r="F59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14085926.081406619</v>
+        <v>15494292.208695738</v>
       </c>
       <c r="G59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14375514.953195609</v>
+        <v>15929363.198218364</v>
       </c>
       <c r="H59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>732</v>
+        <v>696</v>
       </c>
       <c r="I59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="J59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="K59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4566,11 +4566,11 @@
       </c>
       <c r="N59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="O59">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="P59">
         <v>3</v>
@@ -4594,19 +4594,19 @@
       </c>
       <c r="F60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16366940.385502718</v>
+        <v>18091176.906567469</v>
       </c>
       <c r="G60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15961705.359798137</v>
+        <v>17644632.482370876</v>
       </c>
       <c r="H60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="I60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>478</v>
+        <v>463</v>
       </c>
       <c r="J60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4626,11 +4626,11 @@
       </c>
       <c r="N60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="O60">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="P60">
         <v>8</v>
@@ -4654,19 +4654,19 @@
       </c>
       <c r="F61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>37059990.447955251</v>
+        <v>42190631.543374673</v>
       </c>
       <c r="G61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>51313919.349024072</v>
+        <v>56820046.060979337</v>
       </c>
       <c r="H61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1596</v>
+        <v>1603</v>
       </c>
       <c r="I61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1633</v>
+        <v>1688</v>
       </c>
       <c r="J61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="L61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4686,11 +4686,11 @@
       </c>
       <c r="N61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2025</v>
+        <v>2016</v>
       </c>
       <c r="O61">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2000</v>
+        <v>1996</v>
       </c>
       <c r="P61">
         <v>10</v>
@@ -4714,19 +4714,19 @@
       </c>
       <c r="F62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>37740310.665981181</v>
+        <v>42052983.529155493</v>
       </c>
       <c r="G62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>36316046.751808286</v>
+        <v>40496738.011696391</v>
       </c>
       <c r="H62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1140</v>
+        <v>1104</v>
       </c>
       <c r="I62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1195</v>
+        <v>1215</v>
       </c>
       <c r="J62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4746,11 +4746,11 @@
       </c>
       <c r="N62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1622</v>
+        <v>1629</v>
       </c>
       <c r="O62">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="P62">
         <v>9</v>
@@ -4774,19 +4774,19 @@
       </c>
       <c r="F63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24540614.424710989</v>
+        <v>27220648.034163546</v>
       </c>
       <c r="G63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>24557087.2031748</v>
+        <v>27163402.734975632</v>
       </c>
       <c r="H63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>723</v>
+        <v>782</v>
       </c>
       <c r="I63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>743</v>
+        <v>724</v>
       </c>
       <c r="J63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4806,11 +4806,11 @@
       </c>
       <c r="N63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="O63">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="P63">
         <v>4</v>
@@ -4834,19 +4834,19 @@
       </c>
       <c r="F64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>34664074.752712265</v>
+        <v>38559981.787422098</v>
       </c>
       <c r="G64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>36884990.167373955</v>
+        <v>41192471.998564802</v>
       </c>
       <c r="H64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1336</v>
+        <v>1402</v>
       </c>
       <c r="I64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1387</v>
+        <v>1396</v>
       </c>
       <c r="J64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4862,15 +4862,15 @@
       </c>
       <c r="M64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>107</v>
+        <v>163</v>
       </c>
       <c r="N64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1875</v>
+        <v>1867</v>
       </c>
       <c r="O64">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2104</v>
+        <v>2149</v>
       </c>
       <c r="P64">
         <v>9</v>
@@ -4894,19 +4894,19 @@
       </c>
       <c r="F65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>2621075.0989817032</v>
+        <v>2942421.1271584849</v>
       </c>
       <c r="G65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>629491.53686487197</v>
+        <v>866549.93732182099</v>
       </c>
       <c r="H65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>293</v>
+        <v>260</v>
       </c>
       <c r="I65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="J65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4926,11 +4926,11 @@
       </c>
       <c r="N65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O65">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P65">
         <v>3</v>
@@ -4954,19 +4954,19 @@
       </c>
       <c r="F66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>28226150.449650105</v>
+        <v>30974184.927460741</v>
       </c>
       <c r="G66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>26876970.800084837</v>
+        <v>29595379.829328042</v>
       </c>
       <c r="H66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1771</v>
+        <v>1605</v>
       </c>
       <c r="I66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1623</v>
+        <v>1574</v>
       </c>
       <c r="J66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="K66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4986,11 +4986,11 @@
       </c>
       <c r="N66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1751</v>
+        <v>1755</v>
       </c>
       <c r="O66">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1674</v>
+        <v>1667</v>
       </c>
       <c r="P66">
         <v>6</v>
@@ -5014,19 +5014,19 @@
       </c>
       <c r="F67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11149314.029646087</v>
+        <v>12270964.333252013</v>
       </c>
       <c r="G67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12473177.909479629</v>
+        <v>13885953.953792712</v>
       </c>
       <c r="H67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>553</v>
+        <v>543</v>
       </c>
       <c r="I67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>582</v>
+        <v>600</v>
       </c>
       <c r="J67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5046,11 +5046,11 @@
       </c>
       <c r="N67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="O67">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="P67">
         <v>3</v>
@@ -5074,19 +5074,19 @@
       </c>
       <c r="F68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18811212.930350754</v>
+        <v>20714455.23746011</v>
       </c>
       <c r="G68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17738676.445421282</v>
+        <v>19791464.354459144</v>
       </c>
       <c r="H68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>899</v>
+        <v>941</v>
       </c>
       <c r="I68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>946</v>
+        <v>892</v>
       </c>
       <c r="J68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="L68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5106,11 +5106,11 @@
       </c>
       <c r="N68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1357</v>
+        <v>1349</v>
       </c>
       <c r="O68">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1365</v>
+        <v>1359</v>
       </c>
       <c r="P68">
         <v>3</v>
@@ -5134,19 +5134,19 @@
       </c>
       <c r="F69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9657810.5725929085</v>
+        <v>11194059.658313934</v>
       </c>
       <c r="G69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12929426.00816833</v>
+        <v>13965270.135004491</v>
       </c>
       <c r="H69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1784</v>
+        <v>1685</v>
       </c>
       <c r="I69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="J69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="O69">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="P69">
         <v>4</v>
@@ -5194,19 +5194,19 @@
       </c>
       <c r="F70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>31676139.724773306</v>
+        <v>35080672.915383458</v>
       </c>
       <c r="G70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>32852093.120552234</v>
+        <v>36289796.525273778</v>
       </c>
       <c r="H70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1261</v>
+        <v>1232</v>
       </c>
       <c r="I70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1175</v>
+        <v>1233</v>
       </c>
       <c r="J70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5222,15 +5222,15 @@
       </c>
       <c r="M70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1748</v>
+        <v>1742</v>
       </c>
       <c r="O70">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1728</v>
+        <v>1731</v>
       </c>
       <c r="P70">
         <v>4</v>
@@ -5254,19 +5254,19 @@
       </c>
       <c r="F71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7069736.1221274221</v>
+        <v>7880801.5686250767</v>
       </c>
       <c r="G71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6760049.5165477693</v>
+        <v>7436736.8711797697</v>
       </c>
       <c r="H71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>563</v>
+        <v>591</v>
       </c>
       <c r="I71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>473</v>
+        <v>440</v>
       </c>
       <c r="J71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="L71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5286,11 +5286,11 @@
       </c>
       <c r="N71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="O71">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="P71">
         <v>2</v>
@@ -5314,19 +5314,19 @@
       </c>
       <c r="F72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11067997.809093548</v>
+        <v>12327433.580337113</v>
       </c>
       <c r="G72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10338062.634815617</v>
+        <v>11372239.052546794</v>
       </c>
       <c r="H72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>825</v>
+        <v>873</v>
       </c>
       <c r="I72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>879</v>
+        <v>794</v>
       </c>
       <c r="J72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5346,11 +5346,11 @@
       </c>
       <c r="N72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="O72">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="P72">
         <v>3</v>
@@ -5374,19 +5374,19 @@
       </c>
       <c r="F73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6646183.4289873363</v>
+        <v>7675922.5408083284</v>
       </c>
       <c r="G73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10027767.237602197</v>
+        <v>11027043.533425763</v>
       </c>
       <c r="H73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>497</v>
+        <v>518</v>
       </c>
       <c r="I73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>437</v>
+        <v>460</v>
       </c>
       <c r="J73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5406,11 +5406,11 @@
       </c>
       <c r="N73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="O73">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="P73">
         <v>7</v>
@@ -5434,19 +5434,19 @@
       </c>
       <c r="F74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7438912.9088206459</v>
+        <v>8168937.7104559364</v>
       </c>
       <c r="G74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8685443.1066132579</v>
+        <v>9440020.5816278141</v>
       </c>
       <c r="H74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="I74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>710</v>
+        <v>719</v>
       </c>
       <c r="J74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5458,19 +5458,19 @@
       </c>
       <c r="L74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="O74">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="P74">
         <v>2</v>
@@ -5494,19 +5494,19 @@
       </c>
       <c r="F75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8497870.0991402362</v>
+        <v>9324331.1601992901</v>
       </c>
       <c r="G75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9304320.9951788951</v>
+        <v>10312525.498841934</v>
       </c>
       <c r="H75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="I75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="J75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5526,11 +5526,11 @@
       </c>
       <c r="N75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="O75">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="P75">
         <v>1</v>
@@ -5554,19 +5554,19 @@
       </c>
       <c r="F76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>23923392.832980826</v>
+        <v>26416851.045317288</v>
       </c>
       <c r="G76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23499947.38004652</v>
+        <v>26078957.954257365</v>
       </c>
       <c r="H76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>725</v>
+        <v>858</v>
       </c>
       <c r="I76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>747</v>
+        <v>771</v>
       </c>
       <c r="J76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="N76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="O76">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -5614,19 +5614,19 @@
       </c>
       <c r="F77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14714128.498747272</v>
+        <v>16071643.609950272</v>
       </c>
       <c r="G77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14617965.617096372</v>
+        <v>16027104.838134946</v>
       </c>
       <c r="H77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>673</v>
+        <v>682</v>
       </c>
       <c r="I77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="J77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5646,11 +5646,11 @@
       </c>
       <c r="N77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="O77">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="P77">
         <v>2</v>
@@ -5674,19 +5674,19 @@
       </c>
       <c r="F78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11668411.154587179</v>
+        <v>12913446.391234845</v>
       </c>
       <c r="G78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12972567.696969476</v>
+        <v>13467808.102383876</v>
       </c>
       <c r="H78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1067</v>
+        <v>813</v>
       </c>
       <c r="I78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1182</v>
+        <v>134</v>
       </c>
       <c r="J78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="N78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="O78">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -5734,19 +5734,19 @@
       </c>
       <c r="F79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13451041.548536345</v>
+        <v>15027790.131356351</v>
       </c>
       <c r="G79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10024481.605834993</v>
+        <v>11427700.005160464</v>
       </c>
       <c r="H79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>804</v>
+        <v>821</v>
       </c>
       <c r="I79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>844</v>
+        <v>1081</v>
       </c>
       <c r="J79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5754,11 +5754,11 @@
       </c>
       <c r="K79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5766,11 +5766,11 @@
       </c>
       <c r="N79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1015</v>
+        <v>1022</v>
       </c>
       <c r="O79">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="P79">
         <v>3</v>
@@ -5794,19 +5794,19 @@
       </c>
       <c r="F80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13549867.950274644</v>
+        <v>15080277.199489065</v>
       </c>
       <c r="G80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14559640.370847676</v>
+        <v>16388269.707009552</v>
       </c>
       <c r="H80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>645</v>
+        <v>671</v>
       </c>
       <c r="I80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>756</v>
+        <v>794</v>
       </c>
       <c r="J80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5826,11 +5826,11 @@
       </c>
       <c r="N80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="O80">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="P80">
         <v>3</v>
@@ -5854,19 +5854,19 @@
       </c>
       <c r="F81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6882758.8965735016</v>
+        <v>7537594.2901824489</v>
       </c>
       <c r="G81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7315762.4698836477</v>
+        <v>7936306.0676140552</v>
       </c>
       <c r="H81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>588</v>
+        <v>561</v>
       </c>
       <c r="I81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>599</v>
+        <v>582</v>
       </c>
       <c r="J81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5886,11 +5886,11 @@
       </c>
       <c r="N81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="O81">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="P81">
         <v>1</v>
@@ -5914,19 +5914,19 @@
       </c>
       <c r="F82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>26079892.628516715</v>
+        <v>28907365.834728513</v>
       </c>
       <c r="G82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>28525506.244806383</v>
+        <v>31990138.886422463</v>
       </c>
       <c r="H82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1202</v>
+        <v>1295</v>
       </c>
       <c r="I82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1277</v>
+        <v>1311</v>
       </c>
       <c r="J82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="L82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5946,11 +5946,11 @@
       </c>
       <c r="N82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1712</v>
+        <v>1718</v>
       </c>
       <c r="O82">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1750</v>
+        <v>1752</v>
       </c>
       <c r="P82">
         <v>1</v>
@@ -5974,19 +5974,19 @@
       </c>
       <c r="F83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7165191.5008343831</v>
+        <v>7812991.3725561891</v>
       </c>
       <c r="G83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5946913.5955582066</v>
+        <v>6516778.8492811872</v>
       </c>
       <c r="H83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>687</v>
+        <v>667</v>
       </c>
       <c r="I83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>692</v>
+        <v>679</v>
       </c>
       <c r="J83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="L83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="O83">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="P83">
         <v>2</v>
@@ -6034,19 +6034,19 @@
       </c>
       <c r="F84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12970475.295201844</v>
+        <v>14412259.778720619</v>
       </c>
       <c r="G84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13699798.317924472</v>
+        <v>15070172.236953417</v>
       </c>
       <c r="H84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>582</v>
+        <v>593</v>
       </c>
       <c r="I84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="J84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="M84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="O84">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="P84">
         <v>7</v>
@@ -6094,19 +6094,19 @@
       </c>
       <c r="F85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>3870008.7806480499</v>
+        <v>4236420.8188401982</v>
       </c>
       <c r="G85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3450645.4612574582</v>
+        <v>3753216.5787746692</v>
       </c>
       <c r="H85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>279</v>
+        <v>334</v>
       </c>
       <c r="I85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="J85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="M85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="O85">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="P85">
         <v>2</v>
@@ -6163,43 +6163,43 @@
       <c r="A3" s="11"/>
       <c r="B3" s="11">
         <f t="shared" ref="B3:K3" si="0">SUBTOTAL(9,B6:B90)</f>
-        <v>83966</v>
+        <v>83925</v>
       </c>
       <c r="C3" s="11">
         <f t="shared" si="0"/>
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="D3" s="11">
         <f t="shared" si="0"/>
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E3" s="11">
         <f t="shared" si="0"/>
-        <v>69512</v>
+        <v>68742</v>
       </c>
       <c r="F3" s="11">
         <f t="shared" si="0"/>
-        <v>1358024381.1515994</v>
+        <v>1503921962.980973</v>
       </c>
       <c r="G3" s="11">
         <f t="shared" si="0"/>
-        <v>84646</v>
+        <v>84655</v>
       </c>
       <c r="H3" s="11">
         <f t="shared" si="0"/>
-        <v>649</v>
+        <v>730</v>
       </c>
       <c r="I3" s="11">
         <f t="shared" si="0"/>
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="J3" s="11">
         <f t="shared" si="0"/>
-        <v>71621</v>
+        <v>72578</v>
       </c>
       <c r="K3" s="11">
         <f t="shared" si="0"/>
-        <v>1352856501.8340027</v>
+        <v>1499455177.6107061</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -6259,7 +6259,7 @@
         <v>117</v>
       </c>
       <c r="B6" s="10">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C6" s="10">
         <v>3</v>
@@ -6268,13 +6268,13 @@
         <v>2</v>
       </c>
       <c r="E6" s="10">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="F6" s="10">
-        <v>6721217.3677318636</v>
+        <v>7403766.379118205</v>
       </c>
       <c r="G6" s="10">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H6" s="10">
         <v>0</v>
@@ -6283,10 +6283,10 @@
         <v>2</v>
       </c>
       <c r="J6" s="10">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="K6" s="10">
-        <v>6152818.0823086826</v>
+        <v>6772587.9741216879</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
@@ -6303,13 +6303,13 @@
         <v>1</v>
       </c>
       <c r="E7" s="10">
-        <v>577</v>
+        <v>610</v>
       </c>
       <c r="F7" s="10">
-        <v>8156654.6793239554</v>
+        <v>9081858.2921876088</v>
       </c>
       <c r="G7" s="10">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="H7" s="10">
         <v>1</v>
@@ -6318,10 +6318,10 @@
         <v>2</v>
       </c>
       <c r="J7" s="10">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K7" s="10">
-        <v>7429191.778023608</v>
+        <v>8061375.9813275402</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
@@ -6329,7 +6329,7 @@
         <v>119</v>
       </c>
       <c r="B8" s="10">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C8" s="10">
         <v>2</v>
@@ -6338,25 +6338,25 @@
         <v>2</v>
       </c>
       <c r="E8" s="10">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="F8" s="10">
-        <v>7399552.3442232348</v>
+        <v>8472343.6507805083</v>
       </c>
       <c r="G8" s="10">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H8" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I8" s="10">
         <v>1</v>
       </c>
       <c r="J8" s="10">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="K8" s="10">
-        <v>7950360.3691030573</v>
+        <v>9235547.2123001292</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
@@ -6364,7 +6364,7 @@
         <v>121</v>
       </c>
       <c r="B9" s="10">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="C9" s="10">
         <v>2</v>
@@ -6373,13 +6373,13 @@
         <v>2</v>
       </c>
       <c r="E9" s="10">
-        <v>980</v>
+        <v>944</v>
       </c>
       <c r="F9" s="10">
-        <v>15552827.417094398</v>
+        <v>17086090.225409012</v>
       </c>
       <c r="G9" s="10">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="H9" s="10">
         <v>2</v>
@@ -6388,10 +6388,10 @@
         <v>3</v>
       </c>
       <c r="J9" s="10">
-        <v>1029</v>
+        <v>992</v>
       </c>
       <c r="K9" s="10">
-        <v>15725446.023067832</v>
+        <v>17268876.652935285</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
@@ -6399,7 +6399,7 @@
         <v>123</v>
       </c>
       <c r="B10" s="10">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C10" s="10">
         <v>1</v>
@@ -6408,13 +6408,13 @@
         <v>0</v>
       </c>
       <c r="E10" s="10">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="F10" s="10">
-        <v>5858964.4469372071</v>
+        <v>6579428.4202598128</v>
       </c>
       <c r="G10" s="10">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H10" s="10">
         <v>1</v>
@@ -6423,10 +6423,10 @@
         <v>1</v>
       </c>
       <c r="J10" s="10">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="K10" s="10">
-        <v>6781752.4824333154</v>
+        <v>7621380.8444610247</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
@@ -6434,7 +6434,7 @@
         <v>125</v>
       </c>
       <c r="B11" s="10">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C11" s="10">
         <v>2</v>
@@ -6443,13 +6443,13 @@
         <v>2</v>
       </c>
       <c r="E11" s="10">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F11" s="10">
-        <v>5921570.4369004704</v>
+        <v>6507233.0071156528</v>
       </c>
       <c r="G11" s="10">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H11" s="10">
         <v>2</v>
@@ -6458,10 +6458,10 @@
         <v>2</v>
       </c>
       <c r="J11" s="10">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K11" s="10">
-        <v>5992231.4276800314</v>
+        <v>6557460.7367064152</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -6469,7 +6469,7 @@
         <v>131</v>
       </c>
       <c r="B12" s="10">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C12" s="10">
         <v>0</v>
@@ -6478,25 +6478,25 @@
         <v>1</v>
       </c>
       <c r="E12" s="10">
-        <v>525</v>
+        <v>483</v>
       </c>
       <c r="F12" s="10">
-        <v>6799052.3254508786</v>
+        <v>7502762.8835716713</v>
       </c>
       <c r="G12" s="10">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="H12" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="10">
         <v>4</v>
       </c>
       <c r="J12" s="10">
-        <v>512</v>
+        <v>490</v>
       </c>
       <c r="K12" s="10">
-        <v>6874438.380801552</v>
+        <v>7573764.9543150803</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
@@ -6504,7 +6504,7 @@
         <v>133</v>
       </c>
       <c r="B13" s="10">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C13" s="10">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>1</v>
       </c>
       <c r="E13" s="10">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="F13" s="10">
-        <v>2979868.2358265291</v>
+        <v>3333683.0118716359</v>
       </c>
       <c r="G13" s="10">
         <v>168</v>
@@ -6528,10 +6528,10 @@
         <v>1</v>
       </c>
       <c r="J13" s="10">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="K13" s="10">
-        <v>3098186.935847898</v>
+        <v>3412858.6587270629</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
@@ -6539,7 +6539,7 @@
         <v>141</v>
       </c>
       <c r="B14" s="10">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C14" s="10">
         <v>1</v>
@@ -6548,13 +6548,13 @@
         <v>0</v>
       </c>
       <c r="E14" s="10">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F14" s="10">
-        <v>3006238.1098317681</v>
+        <v>3327945.8076576372</v>
       </c>
       <c r="G14" s="10">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H14" s="10">
         <v>0</v>
@@ -6563,10 +6563,10 @@
         <v>1</v>
       </c>
       <c r="J14" s="10">
-        <v>1</v>
+        <v>136</v>
       </c>
       <c r="K14" s="10">
-        <v>268270.17518669402</v>
+        <v>356764.62464087899</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
@@ -6583,13 +6583,13 @@
         <v>0</v>
       </c>
       <c r="E15" s="10">
-        <v>286</v>
+        <v>369</v>
       </c>
       <c r="F15" s="10">
-        <v>4782564.6090684468</v>
+        <v>5285015.9714740682</v>
       </c>
       <c r="G15" s="10">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="H15" s="10">
         <v>1</v>
@@ -6598,10 +6598,10 @@
         <v>1</v>
       </c>
       <c r="J15" s="10">
-        <v>509</v>
+        <v>379</v>
       </c>
       <c r="K15" s="10">
-        <v>6812954.8209106149</v>
+        <v>7406718.8965042289</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
@@ -6609,7 +6609,7 @@
         <v>143</v>
       </c>
       <c r="B16" s="10">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C16" s="10">
         <v>0</v>
@@ -6618,13 +6618,13 @@
         <v>1</v>
       </c>
       <c r="E16" s="10">
-        <v>321</v>
+        <v>252</v>
       </c>
       <c r="F16" s="10">
-        <v>2250565.6269620662</v>
+        <v>2493060.9630141081</v>
       </c>
       <c r="G16" s="10">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H16" s="10">
         <v>0</v>
@@ -6633,10 +6633,10 @@
         <v>2</v>
       </c>
       <c r="J16" s="10">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="K16" s="10">
-        <v>2959702.482844451</v>
+        <v>3295803.4780012751</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -6644,22 +6644,22 @@
         <v>145</v>
       </c>
       <c r="B17" s="10">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C17" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" s="10">
         <v>0</v>
       </c>
       <c r="E17" s="10">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="F17" s="10">
-        <v>3008058.056240594</v>
+        <v>3339864.9400243089</v>
       </c>
       <c r="G17" s="10">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="H17" s="10">
         <v>0</v>
@@ -6668,10 +6668,10 @@
         <v>1</v>
       </c>
       <c r="J17" s="10">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="K17" s="10">
-        <v>3318437.6932629938</v>
+        <v>3668103.6269933642</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
@@ -6679,7 +6679,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="10">
-        <v>1445</v>
+        <v>1433</v>
       </c>
       <c r="C18" s="10">
         <v>0</v>
@@ -6688,13 +6688,13 @@
         <v>2</v>
       </c>
       <c r="E18" s="10">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="F18" s="10">
-        <v>7512189.1632019328</v>
+        <v>7512201.2733524209</v>
       </c>
       <c r="G18" s="10">
-        <v>1426</v>
+        <v>1430</v>
       </c>
       <c r="H18" s="10">
         <v>2</v>
@@ -6703,10 +6703,10 @@
         <v>3</v>
       </c>
       <c r="J18" s="10">
-        <v>867</v>
+        <v>1100</v>
       </c>
       <c r="K18" s="10">
-        <v>9987199.9195197597</v>
+        <v>11435917.552780986</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
@@ -6714,7 +6714,7 @@
         <v>45</v>
       </c>
       <c r="B19" s="10">
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="C19" s="10">
         <v>0</v>
@@ -6723,13 +6723,13 @@
         <v>2</v>
       </c>
       <c r="E19" s="10">
-        <v>1281</v>
+        <v>1090</v>
       </c>
       <c r="F19" s="10">
-        <v>21031434.832303733</v>
+        <v>23900483.28657113</v>
       </c>
       <c r="G19" s="10">
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="H19" s="10">
         <v>1</v>
@@ -6738,10 +6738,10 @@
         <v>3</v>
       </c>
       <c r="J19" s="10">
-        <v>896</v>
+        <v>888</v>
       </c>
       <c r="K19" s="10">
-        <v>21848454.097331937</v>
+        <v>24163229.470245697</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
@@ -6749,7 +6749,7 @@
         <v>47</v>
       </c>
       <c r="B20" s="10">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C20" s="10">
         <v>1</v>
@@ -6758,13 +6758,13 @@
         <v>3</v>
       </c>
       <c r="E20" s="10">
-        <v>909</v>
+        <v>882</v>
       </c>
       <c r="F20" s="10">
-        <v>12464962.956552835</v>
+        <v>13687331.401381763</v>
       </c>
       <c r="G20" s="10">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="H20" s="10">
         <v>2</v>
@@ -6773,10 +6773,10 @@
         <v>5</v>
       </c>
       <c r="J20" s="10">
-        <v>943</v>
+        <v>1346</v>
       </c>
       <c r="K20" s="10">
-        <v>12945342.206328144</v>
+        <v>14290505.340465739</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
@@ -6784,7 +6784,7 @@
         <v>49</v>
       </c>
       <c r="B21" s="10">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="C21" s="10">
         <v>0</v>
@@ -6793,13 +6793,13 @@
         <v>2</v>
       </c>
       <c r="E21" s="10">
-        <v>636</v>
+        <v>697</v>
       </c>
       <c r="F21" s="10">
-        <v>13216752.071126426</v>
+        <v>14508159.402924469</v>
       </c>
       <c r="G21" s="10">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="H21" s="10">
         <v>3</v>
@@ -6808,10 +6808,10 @@
         <v>3</v>
       </c>
       <c r="J21" s="10">
-        <v>726</v>
+        <v>801</v>
       </c>
       <c r="K21" s="10">
-        <v>8571431.2894174531</v>
+        <v>9683317.7825561687</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
@@ -6819,34 +6819,34 @@
         <v>51</v>
       </c>
       <c r="B22" s="10">
-        <v>2802</v>
+        <v>2790</v>
       </c>
       <c r="C22" s="10">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D22" s="10">
         <v>10</v>
       </c>
       <c r="E22" s="10">
-        <v>2035</v>
+        <v>1885</v>
       </c>
       <c r="F22" s="10">
-        <v>43765663.42008768</v>
+        <v>48234189.966538787</v>
       </c>
       <c r="G22" s="10">
-        <v>2942</v>
+        <v>2915</v>
       </c>
       <c r="H22" s="10">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I22" s="10">
         <v>10</v>
       </c>
       <c r="J22" s="10">
-        <v>2900</v>
+        <v>2175</v>
       </c>
       <c r="K22" s="10">
-        <v>49075557.599973261</v>
+        <v>54021728.128000915</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
@@ -6863,25 +6863,25 @@
         <v>2</v>
       </c>
       <c r="E23" s="10">
-        <v>1139</v>
+        <v>1183</v>
       </c>
       <c r="F23" s="10">
-        <v>24021205.021760464</v>
+        <v>26648723.196364921</v>
       </c>
       <c r="G23" s="10">
-        <v>1367</v>
+        <v>1370</v>
       </c>
       <c r="H23" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23" s="10">
         <v>1</v>
       </c>
       <c r="J23" s="10">
-        <v>9</v>
+        <v>1206</v>
       </c>
       <c r="K23" s="10">
-        <v>8067116.1734909713</v>
+        <v>9209407.9122159164</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
@@ -6889,34 +6889,34 @@
         <v>55</v>
       </c>
       <c r="B24" s="10">
-        <v>2984</v>
+        <v>2996</v>
       </c>
       <c r="C24" s="10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D24" s="10">
         <v>12</v>
       </c>
       <c r="E24" s="10">
-        <v>2383</v>
+        <v>2404</v>
       </c>
       <c r="F24" s="10">
-        <v>46803671.881852701</v>
+        <v>52087375.427271821</v>
       </c>
       <c r="G24" s="10">
-        <v>2962</v>
+        <v>2968</v>
       </c>
       <c r="H24" s="10">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I24" s="10">
         <v>10</v>
       </c>
       <c r="J24" s="10">
-        <v>2214</v>
+        <v>2213</v>
       </c>
       <c r="K24" s="10">
-        <v>47738508.937325202</v>
+        <v>52488658.529909022</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
@@ -6924,7 +6924,7 @@
         <v>67</v>
       </c>
       <c r="B25" s="10">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C25" s="10">
         <v>3</v>
@@ -6933,13 +6933,13 @@
         <v>1</v>
       </c>
       <c r="E25" s="10">
-        <v>463</v>
+        <v>527</v>
       </c>
       <c r="F25" s="10">
-        <v>6796338.2171994355</v>
+        <v>7489624.1028591068</v>
       </c>
       <c r="G25" s="10">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="H25" s="10">
         <v>4</v>
@@ -6948,10 +6948,10 @@
         <v>1</v>
       </c>
       <c r="J25" s="10">
-        <v>515</v>
+        <v>901</v>
       </c>
       <c r="K25" s="10">
-        <v>7122002.4557506125</v>
+        <v>8131500.9638309013</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
@@ -6959,7 +6959,7 @@
         <v>74</v>
       </c>
       <c r="B26" s="10">
-        <v>1709</v>
+        <v>1713</v>
       </c>
       <c r="C26" s="10">
         <v>6</v>
@@ -6968,25 +6968,25 @@
         <v>1</v>
       </c>
       <c r="E26" s="10">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="F26" s="10">
-        <v>18988796.478382163</v>
+        <v>21050766.076841544</v>
       </c>
       <c r="G26" s="10">
-        <v>1732</v>
+        <v>1729</v>
       </c>
       <c r="H26" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I26" s="10">
         <v>2</v>
       </c>
       <c r="J26" s="10">
-        <v>1334</v>
+        <v>1375</v>
       </c>
       <c r="K26" s="10">
-        <v>19306182.14601028</v>
+        <v>21530945.293318376</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
@@ -6994,7 +6994,7 @@
         <v>70</v>
       </c>
       <c r="B27" s="10">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C27" s="10">
         <v>4</v>
@@ -7003,13 +7003,13 @@
         <v>1</v>
       </c>
       <c r="E27" s="10">
-        <v>826</v>
+        <v>773</v>
       </c>
       <c r="F27" s="10">
-        <v>8482004.1993926615</v>
+        <v>9392854.7496682443</v>
       </c>
       <c r="G27" s="10">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="H27" s="10">
         <v>7</v>
@@ -7018,10 +7018,10 @@
         <v>1</v>
       </c>
       <c r="J27" s="10">
-        <v>766</v>
+        <v>755</v>
       </c>
       <c r="K27" s="10">
-        <v>7846298.3074562633</v>
+        <v>8641800.9232224785</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
@@ -7029,7 +7029,7 @@
         <v>72</v>
       </c>
       <c r="B28" s="10">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="C28" s="10">
         <v>1</v>
@@ -7038,25 +7038,25 @@
         <v>1</v>
       </c>
       <c r="E28" s="10">
-        <v>570</v>
+        <v>756</v>
       </c>
       <c r="F28" s="10">
-        <v>8755237.1310375761</v>
+        <v>9579970.5974776149</v>
       </c>
       <c r="G28" s="10">
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="H28" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I28" s="10">
         <v>1</v>
       </c>
       <c r="J28" s="10">
-        <v>757</v>
+        <v>723</v>
       </c>
       <c r="K28" s="10">
-        <v>9960916.6373697724</v>
+        <v>11009560.832062732</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
@@ -7064,7 +7064,7 @@
         <v>79</v>
       </c>
       <c r="B29" s="10">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C29" s="10">
         <v>1</v>
@@ -7073,13 +7073,13 @@
         <v>0</v>
       </c>
       <c r="E29" s="10">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="F29" s="10">
-        <v>2560118.3425952001</v>
+        <v>2855776.6463130671</v>
       </c>
       <c r="G29" s="10">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="H29" s="10">
         <v>1</v>
@@ -7088,10 +7088,10 @@
         <v>2</v>
       </c>
       <c r="J29" s="10">
-        <v>146</v>
+        <v>197</v>
       </c>
       <c r="K29" s="10">
-        <v>2055834.390430477</v>
+        <v>2269431.611853485</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
@@ -7099,7 +7099,7 @@
         <v>109</v>
       </c>
       <c r="B30" s="10">
-        <v>1663</v>
+        <v>1668</v>
       </c>
       <c r="C30" s="10">
         <v>1</v>
@@ -7108,13 +7108,13 @@
         <v>5</v>
       </c>
       <c r="E30" s="10">
-        <v>1514</v>
+        <v>1464</v>
       </c>
       <c r="F30" s="10">
-        <v>22718777.941925272</v>
+        <v>24822617.942399263</v>
       </c>
       <c r="G30" s="10">
-        <v>1661</v>
+        <v>1667</v>
       </c>
       <c r="H30" s="10">
         <v>9</v>
@@ -7123,10 +7123,10 @@
         <v>6</v>
       </c>
       <c r="J30" s="10">
-        <v>1398</v>
+        <v>1347</v>
       </c>
       <c r="K30" s="10">
-        <v>18674864.213929038</v>
+        <v>20667503.031828664</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
@@ -7134,7 +7134,7 @@
         <v>111</v>
       </c>
       <c r="B31" s="10">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="C31" s="10">
         <v>1</v>
@@ -7143,13 +7143,13 @@
         <v>1</v>
       </c>
       <c r="E31" s="10">
-        <v>648</v>
+        <v>606</v>
       </c>
       <c r="F31" s="10">
-        <v>14153077.91888571</v>
+        <v>15651652.677112721</v>
       </c>
       <c r="G31" s="10">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H31" s="10">
         <v>1</v>
@@ -7158,10 +7158,10 @@
         <v>1</v>
       </c>
       <c r="J31" s="10">
-        <v>617</v>
+        <v>629</v>
       </c>
       <c r="K31" s="10">
-        <v>14551107.043437852</v>
+        <v>16374105.086462455</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
@@ -7169,7 +7169,7 @@
         <v>113</v>
       </c>
       <c r="B32" s="10">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="C32" s="10">
         <v>0</v>
@@ -7178,13 +7178,13 @@
         <v>1</v>
       </c>
       <c r="E32" s="10">
-        <v>733</v>
+        <v>558</v>
       </c>
       <c r="F32" s="10">
-        <v>15725447.580771975</v>
+        <v>17399020.220064308</v>
       </c>
       <c r="G32" s="10">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="H32" s="10">
         <v>1</v>
@@ -7193,10 +7193,10 @@
         <v>1</v>
       </c>
       <c r="J32" s="10">
-        <v>826</v>
+        <v>836</v>
       </c>
       <c r="K32" s="10">
-        <v>14437291.715968899</v>
+        <v>16060768.424630741</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
@@ -7204,7 +7204,7 @@
         <v>115</v>
       </c>
       <c r="B33" s="10">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C33" s="10">
         <v>0</v>
@@ -7213,13 +7213,13 @@
         <v>3</v>
       </c>
       <c r="E33" s="10">
-        <v>967</v>
+        <v>1039</v>
       </c>
       <c r="F33" s="10">
-        <v>19703437.006434254</v>
+        <v>21903595.915449053</v>
       </c>
       <c r="G33" s="10">
-        <v>1116</v>
+        <v>1109</v>
       </c>
       <c r="H33" s="10">
         <v>2</v>
@@ -7228,10 +7228,10 @@
         <v>2</v>
       </c>
       <c r="J33" s="10">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="K33" s="10">
-        <v>20056812.599486277</v>
+        <v>22045259.973748617</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
@@ -7239,22 +7239,22 @@
         <v>16</v>
       </c>
       <c r="B34" s="10">
-        <v>1487</v>
+        <v>1497</v>
       </c>
       <c r="C34" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34" s="10">
         <v>5</v>
       </c>
       <c r="E34" s="10">
-        <v>1178</v>
+        <v>1173</v>
       </c>
       <c r="F34" s="10">
-        <v>29722501.854668796</v>
+        <v>33172620.572869904</v>
       </c>
       <c r="G34" s="10">
-        <v>1478</v>
+        <v>1468</v>
       </c>
       <c r="H34" s="10">
         <v>3</v>
@@ -7263,10 +7263,10 @@
         <v>5</v>
       </c>
       <c r="J34" s="10">
-        <v>1146</v>
+        <v>1181</v>
       </c>
       <c r="K34" s="10">
-        <v>28294835.68957008</v>
+        <v>31324284.763955772</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
@@ -7283,13 +7283,13 @@
         <v>2</v>
       </c>
       <c r="E35" s="10">
-        <v>528</v>
+        <v>448</v>
       </c>
       <c r="F35" s="10">
-        <v>10980480.649050532</v>
+        <v>12052276.283295762</v>
       </c>
       <c r="G35" s="10">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H35" s="10">
         <v>0</v>
@@ -7298,10 +7298,10 @@
         <v>5</v>
       </c>
       <c r="J35" s="10">
-        <v>528</v>
+        <v>554</v>
       </c>
       <c r="K35" s="10">
-        <v>11557874.043439522</v>
+        <v>12818085.34321888</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
@@ -7309,7 +7309,7 @@
         <v>43</v>
       </c>
       <c r="B36" s="10">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="C36" s="10">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         <v>10</v>
       </c>
       <c r="E36" s="10">
-        <v>1770</v>
+        <v>1575</v>
       </c>
       <c r="F36" s="10">
-        <v>35060631.354011633</v>
+        <v>38950361.986051217</v>
       </c>
       <c r="G36" s="10">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="H36" s="10">
         <v>6</v>
@@ -7333,10 +7333,10 @@
         <v>11</v>
       </c>
       <c r="J36" s="10">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="K36" s="10">
-        <v>35288715.200185522</v>
+        <v>39218450.568227202</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
@@ -7344,22 +7344,22 @@
         <v>152</v>
       </c>
       <c r="B37" s="10">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="C37" s="10">
         <v>2</v>
       </c>
       <c r="D37" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" s="10">
-        <v>674</v>
+        <v>660</v>
       </c>
       <c r="F37" s="10">
-        <v>12333157.928200064</v>
+        <v>13641140.097482843</v>
       </c>
       <c r="G37" s="10">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="H37" s="10">
         <v>1</v>
@@ -7368,10 +7368,10 @@
         <v>2</v>
       </c>
       <c r="J37" s="10">
-        <v>696</v>
+        <v>747</v>
       </c>
       <c r="K37" s="10">
-        <v>11529791.435436616</v>
+        <v>12702349.062420461</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
@@ -7379,7 +7379,7 @@
         <v>149</v>
       </c>
       <c r="B38" s="10">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C38" s="10">
         <v>0</v>
@@ -7388,13 +7388,13 @@
         <v>1</v>
       </c>
       <c r="E38" s="10">
-        <v>459</v>
+        <v>422</v>
       </c>
       <c r="F38" s="10">
-        <v>10103964.004989509</v>
+        <v>11020053.945719752</v>
       </c>
       <c r="G38" s="10">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="H38" s="10">
         <v>0</v>
@@ -7403,10 +7403,10 @@
         <v>1</v>
       </c>
       <c r="J38" s="10">
-        <v>557</v>
+        <v>580</v>
       </c>
       <c r="K38" s="10">
-        <v>11112334.557640174</v>
+        <v>12313396.90175152</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
@@ -7414,34 +7414,34 @@
         <v>154</v>
       </c>
       <c r="B39" s="10">
-        <v>1122</v>
+        <v>1113</v>
       </c>
       <c r="C39" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D39" s="10">
         <v>3</v>
       </c>
       <c r="E39" s="10">
-        <v>872</v>
+        <v>815</v>
       </c>
       <c r="F39" s="10">
-        <v>17854652.580006875</v>
+        <v>19655782.859162141</v>
       </c>
       <c r="G39" s="10">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="H39" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I39" s="10">
         <v>1</v>
       </c>
       <c r="J39" s="10">
-        <v>836</v>
+        <v>793</v>
       </c>
       <c r="K39" s="10">
-        <v>17193856.285997957</v>
+        <v>19043186.757094968</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
@@ -7449,22 +7449,22 @@
         <v>2</v>
       </c>
       <c r="B40" s="10">
-        <v>1183</v>
+        <v>1173</v>
       </c>
       <c r="C40" s="10">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D40" s="10">
         <v>1</v>
       </c>
       <c r="E40" s="10">
-        <v>869</v>
+        <v>823</v>
       </c>
       <c r="F40" s="10">
-        <v>17212785.665607128</v>
+        <v>19180872.019964613</v>
       </c>
       <c r="G40" s="10">
-        <v>1365</v>
+        <v>1351</v>
       </c>
       <c r="H40" s="10">
         <v>120</v>
@@ -7473,10 +7473,10 @@
         <v>1</v>
       </c>
       <c r="J40" s="10">
-        <v>769</v>
+        <v>779</v>
       </c>
       <c r="K40" s="10">
-        <v>15645497.955338975</v>
+        <v>17431602.978954356</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
@@ -7484,34 +7484,34 @@
         <v>156</v>
       </c>
       <c r="B41" s="10">
-        <v>1840</v>
+        <v>1834</v>
       </c>
       <c r="C41" s="10">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D41" s="10">
         <v>4</v>
       </c>
       <c r="E41" s="10">
-        <v>1382</v>
+        <v>1425</v>
       </c>
       <c r="F41" s="10">
-        <v>27010112.979283512</v>
+        <v>29876677.049243852</v>
       </c>
       <c r="G41" s="10">
-        <v>2469</v>
+        <v>2445</v>
       </c>
       <c r="H41" s="10">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I41" s="10">
         <v>5</v>
       </c>
       <c r="J41" s="10">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="K41" s="10">
-        <v>28638765.273579638</v>
+        <v>31725346.660909802</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
@@ -7519,7 +7519,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="10">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C42" s="10">
         <v>2</v>
@@ -7528,13 +7528,13 @@
         <v>6</v>
       </c>
       <c r="E42" s="10">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="F42" s="10">
-        <v>11241543.166229179</v>
+        <v>12462518.939564969</v>
       </c>
       <c r="G42" s="10">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="H42" s="10">
         <v>0</v>
@@ -7543,10 +7543,10 @@
         <v>6</v>
       </c>
       <c r="J42" s="10">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="K42" s="10">
-        <v>10344833.566559069</v>
+        <v>11421939.055878559</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
@@ -7554,7 +7554,7 @@
         <v>8</v>
       </c>
       <c r="B43" s="10">
-        <v>1946</v>
+        <v>1943</v>
       </c>
       <c r="C43" s="10">
         <v>2</v>
@@ -7563,13 +7563,13 @@
         <v>6</v>
       </c>
       <c r="E43" s="10">
-        <v>1917</v>
+        <v>2011</v>
       </c>
       <c r="F43" s="10">
-        <v>30939701.804248367</v>
+        <v>34603754.857470505</v>
       </c>
       <c r="G43" s="10">
-        <v>2049</v>
+        <v>2054</v>
       </c>
       <c r="H43" s="10">
         <v>2</v>
@@ -7578,10 +7578,10 @@
         <v>6</v>
       </c>
       <c r="J43" s="10">
-        <v>1934</v>
+        <v>1970</v>
       </c>
       <c r="K43" s="10">
-        <v>34562600.775030553</v>
+        <v>38251004.015172802</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.35">
@@ -7589,7 +7589,7 @@
         <v>39</v>
       </c>
       <c r="B44" s="10">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C44" s="10">
         <v>3</v>
@@ -7598,25 +7598,25 @@
         <v>4</v>
       </c>
       <c r="E44" s="10">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="F44" s="10">
-        <v>21592902.705368832</v>
+        <v>23998515.44422197</v>
       </c>
       <c r="G44" s="10">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H44" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I44" s="10">
         <v>2</v>
       </c>
       <c r="J44" s="10">
-        <v>797</v>
+        <v>772</v>
       </c>
       <c r="K44" s="10">
-        <v>22304769.355051536</v>
+        <v>24688120.726337377</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.35">
@@ -7624,7 +7624,7 @@
         <v>6</v>
       </c>
       <c r="B45" s="10">
-        <v>1154</v>
+        <v>1143</v>
       </c>
       <c r="C45" s="10">
         <v>0</v>
@@ -7633,13 +7633,13 @@
         <v>3</v>
       </c>
       <c r="E45" s="10">
-        <v>934</v>
+        <v>909</v>
       </c>
       <c r="F45" s="10">
-        <v>19361417.568360262</v>
+        <v>21126962.544779114</v>
       </c>
       <c r="G45" s="10">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="H45" s="10">
         <v>0</v>
@@ -7648,10 +7648,10 @@
         <v>3</v>
       </c>
       <c r="J45" s="10">
-        <v>925</v>
+        <v>936</v>
       </c>
       <c r="K45" s="10">
-        <v>10411236.41967774</v>
+        <v>12296140.818591988</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
@@ -7659,7 +7659,7 @@
         <v>41</v>
       </c>
       <c r="B46" s="10">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="C46" s="10">
         <v>0</v>
@@ -7668,13 +7668,13 @@
         <v>5</v>
       </c>
       <c r="E46" s="10">
-        <v>630</v>
+        <v>615</v>
       </c>
       <c r="F46" s="10">
-        <v>18232693.534131359</v>
+        <v>20292399.117647201</v>
       </c>
       <c r="G46" s="10">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H46" s="10">
         <v>3</v>
@@ -7683,10 +7683,10 @@
         <v>4</v>
       </c>
       <c r="J46" s="10">
-        <v>645</v>
+        <v>668</v>
       </c>
       <c r="K46" s="10">
-        <v>17755224.245391376</v>
+        <v>19732293.398156039</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.35">
@@ -7694,7 +7694,7 @@
         <v>158</v>
       </c>
       <c r="B47" s="10">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="C47" s="10">
         <v>0</v>
@@ -7703,25 +7703,25 @@
         <v>10</v>
       </c>
       <c r="E47" s="10">
-        <v>600</v>
+        <v>655</v>
       </c>
       <c r="F47" s="10">
-        <v>10453278.752228426</v>
+        <v>11675592.217419149</v>
       </c>
       <c r="G47" s="10">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="H47" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I47" s="10">
         <v>10</v>
       </c>
       <c r="J47" s="10">
-        <v>708</v>
+        <v>566</v>
       </c>
       <c r="K47" s="10">
-        <v>11363931.519229412</v>
+        <v>12617432.245743323</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.35">
@@ -7729,7 +7729,7 @@
         <v>160</v>
       </c>
       <c r="B48" s="10">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C48" s="10">
         <v>1</v>
@@ -7738,13 +7738,13 @@
         <v>1</v>
       </c>
       <c r="E48" s="10">
-        <v>743</v>
+        <v>711</v>
       </c>
       <c r="F48" s="10">
-        <v>10321050.736769276</v>
+        <v>11469697.687318595</v>
       </c>
       <c r="G48" s="10">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="H48" s="10">
         <v>0</v>
@@ -7753,10 +7753,10 @@
         <v>2</v>
       </c>
       <c r="J48" s="10">
-        <v>744</v>
+        <v>701</v>
       </c>
       <c r="K48" s="10">
-        <v>9780767.8360642996</v>
+        <v>10927877.013120186</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
@@ -7770,16 +7770,16 @@
         <v>7</v>
       </c>
       <c r="D49" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E49" s="10">
-        <v>1018</v>
+        <v>1068</v>
       </c>
       <c r="F49" s="10">
-        <v>36614471.61384137</v>
+        <v>39658020.754120097</v>
       </c>
       <c r="G49" s="10">
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="H49" s="10">
         <v>0</v>
@@ -7788,10 +7788,10 @@
         <v>4</v>
       </c>
       <c r="J49" s="10">
-        <v>1127</v>
+        <v>1072</v>
       </c>
       <c r="K49" s="10">
-        <v>30732060.500332795</v>
+        <v>33970655.650308527</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
@@ -7808,13 +7808,13 @@
         <v>2</v>
       </c>
       <c r="E50" s="10">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F50" s="10">
-        <v>6249555.1480661668</v>
+        <v>6956384.4550691703</v>
       </c>
       <c r="G50" s="10">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H50" s="10">
         <v>0</v>
@@ -7823,10 +7823,10 @@
         <v>1</v>
       </c>
       <c r="J50" s="10">
-        <v>429</v>
+        <v>490</v>
       </c>
       <c r="K50" s="10">
-        <v>5123293.8080037152</v>
+        <v>5665017.8500306131</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
@@ -7834,7 +7834,7 @@
         <v>31</v>
       </c>
       <c r="B51" s="10">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="C51" s="10">
         <v>0</v>
@@ -7843,25 +7843,25 @@
         <v>4</v>
       </c>
       <c r="E51" s="10">
-        <v>882</v>
+        <v>906</v>
       </c>
       <c r="F51" s="10">
-        <v>16076235.359384179</v>
+        <v>17566001.730502713</v>
       </c>
       <c r="G51" s="10">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="H51" s="10">
         <v>2</v>
       </c>
       <c r="I51" s="10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J51" s="10">
-        <v>3212</v>
+        <v>923</v>
       </c>
       <c r="K51" s="10">
-        <v>14733574.789885193</v>
+        <v>16286567.597074073</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
@@ -7869,22 +7869,22 @@
         <v>33</v>
       </c>
       <c r="B52" s="10">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="C52" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D52" s="10">
         <v>12</v>
       </c>
       <c r="E52" s="10">
-        <v>1001</v>
+        <v>959</v>
       </c>
       <c r="F52" s="10">
-        <v>20734256.805620253</v>
+        <v>23215427.489808504</v>
       </c>
       <c r="G52" s="10">
-        <v>1363</v>
+        <v>1354</v>
       </c>
       <c r="H52" s="10">
         <v>3</v>
@@ -7893,10 +7893,10 @@
         <v>12</v>
       </c>
       <c r="J52" s="10">
-        <v>1033</v>
+        <v>1017</v>
       </c>
       <c r="K52" s="10">
-        <v>26407949.501988936</v>
+        <v>29152507.694931164</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.35">
@@ -7904,7 +7904,7 @@
         <v>85</v>
       </c>
       <c r="B53" s="10">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C53" s="10">
         <v>0</v>
@@ -7913,25 +7913,25 @@
         <v>5</v>
       </c>
       <c r="E53" s="10">
-        <v>392</v>
+        <v>363</v>
       </c>
       <c r="F53" s="10">
-        <v>10925987.34804726</v>
+        <v>12332994.762099404</v>
       </c>
       <c r="G53" s="10">
         <v>483</v>
       </c>
       <c r="H53" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" s="10">
         <v>6</v>
       </c>
       <c r="J53" s="10">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="K53" s="10">
-        <v>13673852.473286686</v>
+        <v>15040340.008889956</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.35">
@@ -7948,13 +7948,13 @@
         <v>7</v>
       </c>
       <c r="E54" s="10">
-        <v>383</v>
+        <v>322</v>
       </c>
       <c r="F54" s="10">
-        <v>12764477.259903496</v>
+        <v>14070540.257583896</v>
       </c>
       <c r="G54" s="10">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="H54" s="10">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>4</v>
       </c>
       <c r="J54" s="10">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="K54" s="10">
-        <v>10116058.890716156</v>
+        <v>11090723.62741236</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.35">
@@ -7983,25 +7983,25 @@
         <v>2</v>
       </c>
       <c r="E55" s="10">
-        <v>327</v>
+        <v>358</v>
       </c>
       <c r="F55" s="10">
-        <v>9941003.7667885516</v>
+        <v>10956552.874769645</v>
       </c>
       <c r="G55" s="10">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H55" s="10">
         <v>1</v>
       </c>
       <c r="I55" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J55" s="10">
-        <v>346</v>
+        <v>2787</v>
       </c>
       <c r="K55" s="10">
-        <v>8825567.6649791468</v>
+        <v>9670437.9324168526</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.35">
@@ -8009,7 +8009,7 @@
         <v>166</v>
       </c>
       <c r="B56" s="10">
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="C56" s="10">
         <v>0</v>
@@ -8018,25 +8018,25 @@
         <v>1</v>
       </c>
       <c r="E56" s="10">
-        <v>969</v>
+        <v>958</v>
       </c>
       <c r="F56" s="10">
-        <v>21509029.915585216</v>
+        <v>24000525.631255325</v>
       </c>
       <c r="G56" s="10">
         <v>1101</v>
       </c>
       <c r="H56" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I56" s="10">
         <v>0</v>
       </c>
       <c r="J56" s="10">
-        <v>931</v>
+        <v>964</v>
       </c>
       <c r="K56" s="10">
-        <v>20653643.392732065</v>
+        <v>22657317.560193349</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
@@ -8053,25 +8053,25 @@
         <v>3</v>
       </c>
       <c r="E57" s="10">
-        <v>1005</v>
+        <v>989</v>
       </c>
       <c r="F57" s="10">
-        <v>22333476.918126777</v>
+        <v>24952414.545414973</v>
       </c>
       <c r="G57" s="10">
-        <v>973</v>
+        <v>982</v>
       </c>
       <c r="H57" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I57" s="10">
         <v>1</v>
       </c>
       <c r="J57" s="10">
-        <v>891</v>
+        <v>937</v>
       </c>
       <c r="K57" s="10">
-        <v>18249780.65836753</v>
+        <v>20747156.830999862</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.35">
@@ -8079,22 +8079,22 @@
         <v>95</v>
       </c>
       <c r="B58" s="10">
-        <v>2229</v>
+        <v>2236</v>
       </c>
       <c r="C58" s="10">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D58" s="10">
         <v>7</v>
       </c>
       <c r="E58" s="10">
-        <v>1427</v>
+        <v>1476</v>
       </c>
       <c r="F58" s="10">
-        <v>30720766.019070383</v>
+        <v>32989159.026679937</v>
       </c>
       <c r="G58" s="10">
-        <v>2075</v>
+        <v>2068</v>
       </c>
       <c r="H58" s="10">
         <v>6</v>
@@ -8103,10 +8103,10 @@
         <v>8</v>
       </c>
       <c r="J58" s="10">
-        <v>1631</v>
+        <v>1639</v>
       </c>
       <c r="K58" s="10">
-        <v>39207641.101986013</v>
+        <v>42923506.72697591</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.35">
@@ -8114,34 +8114,34 @@
         <v>174</v>
       </c>
       <c r="B59" s="10">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="C59" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D59" s="10">
         <v>0</v>
       </c>
       <c r="E59" s="10">
-        <v>554</v>
+        <v>580</v>
       </c>
       <c r="F59" s="10">
-        <v>10654324.550770273</v>
+        <v>11837990.619278032</v>
       </c>
       <c r="G59" s="10">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H59" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" s="10">
         <v>0</v>
       </c>
       <c r="J59" s="10">
-        <v>520</v>
+        <v>567</v>
       </c>
       <c r="K59" s="10">
-        <v>8875675.9081516638</v>
+        <v>10041405.614067961</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.35">
@@ -8149,7 +8149,7 @@
         <v>99</v>
       </c>
       <c r="B60" s="10">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C60" s="10">
         <v>2</v>
@@ -8158,13 +8158,13 @@
         <v>5</v>
       </c>
       <c r="E60" s="10">
-        <v>652</v>
+        <v>684</v>
       </c>
       <c r="F60" s="10">
-        <v>15305923.087041697</v>
+        <v>17085232.849608403</v>
       </c>
       <c r="G60" s="10">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="H60" s="10">
         <v>4</v>
@@ -8173,10 +8173,10 @@
         <v>5</v>
       </c>
       <c r="J60" s="10">
-        <v>758</v>
+        <v>733</v>
       </c>
       <c r="K60" s="10">
-        <v>15926711.477734976</v>
+        <v>17707083.120192073</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.35">
@@ -8193,25 +8193,25 @@
         <v>1</v>
       </c>
       <c r="E61" s="10">
-        <v>594</v>
+        <v>686</v>
       </c>
       <c r="F61" s="10">
-        <v>12874140.232146041</v>
+        <v>14228080.103506284</v>
       </c>
       <c r="G61" s="10">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="H61" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I61" s="10">
         <v>1</v>
       </c>
       <c r="J61" s="10">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="K61" s="10">
-        <v>9823421.513111636</v>
+        <v>10974111.643722907</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.35">
@@ -8219,34 +8219,34 @@
         <v>168</v>
       </c>
       <c r="B62" s="10">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="C62" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D62" s="10">
         <v>1</v>
       </c>
       <c r="E62" s="10">
-        <v>1199</v>
+        <v>1072</v>
       </c>
       <c r="F62" s="10">
-        <v>21103865.275950637</v>
+        <v>23707410.117147829</v>
       </c>
       <c r="G62" s="10">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="H62" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I62" s="10">
         <v>0</v>
       </c>
       <c r="J62" s="10">
-        <v>999</v>
+        <v>984</v>
       </c>
       <c r="K62" s="10">
-        <v>21418755.666532356</v>
+        <v>23768120.633329134</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.35">
@@ -8254,22 +8254,22 @@
         <v>101</v>
       </c>
       <c r="B63" s="10">
-        <v>1327</v>
+        <v>1334</v>
       </c>
       <c r="C63" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D63" s="10">
         <v>4</v>
       </c>
       <c r="E63" s="10">
-        <v>1500</v>
+        <v>1443</v>
       </c>
       <c r="F63" s="10">
-        <v>27064315.72966738</v>
+        <v>29468066.465633627</v>
       </c>
       <c r="G63" s="10">
-        <v>1399</v>
+        <v>1408</v>
       </c>
       <c r="H63" s="10">
         <v>1</v>
@@ -8278,10 +8278,10 @@
         <v>4</v>
       </c>
       <c r="J63" s="10">
-        <v>1429</v>
+        <v>1477</v>
       </c>
       <c r="K63" s="10">
-        <v>25056798.087375559</v>
+        <v>28107742.326862235</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.35">
@@ -8289,7 +8289,7 @@
         <v>103</v>
       </c>
       <c r="B64" s="10">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C64" s="10">
         <v>4</v>
@@ -8298,25 +8298,25 @@
         <v>5</v>
       </c>
       <c r="E64" s="10">
-        <v>732</v>
+        <v>696</v>
       </c>
       <c r="F64" s="10">
-        <v>14085926.081406619</v>
+        <v>15494292.208695738</v>
       </c>
       <c r="G64" s="10">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="H64" s="10">
         <v>1</v>
       </c>
       <c r="I64" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J64" s="10">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="K64" s="10">
-        <v>14375514.953195609</v>
+        <v>15929363.198218364</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.35">
@@ -8324,7 +8324,7 @@
         <v>105</v>
       </c>
       <c r="B65" s="10">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C65" s="10">
         <v>3</v>
@@ -8333,13 +8333,13 @@
         <v>5</v>
       </c>
       <c r="E65" s="10">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="F65" s="10">
-        <v>16366940.385502718</v>
+        <v>18091176.906567469</v>
       </c>
       <c r="G65" s="10">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="H65" s="10">
         <v>4</v>
@@ -8348,10 +8348,10 @@
         <v>5</v>
       </c>
       <c r="J65" s="10">
-        <v>478</v>
+        <v>463</v>
       </c>
       <c r="K65" s="10">
-        <v>15961705.359798137</v>
+        <v>17644632.482370876</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.35">
@@ -8359,22 +8359,22 @@
         <v>24</v>
       </c>
       <c r="B66" s="10">
-        <v>2025</v>
+        <v>2016</v>
       </c>
       <c r="C66" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D66" s="10">
         <v>9</v>
       </c>
       <c r="E66" s="10">
-        <v>1596</v>
+        <v>1603</v>
       </c>
       <c r="F66" s="10">
-        <v>37059990.447955251</v>
+        <v>42190631.543374673</v>
       </c>
       <c r="G66" s="10">
-        <v>2000</v>
+        <v>1996</v>
       </c>
       <c r="H66" s="10">
         <v>2</v>
@@ -8383,10 +8383,10 @@
         <v>11</v>
       </c>
       <c r="J66" s="10">
-        <v>1633</v>
+        <v>1688</v>
       </c>
       <c r="K66" s="10">
-        <v>51313919.349024072</v>
+        <v>56820046.060979337</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.35">
@@ -8394,22 +8394,22 @@
         <v>27</v>
       </c>
       <c r="B67" s="10">
-        <v>1622</v>
+        <v>1629</v>
       </c>
       <c r="C67" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D67" s="10">
         <v>8</v>
       </c>
       <c r="E67" s="10">
-        <v>1140</v>
+        <v>1104</v>
       </c>
       <c r="F67" s="10">
-        <v>37740310.665981181</v>
+        <v>42052983.529155493</v>
       </c>
       <c r="G67" s="10">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="H67" s="10">
         <v>5</v>
@@ -8418,10 +8418,10 @@
         <v>6</v>
       </c>
       <c r="J67" s="10">
-        <v>1195</v>
+        <v>1215</v>
       </c>
       <c r="K67" s="10">
-        <v>36316046.751808286</v>
+        <v>40496738.011696391</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.35">
@@ -8429,22 +8429,22 @@
         <v>29</v>
       </c>
       <c r="B68" s="10">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="C68" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68" s="10">
         <v>1</v>
       </c>
       <c r="E68" s="10">
-        <v>723</v>
+        <v>782</v>
       </c>
       <c r="F68" s="10">
-        <v>24540614.424710989</v>
+        <v>27220648.034163546</v>
       </c>
       <c r="G68" s="10">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="H68" s="10">
         <v>3</v>
@@ -8453,10 +8453,10 @@
         <v>1</v>
       </c>
       <c r="J68" s="10">
-        <v>743</v>
+        <v>724</v>
       </c>
       <c r="K68" s="10">
-        <v>24557087.2031748</v>
+        <v>27163402.734975632</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.35">
@@ -8464,7 +8464,7 @@
         <v>57</v>
       </c>
       <c r="B69" s="10">
-        <v>1875</v>
+        <v>1867</v>
       </c>
       <c r="C69" s="10">
         <v>37</v>
@@ -8473,25 +8473,25 @@
         <v>13</v>
       </c>
       <c r="E69" s="10">
-        <v>1336</v>
+        <v>1402</v>
       </c>
       <c r="F69" s="10">
-        <v>34664074.752712265</v>
+        <v>38559981.787422098</v>
       </c>
       <c r="G69" s="10">
-        <v>2104</v>
+        <v>2149</v>
       </c>
       <c r="H69" s="10">
-        <v>107</v>
+        <v>163</v>
       </c>
       <c r="I69" s="10">
         <v>12</v>
       </c>
       <c r="J69" s="10">
-        <v>1387</v>
+        <v>1396</v>
       </c>
       <c r="K69" s="10">
-        <v>36884990.167373955</v>
+        <v>41192471.998564802</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.35">
@@ -8499,7 +8499,7 @@
         <v>137</v>
       </c>
       <c r="B70" s="10">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C70" s="10">
         <v>0</v>
@@ -8508,13 +8508,13 @@
         <v>1</v>
       </c>
       <c r="E70" s="10">
-        <v>293</v>
+        <v>260</v>
       </c>
       <c r="F70" s="10">
-        <v>2621075.0989817032</v>
+        <v>2942421.1271584849</v>
       </c>
       <c r="G70" s="10">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H70" s="10">
         <v>0</v>
@@ -8523,10 +8523,10 @@
         <v>0</v>
       </c>
       <c r="J70" s="10">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="K70" s="10">
-        <v>629491.53686487197</v>
+        <v>866549.93732182099</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.35">
@@ -8534,7 +8534,7 @@
         <v>10</v>
       </c>
       <c r="B71" s="10">
-        <v>1751</v>
+        <v>1755</v>
       </c>
       <c r="C71" s="10">
         <v>2</v>
@@ -8543,25 +8543,25 @@
         <v>7</v>
       </c>
       <c r="E71" s="10">
-        <v>1771</v>
+        <v>1605</v>
       </c>
       <c r="F71" s="10">
-        <v>28226150.449650105</v>
+        <v>30974184.927460741</v>
       </c>
       <c r="G71" s="10">
-        <v>1674</v>
+        <v>1667</v>
       </c>
       <c r="H71" s="10">
         <v>4</v>
       </c>
       <c r="I71" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J71" s="10">
-        <v>1623</v>
+        <v>1574</v>
       </c>
       <c r="K71" s="10">
-        <v>26876970.800084837</v>
+        <v>29595379.829328042</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.35">
@@ -8569,7 +8569,7 @@
         <v>12</v>
       </c>
       <c r="B72" s="10">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C72" s="10">
         <v>1</v>
@@ -8578,13 +8578,13 @@
         <v>2</v>
       </c>
       <c r="E72" s="10">
-        <v>553</v>
+        <v>543</v>
       </c>
       <c r="F72" s="10">
-        <v>11149314.029646087</v>
+        <v>12270964.333252013</v>
       </c>
       <c r="G72" s="10">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="H72" s="10">
         <v>1</v>
@@ -8593,10 +8593,10 @@
         <v>3</v>
       </c>
       <c r="J72" s="10">
-        <v>582</v>
+        <v>600</v>
       </c>
       <c r="K72" s="10">
-        <v>12473177.909479629</v>
+        <v>13885953.953792712</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.35">
@@ -8604,22 +8604,22 @@
         <v>162</v>
       </c>
       <c r="B73" s="10">
-        <v>1357</v>
+        <v>1349</v>
       </c>
       <c r="C73" s="10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D73" s="10">
         <v>5</v>
       </c>
       <c r="E73" s="10">
-        <v>899</v>
+        <v>941</v>
       </c>
       <c r="F73" s="10">
-        <v>18811212.930350754</v>
+        <v>20714455.23746011</v>
       </c>
       <c r="G73" s="10">
-        <v>1365</v>
+        <v>1359</v>
       </c>
       <c r="H73" s="10">
         <v>19</v>
@@ -8628,10 +8628,10 @@
         <v>4</v>
       </c>
       <c r="J73" s="10">
-        <v>946</v>
+        <v>892</v>
       </c>
       <c r="K73" s="10">
-        <v>17738676.445421282</v>
+        <v>19791464.354459144</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.35">
@@ -8648,13 +8648,13 @@
         <v>5</v>
       </c>
       <c r="E74" s="10">
-        <v>1784</v>
+        <v>1685</v>
       </c>
       <c r="F74" s="10">
-        <v>9657810.5725929085</v>
+        <v>11194059.658313934</v>
       </c>
       <c r="G74" s="10">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="H74" s="10">
         <v>1</v>
@@ -8663,10 +8663,10 @@
         <v>5</v>
       </c>
       <c r="J74" s="10">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="K74" s="10">
-        <v>12929426.00816833</v>
+        <v>13965270.135004491</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.35">
@@ -8674,7 +8674,7 @@
         <v>59</v>
       </c>
       <c r="B75" s="10">
-        <v>1748</v>
+        <v>1742</v>
       </c>
       <c r="C75" s="10">
         <v>4</v>
@@ -8683,25 +8683,25 @@
         <v>5</v>
       </c>
       <c r="E75" s="10">
-        <v>1261</v>
+        <v>1232</v>
       </c>
       <c r="F75" s="10">
-        <v>31676139.724773306</v>
+        <v>35080672.915383458</v>
       </c>
       <c r="G75" s="10">
-        <v>1728</v>
+        <v>1731</v>
       </c>
       <c r="H75" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I75" s="10">
         <v>4</v>
       </c>
       <c r="J75" s="10">
-        <v>1175</v>
+        <v>1233</v>
       </c>
       <c r="K75" s="10">
-        <v>32852093.120552234</v>
+        <v>36289796.525273778</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.35">
@@ -8709,22 +8709,22 @@
         <v>139</v>
       </c>
       <c r="B76" s="10">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C76" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D76" s="10">
         <v>2</v>
       </c>
       <c r="E76" s="10">
-        <v>563</v>
+        <v>591</v>
       </c>
       <c r="F76" s="10">
-        <v>7069736.1221274221</v>
+        <v>7880801.5686250767</v>
       </c>
       <c r="G76" s="10">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="H76" s="10">
         <v>2</v>
@@ -8733,10 +8733,10 @@
         <v>1</v>
       </c>
       <c r="J76" s="10">
-        <v>473</v>
+        <v>440</v>
       </c>
       <c r="K76" s="10">
-        <v>6760049.5165477693</v>
+        <v>7436736.8711797697</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.35">
@@ -8744,7 +8744,7 @@
         <v>170</v>
       </c>
       <c r="B77" s="10">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C77" s="10">
         <v>1</v>
@@ -8753,13 +8753,13 @@
         <v>1</v>
       </c>
       <c r="E77" s="10">
-        <v>825</v>
+        <v>873</v>
       </c>
       <c r="F77" s="10">
-        <v>11067997.809093548</v>
+        <v>12327433.580337113</v>
       </c>
       <c r="G77" s="10">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="H77" s="10">
         <v>2</v>
@@ -8768,10 +8768,10 @@
         <v>1</v>
       </c>
       <c r="J77" s="10">
-        <v>879</v>
+        <v>794</v>
       </c>
       <c r="K77" s="10">
-        <v>10338062.634815617</v>
+        <v>11372239.052546794</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.35">
@@ -8779,7 +8779,7 @@
         <v>61</v>
       </c>
       <c r="B78" s="10">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C78" s="10">
         <v>0</v>
@@ -8788,13 +8788,13 @@
         <v>4</v>
       </c>
       <c r="E78" s="10">
-        <v>497</v>
+        <v>518</v>
       </c>
       <c r="F78" s="10">
-        <v>6646183.4289873363</v>
+        <v>7675922.5408083284</v>
       </c>
       <c r="G78" s="10">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H78" s="10">
         <v>0</v>
@@ -8803,10 +8803,10 @@
         <v>3</v>
       </c>
       <c r="J78" s="10">
-        <v>437</v>
+        <v>460</v>
       </c>
       <c r="K78" s="10">
-        <v>10027767.237602197</v>
+        <v>11027043.533425763</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.35">
@@ -8814,34 +8814,34 @@
         <v>129</v>
       </c>
       <c r="B79" s="10">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="C79" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D79" s="10">
         <v>1</v>
       </c>
       <c r="E79" s="10">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="F79" s="10">
-        <v>7438912.9088206459</v>
+        <v>8168937.7104559364</v>
       </c>
       <c r="G79" s="10">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="H79" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I79" s="10">
         <v>1</v>
       </c>
       <c r="J79" s="10">
-        <v>710</v>
+        <v>719</v>
       </c>
       <c r="K79" s="10">
-        <v>8685443.1066132579</v>
+        <v>9440020.5816278141</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.35">
@@ -8849,7 +8849,7 @@
         <v>35</v>
       </c>
       <c r="B80" s="10">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C80" s="10">
         <v>2</v>
@@ -8858,13 +8858,13 @@
         <v>5</v>
       </c>
       <c r="E80" s="10">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="F80" s="10">
-        <v>8497870.0991402362</v>
+        <v>9324331.1601992901</v>
       </c>
       <c r="G80" s="10">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="H80" s="10">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>7</v>
       </c>
       <c r="J80" s="10">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="K80" s="10">
-        <v>9304320.9951788951</v>
+        <v>10312525.498841934</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.35">
@@ -8884,7 +8884,7 @@
         <v>107</v>
       </c>
       <c r="B81" s="10">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="C81" s="10">
         <v>1</v>
@@ -8893,10 +8893,10 @@
         <v>4</v>
       </c>
       <c r="E81" s="10">
-        <v>725</v>
+        <v>858</v>
       </c>
       <c r="F81" s="10">
-        <v>23923392.832980826</v>
+        <v>26416851.045317288</v>
       </c>
       <c r="G81" s="10">
         <v>950</v>
@@ -8908,10 +8908,10 @@
         <v>3</v>
       </c>
       <c r="J81" s="10">
-        <v>747</v>
+        <v>771</v>
       </c>
       <c r="K81" s="10">
-        <v>23499947.38004652</v>
+        <v>26078957.954257365</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.35">
@@ -8919,7 +8919,7 @@
         <v>37</v>
       </c>
       <c r="B82" s="10">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C82" s="10">
         <v>1</v>
@@ -8928,13 +8928,13 @@
         <v>9</v>
       </c>
       <c r="E82" s="10">
-        <v>673</v>
+        <v>682</v>
       </c>
       <c r="F82" s="10">
-        <v>14714128.498747272</v>
+        <v>16071643.609950272</v>
       </c>
       <c r="G82" s="10">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="H82" s="10">
         <v>2</v>
@@ -8943,10 +8943,10 @@
         <v>10</v>
       </c>
       <c r="J82" s="10">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="K82" s="10">
-        <v>14617965.617096372</v>
+        <v>16027104.838134946</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.35">
@@ -8954,7 +8954,7 @@
         <v>76</v>
       </c>
       <c r="B83" s="10">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="C83" s="10">
         <v>0</v>
@@ -8963,10 +8963,10 @@
         <v>2</v>
       </c>
       <c r="E83" s="10">
-        <v>1067</v>
+        <v>813</v>
       </c>
       <c r="F83" s="10">
-        <v>11668411.154587179</v>
+        <v>12913446.391234845</v>
       </c>
       <c r="G83" s="10">
         <v>971</v>
@@ -8978,10 +8978,10 @@
         <v>2</v>
       </c>
       <c r="J83" s="10">
-        <v>1182</v>
+        <v>134</v>
       </c>
       <c r="K83" s="10">
-        <v>12972567.696969476</v>
+        <v>13467808.102383876</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.35">
@@ -8989,34 +8989,34 @@
         <v>65</v>
       </c>
       <c r="B84" s="10">
-        <v>1015</v>
+        <v>1022</v>
       </c>
       <c r="C84" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D84" s="10">
         <v>4</v>
       </c>
       <c r="E84" s="10">
-        <v>804</v>
+        <v>821</v>
       </c>
       <c r="F84" s="10">
-        <v>13451041.548536345</v>
+        <v>15027790.131356351</v>
       </c>
       <c r="G84" s="10">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="H84" s="10">
         <v>1</v>
       </c>
       <c r="I84" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J84" s="10">
-        <v>844</v>
+        <v>1081</v>
       </c>
       <c r="K84" s="10">
-        <v>10024481.605834993</v>
+        <v>11427700.005160464</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.35">
@@ -9024,7 +9024,7 @@
         <v>89</v>
       </c>
       <c r="B85" s="10">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C85" s="10">
         <v>2</v>
@@ -9033,13 +9033,13 @@
         <v>5</v>
       </c>
       <c r="E85" s="10">
-        <v>645</v>
+        <v>671</v>
       </c>
       <c r="F85" s="10">
-        <v>13549867.950274644</v>
+        <v>15080277.199489065</v>
       </c>
       <c r="G85" s="10">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="H85" s="10">
         <v>2</v>
@@ -9048,10 +9048,10 @@
         <v>6</v>
       </c>
       <c r="J85" s="10">
-        <v>756</v>
+        <v>794</v>
       </c>
       <c r="K85" s="10">
-        <v>14559640.370847676</v>
+        <v>16388269.707009552</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.35">
@@ -9059,7 +9059,7 @@
         <v>147</v>
       </c>
       <c r="B86" s="10">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C86" s="10">
         <v>1</v>
@@ -9068,13 +9068,13 @@
         <v>1</v>
       </c>
       <c r="E86" s="10">
-        <v>588</v>
+        <v>561</v>
       </c>
       <c r="F86" s="10">
-        <v>6882758.8965735016</v>
+        <v>7537594.2901824489</v>
       </c>
       <c r="G86" s="10">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="H86" s="10">
         <v>1</v>
@@ -9083,10 +9083,10 @@
         <v>1</v>
       </c>
       <c r="J86" s="10">
-        <v>599</v>
+        <v>582</v>
       </c>
       <c r="K86" s="10">
-        <v>7315762.4698836477</v>
+        <v>7936306.0676140552</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.35">
@@ -9094,22 +9094,22 @@
         <v>164</v>
       </c>
       <c r="B87" s="10">
-        <v>1712</v>
+        <v>1718</v>
       </c>
       <c r="C87" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D87" s="10">
         <v>10</v>
       </c>
       <c r="E87" s="10">
-        <v>1202</v>
+        <v>1295</v>
       </c>
       <c r="F87" s="10">
-        <v>26079892.628516715</v>
+        <v>28907365.834728513</v>
       </c>
       <c r="G87" s="10">
-        <v>1750</v>
+        <v>1752</v>
       </c>
       <c r="H87" s="10">
         <v>0</v>
@@ -9118,10 +9118,10 @@
         <v>10</v>
       </c>
       <c r="J87" s="10">
-        <v>1277</v>
+        <v>1311</v>
       </c>
       <c r="K87" s="10">
-        <v>28525506.244806383</v>
+        <v>31990138.886422463</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.35">
@@ -9132,19 +9132,19 @@
         <v>656</v>
       </c>
       <c r="C88" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D88" s="10">
         <v>3</v>
       </c>
       <c r="E88" s="10">
-        <v>687</v>
+        <v>667</v>
       </c>
       <c r="F88" s="10">
-        <v>7165191.5008343831</v>
+        <v>7812991.3725561891</v>
       </c>
       <c r="G88" s="10">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="H88" s="10">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>3</v>
       </c>
       <c r="J88" s="10">
-        <v>692</v>
+        <v>679</v>
       </c>
       <c r="K88" s="10">
-        <v>5946913.5955582066</v>
+        <v>6516778.8492811872</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.35">
@@ -9173,25 +9173,25 @@
         <v>6</v>
       </c>
       <c r="E89" s="10">
-        <v>582</v>
+        <v>593</v>
       </c>
       <c r="F89" s="10">
-        <v>12970475.295201844</v>
+        <v>14412259.778720619</v>
       </c>
       <c r="G89" s="10">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H89" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I89" s="10">
         <v>7</v>
       </c>
       <c r="J89" s="10">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="K89" s="10">
-        <v>13699798.317924472</v>
+        <v>15070172.236953417</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.35">
@@ -9208,25 +9208,25 @@
         <v>1</v>
       </c>
       <c r="E90" s="10">
-        <v>279</v>
+        <v>334</v>
       </c>
       <c r="F90" s="10">
-        <v>3870008.7806480499</v>
+        <v>4236420.8188401982</v>
       </c>
       <c r="G90" s="10">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="H90" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I90" s="10">
         <v>0</v>
       </c>
       <c r="J90" s="10">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="K90" s="10">
-        <v>3450645.4612574582</v>
+        <v>3753216.5787746692</v>
       </c>
     </row>
   </sheetData>

--- a/SITE MONITORING.xlsx
+++ b/SITE MONITORING.xlsx
@@ -1114,19 +1114,19 @@
       </c>
       <c r="F2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7403766.379118205</v>
+        <v>8148583.395282384</v>
       </c>
       <c r="G2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6772587.9741216879</v>
+        <v>7383118.5990972444</v>
       </c>
       <c r="H2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="I2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="J2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1146,11 +1146,11 @@
       </c>
       <c r="N2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="O2">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="P2">
         <v>3</v>
@@ -1174,19 +1174,19 @@
       </c>
       <c r="F3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9081858.2921876088</v>
+        <v>10074713.131280864</v>
       </c>
       <c r="G3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8061375.9813275402</v>
+        <v>8806603.2716049217</v>
       </c>
       <c r="H3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>610</v>
+        <v>635</v>
       </c>
       <c r="I3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="J3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1202,15 +1202,15 @@
       </c>
       <c r="M3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="O3">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="P3">
         <v>2</v>
@@ -1234,19 +1234,19 @@
       </c>
       <c r="F4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8472343.6507805083</v>
+        <v>9579603.6779472157</v>
       </c>
       <c r="G4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9235547.2123001292</v>
+        <v>10474601.900855821</v>
       </c>
       <c r="H4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="I4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>699</v>
+        <v>690</v>
       </c>
       <c r="J4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1266,11 +1266,11 @@
       </c>
       <c r="N4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="O4">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="P4">
         <v>4</v>
@@ -1294,23 +1294,23 @@
       </c>
       <c r="F5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17086090.225409012</v>
+        <v>18772595.596177574</v>
       </c>
       <c r="G5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17268876.652935285</v>
+        <v>19007257.264013216</v>
       </c>
       <c r="H5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>944</v>
+        <v>1251</v>
       </c>
       <c r="I5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>992</v>
+        <v>1021</v>
       </c>
       <c r="J5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -1318,19 +1318,19 @@
       </c>
       <c r="L5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="O5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1210</v>
+        <v>1215</v>
       </c>
       <c r="P5">
         <v>3</v>
@@ -1354,23 +1354,23 @@
       </c>
       <c r="F6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6579428.4202598128</v>
+        <v>7351981.8698023772</v>
       </c>
       <c r="G6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7621380.8444610247</v>
+        <v>8379190.2540950719</v>
       </c>
       <c r="H6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="I6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="J6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -1386,11 +1386,11 @@
       </c>
       <c r="N6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="O6">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="P6">
         <v>3</v>
@@ -1414,19 +1414,19 @@
       </c>
       <c r="F7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6507233.0071156528</v>
+        <v>7102539.9786560358</v>
       </c>
       <c r="G7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6557460.7367064152</v>
+        <v>7143934.4550414039</v>
       </c>
       <c r="H7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>355</v>
+        <v>315</v>
       </c>
       <c r="I7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="J7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1446,11 +1446,11 @@
       </c>
       <c r="N7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="O7">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="P7">
         <v>2</v>
@@ -1474,19 +1474,19 @@
       </c>
       <c r="F8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7502762.8835716713</v>
+        <v>8274433.0801868876</v>
       </c>
       <c r="G8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7573764.9543150803</v>
+        <v>8338127.2616301412</v>
       </c>
       <c r="H8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>483</v>
+        <v>504</v>
       </c>
       <c r="I8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="J8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="K8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O8">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="P8">
         <v>9</v>
@@ -1534,19 +1534,19 @@
       </c>
       <c r="F9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>3333683.0118716359</v>
+        <v>3656016.5393009051</v>
       </c>
       <c r="G9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3412858.6587270629</v>
+        <v>3746619.7807002808</v>
       </c>
       <c r="H9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="J9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1566,11 +1566,11 @@
       </c>
       <c r="N9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O9">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P9">
         <v>1</v>
@@ -1594,19 +1594,19 @@
       </c>
       <c r="F10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>3327945.8076576372</v>
+        <v>3662736.030057156</v>
       </c>
       <c r="G10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>356764.62464087899</v>
+        <v>586274.09262576199</v>
       </c>
       <c r="H10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>172</v>
+        <v>234</v>
       </c>
       <c r="I10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="J10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1626,11 +1626,11 @@
       </c>
       <c r="N10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="O10">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P10">
         <v>1</v>
@@ -1654,19 +1654,19 @@
       </c>
       <c r="F11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5285015.9714740682</v>
+        <v>5886575.0213002944</v>
       </c>
       <c r="G11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7406718.8965042289</v>
+        <v>7938415.2501511136</v>
       </c>
       <c r="H11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>369</v>
+        <v>341</v>
       </c>
       <c r="I11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>379</v>
+        <v>329</v>
       </c>
       <c r="J11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="O11">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="P11">
         <v>4</v>
@@ -1714,19 +1714,19 @@
       </c>
       <c r="F12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>2493060.9630141081</v>
+        <v>2763314.70019016</v>
       </c>
       <c r="G12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3295803.4780012751</v>
+        <v>3605141.5898137731</v>
       </c>
       <c r="H12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="I12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="J12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1746,11 +1746,11 @@
       </c>
       <c r="N12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O12">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P12">
         <v>3</v>
@@ -1774,19 +1774,19 @@
       </c>
       <c r="F13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>3339864.9400243089</v>
+        <v>3731770.761003104</v>
       </c>
       <c r="G13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3668103.6269933642</v>
+        <v>3976103.8294773069</v>
       </c>
       <c r="H13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="I13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>241</v>
+        <v>1029</v>
       </c>
       <c r="J13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="K13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -1802,11 +1802,11 @@
       </c>
       <c r="M13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O13">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -1834,19 +1834,19 @@
       </c>
       <c r="F14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7512201.2733524209</v>
+        <v>7512211.1851744372</v>
       </c>
       <c r="G14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11435917.552780986</v>
+        <v>13395441.917632751</v>
       </c>
       <c r="H14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="I14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1100</v>
+        <v>1622</v>
       </c>
       <c r="J14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="N14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1433</v>
+        <v>1428</v>
       </c>
       <c r="O14">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -1894,19 +1894,19 @@
       </c>
       <c r="F15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>23900483.28657113</v>
+        <v>27027994.608759265</v>
       </c>
       <c r="G15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>24163229.470245697</v>
+        <v>26636902.010980774</v>
       </c>
       <c r="H15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1090</v>
+        <v>1196</v>
       </c>
       <c r="I15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>888</v>
+        <v>881</v>
       </c>
       <c r="J15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1926,11 +1926,11 @@
       </c>
       <c r="N15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1283</v>
+        <v>1287</v>
       </c>
       <c r="O15">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1229</v>
+        <v>1235</v>
       </c>
       <c r="P15">
         <v>4</v>
@@ -1954,19 +1954,19 @@
       </c>
       <c r="F16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13687331.401381763</v>
+        <v>15102559.791172484</v>
       </c>
       <c r="G16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14290505.340465739</v>
+        <v>15824748.753173972</v>
       </c>
       <c r="H16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>882</v>
+        <v>941</v>
       </c>
       <c r="I16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1346</v>
+        <v>966</v>
       </c>
       <c r="J16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1986,11 +1986,11 @@
       </c>
       <c r="N16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="O16">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="P16">
         <v>3</v>
@@ -2014,19 +2014,19 @@
       </c>
       <c r="F17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14508159.402924469</v>
+        <v>15734908.735146243</v>
       </c>
       <c r="G17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9683317.7825561687</v>
+        <v>10910855.575781677</v>
       </c>
       <c r="H17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>697</v>
+        <v>607</v>
       </c>
       <c r="I17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>801</v>
+        <v>657</v>
       </c>
       <c r="J17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2046,11 +2046,11 @@
       </c>
       <c r="N17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="O17">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="P17">
         <v>4</v>
@@ -2074,19 +2074,19 @@
       </c>
       <c r="F18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>48234189.966538787</v>
+        <v>52792789.530242719</v>
       </c>
       <c r="G18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>54021728.128000915</v>
+        <v>58761430.803304039</v>
       </c>
       <c r="H18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1885</v>
+        <v>1911</v>
       </c>
       <c r="I18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2175</v>
+        <v>2097</v>
       </c>
       <c r="J18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2098,19 +2098,19 @@
       </c>
       <c r="L18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2790</v>
+        <v>2784</v>
       </c>
       <c r="O18">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2915</v>
+        <v>2902</v>
       </c>
       <c r="P18">
         <v>5</v>
@@ -2134,19 +2134,19 @@
       </c>
       <c r="F19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>26648723.196364921</v>
+        <v>29359803.28090911</v>
       </c>
       <c r="G19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9209407.9122159164</v>
+        <v>11582816.775124433</v>
       </c>
       <c r="H19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1183</v>
+        <v>1146</v>
       </c>
       <c r="I19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1206</v>
+        <v>1135</v>
       </c>
       <c r="J19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2166,11 +2166,11 @@
       </c>
       <c r="N19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="O19">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="P19">
         <v>1</v>
@@ -2194,19 +2194,19 @@
       </c>
       <c r="F20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>52087375.427271821</v>
+        <v>57514764.250181429</v>
       </c>
       <c r="G20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>52488658.529909022</v>
+        <v>57579834.233493693</v>
       </c>
       <c r="H20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2404</v>
+        <v>2495</v>
       </c>
       <c r="I20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2213</v>
+        <v>2229</v>
       </c>
       <c r="J20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2222,15 +2222,15 @@
       </c>
       <c r="M20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2996</v>
+        <v>2991</v>
       </c>
       <c r="O20">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2968</v>
+        <v>2969</v>
       </c>
       <c r="P20">
         <v>8</v>
@@ -2254,19 +2254,19 @@
       </c>
       <c r="F21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7489624.1028591068</v>
+        <v>8321119.8683109106</v>
       </c>
       <c r="G21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8131500.9638309013</v>
+        <v>9053768.2708089184</v>
       </c>
       <c r="H21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>527</v>
+        <v>453</v>
       </c>
       <c r="I21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>901</v>
+        <v>501</v>
       </c>
       <c r="J21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2286,11 +2286,11 @@
       </c>
       <c r="N21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="O21">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="P21">
         <v>1</v>
@@ -2314,19 +2314,19 @@
       </c>
       <c r="F22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21050766.076841544</v>
+        <v>22879391.702904098</v>
       </c>
       <c r="G22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21530945.293318376</v>
+        <v>23681600.887948416</v>
       </c>
       <c r="H22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="I22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1375</v>
+        <v>1298</v>
       </c>
       <c r="J22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2342,15 +2342,15 @@
       </c>
       <c r="M22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1713</v>
+        <v>1705</v>
       </c>
       <c r="O22">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1729</v>
+        <v>1739</v>
       </c>
       <c r="P22">
         <v>8</v>
@@ -2374,19 +2374,19 @@
       </c>
       <c r="F23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9392854.7496682443</v>
+        <v>10369757.486323014</v>
       </c>
       <c r="G23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8641800.9232224785</v>
+        <v>9476804.7699170522</v>
       </c>
       <c r="H23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>773</v>
+        <v>806</v>
       </c>
       <c r="I23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>755</v>
+        <v>740</v>
       </c>
       <c r="J23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2402,11 +2402,11 @@
       </c>
       <c r="M23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="O23">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -2434,19 +2434,19 @@
       </c>
       <c r="F24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9579970.5974776149</v>
+        <v>10593685.684289929</v>
       </c>
       <c r="G24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11009560.832062732</v>
+        <v>12126669.665737486</v>
       </c>
       <c r="H24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>756</v>
+        <v>671</v>
       </c>
       <c r="I24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>723</v>
+        <v>837</v>
       </c>
       <c r="J24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2466,11 +2466,11 @@
       </c>
       <c r="N24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="O24">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="P24">
         <v>3</v>
@@ -2494,19 +2494,19 @@
       </c>
       <c r="F25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>2855776.6463130671</v>
+        <v>3161051.6615617769</v>
       </c>
       <c r="G25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>2269431.611853485</v>
+        <v>2535906.26679195</v>
       </c>
       <c r="H25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="I25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="J25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2526,11 +2526,11 @@
       </c>
       <c r="N25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="O25">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P25">
         <v>1</v>
@@ -2554,19 +2554,19 @@
       </c>
       <c r="F26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24822617.942399263</v>
+        <v>26915593.394559879</v>
       </c>
       <c r="G26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20667503.031828664</v>
+        <v>22506648.705730204</v>
       </c>
       <c r="H26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1464</v>
+        <v>1411</v>
       </c>
       <c r="I26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1347</v>
+        <v>1297</v>
       </c>
       <c r="J26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2586,11 +2586,11 @@
       </c>
       <c r="N26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1668</v>
+        <v>1672</v>
       </c>
       <c r="O26">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="P26">
         <v>1</v>
@@ -2614,19 +2614,19 @@
       </c>
       <c r="F27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15651652.677112721</v>
+        <v>17367448.012160983</v>
       </c>
       <c r="G27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16374105.086462455</v>
+        <v>18114098.002767928</v>
       </c>
       <c r="H27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>606</v>
+        <v>725</v>
       </c>
       <c r="I27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="J27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2646,11 +2646,11 @@
       </c>
       <c r="N27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="O27">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="P27">
         <v>1</v>
@@ -2674,19 +2674,19 @@
       </c>
       <c r="F28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17399020.220064308</v>
+        <v>19051561.870875113</v>
       </c>
       <c r="G28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16060768.424630741</v>
+        <v>17747943.348565217</v>
       </c>
       <c r="H28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>558</v>
+        <v>662</v>
       </c>
       <c r="I28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>836</v>
+        <v>827</v>
       </c>
       <c r="J28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2702,11 +2702,11 @@
       </c>
       <c r="M28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="O28">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -2734,19 +2734,19 @@
       </c>
       <c r="F29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21903595.915449053</v>
+        <v>24407338.796157703</v>
       </c>
       <c r="G29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22045259.973748617</v>
+        <v>24181368.527279563</v>
       </c>
       <c r="H29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1039</v>
+        <v>970</v>
       </c>
       <c r="I29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>862</v>
+        <v>832</v>
       </c>
       <c r="J29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2766,11 +2766,11 @@
       </c>
       <c r="N29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1112</v>
+        <v>1119</v>
       </c>
       <c r="O29">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1109</v>
+        <v>1117</v>
       </c>
       <c r="P29">
         <v>1</v>
@@ -2794,19 +2794,19 @@
       </c>
       <c r="F30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>33172620.572869904</v>
+        <v>36449833.351521991</v>
       </c>
       <c r="G30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>31324284.763955772</v>
+        <v>34386413.695715845</v>
       </c>
       <c r="H30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1173</v>
+        <v>1121</v>
       </c>
       <c r="I30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="J30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2822,15 +2822,15 @@
       </c>
       <c r="M30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="O30">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1468</v>
+        <v>1459</v>
       </c>
       <c r="P30">
         <v>4</v>
@@ -2854,19 +2854,19 @@
       </c>
       <c r="F31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12052276.283295762</v>
+        <v>13310870.256587757</v>
       </c>
       <c r="G31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12818085.34321888</v>
+        <v>14130527.972239308</v>
       </c>
       <c r="H31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>448</v>
+        <v>479</v>
       </c>
       <c r="I31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>554</v>
+        <v>520</v>
       </c>
       <c r="J31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="N31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="O31">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -2914,19 +2914,19 @@
       </c>
       <c r="F32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>38950361.986051217</v>
+        <v>42702953.094052374</v>
       </c>
       <c r="G32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>39218450.568227202</v>
+        <v>42991561.47800532</v>
       </c>
       <c r="H32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1575</v>
+        <v>1549</v>
       </c>
       <c r="I32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1576</v>
+        <v>1571</v>
       </c>
       <c r="J32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2946,11 +2946,11 @@
       </c>
       <c r="N32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1967</v>
+        <v>1963</v>
       </c>
       <c r="O32">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1939</v>
+        <v>1943</v>
       </c>
       <c r="P32">
         <v>5</v>
@@ -2974,19 +2974,19 @@
       </c>
       <c r="F33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13641140.097482843</v>
+        <v>14955957.56824052</v>
       </c>
       <c r="G33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12702349.062420461</v>
+        <v>14128877.58695925</v>
       </c>
       <c r="H33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="I33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>747</v>
+        <v>887</v>
       </c>
       <c r="J33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3006,11 +3006,11 @@
       </c>
       <c r="N33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="O33">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="P33">
         <v>3</v>
@@ -3034,19 +3034,19 @@
       </c>
       <c r="F34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11020053.945719752</v>
+        <v>11919577.193698112</v>
       </c>
       <c r="G34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12313396.90175152</v>
+        <v>13624004.505409231</v>
       </c>
       <c r="H34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="I34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>580</v>
+        <v>746</v>
       </c>
       <c r="J34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3062,15 +3062,15 @@
       </c>
       <c r="M34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>698</v>
+        <v>689</v>
       </c>
       <c r="O34">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>734</v>
+        <v>745</v>
       </c>
       <c r="P34">
         <v>4</v>
@@ -3094,23 +3094,23 @@
       </c>
       <c r="F35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19655782.859162141</v>
+        <v>21458136.24003084</v>
       </c>
       <c r="G35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19043186.757094968</v>
+        <v>20541227.171415836</v>
       </c>
       <c r="H35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>815</v>
+        <v>861</v>
       </c>
       <c r="I35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>793</v>
+        <v>465</v>
       </c>
       <c r="J35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -3126,11 +3126,11 @@
       </c>
       <c r="N35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1113</v>
+        <v>1106</v>
       </c>
       <c r="O35">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1180</v>
+        <v>1164</v>
       </c>
       <c r="P35">
         <v>13</v>
@@ -3154,19 +3154,19 @@
       </c>
       <c r="F36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19180872.019964613</v>
+        <v>21107464.808607873</v>
       </c>
       <c r="G36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17431602.978954356</v>
+        <v>19115642.615416333</v>
       </c>
       <c r="H36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>823</v>
+        <v>803</v>
       </c>
       <c r="I36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>779</v>
+        <v>811</v>
       </c>
       <c r="J36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="L36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3186,11 +3186,11 @@
       </c>
       <c r="N36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1173</v>
+        <v>1154</v>
       </c>
       <c r="O36">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1351</v>
+        <v>1335</v>
       </c>
       <c r="P36">
         <v>4</v>
@@ -3214,19 +3214,19 @@
       </c>
       <c r="F37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>29876677.049243852</v>
+        <v>32820003.555210747</v>
       </c>
       <c r="G37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>31725346.660909802</v>
+        <v>34893533.726597093</v>
       </c>
       <c r="H37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1425</v>
+        <v>1392</v>
       </c>
       <c r="I37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1441</v>
+        <v>1575</v>
       </c>
       <c r="J37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="L37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3246,11 +3246,11 @@
       </c>
       <c r="N37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1834</v>
+        <v>1824</v>
       </c>
       <c r="O37">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2445</v>
+        <v>2418</v>
       </c>
       <c r="P37">
         <v>16</v>
@@ -3274,19 +3274,19 @@
       </c>
       <c r="F38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12462518.939564969</v>
+        <v>13698654.037510132</v>
       </c>
       <c r="G38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11421939.055878559</v>
+        <v>12519238.361120775</v>
       </c>
       <c r="H38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>452</v>
+        <v>425</v>
       </c>
       <c r="I38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="J38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3302,11 +3302,11 @@
       </c>
       <c r="M38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="O38">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -3334,19 +3334,19 @@
       </c>
       <c r="F39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>34603754.857470505</v>
+        <v>38445948.814468734</v>
       </c>
       <c r="G39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>38251004.015172802</v>
+        <v>41918196.556400456</v>
       </c>
       <c r="H39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2011</v>
+        <v>2038</v>
       </c>
       <c r="I39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1970</v>
+        <v>1950</v>
       </c>
       <c r="J39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3366,11 +3366,11 @@
       </c>
       <c r="N39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1943</v>
+        <v>1969</v>
       </c>
       <c r="O39">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2054</v>
+        <v>2064</v>
       </c>
       <c r="P39">
         <v>4</v>
@@ -3394,19 +3394,19 @@
       </c>
       <c r="F40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>23998515.44422197</v>
+        <v>26462235.347880993</v>
       </c>
       <c r="G40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>24688120.726337377</v>
+        <v>27157435.659359276</v>
       </c>
       <c r="H40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>736</v>
+        <v>705</v>
       </c>
       <c r="I40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>772</v>
+        <v>803</v>
       </c>
       <c r="J40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="L40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="N40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="O40">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -3454,19 +3454,19 @@
       </c>
       <c r="F41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21126962.544779114</v>
+        <v>22902447.746424876</v>
       </c>
       <c r="G41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12296140.818591988</v>
+        <v>14174402.098842507</v>
       </c>
       <c r="H41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>909</v>
+        <v>903</v>
       </c>
       <c r="I41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>936</v>
+        <v>919</v>
       </c>
       <c r="J41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3486,11 +3486,11 @@
       </c>
       <c r="N41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1143</v>
+        <v>1153</v>
       </c>
       <c r="O41">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1088</v>
+        <v>1082</v>
       </c>
       <c r="P41">
         <v>4</v>
@@ -3514,19 +3514,19 @@
       </c>
       <c r="F42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20292399.117647201</v>
+        <v>22203549.116332825</v>
       </c>
       <c r="G42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19732293.398156039</v>
+        <v>21668424.355895929</v>
       </c>
       <c r="H42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>615</v>
+        <v>595</v>
       </c>
       <c r="I42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>668</v>
+        <v>651</v>
       </c>
       <c r="J42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3546,11 +3546,11 @@
       </c>
       <c r="N42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="O42">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="P42">
         <v>2</v>
@@ -3574,19 +3574,19 @@
       </c>
       <c r="F43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11675592.217419149</v>
+        <v>13229112.238779062</v>
       </c>
       <c r="G43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12617432.245743323</v>
+        <v>13892344.82190132</v>
       </c>
       <c r="H43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>655</v>
+        <v>761</v>
       </c>
       <c r="I43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="J43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="L43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3606,11 +3606,11 @@
       </c>
       <c r="N43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="O43">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="P43">
         <v>2</v>
@@ -3634,19 +3634,19 @@
       </c>
       <c r="F44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11469697.687318595</v>
+        <v>12706768.574557343</v>
       </c>
       <c r="G44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10927877.013120186</v>
+        <v>12158153.26136156</v>
       </c>
       <c r="H44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>711</v>
+        <v>729</v>
       </c>
       <c r="I44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="J44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3666,11 +3666,11 @@
       </c>
       <c r="N44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="O44">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="P44">
         <v>3</v>
@@ -3694,19 +3694,19 @@
       </c>
       <c r="F45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>39658020.754120097</v>
+        <v>43323385.421304703</v>
       </c>
       <c r="G45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>33970655.650308527</v>
+        <v>37265260.436432607</v>
       </c>
       <c r="H45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1068</v>
+        <v>1120</v>
       </c>
       <c r="I45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1072</v>
+        <v>1078</v>
       </c>
       <c r="J45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="L45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3726,11 +3726,11 @@
       </c>
       <c r="N45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1281</v>
+        <v>1285</v>
       </c>
       <c r="O45">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="P45">
         <v>4</v>
@@ -3754,19 +3754,19 @@
       </c>
       <c r="F46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17566001.730502713</v>
+        <v>19117456.997472573</v>
       </c>
       <c r="G46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16286567.597074073</v>
+        <v>17869965.656653393</v>
       </c>
       <c r="H46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>906</v>
+        <v>968</v>
       </c>
       <c r="I46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>923</v>
+        <v>881</v>
       </c>
       <c r="J46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3786,11 +3786,11 @@
       </c>
       <c r="N46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="O46">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="P46">
         <v>4</v>
@@ -3814,19 +3814,19 @@
       </c>
       <c r="F47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>23215427.489808504</v>
+        <v>25734348.457785707</v>
       </c>
       <c r="G47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>29152507.694931164</v>
+        <v>32049677.103434991</v>
       </c>
       <c r="H47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>959</v>
+        <v>939</v>
       </c>
       <c r="I47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1017</v>
+        <v>1045</v>
       </c>
       <c r="J47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3846,11 +3846,11 @@
       </c>
       <c r="N47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="O47">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="P47">
         <v>6</v>
@@ -3874,19 +3874,19 @@
       </c>
       <c r="F48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12332994.762099404</v>
+        <v>13719210.446378822</v>
       </c>
       <c r="G48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15040340.008889956</v>
+        <v>16535390.401304321</v>
       </c>
       <c r="H48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="I48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="J48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="N48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="O48">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -3934,19 +3934,19 @@
       </c>
       <c r="F49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14070540.257583896</v>
+        <v>15256433.802802257</v>
       </c>
       <c r="G49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11090723.62741236</v>
+        <v>12078370.394055249</v>
       </c>
       <c r="H49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>322</v>
+        <v>292</v>
       </c>
       <c r="I49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="J49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="N49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="O49">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -3994,19 +3994,19 @@
       </c>
       <c r="F50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10956552.874769645</v>
+        <v>12039200.120742671</v>
       </c>
       <c r="G50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9670437.9324168526</v>
+        <v>10518219.170153208</v>
       </c>
       <c r="H50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="I50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2787</v>
+        <v>332</v>
       </c>
       <c r="J50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4026,11 +4026,11 @@
       </c>
       <c r="N50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="O50">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P50">
         <v>4</v>
@@ -4054,19 +4054,19 @@
       </c>
       <c r="F51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24000525.631255325</v>
+        <v>26234347.209597055</v>
       </c>
       <c r="G51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22657317.560193349</v>
+        <v>24717928.535999633</v>
       </c>
       <c r="H51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>958</v>
+        <v>935</v>
       </c>
       <c r="I51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>964</v>
+        <v>925</v>
       </c>
       <c r="J51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="L51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4086,11 +4086,11 @@
       </c>
       <c r="N51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="O51">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="P51">
         <v>5</v>
@@ -4114,19 +4114,19 @@
       </c>
       <c r="F52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24952414.545414973</v>
+        <v>27600521.52657304</v>
       </c>
       <c r="G52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20747156.830999862</v>
+        <v>23324427.700908128</v>
       </c>
       <c r="H52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>989</v>
+        <v>1150</v>
       </c>
       <c r="I52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>937</v>
+        <v>889</v>
       </c>
       <c r="J52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4138,19 +4138,19 @@
       </c>
       <c r="L52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="O52">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>982</v>
+        <v>995</v>
       </c>
       <c r="P52">
         <v>4</v>
@@ -4174,19 +4174,19 @@
       </c>
       <c r="F53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>32989159.026679937</v>
+        <v>35787847.640754372</v>
       </c>
       <c r="G53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>42923506.72697591</v>
+        <v>46682576.652989939</v>
       </c>
       <c r="H53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1476</v>
+        <v>1251</v>
       </c>
       <c r="I53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1639</v>
+        <v>1445</v>
       </c>
       <c r="J53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4206,11 +4206,11 @@
       </c>
       <c r="N53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2236</v>
+        <v>2223</v>
       </c>
       <c r="O53">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2068</v>
+        <v>2076</v>
       </c>
       <c r="P53">
         <v>8</v>
@@ -4234,19 +4234,19 @@
       </c>
       <c r="F54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11837990.619278032</v>
+        <v>12957556.739625184</v>
       </c>
       <c r="G54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10041405.614067961</v>
+        <v>11099238.69559554</v>
       </c>
       <c r="H54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>580</v>
+        <v>547</v>
       </c>
       <c r="I54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="J54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="M54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -4294,19 +4294,19 @@
       </c>
       <c r="F55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17085232.849608403</v>
+        <v>18801809.362829365</v>
       </c>
       <c r="G55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17707083.120192073</v>
+        <v>19739544.691658638</v>
       </c>
       <c r="H55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="I55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>733</v>
+        <v>695</v>
       </c>
       <c r="J55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4326,11 +4326,11 @@
       </c>
       <c r="N55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="O55">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="P55">
         <v>6</v>
@@ -4354,19 +4354,19 @@
       </c>
       <c r="F56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14228080.103506284</v>
+        <v>15612754.366214955</v>
       </c>
       <c r="G56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10974111.643722907</v>
+        <v>12105700.997142749</v>
       </c>
       <c r="H56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>686</v>
+        <v>665</v>
       </c>
       <c r="I56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="J56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="L56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4386,11 +4386,11 @@
       </c>
       <c r="N56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="O56">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="P56">
         <v>3</v>
@@ -4414,19 +4414,19 @@
       </c>
       <c r="F57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>23707410.117147829</v>
+        <v>26124638.488840576</v>
       </c>
       <c r="G57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23768120.633329134</v>
+        <v>25947240.738314714</v>
       </c>
       <c r="H57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="I57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="J57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="O57">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="P57">
         <v>3</v>
@@ -4474,19 +4474,19 @@
       </c>
       <c r="F58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>29468066.465633627</v>
+        <v>32375875.294686958</v>
       </c>
       <c r="G58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>28107742.326862235</v>
+        <v>31385541.692812439</v>
       </c>
       <c r="H58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1443</v>
+        <v>1352</v>
       </c>
       <c r="I58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1477</v>
+        <v>1510</v>
       </c>
       <c r="J58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4502,15 +4502,15 @@
       </c>
       <c r="M58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1334</v>
+        <v>1337</v>
       </c>
       <c r="O58">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1408</v>
+        <v>1425</v>
       </c>
       <c r="P58">
         <v>4</v>
@@ -4534,19 +4534,19 @@
       </c>
       <c r="F59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15494292.208695738</v>
+        <v>16921073.286912169</v>
       </c>
       <c r="G59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15929363.198218364</v>
+        <v>17447941.078375421</v>
       </c>
       <c r="H59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>696</v>
+        <v>740</v>
       </c>
       <c r="I59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="J59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4566,11 +4566,11 @@
       </c>
       <c r="N59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="O59">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="P59">
         <v>3</v>
@@ -4594,19 +4594,19 @@
       </c>
       <c r="F60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18091176.906567469</v>
+        <v>19757041.776899666</v>
       </c>
       <c r="G60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17644632.482370876</v>
+        <v>19448677.858427402</v>
       </c>
       <c r="H60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="I60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="J60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4622,11 +4622,11 @@
       </c>
       <c r="M60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="O60">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -4654,19 +4654,19 @@
       </c>
       <c r="F61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>42190631.543374673</v>
+        <v>47114478.212284766</v>
       </c>
       <c r="G61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>56820046.060979337</v>
+        <v>62697973.94385463</v>
       </c>
       <c r="H61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1603</v>
+        <v>1572</v>
       </c>
       <c r="I61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1688</v>
+        <v>1606</v>
       </c>
       <c r="J61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4674,23 +4674,23 @@
       </c>
       <c r="K61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="O61">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1996</v>
+        <v>1970</v>
       </c>
       <c r="P61">
         <v>10</v>
@@ -4714,19 +4714,19 @@
       </c>
       <c r="F62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>42052983.529155493</v>
+        <v>46229977.312252909</v>
       </c>
       <c r="G62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>40496738.011696391</v>
+        <v>45449660.687625058</v>
       </c>
       <c r="H62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1104</v>
+        <v>1081</v>
       </c>
       <c r="I62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="J62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4742,15 +4742,15 @@
       </c>
       <c r="M62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1629</v>
+        <v>1624</v>
       </c>
       <c r="O62">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="P62">
         <v>9</v>
@@ -4774,19 +4774,19 @@
       </c>
       <c r="F63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>27220648.034163546</v>
+        <v>29968181.395187031</v>
       </c>
       <c r="G63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>27163402.734975632</v>
+        <v>30160380.248123996</v>
       </c>
       <c r="H63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>782</v>
+        <v>688</v>
       </c>
       <c r="I63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="J63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4806,11 +4806,11 @@
       </c>
       <c r="N63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="O63">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="P63">
         <v>4</v>
@@ -4834,19 +4834,19 @@
       </c>
       <c r="F64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>38559981.787422098</v>
+        <v>42307324.288243957</v>
       </c>
       <c r="G64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>41192471.998564802</v>
+        <v>45476168.730734654</v>
       </c>
       <c r="H64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1402</v>
+        <v>1274</v>
       </c>
       <c r="I64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1396</v>
+        <v>1437</v>
       </c>
       <c r="J64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4858,19 +4858,19 @@
       </c>
       <c r="L64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>163</v>
+        <v>366</v>
       </c>
       <c r="N64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1867</v>
+        <v>1862</v>
       </c>
       <c r="O64">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2149</v>
+        <v>2335</v>
       </c>
       <c r="P64">
         <v>9</v>
@@ -4894,19 +4894,19 @@
       </c>
       <c r="F65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>2942421.1271584849</v>
+        <v>3303333.5893165562</v>
       </c>
       <c r="G65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>866549.93732182099</v>
+        <v>1088246.2504583341</v>
       </c>
       <c r="H65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="I65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>265</v>
+        <v>415</v>
       </c>
       <c r="J65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4914,11 +4914,11 @@
       </c>
       <c r="K65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4926,11 +4926,11 @@
       </c>
       <c r="N65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O65">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P65">
         <v>3</v>
@@ -4954,19 +4954,19 @@
       </c>
       <c r="F66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>30974184.927460741</v>
+        <v>33805872.393411718</v>
       </c>
       <c r="G66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>29595379.829328042</v>
+        <v>32336066.762660287</v>
       </c>
       <c r="H66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1605</v>
+        <v>1626</v>
       </c>
       <c r="I66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1574</v>
+        <v>1542</v>
       </c>
       <c r="J66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="M66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -4990,7 +4990,7 @@
       </c>
       <c r="O66">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1667</v>
+        <v>1674</v>
       </c>
       <c r="P66">
         <v>6</v>
@@ -5014,19 +5014,19 @@
       </c>
       <c r="F67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12270964.333252013</v>
+        <v>13264992.414578712</v>
       </c>
       <c r="G67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13885953.953792712</v>
+        <v>15325394.688526897</v>
       </c>
       <c r="H67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="I67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>600</v>
+        <v>614</v>
       </c>
       <c r="J67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5046,11 +5046,11 @@
       </c>
       <c r="N67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>652</v>
+        <v>666</v>
       </c>
       <c r="O67">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="P67">
         <v>3</v>
@@ -5074,19 +5074,19 @@
       </c>
       <c r="F68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20714455.23746011</v>
+        <v>22548489.861411422</v>
       </c>
       <c r="G68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19791464.354459144</v>
+        <v>21867582.03235082</v>
       </c>
       <c r="H68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>941</v>
+        <v>971</v>
       </c>
       <c r="I68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>892</v>
+        <v>859</v>
       </c>
       <c r="J68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5106,11 +5106,11 @@
       </c>
       <c r="N68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1349</v>
+        <v>1342</v>
       </c>
       <c r="O68">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1359</v>
+        <v>1369</v>
       </c>
       <c r="P68">
         <v>3</v>
@@ -5134,19 +5134,19 @@
       </c>
       <c r="F69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11194059.658313934</v>
+        <v>12696820.613842988</v>
       </c>
       <c r="G69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13965270.135004491</v>
+        <v>14511263.008932166</v>
       </c>
       <c r="H69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1685</v>
+        <v>1380</v>
       </c>
       <c r="I69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1220</v>
+        <v>597</v>
       </c>
       <c r="J69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="L69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5166,11 +5166,11 @@
       </c>
       <c r="N69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1402</v>
+        <v>1396</v>
       </c>
       <c r="O69">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1294</v>
+        <v>1287</v>
       </c>
       <c r="P69">
         <v>4</v>
@@ -5194,19 +5194,19 @@
       </c>
       <c r="F70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>35080672.915383458</v>
+        <v>38688418.739473499</v>
       </c>
       <c r="G70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>36289796.525273778</v>
+        <v>39831462.257459968</v>
       </c>
       <c r="H70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1232</v>
+        <v>1488</v>
       </c>
       <c r="I70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="J70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5218,19 +5218,19 @@
       </c>
       <c r="L70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1742</v>
+        <v>1745</v>
       </c>
       <c r="O70">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1731</v>
+        <v>1737</v>
       </c>
       <c r="P70">
         <v>4</v>
@@ -5254,19 +5254,19 @@
       </c>
       <c r="F71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7880801.5686250767</v>
+        <v>8715480.3903808221</v>
       </c>
       <c r="G71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7436736.8711797697</v>
+        <v>8057116.8412494138</v>
       </c>
       <c r="H71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>591</v>
+        <v>514</v>
       </c>
       <c r="I71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="J71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="N71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="O71">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -5314,19 +5314,19 @@
       </c>
       <c r="F72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12327433.580337113</v>
+        <v>13545098.441002436</v>
       </c>
       <c r="G72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11372239.052546794</v>
+        <v>12597475.045724921</v>
       </c>
       <c r="H72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>873</v>
+        <v>845</v>
       </c>
       <c r="I72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>794</v>
+        <v>999</v>
       </c>
       <c r="J72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="N72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="O72">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -5374,19 +5374,19 @@
       </c>
       <c r="F73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7675922.5408083284</v>
+        <v>8794172.8037036434</v>
       </c>
       <c r="G73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11027043.533425763</v>
+        <v>12245132.80994164</v>
       </c>
       <c r="H73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>518</v>
+        <v>431</v>
       </c>
       <c r="I73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>460</v>
+        <v>493</v>
       </c>
       <c r="J73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="L73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="O73">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="P73">
         <v>7</v>
@@ -5434,19 +5434,19 @@
       </c>
       <c r="F74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8168937.7104559364</v>
+        <v>8938535.046445122</v>
       </c>
       <c r="G74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9440020.5816278141</v>
+        <v>10277085.972706931</v>
       </c>
       <c r="H74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>764</v>
+        <v>709</v>
       </c>
       <c r="I74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>719</v>
+        <v>732</v>
       </c>
       <c r="J74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5466,11 +5466,11 @@
       </c>
       <c r="N74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="O74">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="P74">
         <v>2</v>
@@ -5494,19 +5494,19 @@
       </c>
       <c r="F75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9324331.1601992901</v>
+        <v>10267447.870031901</v>
       </c>
       <c r="G75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10312525.498841934</v>
+        <v>11211811.326490723</v>
       </c>
       <c r="H75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="I75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="J75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="L75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="O75">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="P75">
         <v>1</v>
@@ -5554,19 +5554,19 @@
       </c>
       <c r="F76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>26416851.045317288</v>
+        <v>28811381.822914738</v>
       </c>
       <c r="G76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>26078957.954257365</v>
+        <v>29014112.452576768</v>
       </c>
       <c r="H76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>858</v>
+        <v>756</v>
       </c>
       <c r="I76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>771</v>
+        <v>755</v>
       </c>
       <c r="J76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5586,11 +5586,11 @@
       </c>
       <c r="N76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="O76">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="P76">
         <v>4</v>
@@ -5614,19 +5614,19 @@
       </c>
       <c r="F77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16071643.609950272</v>
+        <v>17376373.350340452</v>
       </c>
       <c r="G77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16027104.838134946</v>
+        <v>17505873.817607421</v>
       </c>
       <c r="H77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="I77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>730</v>
+        <v>721</v>
       </c>
       <c r="J77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="L77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="N77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="O77">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -5674,19 +5674,19 @@
       </c>
       <c r="F78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12913446.391234845</v>
+        <v>14290245.398241306</v>
       </c>
       <c r="G78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13467808.102383876</v>
+        <v>14020057.900462007</v>
       </c>
       <c r="H78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>813</v>
+        <v>879</v>
       </c>
       <c r="I78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>134</v>
+        <v>791</v>
       </c>
       <c r="J78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5706,11 +5706,11 @@
       </c>
       <c r="N78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="O78">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>971</v>
+        <v>964</v>
       </c>
       <c r="P78">
         <v>3</v>
@@ -5734,19 +5734,19 @@
       </c>
       <c r="F79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15027790.131356351</v>
+        <v>16556444.499608569</v>
       </c>
       <c r="G79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11427700.005160464</v>
+        <v>13094329.610911908</v>
       </c>
       <c r="H79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>821</v>
+        <v>812</v>
       </c>
       <c r="I79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1081</v>
+        <v>891</v>
       </c>
       <c r="J79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5766,11 +5766,11 @@
       </c>
       <c r="N79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="O79">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="P79">
         <v>3</v>
@@ -5794,19 +5794,19 @@
       </c>
       <c r="F80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15080277.199489065</v>
+        <v>16880084.510550667</v>
       </c>
       <c r="G80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16388269.707009552</v>
+        <v>18305554.193984501</v>
       </c>
       <c r="H80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>671</v>
+        <v>704</v>
       </c>
       <c r="I80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>794</v>
+        <v>749</v>
       </c>
       <c r="J80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5826,11 +5826,11 @@
       </c>
       <c r="N80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="O80">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="P80">
         <v>3</v>
@@ -5854,19 +5854,19 @@
       </c>
       <c r="F81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7537594.2901824489</v>
+        <v>8199813.1471998431</v>
       </c>
       <c r="G81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7936306.0676140552</v>
+        <v>8668989.4204564169</v>
       </c>
       <c r="H81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="I81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>582</v>
+        <v>540</v>
       </c>
       <c r="J81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5886,11 +5886,11 @@
       </c>
       <c r="N81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="O81">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="P81">
         <v>1</v>
@@ -5914,19 +5914,19 @@
       </c>
       <c r="F82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>28907365.834728513</v>
+        <v>32144265.812579334</v>
       </c>
       <c r="G82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>31990138.886422463</v>
+        <v>35301547.313618742</v>
       </c>
       <c r="H82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1295</v>
+        <v>1251</v>
       </c>
       <c r="I82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1311</v>
+        <v>1290</v>
       </c>
       <c r="J82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5946,11 +5946,11 @@
       </c>
       <c r="N82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1718</v>
+        <v>1715</v>
       </c>
       <c r="O82">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1752</v>
+        <v>1754</v>
       </c>
       <c r="P82">
         <v>1</v>
@@ -5974,19 +5974,19 @@
       </c>
       <c r="F83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7812991.3725561891</v>
+        <v>9037128.4041979909</v>
       </c>
       <c r="G83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6516778.8492811872</v>
+        <v>7537881.091569989</v>
       </c>
       <c r="H83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>667</v>
+        <v>937</v>
       </c>
       <c r="I83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>679</v>
+        <v>872</v>
       </c>
       <c r="J83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6006,11 +6006,11 @@
       </c>
       <c r="N83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="O83">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="P83">
         <v>2</v>
@@ -6034,19 +6034,19 @@
       </c>
       <c r="F84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14412259.778720619</v>
+        <v>15900425.501327815</v>
       </c>
       <c r="G84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15070172.236953417</v>
+        <v>16485262.08125736</v>
       </c>
       <c r="H84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>593</v>
+        <v>570</v>
       </c>
       <c r="I84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>555</v>
+        <v>580</v>
       </c>
       <c r="J84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6066,11 +6066,11 @@
       </c>
       <c r="N84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="O84">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="P84">
         <v>7</v>
@@ -6094,19 +6094,19 @@
       </c>
       <c r="F85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4236420.8188401982</v>
+        <v>4623806.3159846626</v>
       </c>
       <c r="G85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3753216.5787746692</v>
+        <v>4055469.882370349</v>
       </c>
       <c r="H85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>334</v>
+        <v>313</v>
       </c>
       <c r="I85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>338</v>
+        <v>309</v>
       </c>
       <c r="J85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6126,11 +6126,11 @@
       </c>
       <c r="N85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="O85">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="P85">
         <v>2</v>
@@ -6163,31 +6163,31 @@
       <c r="A3" s="11"/>
       <c r="B3" s="11">
         <f t="shared" ref="B3:K3" si="0">SUBTOTAL(9,B6:B90)</f>
-        <v>83925</v>
+        <v>83890</v>
       </c>
       <c r="C3" s="11">
         <f t="shared" si="0"/>
-        <v>458</v>
+        <v>476</v>
       </c>
       <c r="D3" s="11">
         <f t="shared" si="0"/>
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E3" s="11">
         <f t="shared" si="0"/>
-        <v>68742</v>
+        <v>68778</v>
       </c>
       <c r="F3" s="11">
         <f t="shared" si="0"/>
-        <v>1503921962.980973</v>
+        <v>1654537154.120717</v>
       </c>
       <c r="G3" s="11">
         <f t="shared" si="0"/>
-        <v>84655</v>
+        <v>84861</v>
       </c>
       <c r="H3" s="11">
         <f t="shared" si="0"/>
-        <v>730</v>
+        <v>961</v>
       </c>
       <c r="I3" s="11">
         <f t="shared" si="0"/>
@@ -6195,11 +6195,11 @@
       </c>
       <c r="J3" s="11">
         <f t="shared" si="0"/>
-        <v>72578</v>
+        <v>70217</v>
       </c>
       <c r="K3" s="11">
         <f t="shared" si="0"/>
-        <v>1499455177.6107061</v>
+        <v>1652301217.7925961</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -6259,7 +6259,7 @@
         <v>117</v>
       </c>
       <c r="B6" s="10">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C6" s="10">
         <v>3</v>
@@ -6268,13 +6268,13 @@
         <v>2</v>
       </c>
       <c r="E6" s="10">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="F6" s="10">
-        <v>7403766.379118205</v>
+        <v>8148583.395282384</v>
       </c>
       <c r="G6" s="10">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H6" s="10">
         <v>0</v>
@@ -6283,10 +6283,10 @@
         <v>2</v>
       </c>
       <c r="J6" s="10">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="K6" s="10">
-        <v>6772587.9741216879</v>
+        <v>7383118.5990972444</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
@@ -6294,7 +6294,7 @@
         <v>127</v>
       </c>
       <c r="B7" s="10">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C7" s="10">
         <v>1</v>
@@ -6303,25 +6303,25 @@
         <v>1</v>
       </c>
       <c r="E7" s="10">
-        <v>610</v>
+        <v>635</v>
       </c>
       <c r="F7" s="10">
-        <v>9081858.2921876088</v>
+        <v>10074713.131280864</v>
       </c>
       <c r="G7" s="10">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="H7" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" s="10">
         <v>2</v>
       </c>
       <c r="J7" s="10">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="K7" s="10">
-        <v>8061375.9813275402</v>
+        <v>8806603.2716049217</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
@@ -6329,7 +6329,7 @@
         <v>119</v>
       </c>
       <c r="B8" s="10">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="C8" s="10">
         <v>2</v>
@@ -6338,13 +6338,13 @@
         <v>2</v>
       </c>
       <c r="E8" s="10">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="F8" s="10">
-        <v>8472343.6507805083</v>
+        <v>9579603.6779472157</v>
       </c>
       <c r="G8" s="10">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="H8" s="10">
         <v>5</v>
@@ -6353,10 +6353,10 @@
         <v>1</v>
       </c>
       <c r="J8" s="10">
-        <v>699</v>
+        <v>690</v>
       </c>
       <c r="K8" s="10">
-        <v>9235547.2123001292</v>
+        <v>10474601.900855821</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
@@ -6364,34 +6364,34 @@
         <v>121</v>
       </c>
       <c r="B9" s="10">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="C9" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" s="10">
-        <v>944</v>
+        <v>1251</v>
       </c>
       <c r="F9" s="10">
-        <v>17086090.225409012</v>
+        <v>18772595.596177574</v>
       </c>
       <c r="G9" s="10">
-        <v>1210</v>
+        <v>1215</v>
       </c>
       <c r="H9" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I9" s="10">
         <v>3</v>
       </c>
       <c r="J9" s="10">
-        <v>992</v>
+        <v>1021</v>
       </c>
       <c r="K9" s="10">
-        <v>17268876.652935285</v>
+        <v>19007257.264013216</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
@@ -6399,22 +6399,22 @@
         <v>123</v>
       </c>
       <c r="B10" s="10">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C10" s="10">
         <v>1</v>
       </c>
       <c r="D10" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="10">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="F10" s="10">
-        <v>6579428.4202598128</v>
+        <v>7351981.8698023772</v>
       </c>
       <c r="G10" s="10">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H10" s="10">
         <v>1</v>
@@ -6423,10 +6423,10 @@
         <v>1</v>
       </c>
       <c r="J10" s="10">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="K10" s="10">
-        <v>7621380.8444610247</v>
+        <v>8379190.2540950719</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
@@ -6434,7 +6434,7 @@
         <v>125</v>
       </c>
       <c r="B11" s="10">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C11" s="10">
         <v>2</v>
@@ -6443,13 +6443,13 @@
         <v>2</v>
       </c>
       <c r="E11" s="10">
-        <v>355</v>
+        <v>315</v>
       </c>
       <c r="F11" s="10">
-        <v>6507233.0071156528</v>
+        <v>7102539.9786560358</v>
       </c>
       <c r="G11" s="10">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H11" s="10">
         <v>2</v>
@@ -6458,10 +6458,10 @@
         <v>2</v>
       </c>
       <c r="J11" s="10">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="K11" s="10">
-        <v>6557460.7367064152</v>
+        <v>7143934.4550414039</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -6478,25 +6478,25 @@
         <v>1</v>
       </c>
       <c r="E12" s="10">
-        <v>483</v>
+        <v>504</v>
       </c>
       <c r="F12" s="10">
-        <v>7502762.8835716713</v>
+        <v>8274433.0801868876</v>
       </c>
       <c r="G12" s="10">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="H12" s="10">
         <v>1</v>
       </c>
       <c r="I12" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J12" s="10">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="K12" s="10">
-        <v>7573764.9543150803</v>
+        <v>8338127.2616301412</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
@@ -6504,7 +6504,7 @@
         <v>133</v>
       </c>
       <c r="B13" s="10">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C13" s="10">
         <v>0</v>
@@ -6513,13 +6513,13 @@
         <v>1</v>
       </c>
       <c r="E13" s="10">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F13" s="10">
-        <v>3333683.0118716359</v>
+        <v>3656016.5393009051</v>
       </c>
       <c r="G13" s="10">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H13" s="10">
         <v>0</v>
@@ -6528,10 +6528,10 @@
         <v>1</v>
       </c>
       <c r="J13" s="10">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="K13" s="10">
-        <v>3412858.6587270629</v>
+        <v>3746619.7807002808</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
@@ -6539,7 +6539,7 @@
         <v>141</v>
       </c>
       <c r="B14" s="10">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C14" s="10">
         <v>1</v>
@@ -6548,13 +6548,13 @@
         <v>0</v>
       </c>
       <c r="E14" s="10">
-        <v>172</v>
+        <v>234</v>
       </c>
       <c r="F14" s="10">
-        <v>3327945.8076576372</v>
+        <v>3662736.030057156</v>
       </c>
       <c r="G14" s="10">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H14" s="10">
         <v>0</v>
@@ -6563,10 +6563,10 @@
         <v>1</v>
       </c>
       <c r="J14" s="10">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="K14" s="10">
-        <v>356764.62464087899</v>
+        <v>586274.09262576199</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
@@ -6583,14 +6583,14 @@
         <v>0</v>
       </c>
       <c r="E15" s="10">
+        <v>341</v>
+      </c>
+      <c r="F15" s="10">
+        <v>5886575.0213002944</v>
+      </c>
+      <c r="G15" s="10">
         <v>369</v>
       </c>
-      <c r="F15" s="10">
-        <v>5285015.9714740682</v>
-      </c>
-      <c r="G15" s="10">
-        <v>371</v>
-      </c>
       <c r="H15" s="10">
         <v>1</v>
       </c>
@@ -6598,10 +6598,10 @@
         <v>1</v>
       </c>
       <c r="J15" s="10">
-        <v>379</v>
+        <v>329</v>
       </c>
       <c r="K15" s="10">
-        <v>7406718.8965042289</v>
+        <v>7938415.2501511136</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
@@ -6609,7 +6609,7 @@
         <v>143</v>
       </c>
       <c r="B16" s="10">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C16" s="10">
         <v>0</v>
@@ -6618,13 +6618,13 @@
         <v>1</v>
       </c>
       <c r="E16" s="10">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="F16" s="10">
-        <v>2493060.9630141081</v>
+        <v>2763314.70019016</v>
       </c>
       <c r="G16" s="10">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H16" s="10">
         <v>0</v>
@@ -6633,10 +6633,10 @@
         <v>2</v>
       </c>
       <c r="J16" s="10">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="K16" s="10">
-        <v>3295803.4780012751</v>
+        <v>3605141.5898137731</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -6644,7 +6644,7 @@
         <v>145</v>
       </c>
       <c r="B17" s="10">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C17" s="10">
         <v>7</v>
@@ -6653,25 +6653,25 @@
         <v>0</v>
       </c>
       <c r="E17" s="10">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="F17" s="10">
-        <v>3339864.9400243089</v>
+        <v>3731770.761003104</v>
       </c>
       <c r="G17" s="10">
         <v>242</v>
       </c>
       <c r="H17" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" s="10">
-        <v>241</v>
+        <v>1029</v>
       </c>
       <c r="K17" s="10">
-        <v>3668103.6269933642</v>
+        <v>3976103.8294773069</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
@@ -6679,7 +6679,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="10">
-        <v>1433</v>
+        <v>1428</v>
       </c>
       <c r="C18" s="10">
         <v>0</v>
@@ -6688,10 +6688,10 @@
         <v>2</v>
       </c>
       <c r="E18" s="10">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="F18" s="10">
-        <v>7512201.2733524209</v>
+        <v>7512211.1851744372</v>
       </c>
       <c r="G18" s="10">
         <v>1430</v>
@@ -6703,10 +6703,10 @@
         <v>3</v>
       </c>
       <c r="J18" s="10">
-        <v>1100</v>
+        <v>1622</v>
       </c>
       <c r="K18" s="10">
-        <v>11435917.552780986</v>
+        <v>13395441.917632751</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
@@ -6714,7 +6714,7 @@
         <v>45</v>
       </c>
       <c r="B19" s="10">
-        <v>1283</v>
+        <v>1287</v>
       </c>
       <c r="C19" s="10">
         <v>0</v>
@@ -6723,13 +6723,13 @@
         <v>2</v>
       </c>
       <c r="E19" s="10">
-        <v>1090</v>
+        <v>1196</v>
       </c>
       <c r="F19" s="10">
-        <v>23900483.28657113</v>
+        <v>27027994.608759265</v>
       </c>
       <c r="G19" s="10">
-        <v>1229</v>
+        <v>1235</v>
       </c>
       <c r="H19" s="10">
         <v>1</v>
@@ -6738,10 +6738,10 @@
         <v>3</v>
       </c>
       <c r="J19" s="10">
-        <v>888</v>
+        <v>881</v>
       </c>
       <c r="K19" s="10">
-        <v>24163229.470245697</v>
+        <v>26636902.010980774</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
@@ -6749,7 +6749,7 @@
         <v>47</v>
       </c>
       <c r="B20" s="10">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="C20" s="10">
         <v>1</v>
@@ -6758,13 +6758,13 @@
         <v>3</v>
       </c>
       <c r="E20" s="10">
-        <v>882</v>
+        <v>941</v>
       </c>
       <c r="F20" s="10">
-        <v>13687331.401381763</v>
+        <v>15102559.791172484</v>
       </c>
       <c r="G20" s="10">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="H20" s="10">
         <v>2</v>
@@ -6773,10 +6773,10 @@
         <v>5</v>
       </c>
       <c r="J20" s="10">
-        <v>1346</v>
+        <v>966</v>
       </c>
       <c r="K20" s="10">
-        <v>14290505.340465739</v>
+        <v>15824748.753173972</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
@@ -6784,7 +6784,7 @@
         <v>49</v>
       </c>
       <c r="B21" s="10">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="C21" s="10">
         <v>0</v>
@@ -6793,13 +6793,13 @@
         <v>2</v>
       </c>
       <c r="E21" s="10">
-        <v>697</v>
+        <v>607</v>
       </c>
       <c r="F21" s="10">
-        <v>14508159.402924469</v>
+        <v>15734908.735146243</v>
       </c>
       <c r="G21" s="10">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="H21" s="10">
         <v>3</v>
@@ -6808,10 +6808,10 @@
         <v>3</v>
       </c>
       <c r="J21" s="10">
-        <v>801</v>
+        <v>657</v>
       </c>
       <c r="K21" s="10">
-        <v>9683317.7825561687</v>
+        <v>10910855.575781677</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
@@ -6819,34 +6819,34 @@
         <v>51</v>
       </c>
       <c r="B22" s="10">
-        <v>2790</v>
+        <v>2784</v>
       </c>
       <c r="C22" s="10">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D22" s="10">
         <v>10</v>
       </c>
       <c r="E22" s="10">
-        <v>1885</v>
+        <v>1911</v>
       </c>
       <c r="F22" s="10">
-        <v>48234189.966538787</v>
+        <v>52792789.530242719</v>
       </c>
       <c r="G22" s="10">
-        <v>2915</v>
+        <v>2902</v>
       </c>
       <c r="H22" s="10">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I22" s="10">
         <v>10</v>
       </c>
       <c r="J22" s="10">
-        <v>2175</v>
+        <v>2097</v>
       </c>
       <c r="K22" s="10">
-        <v>54021728.128000915</v>
+        <v>58761430.803304039</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
@@ -6854,7 +6854,7 @@
         <v>53</v>
       </c>
       <c r="B23" s="10">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="C23" s="10">
         <v>0</v>
@@ -6863,13 +6863,13 @@
         <v>2</v>
       </c>
       <c r="E23" s="10">
-        <v>1183</v>
+        <v>1146</v>
       </c>
       <c r="F23" s="10">
-        <v>26648723.196364921</v>
+        <v>29359803.28090911</v>
       </c>
       <c r="G23" s="10">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="H23" s="10">
         <v>3</v>
@@ -6878,10 +6878,10 @@
         <v>1</v>
       </c>
       <c r="J23" s="10">
-        <v>1206</v>
+        <v>1135</v>
       </c>
       <c r="K23" s="10">
-        <v>9209407.9122159164</v>
+        <v>11582816.775124433</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
@@ -6889,7 +6889,7 @@
         <v>55</v>
       </c>
       <c r="B24" s="10">
-        <v>2996</v>
+        <v>2991</v>
       </c>
       <c r="C24" s="10">
         <v>9</v>
@@ -6898,25 +6898,25 @@
         <v>12</v>
       </c>
       <c r="E24" s="10">
-        <v>2404</v>
+        <v>2495</v>
       </c>
       <c r="F24" s="10">
-        <v>52087375.427271821</v>
+        <v>57514764.250181429</v>
       </c>
       <c r="G24" s="10">
-        <v>2968</v>
+        <v>2969</v>
       </c>
       <c r="H24" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I24" s="10">
         <v>10</v>
       </c>
       <c r="J24" s="10">
-        <v>2213</v>
+        <v>2229</v>
       </c>
       <c r="K24" s="10">
-        <v>52488658.529909022</v>
+        <v>57579834.233493693</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
@@ -6924,7 +6924,7 @@
         <v>67</v>
       </c>
       <c r="B25" s="10">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="C25" s="10">
         <v>3</v>
@@ -6933,13 +6933,13 @@
         <v>1</v>
       </c>
       <c r="E25" s="10">
-        <v>527</v>
+        <v>453</v>
       </c>
       <c r="F25" s="10">
-        <v>7489624.1028591068</v>
+        <v>8321119.8683109106</v>
       </c>
       <c r="G25" s="10">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="H25" s="10">
         <v>4</v>
@@ -6948,10 +6948,10 @@
         <v>1</v>
       </c>
       <c r="J25" s="10">
-        <v>901</v>
+        <v>501</v>
       </c>
       <c r="K25" s="10">
-        <v>8131500.9638309013</v>
+        <v>9053768.2708089184</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
@@ -6959,7 +6959,7 @@
         <v>74</v>
       </c>
       <c r="B26" s="10">
-        <v>1713</v>
+        <v>1705</v>
       </c>
       <c r="C26" s="10">
         <v>6</v>
@@ -6968,25 +6968,25 @@
         <v>1</v>
       </c>
       <c r="E26" s="10">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="F26" s="10">
-        <v>21050766.076841544</v>
+        <v>22879391.702904098</v>
       </c>
       <c r="G26" s="10">
-        <v>1729</v>
+        <v>1739</v>
       </c>
       <c r="H26" s="10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I26" s="10">
         <v>2</v>
       </c>
       <c r="J26" s="10">
-        <v>1375</v>
+        <v>1298</v>
       </c>
       <c r="K26" s="10">
-        <v>21530945.293318376</v>
+        <v>23681600.887948416</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
@@ -6994,7 +6994,7 @@
         <v>70</v>
       </c>
       <c r="B27" s="10">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C27" s="10">
         <v>4</v>
@@ -7003,25 +7003,25 @@
         <v>1</v>
       </c>
       <c r="E27" s="10">
-        <v>773</v>
+        <v>806</v>
       </c>
       <c r="F27" s="10">
-        <v>9392854.7496682443</v>
+        <v>10369757.486323014</v>
       </c>
       <c r="G27" s="10">
         <v>878</v>
       </c>
       <c r="H27" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I27" s="10">
         <v>1</v>
       </c>
       <c r="J27" s="10">
-        <v>755</v>
+        <v>740</v>
       </c>
       <c r="K27" s="10">
-        <v>8641800.9232224785</v>
+        <v>9476804.7699170522</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
@@ -7029,7 +7029,7 @@
         <v>72</v>
       </c>
       <c r="B28" s="10">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C28" s="10">
         <v>1</v>
@@ -7038,13 +7038,13 @@
         <v>1</v>
       </c>
       <c r="E28" s="10">
-        <v>756</v>
+        <v>671</v>
       </c>
       <c r="F28" s="10">
-        <v>9579970.5974776149</v>
+        <v>10593685.684289929</v>
       </c>
       <c r="G28" s="10">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H28" s="10">
         <v>5</v>
@@ -7053,10 +7053,10 @@
         <v>1</v>
       </c>
       <c r="J28" s="10">
-        <v>723</v>
+        <v>837</v>
       </c>
       <c r="K28" s="10">
-        <v>11009560.832062732</v>
+        <v>12126669.665737486</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
@@ -7064,7 +7064,7 @@
         <v>79</v>
       </c>
       <c r="B29" s="10">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C29" s="10">
         <v>1</v>
@@ -7073,13 +7073,13 @@
         <v>0</v>
       </c>
       <c r="E29" s="10">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F29" s="10">
-        <v>2855776.6463130671</v>
+        <v>3161051.6615617769</v>
       </c>
       <c r="G29" s="10">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H29" s="10">
         <v>1</v>
@@ -7088,10 +7088,10 @@
         <v>2</v>
       </c>
       <c r="J29" s="10">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="K29" s="10">
-        <v>2269431.611853485</v>
+        <v>2535906.26679195</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
@@ -7099,7 +7099,7 @@
         <v>109</v>
       </c>
       <c r="B30" s="10">
-        <v>1668</v>
+        <v>1672</v>
       </c>
       <c r="C30" s="10">
         <v>1</v>
@@ -7108,13 +7108,13 @@
         <v>5</v>
       </c>
       <c r="E30" s="10">
-        <v>1464</v>
+        <v>1411</v>
       </c>
       <c r="F30" s="10">
-        <v>24822617.942399263</v>
+        <v>26915593.394559879</v>
       </c>
       <c r="G30" s="10">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="H30" s="10">
         <v>9</v>
@@ -7123,10 +7123,10 @@
         <v>6</v>
       </c>
       <c r="J30" s="10">
-        <v>1347</v>
+        <v>1297</v>
       </c>
       <c r="K30" s="10">
-        <v>20667503.031828664</v>
+        <v>22506648.705730204</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
@@ -7134,7 +7134,7 @@
         <v>111</v>
       </c>
       <c r="B31" s="10">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="C31" s="10">
         <v>1</v>
@@ -7143,13 +7143,13 @@
         <v>1</v>
       </c>
       <c r="E31" s="10">
-        <v>606</v>
+        <v>725</v>
       </c>
       <c r="F31" s="10">
-        <v>15651652.677112721</v>
+        <v>17367448.012160983</v>
       </c>
       <c r="G31" s="10">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="H31" s="10">
         <v>1</v>
@@ -7158,10 +7158,10 @@
         <v>1</v>
       </c>
       <c r="J31" s="10">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="K31" s="10">
-        <v>16374105.086462455</v>
+        <v>18114098.002767928</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
@@ -7169,7 +7169,7 @@
         <v>113</v>
       </c>
       <c r="B32" s="10">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="C32" s="10">
         <v>0</v>
@@ -7178,25 +7178,25 @@
         <v>1</v>
       </c>
       <c r="E32" s="10">
-        <v>558</v>
+        <v>662</v>
       </c>
       <c r="F32" s="10">
-        <v>17399020.220064308</v>
+        <v>19051561.870875113</v>
       </c>
       <c r="G32" s="10">
         <v>1065</v>
       </c>
       <c r="H32" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I32" s="10">
         <v>1</v>
       </c>
       <c r="J32" s="10">
-        <v>836</v>
+        <v>827</v>
       </c>
       <c r="K32" s="10">
-        <v>16060768.424630741</v>
+        <v>17747943.348565217</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
@@ -7204,7 +7204,7 @@
         <v>115</v>
       </c>
       <c r="B33" s="10">
-        <v>1112</v>
+        <v>1119</v>
       </c>
       <c r="C33" s="10">
         <v>0</v>
@@ -7213,13 +7213,13 @@
         <v>3</v>
       </c>
       <c r="E33" s="10">
-        <v>1039</v>
+        <v>970</v>
       </c>
       <c r="F33" s="10">
-        <v>21903595.915449053</v>
+        <v>24407338.796157703</v>
       </c>
       <c r="G33" s="10">
-        <v>1109</v>
+        <v>1117</v>
       </c>
       <c r="H33" s="10">
         <v>2</v>
@@ -7228,10 +7228,10 @@
         <v>2</v>
       </c>
       <c r="J33" s="10">
-        <v>862</v>
+        <v>832</v>
       </c>
       <c r="K33" s="10">
-        <v>22045259.973748617</v>
+        <v>24181368.527279563</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
@@ -7239,7 +7239,7 @@
         <v>16</v>
       </c>
       <c r="B34" s="10">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="C34" s="10">
         <v>1</v>
@@ -7248,25 +7248,25 @@
         <v>5</v>
       </c>
       <c r="E34" s="10">
-        <v>1173</v>
+        <v>1121</v>
       </c>
       <c r="F34" s="10">
-        <v>33172620.572869904</v>
+        <v>36449833.351521991</v>
       </c>
       <c r="G34" s="10">
-        <v>1468</v>
+        <v>1459</v>
       </c>
       <c r="H34" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I34" s="10">
         <v>5</v>
       </c>
       <c r="J34" s="10">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="K34" s="10">
-        <v>31324284.763955772</v>
+        <v>34386413.695715845</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
@@ -7274,7 +7274,7 @@
         <v>18</v>
       </c>
       <c r="B35" s="10">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="C35" s="10">
         <v>0</v>
@@ -7283,10 +7283,10 @@
         <v>2</v>
       </c>
       <c r="E35" s="10">
-        <v>448</v>
+        <v>479</v>
       </c>
       <c r="F35" s="10">
-        <v>12052276.283295762</v>
+        <v>13310870.256587757</v>
       </c>
       <c r="G35" s="10">
         <v>679</v>
@@ -7298,10 +7298,10 @@
         <v>5</v>
       </c>
       <c r="J35" s="10">
-        <v>554</v>
+        <v>520</v>
       </c>
       <c r="K35" s="10">
-        <v>12818085.34321888</v>
+        <v>14130527.972239308</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
@@ -7309,7 +7309,7 @@
         <v>43</v>
       </c>
       <c r="B36" s="10">
-        <v>1967</v>
+        <v>1963</v>
       </c>
       <c r="C36" s="10">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         <v>10</v>
       </c>
       <c r="E36" s="10">
-        <v>1575</v>
+        <v>1549</v>
       </c>
       <c r="F36" s="10">
-        <v>38950361.986051217</v>
+        <v>42702953.094052374</v>
       </c>
       <c r="G36" s="10">
-        <v>1939</v>
+        <v>1943</v>
       </c>
       <c r="H36" s="10">
         <v>6</v>
@@ -7333,10 +7333,10 @@
         <v>11</v>
       </c>
       <c r="J36" s="10">
-        <v>1576</v>
+        <v>1571</v>
       </c>
       <c r="K36" s="10">
-        <v>39218450.568227202</v>
+        <v>42991561.47800532</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
@@ -7344,7 +7344,7 @@
         <v>152</v>
       </c>
       <c r="B37" s="10">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="C37" s="10">
         <v>2</v>
@@ -7353,13 +7353,13 @@
         <v>1</v>
       </c>
       <c r="E37" s="10">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="F37" s="10">
-        <v>13641140.097482843</v>
+        <v>14955957.56824052</v>
       </c>
       <c r="G37" s="10">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H37" s="10">
         <v>1</v>
@@ -7368,10 +7368,10 @@
         <v>2</v>
       </c>
       <c r="J37" s="10">
-        <v>747</v>
+        <v>887</v>
       </c>
       <c r="K37" s="10">
-        <v>12702349.062420461</v>
+        <v>14128877.58695925</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
@@ -7379,7 +7379,7 @@
         <v>149</v>
       </c>
       <c r="B38" s="10">
-        <v>698</v>
+        <v>689</v>
       </c>
       <c r="C38" s="10">
         <v>0</v>
@@ -7388,25 +7388,25 @@
         <v>1</v>
       </c>
       <c r="E38" s="10">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F38" s="10">
-        <v>11020053.945719752</v>
+        <v>11919577.193698112</v>
       </c>
       <c r="G38" s="10">
-        <v>734</v>
+        <v>745</v>
       </c>
       <c r="H38" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" s="10">
         <v>1</v>
       </c>
       <c r="J38" s="10">
-        <v>580</v>
+        <v>746</v>
       </c>
       <c r="K38" s="10">
-        <v>12313396.90175152</v>
+        <v>13624004.505409231</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
@@ -7414,22 +7414,22 @@
         <v>154</v>
       </c>
       <c r="B39" s="10">
-        <v>1113</v>
+        <v>1106</v>
       </c>
       <c r="C39" s="10">
         <v>6</v>
       </c>
       <c r="D39" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E39" s="10">
-        <v>815</v>
+        <v>861</v>
       </c>
       <c r="F39" s="10">
-        <v>19655782.859162141</v>
+        <v>21458136.24003084</v>
       </c>
       <c r="G39" s="10">
-        <v>1180</v>
+        <v>1164</v>
       </c>
       <c r="H39" s="10">
         <v>7</v>
@@ -7438,10 +7438,10 @@
         <v>1</v>
       </c>
       <c r="J39" s="10">
-        <v>793</v>
+        <v>465</v>
       </c>
       <c r="K39" s="10">
-        <v>19043186.757094968</v>
+        <v>20541227.171415836</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
@@ -7449,22 +7449,22 @@
         <v>2</v>
       </c>
       <c r="B40" s="10">
-        <v>1173</v>
+        <v>1154</v>
       </c>
       <c r="C40" s="10">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D40" s="10">
         <v>1</v>
       </c>
       <c r="E40" s="10">
-        <v>823</v>
+        <v>803</v>
       </c>
       <c r="F40" s="10">
-        <v>19180872.019964613</v>
+        <v>21107464.808607873</v>
       </c>
       <c r="G40" s="10">
-        <v>1351</v>
+        <v>1335</v>
       </c>
       <c r="H40" s="10">
         <v>120</v>
@@ -7473,10 +7473,10 @@
         <v>1</v>
       </c>
       <c r="J40" s="10">
-        <v>779</v>
+        <v>811</v>
       </c>
       <c r="K40" s="10">
-        <v>17431602.978954356</v>
+        <v>19115642.615416333</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
@@ -7484,22 +7484,22 @@
         <v>156</v>
       </c>
       <c r="B41" s="10">
-        <v>1834</v>
+        <v>1824</v>
       </c>
       <c r="C41" s="10">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D41" s="10">
         <v>4</v>
       </c>
       <c r="E41" s="10">
-        <v>1425</v>
+        <v>1392</v>
       </c>
       <c r="F41" s="10">
-        <v>29876677.049243852</v>
+        <v>32820003.555210747</v>
       </c>
       <c r="G41" s="10">
-        <v>2445</v>
+        <v>2418</v>
       </c>
       <c r="H41" s="10">
         <v>69</v>
@@ -7508,10 +7508,10 @@
         <v>5</v>
       </c>
       <c r="J41" s="10">
-        <v>1441</v>
+        <v>1575</v>
       </c>
       <c r="K41" s="10">
-        <v>31725346.660909802</v>
+        <v>34893533.726597093</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
@@ -7519,7 +7519,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="10">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C42" s="10">
         <v>2</v>
@@ -7528,25 +7528,25 @@
         <v>6</v>
       </c>
       <c r="E42" s="10">
-        <v>452</v>
+        <v>425</v>
       </c>
       <c r="F42" s="10">
-        <v>12462518.939564969</v>
+        <v>13698654.037510132</v>
       </c>
       <c r="G42" s="10">
         <v>621</v>
       </c>
       <c r="H42" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" s="10">
         <v>6</v>
       </c>
       <c r="J42" s="10">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="K42" s="10">
-        <v>11421939.055878559</v>
+        <v>12519238.361120775</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
@@ -7554,7 +7554,7 @@
         <v>8</v>
       </c>
       <c r="B43" s="10">
-        <v>1943</v>
+        <v>1969</v>
       </c>
       <c r="C43" s="10">
         <v>2</v>
@@ -7563,13 +7563,13 @@
         <v>6</v>
       </c>
       <c r="E43" s="10">
-        <v>2011</v>
+        <v>2038</v>
       </c>
       <c r="F43" s="10">
-        <v>34603754.857470505</v>
+        <v>38445948.814468734</v>
       </c>
       <c r="G43" s="10">
-        <v>2054</v>
+        <v>2064</v>
       </c>
       <c r="H43" s="10">
         <v>2</v>
@@ -7578,10 +7578,10 @@
         <v>6</v>
       </c>
       <c r="J43" s="10">
-        <v>1970</v>
+        <v>1950</v>
       </c>
       <c r="K43" s="10">
-        <v>38251004.015172802</v>
+        <v>41918196.556400456</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.35">
@@ -7589,19 +7589,19 @@
         <v>39</v>
       </c>
       <c r="B44" s="10">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="C44" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D44" s="10">
         <v>4</v>
       </c>
       <c r="E44" s="10">
-        <v>736</v>
+        <v>705</v>
       </c>
       <c r="F44" s="10">
-        <v>23998515.44422197</v>
+        <v>26462235.347880993</v>
       </c>
       <c r="G44" s="10">
         <v>900</v>
@@ -7613,10 +7613,10 @@
         <v>2</v>
       </c>
       <c r="J44" s="10">
-        <v>772</v>
+        <v>803</v>
       </c>
       <c r="K44" s="10">
-        <v>24688120.726337377</v>
+        <v>27157435.659359276</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.35">
@@ -7624,7 +7624,7 @@
         <v>6</v>
       </c>
       <c r="B45" s="10">
-        <v>1143</v>
+        <v>1153</v>
       </c>
       <c r="C45" s="10">
         <v>0</v>
@@ -7633,13 +7633,13 @@
         <v>3</v>
       </c>
       <c r="E45" s="10">
-        <v>909</v>
+        <v>903</v>
       </c>
       <c r="F45" s="10">
-        <v>21126962.544779114</v>
+        <v>22902447.746424876</v>
       </c>
       <c r="G45" s="10">
-        <v>1088</v>
+        <v>1082</v>
       </c>
       <c r="H45" s="10">
         <v>0</v>
@@ -7648,10 +7648,10 @@
         <v>3</v>
       </c>
       <c r="J45" s="10">
-        <v>936</v>
+        <v>919</v>
       </c>
       <c r="K45" s="10">
-        <v>12296140.818591988</v>
+        <v>14174402.098842507</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
@@ -7659,7 +7659,7 @@
         <v>41</v>
       </c>
       <c r="B46" s="10">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="C46" s="10">
         <v>0</v>
@@ -7668,13 +7668,13 @@
         <v>5</v>
       </c>
       <c r="E46" s="10">
-        <v>615</v>
+        <v>595</v>
       </c>
       <c r="F46" s="10">
-        <v>20292399.117647201</v>
+        <v>22203549.116332825</v>
       </c>
       <c r="G46" s="10">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="H46" s="10">
         <v>3</v>
@@ -7683,10 +7683,10 @@
         <v>4</v>
       </c>
       <c r="J46" s="10">
-        <v>668</v>
+        <v>651</v>
       </c>
       <c r="K46" s="10">
-        <v>19732293.398156039</v>
+        <v>21668424.355895929</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.35">
@@ -7694,22 +7694,22 @@
         <v>158</v>
       </c>
       <c r="B47" s="10">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="C47" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D47" s="10">
         <v>10</v>
       </c>
       <c r="E47" s="10">
-        <v>655</v>
+        <v>761</v>
       </c>
       <c r="F47" s="10">
-        <v>11675592.217419149</v>
+        <v>13229112.238779062</v>
       </c>
       <c r="G47" s="10">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="H47" s="10">
         <v>2</v>
@@ -7718,10 +7718,10 @@
         <v>10</v>
       </c>
       <c r="J47" s="10">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="K47" s="10">
-        <v>12617432.245743323</v>
+        <v>13892344.82190132</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.35">
@@ -7729,7 +7729,7 @@
         <v>160</v>
       </c>
       <c r="B48" s="10">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C48" s="10">
         <v>1</v>
@@ -7738,13 +7738,13 @@
         <v>1</v>
       </c>
       <c r="E48" s="10">
-        <v>711</v>
+        <v>729</v>
       </c>
       <c r="F48" s="10">
-        <v>11469697.687318595</v>
+        <v>12706768.574557343</v>
       </c>
       <c r="G48" s="10">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="H48" s="10">
         <v>0</v>
@@ -7753,10 +7753,10 @@
         <v>2</v>
       </c>
       <c r="J48" s="10">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="K48" s="10">
-        <v>10927877.013120186</v>
+        <v>12158153.26136156</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
@@ -7764,22 +7764,22 @@
         <v>83</v>
       </c>
       <c r="B49" s="10">
-        <v>1281</v>
+        <v>1285</v>
       </c>
       <c r="C49" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D49" s="10">
         <v>6</v>
       </c>
       <c r="E49" s="10">
-        <v>1068</v>
+        <v>1120</v>
       </c>
       <c r="F49" s="10">
-        <v>39658020.754120097</v>
+        <v>43323385.421304703</v>
       </c>
       <c r="G49" s="10">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="H49" s="10">
         <v>0</v>
@@ -7788,10 +7788,10 @@
         <v>4</v>
       </c>
       <c r="J49" s="10">
-        <v>1072</v>
+        <v>1078</v>
       </c>
       <c r="K49" s="10">
-        <v>33970655.650308527</v>
+        <v>37265260.436432607</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
@@ -7799,7 +7799,7 @@
         <v>202</v>
       </c>
       <c r="B50" s="10">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C50" s="10">
         <v>0</v>
@@ -7808,13 +7808,13 @@
         <v>2</v>
       </c>
       <c r="E50" s="10">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="F50" s="10">
-        <v>6956384.4550691703</v>
+        <v>7674705.4629659308</v>
       </c>
       <c r="G50" s="10">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="H50" s="10">
         <v>0</v>
@@ -7823,10 +7823,10 @@
         <v>1</v>
       </c>
       <c r="J50" s="10">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="K50" s="10">
-        <v>5665017.8500306131</v>
+        <v>6161407.6858986113</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
@@ -7834,7 +7834,7 @@
         <v>31</v>
       </c>
       <c r="B51" s="10">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="C51" s="10">
         <v>0</v>
@@ -7843,13 +7843,13 @@
         <v>4</v>
       </c>
       <c r="E51" s="10">
-        <v>906</v>
+        <v>968</v>
       </c>
       <c r="F51" s="10">
-        <v>17566001.730502713</v>
+        <v>19117456.997472573</v>
       </c>
       <c r="G51" s="10">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="H51" s="10">
         <v>2</v>
@@ -7858,10 +7858,10 @@
         <v>7</v>
       </c>
       <c r="J51" s="10">
-        <v>923</v>
+        <v>881</v>
       </c>
       <c r="K51" s="10">
-        <v>16286567.597074073</v>
+        <v>17869965.656653393</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
@@ -7869,7 +7869,7 @@
         <v>33</v>
       </c>
       <c r="B52" s="10">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="C52" s="10">
         <v>4</v>
@@ -7878,13 +7878,13 @@
         <v>12</v>
       </c>
       <c r="E52" s="10">
-        <v>959</v>
+        <v>939</v>
       </c>
       <c r="F52" s="10">
-        <v>23215427.489808504</v>
+        <v>25734348.457785707</v>
       </c>
       <c r="G52" s="10">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="H52" s="10">
         <v>3</v>
@@ -7893,10 +7893,10 @@
         <v>12</v>
       </c>
       <c r="J52" s="10">
-        <v>1017</v>
+        <v>1045</v>
       </c>
       <c r="K52" s="10">
-        <v>29152507.694931164</v>
+        <v>32049677.103434991</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.35">
@@ -7904,7 +7904,7 @@
         <v>85</v>
       </c>
       <c r="B53" s="10">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C53" s="10">
         <v>0</v>
@@ -7913,10 +7913,10 @@
         <v>5</v>
       </c>
       <c r="E53" s="10">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="F53" s="10">
-        <v>12332994.762099404</v>
+        <v>13719210.446378822</v>
       </c>
       <c r="G53" s="10">
         <v>483</v>
@@ -7928,10 +7928,10 @@
         <v>6</v>
       </c>
       <c r="J53" s="10">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="K53" s="10">
-        <v>15040340.008889956</v>
+        <v>16535390.401304321</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.35">
@@ -7939,7 +7939,7 @@
         <v>81</v>
       </c>
       <c r="B54" s="10">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C54" s="10">
         <v>0</v>
@@ -7948,10 +7948,10 @@
         <v>7</v>
       </c>
       <c r="E54" s="10">
-        <v>322</v>
+        <v>292</v>
       </c>
       <c r="F54" s="10">
-        <v>14070540.257583896</v>
+        <v>15256433.802802257</v>
       </c>
       <c r="G54" s="10">
         <v>456</v>
@@ -7963,10 +7963,10 @@
         <v>4</v>
       </c>
       <c r="J54" s="10">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="K54" s="10">
-        <v>11090723.62741236</v>
+        <v>12078370.394055249</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.35">
@@ -7974,7 +7974,7 @@
         <v>87</v>
       </c>
       <c r="B55" s="10">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C55" s="10">
         <v>9</v>
@@ -7983,13 +7983,13 @@
         <v>2</v>
       </c>
       <c r="E55" s="10">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="F55" s="10">
-        <v>10956552.874769645</v>
+        <v>12039200.120742671</v>
       </c>
       <c r="G55" s="10">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H55" s="10">
         <v>1</v>
@@ -7998,10 +7998,10 @@
         <v>4</v>
       </c>
       <c r="J55" s="10">
-        <v>2787</v>
+        <v>332</v>
       </c>
       <c r="K55" s="10">
-        <v>9670437.9324168526</v>
+        <v>10518219.170153208</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.35">
@@ -8009,22 +8009,22 @@
         <v>166</v>
       </c>
       <c r="B56" s="10">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="C56" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56" s="10">
         <v>1</v>
       </c>
       <c r="E56" s="10">
-        <v>958</v>
+        <v>935</v>
       </c>
       <c r="F56" s="10">
-        <v>24000525.631255325</v>
+        <v>26234347.209597055</v>
       </c>
       <c r="G56" s="10">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="H56" s="10">
         <v>2</v>
@@ -8033,10 +8033,10 @@
         <v>0</v>
       </c>
       <c r="J56" s="10">
-        <v>964</v>
+        <v>925</v>
       </c>
       <c r="K56" s="10">
-        <v>22657317.560193349</v>
+        <v>24717928.535999633</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
@@ -8044,34 +8044,34 @@
         <v>93</v>
       </c>
       <c r="B57" s="10">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="C57" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D57" s="10">
         <v>3</v>
       </c>
       <c r="E57" s="10">
-        <v>989</v>
+        <v>1150</v>
       </c>
       <c r="F57" s="10">
-        <v>24952414.545414973</v>
+        <v>27600521.52657304</v>
       </c>
       <c r="G57" s="10">
-        <v>982</v>
+        <v>995</v>
       </c>
       <c r="H57" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I57" s="10">
         <v>1</v>
       </c>
       <c r="J57" s="10">
-        <v>937</v>
+        <v>889</v>
       </c>
       <c r="K57" s="10">
-        <v>20747156.830999862</v>
+        <v>23324427.700908128</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.35">
@@ -8079,7 +8079,7 @@
         <v>95</v>
       </c>
       <c r="B58" s="10">
-        <v>2236</v>
+        <v>2223</v>
       </c>
       <c r="C58" s="10">
         <v>31</v>
@@ -8088,13 +8088,13 @@
         <v>7</v>
       </c>
       <c r="E58" s="10">
-        <v>1476</v>
+        <v>1251</v>
       </c>
       <c r="F58" s="10">
-        <v>32989159.026679937</v>
+        <v>35787847.640754372</v>
       </c>
       <c r="G58" s="10">
-        <v>2068</v>
+        <v>2076</v>
       </c>
       <c r="H58" s="10">
         <v>6</v>
@@ -8103,10 +8103,10 @@
         <v>8</v>
       </c>
       <c r="J58" s="10">
-        <v>1639</v>
+        <v>1445</v>
       </c>
       <c r="K58" s="10">
-        <v>42923506.72697591</v>
+        <v>46682576.652989939</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.35">
@@ -8123,25 +8123,25 @@
         <v>0</v>
       </c>
       <c r="E59" s="10">
-        <v>580</v>
+        <v>547</v>
       </c>
       <c r="F59" s="10">
-        <v>11837990.619278032</v>
+        <v>12957556.739625184</v>
       </c>
       <c r="G59" s="10">
         <v>682</v>
       </c>
       <c r="H59" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I59" s="10">
         <v>0</v>
       </c>
       <c r="J59" s="10">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="K59" s="10">
-        <v>10041405.614067961</v>
+        <v>11099238.69559554</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.35">
@@ -8149,7 +8149,7 @@
         <v>99</v>
       </c>
       <c r="B60" s="10">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C60" s="10">
         <v>2</v>
@@ -8158,13 +8158,13 @@
         <v>5</v>
       </c>
       <c r="E60" s="10">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="F60" s="10">
-        <v>17085232.849608403</v>
+        <v>18801809.362829365</v>
       </c>
       <c r="G60" s="10">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="H60" s="10">
         <v>4</v>
@@ -8173,10 +8173,10 @@
         <v>5</v>
       </c>
       <c r="J60" s="10">
-        <v>733</v>
+        <v>695</v>
       </c>
       <c r="K60" s="10">
-        <v>17707083.120192073</v>
+        <v>19739544.691658638</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.35">
@@ -8184,22 +8184,22 @@
         <v>172</v>
       </c>
       <c r="B61" s="10">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C61" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D61" s="10">
         <v>1</v>
       </c>
       <c r="E61" s="10">
-        <v>686</v>
+        <v>665</v>
       </c>
       <c r="F61" s="10">
-        <v>14228080.103506284</v>
+        <v>15612754.366214955</v>
       </c>
       <c r="G61" s="10">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="H61" s="10">
         <v>3</v>
@@ -8208,10 +8208,10 @@
         <v>1</v>
       </c>
       <c r="J61" s="10">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="K61" s="10">
-        <v>10974111.643722907</v>
+        <v>12105700.997142749</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.35">
@@ -8228,13 +8228,13 @@
         <v>1</v>
       </c>
       <c r="E62" s="10">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="F62" s="10">
-        <v>23707410.117147829</v>
+        <v>26124638.488840576</v>
       </c>
       <c r="G62" s="10">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="H62" s="10">
         <v>5</v>
@@ -8243,10 +8243,10 @@
         <v>0</v>
       </c>
       <c r="J62" s="10">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="K62" s="10">
-        <v>23768120.633329134</v>
+        <v>25947240.738314714</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.35">
@@ -8254,7 +8254,7 @@
         <v>101</v>
       </c>
       <c r="B63" s="10">
-        <v>1334</v>
+        <v>1337</v>
       </c>
       <c r="C63" s="10">
         <v>5</v>
@@ -8263,25 +8263,25 @@
         <v>4</v>
       </c>
       <c r="E63" s="10">
-        <v>1443</v>
+        <v>1352</v>
       </c>
       <c r="F63" s="10">
-        <v>29468066.465633627</v>
+        <v>32375875.294686958</v>
       </c>
       <c r="G63" s="10">
-        <v>1408</v>
+        <v>1425</v>
       </c>
       <c r="H63" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I63" s="10">
         <v>4</v>
       </c>
       <c r="J63" s="10">
-        <v>1477</v>
+        <v>1510</v>
       </c>
       <c r="K63" s="10">
-        <v>28107742.326862235</v>
+        <v>31385541.692812439</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.35">
@@ -8289,7 +8289,7 @@
         <v>103</v>
       </c>
       <c r="B64" s="10">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C64" s="10">
         <v>4</v>
@@ -8298,13 +8298,13 @@
         <v>5</v>
       </c>
       <c r="E64" s="10">
-        <v>696</v>
+        <v>740</v>
       </c>
       <c r="F64" s="10">
-        <v>15494292.208695738</v>
+        <v>16921073.286912169</v>
       </c>
       <c r="G64" s="10">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="H64" s="10">
         <v>1</v>
@@ -8313,10 +8313,10 @@
         <v>4</v>
       </c>
       <c r="J64" s="10">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="K64" s="10">
-        <v>15929363.198218364</v>
+        <v>17447941.078375421</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.35">
@@ -8324,7 +8324,7 @@
         <v>105</v>
       </c>
       <c r="B65" s="10">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="C65" s="10">
         <v>3</v>
@@ -8333,25 +8333,25 @@
         <v>5</v>
       </c>
       <c r="E65" s="10">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="F65" s="10">
-        <v>18091176.906567469</v>
+        <v>19757041.776899666</v>
       </c>
       <c r="G65" s="10">
         <v>651</v>
       </c>
       <c r="H65" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I65" s="10">
         <v>5</v>
       </c>
       <c r="J65" s="10">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="K65" s="10">
-        <v>17644632.482370876</v>
+        <v>19448677.858427402</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.35">
@@ -8359,34 +8359,34 @@
         <v>24</v>
       </c>
       <c r="B66" s="10">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="C66" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D66" s="10">
         <v>9</v>
       </c>
       <c r="E66" s="10">
-        <v>1603</v>
+        <v>1572</v>
       </c>
       <c r="F66" s="10">
-        <v>42190631.543374673</v>
+        <v>47114478.212284766</v>
       </c>
       <c r="G66" s="10">
-        <v>1996</v>
+        <v>1970</v>
       </c>
       <c r="H66" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I66" s="10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J66" s="10">
-        <v>1688</v>
+        <v>1606</v>
       </c>
       <c r="K66" s="10">
-        <v>56820046.060979337</v>
+        <v>62697973.94385463</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.35">
@@ -8394,7 +8394,7 @@
         <v>27</v>
       </c>
       <c r="B67" s="10">
-        <v>1629</v>
+        <v>1624</v>
       </c>
       <c r="C67" s="10">
         <v>14</v>
@@ -8403,25 +8403,25 @@
         <v>8</v>
       </c>
       <c r="E67" s="10">
-        <v>1104</v>
+        <v>1081</v>
       </c>
       <c r="F67" s="10">
-        <v>42052983.529155493</v>
+        <v>46229977.312252909</v>
       </c>
       <c r="G67" s="10">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="H67" s="10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I67" s="10">
         <v>6</v>
       </c>
       <c r="J67" s="10">
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="K67" s="10">
-        <v>40496738.011696391</v>
+        <v>45449660.687625058</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.35">
@@ -8429,7 +8429,7 @@
         <v>29</v>
       </c>
       <c r="B68" s="10">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="C68" s="10">
         <v>2</v>
@@ -8438,13 +8438,13 @@
         <v>1</v>
       </c>
       <c r="E68" s="10">
-        <v>782</v>
+        <v>688</v>
       </c>
       <c r="F68" s="10">
-        <v>27220648.034163546</v>
+        <v>29968181.395187031</v>
       </c>
       <c r="G68" s="10">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="H68" s="10">
         <v>3</v>
@@ -8453,10 +8453,10 @@
         <v>1</v>
       </c>
       <c r="J68" s="10">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="K68" s="10">
-        <v>27163402.734975632</v>
+        <v>30160380.248123996</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.35">
@@ -8464,34 +8464,34 @@
         <v>57</v>
       </c>
       <c r="B69" s="10">
-        <v>1867</v>
+        <v>1862</v>
       </c>
       <c r="C69" s="10">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D69" s="10">
         <v>13</v>
       </c>
       <c r="E69" s="10">
-        <v>1402</v>
+        <v>1274</v>
       </c>
       <c r="F69" s="10">
-        <v>38559981.787422098</v>
+        <v>42307324.288243957</v>
       </c>
       <c r="G69" s="10">
-        <v>2149</v>
+        <v>2335</v>
       </c>
       <c r="H69" s="10">
-        <v>163</v>
+        <v>366</v>
       </c>
       <c r="I69" s="10">
         <v>12</v>
       </c>
       <c r="J69" s="10">
-        <v>1396</v>
+        <v>1437</v>
       </c>
       <c r="K69" s="10">
-        <v>41192471.998564802</v>
+        <v>45476168.730734654</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.35">
@@ -8499,34 +8499,34 @@
         <v>137</v>
       </c>
       <c r="B70" s="10">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C70" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D70" s="10">
         <v>1</v>
       </c>
       <c r="E70" s="10">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="F70" s="10">
-        <v>2942421.1271584849</v>
+        <v>3303333.5893165562</v>
       </c>
       <c r="G70" s="10">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="H70" s="10">
         <v>0</v>
       </c>
       <c r="I70" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" s="10">
-        <v>265</v>
+        <v>415</v>
       </c>
       <c r="K70" s="10">
-        <v>866549.93732182099</v>
+        <v>1088246.2504583341</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.35">
@@ -8543,25 +8543,25 @@
         <v>7</v>
       </c>
       <c r="E71" s="10">
-        <v>1605</v>
+        <v>1626</v>
       </c>
       <c r="F71" s="10">
-        <v>30974184.927460741</v>
+        <v>33805872.393411718</v>
       </c>
       <c r="G71" s="10">
-        <v>1667</v>
+        <v>1674</v>
       </c>
       <c r="H71" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I71" s="10">
         <v>6</v>
       </c>
       <c r="J71" s="10">
-        <v>1574</v>
+        <v>1542</v>
       </c>
       <c r="K71" s="10">
-        <v>29595379.829328042</v>
+        <v>32336066.762660287</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.35">
@@ -8569,7 +8569,7 @@
         <v>12</v>
       </c>
       <c r="B72" s="10">
-        <v>652</v>
+        <v>666</v>
       </c>
       <c r="C72" s="10">
         <v>1</v>
@@ -8578,13 +8578,13 @@
         <v>2</v>
       </c>
       <c r="E72" s="10">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="F72" s="10">
-        <v>12270964.333252013</v>
+        <v>13264992.414578712</v>
       </c>
       <c r="G72" s="10">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="H72" s="10">
         <v>1</v>
@@ -8593,10 +8593,10 @@
         <v>3</v>
       </c>
       <c r="J72" s="10">
-        <v>600</v>
+        <v>614</v>
       </c>
       <c r="K72" s="10">
-        <v>13885953.953792712</v>
+        <v>15325394.688526897</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.35">
@@ -8604,7 +8604,7 @@
         <v>162</v>
       </c>
       <c r="B73" s="10">
-        <v>1349</v>
+        <v>1342</v>
       </c>
       <c r="C73" s="10">
         <v>21</v>
@@ -8613,13 +8613,13 @@
         <v>5</v>
       </c>
       <c r="E73" s="10">
-        <v>941</v>
+        <v>971</v>
       </c>
       <c r="F73" s="10">
-        <v>20714455.23746011</v>
+        <v>22548489.861411422</v>
       </c>
       <c r="G73" s="10">
-        <v>1359</v>
+        <v>1369</v>
       </c>
       <c r="H73" s="10">
         <v>19</v>
@@ -8628,10 +8628,10 @@
         <v>4</v>
       </c>
       <c r="J73" s="10">
-        <v>892</v>
+        <v>859</v>
       </c>
       <c r="K73" s="10">
-        <v>19791464.354459144</v>
+        <v>21867582.03235082</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.35">
@@ -8639,22 +8639,22 @@
         <v>63</v>
       </c>
       <c r="B74" s="10">
-        <v>1402</v>
+        <v>1396</v>
       </c>
       <c r="C74" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D74" s="10">
         <v>5</v>
       </c>
       <c r="E74" s="10">
-        <v>1685</v>
+        <v>1380</v>
       </c>
       <c r="F74" s="10">
-        <v>11194059.658313934</v>
+        <v>12696820.613842988</v>
       </c>
       <c r="G74" s="10">
-        <v>1294</v>
+        <v>1287</v>
       </c>
       <c r="H74" s="10">
         <v>1</v>
@@ -8663,10 +8663,10 @@
         <v>5</v>
       </c>
       <c r="J74" s="10">
-        <v>1220</v>
+        <v>597</v>
       </c>
       <c r="K74" s="10">
-        <v>13965270.135004491</v>
+        <v>14511263.008932166</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.35">
@@ -8674,34 +8674,34 @@
         <v>59</v>
       </c>
       <c r="B75" s="10">
-        <v>1742</v>
+        <v>1745</v>
       </c>
       <c r="C75" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D75" s="10">
         <v>5</v>
       </c>
       <c r="E75" s="10">
-        <v>1232</v>
+        <v>1488</v>
       </c>
       <c r="F75" s="10">
-        <v>35080672.915383458</v>
+        <v>38688418.739473499</v>
       </c>
       <c r="G75" s="10">
-        <v>1731</v>
+        <v>1737</v>
       </c>
       <c r="H75" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I75" s="10">
         <v>4</v>
       </c>
       <c r="J75" s="10">
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="K75" s="10">
-        <v>36289796.525273778</v>
+        <v>39831462.257459968</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.35">
@@ -8709,7 +8709,7 @@
         <v>139</v>
       </c>
       <c r="B76" s="10">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="C76" s="10">
         <v>2</v>
@@ -8718,10 +8718,10 @@
         <v>2</v>
       </c>
       <c r="E76" s="10">
-        <v>591</v>
+        <v>514</v>
       </c>
       <c r="F76" s="10">
-        <v>7880801.5686250767</v>
+        <v>8715480.3903808221</v>
       </c>
       <c r="G76" s="10">
         <v>517</v>
@@ -8733,10 +8733,10 @@
         <v>1</v>
       </c>
       <c r="J76" s="10">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="K76" s="10">
-        <v>7436736.8711797697</v>
+        <v>8057116.8412494138</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.35">
@@ -8744,7 +8744,7 @@
         <v>170</v>
       </c>
       <c r="B77" s="10">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="C77" s="10">
         <v>1</v>
@@ -8753,10 +8753,10 @@
         <v>1</v>
       </c>
       <c r="E77" s="10">
-        <v>873</v>
+        <v>845</v>
       </c>
       <c r="F77" s="10">
-        <v>12327433.580337113</v>
+        <v>13545098.441002436</v>
       </c>
       <c r="G77" s="10">
         <v>890</v>
@@ -8768,10 +8768,10 @@
         <v>1</v>
       </c>
       <c r="J77" s="10">
-        <v>794</v>
+        <v>999</v>
       </c>
       <c r="K77" s="10">
-        <v>11372239.052546794</v>
+        <v>12597475.045724921</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.35">
@@ -8782,19 +8782,19 @@
         <v>688</v>
       </c>
       <c r="C78" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D78" s="10">
         <v>4</v>
       </c>
       <c r="E78" s="10">
-        <v>518</v>
+        <v>431</v>
       </c>
       <c r="F78" s="10">
-        <v>7675922.5408083284</v>
+        <v>8794172.8037036434</v>
       </c>
       <c r="G78" s="10">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="H78" s="10">
         <v>0</v>
@@ -8803,10 +8803,10 @@
         <v>3</v>
       </c>
       <c r="J78" s="10">
-        <v>460</v>
+        <v>493</v>
       </c>
       <c r="K78" s="10">
-        <v>11027043.533425763</v>
+        <v>12245132.80994164</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.35">
@@ -8814,7 +8814,7 @@
         <v>129</v>
       </c>
       <c r="B79" s="10">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="C79" s="10">
         <v>3</v>
@@ -8823,13 +8823,13 @@
         <v>1</v>
       </c>
       <c r="E79" s="10">
-        <v>764</v>
+        <v>709</v>
       </c>
       <c r="F79" s="10">
-        <v>8168937.7104559364</v>
+        <v>8938535.046445122</v>
       </c>
       <c r="G79" s="10">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="H79" s="10">
         <v>5</v>
@@ -8838,10 +8838,10 @@
         <v>1</v>
       </c>
       <c r="J79" s="10">
-        <v>719</v>
+        <v>732</v>
       </c>
       <c r="K79" s="10">
-        <v>9440020.5816278141</v>
+        <v>10277085.972706931</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.35">
@@ -8852,19 +8852,19 @@
         <v>443</v>
       </c>
       <c r="C80" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D80" s="10">
         <v>5</v>
       </c>
       <c r="E80" s="10">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="F80" s="10">
-        <v>9324331.1601992901</v>
+        <v>10267447.870031901</v>
       </c>
       <c r="G80" s="10">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="H80" s="10">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>7</v>
       </c>
       <c r="J80" s="10">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="K80" s="10">
-        <v>10312525.498841934</v>
+        <v>11211811.326490723</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.35">
@@ -8884,7 +8884,7 @@
         <v>107</v>
       </c>
       <c r="B81" s="10">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="C81" s="10">
         <v>1</v>
@@ -8893,13 +8893,13 @@
         <v>4</v>
       </c>
       <c r="E81" s="10">
-        <v>858</v>
+        <v>756</v>
       </c>
       <c r="F81" s="10">
-        <v>26416851.045317288</v>
+        <v>28811381.822914738</v>
       </c>
       <c r="G81" s="10">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="H81" s="10">
         <v>4</v>
@@ -8908,10 +8908,10 @@
         <v>3</v>
       </c>
       <c r="J81" s="10">
-        <v>771</v>
+        <v>755</v>
       </c>
       <c r="K81" s="10">
-        <v>26078957.954257365</v>
+        <v>29014112.452576768</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.35">
@@ -8919,19 +8919,19 @@
         <v>37</v>
       </c>
       <c r="B82" s="10">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C82" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D82" s="10">
         <v>9</v>
       </c>
       <c r="E82" s="10">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="F82" s="10">
-        <v>16071643.609950272</v>
+        <v>17376373.350340452</v>
       </c>
       <c r="G82" s="10">
         <v>772</v>
@@ -8943,10 +8943,10 @@
         <v>10</v>
       </c>
       <c r="J82" s="10">
-        <v>730</v>
+        <v>721</v>
       </c>
       <c r="K82" s="10">
-        <v>16027104.838134946</v>
+        <v>17505873.817607421</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.35">
@@ -8954,7 +8954,7 @@
         <v>76</v>
       </c>
       <c r="B83" s="10">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="C83" s="10">
         <v>0</v>
@@ -8963,13 +8963,13 @@
         <v>2</v>
       </c>
       <c r="E83" s="10">
-        <v>813</v>
+        <v>879</v>
       </c>
       <c r="F83" s="10">
-        <v>12913446.391234845</v>
+        <v>14290245.398241306</v>
       </c>
       <c r="G83" s="10">
-        <v>971</v>
+        <v>964</v>
       </c>
       <c r="H83" s="10">
         <v>1</v>
@@ -8978,10 +8978,10 @@
         <v>2</v>
       </c>
       <c r="J83" s="10">
-        <v>134</v>
+        <v>791</v>
       </c>
       <c r="K83" s="10">
-        <v>13467808.102383876</v>
+        <v>14020057.900462007</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.35">
@@ -8989,7 +8989,7 @@
         <v>65</v>
       </c>
       <c r="B84" s="10">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="C84" s="10">
         <v>4</v>
@@ -8998,13 +8998,13 @@
         <v>4</v>
       </c>
       <c r="E84" s="10">
-        <v>821</v>
+        <v>812</v>
       </c>
       <c r="F84" s="10">
-        <v>15027790.131356351</v>
+        <v>16556444.499608569</v>
       </c>
       <c r="G84" s="10">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="H84" s="10">
         <v>1</v>
@@ -9013,10 +9013,10 @@
         <v>5</v>
       </c>
       <c r="J84" s="10">
-        <v>1081</v>
+        <v>891</v>
       </c>
       <c r="K84" s="10">
-        <v>11427700.005160464</v>
+        <v>13094329.610911908</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.35">
@@ -9024,7 +9024,7 @@
         <v>89</v>
       </c>
       <c r="B85" s="10">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="C85" s="10">
         <v>2</v>
@@ -9033,13 +9033,13 @@
         <v>5</v>
       </c>
       <c r="E85" s="10">
-        <v>671</v>
+        <v>704</v>
       </c>
       <c r="F85" s="10">
-        <v>15080277.199489065</v>
+        <v>16880084.510550667</v>
       </c>
       <c r="G85" s="10">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="H85" s="10">
         <v>2</v>
@@ -9048,10 +9048,10 @@
         <v>6</v>
       </c>
       <c r="J85" s="10">
-        <v>794</v>
+        <v>749</v>
       </c>
       <c r="K85" s="10">
-        <v>16388269.707009552</v>
+        <v>18305554.193984501</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.35">
@@ -9059,7 +9059,7 @@
         <v>147</v>
       </c>
       <c r="B86" s="10">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C86" s="10">
         <v>1</v>
@@ -9068,13 +9068,13 @@
         <v>1</v>
       </c>
       <c r="E86" s="10">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="F86" s="10">
-        <v>7537594.2901824489</v>
+        <v>8199813.1471998431</v>
       </c>
       <c r="G86" s="10">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="H86" s="10">
         <v>1</v>
@@ -9083,10 +9083,10 @@
         <v>1</v>
       </c>
       <c r="J86" s="10">
-        <v>582</v>
+        <v>540</v>
       </c>
       <c r="K86" s="10">
-        <v>7936306.0676140552</v>
+        <v>8668989.4204564169</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.35">
@@ -9094,7 +9094,7 @@
         <v>164</v>
       </c>
       <c r="B87" s="10">
-        <v>1718</v>
+        <v>1715</v>
       </c>
       <c r="C87" s="10">
         <v>5</v>
@@ -9103,13 +9103,13 @@
         <v>10</v>
       </c>
       <c r="E87" s="10">
-        <v>1295</v>
+        <v>1251</v>
       </c>
       <c r="F87" s="10">
-        <v>28907365.834728513</v>
+        <v>32144265.812579334</v>
       </c>
       <c r="G87" s="10">
-        <v>1752</v>
+        <v>1754</v>
       </c>
       <c r="H87" s="10">
         <v>0</v>
@@ -9118,10 +9118,10 @@
         <v>10</v>
       </c>
       <c r="J87" s="10">
-        <v>1311</v>
+        <v>1290</v>
       </c>
       <c r="K87" s="10">
-        <v>31990138.886422463</v>
+        <v>35301547.313618742</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.35">
@@ -9129,7 +9129,7 @@
         <v>91</v>
       </c>
       <c r="B88" s="10">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="C88" s="10">
         <v>3</v>
@@ -9138,13 +9138,13 @@
         <v>3</v>
       </c>
       <c r="E88" s="10">
-        <v>667</v>
+        <v>937</v>
       </c>
       <c r="F88" s="10">
-        <v>7812991.3725561891</v>
+        <v>9037128.4041979909</v>
       </c>
       <c r="G88" s="10">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="H88" s="10">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>3</v>
       </c>
       <c r="J88" s="10">
-        <v>679</v>
+        <v>872</v>
       </c>
       <c r="K88" s="10">
-        <v>6516778.8492811872</v>
+        <v>7537881.091569989</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.35">
@@ -9164,7 +9164,7 @@
         <v>97</v>
       </c>
       <c r="B89" s="10">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C89" s="10">
         <v>10</v>
@@ -9173,13 +9173,13 @@
         <v>6</v>
       </c>
       <c r="E89" s="10">
-        <v>593</v>
+        <v>570</v>
       </c>
       <c r="F89" s="10">
-        <v>14412259.778720619</v>
+        <v>15900425.501327815</v>
       </c>
       <c r="G89" s="10">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="H89" s="10">
         <v>4</v>
@@ -9188,10 +9188,10 @@
         <v>7</v>
       </c>
       <c r="J89" s="10">
-        <v>555</v>
+        <v>580</v>
       </c>
       <c r="K89" s="10">
-        <v>15070172.236953417</v>
+        <v>16485262.08125736</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.35">
@@ -9199,7 +9199,7 @@
         <v>78</v>
       </c>
       <c r="B90" s="10">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C90" s="10">
         <v>1</v>
@@ -9208,13 +9208,13 @@
         <v>1</v>
       </c>
       <c r="E90" s="10">
-        <v>334</v>
+        <v>313</v>
       </c>
       <c r="F90" s="10">
-        <v>4236420.8188401982</v>
+        <v>4623806.3159846626</v>
       </c>
       <c r="G90" s="10">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="H90" s="10">
         <v>2</v>
@@ -9223,10 +9223,10 @@
         <v>0</v>
       </c>
       <c r="J90" s="10">
-        <v>338</v>
+        <v>309</v>
       </c>
       <c r="K90" s="10">
-        <v>3753216.5787746692</v>
+        <v>4055469.882370349</v>
       </c>
     </row>
   </sheetData>

--- a/SITE MONITORING.xlsx
+++ b/SITE MONITORING.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
@@ -1873,7 +1873,7 @@
         <v>1430</v>
       </c>
       <c r="P14">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
@@ -1993,7 +1993,7 @@
         <v>1030</v>
       </c>
       <c r="P16">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.35">
@@ -2353,7 +2353,7 @@
         <v>1739</v>
       </c>
       <c r="P22">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
@@ -2713,7 +2713,7 @@
         <v>1065</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.35">
@@ -3733,7 +3733,7 @@
         <v>1242</v>
       </c>
       <c r="P45">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.35">
@@ -4333,7 +4333,7 @@
         <v>867</v>
       </c>
       <c r="P55">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.35">
@@ -4633,7 +4633,7 @@
         <v>651</v>
       </c>
       <c r="P60">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.35">
@@ -4753,7 +4753,7 @@
         <v>1581</v>
       </c>
       <c r="P62">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.35">
@@ -5113,7 +5113,7 @@
         <v>1369</v>
       </c>
       <c r="P68">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.35">
@@ -5653,7 +5653,7 @@
         <v>772</v>
       </c>
       <c r="P77">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.35">
@@ -5953,7 +5953,7 @@
         <v>1754</v>
       </c>
       <c r="P82">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.35">

--- a/SITE MONITORING.xlsx
+++ b/SITE MONITORING.xlsx
@@ -1136,27 +1136,27 @@
       </c>
       <c r="F2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8904722.9124635179</v>
+        <v>10081819.681227973</v>
       </c>
       <c r="G2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8015662.5391808543</v>
+        <v>9328903.5811648574</v>
       </c>
       <c r="H2" s="12">
         <f>IFERROR(G2/F2-1,0)</f>
-        <v>-9.9841441673416687E-2</v>
+        <v>-7.4680575914784608E-2</v>
       </c>
       <c r="I2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="J2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>351</v>
+        <v>386</v>
       </c>
       <c r="K2" s="12">
         <f>IFERROR(J2/I2-1,0)</f>
-        <v>0.16611295681063121</v>
+        <v>0.34027777777777768</v>
       </c>
       <c r="L2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1184,15 +1184,15 @@
       </c>
       <c r="R2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="S2">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="T2" s="12">
         <f>IFERROR(S2/R2-1,0)</f>
-        <v>1.9417475728155331E-2</v>
+        <v>1.9607843137254832E-2</v>
       </c>
       <c r="U2">
         <v>3</v>
@@ -1216,27 +1216,27 @@
       </c>
       <c r="F3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11077997.986731406</v>
+        <v>12646261.849610392</v>
       </c>
       <c r="G3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9594971.2209495213</v>
+        <v>10997989.293437231</v>
       </c>
       <c r="H3" s="12">
         <f t="shared" ref="H3:H66" si="0">IFERROR(G3/F3-1,0)</f>
-        <v>-0.13387136985926251</v>
+        <v>-0.13033674106818693</v>
       </c>
       <c r="I3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>582</v>
+        <v>550</v>
       </c>
       <c r="J3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>493</v>
+        <v>1204</v>
       </c>
       <c r="K3" s="12">
         <f t="shared" ref="K3:K66" si="1">IFERROR(J3/I3-1,0)</f>
-        <v>-0.15292096219931273</v>
+        <v>1.189090909090909</v>
       </c>
       <c r="L3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1244,11 +1244,11 @@
       </c>
       <c r="M3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N3" s="12">
         <f t="shared" ref="N3:N66" si="2">IFERROR(M3/L3-1,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -1256,11 +1256,11 @@
       </c>
       <c r="P3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q3" s="12">
         <f t="shared" ref="Q3:Q66" si="3">IFERROR(P3/O3-1,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -1268,11 +1268,11 @@
       </c>
       <c r="S3">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="T3" s="12">
         <f t="shared" ref="T3:T66" si="4">IFERROR(S3/R3-1,0)</f>
-        <v>-3.1111111111111089E-2</v>
+        <v>-4.0000000000000036E-2</v>
       </c>
       <c r="U3">
         <v>2</v>
@@ -1296,27 +1296,27 @@
       </c>
       <c r="F4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10813572.180837341</v>
+        <v>12713958.118884431</v>
       </c>
       <c r="G4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11700900.530808456</v>
+        <v>14219634.224562662</v>
       </c>
       <c r="H4" s="12">
         <f t="shared" si="0"/>
-        <v>8.2056912843615493E-2</v>
+        <v>0.1184270147501747</v>
       </c>
       <c r="I4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="J4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>724</v>
+        <v>737</v>
       </c>
       <c r="K4" s="12">
         <f t="shared" si="1"/>
-        <v>0.10534351145038179</v>
+        <v>0.12006079027355621</v>
       </c>
       <c r="L4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="O4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -1340,19 +1340,19 @@
       </c>
       <c r="Q4" s="12">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="S4">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="T4" s="12">
         <f t="shared" si="4"/>
-        <v>8.6510263929618691E-2</v>
+        <v>9.1042584434654961E-2</v>
       </c>
       <c r="U4">
         <v>4</v>
@@ -1376,27 +1376,27 @@
       </c>
       <c r="F5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20569414.54593353</v>
+        <v>23642031.302799549</v>
       </c>
       <c r="G5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20538626.012221169</v>
+        <v>23896411.194066271</v>
       </c>
       <c r="H5" s="12">
         <f t="shared" si="0"/>
-        <v>-1.4968113770864599E-3</v>
+        <v>1.0759646157671776E-2</v>
       </c>
       <c r="I5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1053</v>
+        <v>1981</v>
       </c>
       <c r="J5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2035</v>
+        <v>1071</v>
       </c>
       <c r="K5" s="12">
         <f t="shared" si="1"/>
-        <v>0.93257359924026595</v>
+        <v>-0.45936395759717319</v>
       </c>
       <c r="L5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1412,11 +1412,11 @@
       </c>
       <c r="O5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q5" s="12">
         <f t="shared" si="3"/>
@@ -1424,15 +1424,15 @@
       </c>
       <c r="R5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="S5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1208</v>
+        <v>1212</v>
       </c>
       <c r="T5" s="12">
         <f t="shared" si="4"/>
-        <v>1.257334450963965E-2</v>
+        <v>1.8487394957983128E-2</v>
       </c>
       <c r="U5">
         <v>3</v>
@@ -1456,27 +1456,27 @@
       </c>
       <c r="F6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8172898.0041208696</v>
+        <v>9596873.4474547114</v>
       </c>
       <c r="G6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9141121.1433764119</v>
+        <v>10735578.1970079</v>
       </c>
       <c r="H6" s="12">
         <f t="shared" si="0"/>
-        <v>0.11846754220685884</v>
+        <v>0.11865372152585762</v>
       </c>
       <c r="I6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>300</v>
+        <v>328</v>
       </c>
       <c r="J6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>395</v>
+        <v>361</v>
       </c>
       <c r="K6" s="12">
         <f t="shared" si="1"/>
-        <v>0.31666666666666665</v>
+        <v>0.10060975609756095</v>
       </c>
       <c r="L6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1504,15 +1504,15 @@
       </c>
       <c r="R6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="S6">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="T6" s="12">
         <f t="shared" si="4"/>
-        <v>-7.4074074074074181E-3</v>
+        <v>0</v>
       </c>
       <c r="U6">
         <v>3</v>
@@ -1536,27 +1536,27 @@
       </c>
       <c r="F7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7758957.3293836992</v>
+        <v>8856040.2209448274</v>
       </c>
       <c r="G7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7747219.6709535951</v>
+        <v>8947473.0958644543</v>
       </c>
       <c r="H7" s="12">
         <f t="shared" si="0"/>
-        <v>-1.5127881146674849E-3</v>
+        <v>1.0324351813961297E-2</v>
       </c>
       <c r="I7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>345</v>
+        <v>313</v>
       </c>
       <c r="J7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="K7" s="12">
         <f t="shared" si="1"/>
-        <v>-0.22608695652173916</v>
+        <v>-0.12460063897763574</v>
       </c>
       <c r="L7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1584,15 +1584,15 @@
       </c>
       <c r="R7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="S7">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="T7" s="12">
         <f t="shared" si="4"/>
-        <v>4.0760869565217295E-2</v>
+        <v>3.8147138964577554E-2</v>
       </c>
       <c r="U7">
         <v>2</v>
@@ -1616,27 +1616,27 @@
       </c>
       <c r="F8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9035790.3904993646</v>
+        <v>10119494.23898562</v>
       </c>
       <c r="G8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9130871.8624781035</v>
+        <v>10567198.582857665</v>
       </c>
       <c r="H8" s="12">
         <f t="shared" si="0"/>
-        <v>1.0522762024085086E-2</v>
+        <v>4.4241770714908979E-2</v>
       </c>
       <c r="I8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>508</v>
+        <v>481</v>
       </c>
       <c r="J8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>496</v>
+        <v>516</v>
       </c>
       <c r="K8" s="12">
         <f t="shared" si="1"/>
-        <v>-2.3622047244094446E-2</v>
+        <v>7.2765072765072825E-2</v>
       </c>
       <c r="L8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="R8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="S8">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="T8" s="12">
         <f t="shared" si="4"/>
-        <v>-2.2988505747126409E-2</v>
+        <v>-3.3500837520937798E-3</v>
       </c>
       <c r="U8">
         <v>9</v>
@@ -1696,27 +1696,27 @@
       </c>
       <c r="F9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4009064.5599596188</v>
+        <v>4689917.3020850392</v>
       </c>
       <c r="G9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4061429.297431434</v>
+        <v>4719781.875237532</v>
       </c>
       <c r="H9" s="12">
         <f t="shared" si="0"/>
-        <v>1.3061584987881236E-2</v>
+        <v>6.3678251083907345E-3</v>
       </c>
       <c r="I9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="J9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="K9" s="12">
         <f t="shared" si="1"/>
-        <v>-0.13548387096774195</v>
+        <v>4.2857142857142927E-2</v>
       </c>
       <c r="L9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="R9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="S9">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="T9" s="12">
         <f t="shared" si="4"/>
-        <v>-1.7543859649122862E-2</v>
+        <v>-5.9171597633136397E-3</v>
       </c>
       <c r="U9">
         <v>1</v>
@@ -1776,27 +1776,27 @@
       </c>
       <c r="F10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4114366.4045414459</v>
+        <v>4570511.2464642841</v>
       </c>
       <c r="G10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>834088.64330936898</v>
+        <v>1301677.642551824</v>
       </c>
       <c r="H10" s="12">
         <f t="shared" si="0"/>
-        <v>-0.79727409732183785</v>
+        <v>-0.7152008665203935</v>
       </c>
       <c r="I10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="J10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="K10" s="12">
         <f t="shared" si="1"/>
-        <v>-1.9108280254777066E-2</v>
+        <v>1.4814814814814836E-2</v>
       </c>
       <c r="L10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1824,15 +1824,15 @@
       </c>
       <c r="R10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="S10">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="T10" s="12">
         <f t="shared" si="4"/>
-        <v>-9.2233009708737823E-2</v>
+        <v>-8.9108910891089077E-2</v>
       </c>
       <c r="U10">
         <v>1</v>
@@ -1856,27 +1856,27 @@
       </c>
       <c r="F11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6426679.2572523681</v>
+        <v>7208654.6195380623</v>
       </c>
       <c r="G11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8442751.4556307346</v>
+        <v>9475751.8262754045</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" si="0"/>
-        <v>0.31370356566391155</v>
+        <v>0.31449657757117233</v>
       </c>
       <c r="I11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="J11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="K11" s="12">
         <f t="shared" si="1"/>
-        <v>0.125</v>
+        <v>5.0147492625368661E-2</v>
       </c>
       <c r="L11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1904,15 +1904,15 @@
       </c>
       <c r="R11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="S11">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="T11" s="12">
         <f t="shared" si="4"/>
-        <v>4.5454545454545414E-2</v>
+        <v>8.405797101449286E-2</v>
       </c>
       <c r="U11">
         <v>4</v>
@@ -1936,31 +1936,31 @@
       </c>
       <c r="F12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>3076842.9337319238</v>
+        <v>3398341.1812919341</v>
       </c>
       <c r="G12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3928722.993377714</v>
+        <v>4599522.8086553616</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="0"/>
-        <v>0.27686823084353507</v>
+        <v>0.35346116333933808</v>
       </c>
       <c r="I12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>263</v>
+        <v>424</v>
       </c>
       <c r="K12" s="12">
         <f t="shared" si="1"/>
-        <v>0.12393162393162394</v>
+        <v>0.86784140969163004</v>
       </c>
       <c r="L12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="N12" s="12">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -1984,15 +1984,15 @@
       </c>
       <c r="R12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="S12">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="T12" s="12">
         <f t="shared" si="4"/>
-        <v>2.450980392156854E-2</v>
+        <v>0</v>
       </c>
       <c r="U12">
         <v>3</v>
@@ -2016,27 +2016,27 @@
       </c>
       <c r="F13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4106721.092204113</v>
+        <v>4634949.7732747439</v>
       </c>
       <c r="G13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4332106.5259726672</v>
+        <v>4996010.6418833202</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="0"/>
-        <v>5.4882089313639693E-2</v>
+        <v>7.7899629180549823E-2</v>
       </c>
       <c r="I13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="J13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="K13" s="12">
         <f t="shared" si="1"/>
-        <v>0.15999999999999992</v>
+        <v>0.15228426395939088</v>
       </c>
       <c r="L13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2064,15 +2064,15 @@
       </c>
       <c r="R13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="S13">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="T13" s="12">
         <f t="shared" si="4"/>
-        <v>-3.9370078740157521E-2</v>
+        <v>-1.9920318725099584E-2</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -2096,27 +2096,27 @@
       </c>
       <c r="F14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7512212.0363657642</v>
+        <v>8173457.9071941637</v>
       </c>
       <c r="G14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15558073.085482126</v>
+        <v>19523999.849815324</v>
       </c>
       <c r="H14" s="12">
         <f t="shared" si="0"/>
-        <v>1.0710375333080675</v>
+        <v>1.3887074566849571</v>
       </c>
       <c r="I14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>16</v>
+        <v>999</v>
       </c>
       <c r="J14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1327</v>
+        <v>1223</v>
       </c>
       <c r="K14" s="12">
         <f t="shared" si="1"/>
-        <v>81.9375</v>
+        <v>0.22422422422422428</v>
       </c>
       <c r="L14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2144,15 +2144,15 @@
       </c>
       <c r="R14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="S14">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="T14" s="12">
         <f t="shared" si="4"/>
-        <v>9.1549295774648876E-3</v>
+        <v>9.1613812544044659E-3</v>
       </c>
       <c r="U14">
         <v>3</v>
@@ -2176,27 +2176,27 @@
       </c>
       <c r="F15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>30427161.100131635</v>
+        <v>33256265.103515387</v>
       </c>
       <c r="G15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>29254917.109629303</v>
+        <v>34614044.554706417</v>
       </c>
       <c r="H15" s="12">
         <f t="shared" si="0"/>
-        <v>-3.8526236037750516E-2</v>
+        <v>4.0827779276016996E-2</v>
       </c>
       <c r="I15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1102</v>
+        <v>922</v>
       </c>
       <c r="J15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>907</v>
+        <v>1013</v>
       </c>
       <c r="K15" s="12">
         <f t="shared" si="1"/>
-        <v>-0.17695099818511795</v>
+        <v>9.8698481561822149E-2</v>
       </c>
       <c r="L15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2224,15 +2224,15 @@
       </c>
       <c r="R15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="S15">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="T15" s="12">
         <f t="shared" si="4"/>
-        <v>-4.4856921887084344E-2</v>
+        <v>-4.6367851622874823E-2</v>
       </c>
       <c r="U15">
         <v>4</v>
@@ -2256,27 +2256,27 @@
       </c>
       <c r="F16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16637487.25802622</v>
+        <v>19360881.193097025</v>
       </c>
       <c r="G16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17104080.460517026</v>
+        <v>19707768.173094597</v>
       </c>
       <c r="H16" s="12">
         <f t="shared" si="0"/>
-        <v>2.8044691800783506E-2</v>
+        <v>1.7916900400238633E-2</v>
       </c>
       <c r="I16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="J16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="K16" s="12">
         <f t="shared" si="1"/>
-        <v>-8.6021505376343566E-3</v>
+        <v>8.79120879120876E-3</v>
       </c>
       <c r="L16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2296,15 +2296,15 @@
       </c>
       <c r="P16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q16" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="S16">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="T16" s="12">
         <f t="shared" si="4"/>
-        <v>9.7751710654936375E-4</v>
+        <v>2.9382957884427352E-3</v>
       </c>
       <c r="U16">
         <v>4</v>
@@ -2336,31 +2336,31 @@
       </c>
       <c r="F17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17060687.407777634</v>
+        <v>19456613.387876816</v>
       </c>
       <c r="G17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12169391.271711731</v>
+        <v>14701576.182038048</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="0"/>
-        <v>-0.28669982745455236</v>
+        <v>-0.24439182251529834</v>
       </c>
       <c r="I17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="J17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>681</v>
+        <v>654</v>
       </c>
       <c r="K17" s="12">
         <f t="shared" si="1"/>
-        <v>6.240249609984394E-2</v>
+        <v>3.3175355450236976E-2</v>
       </c>
       <c r="L17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -2368,31 +2368,31 @@
       </c>
       <c r="N17" s="12">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q17" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="S17">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>903</v>
+        <v>912</v>
       </c>
       <c r="T17" s="12">
         <f t="shared" si="4"/>
-        <v>-5.3459119496855334E-2</v>
+        <v>-3.8988408851422518E-2</v>
       </c>
       <c r="U17">
         <v>4</v>
@@ -2416,27 +2416,27 @@
       </c>
       <c r="F18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>57559835.304311313</v>
+        <v>66752926.934528187</v>
       </c>
       <c r="G18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>63483376.813367918</v>
+        <v>72814817.405791759</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="0"/>
-        <v>0.10291102255139584</v>
+        <v>9.0810856536809537E-2</v>
       </c>
       <c r="I18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1895</v>
+        <v>2123</v>
       </c>
       <c r="J18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2091</v>
+        <v>2002</v>
       </c>
       <c r="K18" s="12">
         <f t="shared" si="1"/>
-        <v>0.10343007915567282</v>
+        <v>-5.6994818652849721E-2</v>
       </c>
       <c r="L18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2456,23 +2456,23 @@
       </c>
       <c r="P18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q18" s="12">
         <f t="shared" si="3"/>
-        <v>0.46610169491525433</v>
+        <v>0.48305084745762716</v>
       </c>
       <c r="R18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2777</v>
+        <v>2745</v>
       </c>
       <c r="S18">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2872</v>
+        <v>2837</v>
       </c>
       <c r="T18" s="12">
         <f t="shared" si="4"/>
-        <v>3.4209578682030894E-2</v>
+        <v>3.3515482695810617E-2</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -2496,27 +2496,27 @@
       </c>
       <c r="F19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>32045023.177340128</v>
+        <v>36794577.136621326</v>
       </c>
       <c r="G19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13732806.891209688</v>
+        <v>18253988.933064144</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="0"/>
-        <v>-0.57145273962789589</v>
+        <v>-0.50389458573513246</v>
       </c>
       <c r="I19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="J19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1143</v>
+        <v>1176</v>
       </c>
       <c r="K19" s="12">
         <f t="shared" si="1"/>
-        <v>-2.3911187019641345E-2</v>
+        <v>5.9880239520957446E-3</v>
       </c>
       <c r="L19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="P19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q19" s="12">
         <f t="shared" si="3"/>
@@ -2548,11 +2548,11 @@
       </c>
       <c r="S19">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1367</v>
+        <v>1375</v>
       </c>
       <c r="T19" s="12">
         <f t="shared" si="4"/>
-        <v>-5.8539944903581276E-2</v>
+        <v>-5.3030303030302983E-2</v>
       </c>
       <c r="U19">
         <v>1</v>
@@ -2576,31 +2576,31 @@
       </c>
       <c r="F20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>63795978.508467458</v>
+        <v>73829830.108036533</v>
       </c>
       <c r="G20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>62485638.947705641</v>
+        <v>72601988.544970065</v>
       </c>
       <c r="H20" s="12">
         <f t="shared" si="0"/>
-        <v>-2.0539532293370133E-2</v>
+        <v>-1.6630697392500338E-2</v>
       </c>
       <c r="I20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2472</v>
+        <v>2398</v>
       </c>
       <c r="J20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2209</v>
+        <v>2168</v>
       </c>
       <c r="K20" s="12">
         <f t="shared" si="1"/>
-        <v>-0.10639158576051777</v>
+        <v>-9.591326105087572E-2</v>
       </c>
       <c r="L20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -2608,31 +2608,31 @@
       </c>
       <c r="N20" s="12">
         <f t="shared" si="2"/>
-        <v>-0.16666666666666663</v>
+        <v>-9.0909090909090939E-2</v>
       </c>
       <c r="O20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q20" s="12">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="R20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2999</v>
+        <v>3017</v>
       </c>
       <c r="S20">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2972</v>
+        <v>2967</v>
       </c>
       <c r="T20" s="12">
         <f t="shared" si="4"/>
-        <v>-9.003001000333466E-3</v>
+        <v>-1.6572754391779965E-2</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2656,27 +2656,27 @@
       </c>
       <c r="F21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9011397.0943409987</v>
+        <v>10266236.082020912</v>
       </c>
       <c r="G21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9650938.5786911491</v>
+        <v>10855173.82160108</v>
       </c>
       <c r="H21" s="12">
         <f t="shared" si="0"/>
-        <v>7.0970292137250368E-2</v>
+        <v>5.7366471496945737E-2</v>
       </c>
       <c r="I21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>687</v>
+        <v>475</v>
       </c>
       <c r="J21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="K21" s="12">
         <f t="shared" si="1"/>
-        <v>-0.31877729257641918</v>
+        <v>0</v>
       </c>
       <c r="L21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -2700,19 +2700,19 @@
       </c>
       <c r="Q21" s="12">
         <f t="shared" si="3"/>
-        <v>0.33333333333333326</v>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="R21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="S21">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="T21" s="12">
         <f t="shared" si="4"/>
-        <v>-1.9927536231884035E-2</v>
+        <v>-2.722323049001818E-2</v>
       </c>
       <c r="U21">
         <v>1</v>
@@ -2736,27 +2736,27 @@
       </c>
       <c r="F22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24671664.355904289</v>
+        <v>28739105.010453988</v>
       </c>
       <c r="G22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>25739797.312284291</v>
+        <v>29878204.248217441</v>
       </c>
       <c r="H22" s="12">
         <f t="shared" si="0"/>
-        <v>4.329391568284624E-2</v>
+        <v>3.9635863307124541E-2</v>
       </c>
       <c r="I22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1298</v>
+        <v>1251</v>
       </c>
       <c r="J22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1348</v>
+        <v>1281</v>
       </c>
       <c r="K22" s="12">
         <f t="shared" si="1"/>
-        <v>3.8520801232665658E-2</v>
+        <v>2.3980815347721895E-2</v>
       </c>
       <c r="L22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2764,35 +2764,35 @@
       </c>
       <c r="M22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N22" s="12">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q22" s="12">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.39999999999999991</v>
       </c>
       <c r="R22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="S22">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1749</v>
+        <v>1717</v>
       </c>
       <c r="T22" s="12">
         <f t="shared" si="4"/>
-        <v>2.821869488536155E-2</v>
+        <v>8.8131609870740757E-3</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2816,27 +2816,27 @@
       </c>
       <c r="F23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11251576.178390903</v>
+        <v>12792800.080579426</v>
       </c>
       <c r="G23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10264637.068090342</v>
+        <v>12026624.385429287</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="0"/>
-        <v>-8.771563153934081E-2</v>
+        <v>-5.9891164586653667E-2</v>
       </c>
       <c r="I23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="J23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>765</v>
+        <v>833</v>
       </c>
       <c r="K23" s="12">
         <f t="shared" si="1"/>
-        <v>1.0568031704095038E-2</v>
+        <v>0.10477453580901863</v>
       </c>
       <c r="L23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2852,19 +2852,19 @@
       </c>
       <c r="O23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q23" s="12">
         <f t="shared" si="3"/>
-        <v>0.60000000000000009</v>
+        <v>0.28571428571428581</v>
       </c>
       <c r="R23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="S23">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="T23" s="12">
         <f t="shared" si="4"/>
-        <v>1.387283236994219E-2</v>
+        <v>2.0954598370197974E-2</v>
       </c>
       <c r="U23">
         <v>1</v>
@@ -2896,27 +2896,27 @@
       </c>
       <c r="F24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11850976.593486</v>
+        <v>14116105.390142018</v>
       </c>
       <c r="G24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13079902.716852484</v>
+        <v>15041764.988150029</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="0"/>
-        <v>0.10369829977066836</v>
+        <v>6.5574715718291987E-2</v>
       </c>
       <c r="I24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>881</v>
+        <v>716</v>
       </c>
       <c r="J24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>807</v>
+        <v>668</v>
       </c>
       <c r="K24" s="12">
         <f t="shared" si="1"/>
-        <v>-8.399545970488087E-2</v>
+        <v>-6.7039106145251437E-2</v>
       </c>
       <c r="L24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2944,15 +2944,15 @@
       </c>
       <c r="R24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>892</v>
+        <v>903</v>
       </c>
       <c r="S24">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="T24" s="12">
         <f t="shared" si="4"/>
-        <v>-2.2421524663677195E-3</v>
+        <v>-1.8826135105204922E-2</v>
       </c>
       <c r="U24">
         <v>3</v>
@@ -2976,27 +2976,27 @@
       </c>
       <c r="F25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>3490224.814658503</v>
+        <v>4085296.183992228</v>
       </c>
       <c r="G25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>2753796.6769717392</v>
+        <v>3252983.6141009722</v>
       </c>
       <c r="H25" s="12">
         <f t="shared" si="0"/>
-        <v>-0.21099733592915237</v>
+        <v>-0.20373371535522411</v>
       </c>
       <c r="I25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="J25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K25" s="12">
         <f t="shared" si="1"/>
-        <v>-5.5248618784530357E-2</v>
+        <v>-5.6994818652849721E-2</v>
       </c>
       <c r="L25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3024,15 +3024,15 @@
       </c>
       <c r="R25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="S25">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="T25" s="12">
         <f t="shared" si="4"/>
-        <v>-3.3472803347280311E-2</v>
+        <v>8.9285714285713969E-3</v>
       </c>
       <c r="U25">
         <v>1</v>
@@ -3056,27 +3056,27 @@
       </c>
       <c r="F26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>29071248.072626371</v>
+        <v>32881334.951630816</v>
       </c>
       <c r="G26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>24370086.898229964</v>
+        <v>28162389.603792943</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="0"/>
-        <v>-0.16171170782389088</v>
+        <v>-0.14351440885169497</v>
       </c>
       <c r="I26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1425</v>
+        <v>1346</v>
       </c>
       <c r="J26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1293</v>
+        <v>1478</v>
       </c>
       <c r="K26" s="12">
         <f t="shared" si="1"/>
-        <v>-9.2631578947368398E-2</v>
+        <v>9.8068350668647941E-2</v>
       </c>
       <c r="L26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3084,11 +3084,11 @@
       </c>
       <c r="M26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N26" s="12">
         <f t="shared" si="2"/>
-        <v>0.19999999999999996</v>
+        <v>0</v>
       </c>
       <c r="O26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -3096,23 +3096,23 @@
       </c>
       <c r="P26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q26" s="12">
         <f t="shared" si="3"/>
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1670</v>
+        <v>1664</v>
       </c>
       <c r="S26">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1663</v>
+        <v>1644</v>
       </c>
       <c r="T26" s="12">
         <f t="shared" si="4"/>
-        <v>-4.1916167664670656E-3</v>
+        <v>-1.2019230769230727E-2</v>
       </c>
       <c r="U26">
         <v>1</v>
@@ -3136,27 +3136,27 @@
       </c>
       <c r="F27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19157411.185149383</v>
+        <v>22398496.405254211</v>
       </c>
       <c r="G27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19821996.514491428</v>
+        <v>23291306.937544983</v>
       </c>
       <c r="H27" s="12">
         <f t="shared" si="0"/>
-        <v>3.469076917121372E-2</v>
+        <v>3.9860288661221821E-2</v>
       </c>
       <c r="I27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>647</v>
+        <v>634</v>
       </c>
       <c r="J27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="K27" s="12">
         <f t="shared" si="1"/>
-        <v>-2.7820710973724849E-2</v>
+        <v>1.8927444794952786E-2</v>
       </c>
       <c r="L27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="O27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3180,19 +3180,19 @@
       </c>
       <c r="Q27" s="12">
         <f t="shared" si="3"/>
-        <v>-0.5</v>
+        <v>-0.66666666666666674</v>
       </c>
       <c r="R27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="S27">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="T27" s="12">
         <f t="shared" si="4"/>
-        <v>1.1494252873562871E-3</v>
+        <v>1.0404624277456698E-2</v>
       </c>
       <c r="U27">
         <v>1</v>
@@ -3216,27 +3216,27 @@
       </c>
       <c r="F28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20847256.078643773</v>
+        <v>24190546.883645892</v>
       </c>
       <c r="G28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19414730.029029332</v>
+        <v>22608286.960778888</v>
       </c>
       <c r="H28" s="12">
         <f t="shared" si="0"/>
-        <v>-6.8715328492651939E-2</v>
+        <v>-6.5408191492218659E-2</v>
       </c>
       <c r="I28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>742</v>
+        <v>726</v>
       </c>
       <c r="J28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>824</v>
+        <v>787</v>
       </c>
       <c r="K28" s="12">
         <f t="shared" si="1"/>
-        <v>0.11051212938005395</v>
+        <v>8.4022038567493018E-2</v>
       </c>
       <c r="L28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3268,11 +3268,11 @@
       </c>
       <c r="S28">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="T28" s="12">
         <f t="shared" si="4"/>
-        <v>-6.360424028268552E-2</v>
+        <v>-6.6254416961130769E-2</v>
       </c>
       <c r="U28">
         <v>1</v>
@@ -3296,27 +3296,27 @@
       </c>
       <c r="F29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>27091482.436740737</v>
+        <v>31449964.011454657</v>
       </c>
       <c r="G29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>26418427.83281048</v>
+        <v>30719241.13553416</v>
       </c>
       <c r="H29" s="12">
         <f t="shared" si="0"/>
-        <v>-2.484377167258589E-2</v>
+        <v>-2.3234458254208334E-2</v>
       </c>
       <c r="I29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>964</v>
+        <v>976</v>
       </c>
       <c r="J29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>816</v>
+        <v>869</v>
       </c>
       <c r="K29" s="12">
         <f t="shared" si="1"/>
-        <v>-0.15352697095435686</v>
+        <v>-0.10963114754098358</v>
       </c>
       <c r="L29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="O29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="Q29" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -3348,11 +3348,11 @@
       </c>
       <c r="S29">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1115</v>
+        <v>1120</v>
       </c>
       <c r="T29" s="12">
         <f t="shared" si="4"/>
-        <v>8.9766606822272443E-4</v>
+        <v>5.3859964093356805E-3</v>
       </c>
       <c r="U29">
         <v>1</v>
@@ -3376,27 +3376,27 @@
       </c>
       <c r="F30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>39832891.790901192</v>
+        <v>46108166.034123458</v>
       </c>
       <c r="G30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>37524684.099695168</v>
+        <v>43751923.266922899</v>
       </c>
       <c r="H30" s="12">
         <f t="shared" si="0"/>
-        <v>-5.7947278930255197E-2</v>
+        <v>-5.1102504607465127E-2</v>
       </c>
       <c r="I30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="J30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1207</v>
+        <v>1162</v>
       </c>
       <c r="K30" s="12">
         <f t="shared" si="1"/>
-        <v>3.6941580756013837E-2</v>
+        <v>-5.136986301369828E-3</v>
       </c>
       <c r="L30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3404,11 +3404,11 @@
       </c>
       <c r="M30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N30" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="O30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -3424,15 +3424,15 @@
       </c>
       <c r="R30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="S30">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1455</v>
+        <v>1447</v>
       </c>
       <c r="T30" s="12">
         <f t="shared" si="4"/>
-        <v>-3.3864541832669293E-2</v>
+        <v>-4.0450928381962847E-2</v>
       </c>
       <c r="U30">
         <v>4</v>
@@ -3456,31 +3456,31 @@
       </c>
       <c r="F31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14587539.749331217</v>
+        <v>17087525.954022851</v>
       </c>
       <c r="G31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15406510.595932836</v>
+        <v>17886223.967067465</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="0"/>
-        <v>5.6141807369482155E-2</v>
+        <v>4.6741583023409028E-2</v>
       </c>
       <c r="I31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="J31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>581</v>
+        <v>537</v>
       </c>
       <c r="K31" s="12">
         <f t="shared" si="1"/>
-        <v>6.4102564102564097E-2</v>
+        <v>-9.2250922509224953E-3</v>
       </c>
       <c r="L31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="N31" s="12">
         <f t="shared" si="2"/>
-        <v>0.66666666666666674</v>
+        <v>1.5</v>
       </c>
       <c r="O31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -3508,11 +3508,11 @@
       </c>
       <c r="S31">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="T31" s="12">
         <f t="shared" si="4"/>
-        <v>-1.4450867052023142E-2</v>
+        <v>-1.7341040462427793E-2</v>
       </c>
       <c r="U31">
         <v>3</v>
@@ -3536,27 +3536,27 @@
       </c>
       <c r="F32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>46870678.587666772</v>
+        <v>54279827.871796161</v>
       </c>
       <c r="G32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>46557482.188332088</v>
+        <v>46525766.431750014</v>
       </c>
       <c r="H32" s="12">
         <f t="shared" si="0"/>
-        <v>-6.682139213087801E-3</v>
+        <v>-0.14285346405962285</v>
       </c>
       <c r="I32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1663</v>
+        <v>1654</v>
       </c>
       <c r="J32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>892</v>
+        <v>52</v>
       </c>
       <c r="K32" s="12">
         <f t="shared" si="1"/>
-        <v>-0.46361996392062532</v>
+        <v>-0.96856106408706166</v>
       </c>
       <c r="L32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3564,15 +3564,15 @@
       </c>
       <c r="M32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N32" s="12">
         <f t="shared" si="2"/>
-        <v>0.10000000000000009</v>
+        <v>-9.9999999999999978E-2</v>
       </c>
       <c r="O32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3580,19 +3580,19 @@
       </c>
       <c r="Q32" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-0.53846153846153844</v>
       </c>
       <c r="R32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1968</v>
+        <v>1974</v>
       </c>
       <c r="S32">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1941</v>
+        <v>1922</v>
       </c>
       <c r="T32" s="12">
         <f t="shared" si="4"/>
-        <v>-1.3719512195121908E-2</v>
+        <v>-2.634245187436679E-2</v>
       </c>
       <c r="U32">
         <v>5</v>
@@ -3616,31 +3616,31 @@
       </c>
       <c r="F33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16279779.246790402</v>
+        <v>18746377.997059025</v>
       </c>
       <c r="G33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15562023.232441895</v>
+        <v>18249413.325665232</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="0"/>
-        <v>-4.408880510403812E-2</v>
+        <v>-2.6509903484916331E-2</v>
       </c>
       <c r="I33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>679</v>
+        <v>723</v>
       </c>
       <c r="J33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>774</v>
+        <v>695</v>
       </c>
       <c r="K33" s="12">
         <f t="shared" si="1"/>
-        <v>0.13991163475699553</v>
+        <v>-3.8727524204702601E-2</v>
       </c>
       <c r="L33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="N33" s="12">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -3656,23 +3656,23 @@
       </c>
       <c r="P33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q33" s="12">
         <f t="shared" si="3"/>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="R33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="S33">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="4"/>
-        <v>-2.3640661938534313E-3</v>
+        <v>1.179245283018826E-3</v>
       </c>
       <c r="U33">
         <v>3</v>
@@ -3696,27 +3696,27 @@
       </c>
       <c r="F34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12893390.296193728</v>
+        <v>15180363.769693863</v>
       </c>
       <c r="G34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14995641.256104443</v>
+        <v>17338354.810338959</v>
       </c>
       <c r="H34" s="12">
         <f t="shared" si="0"/>
-        <v>0.16304873362371741</v>
+        <v>0.14215674099676834</v>
       </c>
       <c r="I34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>459</v>
+        <v>572</v>
       </c>
       <c r="J34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="K34" s="12">
         <f t="shared" si="1"/>
-        <v>0.17211328976034856</v>
+        <v>-6.643356643356646E-2</v>
       </c>
       <c r="L34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="P34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q34" s="12">
         <f t="shared" si="3"/>
@@ -3748,11 +3748,11 @@
       </c>
       <c r="S34">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="T34" s="12">
         <f t="shared" si="4"/>
-        <v>7.9710144927536142E-2</v>
+        <v>7.6811594202898625E-2</v>
       </c>
       <c r="U34">
         <v>4</v>
@@ -3776,27 +3776,27 @@
       </c>
       <c r="F35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>23576799.335367773</v>
+        <v>27075611.243230514</v>
       </c>
       <c r="G35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22123498.048207261</v>
+        <v>25902505.08937801</v>
       </c>
       <c r="H35" s="12">
         <f t="shared" si="0"/>
-        <v>-6.1641161146941625E-2</v>
+        <v>-4.3327042308077379E-2</v>
       </c>
       <c r="I35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>941</v>
+        <v>869</v>
       </c>
       <c r="J35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>822</v>
+        <v>832</v>
       </c>
       <c r="K35" s="12">
         <f t="shared" si="1"/>
-        <v>-0.12646121147715195</v>
+        <v>-4.2577675489067879E-2</v>
       </c>
       <c r="L35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3816,23 +3816,23 @@
       </c>
       <c r="P35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q35" s="12">
         <f t="shared" si="3"/>
-        <v>0.19999999999999996</v>
+        <v>0.5</v>
       </c>
       <c r="R35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1110</v>
+        <v>1102</v>
       </c>
       <c r="S35">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="T35" s="12">
         <f t="shared" si="4"/>
-        <v>4.9549549549549488E-2</v>
+        <v>5.5353901996370247E-2</v>
       </c>
       <c r="U35">
         <v>13</v>
@@ -3856,27 +3856,27 @@
       </c>
       <c r="F36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>22904201.531117793</v>
+        <v>26511431.303062446</v>
       </c>
       <c r="G36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20751223.31803656</v>
+        <v>24107934.363502286</v>
       </c>
       <c r="H36" s="12">
         <f t="shared" si="0"/>
-        <v>-9.3999269529487117E-2</v>
+        <v>-9.0658890200414066E-2</v>
       </c>
       <c r="I36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>753</v>
+        <v>789</v>
       </c>
       <c r="J36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="K36" s="12">
         <f t="shared" si="1"/>
-        <v>5.7104913678618807E-2</v>
+        <v>2.5348542458809575E-3</v>
       </c>
       <c r="L36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="O36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3900,19 +3900,19 @@
       </c>
       <c r="Q36" s="12">
         <f t="shared" si="3"/>
-        <v>2.1578947368421053</v>
+        <v>2</v>
       </c>
       <c r="R36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1128</v>
+        <v>1109</v>
       </c>
       <c r="S36">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1331</v>
+        <v>1324</v>
       </c>
       <c r="T36" s="12">
         <f t="shared" si="4"/>
-        <v>0.17996453900709231</v>
+        <v>0.19386834986474311</v>
       </c>
       <c r="U36">
         <v>4</v>
@@ -3936,27 +3936,27 @@
       </c>
       <c r="F37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>36032619.201137818</v>
+        <v>41714812.457557224</v>
       </c>
       <c r="G37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>38476619.904587738</v>
+        <v>44580467.56550619</v>
       </c>
       <c r="H37" s="12">
         <f t="shared" si="0"/>
-        <v>6.7827450727554695E-2</v>
+        <v>6.8696344035218404E-2</v>
       </c>
       <c r="I37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1452</v>
+        <v>1437</v>
       </c>
       <c r="J37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1529</v>
+        <v>1447</v>
       </c>
       <c r="K37" s="12">
         <f t="shared" si="1"/>
-        <v>5.3030303030302983E-2</v>
+        <v>6.9589422407794199E-3</v>
       </c>
       <c r="L37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3972,27 +3972,27 @@
       </c>
       <c r="O37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="P37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q37" s="12">
         <f t="shared" si="3"/>
-        <v>0.53333333333333344</v>
+        <v>0.39999999999999991</v>
       </c>
       <c r="R37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1804</v>
+        <v>1793</v>
       </c>
       <c r="S37">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2397</v>
+        <v>2349</v>
       </c>
       <c r="T37" s="12">
         <f t="shared" si="4"/>
-        <v>0.32871396895787131</v>
+        <v>0.31009481316229781</v>
       </c>
       <c r="U37">
         <v>16</v>
@@ -4016,31 +4016,31 @@
       </c>
       <c r="F38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15020445.159102108</v>
+        <v>17457645.379634544</v>
       </c>
       <c r="G38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13614594.777193189</v>
+        <v>15995398.494616931</v>
       </c>
       <c r="H38" s="12">
         <f t="shared" si="0"/>
-        <v>-9.3595786743843612E-2</v>
+        <v>-8.375968541115042E-2</v>
       </c>
       <c r="I38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="J38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>570</v>
+        <v>697</v>
       </c>
       <c r="K38" s="12">
         <f t="shared" si="1"/>
-        <v>0.21794871794871784</v>
+        <v>0.44605809128630702</v>
       </c>
       <c r="L38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="N38" s="12">
         <f t="shared" si="2"/>
-        <v>0.19999999999999996</v>
+        <v>0</v>
       </c>
       <c r="O38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4064,15 +4064,15 @@
       </c>
       <c r="R38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="S38">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="T38" s="12">
         <f t="shared" si="4"/>
-        <v>-1.748807631160576E-2</v>
+        <v>-1.7405063291139222E-2</v>
       </c>
       <c r="U38">
         <v>3</v>
@@ -4096,27 +4096,27 @@
       </c>
       <c r="F39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>42247576.219750777</v>
+        <v>48793911.539376937</v>
       </c>
       <c r="G39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>45470936.193361871</v>
+        <v>52343763.076205544</v>
       </c>
       <c r="H39" s="12">
         <f t="shared" si="0"/>
-        <v>7.6296920723801787E-2</v>
+        <v>7.2751936150145635E-2</v>
       </c>
       <c r="I39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2213</v>
+        <v>1985</v>
       </c>
       <c r="J39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1914</v>
+        <v>1780</v>
       </c>
       <c r="K39" s="12">
         <f t="shared" si="1"/>
-        <v>-0.13511070944419346</v>
+        <v>-0.10327455919395467</v>
       </c>
       <c r="L39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="O39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4140,11 +4140,11 @@
       </c>
       <c r="Q39" s="12">
         <f t="shared" si="3"/>
-        <v>-0.33333333333333337</v>
+        <v>-0.5</v>
       </c>
       <c r="R39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1992</v>
+        <v>2017</v>
       </c>
       <c r="S39">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="T39" s="12">
         <f t="shared" si="4"/>
-        <v>3.2630522088353375E-2</v>
+        <v>1.98314328210214E-2</v>
       </c>
       <c r="U39">
         <v>4</v>
@@ -4176,27 +4176,27 @@
       </c>
       <c r="F40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>28973262.41277713</v>
+        <v>33739920.607283264</v>
       </c>
       <c r="G40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>29671640.615555849</v>
+        <v>35711327.025523543</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" si="0"/>
-        <v>2.4104230750028988E-2</v>
+        <v>5.8429491912163067E-2</v>
       </c>
       <c r="I40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>740</v>
+        <v>762</v>
       </c>
       <c r="J40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1422</v>
+        <v>2065</v>
       </c>
       <c r="K40" s="12">
         <f t="shared" si="1"/>
-        <v>0.92162162162162153</v>
+        <v>1.7099737532808401</v>
       </c>
       <c r="L40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4204,11 +4204,11 @@
       </c>
       <c r="M40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N40" s="12">
         <f t="shared" si="2"/>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="O40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4224,15 +4224,15 @@
       </c>
       <c r="R40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="S40">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="T40" s="12">
         <f t="shared" si="4"/>
-        <v>3.0927835051546282E-2</v>
+        <v>3.3142857142857141E-2</v>
       </c>
       <c r="U40">
         <v>3</v>
@@ -4256,27 +4256,27 @@
       </c>
       <c r="F41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24778612.015554167</v>
+        <v>28381796.030693352</v>
       </c>
       <c r="G41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16080664.001975443</v>
+        <v>19475103.312340401</v>
       </c>
       <c r="H41" s="12">
         <f t="shared" si="0"/>
-        <v>-0.35102644200243338</v>
+        <v>-0.31381709278443315</v>
       </c>
       <c r="I41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>887</v>
+        <v>955</v>
       </c>
       <c r="J41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>908</v>
+        <v>854</v>
       </c>
       <c r="K41" s="12">
         <f t="shared" si="1"/>
-        <v>2.3675310033821839E-2</v>
+        <v>-0.10575916230366489</v>
       </c>
       <c r="L41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4296,23 +4296,23 @@
       </c>
       <c r="P41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q41" s="12">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="S41">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1081</v>
+        <v>1093</v>
       </c>
       <c r="T41" s="12">
         <f t="shared" si="4"/>
-        <v>-6.3258232235701928E-2</v>
+        <v>-5.0390964378801084E-2</v>
       </c>
       <c r="U41">
         <v>4</v>
@@ -4336,27 +4336,27 @@
       </c>
       <c r="F42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24227242.078079969</v>
+        <v>27882962.771981161</v>
       </c>
       <c r="G42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23529348.521047913</v>
+        <v>27090027.561345614</v>
       </c>
       <c r="H42" s="12">
         <f t="shared" si="0"/>
-        <v>-2.8806149490019251E-2</v>
+        <v>-2.843798261755548E-2</v>
       </c>
       <c r="I42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>649</v>
+        <v>611</v>
       </c>
       <c r="J42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>627</v>
+        <v>982</v>
       </c>
       <c r="K42" s="12">
         <f t="shared" si="1"/>
-        <v>-3.3898305084745783E-2</v>
+        <v>0.60720130932896899</v>
       </c>
       <c r="L42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="P42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q42" s="12">
         <f t="shared" si="3"/>
@@ -4384,15 +4384,15 @@
       </c>
       <c r="R42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="S42">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="T42" s="12">
         <f t="shared" si="4"/>
-        <v>-2.5791324736225141E-2</v>
+        <v>-2.5700934579439227E-2</v>
       </c>
       <c r="U42">
         <v>2</v>
@@ -4416,27 +4416,27 @@
       </c>
       <c r="F43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14652415.851613129</v>
+        <v>17023761.506318234</v>
       </c>
       <c r="G43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15138233.493068304</v>
+        <v>17462894.453000762</v>
       </c>
       <c r="H43" s="12">
         <f t="shared" si="0"/>
-        <v>3.3156146151946064E-2</v>
+        <v>2.5795294801301605E-2</v>
       </c>
       <c r="I43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="J43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>553</v>
+        <v>778</v>
       </c>
       <c r="K43" s="12">
         <f t="shared" si="1"/>
-        <v>-2.12389380530974E-2</v>
+        <v>0.36252189141856395</v>
       </c>
       <c r="L43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4452,7 +4452,7 @@
       </c>
       <c r="O43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4460,19 +4460,19 @@
       </c>
       <c r="Q43" s="12">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>-0.33333333333333337</v>
       </c>
       <c r="R43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="S43">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>706</v>
+        <v>697</v>
       </c>
       <c r="T43" s="12">
         <f t="shared" si="4"/>
-        <v>7.2948328267477214E-2</v>
+        <v>5.4462934947050012E-2</v>
       </c>
       <c r="U43">
         <v>2</v>
@@ -4496,27 +4496,27 @@
       </c>
       <c r="F44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13960317.916001091</v>
+        <v>16200048.119271619</v>
       </c>
       <c r="G44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13328418.590985743</v>
+        <v>15508561.952835817</v>
       </c>
       <c r="H44" s="12">
         <f t="shared" si="0"/>
-        <v>-4.5263963816402408E-2</v>
+        <v>-4.2684204475492149E-2</v>
       </c>
       <c r="I44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>794</v>
+        <v>2510</v>
       </c>
       <c r="J44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>719</v>
+        <v>697</v>
       </c>
       <c r="K44" s="12">
         <f t="shared" si="1"/>
-        <v>-9.4458438287153612E-2</v>
+        <v>-0.72231075697211156</v>
       </c>
       <c r="L44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4544,15 +4544,15 @@
       </c>
       <c r="R44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="S44">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="T44" s="12">
         <f t="shared" si="4"/>
-        <v>-7.2358900144717797E-3</v>
+        <v>-7.2046109510086609E-3</v>
       </c>
       <c r="U44">
         <v>3</v>
@@ -4576,27 +4576,27 @@
       </c>
       <c r="F45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>46742524.804393575</v>
+        <v>53212406.534532376</v>
       </c>
       <c r="G45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>40595640.839021318</v>
+        <v>47059692.469827741</v>
       </c>
       <c r="H45" s="12">
         <f t="shared" si="0"/>
-        <v>-0.13150517630563419</v>
+        <v>-0.11562555549356346</v>
       </c>
       <c r="I45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1117</v>
+        <v>1159</v>
       </c>
       <c r="J45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2756</v>
+        <v>1133</v>
       </c>
       <c r="K45" s="12">
         <f t="shared" si="1"/>
-        <v>1.4673231871083257</v>
+        <v>-2.2433132010353796E-2</v>
       </c>
       <c r="L45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4616,23 +4616,23 @@
       </c>
       <c r="P45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q45" s="12">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>-0.75</v>
       </c>
       <c r="R45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1287</v>
+        <v>1292</v>
       </c>
       <c r="S45">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1240</v>
+        <v>1234</v>
       </c>
       <c r="T45" s="12">
         <f t="shared" si="4"/>
-        <v>-3.6519036519036541E-2</v>
+        <v>-4.4891640866873028E-2</v>
       </c>
       <c r="U45">
         <v>5</v>
@@ -4656,27 +4656,27 @@
       </c>
       <c r="F46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20752353.467917528</v>
+        <v>23670122.597009651</v>
       </c>
       <c r="G46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19574511.266347792</v>
+        <v>22653838.112997834</v>
       </c>
       <c r="H46" s="12">
         <f t="shared" si="0"/>
-        <v>-5.6757042202015384E-2</v>
+        <v>-4.2935328274987916E-2</v>
       </c>
       <c r="I46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="J46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1570</v>
+        <v>922</v>
       </c>
       <c r="K46" s="12">
         <f t="shared" si="1"/>
-        <v>0.69546436285097202</v>
+        <v>-8.6021505376343566E-3</v>
       </c>
       <c r="L46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="O46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4700,19 +4700,19 @@
       </c>
       <c r="Q46" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="S46">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="T46" s="12">
         <f t="shared" si="4"/>
-        <v>5.2143684820393998E-2</v>
+        <v>4.6242774566473965E-2</v>
       </c>
       <c r="U46">
         <v>4</v>
@@ -4736,27 +4736,27 @@
       </c>
       <c r="F47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>28496249.862501446</v>
+        <v>33891083.600854926</v>
       </c>
       <c r="G47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>34212070.475824885</v>
+        <v>39599121.530364431</v>
       </c>
       <c r="H47" s="12">
         <f t="shared" si="0"/>
-        <v>0.20058150251008833</v>
+        <v>0.16842299870770483</v>
       </c>
       <c r="I47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>985</v>
+        <v>1021</v>
       </c>
       <c r="J47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>465</v>
+        <v>1015</v>
       </c>
       <c r="K47" s="12">
         <f t="shared" si="1"/>
-        <v>-0.52791878172588835</v>
+        <v>-5.8765915768853594E-3</v>
       </c>
       <c r="L47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4772,27 +4772,27 @@
       </c>
       <c r="O47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q47" s="12">
         <f t="shared" si="3"/>
-        <v>-0.4</v>
+        <v>-0.55555555555555558</v>
       </c>
       <c r="R47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="S47">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="T47" s="12">
         <f t="shared" si="4"/>
-        <v>2.5152439024390238E-2</v>
+        <v>2.7480916030534264E-2</v>
       </c>
       <c r="U47">
         <v>6</v>
@@ -4816,27 +4816,27 @@
       </c>
       <c r="F48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15097189.995865844</v>
+        <v>17681002.320624005</v>
       </c>
       <c r="G48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17699580.139482781</v>
+        <v>20476254.373544708</v>
       </c>
       <c r="H48" s="12">
         <f t="shared" si="0"/>
-        <v>0.17237579604744768</v>
+        <v>0.15809352898846574</v>
       </c>
       <c r="I48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="J48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>233</v>
+        <v>393</v>
       </c>
       <c r="K48" s="12">
         <f t="shared" si="1"/>
-        <v>-0.37027027027027026</v>
+        <v>0.10393258426966301</v>
       </c>
       <c r="L48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="O48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4860,19 +4860,19 @@
       </c>
       <c r="Q48" s="12">
         <f t="shared" si="3"/>
-        <v>-0.5</v>
+        <v>-0.66666666666666674</v>
       </c>
       <c r="R48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="S48">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="T48" s="12">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.5104602510460206E-2</v>
       </c>
       <c r="U48">
         <v>1</v>
@@ -4896,15 +4896,15 @@
       </c>
       <c r="F49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16420270.784009542</v>
+        <v>18461149.150816448</v>
       </c>
       <c r="G49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12890327.304175895</v>
+        <v>14867632.890376093</v>
       </c>
       <c r="H49" s="12">
         <f t="shared" si="0"/>
-        <v>-0.21497474227228897</v>
+        <v>-0.19465290221553899</v>
       </c>
       <c r="I49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
@@ -4912,15 +4912,15 @@
       </c>
       <c r="J49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>211</v>
+        <v>312</v>
       </c>
       <c r="K49" s="12">
         <f t="shared" si="1"/>
-        <v>-0.29900332225913617</v>
+        <v>3.6544850498338777E-2</v>
       </c>
       <c r="L49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="N49" s="12">
         <f t="shared" si="2"/>
-        <v>-0.4285714285714286</v>
+        <v>-0.33333333333333337</v>
       </c>
       <c r="O49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="R49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="S49">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="T49" s="12">
         <f t="shared" si="4"/>
-        <v>2.9279279279279313E-2</v>
+        <v>3.863636363636358E-2</v>
       </c>
       <c r="U49">
         <v>5</v>
@@ -4976,27 +4976,27 @@
       </c>
       <c r="F50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13190676.148514977</v>
+        <v>15175187.024739441</v>
       </c>
       <c r="G50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11150973.143566536</v>
+        <v>12944386.16594301</v>
       </c>
       <c r="H50" s="12">
         <f t="shared" si="0"/>
-        <v>-0.15463217972932142</v>
+        <v>-0.14700318718706096</v>
       </c>
       <c r="I50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>372</v>
+        <v>349</v>
       </c>
       <c r="J50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>220</v>
+        <v>324</v>
       </c>
       <c r="K50" s="12">
         <f t="shared" si="1"/>
-        <v>-0.40860215053763438</v>
+        <v>-7.1633237822349538E-2</v>
       </c>
       <c r="L50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="O50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5020,19 +5020,19 @@
       </c>
       <c r="Q50" s="12">
         <f t="shared" si="3"/>
-        <v>-0.88888888888888884</v>
+        <v>-0.9</v>
       </c>
       <c r="R50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="S50">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="T50" s="12">
         <f t="shared" si="4"/>
-        <v>9.3896713615022609E-3</v>
+        <v>-1.1682242990654235E-2</v>
       </c>
       <c r="U50">
         <v>4</v>
@@ -5056,27 +5056,27 @@
       </c>
       <c r="F51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>28683571.11333501</v>
+        <v>32732404.044502798</v>
       </c>
       <c r="G51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>26199041.104115095</v>
+        <v>30650599.292324264</v>
       </c>
       <c r="H51" s="12">
         <f t="shared" si="0"/>
-        <v>-8.6618573377875374E-2</v>
+        <v>-6.3600728786927019E-2</v>
       </c>
       <c r="I51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>979</v>
+        <v>967</v>
       </c>
       <c r="J51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>661</v>
+        <v>938</v>
       </c>
       <c r="K51" s="12">
         <f t="shared" si="1"/>
-        <v>-0.32482124616956076</v>
+        <v>-2.9989658738366121E-2</v>
       </c>
       <c r="L51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5096,23 +5096,23 @@
       </c>
       <c r="P51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q51" s="12">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="S51">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1103</v>
+        <v>1108</v>
       </c>
       <c r="T51" s="12">
         <f t="shared" si="4"/>
-        <v>-2.2163120567375905E-2</v>
+        <v>-1.685891748003554E-2</v>
       </c>
       <c r="U51">
         <v>5</v>
@@ -5136,27 +5136,27 @@
       </c>
       <c r="F52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>30270197.395333569</v>
+        <v>34854256.338008754</v>
       </c>
       <c r="G52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>25284897.300338056</v>
+        <v>29971764.592281073</v>
       </c>
       <c r="H52" s="12">
         <f t="shared" si="0"/>
-        <v>-0.16469334606202612</v>
+        <v>-0.14008308478535225</v>
       </c>
       <c r="I52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>951</v>
+        <v>1018</v>
       </c>
       <c r="J52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>715</v>
+        <v>943</v>
       </c>
       <c r="K52" s="12">
         <f t="shared" si="1"/>
-        <v>-0.24815983175604628</v>
+        <v>-7.3673870333988201E-2</v>
       </c>
       <c r="L52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5172,27 +5172,27 @@
       </c>
       <c r="O52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q52" s="12">
         <f t="shared" si="3"/>
-        <v>-0.44444444444444442</v>
+        <v>-0.4</v>
       </c>
       <c r="R52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="S52">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>998</v>
+        <v>1004</v>
       </c>
       <c r="T52" s="12">
         <f t="shared" si="4"/>
-        <v>4.5026178010471263E-2</v>
+        <v>5.6842105263157805E-2</v>
       </c>
       <c r="U52">
         <v>4</v>
@@ -5216,27 +5216,27 @@
       </c>
       <c r="F53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>38883489.20395907</v>
+        <v>46006855.693857841</v>
       </c>
       <c r="G53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>49694243.711567715</v>
+        <v>57135591.312040411</v>
       </c>
       <c r="H53" s="12">
         <f t="shared" si="0"/>
-        <v>0.27802943431598992</v>
+        <v>0.24189298421600913</v>
       </c>
       <c r="I53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1670</v>
+        <v>1410</v>
       </c>
       <c r="J53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1226</v>
+        <v>1660</v>
       </c>
       <c r="K53" s="12">
         <f t="shared" si="1"/>
-        <v>-0.26586826347305392</v>
+        <v>0.17730496453900702</v>
       </c>
       <c r="L53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5252,19 +5252,19 @@
       </c>
       <c r="O53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q53" s="12">
         <f t="shared" si="3"/>
-        <v>-0.82352941176470584</v>
+        <v>-0.77142857142857146</v>
       </c>
       <c r="R53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2219</v>
+        <v>2212</v>
       </c>
       <c r="S53">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="T53" s="12">
         <f t="shared" si="4"/>
-        <v>-6.9400630914826511E-2</v>
+        <v>-6.6455696202531667E-2</v>
       </c>
       <c r="U53">
         <v>8</v>
@@ -5296,27 +5296,27 @@
       </c>
       <c r="F54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14059897.113616962</v>
+        <v>15925948.807056723</v>
       </c>
       <c r="G54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12002259.173613898</v>
+        <v>14278357.522577465</v>
       </c>
       <c r="H54" s="12">
         <f t="shared" si="0"/>
-        <v>-0.14634800833714834</v>
+        <v>-0.10345325760115576</v>
       </c>
       <c r="I54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="J54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>453</v>
+        <v>528</v>
       </c>
       <c r="K54" s="12">
         <f t="shared" si="1"/>
-        <v>-0.21490467937608315</v>
+        <v>-7.3684210526315796E-2</v>
       </c>
       <c r="L54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5332,7 +5332,7 @@
       </c>
       <c r="O54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5340,19 +5340,19 @@
       </c>
       <c r="Q54" s="12">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="R54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="S54">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="T54" s="12">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-1.0233918128654929E-2</v>
       </c>
       <c r="U54">
         <v>2</v>
@@ -5376,31 +5376,31 @@
       </c>
       <c r="F55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20686122.966544252</v>
+        <v>23907515.938926905</v>
       </c>
       <c r="G55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21289344.203055624</v>
+        <v>24722818.188481327</v>
       </c>
       <c r="H55" s="12">
         <f t="shared" si="0"/>
-        <v>2.9160671503643432E-2</v>
+        <v>3.4102340520745011E-2</v>
       </c>
       <c r="I55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="J55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>510</v>
+        <v>701</v>
       </c>
       <c r="K55" s="12">
         <f t="shared" si="1"/>
-        <v>-0.20684292379471225</v>
+        <v>9.1900311526479816E-2</v>
       </c>
       <c r="L55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -5408,31 +5408,31 @@
       </c>
       <c r="N55" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-0.16666666666666663</v>
       </c>
       <c r="O55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q55" s="12">
         <f t="shared" si="3"/>
-        <v>0.66666666666666674</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="R55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="S55">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="T55" s="12">
         <f t="shared" si="4"/>
-        <v>-8.0000000000000071E-3</v>
+        <v>-1.245753114382786E-2</v>
       </c>
       <c r="U55">
         <v>7</v>
@@ -5456,27 +5456,27 @@
       </c>
       <c r="F56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16863635.008035466</v>
+        <v>19219152.45467395</v>
       </c>
       <c r="G56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13013595.533991264</v>
+        <v>15491777.19412148</v>
       </c>
       <c r="H56" s="12">
         <f t="shared" si="0"/>
-        <v>-0.22830424592382781</v>
+        <v>-0.19394066774500252</v>
       </c>
       <c r="I56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="J56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>516</v>
+        <v>631</v>
       </c>
       <c r="K56" s="12">
         <f t="shared" si="1"/>
-        <v>-0.19248826291079812</v>
+        <v>-7.8616352201258399E-3</v>
       </c>
       <c r="L56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5492,27 +5492,27 @@
       </c>
       <c r="O56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q56" s="12">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="S56">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="T56" s="12">
         <f t="shared" si="4"/>
-        <v>-4.949238578680204E-2</v>
+        <v>-6.0453400503778343E-2</v>
       </c>
       <c r="U56">
         <v>3</v>
@@ -5536,27 +5536,27 @@
       </c>
       <c r="F57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>28509568.786117759</v>
+        <v>32693040.576812342</v>
       </c>
       <c r="G57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>27702105.186980639</v>
+        <v>32144751.183899943</v>
       </c>
       <c r="H57" s="12">
         <f t="shared" si="0"/>
-        <v>-2.8322546903280399E-2</v>
+        <v>-1.6770828997204834E-2</v>
       </c>
       <c r="I57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1010</v>
+        <v>1019</v>
       </c>
       <c r="J57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>807</v>
+        <v>937</v>
       </c>
       <c r="K57" s="12">
         <f t="shared" si="1"/>
-        <v>-0.20099009900990095</v>
+        <v>-8.0471050049067738E-2</v>
       </c>
       <c r="L57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="O57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5580,19 +5580,19 @@
       </c>
       <c r="Q57" s="12">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="R57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="S57">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="T57" s="12">
         <f t="shared" si="4"/>
-        <v>2.4051803885291489E-2</v>
+        <v>2.4029574861367919E-2</v>
       </c>
       <c r="U57">
         <v>3</v>
@@ -5616,27 +5616,27 @@
       </c>
       <c r="F58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>35146427.627709694</v>
+        <v>41135039.004691504</v>
       </c>
       <c r="G58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>33966036.339512989</v>
+        <v>40223865.983752102</v>
       </c>
       <c r="H58" s="12">
         <f t="shared" si="0"/>
-        <v>-3.3584957785754432E-2</v>
+        <v>-2.2150775664403377E-2</v>
       </c>
       <c r="I58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1404</v>
+        <v>1444</v>
       </c>
       <c r="J58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1441</v>
+        <v>1524</v>
       </c>
       <c r="K58" s="12">
         <f t="shared" si="1"/>
-        <v>2.6353276353276334E-2</v>
+        <v>5.5401662049861411E-2</v>
       </c>
       <c r="L58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5652,27 +5652,27 @@
       </c>
       <c r="O58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q58" s="12">
         <f t="shared" si="3"/>
-        <v>-0.33333333333333337</v>
+        <v>-0.44444444444444442</v>
       </c>
       <c r="R58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1340</v>
+        <v>1349</v>
       </c>
       <c r="S58">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1436</v>
+        <v>1462</v>
       </c>
       <c r="T58" s="12">
         <f t="shared" si="4"/>
-        <v>7.1641791044776193E-2</v>
+        <v>8.3765752409191929E-2</v>
       </c>
       <c r="U58">
         <v>4</v>
@@ -5696,27 +5696,27 @@
       </c>
       <c r="F59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18496571.488525391</v>
+        <v>21181066.675294984</v>
       </c>
       <c r="G59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18635735.040618103</v>
+        <v>21499850.705537871</v>
       </c>
       <c r="H59" s="12">
         <f t="shared" si="0"/>
-        <v>7.5237485054484576E-3</v>
+        <v>1.5050423811502789E-2</v>
       </c>
       <c r="I59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>693</v>
+        <v>717</v>
       </c>
       <c r="J59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>648</v>
+        <v>726</v>
       </c>
       <c r="K59" s="12">
         <f t="shared" si="1"/>
-        <v>-6.4935064935064957E-2</v>
+        <v>1.2552301255230214E-2</v>
       </c>
       <c r="L59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5744,15 +5744,15 @@
       </c>
       <c r="R59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="S59">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="T59" s="12">
         <f t="shared" si="4"/>
-        <v>-3.8610038610038533E-3</v>
+        <v>-5.1746442432082373E-3</v>
       </c>
       <c r="U59">
         <v>3</v>
@@ -5776,15 +5776,15 @@
       </c>
       <c r="F60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21311583.419039447</v>
+        <v>24380650.130268615</v>
       </c>
       <c r="G60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20855323.597276349</v>
+        <v>24041232.874499574</v>
       </c>
       <c r="H60" s="12">
         <f t="shared" si="0"/>
-        <v>-2.1409006209997639E-2</v>
+        <v>-1.3921583467032095E-2</v>
       </c>
       <c r="I60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
@@ -5792,11 +5792,11 @@
       </c>
       <c r="J60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>450</v>
+        <v>485</v>
       </c>
       <c r="K60" s="12">
         <f t="shared" si="1"/>
-        <v>-6.6225165562914245E-3</v>
+        <v>7.0640176600441418E-2</v>
       </c>
       <c r="L60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="O60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5820,19 +5820,19 @@
       </c>
       <c r="Q60" s="12">
         <f t="shared" si="3"/>
-        <v>1.3333333333333335</v>
+        <v>0.75</v>
       </c>
       <c r="R60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="S60">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>651</v>
+        <v>642</v>
       </c>
       <c r="T60" s="12">
         <f t="shared" si="4"/>
-        <v>-5.6521739130434789E-2</v>
+        <v>-7.3593073593073544E-2</v>
       </c>
       <c r="U60">
         <v>10</v>
@@ -5856,27 +5856,27 @@
       </c>
       <c r="F61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>52066758.950409554</v>
+        <v>61721106.397677347</v>
       </c>
       <c r="G61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>67354281.232562438</v>
+        <v>78146220.43496713</v>
       </c>
       <c r="H61" s="12">
         <f t="shared" si="0"/>
-        <v>0.29361386401472256</v>
+        <v>0.26611826968007635</v>
       </c>
       <c r="I61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1661</v>
+        <v>1673</v>
       </c>
       <c r="J61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1641</v>
+        <v>1781</v>
       </c>
       <c r="K61" s="12">
         <f t="shared" si="1"/>
-        <v>-1.2040939193257105E-2</v>
+        <v>6.4554692169754846E-2</v>
       </c>
       <c r="L61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5892,27 +5892,27 @@
       </c>
       <c r="O61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q61" s="12">
         <f t="shared" si="3"/>
-        <v>0.125</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="R61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2027</v>
+        <v>2023</v>
       </c>
       <c r="S61">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1983</v>
+        <v>1992</v>
       </c>
       <c r="T61" s="12">
         <f t="shared" si="4"/>
-        <v>-2.1706956092747864E-2</v>
+        <v>-1.5323776569451275E-2</v>
       </c>
       <c r="U61">
         <v>10</v>
@@ -5936,27 +5936,27 @@
       </c>
       <c r="F62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>50435773.987107798</v>
+        <v>58992955.728539579</v>
       </c>
       <c r="G62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>49454368.591136239</v>
+        <v>57962386.104648069</v>
       </c>
       <c r="H62" s="12">
         <f t="shared" si="0"/>
-        <v>-1.9458517603445968E-2</v>
+        <v>-1.7469367506075639E-2</v>
       </c>
       <c r="I62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1117</v>
+        <v>1192</v>
       </c>
       <c r="J62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1265</v>
+        <v>1183</v>
       </c>
       <c r="K62" s="12">
         <f t="shared" si="1"/>
-        <v>0.1324977618621308</v>
+        <v>-7.5503355704698016E-3</v>
       </c>
       <c r="L62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5972,15 +5972,15 @@
       </c>
       <c r="O62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="P62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q62" s="12">
         <f t="shared" si="3"/>
-        <v>-0.1428571428571429</v>
+        <v>-0.17647058823529416</v>
       </c>
       <c r="R62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -5988,11 +5988,11 @@
       </c>
       <c r="S62">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="T62" s="12">
         <f t="shared" si="4"/>
-        <v>-2.5246305418719195E-2</v>
+        <v>-2.4630541871921152E-2</v>
       </c>
       <c r="U62">
         <v>8</v>
@@ -6016,27 +6016,27 @@
       </c>
       <c r="F63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>32576705.122849252</v>
+        <v>37368994.644287363</v>
       </c>
       <c r="G63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>32506719.517589524</v>
+        <v>37583945.764142759</v>
       </c>
       <c r="H63" s="12">
         <f t="shared" si="0"/>
-        <v>-2.1483328346376673E-3</v>
+        <v>5.7521247735321523E-3</v>
       </c>
       <c r="I63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>759</v>
+        <v>777</v>
       </c>
       <c r="J63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="K63" s="12">
         <f t="shared" si="1"/>
-        <v>-3.2938076416337281E-2</v>
+        <v>-5.9202059202059232E-2</v>
       </c>
       <c r="L63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6056,23 +6056,23 @@
       </c>
       <c r="P63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q63" s="12">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="R63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="S63">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="T63" s="12">
         <f t="shared" si="4"/>
-        <v>2.4333719582850577E-2</v>
+        <v>3.6130536130536184E-2</v>
       </c>
       <c r="U63">
         <v>4</v>
@@ -6096,27 +6096,27 @@
       </c>
       <c r="F64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>46217872.902747199</v>
+        <v>53896987.492598519</v>
       </c>
       <c r="G64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>49572620.973607913</v>
+        <v>56760340.422445491</v>
       </c>
       <c r="H64" s="12">
         <f t="shared" si="0"/>
-        <v>7.2585514221302549E-2</v>
+        <v>5.3126400250852246E-2</v>
       </c>
       <c r="I64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1247</v>
+        <v>1261</v>
       </c>
       <c r="J64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1308</v>
+        <v>1296</v>
       </c>
       <c r="K64" s="12">
         <f t="shared" si="1"/>
-        <v>4.8917401764234203E-2</v>
+        <v>2.7755749405233843E-2</v>
       </c>
       <c r="L64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6132,27 +6132,27 @@
       </c>
       <c r="O64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q64" s="12">
         <f t="shared" si="3"/>
-        <v>8.2249999999999996</v>
+        <v>7.2666666666666675</v>
       </c>
       <c r="R64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1856</v>
+        <v>1847</v>
       </c>
       <c r="S64">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2317</v>
+        <v>2294</v>
       </c>
       <c r="T64" s="12">
         <f t="shared" si="4"/>
-        <v>0.24838362068965525</v>
+        <v>0.2420140768814294</v>
       </c>
       <c r="U64">
         <v>9</v>
@@ -6176,27 +6176,27 @@
       </c>
       <c r="F65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>3625270.0844115838</v>
+        <v>4177676.11918703</v>
       </c>
       <c r="G65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>1350194.3692348029</v>
+        <v>1830061.480065604</v>
       </c>
       <c r="H65" s="12">
         <f t="shared" si="0"/>
-        <v>-0.62756033680344325</v>
+        <v>-0.56194270980926797</v>
       </c>
       <c r="I65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="J65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="K65" s="12">
         <f t="shared" si="1"/>
-        <v>-6.0150375939849621E-2</v>
+        <v>-6.5843621399176988E-2</v>
       </c>
       <c r="L65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6224,15 +6224,15 @@
       </c>
       <c r="R65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="S65">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="T65" s="12">
         <f t="shared" si="4"/>
-        <v>-7.1428571428571397E-2</v>
+        <v>-6.8965517241379337E-2</v>
       </c>
       <c r="U65">
         <v>3</v>
@@ -6256,31 +6256,31 @@
       </c>
       <c r="F66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>37078833.059941009</v>
+        <v>42837442.990329213</v>
       </c>
       <c r="G66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>35144336.780402198</v>
+        <v>40358257.639780559</v>
       </c>
       <c r="H66" s="12">
         <f t="shared" si="0"/>
-        <v>-5.2172523240187618E-2</v>
+        <v>-5.7874260868192917E-2</v>
       </c>
       <c r="I66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1578</v>
+        <v>1639</v>
       </c>
       <c r="J66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1480</v>
+        <v>1413</v>
       </c>
       <c r="K66" s="12">
         <f t="shared" si="1"/>
-        <v>-6.2103929024081128E-2</v>
+        <v>-0.13788895668090295</v>
       </c>
       <c r="L66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -6288,31 +6288,31 @@
       </c>
       <c r="N66" s="12">
         <f t="shared" si="2"/>
-        <v>-0.1428571428571429</v>
+        <v>-0.25</v>
       </c>
       <c r="O66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q66" s="12">
         <f t="shared" si="3"/>
-        <v>2.5</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="R66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1754</v>
+        <v>1737</v>
       </c>
       <c r="S66">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1669</v>
+        <v>1660</v>
       </c>
       <c r="T66" s="12">
         <f t="shared" si="4"/>
-        <v>-4.8460661345495981E-2</v>
+        <v>-4.4329303396660857E-2</v>
       </c>
       <c r="U66">
         <v>6</v>
@@ -6336,27 +6336,27 @@
       </c>
       <c r="F67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14360464.125569835</v>
+        <v>17129997.41105824</v>
       </c>
       <c r="G67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16822352.835773688</v>
+        <v>19545247.766959641</v>
       </c>
       <c r="H67" s="12">
         <f t="shared" ref="H67:H85" si="5">IFERROR(G67/F67-1,0)</f>
-        <v>0.1714351770720477</v>
+        <v>0.14099537191653289</v>
       </c>
       <c r="I67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>545</v>
+        <v>590</v>
       </c>
       <c r="J67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>638</v>
+        <v>578</v>
       </c>
       <c r="K67" s="12">
         <f t="shared" ref="K67:K85" si="6">IFERROR(J67/I67-1,0)</f>
-        <v>0.17064220183486234</v>
+        <v>-2.033898305084747E-2</v>
       </c>
       <c r="L67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6388,11 +6388,11 @@
       </c>
       <c r="S67">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="T67" s="12">
         <f t="shared" ref="T67:T85" si="9">IFERROR(S67/R67-1,0)</f>
-        <v>0.10676691729323307</v>
+        <v>0.10977443609022552</v>
       </c>
       <c r="U67">
         <v>3</v>
@@ -6416,27 +6416,27 @@
       </c>
       <c r="F68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24699781.872286916</v>
+        <v>28510903.990744784</v>
       </c>
       <c r="G68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23886309.979035523</v>
+        <v>27871659.032617167</v>
       </c>
       <c r="H68" s="12">
         <f t="shared" si="5"/>
-        <v>-3.2934375593175025E-2</v>
+        <v>-2.2421069438385066E-2</v>
       </c>
       <c r="I68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>892</v>
+        <v>885</v>
       </c>
       <c r="J68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>842</v>
+        <v>984</v>
       </c>
       <c r="K68" s="12">
         <f t="shared" si="6"/>
-        <v>-5.6053811659192876E-2</v>
+        <v>0.11186440677966103</v>
       </c>
       <c r="L68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6456,23 +6456,23 @@
       </c>
       <c r="P68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q68" s="12">
         <f t="shared" si="8"/>
-        <v>-0.13636363636363635</v>
+        <v>-4.5454545454545414E-2</v>
       </c>
       <c r="R68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1322</v>
+        <v>1307</v>
       </c>
       <c r="S68">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="T68" s="12">
         <f t="shared" si="9"/>
-        <v>3.4039334341906313E-2</v>
+        <v>4.7436878347360434E-2</v>
       </c>
       <c r="U68">
         <v>4</v>
@@ -6496,27 +6496,27 @@
       </c>
       <c r="F69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14040754.724470759</v>
+        <v>15593757.28553294</v>
       </c>
       <c r="G69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14655444.982134709</v>
+        <v>17271089.170965463</v>
       </c>
       <c r="H69" s="12">
         <f t="shared" si="5"/>
-        <v>4.3779004029793622E-2</v>
+        <v>0.10756431915152742</v>
       </c>
       <c r="I69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1671</v>
+        <v>1312</v>
       </c>
       <c r="J69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>982</v>
+        <v>1190</v>
       </c>
       <c r="K69" s="12">
         <f t="shared" si="6"/>
-        <v>-0.41232794733692402</v>
+        <v>-9.2987804878048808E-2</v>
       </c>
       <c r="L69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="O69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -6540,19 +6540,19 @@
       </c>
       <c r="Q69" s="12">
         <f t="shared" si="8"/>
-        <v>-0.6</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="R69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1397</v>
+        <v>1386</v>
       </c>
       <c r="S69">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1283</v>
+        <v>1265</v>
       </c>
       <c r="T69" s="12">
         <f t="shared" si="9"/>
-        <v>-8.1603435934144541E-2</v>
+        <v>-8.7301587301587324E-2</v>
       </c>
       <c r="U69">
         <v>4</v>
@@ -6576,27 +6576,27 @@
       </c>
       <c r="F70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>42772224.122835599</v>
+        <v>50258291.499809645</v>
       </c>
       <c r="G70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>43224353.113018826</v>
+        <v>50078251.351593465</v>
       </c>
       <c r="H70" s="12">
         <f t="shared" si="5"/>
-        <v>1.0570621459496277E-2</v>
+        <v>-3.5822974248311823E-3</v>
       </c>
       <c r="I70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1397</v>
+        <v>1364</v>
       </c>
       <c r="J70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1213</v>
+        <v>1198</v>
       </c>
       <c r="K70" s="12">
         <f t="shared" si="6"/>
-        <v>-0.13171080887616315</v>
+        <v>-0.1217008797653959</v>
       </c>
       <c r="L70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6616,23 +6616,23 @@
       </c>
       <c r="P70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q70" s="12">
         <f t="shared" si="8"/>
-        <v>0.60000000000000009</v>
+        <v>1</v>
       </c>
       <c r="R70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="S70">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1745</v>
+        <v>1753</v>
       </c>
       <c r="T70" s="12">
         <f t="shared" si="9"/>
-        <v>1.7221584385762601E-3</v>
+        <v>7.4712643678160884E-3</v>
       </c>
       <c r="U70">
         <v>4</v>
@@ -6656,27 +6656,27 @@
       </c>
       <c r="F71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9589492.6070907712</v>
+        <v>11124898.409664072</v>
       </c>
       <c r="G71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8720745.3927304987</v>
+        <v>10184693.362073636</v>
       </c>
       <c r="H71" s="12">
         <f t="shared" si="5"/>
-        <v>-9.0593658075078354E-2</v>
+        <v>-8.451358502057793E-2</v>
       </c>
       <c r="I71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>557</v>
+        <v>515</v>
       </c>
       <c r="J71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>629</v>
+        <v>432</v>
       </c>
       <c r="K71" s="12">
         <f t="shared" si="6"/>
-        <v>0.12926391382405744</v>
+        <v>-0.16116504854368929</v>
       </c>
       <c r="L71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6704,7 +6704,7 @@
       </c>
       <c r="R71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="S71">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="T71" s="12">
         <f t="shared" si="9"/>
-        <v>6.6252587991718404E-2</v>
+        <v>4.0404040404040442E-2</v>
       </c>
       <c r="U71">
         <v>2</v>
@@ -6736,27 +6736,27 @@
       </c>
       <c r="F72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14782444.521858055</v>
+        <v>16955552.557962589</v>
       </c>
       <c r="G72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13423851.621452449</v>
+        <v>15810033.870585823</v>
       </c>
       <c r="H72" s="12">
         <f t="shared" si="5"/>
-        <v>-9.1905834545614074E-2</v>
+        <v>-6.7560091802423283E-2</v>
       </c>
       <c r="I72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>822</v>
+        <v>806</v>
       </c>
       <c r="J72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>669</v>
+        <v>1000</v>
       </c>
       <c r="K72" s="12">
         <f t="shared" si="6"/>
-        <v>-0.18613138686131392</v>
+        <v>0.2406947890818858</v>
       </c>
       <c r="L72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="O72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -6780,19 +6780,19 @@
       </c>
       <c r="Q72" s="12">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>-0.33333333333333337</v>
       </c>
       <c r="R72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="S72">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="T72" s="12">
         <f t="shared" si="9"/>
-        <v>-1.8909899888765347E-2</v>
+        <v>-1.3377926421404673E-2</v>
       </c>
       <c r="U72">
         <v>3</v>
@@ -6816,27 +6816,27 @@
       </c>
       <c r="F73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9926102.0989064872</v>
+        <v>12369088.577015188</v>
       </c>
       <c r="G73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13414443.231452348</v>
+        <v>15807488.14342864</v>
       </c>
       <c r="H73" s="12">
         <f t="shared" si="5"/>
-        <v>0.35143111543555006</v>
+        <v>0.2779832600441432</v>
       </c>
       <c r="I73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>493</v>
+        <v>528</v>
       </c>
       <c r="J73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>485</v>
+        <v>510</v>
       </c>
       <c r="K73" s="12">
         <f t="shared" si="6"/>
-        <v>-1.6227180527383367E-2</v>
+        <v>-3.4090909090909061E-2</v>
       </c>
       <c r="L73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6864,15 +6864,15 @@
       </c>
       <c r="R73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="S73">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="T73" s="12">
         <f t="shared" si="9"/>
-        <v>-5.507246376811592E-2</v>
+        <v>-4.9707602339181256E-2</v>
       </c>
       <c r="U73">
         <v>7</v>
@@ -6896,27 +6896,27 @@
       </c>
       <c r="F74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9748712.1952629611</v>
+        <v>11378936.90622247</v>
       </c>
       <c r="G74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11048829.612400329</v>
+        <v>12568715.058400322</v>
       </c>
       <c r="H74" s="12">
         <f t="shared" si="5"/>
-        <v>0.13336299103886895</v>
+        <v>0.10455969322821645</v>
       </c>
       <c r="I74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>701</v>
+        <v>736</v>
       </c>
       <c r="J74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="K74" s="12">
         <f t="shared" si="6"/>
-        <v>1.2838801711840153E-2</v>
+        <v>-4.6195652173913082E-2</v>
       </c>
       <c r="L74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6932,27 +6932,27 @@
       </c>
       <c r="O74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q74" s="12">
         <f t="shared" si="8"/>
-        <v>0.66666666666666674</v>
+        <v>0.5</v>
       </c>
       <c r="R74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="S74">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>601</v>
+        <v>612</v>
       </c>
       <c r="T74" s="12">
         <f t="shared" si="9"/>
-        <v>1.6920473773265554E-2</v>
+        <v>2.1702838063438978E-2</v>
       </c>
       <c r="U74">
         <v>2</v>
@@ -6976,31 +6976,31 @@
       </c>
       <c r="F75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11180752.377334528</v>
+        <v>12943551.285408163</v>
       </c>
       <c r="G75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11874682.330901796</v>
+        <v>13584670.070504978</v>
       </c>
       <c r="H75" s="12">
         <f t="shared" si="5"/>
-        <v>6.2064692084049078E-2</v>
+        <v>4.9531907508225892E-2</v>
       </c>
       <c r="I75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>391</v>
+        <v>425</v>
       </c>
       <c r="J75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>251</v>
+        <v>463</v>
       </c>
       <c r="K75" s="12">
         <f t="shared" si="6"/>
-        <v>-0.35805626598465479</v>
+        <v>8.9411764705882302E-2</v>
       </c>
       <c r="L75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -7008,31 +7008,31 @@
       </c>
       <c r="N75" s="12">
         <f t="shared" si="7"/>
-        <v>0.39999999999999991</v>
+        <v>0.16666666666666674</v>
       </c>
       <c r="O75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q75" s="12">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
       <c r="R75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="S75">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="T75" s="12">
         <f t="shared" si="9"/>
-        <v>9.0293453724605843E-3</v>
+        <v>6.8027210884353817E-3</v>
       </c>
       <c r="U75">
         <v>1</v>
@@ -7056,27 +7056,27 @@
       </c>
       <c r="F76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>31391312.242365938</v>
+        <v>36997824.771402493</v>
       </c>
       <c r="G76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>31274170.374765057</v>
+        <v>36158999.173775911</v>
       </c>
       <c r="H76" s="12">
         <f t="shared" si="5"/>
-        <v>-3.7316652039408593E-3</v>
+        <v>-2.2672295001379461E-2</v>
       </c>
       <c r="I76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>774</v>
+        <v>784</v>
       </c>
       <c r="J76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>735</v>
+        <v>562</v>
       </c>
       <c r="K76" s="12">
         <f t="shared" si="6"/>
-        <v>-5.0387596899224785E-2</v>
+        <v>-0.28316326530612246</v>
       </c>
       <c r="L76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7092,27 +7092,27 @@
       </c>
       <c r="O76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q76" s="12">
         <f t="shared" si="8"/>
-        <v>-0.19999999999999996</v>
+        <v>-0.16666666666666663</v>
       </c>
       <c r="R76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="S76">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>942</v>
+        <v>928</v>
       </c>
       <c r="T76" s="12">
         <f t="shared" si="9"/>
-        <v>-3.6809815950920255E-2</v>
+        <v>-4.5267489711934172E-2</v>
       </c>
       <c r="U76">
         <v>4</v>
@@ -7136,27 +7136,27 @@
       </c>
       <c r="F77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18988654.507708855</v>
+        <v>21724320.235075474</v>
       </c>
       <c r="G77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18899937.995990712</v>
+        <v>21556780.627003729</v>
       </c>
       <c r="H77" s="12">
         <f t="shared" si="5"/>
-        <v>-4.6720799350015163E-3</v>
+        <v>-7.7120759710234132E-3</v>
       </c>
       <c r="I77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="J77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2118</v>
+        <v>715</v>
       </c>
       <c r="K77" s="12">
         <f t="shared" si="6"/>
-        <v>1.9375866851595007</v>
+        <v>-2.0547945205479423E-2</v>
       </c>
       <c r="L77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7184,7 +7184,7 @@
       </c>
       <c r="R77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="S77">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -7192,7 +7192,7 @@
       </c>
       <c r="T77" s="12">
         <f t="shared" si="9"/>
-        <v>-2.1546261089987362E-2</v>
+        <v>-2.0304568527918732E-2</v>
       </c>
       <c r="U77">
         <v>3</v>
@@ -7216,27 +7216,27 @@
       </c>
       <c r="F78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15805318.288240936</v>
+        <v>18436711.83211863</v>
       </c>
       <c r="G78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15125684.077691879</v>
+        <v>17554926.06836798</v>
       </c>
       <c r="H78" s="12">
         <f t="shared" si="5"/>
-        <v>-4.3000349512398062E-2</v>
+        <v>-4.7827713085718981E-2</v>
       </c>
       <c r="I78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>899</v>
+        <v>918</v>
       </c>
       <c r="J78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>855</v>
+        <v>866</v>
       </c>
       <c r="K78" s="12">
         <f t="shared" si="6"/>
-        <v>-4.8943270300333741E-2</v>
+        <v>-5.6644880174291923E-2</v>
       </c>
       <c r="L78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="P78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q78" s="12">
         <f t="shared" si="8"/>
@@ -7268,11 +7268,11 @@
       </c>
       <c r="S78">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="T78" s="12">
         <f t="shared" si="9"/>
-        <v>2.0191285866099973E-2</v>
+        <v>1.8065887353878818E-2</v>
       </c>
       <c r="U78">
         <v>3</v>
@@ -7296,27 +7296,27 @@
       </c>
       <c r="F79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17980106.353986889</v>
+        <v>20675882.787564185</v>
       </c>
       <c r="G79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14533223.238636944</v>
+        <v>17375063.532339539</v>
       </c>
       <c r="H79" s="12">
         <f t="shared" si="5"/>
-        <v>-0.19170537968401036</v>
+        <v>-0.15964586804535241</v>
       </c>
       <c r="I79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>813</v>
+        <v>796</v>
       </c>
       <c r="J79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>842</v>
+        <v>790</v>
       </c>
       <c r="K79" s="12">
         <f t="shared" si="6"/>
-        <v>3.5670356703566997E-2</v>
+        <v>-7.5376884422110324E-3</v>
       </c>
       <c r="L79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="O79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -7340,19 +7340,19 @@
       </c>
       <c r="Q79" s="12">
         <f t="shared" si="8"/>
-        <v>-0.75</v>
+        <v>-0.8</v>
       </c>
       <c r="R79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1013</v>
+        <v>1018</v>
       </c>
       <c r="S79">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="T79" s="12">
         <f t="shared" si="9"/>
-        <v>-1.6781836130306038E-2</v>
+        <v>-2.3575638506876273E-2</v>
       </c>
       <c r="U79">
         <v>3</v>
@@ -7376,27 +7376,27 @@
       </c>
       <c r="F80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18620384.172661994</v>
+        <v>21557213.686589696</v>
       </c>
       <c r="G80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19678596.684385128</v>
+        <v>23095754.28563593</v>
       </c>
       <c r="H80" s="12">
         <f t="shared" si="5"/>
-        <v>5.6830863526262654E-2</v>
+        <v>7.1370104755390074E-2</v>
       </c>
       <c r="I80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>746</v>
+        <v>715</v>
       </c>
       <c r="J80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>408</v>
+        <v>796</v>
       </c>
       <c r="K80" s="12">
         <f t="shared" si="6"/>
-        <v>-0.45308310991957101</v>
+        <v>0.11328671328671325</v>
       </c>
       <c r="L80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="O80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -7420,19 +7420,19 @@
       </c>
       <c r="Q80" s="12">
         <f t="shared" si="8"/>
-        <v>-0.33333333333333337</v>
+        <v>-0.5</v>
       </c>
       <c r="R80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="S80">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="T80" s="12">
         <f t="shared" si="9"/>
-        <v>9.3333333333334156E-3</v>
+        <v>2.008032128514059E-2</v>
       </c>
       <c r="U80">
         <v>3</v>
@@ -7456,27 +7456,27 @@
       </c>
       <c r="F81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8842619.4253564347</v>
+        <v>9879876.8658112064</v>
       </c>
       <c r="G81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9379650.8358766995</v>
+        <v>10738264.072177881</v>
       </c>
       <c r="H81" s="12">
         <f t="shared" si="5"/>
-        <v>6.0732163704830811E-2</v>
+        <v>8.6882379003839549E-2</v>
       </c>
       <c r="I81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="J81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>540</v>
+        <v>510</v>
       </c>
       <c r="K81" s="12">
         <f t="shared" si="6"/>
-        <v>3.8461538461538547E-2</v>
+        <v>-3.9548022598870025E-2</v>
       </c>
       <c r="L81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7504,15 +7504,15 @@
       </c>
       <c r="R81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="S81">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="T81" s="12">
         <f t="shared" si="9"/>
-        <v>1.7605633802817433E-3</v>
+        <v>1.7699115044247371E-3</v>
       </c>
       <c r="U81">
         <v>1</v>
@@ -7536,27 +7536,27 @@
       </c>
       <c r="F82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>35571479.183830611</v>
+        <v>41733546.900617406</v>
       </c>
       <c r="G82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>38722670.295691326</v>
+        <v>45577456.506966852</v>
       </c>
       <c r="H82" s="12">
         <f t="shared" si="5"/>
-        <v>8.8587575894035986E-2</v>
+        <v>9.2105988870372801E-2</v>
       </c>
       <c r="I82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1321</v>
+        <v>1295</v>
       </c>
       <c r="J82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1316</v>
+        <v>1232</v>
       </c>
       <c r="K82" s="12">
         <f t="shared" si="6"/>
-        <v>-3.7850113550340625E-3</v>
+        <v>-4.8648648648648596E-2</v>
       </c>
       <c r="L82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7572,27 +7572,27 @@
       </c>
       <c r="O82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q82" s="12">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.85714285714285721</v>
       </c>
       <c r="R82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1722</v>
+        <v>1715</v>
       </c>
       <c r="S82">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1762</v>
+        <v>1765</v>
       </c>
       <c r="T82" s="12">
         <f t="shared" si="9"/>
-        <v>2.3228803716608626E-2</v>
+        <v>2.9154518950437414E-2</v>
       </c>
       <c r="U82">
         <v>2</v>
@@ -7616,27 +7616,27 @@
       </c>
       <c r="F83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10381530.962787962</v>
+        <v>11696048.467407828</v>
       </c>
       <c r="G83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8630087.2264204156</v>
+        <v>10779677.36682423</v>
       </c>
       <c r="H83" s="12">
         <f t="shared" si="5"/>
-        <v>-0.1687076542607735</v>
+        <v>-7.8348777635211975E-2</v>
       </c>
       <c r="I83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>673</v>
+        <v>901</v>
       </c>
       <c r="J83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>734</v>
+        <v>636</v>
       </c>
       <c r="K83" s="12">
         <f t="shared" si="6"/>
-        <v>9.0638930163447151E-2</v>
+        <v>-0.29411764705882348</v>
       </c>
       <c r="L83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7652,7 +7652,7 @@
       </c>
       <c r="O83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -7664,15 +7664,15 @@
       </c>
       <c r="R83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="S83">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="T83" s="12">
         <f t="shared" si="9"/>
-        <v>-0.14155251141552516</v>
+        <v>-0.13798449612403096</v>
       </c>
       <c r="U83">
         <v>2</v>
@@ -7696,27 +7696,27 @@
       </c>
       <c r="F84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17326990.22087634</v>
+        <v>19852232.268611159</v>
       </c>
       <c r="G84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17500296.393373366</v>
+        <v>19960572.610525478</v>
       </c>
       <c r="H84" s="12">
         <f t="shared" si="5"/>
-        <v>1.000209328266477E-2</v>
+        <v>5.4573380186377918E-3</v>
       </c>
       <c r="I84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1110</v>
+        <v>551</v>
       </c>
       <c r="J84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>408</v>
+        <v>569</v>
       </c>
       <c r="K84" s="12">
         <f t="shared" si="6"/>
-        <v>-0.63243243243243241</v>
+        <v>3.2667876588021727E-2</v>
       </c>
       <c r="L84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7744,15 +7744,15 @@
       </c>
       <c r="R84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="S84">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="T84" s="12">
         <f t="shared" si="9"/>
-        <v>4.2071197411003292E-2</v>
+        <v>3.8585209003215493E-2</v>
       </c>
       <c r="U84">
         <v>7</v>
@@ -7776,27 +7776,27 @@
       </c>
       <c r="F85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5027836.3395618377</v>
+        <v>5664274.1859372323</v>
       </c>
       <c r="G85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4318945.0415773364</v>
+        <v>4924927.4812102551</v>
       </c>
       <c r="H85" s="12">
         <f t="shared" si="5"/>
-        <v>-0.14099331205483889</v>
+        <v>-0.13052805716265692</v>
       </c>
       <c r="I85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="J85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>380</v>
+        <v>301</v>
       </c>
       <c r="K85" s="12">
         <f t="shared" si="6"/>
-        <v>0.21405750798722045</v>
+        <v>-3.2154340836012874E-2</v>
       </c>
       <c r="L85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="O85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -7820,19 +7820,19 @@
       </c>
       <c r="Q85" s="12">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="S85">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="T85" s="12">
         <f t="shared" si="9"/>
-        <v>1.9553072625698276E-2</v>
+        <v>-2.8089887640448952E-3</v>
       </c>
       <c r="U85">
         <v>2</v>
@@ -7865,43 +7865,43 @@
       <c r="A3" s="11"/>
       <c r="B3" s="11">
         <f t="shared" ref="B3:K3" si="0">SUBTOTAL(9,B6:B90)</f>
-        <v>83880</v>
+        <v>83741</v>
       </c>
       <c r="C3" s="11">
         <f t="shared" si="0"/>
-        <v>516</v>
+        <v>600</v>
       </c>
       <c r="D3" s="11">
         <f t="shared" si="0"/>
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="E3" s="11">
         <f t="shared" si="0"/>
-        <v>70113</v>
+        <v>72428</v>
       </c>
       <c r="F3" s="11">
         <f t="shared" si="0"/>
-        <v>1811393405.3401802</v>
+        <v>2094137380.8293059</v>
       </c>
       <c r="G3" s="11">
         <f t="shared" si="0"/>
-        <v>84798</v>
+        <v>84619</v>
       </c>
       <c r="H3" s="11">
         <f t="shared" si="0"/>
-        <v>996</v>
+        <v>1046</v>
       </c>
       <c r="I3" s="11">
         <f t="shared" si="0"/>
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J3" s="11">
         <f t="shared" si="0"/>
-        <v>71269</v>
+        <v>70425</v>
       </c>
       <c r="K3" s="11">
         <f t="shared" si="0"/>
-        <v>1792933331.470099</v>
+        <v>2082336634.7778966</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -7961,7 +7961,7 @@
         <v>117</v>
       </c>
       <c r="B6" s="10">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C6" s="10">
         <v>3</v>
@@ -7970,13 +7970,13 @@
         <v>2</v>
       </c>
       <c r="E6" s="10">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="F6" s="10">
-        <v>8904722.9124635179</v>
+        <v>10081819.681227973</v>
       </c>
       <c r="G6" s="10">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="H6" s="10">
         <v>0</v>
@@ -7985,10 +7985,10 @@
         <v>2</v>
       </c>
       <c r="J6" s="10">
-        <v>351</v>
+        <v>386</v>
       </c>
       <c r="K6" s="10">
-        <v>8015662.5391808543</v>
+        <v>9328903.5811648574</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
@@ -8005,25 +8005,25 @@
         <v>1</v>
       </c>
       <c r="E7" s="10">
-        <v>582</v>
+        <v>550</v>
       </c>
       <c r="F7" s="10">
-        <v>11077997.986731406</v>
+        <v>12646261.849610392</v>
       </c>
       <c r="G7" s="10">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="H7" s="10">
+        <v>4</v>
+      </c>
+      <c r="I7" s="10">
         <v>3</v>
       </c>
-      <c r="I7" s="10">
-        <v>2</v>
-      </c>
       <c r="J7" s="10">
-        <v>493</v>
+        <v>1204</v>
       </c>
       <c r="K7" s="10">
-        <v>9594971.2209495213</v>
+        <v>10997989.293437231</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
@@ -8031,22 +8031,22 @@
         <v>119</v>
       </c>
       <c r="B8" s="10">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C8" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="10">
         <v>2</v>
       </c>
       <c r="E8" s="10">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="F8" s="10">
-        <v>10813572.180837341</v>
+        <v>12713958.118884431</v>
       </c>
       <c r="G8" s="10">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="H8" s="10">
         <v>6</v>
@@ -8055,10 +8055,10 @@
         <v>1</v>
       </c>
       <c r="J8" s="10">
-        <v>724</v>
+        <v>737</v>
       </c>
       <c r="K8" s="10">
-        <v>11700900.530808456</v>
+        <v>14219634.224562662</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
@@ -8066,34 +8066,34 @@
         <v>121</v>
       </c>
       <c r="B9" s="10">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="C9" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" s="10">
         <v>3</v>
       </c>
       <c r="E9" s="10">
-        <v>1053</v>
+        <v>1981</v>
       </c>
       <c r="F9" s="10">
-        <v>20569414.54593353</v>
+        <v>23642031.302799549</v>
       </c>
       <c r="G9" s="10">
-        <v>1208</v>
+        <v>1212</v>
       </c>
       <c r="H9" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9" s="10">
         <v>4</v>
       </c>
       <c r="J9" s="10">
-        <v>2035</v>
+        <v>1071</v>
       </c>
       <c r="K9" s="10">
-        <v>20538626.012221169</v>
+        <v>23896411.194066271</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
@@ -8101,7 +8101,7 @@
         <v>123</v>
       </c>
       <c r="B10" s="10">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C10" s="10">
         <v>1</v>
@@ -8110,13 +8110,13 @@
         <v>1</v>
       </c>
       <c r="E10" s="10">
-        <v>300</v>
+        <v>328</v>
       </c>
       <c r="F10" s="10">
-        <v>8172898.0041208696</v>
+        <v>9596873.4474547114</v>
       </c>
       <c r="G10" s="10">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="H10" s="10">
         <v>1</v>
@@ -8125,10 +8125,10 @@
         <v>1</v>
       </c>
       <c r="J10" s="10">
-        <v>395</v>
+        <v>361</v>
       </c>
       <c r="K10" s="10">
-        <v>9141121.1433764119</v>
+        <v>10735578.1970079</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
@@ -8136,7 +8136,7 @@
         <v>125</v>
       </c>
       <c r="B11" s="10">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C11" s="10">
         <v>2</v>
@@ -8145,13 +8145,13 @@
         <v>2</v>
       </c>
       <c r="E11" s="10">
-        <v>345</v>
+        <v>313</v>
       </c>
       <c r="F11" s="10">
-        <v>7758957.3293836992</v>
+        <v>8856040.2209448274</v>
       </c>
       <c r="G11" s="10">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="H11" s="10">
         <v>3</v>
@@ -8160,10 +8160,10 @@
         <v>2</v>
       </c>
       <c r="J11" s="10">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="K11" s="10">
-        <v>7747219.6709535951</v>
+        <v>8947473.0958644543</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -8171,7 +8171,7 @@
         <v>131</v>
       </c>
       <c r="B12" s="10">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="C12" s="10">
         <v>0</v>
@@ -8180,10 +8180,10 @@
         <v>1</v>
       </c>
       <c r="E12" s="10">
-        <v>508</v>
+        <v>481</v>
       </c>
       <c r="F12" s="10">
-        <v>9035790.3904993646</v>
+        <v>10119494.23898562</v>
       </c>
       <c r="G12" s="10">
         <v>595</v>
@@ -8195,10 +8195,10 @@
         <v>3</v>
       </c>
       <c r="J12" s="10">
-        <v>496</v>
+        <v>516</v>
       </c>
       <c r="K12" s="10">
-        <v>9130871.8624781035</v>
+        <v>10567198.582857665</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
@@ -8206,7 +8206,7 @@
         <v>133</v>
       </c>
       <c r="B13" s="10">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C13" s="10">
         <v>0</v>
@@ -8215,10 +8215,10 @@
         <v>1</v>
       </c>
       <c r="E13" s="10">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="F13" s="10">
-        <v>4009064.5599596188</v>
+        <v>4689917.3020850392</v>
       </c>
       <c r="G13" s="10">
         <v>168</v>
@@ -8230,10 +8230,10 @@
         <v>1</v>
       </c>
       <c r="J13" s="10">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="K13" s="10">
-        <v>4061429.297431434</v>
+        <v>4719781.875237532</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
@@ -8241,7 +8241,7 @@
         <v>141</v>
       </c>
       <c r="B14" s="10">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C14" s="10">
         <v>1</v>
@@ -8250,13 +8250,13 @@
         <v>0</v>
       </c>
       <c r="E14" s="10">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="F14" s="10">
-        <v>4114366.4045414459</v>
+        <v>4570511.2464642841</v>
       </c>
       <c r="G14" s="10">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H14" s="10">
         <v>1</v>
@@ -8265,10 +8265,10 @@
         <v>1</v>
       </c>
       <c r="J14" s="10">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="K14" s="10">
-        <v>834088.64330936898</v>
+        <v>1301677.642551824</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
@@ -8276,7 +8276,7 @@
         <v>135</v>
       </c>
       <c r="B15" s="10">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="C15" s="10">
         <v>0</v>
@@ -8285,13 +8285,13 @@
         <v>0</v>
       </c>
       <c r="E15" s="10">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="F15" s="10">
-        <v>6426679.2572523681</v>
+        <v>7208654.6195380623</v>
       </c>
       <c r="G15" s="10">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="H15" s="10">
         <v>1</v>
@@ -8300,10 +8300,10 @@
         <v>1</v>
       </c>
       <c r="J15" s="10">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="K15" s="10">
-        <v>8442751.4556307346</v>
+        <v>9475751.8262754045</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
@@ -8311,22 +8311,22 @@
         <v>143</v>
       </c>
       <c r="B16" s="10">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C16" s="10">
         <v>0</v>
       </c>
       <c r="D16" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="10">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F16" s="10">
-        <v>3076842.9337319238</v>
+        <v>3398341.1812919341</v>
       </c>
       <c r="G16" s="10">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="H16" s="10">
         <v>0</v>
@@ -8335,10 +8335,10 @@
         <v>2</v>
       </c>
       <c r="J16" s="10">
-        <v>263</v>
+        <v>424</v>
       </c>
       <c r="K16" s="10">
-        <v>3928722.993377714</v>
+        <v>4599522.8086553616</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -8346,7 +8346,7 @@
         <v>145</v>
       </c>
       <c r="B17" s="10">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C17" s="10">
         <v>7</v>
@@ -8355,13 +8355,13 @@
         <v>0</v>
       </c>
       <c r="E17" s="10">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F17" s="10">
-        <v>4106721.092204113</v>
+        <v>4634949.7732747439</v>
       </c>
       <c r="G17" s="10">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="H17" s="10">
         <v>1</v>
@@ -8370,10 +8370,10 @@
         <v>2</v>
       </c>
       <c r="J17" s="10">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="K17" s="10">
-        <v>4332106.5259726672</v>
+        <v>4996010.6418833202</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
@@ -8381,7 +8381,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="10">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="C18" s="10">
         <v>0</v>
@@ -8390,13 +8390,13 @@
         <v>1</v>
       </c>
       <c r="E18" s="10">
-        <v>16</v>
+        <v>999</v>
       </c>
       <c r="F18" s="10">
-        <v>7512212.0363657642</v>
+        <v>8173457.9071941637</v>
       </c>
       <c r="G18" s="10">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H18" s="10">
         <v>3</v>
@@ -8405,10 +8405,10 @@
         <v>3</v>
       </c>
       <c r="J18" s="10">
-        <v>1327</v>
+        <v>1223</v>
       </c>
       <c r="K18" s="10">
-        <v>15558073.085482126</v>
+        <v>19523999.849815324</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
@@ -8416,7 +8416,7 @@
         <v>45</v>
       </c>
       <c r="B19" s="10">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="C19" s="10">
         <v>0</v>
@@ -8425,13 +8425,13 @@
         <v>2</v>
       </c>
       <c r="E19" s="10">
-        <v>1102</v>
+        <v>922</v>
       </c>
       <c r="F19" s="10">
-        <v>30427161.100131635</v>
+        <v>33256265.103515387</v>
       </c>
       <c r="G19" s="10">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="H19" s="10">
         <v>1</v>
@@ -8440,10 +8440,10 @@
         <v>3</v>
       </c>
       <c r="J19" s="10">
-        <v>907</v>
+        <v>1013</v>
       </c>
       <c r="K19" s="10">
-        <v>29254917.109629303</v>
+        <v>34614044.554706417</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
@@ -8451,7 +8451,7 @@
         <v>47</v>
       </c>
       <c r="B20" s="10">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="C20" s="10">
         <v>2</v>
@@ -8460,25 +8460,25 @@
         <v>4</v>
       </c>
       <c r="E20" s="10">
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="F20" s="10">
-        <v>16637487.25802622</v>
+        <v>19360881.193097025</v>
       </c>
       <c r="G20" s="10">
         <v>1024</v>
       </c>
       <c r="H20" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I20" s="10">
         <v>5</v>
       </c>
       <c r="J20" s="10">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="K20" s="10">
-        <v>17104080.460517026</v>
+        <v>19707768.173094597</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
@@ -8486,34 +8486,34 @@
         <v>49</v>
       </c>
       <c r="B21" s="10">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="C21" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" s="10">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="F21" s="10">
-        <v>17060687.407777634</v>
+        <v>19456613.387876816</v>
       </c>
       <c r="G21" s="10">
-        <v>903</v>
+        <v>912</v>
       </c>
       <c r="H21" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I21" s="10">
         <v>3</v>
       </c>
       <c r="J21" s="10">
-        <v>681</v>
+        <v>654</v>
       </c>
       <c r="K21" s="10">
-        <v>12169391.271711731</v>
+        <v>14701576.182038048</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
@@ -8521,7 +8521,7 @@
         <v>51</v>
       </c>
       <c r="B22" s="10">
-        <v>2777</v>
+        <v>2745</v>
       </c>
       <c r="C22" s="10">
         <v>118</v>
@@ -8530,25 +8530,25 @@
         <v>10</v>
       </c>
       <c r="E22" s="10">
-        <v>1895</v>
+        <v>2123</v>
       </c>
       <c r="F22" s="10">
-        <v>57559835.304311313</v>
+        <v>66752926.934528187</v>
       </c>
       <c r="G22" s="10">
-        <v>2872</v>
+        <v>2837</v>
       </c>
       <c r="H22" s="10">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I22" s="10">
         <v>10</v>
       </c>
       <c r="J22" s="10">
-        <v>2091</v>
+        <v>2002</v>
       </c>
       <c r="K22" s="10">
-        <v>63483376.813367918</v>
+        <v>72814817.405791759</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
@@ -8565,25 +8565,25 @@
         <v>2</v>
       </c>
       <c r="E23" s="10">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="F23" s="10">
-        <v>32045023.177340128</v>
+        <v>36794577.136621326</v>
       </c>
       <c r="G23" s="10">
-        <v>1367</v>
+        <v>1375</v>
       </c>
       <c r="H23" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I23" s="10">
         <v>1</v>
       </c>
       <c r="J23" s="10">
-        <v>1143</v>
+        <v>1176</v>
       </c>
       <c r="K23" s="10">
-        <v>13732806.891209688</v>
+        <v>18253988.933064144</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
@@ -8591,34 +8591,34 @@
         <v>55</v>
       </c>
       <c r="B24" s="10">
-        <v>2999</v>
+        <v>3017</v>
       </c>
       <c r="C24" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D24" s="10">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E24" s="10">
-        <v>2472</v>
+        <v>2398</v>
       </c>
       <c r="F24" s="10">
-        <v>63795978.508467458</v>
+        <v>73829830.108036533</v>
       </c>
       <c r="G24" s="10">
-        <v>2972</v>
+        <v>2967</v>
       </c>
       <c r="H24" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I24" s="10">
         <v>10</v>
       </c>
       <c r="J24" s="10">
-        <v>2209</v>
+        <v>2168</v>
       </c>
       <c r="K24" s="10">
-        <v>62485638.947705641</v>
+        <v>72601988.544970065</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
@@ -8626,22 +8626,22 @@
         <v>67</v>
       </c>
       <c r="B25" s="10">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C25" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D25" s="10">
         <v>1</v>
       </c>
       <c r="E25" s="10">
-        <v>687</v>
+        <v>475</v>
       </c>
       <c r="F25" s="10">
-        <v>9011397.0943409987</v>
+        <v>10266236.082020912</v>
       </c>
       <c r="G25" s="10">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="H25" s="10">
         <v>4</v>
@@ -8650,10 +8650,10 @@
         <v>1</v>
       </c>
       <c r="J25" s="10">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="K25" s="10">
-        <v>9650938.5786911491</v>
+        <v>10855173.82160108</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
@@ -8661,34 +8661,34 @@
         <v>74</v>
       </c>
       <c r="B26" s="10">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="C26" s="10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D26" s="10">
         <v>1</v>
       </c>
       <c r="E26" s="10">
-        <v>1298</v>
+        <v>1251</v>
       </c>
       <c r="F26" s="10">
-        <v>24671664.355904289</v>
+        <v>28739105.010453988</v>
       </c>
       <c r="G26" s="10">
-        <v>1749</v>
+        <v>1717</v>
       </c>
       <c r="H26" s="10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I26" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26" s="10">
-        <v>1348</v>
+        <v>1281</v>
       </c>
       <c r="K26" s="10">
-        <v>25739797.312284291</v>
+        <v>29878204.248217441</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
@@ -8696,34 +8696,34 @@
         <v>70</v>
       </c>
       <c r="B27" s="10">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="C27" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D27" s="10">
         <v>1</v>
       </c>
       <c r="E27" s="10">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="F27" s="10">
-        <v>11251576.178390903</v>
+        <v>12792800.080579426</v>
       </c>
       <c r="G27" s="10">
         <v>877</v>
       </c>
       <c r="H27" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I27" s="10">
         <v>1</v>
       </c>
       <c r="J27" s="10">
-        <v>765</v>
+        <v>833</v>
       </c>
       <c r="K27" s="10">
-        <v>10264637.068090342</v>
+        <v>12026624.385429287</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
@@ -8731,7 +8731,7 @@
         <v>72</v>
       </c>
       <c r="B28" s="10">
-        <v>892</v>
+        <v>903</v>
       </c>
       <c r="C28" s="10">
         <v>1</v>
@@ -8740,13 +8740,13 @@
         <v>1</v>
       </c>
       <c r="E28" s="10">
-        <v>881</v>
+        <v>716</v>
       </c>
       <c r="F28" s="10">
-        <v>11850976.593486</v>
+        <v>14116105.390142018</v>
       </c>
       <c r="G28" s="10">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="H28" s="10">
         <v>5</v>
@@ -8755,10 +8755,10 @@
         <v>1</v>
       </c>
       <c r="J28" s="10">
-        <v>807</v>
+        <v>668</v>
       </c>
       <c r="K28" s="10">
-        <v>13079902.716852484</v>
+        <v>15041764.988150029</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
@@ -8766,7 +8766,7 @@
         <v>79</v>
       </c>
       <c r="B29" s="10">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="C29" s="10">
         <v>1</v>
@@ -8775,13 +8775,13 @@
         <v>0</v>
       </c>
       <c r="E29" s="10">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="F29" s="10">
-        <v>3490224.814658503</v>
+        <v>4085296.183992228</v>
       </c>
       <c r="G29" s="10">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="H29" s="10">
         <v>1</v>
@@ -8790,10 +8790,10 @@
         <v>2</v>
       </c>
       <c r="J29" s="10">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K29" s="10">
-        <v>2753796.6769717392</v>
+        <v>3252983.6141009722</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
@@ -8801,7 +8801,7 @@
         <v>109</v>
       </c>
       <c r="B30" s="10">
-        <v>1670</v>
+        <v>1664</v>
       </c>
       <c r="C30" s="10">
         <v>2</v>
@@ -8810,25 +8810,25 @@
         <v>5</v>
       </c>
       <c r="E30" s="10">
-        <v>1425</v>
+        <v>1346</v>
       </c>
       <c r="F30" s="10">
-        <v>29071248.072626371</v>
+        <v>32881334.951630816</v>
       </c>
       <c r="G30" s="10">
-        <v>1663</v>
+        <v>1644</v>
       </c>
       <c r="H30" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I30" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J30" s="10">
-        <v>1293</v>
+        <v>1478</v>
       </c>
       <c r="K30" s="10">
-        <v>24370086.898229964</v>
+        <v>28162389.603792943</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
@@ -8836,22 +8836,22 @@
         <v>111</v>
       </c>
       <c r="B31" s="10">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="C31" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" s="10">
         <v>1</v>
       </c>
       <c r="E31" s="10">
-        <v>647</v>
+        <v>634</v>
       </c>
       <c r="F31" s="10">
-        <v>19157411.185149383</v>
+        <v>22398496.405254211</v>
       </c>
       <c r="G31" s="10">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="H31" s="10">
         <v>1</v>
@@ -8860,10 +8860,10 @@
         <v>1</v>
       </c>
       <c r="J31" s="10">
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="K31" s="10">
-        <v>19821996.514491428</v>
+        <v>23291306.937544983</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
@@ -8880,13 +8880,13 @@
         <v>1</v>
       </c>
       <c r="E32" s="10">
-        <v>742</v>
+        <v>726</v>
       </c>
       <c r="F32" s="10">
-        <v>20847256.078643773</v>
+        <v>24190546.883645892</v>
       </c>
       <c r="G32" s="10">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="H32" s="10">
         <v>2</v>
@@ -8895,10 +8895,10 @@
         <v>2</v>
       </c>
       <c r="J32" s="10">
-        <v>824</v>
+        <v>787</v>
       </c>
       <c r="K32" s="10">
-        <v>19414730.029029332</v>
+        <v>22608286.960778888</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
@@ -8909,19 +8909,19 @@
         <v>1114</v>
       </c>
       <c r="C33" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33" s="10">
         <v>2</v>
       </c>
       <c r="E33" s="10">
-        <v>964</v>
+        <v>976</v>
       </c>
       <c r="F33" s="10">
-        <v>27091482.436740737</v>
+        <v>31449964.011454657</v>
       </c>
       <c r="G33" s="10">
-        <v>1115</v>
+        <v>1120</v>
       </c>
       <c r="H33" s="10">
         <v>2</v>
@@ -8930,10 +8930,10 @@
         <v>2</v>
       </c>
       <c r="J33" s="10">
-        <v>816</v>
+        <v>869</v>
       </c>
       <c r="K33" s="10">
-        <v>26418427.83281048</v>
+        <v>30719241.13553416</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
@@ -8941,7 +8941,7 @@
         <v>16</v>
       </c>
       <c r="B34" s="10">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="C34" s="10">
         <v>1</v>
@@ -8950,25 +8950,25 @@
         <v>5</v>
       </c>
       <c r="E34" s="10">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="F34" s="10">
-        <v>39832891.790901192</v>
+        <v>46108166.034123458</v>
       </c>
       <c r="G34" s="10">
-        <v>1455</v>
+        <v>1447</v>
       </c>
       <c r="H34" s="10">
         <v>4</v>
       </c>
       <c r="I34" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J34" s="10">
-        <v>1207</v>
+        <v>1162</v>
       </c>
       <c r="K34" s="10">
-        <v>37524684.099695168</v>
+        <v>43751923.266922899</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
@@ -8982,16 +8982,16 @@
         <v>0</v>
       </c>
       <c r="D35" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" s="10">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="F35" s="10">
-        <v>14587539.749331217</v>
+        <v>17087525.954022851</v>
       </c>
       <c r="G35" s="10">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="H35" s="10">
         <v>0</v>
@@ -9000,10 +9000,10 @@
         <v>5</v>
       </c>
       <c r="J35" s="10">
-        <v>581</v>
+        <v>537</v>
       </c>
       <c r="K35" s="10">
-        <v>15406510.595932836</v>
+        <v>17886223.967067465</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
@@ -9011,34 +9011,34 @@
         <v>43</v>
       </c>
       <c r="B36" s="10">
-        <v>1968</v>
+        <v>1974</v>
       </c>
       <c r="C36" s="10">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D36" s="10">
         <v>10</v>
       </c>
       <c r="E36" s="10">
-        <v>1663</v>
+        <v>1654</v>
       </c>
       <c r="F36" s="10">
-        <v>46870678.587666772</v>
+        <v>54279827.871796161</v>
       </c>
       <c r="G36" s="10">
-        <v>1941</v>
+        <v>1922</v>
       </c>
       <c r="H36" s="10">
         <v>6</v>
       </c>
       <c r="I36" s="10">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J36" s="10">
-        <v>892</v>
+        <v>52</v>
       </c>
       <c r="K36" s="10">
-        <v>46557482.188332088</v>
+        <v>46525766.431750014</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
@@ -9046,34 +9046,34 @@
         <v>152</v>
       </c>
       <c r="B37" s="10">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C37" s="10">
         <v>2</v>
       </c>
       <c r="D37" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" s="10">
-        <v>679</v>
+        <v>723</v>
       </c>
       <c r="F37" s="10">
-        <v>16279779.246790402</v>
+        <v>18746377.997059025</v>
       </c>
       <c r="G37" s="10">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="H37" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I37" s="10">
         <v>2</v>
       </c>
       <c r="J37" s="10">
-        <v>774</v>
+        <v>695</v>
       </c>
       <c r="K37" s="10">
-        <v>15562023.232441895</v>
+        <v>18249413.325665232</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
@@ -9090,25 +9090,25 @@
         <v>1</v>
       </c>
       <c r="E38" s="10">
-        <v>459</v>
+        <v>572</v>
       </c>
       <c r="F38" s="10">
-        <v>12893390.296193728</v>
+        <v>15180363.769693863</v>
       </c>
       <c r="G38" s="10">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="H38" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" s="10">
         <v>1</v>
       </c>
       <c r="J38" s="10">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="K38" s="10">
-        <v>14995641.256104443</v>
+        <v>17338354.810338959</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
@@ -9116,7 +9116,7 @@
         <v>154</v>
       </c>
       <c r="B39" s="10">
-        <v>1110</v>
+        <v>1102</v>
       </c>
       <c r="C39" s="10">
         <v>10</v>
@@ -9125,25 +9125,25 @@
         <v>2</v>
       </c>
       <c r="E39" s="10">
-        <v>941</v>
+        <v>869</v>
       </c>
       <c r="F39" s="10">
-        <v>23576799.335367773</v>
+        <v>27075611.243230514</v>
       </c>
       <c r="G39" s="10">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="H39" s="10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I39" s="10">
         <v>1</v>
       </c>
       <c r="J39" s="10">
-        <v>822</v>
+        <v>832</v>
       </c>
       <c r="K39" s="10">
-        <v>22123498.048207261</v>
+        <v>25902505.08937801</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
@@ -9151,22 +9151,22 @@
         <v>2</v>
       </c>
       <c r="B40" s="10">
-        <v>1128</v>
+        <v>1109</v>
       </c>
       <c r="C40" s="10">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D40" s="10">
         <v>1</v>
       </c>
       <c r="E40" s="10">
-        <v>753</v>
+        <v>789</v>
       </c>
       <c r="F40" s="10">
-        <v>22904201.531117793</v>
+        <v>26511431.303062446</v>
       </c>
       <c r="G40" s="10">
-        <v>1331</v>
+        <v>1324</v>
       </c>
       <c r="H40" s="10">
         <v>120</v>
@@ -9175,10 +9175,10 @@
         <v>1</v>
       </c>
       <c r="J40" s="10">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="K40" s="10">
-        <v>20751223.31803656</v>
+        <v>24107934.363502286</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
@@ -9186,34 +9186,34 @@
         <v>156</v>
       </c>
       <c r="B41" s="10">
-        <v>1804</v>
+        <v>1793</v>
       </c>
       <c r="C41" s="10">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D41" s="10">
         <v>4</v>
       </c>
       <c r="E41" s="10">
-        <v>1452</v>
+        <v>1437</v>
       </c>
       <c r="F41" s="10">
-        <v>36032619.201137818</v>
+        <v>41714812.457557224</v>
       </c>
       <c r="G41" s="10">
-        <v>2397</v>
+        <v>2349</v>
       </c>
       <c r="H41" s="10">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I41" s="10">
         <v>5</v>
       </c>
       <c r="J41" s="10">
-        <v>1529</v>
+        <v>1447</v>
       </c>
       <c r="K41" s="10">
-        <v>38476619.904587738</v>
+        <v>44580467.56550619</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
@@ -9221,22 +9221,22 @@
         <v>14</v>
       </c>
       <c r="B42" s="10">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C42" s="10">
         <v>2</v>
       </c>
       <c r="D42" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E42" s="10">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="F42" s="10">
-        <v>15020445.159102108</v>
+        <v>17457645.379634544</v>
       </c>
       <c r="G42" s="10">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="H42" s="10">
         <v>1</v>
@@ -9245,10 +9245,10 @@
         <v>6</v>
       </c>
       <c r="J42" s="10">
-        <v>570</v>
+        <v>697</v>
       </c>
       <c r="K42" s="10">
-        <v>13614594.777193189</v>
+        <v>15995398.494616931</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
@@ -9256,19 +9256,19 @@
         <v>8</v>
       </c>
       <c r="B43" s="10">
-        <v>1992</v>
+        <v>2017</v>
       </c>
       <c r="C43" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D43" s="10">
         <v>5</v>
       </c>
       <c r="E43" s="10">
-        <v>2213</v>
+        <v>1985</v>
       </c>
       <c r="F43" s="10">
-        <v>42247576.219750777</v>
+        <v>48793911.539376937</v>
       </c>
       <c r="G43" s="10">
         <v>2057</v>
@@ -9280,10 +9280,10 @@
         <v>6</v>
       </c>
       <c r="J43" s="10">
-        <v>1914</v>
+        <v>1780</v>
       </c>
       <c r="K43" s="10">
-        <v>45470936.193361871</v>
+        <v>52343763.076205544</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.35">
@@ -9291,7 +9291,7 @@
         <v>39</v>
       </c>
       <c r="B44" s="10">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C44" s="10">
         <v>4</v>
@@ -9300,25 +9300,25 @@
         <v>4</v>
       </c>
       <c r="E44" s="10">
-        <v>740</v>
+        <v>762</v>
       </c>
       <c r="F44" s="10">
-        <v>28973262.41277713</v>
+        <v>33739920.607283264</v>
       </c>
       <c r="G44" s="10">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="H44" s="10">
         <v>3</v>
       </c>
       <c r="I44" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J44" s="10">
-        <v>1422</v>
+        <v>2065</v>
       </c>
       <c r="K44" s="10">
-        <v>29671640.615555849</v>
+        <v>35711327.025523543</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.35">
@@ -9326,7 +9326,7 @@
         <v>6</v>
       </c>
       <c r="B45" s="10">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="C45" s="10">
         <v>1</v>
@@ -9335,25 +9335,25 @@
         <v>3</v>
       </c>
       <c r="E45" s="10">
-        <v>887</v>
+        <v>955</v>
       </c>
       <c r="F45" s="10">
-        <v>24778612.015554167</v>
+        <v>28381796.030693352</v>
       </c>
       <c r="G45" s="10">
-        <v>1081</v>
+        <v>1093</v>
       </c>
       <c r="H45" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" s="10">
         <v>3</v>
       </c>
       <c r="J45" s="10">
-        <v>908</v>
+        <v>854</v>
       </c>
       <c r="K45" s="10">
-        <v>16080664.001975443</v>
+        <v>19475103.312340401</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
@@ -9361,7 +9361,7 @@
         <v>41</v>
       </c>
       <c r="B46" s="10">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C46" s="10">
         <v>0</v>
@@ -9370,25 +9370,25 @@
         <v>5</v>
       </c>
       <c r="E46" s="10">
-        <v>649</v>
+        <v>611</v>
       </c>
       <c r="F46" s="10">
-        <v>24227242.078079969</v>
+        <v>27882962.771981161</v>
       </c>
       <c r="G46" s="10">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="H46" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I46" s="10">
         <v>4</v>
       </c>
       <c r="J46" s="10">
-        <v>627</v>
+        <v>982</v>
       </c>
       <c r="K46" s="10">
-        <v>23529348.521047913</v>
+        <v>27090027.561345614</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.35">
@@ -9396,22 +9396,22 @@
         <v>158</v>
       </c>
       <c r="B47" s="10">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C47" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D47" s="10">
         <v>10</v>
       </c>
       <c r="E47" s="10">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="F47" s="10">
-        <v>14652415.851613129</v>
+        <v>17023761.506318234</v>
       </c>
       <c r="G47" s="10">
-        <v>706</v>
+        <v>697</v>
       </c>
       <c r="H47" s="10">
         <v>2</v>
@@ -9420,10 +9420,10 @@
         <v>10</v>
       </c>
       <c r="J47" s="10">
-        <v>553</v>
+        <v>778</v>
       </c>
       <c r="K47" s="10">
-        <v>15138233.493068304</v>
+        <v>17462894.453000762</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.35">
@@ -9431,7 +9431,7 @@
         <v>160</v>
       </c>
       <c r="B48" s="10">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="C48" s="10">
         <v>1</v>
@@ -9440,13 +9440,13 @@
         <v>1</v>
       </c>
       <c r="E48" s="10">
-        <v>794</v>
+        <v>2510</v>
       </c>
       <c r="F48" s="10">
-        <v>13960317.916001091</v>
+        <v>16200048.119271619</v>
       </c>
       <c r="G48" s="10">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="H48" s="10">
         <v>0</v>
@@ -9455,10 +9455,10 @@
         <v>2</v>
       </c>
       <c r="J48" s="10">
-        <v>719</v>
+        <v>697</v>
       </c>
       <c r="K48" s="10">
-        <v>13328418.590985743</v>
+        <v>15508561.952835817</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
@@ -9466,7 +9466,7 @@
         <v>83</v>
       </c>
       <c r="B49" s="10">
-        <v>1287</v>
+        <v>1292</v>
       </c>
       <c r="C49" s="10">
         <v>8</v>
@@ -9475,25 +9475,25 @@
         <v>6</v>
       </c>
       <c r="E49" s="10">
-        <v>1117</v>
+        <v>1159</v>
       </c>
       <c r="F49" s="10">
-        <v>46742524.804393575</v>
+        <v>53212406.534532376</v>
       </c>
       <c r="G49" s="10">
-        <v>1240</v>
+        <v>1234</v>
       </c>
       <c r="H49" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I49" s="10">
         <v>5</v>
       </c>
       <c r="J49" s="10">
-        <v>2756</v>
+        <v>1133</v>
       </c>
       <c r="K49" s="10">
-        <v>40595640.839021318</v>
+        <v>47059692.469827741</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
@@ -9501,22 +9501,22 @@
         <v>202</v>
       </c>
       <c r="B50" s="10">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="C50" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50" s="10">
         <v>2</v>
       </c>
       <c r="E50" s="10">
-        <v>444</v>
+        <v>466</v>
       </c>
       <c r="F50" s="10">
-        <v>8358481.1128954859</v>
+        <v>9644974.3017519489</v>
       </c>
       <c r="G50" s="10">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H50" s="10">
         <v>0</v>
@@ -9525,10 +9525,10 @@
         <v>1</v>
       </c>
       <c r="J50" s="10">
-        <v>797</v>
+        <v>473</v>
       </c>
       <c r="K50" s="10">
-        <v>6648261.4434765307</v>
+        <v>7719861.9891268816</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
@@ -9536,22 +9536,22 @@
         <v>31</v>
       </c>
       <c r="B51" s="10">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="C51" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51" s="10">
         <v>5</v>
       </c>
       <c r="E51" s="10">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="F51" s="10">
-        <v>20752353.467917528</v>
+        <v>23670122.597009651</v>
       </c>
       <c r="G51" s="10">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="H51" s="10">
         <v>2</v>
@@ -9560,10 +9560,10 @@
         <v>7</v>
       </c>
       <c r="J51" s="10">
-        <v>1570</v>
+        <v>922</v>
       </c>
       <c r="K51" s="10">
-        <v>19574511.266347792</v>
+        <v>22653838.112997834</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
@@ -9571,34 +9571,34 @@
         <v>33</v>
       </c>
       <c r="B52" s="10">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="C52" s="10">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D52" s="10">
         <v>12</v>
       </c>
       <c r="E52" s="10">
-        <v>985</v>
+        <v>1021</v>
       </c>
       <c r="F52" s="10">
-        <v>28496249.862501446</v>
+        <v>33891083.600854926</v>
       </c>
       <c r="G52" s="10">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H52" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I52" s="10">
         <v>12</v>
       </c>
       <c r="J52" s="10">
-        <v>465</v>
+        <v>1015</v>
       </c>
       <c r="K52" s="10">
-        <v>34212070.475824885</v>
+        <v>39599121.530364431</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.35">
@@ -9606,22 +9606,22 @@
         <v>85</v>
       </c>
       <c r="B53" s="10">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="C53" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D53" s="10">
         <v>5</v>
       </c>
       <c r="E53" s="10">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="F53" s="10">
-        <v>15097189.995865844</v>
+        <v>17681002.320624005</v>
       </c>
       <c r="G53" s="10">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="H53" s="10">
         <v>1</v>
@@ -9630,10 +9630,10 @@
         <v>6</v>
       </c>
       <c r="J53" s="10">
-        <v>233</v>
+        <v>393</v>
       </c>
       <c r="K53" s="10">
-        <v>17699580.139482781</v>
+        <v>20476254.373544708</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.35">
@@ -9641,19 +9641,19 @@
         <v>81</v>
       </c>
       <c r="B54" s="10">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="C54" s="10">
         <v>0</v>
       </c>
       <c r="D54" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E54" s="10">
         <v>301</v>
       </c>
       <c r="F54" s="10">
-        <v>16420270.784009542</v>
+        <v>18461149.150816448</v>
       </c>
       <c r="G54" s="10">
         <v>457</v>
@@ -9665,10 +9665,10 @@
         <v>4</v>
       </c>
       <c r="J54" s="10">
-        <v>211</v>
+        <v>312</v>
       </c>
       <c r="K54" s="10">
-        <v>12890327.304175895</v>
+        <v>14867632.890376093</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.35">
@@ -9676,22 +9676,22 @@
         <v>87</v>
       </c>
       <c r="B55" s="10">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C55" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D55" s="10">
         <v>2</v>
       </c>
       <c r="E55" s="10">
-        <v>372</v>
+        <v>349</v>
       </c>
       <c r="F55" s="10">
-        <v>13190676.148514977</v>
+        <v>15175187.024739441</v>
       </c>
       <c r="G55" s="10">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="H55" s="10">
         <v>1</v>
@@ -9700,10 +9700,10 @@
         <v>4</v>
       </c>
       <c r="J55" s="10">
-        <v>220</v>
+        <v>324</v>
       </c>
       <c r="K55" s="10">
-        <v>11150973.143566536</v>
+        <v>12944386.16594301</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.35">
@@ -9711,7 +9711,7 @@
         <v>166</v>
       </c>
       <c r="B56" s="10">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="C56" s="10">
         <v>1</v>
@@ -9720,25 +9720,25 @@
         <v>1</v>
       </c>
       <c r="E56" s="10">
-        <v>979</v>
+        <v>967</v>
       </c>
       <c r="F56" s="10">
-        <v>28683571.11333501</v>
+        <v>32732404.044502798</v>
       </c>
       <c r="G56" s="10">
-        <v>1103</v>
+        <v>1108</v>
       </c>
       <c r="H56" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I56" s="10">
         <v>0</v>
       </c>
       <c r="J56" s="10">
-        <v>661</v>
+        <v>938</v>
       </c>
       <c r="K56" s="10">
-        <v>26199041.104115095</v>
+        <v>30650599.292324264</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
@@ -9746,34 +9746,34 @@
         <v>93</v>
       </c>
       <c r="B57" s="10">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="C57" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D57" s="10">
         <v>3</v>
       </c>
       <c r="E57" s="10">
-        <v>951</v>
+        <v>1018</v>
       </c>
       <c r="F57" s="10">
-        <v>30270197.395333569</v>
+        <v>34854256.338008754</v>
       </c>
       <c r="G57" s="10">
-        <v>998</v>
+        <v>1004</v>
       </c>
       <c r="H57" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I57" s="10">
         <v>1</v>
       </c>
       <c r="J57" s="10">
-        <v>715</v>
+        <v>943</v>
       </c>
       <c r="K57" s="10">
-        <v>25284897.300338056</v>
+        <v>29971764.592281073</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.35">
@@ -9781,34 +9781,34 @@
         <v>95</v>
       </c>
       <c r="B58" s="10">
-        <v>2219</v>
+        <v>2212</v>
       </c>
       <c r="C58" s="10">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D58" s="10">
         <v>7</v>
       </c>
       <c r="E58" s="10">
-        <v>1670</v>
+        <v>1410</v>
       </c>
       <c r="F58" s="10">
-        <v>38883489.20395907</v>
+        <v>46006855.693857841</v>
       </c>
       <c r="G58" s="10">
         <v>2065</v>
       </c>
       <c r="H58" s="10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I58" s="10">
         <v>8</v>
       </c>
       <c r="J58" s="10">
-        <v>1226</v>
+        <v>1660</v>
       </c>
       <c r="K58" s="10">
-        <v>49694243.711567715</v>
+        <v>57135591.312040411</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.35">
@@ -9816,22 +9816,22 @@
         <v>174</v>
       </c>
       <c r="B59" s="10">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C59" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D59" s="10">
         <v>0</v>
       </c>
       <c r="E59" s="10">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="F59" s="10">
-        <v>14059897.113616962</v>
+        <v>15925948.807056723</v>
       </c>
       <c r="G59" s="10">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="H59" s="10">
         <v>4</v>
@@ -9840,10 +9840,10 @@
         <v>0</v>
       </c>
       <c r="J59" s="10">
-        <v>453</v>
+        <v>528</v>
       </c>
       <c r="K59" s="10">
-        <v>12002259.173613898</v>
+        <v>14278357.522577465</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.35">
@@ -9851,34 +9851,34 @@
         <v>99</v>
       </c>
       <c r="B60" s="10">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="C60" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D60" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E60" s="10">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F60" s="10">
-        <v>20686122.966544252</v>
+        <v>23907515.938926905</v>
       </c>
       <c r="G60" s="10">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="H60" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I60" s="10">
         <v>5</v>
       </c>
       <c r="J60" s="10">
-        <v>510</v>
+        <v>701</v>
       </c>
       <c r="K60" s="10">
-        <v>21289344.203055624</v>
+        <v>24722818.188481327</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.35">
@@ -9886,34 +9886,34 @@
         <v>172</v>
       </c>
       <c r="B61" s="10">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="C61" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" s="10">
         <v>1</v>
       </c>
       <c r="E61" s="10">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F61" s="10">
-        <v>16863635.008035466</v>
+        <v>19219152.45467395</v>
       </c>
       <c r="G61" s="10">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="H61" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I61" s="10">
         <v>1</v>
       </c>
       <c r="J61" s="10">
-        <v>516</v>
+        <v>631</v>
       </c>
       <c r="K61" s="10">
-        <v>13013595.533991264</v>
+        <v>15491777.19412148</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.35">
@@ -9921,22 +9921,22 @@
         <v>168</v>
       </c>
       <c r="B62" s="10">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="C62" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D62" s="10">
         <v>1</v>
       </c>
       <c r="E62" s="10">
-        <v>1010</v>
+        <v>1019</v>
       </c>
       <c r="F62" s="10">
-        <v>28509568.786117759</v>
+        <v>32693040.576812342</v>
       </c>
       <c r="G62" s="10">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H62" s="10">
         <v>6</v>
@@ -9945,10 +9945,10 @@
         <v>0</v>
       </c>
       <c r="J62" s="10">
-        <v>807</v>
+        <v>937</v>
       </c>
       <c r="K62" s="10">
-        <v>27702105.186980639</v>
+        <v>32144751.183899943</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.35">
@@ -9956,34 +9956,34 @@
         <v>101</v>
       </c>
       <c r="B63" s="10">
-        <v>1340</v>
+        <v>1349</v>
       </c>
       <c r="C63" s="10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D63" s="10">
         <v>4</v>
       </c>
       <c r="E63" s="10">
-        <v>1404</v>
+        <v>1444</v>
       </c>
       <c r="F63" s="10">
-        <v>35146427.627709694</v>
+        <v>41135039.004691504</v>
       </c>
       <c r="G63" s="10">
-        <v>1436</v>
+        <v>1462</v>
       </c>
       <c r="H63" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I63" s="10">
         <v>4</v>
       </c>
       <c r="J63" s="10">
-        <v>1441</v>
+        <v>1524</v>
       </c>
       <c r="K63" s="10">
-        <v>33966036.339512989</v>
+        <v>40223865.983752102</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.35">
@@ -9991,7 +9991,7 @@
         <v>103</v>
       </c>
       <c r="B64" s="10">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="C64" s="10">
         <v>4</v>
@@ -10000,13 +10000,13 @@
         <v>5</v>
       </c>
       <c r="E64" s="10">
-        <v>693</v>
+        <v>717</v>
       </c>
       <c r="F64" s="10">
-        <v>18496571.488525391</v>
+        <v>21181066.675294984</v>
       </c>
       <c r="G64" s="10">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="H64" s="10">
         <v>1</v>
@@ -10015,10 +10015,10 @@
         <v>4</v>
       </c>
       <c r="J64" s="10">
-        <v>648</v>
+        <v>726</v>
       </c>
       <c r="K64" s="10">
-        <v>18635735.040618103</v>
+        <v>21499850.705537871</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.35">
@@ -10026,10 +10026,10 @@
         <v>105</v>
       </c>
       <c r="B65" s="10">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="C65" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D65" s="10">
         <v>5</v>
@@ -10038,10 +10038,10 @@
         <v>453</v>
       </c>
       <c r="F65" s="10">
-        <v>21311583.419039447</v>
+        <v>24380650.130268615</v>
       </c>
       <c r="G65" s="10">
-        <v>651</v>
+        <v>642</v>
       </c>
       <c r="H65" s="10">
         <v>7</v>
@@ -10050,10 +10050,10 @@
         <v>5</v>
       </c>
       <c r="J65" s="10">
-        <v>450</v>
+        <v>485</v>
       </c>
       <c r="K65" s="10">
-        <v>20855323.597276349</v>
+        <v>24041232.874499574</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.35">
@@ -10061,34 +10061,34 @@
         <v>24</v>
       </c>
       <c r="B66" s="10">
-        <v>2027</v>
+        <v>2023</v>
       </c>
       <c r="C66" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D66" s="10">
         <v>9</v>
       </c>
       <c r="E66" s="10">
-        <v>1661</v>
+        <v>1673</v>
       </c>
       <c r="F66" s="10">
-        <v>52066758.950409554</v>
+        <v>61721106.397677347</v>
       </c>
       <c r="G66" s="10">
-        <v>1983</v>
+        <v>1992</v>
       </c>
       <c r="H66" s="10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I66" s="10">
         <v>10</v>
       </c>
       <c r="J66" s="10">
-        <v>1641</v>
+        <v>1781</v>
       </c>
       <c r="K66" s="10">
-        <v>67354281.232562438</v>
+        <v>78146220.43496713</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.35">
@@ -10099,31 +10099,31 @@
         <v>1624</v>
       </c>
       <c r="C67" s="10">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D67" s="10">
         <v>8</v>
       </c>
       <c r="E67" s="10">
-        <v>1117</v>
+        <v>1192</v>
       </c>
       <c r="F67" s="10">
-        <v>50435773.987107798</v>
+        <v>58992955.728539579</v>
       </c>
       <c r="G67" s="10">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="H67" s="10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I67" s="10">
         <v>6</v>
       </c>
       <c r="J67" s="10">
-        <v>1265</v>
+        <v>1183</v>
       </c>
       <c r="K67" s="10">
-        <v>49454368.591136239</v>
+        <v>57962386.104648069</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.35">
@@ -10131,7 +10131,7 @@
         <v>29</v>
       </c>
       <c r="B68" s="10">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="C68" s="10">
         <v>2</v>
@@ -10140,25 +10140,25 @@
         <v>1</v>
       </c>
       <c r="E68" s="10">
-        <v>759</v>
+        <v>777</v>
       </c>
       <c r="F68" s="10">
-        <v>32576705.122849252</v>
+        <v>37368994.644287363</v>
       </c>
       <c r="G68" s="10">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="H68" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I68" s="10">
         <v>1</v>
       </c>
       <c r="J68" s="10">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="K68" s="10">
-        <v>32506719.517589524</v>
+        <v>37583945.764142759</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.35">
@@ -10166,34 +10166,34 @@
         <v>57</v>
       </c>
       <c r="B69" s="10">
-        <v>1856</v>
+        <v>1847</v>
       </c>
       <c r="C69" s="10">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D69" s="10">
         <v>13</v>
       </c>
       <c r="E69" s="10">
-        <v>1247</v>
+        <v>1261</v>
       </c>
       <c r="F69" s="10">
-        <v>46217872.902747199</v>
+        <v>53896987.492598519</v>
       </c>
       <c r="G69" s="10">
-        <v>2317</v>
+        <v>2294</v>
       </c>
       <c r="H69" s="10">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="I69" s="10">
         <v>12</v>
       </c>
       <c r="J69" s="10">
-        <v>1308</v>
+        <v>1296</v>
       </c>
       <c r="K69" s="10">
-        <v>49572620.973607913</v>
+        <v>56760340.422445491</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.35">
@@ -10201,7 +10201,7 @@
         <v>137</v>
       </c>
       <c r="B70" s="10">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="C70" s="10">
         <v>1</v>
@@ -10210,13 +10210,13 @@
         <v>1</v>
       </c>
       <c r="E70" s="10">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="F70" s="10">
-        <v>3625270.0844115838</v>
+        <v>4177676.11918703</v>
       </c>
       <c r="G70" s="10">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="H70" s="10">
         <v>0</v>
@@ -10225,10 +10225,10 @@
         <v>1</v>
       </c>
       <c r="J70" s="10">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="K70" s="10">
-        <v>1350194.3692348029</v>
+        <v>1830061.480065604</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.35">
@@ -10236,34 +10236,34 @@
         <v>10</v>
       </c>
       <c r="B71" s="10">
-        <v>1754</v>
+        <v>1737</v>
       </c>
       <c r="C71" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D71" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E71" s="10">
-        <v>1578</v>
+        <v>1639</v>
       </c>
       <c r="F71" s="10">
-        <v>37078833.059941009</v>
+        <v>42837442.990329213</v>
       </c>
       <c r="G71" s="10">
-        <v>1669</v>
+        <v>1660</v>
       </c>
       <c r="H71" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I71" s="10">
         <v>6</v>
       </c>
       <c r="J71" s="10">
-        <v>1480</v>
+        <v>1413</v>
       </c>
       <c r="K71" s="10">
-        <v>35144336.780402198</v>
+        <v>40358257.639780559</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.35">
@@ -10280,13 +10280,13 @@
         <v>2</v>
       </c>
       <c r="E72" s="10">
-        <v>545</v>
+        <v>590</v>
       </c>
       <c r="F72" s="10">
-        <v>14360464.125569835</v>
+        <v>17129997.41105824</v>
       </c>
       <c r="G72" s="10">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="H72" s="10">
         <v>1</v>
@@ -10295,10 +10295,10 @@
         <v>3</v>
       </c>
       <c r="J72" s="10">
-        <v>638</v>
+        <v>578</v>
       </c>
       <c r="K72" s="10">
-        <v>16822352.835773688</v>
+        <v>19545247.766959641</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.35">
@@ -10306,7 +10306,7 @@
         <v>162</v>
       </c>
       <c r="B73" s="10">
-        <v>1322</v>
+        <v>1307</v>
       </c>
       <c r="C73" s="10">
         <v>22</v>
@@ -10315,25 +10315,25 @@
         <v>5</v>
       </c>
       <c r="E73" s="10">
-        <v>892</v>
+        <v>885</v>
       </c>
       <c r="F73" s="10">
-        <v>24699781.872286916</v>
+        <v>28510903.990744784</v>
       </c>
       <c r="G73" s="10">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="H73" s="10">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I73" s="10">
         <v>4</v>
       </c>
       <c r="J73" s="10">
-        <v>842</v>
+        <v>984</v>
       </c>
       <c r="K73" s="10">
-        <v>23886309.979035523</v>
+        <v>27871659.032617167</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.35">
@@ -10341,22 +10341,22 @@
         <v>63</v>
       </c>
       <c r="B74" s="10">
-        <v>1397</v>
+        <v>1386</v>
       </c>
       <c r="C74" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D74" s="10">
         <v>5</v>
       </c>
       <c r="E74" s="10">
-        <v>1671</v>
+        <v>1312</v>
       </c>
       <c r="F74" s="10">
-        <v>14040754.724470759</v>
+        <v>15593757.28553294</v>
       </c>
       <c r="G74" s="10">
-        <v>1283</v>
+        <v>1265</v>
       </c>
       <c r="H74" s="10">
         <v>2</v>
@@ -10365,10 +10365,10 @@
         <v>5</v>
       </c>
       <c r="J74" s="10">
-        <v>982</v>
+        <v>1190</v>
       </c>
       <c r="K74" s="10">
-        <v>14655444.982134709</v>
+        <v>17271089.170965463</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.35">
@@ -10376,7 +10376,7 @@
         <v>59</v>
       </c>
       <c r="B75" s="10">
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="C75" s="10">
         <v>5</v>
@@ -10385,25 +10385,25 @@
         <v>5</v>
       </c>
       <c r="E75" s="10">
-        <v>1397</v>
+        <v>1364</v>
       </c>
       <c r="F75" s="10">
-        <v>42772224.122835599</v>
+        <v>50258291.499809645</v>
       </c>
       <c r="G75" s="10">
-        <v>1745</v>
+        <v>1753</v>
       </c>
       <c r="H75" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I75" s="10">
         <v>4</v>
       </c>
       <c r="J75" s="10">
-        <v>1213</v>
+        <v>1198</v>
       </c>
       <c r="K75" s="10">
-        <v>43224353.113018826</v>
+        <v>50078251.351593465</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.35">
@@ -10411,7 +10411,7 @@
         <v>139</v>
       </c>
       <c r="B76" s="10">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="C76" s="10">
         <v>2</v>
@@ -10420,10 +10420,10 @@
         <v>2</v>
       </c>
       <c r="E76" s="10">
-        <v>557</v>
+        <v>515</v>
       </c>
       <c r="F76" s="10">
-        <v>9589492.6070907712</v>
+        <v>11124898.409664072</v>
       </c>
       <c r="G76" s="10">
         <v>515</v>
@@ -10435,10 +10435,10 @@
         <v>1</v>
       </c>
       <c r="J76" s="10">
-        <v>629</v>
+        <v>432</v>
       </c>
       <c r="K76" s="10">
-        <v>8720745.3927304987</v>
+        <v>10184693.362073636</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.35">
@@ -10446,22 +10446,22 @@
         <v>170</v>
       </c>
       <c r="B77" s="10">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="C77" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D77" s="10">
         <v>1</v>
       </c>
       <c r="E77" s="10">
-        <v>822</v>
+        <v>806</v>
       </c>
       <c r="F77" s="10">
-        <v>14782444.521858055</v>
+        <v>16955552.557962589</v>
       </c>
       <c r="G77" s="10">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="H77" s="10">
         <v>2</v>
@@ -10470,10 +10470,10 @@
         <v>1</v>
       </c>
       <c r="J77" s="10">
-        <v>669</v>
+        <v>1000</v>
       </c>
       <c r="K77" s="10">
-        <v>13423851.621452449</v>
+        <v>15810033.870585823</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.35">
@@ -10481,7 +10481,7 @@
         <v>61</v>
       </c>
       <c r="B78" s="10">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="C78" s="10">
         <v>1</v>
@@ -10490,13 +10490,13 @@
         <v>4</v>
       </c>
       <c r="E78" s="10">
-        <v>493</v>
+        <v>528</v>
       </c>
       <c r="F78" s="10">
-        <v>9926102.0989064872</v>
+        <v>12369088.577015188</v>
       </c>
       <c r="G78" s="10">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="H78" s="10">
         <v>0</v>
@@ -10505,10 +10505,10 @@
         <v>3</v>
       </c>
       <c r="J78" s="10">
-        <v>485</v>
+        <v>510</v>
       </c>
       <c r="K78" s="10">
-        <v>13414443.231452348</v>
+        <v>15807488.14342864</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.35">
@@ -10516,34 +10516,34 @@
         <v>129</v>
       </c>
       <c r="B79" s="10">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="C79" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D79" s="10">
         <v>1</v>
       </c>
       <c r="E79" s="10">
-        <v>701</v>
+        <v>736</v>
       </c>
       <c r="F79" s="10">
-        <v>9748712.1952629611</v>
+        <v>11378936.90622247</v>
       </c>
       <c r="G79" s="10">
-        <v>601</v>
+        <v>612</v>
       </c>
       <c r="H79" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I79" s="10">
         <v>1</v>
       </c>
       <c r="J79" s="10">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="K79" s="10">
-        <v>11048829.612400329</v>
+        <v>12568715.058400322</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.35">
@@ -10551,34 +10551,34 @@
         <v>35</v>
       </c>
       <c r="B80" s="10">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C80" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D80" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E80" s="10">
-        <v>391</v>
+        <v>425</v>
       </c>
       <c r="F80" s="10">
-        <v>11180752.377334528</v>
+        <v>12943551.285408163</v>
       </c>
       <c r="G80" s="10">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="H80" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" s="10">
         <v>7</v>
       </c>
       <c r="J80" s="10">
-        <v>251</v>
+        <v>463</v>
       </c>
       <c r="K80" s="10">
-        <v>11874682.330901796</v>
+        <v>13584670.070504978</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.35">
@@ -10586,34 +10586,34 @@
         <v>107</v>
       </c>
       <c r="B81" s="10">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="C81" s="10">
+        <v>6</v>
+      </c>
+      <c r="D81" s="10">
+        <v>4</v>
+      </c>
+      <c r="E81" s="10">
+        <v>784</v>
+      </c>
+      <c r="F81" s="10">
+        <v>36997824.771402493</v>
+      </c>
+      <c r="G81" s="10">
+        <v>928</v>
+      </c>
+      <c r="H81" s="10">
         <v>5</v>
-      </c>
-      <c r="D81" s="10">
-        <v>4</v>
-      </c>
-      <c r="E81" s="10">
-        <v>774</v>
-      </c>
-      <c r="F81" s="10">
-        <v>31391312.242365938</v>
-      </c>
-      <c r="G81" s="10">
-        <v>942</v>
-      </c>
-      <c r="H81" s="10">
-        <v>4</v>
       </c>
       <c r="I81" s="10">
         <v>3</v>
       </c>
       <c r="J81" s="10">
-        <v>735</v>
+        <v>562</v>
       </c>
       <c r="K81" s="10">
-        <v>31274170.374765057</v>
+        <v>36158999.173775911</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.35">
@@ -10621,7 +10621,7 @@
         <v>37</v>
       </c>
       <c r="B82" s="10">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C82" s="10">
         <v>2</v>
@@ -10630,10 +10630,10 @@
         <v>9</v>
       </c>
       <c r="E82" s="10">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="F82" s="10">
-        <v>18988654.507708855</v>
+        <v>21724320.235075474</v>
       </c>
       <c r="G82" s="10">
         <v>772</v>
@@ -10645,10 +10645,10 @@
         <v>10</v>
       </c>
       <c r="J82" s="10">
-        <v>2118</v>
+        <v>715</v>
       </c>
       <c r="K82" s="10">
-        <v>18899937.995990712</v>
+        <v>21556780.627003729</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.35">
@@ -10665,25 +10665,25 @@
         <v>2</v>
       </c>
       <c r="E83" s="10">
-        <v>899</v>
+        <v>918</v>
       </c>
       <c r="F83" s="10">
-        <v>15805318.288240936</v>
+        <v>18436711.83211863</v>
       </c>
       <c r="G83" s="10">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="H83" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I83" s="10">
         <v>2</v>
       </c>
       <c r="J83" s="10">
-        <v>855</v>
+        <v>866</v>
       </c>
       <c r="K83" s="10">
-        <v>15125684.077691879</v>
+        <v>17554926.06836798</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.35">
@@ -10691,22 +10691,22 @@
         <v>65</v>
       </c>
       <c r="B84" s="10">
-        <v>1013</v>
+        <v>1018</v>
       </c>
       <c r="C84" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D84" s="10">
         <v>4</v>
       </c>
       <c r="E84" s="10">
-        <v>813</v>
+        <v>796</v>
       </c>
       <c r="F84" s="10">
-        <v>17980106.353986889</v>
+        <v>20675882.787564185</v>
       </c>
       <c r="G84" s="10">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="H84" s="10">
         <v>1</v>
@@ -10715,10 +10715,10 @@
         <v>5</v>
       </c>
       <c r="J84" s="10">
-        <v>842</v>
+        <v>790</v>
       </c>
       <c r="K84" s="10">
-        <v>14533223.238636944</v>
+        <v>17375063.532339539</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.35">
@@ -10726,22 +10726,22 @@
         <v>89</v>
       </c>
       <c r="B85" s="10">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="C85" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D85" s="10">
         <v>5</v>
       </c>
       <c r="E85" s="10">
-        <v>746</v>
+        <v>715</v>
       </c>
       <c r="F85" s="10">
-        <v>18620384.172661994</v>
+        <v>21557213.686589696</v>
       </c>
       <c r="G85" s="10">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="H85" s="10">
         <v>2</v>
@@ -10750,10 +10750,10 @@
         <v>6</v>
       </c>
       <c r="J85" s="10">
-        <v>408</v>
+        <v>796</v>
       </c>
       <c r="K85" s="10">
-        <v>19678596.684385128</v>
+        <v>23095754.28563593</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.35">
@@ -10761,7 +10761,7 @@
         <v>147</v>
       </c>
       <c r="B86" s="10">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C86" s="10">
         <v>1</v>
@@ -10770,13 +10770,13 @@
         <v>1</v>
       </c>
       <c r="E86" s="10">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="F86" s="10">
-        <v>8842619.4253564347</v>
+        <v>9879876.8658112064</v>
       </c>
       <c r="G86" s="10">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="H86" s="10">
         <v>1</v>
@@ -10785,10 +10785,10 @@
         <v>1</v>
       </c>
       <c r="J86" s="10">
-        <v>540</v>
+        <v>510</v>
       </c>
       <c r="K86" s="10">
-        <v>9379650.8358766995</v>
+        <v>10738264.072177881</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.35">
@@ -10796,34 +10796,34 @@
         <v>164</v>
       </c>
       <c r="B87" s="10">
-        <v>1722</v>
+        <v>1715</v>
       </c>
       <c r="C87" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D87" s="10">
         <v>10</v>
       </c>
       <c r="E87" s="10">
-        <v>1321</v>
+        <v>1295</v>
       </c>
       <c r="F87" s="10">
-        <v>35571479.183830611</v>
+        <v>41733546.900617406</v>
       </c>
       <c r="G87" s="10">
-        <v>1762</v>
+        <v>1765</v>
       </c>
       <c r="H87" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I87" s="10">
         <v>10</v>
       </c>
       <c r="J87" s="10">
-        <v>1316</v>
+        <v>1232</v>
       </c>
       <c r="K87" s="10">
-        <v>38722670.295691326</v>
+        <v>45577456.506966852</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.35">
@@ -10831,22 +10831,22 @@
         <v>91</v>
       </c>
       <c r="B88" s="10">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="C88" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D88" s="10">
         <v>3</v>
       </c>
       <c r="E88" s="10">
-        <v>673</v>
+        <v>901</v>
       </c>
       <c r="F88" s="10">
-        <v>10381530.962787962</v>
+        <v>11696048.467407828</v>
       </c>
       <c r="G88" s="10">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="H88" s="10">
         <v>0</v>
@@ -10855,10 +10855,10 @@
         <v>3</v>
       </c>
       <c r="J88" s="10">
-        <v>734</v>
+        <v>636</v>
       </c>
       <c r="K88" s="10">
-        <v>8630087.2264204156</v>
+        <v>10779677.36682423</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.35">
@@ -10866,7 +10866,7 @@
         <v>97</v>
       </c>
       <c r="B89" s="10">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="C89" s="10">
         <v>10</v>
@@ -10875,13 +10875,13 @@
         <v>7</v>
       </c>
       <c r="E89" s="10">
-        <v>1110</v>
+        <v>551</v>
       </c>
       <c r="F89" s="10">
-        <v>17326990.22087634</v>
+        <v>19852232.268611159</v>
       </c>
       <c r="G89" s="10">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="H89" s="10">
         <v>4</v>
@@ -10890,10 +10890,10 @@
         <v>7</v>
       </c>
       <c r="J89" s="10">
-        <v>408</v>
+        <v>569</v>
       </c>
       <c r="K89" s="10">
-        <v>17500296.393373366</v>
+        <v>19960572.610525478</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.35">
@@ -10901,22 +10901,22 @@
         <v>78</v>
       </c>
       <c r="B90" s="10">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C90" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D90" s="10">
         <v>1</v>
       </c>
       <c r="E90" s="10">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F90" s="10">
-        <v>5027836.3395618377</v>
+        <v>5664274.1859372323</v>
       </c>
       <c r="G90" s="10">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="H90" s="10">
         <v>2</v>
@@ -10925,10 +10925,10 @@
         <v>1</v>
       </c>
       <c r="J90" s="10">
-        <v>380</v>
+        <v>301</v>
       </c>
       <c r="K90" s="10">
-        <v>4318945.0415773364</v>
+        <v>4924927.4812102551</v>
       </c>
     </row>
   </sheetData>

--- a/SITE MONITORING.xlsx
+++ b/SITE MONITORING.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
@@ -1136,27 +1136,27 @@
       </c>
       <c r="F2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10081819.681227973</v>
+        <v>10600029.17885459</v>
       </c>
       <c r="G2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9328903.5811648574</v>
+        <v>10028253.355198471</v>
       </c>
       <c r="H2" s="12">
         <f>IFERROR(G2/F2-1,0)</f>
-        <v>-7.4680575914784608E-2</v>
+        <v>-5.3940966954763025E-2</v>
       </c>
       <c r="I2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>288</v>
+        <v>366</v>
       </c>
       <c r="J2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>386</v>
+        <v>430</v>
       </c>
       <c r="K2" s="12">
         <f>IFERROR(J2/I2-1,0)</f>
-        <v>0.34027777777777768</v>
+        <v>0.17486338797814205</v>
       </c>
       <c r="L2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1184,15 +1184,15 @@
       </c>
       <c r="R2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="S2">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="T2" s="12">
         <f>IFERROR(S2/R2-1,0)</f>
-        <v>1.9607843137254832E-2</v>
+        <v>2.421307506053294E-3</v>
       </c>
       <c r="U2">
         <v>3</v>
@@ -1216,27 +1216,27 @@
       </c>
       <c r="F3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12646261.849610392</v>
+        <v>13325051.244588085</v>
       </c>
       <c r="G3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10997989.293437231</v>
+        <v>11844501.537288273</v>
       </c>
       <c r="H3" s="12">
         <f t="shared" ref="H3:H66" si="0">IFERROR(G3/F3-1,0)</f>
-        <v>-0.13033674106818693</v>
+        <v>-0.11111024491565324</v>
       </c>
       <c r="I3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>550</v>
+        <v>568</v>
       </c>
       <c r="J3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1204</v>
+        <v>544</v>
       </c>
       <c r="K3" s="12">
         <f t="shared" ref="K3:K66" si="1">IFERROR(J3/I3-1,0)</f>
-        <v>1.189090909090909</v>
+        <v>-4.2253521126760618E-2</v>
       </c>
       <c r="L3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -1260,19 +1260,19 @@
       </c>
       <c r="Q3" s="12">
         <f t="shared" ref="Q3:Q66" si="3">IFERROR(P3/O3-1,0)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="S3">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>648</v>
+        <v>639</v>
       </c>
       <c r="T3" s="12">
         <f t="shared" ref="T3:T66" si="4">IFERROR(S3/R3-1,0)</f>
-        <v>-4.0000000000000036E-2</v>
+        <v>-5.8910162002945521E-2</v>
       </c>
       <c r="U3">
         <v>2</v>
@@ -1296,27 +1296,27 @@
       </c>
       <c r="F4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12713958.118884431</v>
+        <v>13568687.102148704</v>
       </c>
       <c r="G4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14219634.224562662</v>
+        <v>15687996.009139288</v>
       </c>
       <c r="H4" s="12">
         <f t="shared" si="0"/>
-        <v>0.1184270147501747</v>
+        <v>0.15619115475475698</v>
       </c>
       <c r="I4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>658</v>
+        <v>569</v>
       </c>
       <c r="J4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>737</v>
+        <v>803</v>
       </c>
       <c r="K4" s="12">
         <f t="shared" si="1"/>
-        <v>0.12006079027355621</v>
+        <v>0.41124780316344456</v>
       </c>
       <c r="L4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="O4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -1340,19 +1340,19 @@
       </c>
       <c r="Q4" s="12">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="R4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="S4">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>743</v>
+        <v>756</v>
       </c>
       <c r="T4" s="12">
         <f t="shared" si="4"/>
-        <v>9.1042584434654961E-2</v>
+        <v>0.10850439882697938</v>
       </c>
       <c r="U4">
         <v>4</v>
@@ -1376,27 +1376,27 @@
       </c>
       <c r="F5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>23642031.302799549</v>
+        <v>24977688.513464183</v>
       </c>
       <c r="G5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23896411.194066271</v>
+        <v>25629330.071108133</v>
       </c>
       <c r="H5" s="12">
         <f t="shared" si="0"/>
-        <v>1.0759646157671776E-2</v>
+        <v>2.608894563212627E-2</v>
       </c>
       <c r="I5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1981</v>
+        <v>1188</v>
       </c>
       <c r="J5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1071</v>
+        <v>1123</v>
       </c>
       <c r="K5" s="12">
         <f t="shared" si="1"/>
-        <v>-0.45936395759717319</v>
+        <v>-5.4713804713804715E-2</v>
       </c>
       <c r="L5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1424,15 +1424,15 @@
       </c>
       <c r="R5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="S5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1212</v>
+        <v>1206</v>
       </c>
       <c r="T5" s="12">
         <f t="shared" si="4"/>
-        <v>1.8487394957983128E-2</v>
+        <v>1.1744966442952975E-2</v>
       </c>
       <c r="U5">
         <v>3</v>
@@ -1456,27 +1456,27 @@
       </c>
       <c r="F6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9596873.4474547114</v>
+        <v>10213403.496292388</v>
       </c>
       <c r="G6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10735578.1970079</v>
+        <v>11564273.043757185</v>
       </c>
       <c r="H6" s="12">
         <f t="shared" si="0"/>
-        <v>0.11865372152585762</v>
+        <v>0.1322643864951758</v>
       </c>
       <c r="I6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="J6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="K6" s="12">
         <f t="shared" si="1"/>
-        <v>0.10060975609756095</v>
+        <v>0.22402597402597402</v>
       </c>
       <c r="L6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1504,15 +1504,15 @@
       </c>
       <c r="R6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="S6">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="T6" s="12">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-4.8426150121065881E-3</v>
       </c>
       <c r="U6">
         <v>3</v>
@@ -1536,27 +1536,27 @@
       </c>
       <c r="F7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8856040.2209448274</v>
+        <v>9311664.9737815727</v>
       </c>
       <c r="G7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>8947473.0958644543</v>
+        <v>9571632.1562437192</v>
       </c>
       <c r="H7" s="12">
         <f t="shared" si="0"/>
-        <v>1.0324351813961297E-2</v>
+        <v>2.7918442426152934E-2</v>
       </c>
       <c r="I7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="J7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="K7" s="12">
         <f t="shared" si="1"/>
-        <v>-0.12460063897763574</v>
+        <v>-0.14893617021276595</v>
       </c>
       <c r="L7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="R7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="S7">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="T7" s="12">
         <f t="shared" si="4"/>
-        <v>3.8147138964577554E-2</v>
+        <v>3.2520325203251987E-2</v>
       </c>
       <c r="U7">
         <v>2</v>
@@ -1616,19 +1616,19 @@
       </c>
       <c r="F8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10119494.23898562</v>
+        <v>10676512.083891636</v>
       </c>
       <c r="G8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10567198.582857665</v>
+        <v>11355109.563810242</v>
       </c>
       <c r="H8" s="12">
         <f t="shared" si="0"/>
-        <v>4.4241770714908979E-2</v>
+        <v>6.3559847503235734E-2</v>
       </c>
       <c r="I8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>481</v>
+        <v>464</v>
       </c>
       <c r="J8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="K8" s="12">
         <f t="shared" si="1"/>
-        <v>7.2765072765072825E-2</v>
+        <v>0.11206896551724133</v>
       </c>
       <c r="L8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1652,19 +1652,19 @@
       </c>
       <c r="O8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="S8">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="T8" s="12">
         <f t="shared" si="4"/>
-        <v>-3.3500837520937798E-3</v>
+        <v>0</v>
       </c>
       <c r="U8">
         <v>9</v>
@@ -1696,27 +1696,27 @@
       </c>
       <c r="F9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4689917.3020850392</v>
+        <v>4961594.8237775872</v>
       </c>
       <c r="G9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4719781.875237532</v>
+        <v>5041914.6980878524</v>
       </c>
       <c r="H9" s="12">
         <f t="shared" si="0"/>
-        <v>6.3678251083907345E-3</v>
+        <v>1.6188317902410265E-2</v>
       </c>
       <c r="I9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="J9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="K9" s="12">
         <f t="shared" si="1"/>
-        <v>4.2857142857142927E-2</v>
+        <v>5.8823529411764719E-2</v>
       </c>
       <c r="L9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="R9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="S9">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="T9" s="12">
         <f t="shared" si="4"/>
-        <v>-5.9171597633136397E-3</v>
+        <v>0</v>
       </c>
       <c r="U9">
         <v>1</v>
@@ -1776,27 +1776,27 @@
       </c>
       <c r="F10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4570511.2464642841</v>
+        <v>4849624.7900021672</v>
       </c>
       <c r="G10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>1301677.642551824</v>
+        <v>1744525.7676470859</v>
       </c>
       <c r="H10" s="12">
         <f t="shared" si="0"/>
-        <v>-0.7152008665203935</v>
+        <v>-0.6402761361572662</v>
       </c>
       <c r="I10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="J10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>137</v>
+        <v>236</v>
       </c>
       <c r="K10" s="12">
         <f t="shared" si="1"/>
-        <v>1.4814814814814836E-2</v>
+        <v>0.54248366013071903</v>
       </c>
       <c r="L10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1824,15 +1824,15 @@
       </c>
       <c r="R10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="S10">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="T10" s="12">
         <f t="shared" si="4"/>
-        <v>-8.9108910891089077E-2</v>
+        <v>-6.9999999999999951E-2</v>
       </c>
       <c r="U10">
         <v>1</v>
@@ -1856,31 +1856,31 @@
       </c>
       <c r="F11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7208654.6195380623</v>
+        <v>7595456.617649341</v>
       </c>
       <c r="G11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9475751.8262754045</v>
+        <v>10045007.129200447</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" si="0"/>
-        <v>0.31449657757117233</v>
+        <v>0.32250207391865771</v>
       </c>
       <c r="I11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="J11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="K11" s="12">
         <f t="shared" si="1"/>
-        <v>5.0147492625368661E-2</v>
+        <v>0.12612612612612617</v>
       </c>
       <c r="L11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -1904,15 +1904,15 @@
       </c>
       <c r="R11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="S11">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="T11" s="12">
         <f t="shared" si="4"/>
-        <v>8.405797101449286E-2</v>
+        <v>8.35734870317002E-2</v>
       </c>
       <c r="U11">
         <v>4</v>
@@ -1936,27 +1936,27 @@
       </c>
       <c r="F12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>3398341.1812919341</v>
+        <v>3597838.8388986508</v>
       </c>
       <c r="G12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4599522.8086553616</v>
+        <v>4956645.1081354842</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="0"/>
-        <v>0.35346116333933808</v>
+        <v>0.37767291145614035</v>
       </c>
       <c r="I12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>227</v>
+        <v>191</v>
       </c>
       <c r="J12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>424</v>
+        <v>289</v>
       </c>
       <c r="K12" s="12">
         <f t="shared" si="1"/>
-        <v>0.86784140969163004</v>
+        <v>0.51308900523560208</v>
       </c>
       <c r="L12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1984,15 +1984,15 @@
       </c>
       <c r="R12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="S12">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="T12" s="12">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.8691588785046731E-2</v>
       </c>
       <c r="U12">
         <v>3</v>
@@ -2016,27 +2016,27 @@
       </c>
       <c r="F13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4634949.7732747439</v>
+        <v>4842985.5262534879</v>
       </c>
       <c r="G13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4996010.6418833202</v>
+        <v>5379290.5404999712</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="0"/>
-        <v>7.7899629180549823E-2</v>
+        <v>0.11073851270857848</v>
       </c>
       <c r="I13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="J13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="K13" s="12">
         <f t="shared" si="1"/>
-        <v>0.15228426395939088</v>
+        <v>0.44508670520231219</v>
       </c>
       <c r="L13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2064,15 +2064,15 @@
       </c>
       <c r="R13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="S13">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="T13" s="12">
         <f t="shared" si="4"/>
-        <v>-1.9920318725099584E-2</v>
+        <v>0</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -2096,31 +2096,31 @@
       </c>
       <c r="F14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8173457.9071941637</v>
+        <v>9663067.6915364582</v>
       </c>
       <c r="G14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19523999.849815324</v>
+        <v>21389073.525880821</v>
       </c>
       <c r="H14" s="12">
         <f t="shared" si="0"/>
-        <v>1.3887074566849571</v>
+        <v>1.2134868769070883</v>
       </c>
       <c r="I14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>999</v>
+        <v>1150</v>
       </c>
       <c r="J14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1223</v>
+        <v>1023</v>
       </c>
       <c r="K14" s="12">
         <f t="shared" si="1"/>
-        <v>0.22422422422422428</v>
+        <v>-0.11043478260869566</v>
       </c>
       <c r="L14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="N14" s="12">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="O14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2144,15 +2144,15 @@
       </c>
       <c r="R14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1419</v>
+        <v>1430</v>
       </c>
       <c r="S14">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1432</v>
+        <v>1435</v>
       </c>
       <c r="T14" s="12">
         <f t="shared" si="4"/>
-        <v>9.1613812544044659E-3</v>
+        <v>3.4965034965035446E-3</v>
       </c>
       <c r="U14">
         <v>3</v>
@@ -2176,27 +2176,27 @@
       </c>
       <c r="F15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>33256265.103515387</v>
+        <v>35364801.206156261</v>
       </c>
       <c r="G15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>34614044.554706417</v>
+        <v>37576961.856111161</v>
       </c>
       <c r="H15" s="12">
         <f t="shared" si="0"/>
-        <v>4.0827779276016996E-2</v>
+        <v>6.2552610915562301E-2</v>
       </c>
       <c r="I15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>922</v>
+        <v>880</v>
       </c>
       <c r="J15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1013</v>
+        <v>888</v>
       </c>
       <c r="K15" s="12">
         <f t="shared" si="1"/>
-        <v>9.8698481561822149E-2</v>
+        <v>9.0909090909090384E-3</v>
       </c>
       <c r="L15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2224,15 +2224,15 @@
       </c>
       <c r="R15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1294</v>
+        <v>1284</v>
       </c>
       <c r="S15">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1234</v>
+        <v>1241</v>
       </c>
       <c r="T15" s="12">
         <f t="shared" si="4"/>
-        <v>-4.6367851622874823E-2</v>
+        <v>-3.3489096573208754E-2</v>
       </c>
       <c r="U15">
         <v>4</v>
@@ -2256,27 +2256,27 @@
       </c>
       <c r="F16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19360881.193097025</v>
+        <v>20529893.129484031</v>
       </c>
       <c r="G16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19707768.173094597</v>
+        <v>21206747.857916113</v>
       </c>
       <c r="H16" s="12">
         <f t="shared" si="0"/>
-        <v>1.7916900400238633E-2</v>
+        <v>3.2969228050194532E-2</v>
       </c>
       <c r="I16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>910</v>
+        <v>933</v>
       </c>
       <c r="J16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>918</v>
+        <v>1135</v>
       </c>
       <c r="K16" s="12">
         <f t="shared" si="1"/>
-        <v>8.79120879120876E-3</v>
+        <v>0.21650589496248651</v>
       </c>
       <c r="L16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2304,15 +2304,15 @@
       </c>
       <c r="R16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="S16">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="T16" s="12">
         <f t="shared" si="4"/>
-        <v>2.9382957884427352E-3</v>
+        <v>1.0816125860373615E-2</v>
       </c>
       <c r="U16">
         <v>4</v>
@@ -2336,27 +2336,27 @@
       </c>
       <c r="F17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19456613.387876816</v>
+        <v>20518785.163835421</v>
       </c>
       <c r="G17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14701576.182038048</v>
+        <v>16147770.054623244</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="0"/>
-        <v>-0.24439182251529834</v>
+        <v>-0.21302504384694942</v>
       </c>
       <c r="I17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>633</v>
+        <v>854</v>
       </c>
       <c r="J17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="K17" s="12">
         <f t="shared" si="1"/>
-        <v>3.3175355450236976E-2</v>
+        <v>-0.22833723653395788</v>
       </c>
       <c r="L17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2384,15 +2384,15 @@
       </c>
       <c r="R17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="S17">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="T17" s="12">
         <f t="shared" si="4"/>
-        <v>-3.8988408851422518E-2</v>
+        <v>-4.0923399790136372E-2</v>
       </c>
       <c r="U17">
         <v>4</v>
@@ -2416,27 +2416,27 @@
       </c>
       <c r="F18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>66752926.934528187</v>
+        <v>70768744.060212836</v>
       </c>
       <c r="G18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>72814817.405791759</v>
+        <v>77632214.60653232</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="0"/>
-        <v>9.0810856536809537E-2</v>
+        <v>9.6984489939227592E-2</v>
       </c>
       <c r="I18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2123</v>
+        <v>2113</v>
       </c>
       <c r="J18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2002</v>
+        <v>2030</v>
       </c>
       <c r="K18" s="12">
         <f t="shared" si="1"/>
-        <v>-5.6994818652849721E-2</v>
+        <v>-3.9280643634642676E-2</v>
       </c>
       <c r="L18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2452,27 +2452,27 @@
       </c>
       <c r="O18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q18" s="12">
         <f t="shared" si="3"/>
-        <v>0.48305084745762716</v>
+        <v>0.47899159663865554</v>
       </c>
       <c r="R18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2745</v>
+        <v>2741</v>
       </c>
       <c r="S18">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2837</v>
+        <v>2824</v>
       </c>
       <c r="T18" s="12">
         <f t="shared" si="4"/>
-        <v>3.3515482695810617E-2</v>
+        <v>3.0280919372491777E-2</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -2496,27 +2496,27 @@
       </c>
       <c r="F19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>36794577.136621326</v>
+        <v>38832237.438178219</v>
       </c>
       <c r="G19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18253988.933064144</v>
+        <v>20817166.925483521</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="0"/>
-        <v>-0.50389458573513246</v>
+        <v>-0.4639204872337086</v>
       </c>
       <c r="I19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1169</v>
+        <v>1238</v>
       </c>
       <c r="J19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1176</v>
+        <v>1147</v>
       </c>
       <c r="K19" s="12">
         <f t="shared" si="1"/>
-        <v>5.9880239520957446E-3</v>
+        <v>-7.3505654281098565E-2</v>
       </c>
       <c r="L19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2544,15 +2544,15 @@
       </c>
       <c r="R19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="S19">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="T19" s="12">
         <f t="shared" si="4"/>
-        <v>-5.3030303030302983E-2</v>
+        <v>-4.9689440993788803E-2</v>
       </c>
       <c r="U19">
         <v>1</v>
@@ -2576,27 +2576,27 @@
       </c>
       <c r="F20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>73829830.108036533</v>
+        <v>78073507.036272019</v>
       </c>
       <c r="G20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>72601988.544970065</v>
+        <v>78167301.424380407</v>
       </c>
       <c r="H20" s="12">
         <f t="shared" si="0"/>
-        <v>-1.6630697392500338E-2</v>
+        <v>1.2013599960971622E-3</v>
       </c>
       <c r="I20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2398</v>
+        <v>2378</v>
       </c>
       <c r="J20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2168</v>
+        <v>2154</v>
       </c>
       <c r="K20" s="12">
         <f t="shared" si="1"/>
-        <v>-9.591326105087572E-2</v>
+        <v>-9.4196804037005921E-2</v>
       </c>
       <c r="L20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="O20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -2620,19 +2620,19 @@
       </c>
       <c r="Q20" s="12">
         <f t="shared" si="3"/>
-        <v>0.33333333333333326</v>
+        <v>0.23076923076923084</v>
       </c>
       <c r="R20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>3017</v>
+        <v>3018</v>
       </c>
       <c r="S20">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2967</v>
+        <v>2957</v>
       </c>
       <c r="T20" s="12">
         <f t="shared" si="4"/>
-        <v>-1.6572754391779965E-2</v>
+        <v>-2.0212060967528145E-2</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2656,27 +2656,27 @@
       </c>
       <c r="F21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10266236.082020912</v>
+        <v>10898300.815067604</v>
       </c>
       <c r="G21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10855173.82160108</v>
+        <v>11614733.231166488</v>
       </c>
       <c r="H21" s="12">
         <f t="shared" si="0"/>
-        <v>5.7366471496945737E-2</v>
+        <v>6.5737992394958367E-2</v>
       </c>
       <c r="I21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>475</v>
+        <v>732</v>
       </c>
       <c r="J21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>475</v>
+        <v>453</v>
       </c>
       <c r="K21" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-0.38114754098360659</v>
       </c>
       <c r="L21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2704,15 +2704,15 @@
       </c>
       <c r="R21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="S21">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="T21" s="12">
         <f t="shared" si="4"/>
-        <v>-2.722323049001818E-2</v>
+        <v>-3.0909090909090886E-2</v>
       </c>
       <c r="U21">
         <v>1</v>
@@ -2736,27 +2736,27 @@
       </c>
       <c r="F22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>28739105.010453988</v>
+        <v>30552762.607075132</v>
       </c>
       <c r="G22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>29878204.248217441</v>
+        <v>31893649.023847744</v>
       </c>
       <c r="H22" s="12">
         <f t="shared" si="0"/>
-        <v>3.9635863307124541E-2</v>
+        <v>4.3887567026822616E-2</v>
       </c>
       <c r="I22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1251</v>
+        <v>1289</v>
       </c>
       <c r="J22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="K22" s="12">
         <f t="shared" si="1"/>
-        <v>2.3980815347721895E-2</v>
+        <v>-7.7579519006981679E-3</v>
       </c>
       <c r="L22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2776,23 +2776,23 @@
       </c>
       <c r="P22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q22" s="12">
         <f t="shared" si="3"/>
-        <v>0.39999999999999991</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="R22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1702</v>
+        <v>1708</v>
       </c>
       <c r="S22">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1717</v>
+        <v>1714</v>
       </c>
       <c r="T22" s="12">
         <f t="shared" si="4"/>
-        <v>8.8131609870740757E-3</v>
+        <v>3.5128805620607828E-3</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2816,27 +2816,27 @@
       </c>
       <c r="F23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12792800.080579426</v>
+        <v>13458741.548888275</v>
       </c>
       <c r="G23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12026624.385429287</v>
+        <v>12988114.50952672</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="0"/>
-        <v>-5.9891164586653667E-2</v>
+        <v>-3.4968131132619207E-2</v>
       </c>
       <c r="I23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="J23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>833</v>
+        <v>894</v>
       </c>
       <c r="K23" s="12">
         <f t="shared" si="1"/>
-        <v>0.10477453580901863</v>
+        <v>0.18725099601593631</v>
       </c>
       <c r="L23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2852,27 +2852,27 @@
       </c>
       <c r="O23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q23" s="12">
         <f t="shared" si="3"/>
-        <v>0.28571428571428581</v>
+        <v>0.25</v>
       </c>
       <c r="R23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="S23">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="T23" s="12">
         <f t="shared" si="4"/>
-        <v>2.0954598370197974E-2</v>
+        <v>2.9239766081871288E-2</v>
       </c>
       <c r="U23">
         <v>1</v>
@@ -2896,27 +2896,27 @@
       </c>
       <c r="F24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14116105.390142018</v>
+        <v>15117116.893560741</v>
       </c>
       <c r="G24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15041764.988150029</v>
+        <v>16143654.376540195</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="0"/>
-        <v>6.5574715718291987E-2</v>
+        <v>6.7905639032050935E-2</v>
       </c>
       <c r="I24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>716</v>
+        <v>732</v>
       </c>
       <c r="J24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>668</v>
+        <v>871</v>
       </c>
       <c r="K24" s="12">
         <f t="shared" si="1"/>
-        <v>-6.7039106145251437E-2</v>
+        <v>0.18989071038251359</v>
       </c>
       <c r="L24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2944,15 +2944,15 @@
       </c>
       <c r="R24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="S24">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="T24" s="12">
         <f t="shared" si="4"/>
-        <v>-1.8826135105204922E-2</v>
+        <v>-1.9955654101995512E-2</v>
       </c>
       <c r="U24">
         <v>3</v>
@@ -2976,27 +2976,27 @@
       </c>
       <c r="F25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4085296.183992228</v>
+        <v>4374488.2756901234</v>
       </c>
       <c r="G25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3252983.6141009722</v>
+        <v>3544161.3962469618</v>
       </c>
       <c r="H25" s="12">
         <f t="shared" si="0"/>
-        <v>-0.20373371535522411</v>
+        <v>-0.18981120238850535</v>
       </c>
       <c r="I25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="J25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="K25" s="12">
         <f t="shared" si="1"/>
-        <v>-5.6994818652849721E-2</v>
+        <v>-5.5865921787709993E-3</v>
       </c>
       <c r="L25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3024,15 +3024,15 @@
       </c>
       <c r="R25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="S25">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="T25" s="12">
         <f t="shared" si="4"/>
-        <v>8.9285714285713969E-3</v>
+        <v>9.009009009008917E-3</v>
       </c>
       <c r="U25">
         <v>1</v>
@@ -3056,27 +3056,27 @@
       </c>
       <c r="F26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>32881334.951630816</v>
+        <v>34543080.136784635</v>
       </c>
       <c r="G26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>28162389.603792943</v>
+        <v>30361312.978099201</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="0"/>
-        <v>-0.14351440885169497</v>
+        <v>-0.12105947536022721</v>
       </c>
       <c r="I26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1346</v>
+        <v>1360</v>
       </c>
       <c r="J26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1478</v>
+        <v>1456</v>
       </c>
       <c r="K26" s="12">
         <f t="shared" si="1"/>
-        <v>9.8068350668647941E-2</v>
+        <v>7.0588235294117618E-2</v>
       </c>
       <c r="L26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3104,15 +3104,15 @@
       </c>
       <c r="R26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1664</v>
+        <v>1670</v>
       </c>
       <c r="S26">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1644</v>
+        <v>1647</v>
       </c>
       <c r="T26" s="12">
         <f t="shared" si="4"/>
-        <v>-1.2019230769230727E-2</v>
+        <v>-1.377245508982039E-2</v>
       </c>
       <c r="U26">
         <v>1</v>
@@ -3136,27 +3136,27 @@
       </c>
       <c r="F27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>22398496.405254211</v>
+        <v>23829126.881211925</v>
       </c>
       <c r="G27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23291306.937544983</v>
+        <v>25123400.694838129</v>
       </c>
       <c r="H27" s="12">
         <f t="shared" si="0"/>
-        <v>3.9860288661221821E-2</v>
+        <v>5.4314781237187137E-2</v>
       </c>
       <c r="I27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="J27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>646</v>
+        <v>683</v>
       </c>
       <c r="K27" s="12">
         <f t="shared" si="1"/>
-        <v>1.8927444794952786E-2</v>
+        <v>7.5590551181102361E-2</v>
       </c>
       <c r="L27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3172,27 +3172,27 @@
       </c>
       <c r="O27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q27" s="12">
         <f t="shared" si="3"/>
-        <v>-0.66666666666666674</v>
+        <v>-0.5</v>
       </c>
       <c r="R27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>865</v>
+        <v>858</v>
       </c>
       <c r="S27">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="T27" s="12">
         <f t="shared" si="4"/>
-        <v>1.0404624277456698E-2</v>
+        <v>1.9813519813519864E-2</v>
       </c>
       <c r="U27">
         <v>1</v>
@@ -3216,27 +3216,27 @@
       </c>
       <c r="F28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24190546.883645892</v>
+        <v>25615523.717296895</v>
       </c>
       <c r="G28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22608286.960778888</v>
+        <v>24340756.119797848</v>
       </c>
       <c r="H28" s="12">
         <f t="shared" si="0"/>
-        <v>-6.5408191492218659E-2</v>
+        <v>-4.9765431758018619E-2</v>
       </c>
       <c r="I28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="J28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>787</v>
+        <v>813</v>
       </c>
       <c r="K28" s="12">
         <f t="shared" si="1"/>
-        <v>8.4022038567493018E-2</v>
+        <v>0.19033674963396785</v>
       </c>
       <c r="L28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="O28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3260,19 +3260,19 @@
       </c>
       <c r="Q28" s="12">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="S28">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="T28" s="12">
         <f t="shared" si="4"/>
-        <v>-6.6254416961130769E-2</v>
+        <v>-6.9849690539345755E-2</v>
       </c>
       <c r="U28">
         <v>1</v>
@@ -3296,27 +3296,27 @@
       </c>
       <c r="F29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>31449964.011454657</v>
+        <v>33440236.344155505</v>
       </c>
       <c r="G29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>30719241.13553416</v>
+        <v>33277591.184311975</v>
       </c>
       <c r="H29" s="12">
         <f t="shared" si="0"/>
-        <v>-2.3234458254208334E-2</v>
+        <v>-4.8637562895681441E-3</v>
       </c>
       <c r="I29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="J29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="K29" s="12">
         <f t="shared" si="1"/>
-        <v>-0.10963114754098358</v>
+        <v>-0.11644535240040854</v>
       </c>
       <c r="L29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3336,23 +3336,23 @@
       </c>
       <c r="P29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q29" s="12">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="S29">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="T29" s="12">
         <f t="shared" si="4"/>
-        <v>5.3859964093356805E-3</v>
+        <v>9.8831985624439067E-3</v>
       </c>
       <c r="U29">
         <v>1</v>
@@ -3376,27 +3376,27 @@
       </c>
       <c r="F30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>46108166.034123458</v>
+        <v>48824205.713933267</v>
       </c>
       <c r="G30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>43751923.266922899</v>
+        <v>46926675.133656777</v>
       </c>
       <c r="H30" s="12">
         <f t="shared" si="0"/>
-        <v>-5.1102504607465127E-2</v>
+        <v>-3.8864545823732222E-2</v>
       </c>
       <c r="I30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="J30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1162</v>
+        <v>1108</v>
       </c>
       <c r="K30" s="12">
         <f t="shared" si="1"/>
-        <v>-5.136986301369828E-3</v>
+        <v>-4.8109965635738883E-2</v>
       </c>
       <c r="L30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3424,15 +3424,15 @@
       </c>
       <c r="R30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1508</v>
+        <v>1504</v>
       </c>
       <c r="S30">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1447</v>
+        <v>1453</v>
       </c>
       <c r="T30" s="12">
         <f t="shared" si="4"/>
-        <v>-4.0450928381962847E-2</v>
+        <v>-3.3909574468085069E-2</v>
       </c>
       <c r="U30">
         <v>4</v>
@@ -3456,31 +3456,31 @@
       </c>
       <c r="F31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17087525.954022851</v>
+        <v>18136491.705534205</v>
       </c>
       <c r="G31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17886223.967067465</v>
+        <v>19333862.377965305</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="0"/>
-        <v>4.6741583023409028E-2</v>
+        <v>6.6019971881647432E-2</v>
       </c>
       <c r="I31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>542</v>
+        <v>408</v>
       </c>
       <c r="J31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>537</v>
+        <v>566</v>
       </c>
       <c r="K31" s="12">
         <f t="shared" si="1"/>
-        <v>-9.2250922509224953E-3</v>
+        <v>0.38725490196078427</v>
       </c>
       <c r="L31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -3488,31 +3488,31 @@
       </c>
       <c r="N31" s="12">
         <f t="shared" si="2"/>
-        <v>1.5</v>
+        <v>0.66666666666666674</v>
       </c>
       <c r="O31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q31" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="R31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="S31">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="T31" s="12">
         <f t="shared" si="4"/>
-        <v>-1.7341040462427793E-2</v>
+        <v>-8.6830680173661801E-3</v>
       </c>
       <c r="U31">
         <v>3</v>
@@ -3536,27 +3536,27 @@
       </c>
       <c r="F32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>54279827.871796161</v>
+        <v>57697960.692234173</v>
       </c>
       <c r="G32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>46525766.431750014</v>
+        <v>46664841.921978779</v>
       </c>
       <c r="H32" s="12">
         <f t="shared" si="0"/>
-        <v>-0.14285346405962285</v>
+        <v>-0.19122198840106308</v>
       </c>
       <c r="I32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1654</v>
+        <v>1905</v>
       </c>
       <c r="J32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>52</v>
+        <v>985</v>
       </c>
       <c r="K32" s="12">
         <f t="shared" si="1"/>
-        <v>-0.96856106408706166</v>
+        <v>-0.48293963254593175</v>
       </c>
       <c r="L32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3584,15 +3584,15 @@
       </c>
       <c r="R32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1974</v>
+        <v>1971</v>
       </c>
       <c r="S32">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1922</v>
+        <v>1906</v>
       </c>
       <c r="T32" s="12">
         <f t="shared" si="4"/>
-        <v>-2.634245187436679E-2</v>
+        <v>-3.2978183663115224E-2</v>
       </c>
       <c r="U32">
         <v>5</v>
@@ -3616,27 +3616,27 @@
       </c>
       <c r="F33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18746377.997059025</v>
+        <v>19871805.127006289</v>
       </c>
       <c r="G33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18249413.325665232</v>
+        <v>19594455.916085906</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="0"/>
-        <v>-2.6509903484916331E-2</v>
+        <v>-1.3956920830682784E-2</v>
       </c>
       <c r="I33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>723</v>
+        <v>708</v>
       </c>
       <c r="J33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>695</v>
+        <v>673</v>
       </c>
       <c r="K33" s="12">
         <f t="shared" si="1"/>
-        <v>-3.8727524204702601E-2</v>
+        <v>-4.9435028248587587E-2</v>
       </c>
       <c r="L33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3664,15 +3664,15 @@
       </c>
       <c r="R33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="S33">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="4"/>
-        <v>1.179245283018826E-3</v>
+        <v>1.7857142857142794E-2</v>
       </c>
       <c r="U33">
         <v>3</v>
@@ -3696,27 +3696,27 @@
       </c>
       <c r="F34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15180363.769693863</v>
+        <v>16205189.746109076</v>
       </c>
       <c r="G34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17338354.810338959</v>
+        <v>18498161.104133904</v>
       </c>
       <c r="H34" s="12">
         <f t="shared" si="0"/>
-        <v>0.14215674099676834</v>
+        <v>0.14149611290885256</v>
       </c>
       <c r="I34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>572</v>
+        <v>598</v>
       </c>
       <c r="J34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>534</v>
+        <v>458</v>
       </c>
       <c r="K34" s="12">
         <f t="shared" si="1"/>
-        <v>-6.643356643356646E-2</v>
+        <v>-0.23411371237458189</v>
       </c>
       <c r="L34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="O34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3740,19 +3740,19 @@
       </c>
       <c r="Q34" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>690</v>
+        <v>699</v>
       </c>
       <c r="S34">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="T34" s="12">
         <f t="shared" si="4"/>
-        <v>7.6811594202898625E-2</v>
+        <v>6.7238912732475065E-2</v>
       </c>
       <c r="U34">
         <v>4</v>
@@ -3776,27 +3776,27 @@
       </c>
       <c r="F35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>27075611.243230514</v>
+        <v>28717039.311782409</v>
       </c>
       <c r="G35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>25902505.08937801</v>
+        <v>27878934.567649979</v>
       </c>
       <c r="H35" s="12">
         <f t="shared" si="0"/>
-        <v>-4.3327042308077379E-2</v>
+        <v>-2.9184928677120303E-2</v>
       </c>
       <c r="I35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="J35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="K35" s="12">
         <f t="shared" si="1"/>
-        <v>-4.2577675489067879E-2</v>
+        <v>-4.2334096109839847E-2</v>
       </c>
       <c r="L35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="O35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3820,19 +3820,19 @@
       </c>
       <c r="Q35" s="12">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0.36363636363636354</v>
       </c>
       <c r="R35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="S35">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="T35" s="12">
         <f t="shared" si="4"/>
-        <v>5.5353901996370247E-2</v>
+        <v>5.464480874316946E-2</v>
       </c>
       <c r="U35">
         <v>13</v>
@@ -3856,27 +3856,27 @@
       </c>
       <c r="F36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>26511431.303062446</v>
+        <v>28045446.933988571</v>
       </c>
       <c r="G36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>24107934.363502286</v>
+        <v>25972836.316768873</v>
       </c>
       <c r="H36" s="12">
         <f t="shared" si="0"/>
-        <v>-9.0658890200414066E-2</v>
+        <v>-7.3901857299620288E-2</v>
       </c>
       <c r="I36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>789</v>
+        <v>755</v>
       </c>
       <c r="J36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>791</v>
+        <v>806</v>
       </c>
       <c r="K36" s="12">
         <f t="shared" si="1"/>
-        <v>2.5348542458809575E-3</v>
+        <v>6.7549668874172131E-2</v>
       </c>
       <c r="L36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3904,15 +3904,15 @@
       </c>
       <c r="R36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="S36">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1324</v>
+        <v>1315</v>
       </c>
       <c r="T36" s="12">
         <f t="shared" si="4"/>
-        <v>0.19386834986474311</v>
+        <v>0.19004524886877827</v>
       </c>
       <c r="U36">
         <v>4</v>
@@ -3936,27 +3936,27 @@
       </c>
       <c r="F37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>41714812.457557224</v>
+        <v>44086773.432414651</v>
       </c>
       <c r="G37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>44580467.56550619</v>
+        <v>47814301.153092101</v>
       </c>
       <c r="H37" s="12">
         <f t="shared" si="0"/>
-        <v>6.8696344035218404E-2</v>
+        <v>8.4549796468815774E-2</v>
       </c>
       <c r="I37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1437</v>
+        <v>1334</v>
       </c>
       <c r="J37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1447</v>
+        <v>1627</v>
       </c>
       <c r="K37" s="12">
         <f t="shared" si="1"/>
-        <v>6.9589422407794199E-3</v>
+        <v>0.21964017991004492</v>
       </c>
       <c r="L37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3984,15 +3984,15 @@
       </c>
       <c r="R37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1793</v>
+        <v>1791</v>
       </c>
       <c r="S37">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2349</v>
+        <v>2319</v>
       </c>
       <c r="T37" s="12">
         <f t="shared" si="4"/>
-        <v>0.31009481316229781</v>
+        <v>0.29480737018425462</v>
       </c>
       <c r="U37">
         <v>16</v>
@@ -4016,31 +4016,31 @@
       </c>
       <c r="F38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17457645.379634544</v>
+        <v>17501171.752967127</v>
       </c>
       <c r="G38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15995398.494616931</v>
+        <v>17234881.682922155</v>
       </c>
       <c r="H38" s="12">
         <f t="shared" si="0"/>
-        <v>-8.375968541115042E-2</v>
+        <v>-1.5215556638361938E-2</v>
       </c>
       <c r="I38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>482</v>
+        <v>38</v>
       </c>
       <c r="J38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>697</v>
+        <v>485</v>
       </c>
       <c r="K38" s="12">
         <f t="shared" si="1"/>
-        <v>0.44605809128630702</v>
+        <v>11.763157894736842</v>
       </c>
       <c r="L38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="N38" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="O38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4064,15 +4064,15 @@
       </c>
       <c r="R38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="S38">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="T38" s="12">
         <f t="shared" si="4"/>
-        <v>-1.7405063291139222E-2</v>
+        <v>1.6051364365972098E-3</v>
       </c>
       <c r="U38">
         <v>3</v>
@@ -4096,27 +4096,27 @@
       </c>
       <c r="F39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>48793911.539376937</v>
+        <v>51906929.79847452</v>
       </c>
       <c r="G39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>52343763.076205544</v>
+        <v>55848173.692558862</v>
       </c>
       <c r="H39" s="12">
         <f t="shared" si="0"/>
-        <v>7.2751936150145635E-2</v>
+        <v>7.5929050502234974E-2</v>
       </c>
       <c r="I39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1985</v>
+        <v>2207</v>
       </c>
       <c r="J39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1780</v>
+        <v>1813</v>
       </c>
       <c r="K39" s="12">
         <f t="shared" si="1"/>
-        <v>-0.10327455919395467</v>
+        <v>-0.17852288173991848</v>
       </c>
       <c r="L39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4132,27 +4132,27 @@
       </c>
       <c r="O39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q39" s="12">
         <f t="shared" si="3"/>
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="R39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2017</v>
+        <v>2026</v>
       </c>
       <c r="S39">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2057</v>
+        <v>2060</v>
       </c>
       <c r="T39" s="12">
         <f t="shared" si="4"/>
-        <v>1.98314328210214E-2</v>
+        <v>1.6781836130306038E-2</v>
       </c>
       <c r="U39">
         <v>4</v>
@@ -4176,27 +4176,27 @@
       </c>
       <c r="F40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>33739920.607283264</v>
+        <v>35818386.015351824</v>
       </c>
       <c r="G40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>35711327.025523543</v>
+        <v>38783782.459595293</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" si="0"/>
-        <v>5.8429491912163067E-2</v>
+        <v>8.2789784078280082E-2</v>
       </c>
       <c r="I40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>762</v>
+        <v>802</v>
       </c>
       <c r="J40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2065</v>
+        <v>1214</v>
       </c>
       <c r="K40" s="12">
         <f t="shared" si="1"/>
-        <v>1.7099737532808401</v>
+        <v>0.513715710723192</v>
       </c>
       <c r="L40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4224,15 +4224,15 @@
       </c>
       <c r="R40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="S40">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="T40" s="12">
         <f t="shared" si="4"/>
-        <v>3.3142857142857141E-2</v>
+        <v>3.436426116838498E-2</v>
       </c>
       <c r="U40">
         <v>3</v>
@@ -4256,27 +4256,27 @@
       </c>
       <c r="F41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>28381796.030693352</v>
+        <v>30056084.115850814</v>
       </c>
       <c r="G41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19475103.312340401</v>
+        <v>21319527.778955884</v>
       </c>
       <c r="H41" s="12">
         <f t="shared" si="0"/>
-        <v>-0.31381709278443315</v>
+        <v>-0.29067513596315397</v>
       </c>
       <c r="I41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>955</v>
+        <v>939</v>
       </c>
       <c r="J41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>854</v>
+        <v>936</v>
       </c>
       <c r="K41" s="12">
         <f t="shared" si="1"/>
-        <v>-0.10575916230366489</v>
+        <v>-3.1948881789137795E-3</v>
       </c>
       <c r="L41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4292,27 +4292,27 @@
       </c>
       <c r="O41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q41" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1151</v>
+        <v>1145</v>
       </c>
       <c r="S41">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1093</v>
+        <v>1088</v>
       </c>
       <c r="T41" s="12">
         <f t="shared" si="4"/>
-        <v>-5.0390964378801084E-2</v>
+        <v>-4.9781659388646315E-2</v>
       </c>
       <c r="U41">
         <v>4</v>
@@ -4336,27 +4336,27 @@
       </c>
       <c r="F42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>27882962.771981161</v>
+        <v>29545546.930951878</v>
       </c>
       <c r="G42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>27090027.561345614</v>
+        <v>28979341.557539623</v>
       </c>
       <c r="H42" s="12">
         <f t="shared" si="0"/>
-        <v>-2.843798261755548E-2</v>
+        <v>-1.9163814253819078E-2</v>
       </c>
       <c r="I42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>611</v>
+        <v>646</v>
       </c>
       <c r="J42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>982</v>
+        <v>564</v>
       </c>
       <c r="K42" s="12">
         <f t="shared" si="1"/>
-        <v>0.60720130932896899</v>
+        <v>-0.12693498452012386</v>
       </c>
       <c r="L42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="P42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q42" s="12">
         <f t="shared" si="3"/>
@@ -4384,15 +4384,15 @@
       </c>
       <c r="R42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="S42">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="T42" s="12">
         <f t="shared" si="4"/>
-        <v>-2.5700934579439227E-2</v>
+        <v>-3.1395348837209291E-2</v>
       </c>
       <c r="U42">
         <v>2</v>
@@ -4416,27 +4416,27 @@
       </c>
       <c r="F43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17023761.506318234</v>
+        <v>18049660.276563376</v>
       </c>
       <c r="G43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17462894.453000762</v>
+        <v>18792405.690429319</v>
       </c>
       <c r="H43" s="12">
         <f t="shared" si="0"/>
-        <v>2.5795294801301605E-2</v>
+        <v>4.1150104904210449E-2</v>
       </c>
       <c r="I43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="J43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>778</v>
+        <v>1046</v>
       </c>
       <c r="K43" s="12">
         <f t="shared" si="1"/>
-        <v>0.36252189141856395</v>
+        <v>0.79416809605488847</v>
       </c>
       <c r="L43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4464,15 +4464,15 @@
       </c>
       <c r="R43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="S43">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="T43" s="12">
         <f t="shared" si="4"/>
-        <v>5.4462934947050012E-2</v>
+        <v>4.5248868778280604E-2</v>
       </c>
       <c r="U43">
         <v>2</v>
@@ -4496,27 +4496,27 @@
       </c>
       <c r="F44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16200048.119271619</v>
+        <v>17220687.382163826</v>
       </c>
       <c r="G44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15508561.952835817</v>
+        <v>16321357.881679956</v>
       </c>
       <c r="H44" s="12">
         <f t="shared" si="0"/>
-        <v>-4.2684204475492149E-2</v>
+        <v>-5.222378645670922E-2</v>
       </c>
       <c r="I44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2510</v>
+        <v>750</v>
       </c>
       <c r="J44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>697</v>
+        <v>475</v>
       </c>
       <c r="K44" s="12">
         <f t="shared" si="1"/>
-        <v>-0.72231075697211156</v>
+        <v>-0.3666666666666667</v>
       </c>
       <c r="L44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4544,15 +4544,15 @@
       </c>
       <c r="R44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="S44">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="T44" s="12">
         <f t="shared" si="4"/>
-        <v>-7.2046109510086609E-3</v>
+        <v>-1.5781922525107572E-2</v>
       </c>
       <c r="U44">
         <v>3</v>
@@ -4576,27 +4576,27 @@
       </c>
       <c r="F45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>53212406.534532376</v>
+        <v>56121265.077946588</v>
       </c>
       <c r="G45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>47059692.469827741</v>
+        <v>50336716.63548696</v>
       </c>
       <c r="H45" s="12">
         <f t="shared" si="0"/>
-        <v>-0.11562555549356346</v>
+        <v>-0.10307231019160912</v>
       </c>
       <c r="I45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1159</v>
+        <v>1180</v>
       </c>
       <c r="J45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1133</v>
+        <v>1074</v>
       </c>
       <c r="K45" s="12">
         <f t="shared" si="1"/>
-        <v>-2.2433132010353796E-2</v>
+        <v>-8.9830508474576298E-2</v>
       </c>
       <c r="L45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4624,15 +4624,15 @@
       </c>
       <c r="R45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="S45">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="T45" s="12">
         <f t="shared" si="4"/>
-        <v>-4.4891640866873028E-2</v>
+        <v>-4.4787644787644743E-2</v>
       </c>
       <c r="U45">
         <v>5</v>
@@ -4656,27 +4656,27 @@
       </c>
       <c r="F46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>23670122.597009651</v>
+        <v>25070780.558970418</v>
       </c>
       <c r="G46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22653838.112997834</v>
+        <v>24322654.950506765</v>
       </c>
       <c r="H46" s="12">
         <f t="shared" si="0"/>
-        <v>-4.2935328274987916E-2</v>
+        <v>-2.9840539136942401E-2</v>
       </c>
       <c r="I46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>930</v>
+        <v>888</v>
       </c>
       <c r="J46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="K46" s="12">
         <f t="shared" si="1"/>
-        <v>-8.6021505376343566E-3</v>
+        <v>3.716216216216206E-2</v>
       </c>
       <c r="L46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4704,15 +4704,15 @@
       </c>
       <c r="R46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="S46">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>905</v>
+        <v>913</v>
       </c>
       <c r="T46" s="12">
         <f t="shared" si="4"/>
-        <v>4.6242774566473965E-2</v>
+        <v>5.1843317972350311E-2</v>
       </c>
       <c r="U46">
         <v>4</v>
@@ -4736,27 +4736,27 @@
       </c>
       <c r="F47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>33891083.600854926</v>
+        <v>36249311.027373917</v>
       </c>
       <c r="G47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>39599121.530364431</v>
+        <v>42593266.870044634</v>
       </c>
       <c r="H47" s="12">
         <f t="shared" si="0"/>
-        <v>0.16842299870770483</v>
+        <v>0.17500900466439306</v>
       </c>
       <c r="I47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="J47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1015</v>
+        <v>956</v>
       </c>
       <c r="K47" s="12">
         <f t="shared" si="1"/>
-        <v>-5.8765915768853594E-3</v>
+        <v>-5.8128078817733964E-2</v>
       </c>
       <c r="L47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4784,15 +4784,15 @@
       </c>
       <c r="R47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1310</v>
+        <v>1307</v>
       </c>
       <c r="S47">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="T47" s="12">
         <f t="shared" si="4"/>
-        <v>2.7480916030534264E-2</v>
+        <v>3.136954858454466E-2</v>
       </c>
       <c r="U47">
         <v>6</v>
@@ -4816,27 +4816,27 @@
       </c>
       <c r="F48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17681002.320624005</v>
+        <v>18877382.814397447</v>
       </c>
       <c r="G48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20476254.373544708</v>
+        <v>21999896.923067365</v>
       </c>
       <c r="H48" s="12">
         <f t="shared" si="0"/>
-        <v>0.15809352898846574</v>
+        <v>0.16541032935394151</v>
       </c>
       <c r="I48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="K48" s="12">
         <f t="shared" si="1"/>
-        <v>0.10393258426966301</v>
+        <v>6.197183098591541E-2</v>
       </c>
       <c r="L48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="O48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4860,19 +4860,19 @@
       </c>
       <c r="Q48" s="12">
         <f t="shared" si="3"/>
-        <v>-0.66666666666666674</v>
+        <v>-0.8</v>
       </c>
       <c r="R48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="S48">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="T48" s="12">
         <f t="shared" si="4"/>
-        <v>2.5104602510460206E-2</v>
+        <v>1.4583333333333393E-2</v>
       </c>
       <c r="U48">
         <v>1</v>
@@ -4896,27 +4896,27 @@
       </c>
       <c r="F49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18461149.150816448</v>
+        <v>19430174.451933045</v>
       </c>
       <c r="G49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14867632.890376093</v>
+        <v>16002679.555755092</v>
       </c>
       <c r="H49" s="12">
         <f t="shared" si="0"/>
-        <v>-0.19465290221553899</v>
+        <v>-0.17640062391910039</v>
       </c>
       <c r="I49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="J49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="K49" s="12">
         <f t="shared" si="1"/>
-        <v>3.6544850498338777E-2</v>
+        <v>-5.031446540880502E-2</v>
       </c>
       <c r="L49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4944,15 +4944,15 @@
       </c>
       <c r="R49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="S49">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="T49" s="12">
         <f t="shared" si="4"/>
-        <v>3.863636363636358E-2</v>
+        <v>3.3860045146726803E-2</v>
       </c>
       <c r="U49">
         <v>5</v>
@@ -4976,27 +4976,27 @@
       </c>
       <c r="F50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15175187.024739441</v>
+        <v>16077907.296333432</v>
       </c>
       <c r="G50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12944386.16594301</v>
+        <v>13853359.611095656</v>
       </c>
       <c r="H50" s="12">
         <f t="shared" si="0"/>
-        <v>-0.14700318718706096</v>
+        <v>-0.13836052442876601</v>
       </c>
       <c r="I50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>349</v>
+        <v>383</v>
       </c>
       <c r="J50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="K50" s="12">
         <f t="shared" si="1"/>
-        <v>-7.1633237822349538E-2</v>
+        <v>-0.21148825065274146</v>
       </c>
       <c r="L50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5028,11 +5028,11 @@
       </c>
       <c r="S50">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="T50" s="12">
         <f t="shared" si="4"/>
-        <v>-1.1682242990654235E-2</v>
+        <v>-1.4018691588784993E-2</v>
       </c>
       <c r="U50">
         <v>4</v>
@@ -5056,27 +5056,27 @@
       </c>
       <c r="F51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>32732404.044502798</v>
+        <v>34631933.852164701</v>
       </c>
       <c r="G51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>30650599.292324264</v>
+        <v>32913629.915348537</v>
       </c>
       <c r="H51" s="12">
         <f t="shared" si="0"/>
-        <v>-6.3600728786927019E-2</v>
+        <v>-4.961617055955303E-2</v>
       </c>
       <c r="I51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>967</v>
+        <v>987</v>
       </c>
       <c r="J51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>938</v>
+        <v>872</v>
       </c>
       <c r="K51" s="12">
         <f t="shared" si="1"/>
-        <v>-2.9989658738366121E-2</v>
+        <v>-0.11651469098277611</v>
       </c>
       <c r="L51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="O51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5100,19 +5100,19 @@
       </c>
       <c r="Q51" s="12">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>0.66666666666666674</v>
       </c>
       <c r="R51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="S51">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1108</v>
+        <v>1104</v>
       </c>
       <c r="T51" s="12">
         <f t="shared" si="4"/>
-        <v>-1.685891748003554E-2</v>
+        <v>-1.7793594306049876E-2</v>
       </c>
       <c r="U51">
         <v>5</v>
@@ -5136,27 +5136,27 @@
       </c>
       <c r="F52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>34854256.338008754</v>
+        <v>36634153.112307087</v>
       </c>
       <c r="G52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>29971764.592281073</v>
+        <v>32757032.238542307</v>
       </c>
       <c r="H52" s="12">
         <f t="shared" si="0"/>
-        <v>-0.14008308478535225</v>
+        <v>-0.10583350628794197</v>
       </c>
       <c r="I52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1018</v>
+        <v>930</v>
       </c>
       <c r="J52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>943</v>
+        <v>1002</v>
       </c>
       <c r="K52" s="12">
         <f t="shared" si="1"/>
-        <v>-7.3673870333988201E-2</v>
+        <v>7.7419354838709653E-2</v>
       </c>
       <c r="L52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5176,23 +5176,23 @@
       </c>
       <c r="P52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q52" s="12">
         <f t="shared" si="3"/>
-        <v>-0.4</v>
+        <v>-0.30000000000000004</v>
       </c>
       <c r="R52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="S52">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="T52" s="12">
         <f t="shared" si="4"/>
-        <v>5.6842105263157805E-2</v>
+        <v>6.1440677966101642E-2</v>
       </c>
       <c r="U52">
         <v>4</v>
@@ -5216,27 +5216,27 @@
       </c>
       <c r="F53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>46006855.693857841</v>
+        <v>49012795.183127128</v>
       </c>
       <c r="G53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>57135591.312040411</v>
+        <v>61098674.970430002</v>
       </c>
       <c r="H53" s="12">
         <f t="shared" si="0"/>
-        <v>0.24189298421600913</v>
+        <v>0.24658621778550383</v>
       </c>
       <c r="I53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1410</v>
+        <v>1566</v>
       </c>
       <c r="J53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1660</v>
+        <v>1601</v>
       </c>
       <c r="K53" s="12">
         <f t="shared" si="1"/>
-        <v>0.17730496453900702</v>
+        <v>2.2349936143039484E-2</v>
       </c>
       <c r="L53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5264,15 +5264,15 @@
       </c>
       <c r="R53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2212</v>
+        <v>2196</v>
       </c>
       <c r="S53">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2065</v>
+        <v>2048</v>
       </c>
       <c r="T53" s="12">
         <f t="shared" si="4"/>
-        <v>-6.6455696202531667E-2</v>
+        <v>-6.7395264116575593E-2</v>
       </c>
       <c r="U53">
         <v>8</v>
@@ -5296,27 +5296,27 @@
       </c>
       <c r="F54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15925948.807056723</v>
+        <v>16802002.123263378</v>
       </c>
       <c r="G54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14278357.522577465</v>
+        <v>15233052.180801317</v>
       </c>
       <c r="H54" s="12">
         <f t="shared" si="0"/>
-        <v>-0.10345325760115576</v>
+        <v>-9.3378749208093192E-2</v>
       </c>
       <c r="I54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>570</v>
+        <v>556</v>
       </c>
       <c r="J54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>528</v>
+        <v>447</v>
       </c>
       <c r="K54" s="12">
         <f t="shared" si="1"/>
-        <v>-7.3684210526315796E-2</v>
+        <v>-0.1960431654676259</v>
       </c>
       <c r="L54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5344,15 +5344,15 @@
       </c>
       <c r="R54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="S54">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="T54" s="12">
         <f t="shared" si="4"/>
-        <v>-1.0233918128654929E-2</v>
+        <v>-1.3138686131386912E-2</v>
       </c>
       <c r="U54">
         <v>2</v>
@@ -5376,31 +5376,31 @@
       </c>
       <c r="F55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>23907515.938926905</v>
+        <v>25317769.097523954</v>
       </c>
       <c r="G55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>24722818.188481327</v>
+        <v>26561551.871163208</v>
       </c>
       <c r="H55" s="12">
         <f t="shared" si="0"/>
-        <v>3.4102340520745011E-2</v>
+        <v>4.912687088851353E-2</v>
       </c>
       <c r="I55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="J55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>701</v>
+        <v>715</v>
       </c>
       <c r="K55" s="12">
         <f t="shared" si="1"/>
-        <v>9.1900311526479816E-2</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="L55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="N55" s="12">
         <f t="shared" si="2"/>
-        <v>-0.16666666666666663</v>
+        <v>0</v>
       </c>
       <c r="O55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -5424,15 +5424,15 @@
       </c>
       <c r="R55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="S55">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="T55" s="12">
         <f t="shared" si="4"/>
-        <v>-1.245753114382786E-2</v>
+        <v>-1.9209039548022555E-2</v>
       </c>
       <c r="U55">
         <v>7</v>
@@ -5456,27 +5456,27 @@
       </c>
       <c r="F56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19219152.45467395</v>
+        <v>20332674.780575395</v>
       </c>
       <c r="G56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15491777.19412148</v>
+        <v>16875594.073253468</v>
       </c>
       <c r="H56" s="12">
         <f t="shared" si="0"/>
-        <v>-0.19394066774500252</v>
+        <v>-0.17002586942592579</v>
       </c>
       <c r="I56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>636</v>
+        <v>609</v>
       </c>
       <c r="J56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>631</v>
+        <v>740</v>
       </c>
       <c r="K56" s="12">
         <f t="shared" si="1"/>
-        <v>-7.8616352201258399E-3</v>
+        <v>0.21510673234811173</v>
       </c>
       <c r="L56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5504,15 +5504,15 @@
       </c>
       <c r="R56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="S56">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="T56" s="12">
         <f t="shared" si="4"/>
-        <v>-6.0453400503778343E-2</v>
+        <v>-4.4416243654822329E-2</v>
       </c>
       <c r="U56">
         <v>3</v>
@@ -5536,27 +5536,27 @@
       </c>
       <c r="F57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>32693040.576812342</v>
+        <v>34530254.150361381</v>
       </c>
       <c r="G57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>32144751.183899943</v>
+        <v>34330986.777931541</v>
       </c>
       <c r="H57" s="12">
         <f t="shared" si="0"/>
-        <v>-1.6770828997204834E-2</v>
+        <v>-5.7708052643381524E-3</v>
       </c>
       <c r="I57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1019</v>
+        <v>1043</v>
       </c>
       <c r="J57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>937</v>
+        <v>869</v>
       </c>
       <c r="K57" s="12">
         <f t="shared" si="1"/>
-        <v>-8.0471050049067738E-2</v>
+        <v>-0.16682646212847552</v>
       </c>
       <c r="L57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="O57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5580,19 +5580,19 @@
       </c>
       <c r="Q57" s="12">
         <f t="shared" si="3"/>
-        <v>0.19999999999999996</v>
+        <v>-0.1428571428571429</v>
       </c>
       <c r="R57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1082</v>
+        <v>1089</v>
       </c>
       <c r="S57">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="T57" s="12">
         <f t="shared" si="4"/>
-        <v>2.4029574861367919E-2</v>
+        <v>2.1120293847566529E-2</v>
       </c>
       <c r="U57">
         <v>3</v>
@@ -5616,27 +5616,27 @@
       </c>
       <c r="F58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>41135039.004691504</v>
+        <v>43893016.899277039</v>
       </c>
       <c r="G58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>40223865.983752102</v>
+        <v>43409662.357671969</v>
       </c>
       <c r="H58" s="12">
         <f t="shared" si="0"/>
-        <v>-2.2150775664403377E-2</v>
+        <v>-1.1012105700417996E-2</v>
       </c>
       <c r="I58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1444</v>
+        <v>1437</v>
       </c>
       <c r="J58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1524</v>
+        <v>1339</v>
       </c>
       <c r="K58" s="12">
         <f t="shared" si="1"/>
-        <v>5.5401662049861411E-2</v>
+        <v>-6.8197633959638182E-2</v>
       </c>
       <c r="L58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5664,15 +5664,15 @@
       </c>
       <c r="R58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1349</v>
+        <v>1362</v>
       </c>
       <c r="S58">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1462</v>
+        <v>1478</v>
       </c>
       <c r="T58" s="12">
         <f t="shared" si="4"/>
-        <v>8.3765752409191929E-2</v>
+        <v>8.5168869309838469E-2</v>
       </c>
       <c r="U58">
         <v>4</v>
@@ -5696,27 +5696,27 @@
       </c>
       <c r="F59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21181066.675294984</v>
+        <v>22329910.806698915</v>
       </c>
       <c r="G59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21499850.705537871</v>
+        <v>23201281.738800615</v>
       </c>
       <c r="H59" s="12">
         <f t="shared" si="0"/>
-        <v>1.5050423811502789E-2</v>
+        <v>3.9022589012773556E-2</v>
       </c>
       <c r="I59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>717</v>
+        <v>702</v>
       </c>
       <c r="J59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>726</v>
+        <v>693</v>
       </c>
       <c r="K59" s="12">
         <f t="shared" si="1"/>
-        <v>1.2552301255230214E-2</v>
+        <v>-1.2820512820512775E-2</v>
       </c>
       <c r="L59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5736,15 +5736,15 @@
       </c>
       <c r="P59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q59" s="12">
         <f t="shared" si="3"/>
-        <v>-0.75</v>
+        <v>-0.5</v>
       </c>
       <c r="R59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="S59">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="T59" s="12">
         <f t="shared" si="4"/>
-        <v>-5.1746442432082373E-3</v>
+        <v>-1.2836970474967901E-2</v>
       </c>
       <c r="U59">
         <v>3</v>
@@ -5776,27 +5776,27 @@
       </c>
       <c r="F60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24380650.130268615</v>
+        <v>25864409.160511479</v>
       </c>
       <c r="G60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>24041232.874499574</v>
+        <v>25848326.485295001</v>
       </c>
       <c r="H60" s="12">
         <f t="shared" si="0"/>
-        <v>-1.3921583467032095E-2</v>
+        <v>-6.2180717590221146E-4</v>
       </c>
       <c r="I60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>453</v>
+        <v>466</v>
       </c>
       <c r="J60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>485</v>
+        <v>468</v>
       </c>
       <c r="K60" s="12">
         <f t="shared" si="1"/>
-        <v>7.0640176600441418E-2</v>
+        <v>4.2918454935623185E-3</v>
       </c>
       <c r="L60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5828,11 +5828,11 @@
       </c>
       <c r="S60">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="T60" s="12">
         <f t="shared" si="4"/>
-        <v>-7.3593073593073544E-2</v>
+        <v>-7.9365079365079416E-2</v>
       </c>
       <c r="U60">
         <v>10</v>
@@ -5856,27 +5856,27 @@
       </c>
       <c r="F61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>61721106.397677347</v>
+        <v>66090588.086731672</v>
       </c>
       <c r="G61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>78146220.43496713</v>
+        <v>83965424.239891231</v>
       </c>
       <c r="H61" s="12">
         <f t="shared" si="0"/>
-        <v>0.26611826968007635</v>
+        <v>0.27045963231106596</v>
       </c>
       <c r="I61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1673</v>
+        <v>1642</v>
       </c>
       <c r="J61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1781</v>
+        <v>1969</v>
       </c>
       <c r="K61" s="12">
         <f t="shared" si="1"/>
-        <v>6.4554692169754846E-2</v>
+        <v>0.1991473812423874</v>
       </c>
       <c r="L61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5884,15 +5884,15 @@
       </c>
       <c r="M61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N61" s="12">
         <f t="shared" si="2"/>
-        <v>0.11111111111111116</v>
+        <v>0.22222222222222232</v>
       </c>
       <c r="O61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5900,19 +5900,19 @@
       </c>
       <c r="Q61" s="12">
         <f t="shared" si="3"/>
-        <v>0.10000000000000009</v>
+        <v>0</v>
       </c>
       <c r="R61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2023</v>
+        <v>2028</v>
       </c>
       <c r="S61">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1992</v>
+        <v>1983</v>
       </c>
       <c r="T61" s="12">
         <f t="shared" si="4"/>
-        <v>-1.5323776569451275E-2</v>
+        <v>-2.2189349112425982E-2</v>
       </c>
       <c r="U61">
         <v>10</v>
@@ -5936,27 +5936,27 @@
       </c>
       <c r="F62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>58992955.728539579</v>
+        <v>62841028.586884134</v>
       </c>
       <c r="G62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>57962386.104648069</v>
+        <v>62126278.515833758</v>
       </c>
       <c r="H62" s="12">
         <f t="shared" si="0"/>
-        <v>-1.7469367506075639E-2</v>
+        <v>-1.1373939719369175E-2</v>
       </c>
       <c r="I62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1192</v>
+        <v>1197</v>
       </c>
       <c r="J62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1183</v>
+        <v>1096</v>
       </c>
       <c r="K62" s="12">
         <f t="shared" si="1"/>
-        <v>-7.5503355704698016E-3</v>
+        <v>-8.4377610693400218E-2</v>
       </c>
       <c r="L62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5976,23 +5976,23 @@
       </c>
       <c r="P62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q62" s="12">
         <f t="shared" si="3"/>
-        <v>-0.17647058823529416</v>
+        <v>-5.8823529411764719E-2</v>
       </c>
       <c r="R62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1624</v>
+        <v>1614</v>
       </c>
       <c r="S62">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="T62" s="12">
         <f t="shared" si="4"/>
-        <v>-2.4630541871921152E-2</v>
+        <v>-1.9206939281288693E-2</v>
       </c>
       <c r="U62">
         <v>8</v>
@@ -6016,27 +6016,27 @@
       </c>
       <c r="F63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>37368994.644287363</v>
+        <v>39412261.823200494</v>
       </c>
       <c r="G63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>37583945.764142759</v>
+        <v>40280606.360153332</v>
       </c>
       <c r="H63" s="12">
         <f t="shared" si="0"/>
-        <v>5.7521247735321523E-3</v>
+        <v>2.2032344676084392E-2</v>
       </c>
       <c r="I63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>777</v>
+        <v>740</v>
       </c>
       <c r="J63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="K63" s="12">
         <f t="shared" si="1"/>
-        <v>-5.9202059202059232E-2</v>
+        <v>-2.7027027027026973E-2</v>
       </c>
       <c r="L63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6056,23 +6056,23 @@
       </c>
       <c r="P63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q63" s="12">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="S63">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="T63" s="12">
         <f t="shared" si="4"/>
-        <v>3.6130536130536184E-2</v>
+        <v>3.4762456546929332E-2</v>
       </c>
       <c r="U63">
         <v>4</v>
@@ -6096,27 +6096,27 @@
       </c>
       <c r="F64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>53896987.492598519</v>
+        <v>57167525.883572713</v>
       </c>
       <c r="G64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>56760340.422445491</v>
+        <v>60465669.223312296</v>
       </c>
       <c r="H64" s="12">
         <f t="shared" si="0"/>
-        <v>5.3126400250852246E-2</v>
+        <v>5.7692602378080382E-2</v>
       </c>
       <c r="I64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1261</v>
+        <v>1280</v>
       </c>
       <c r="J64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1296</v>
+        <v>1405</v>
       </c>
       <c r="K64" s="12">
         <f t="shared" si="1"/>
-        <v>2.7755749405233843E-2</v>
+        <v>9.765625E-2</v>
       </c>
       <c r="L64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6132,27 +6132,27 @@
       </c>
       <c r="O64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q64" s="12">
         <f t="shared" si="3"/>
-        <v>7.2666666666666675</v>
+        <v>7.1086956521739122</v>
       </c>
       <c r="R64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1847</v>
+        <v>1831</v>
       </c>
       <c r="S64">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2294</v>
+        <v>2275</v>
       </c>
       <c r="T64" s="12">
         <f t="shared" si="4"/>
-        <v>0.2420140768814294</v>
+        <v>0.24249044238121242</v>
       </c>
       <c r="U64">
         <v>9</v>
@@ -6176,27 +6176,27 @@
       </c>
       <c r="F65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4177676.11918703</v>
+        <v>4378520.589103437</v>
       </c>
       <c r="G65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>1830061.480065604</v>
+        <v>2048502.629354598</v>
       </c>
       <c r="H65" s="12">
         <f t="shared" si="0"/>
-        <v>-0.56194270980926797</v>
+        <v>-0.53214731147945626</v>
       </c>
       <c r="I65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>243</v>
+        <v>205</v>
       </c>
       <c r="J65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="K65" s="12">
         <f t="shared" si="1"/>
-        <v>-6.5843621399176988E-2</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="L65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6224,15 +6224,15 @@
       </c>
       <c r="R65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="S65">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="T65" s="12">
         <f t="shared" si="4"/>
-        <v>-6.8965517241379337E-2</v>
+        <v>-5.4054054054054057E-2</v>
       </c>
       <c r="U65">
         <v>3</v>
@@ -6256,27 +6256,27 @@
       </c>
       <c r="F66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>42837442.990329213</v>
+        <v>45352921.739393339</v>
       </c>
       <c r="G66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>40358257.639780559</v>
+        <v>43209518.753187433</v>
       </c>
       <c r="H66" s="12">
         <f t="shared" si="0"/>
-        <v>-5.7874260868192917E-2</v>
+        <v>-4.7260527084061144E-2</v>
       </c>
       <c r="I66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1639</v>
+        <v>1505</v>
       </c>
       <c r="J66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1413</v>
+        <v>1620</v>
       </c>
       <c r="K66" s="12">
         <f t="shared" si="1"/>
-        <v>-0.13788895668090295</v>
+        <v>7.6411960132890311E-2</v>
       </c>
       <c r="L66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6296,23 +6296,23 @@
       </c>
       <c r="P66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q66" s="12">
         <f t="shared" si="3"/>
-        <v>0.60000000000000009</v>
+        <v>0.8</v>
       </c>
       <c r="R66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1737</v>
+        <v>1739</v>
       </c>
       <c r="S66">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="T66" s="12">
         <f t="shared" si="4"/>
-        <v>-4.4329303396660857E-2</v>
+        <v>-4.6003450258769396E-2</v>
       </c>
       <c r="U66">
         <v>6</v>
@@ -6336,27 +6336,27 @@
       </c>
       <c r="F67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17129997.41105824</v>
+        <v>18336011.237021081</v>
       </c>
       <c r="G67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19545247.766959641</v>
+        <v>20578373.523585159</v>
       </c>
       <c r="H67" s="12">
         <f t="shared" ref="H67:H85" si="5">IFERROR(G67/F67-1,0)</f>
-        <v>0.14099537191653289</v>
+        <v>0.12229280717480506</v>
       </c>
       <c r="I67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>590</v>
+        <v>714</v>
       </c>
       <c r="J67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>578</v>
+        <v>591</v>
       </c>
       <c r="K67" s="12">
         <f t="shared" ref="K67:K85" si="6">IFERROR(J67/I67-1,0)</f>
-        <v>-2.033898305084747E-2</v>
+        <v>-0.17226890756302526</v>
       </c>
       <c r="L67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6376,11 +6376,11 @@
       </c>
       <c r="P67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q67" s="12">
         <f t="shared" ref="Q67:Q85" si="8">IFERROR(P67/O67-1,0)</f>
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
       <c r="R67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -6388,11 +6388,11 @@
       </c>
       <c r="S67">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="T67" s="12">
         <f t="shared" ref="T67:T85" si="9">IFERROR(S67/R67-1,0)</f>
-        <v>0.10977443609022552</v>
+        <v>0.11278195488721798</v>
       </c>
       <c r="U67">
         <v>3</v>
@@ -6416,27 +6416,27 @@
       </c>
       <c r="F68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>28510903.990744784</v>
+        <v>30336217.121641062</v>
       </c>
       <c r="G68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>27871659.032617167</v>
+        <v>30139103.683555558</v>
       </c>
       <c r="H68" s="12">
         <f t="shared" si="5"/>
-        <v>-2.2421069438385066E-2</v>
+        <v>-6.4976274825278013E-3</v>
       </c>
       <c r="I68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>885</v>
+        <v>1024</v>
       </c>
       <c r="J68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>984</v>
+        <v>1057</v>
       </c>
       <c r="K68" s="12">
         <f t="shared" si="6"/>
-        <v>0.11186440677966103</v>
+        <v>3.22265625E-2</v>
       </c>
       <c r="L68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6456,23 +6456,23 @@
       </c>
       <c r="P68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q68" s="12">
         <f t="shared" si="8"/>
-        <v>-4.5454545454545414E-2</v>
+        <v>0</v>
       </c>
       <c r="R68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="S68">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1369</v>
+        <v>1362</v>
       </c>
       <c r="T68" s="12">
         <f t="shared" si="9"/>
-        <v>4.7436878347360434E-2</v>
+        <v>4.2879019908116378E-2</v>
       </c>
       <c r="U68">
         <v>4</v>
@@ -6496,27 +6496,27 @@
       </c>
       <c r="F69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15593757.28553294</v>
+        <v>16618312.391290843</v>
       </c>
       <c r="G69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17271089.170965463</v>
+        <v>18957921.415138125</v>
       </c>
       <c r="H69" s="12">
         <f t="shared" si="5"/>
-        <v>0.10756431915152742</v>
+        <v>0.14078499481532192</v>
       </c>
       <c r="I69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1312</v>
+        <v>1437</v>
       </c>
       <c r="J69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1190</v>
+        <v>1206</v>
       </c>
       <c r="K69" s="12">
         <f t="shared" si="6"/>
-        <v>-9.2987804878048808E-2</v>
+        <v>-0.16075156576200422</v>
       </c>
       <c r="L69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6536,23 +6536,23 @@
       </c>
       <c r="P69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q69" s="12">
         <f t="shared" si="8"/>
-        <v>-0.7142857142857143</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="R69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1386</v>
+        <v>1376</v>
       </c>
       <c r="S69">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="T69" s="12">
         <f t="shared" si="9"/>
-        <v>-8.7301587301587324E-2</v>
+        <v>-8.2848837209302362E-2</v>
       </c>
       <c r="U69">
         <v>4</v>
@@ -6576,27 +6576,27 @@
       </c>
       <c r="F70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>50258291.499809645</v>
+        <v>53443829.91769053</v>
       </c>
       <c r="G70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>50078251.351593465</v>
+        <v>53768628.46778176</v>
       </c>
       <c r="H70" s="12">
         <f t="shared" si="5"/>
-        <v>-3.5822974248311823E-3</v>
+        <v>6.0773816283647975E-3</v>
       </c>
       <c r="I70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1364</v>
+        <v>1221</v>
       </c>
       <c r="J70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1198</v>
+        <v>1165</v>
       </c>
       <c r="K70" s="12">
         <f t="shared" si="6"/>
-        <v>-0.1217008797653959</v>
+        <v>-4.586404586404591E-2</v>
       </c>
       <c r="L70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6624,15 +6624,15 @@
       </c>
       <c r="R70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="S70">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="T70" s="12">
         <f t="shared" si="9"/>
-        <v>7.4712643678160884E-3</v>
+        <v>5.7405281285878296E-3</v>
       </c>
       <c r="U70">
         <v>4</v>
@@ -6656,19 +6656,19 @@
       </c>
       <c r="F71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11124898.409664072</v>
+        <v>11826471.965840572</v>
       </c>
       <c r="G71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10184693.362073636</v>
+        <v>10901511.46614914</v>
       </c>
       <c r="H71" s="12">
         <f t="shared" si="5"/>
-        <v>-8.451358502057793E-2</v>
+        <v>-7.8211025432020298E-2</v>
       </c>
       <c r="I71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>515</v>
+        <v>481</v>
       </c>
       <c r="J71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="K71" s="12">
         <f t="shared" si="6"/>
-        <v>-0.16116504854368929</v>
+        <v>-0.10187110187110182</v>
       </c>
       <c r="L71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6704,15 +6704,15 @@
       </c>
       <c r="R71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="S71">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="T71" s="12">
         <f t="shared" si="9"/>
-        <v>4.0404040404040442E-2</v>
+        <v>3.0364372469635637E-2</v>
       </c>
       <c r="U71">
         <v>2</v>
@@ -6736,27 +6736,27 @@
       </c>
       <c r="F72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16955552.557962589</v>
+        <v>17876676.04137864</v>
       </c>
       <c r="G72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15810033.870585823</v>
+        <v>17293360.891407505</v>
       </c>
       <c r="H72" s="12">
         <f t="shared" si="5"/>
-        <v>-6.7560091802423283E-2</v>
+        <v>-3.2629955849787229E-2</v>
       </c>
       <c r="I72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="J72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1000</v>
+        <v>1324</v>
       </c>
       <c r="K72" s="12">
         <f t="shared" si="6"/>
-        <v>0.2406947890818858</v>
+        <v>0.6508728179551122</v>
       </c>
       <c r="L72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6784,15 +6784,15 @@
       </c>
       <c r="R72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="S72">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="T72" s="12">
         <f t="shared" si="9"/>
-        <v>-1.3377926421404673E-2</v>
+        <v>-2.4363233665559259E-2</v>
       </c>
       <c r="U72">
         <v>3</v>
@@ -6816,27 +6816,27 @@
       </c>
       <c r="F73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12369088.577015188</v>
+        <v>13557893.517239362</v>
       </c>
       <c r="G73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15807488.14342864</v>
+        <v>17057156.633488394</v>
       </c>
       <c r="H73" s="12">
         <f t="shared" si="5"/>
-        <v>0.2779832600441432</v>
+        <v>0.25809784623249854</v>
       </c>
       <c r="I73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="J73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="K73" s="12">
         <f t="shared" si="6"/>
-        <v>-3.4090909090909061E-2</v>
+        <v>-4.7258979206049156E-2</v>
       </c>
       <c r="L73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6864,15 +6864,15 @@
       </c>
       <c r="R73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="S73">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="T73" s="12">
         <f t="shared" si="9"/>
-        <v>-4.9707602339181256E-2</v>
+        <v>-4.7267355982274717E-2</v>
       </c>
       <c r="U73">
         <v>7</v>
@@ -6896,27 +6896,27 @@
       </c>
       <c r="F74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11378936.90622247</v>
+        <v>12063598.275348464</v>
       </c>
       <c r="G74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12568715.058400322</v>
+        <v>13402969.79479092</v>
       </c>
       <c r="H74" s="12">
         <f t="shared" si="5"/>
-        <v>0.10455969322821645</v>
+        <v>0.11102587212137305</v>
       </c>
       <c r="I74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>736</v>
+        <v>672</v>
       </c>
       <c r="J74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="K74" s="12">
         <f t="shared" si="6"/>
-        <v>-4.6195652173913082E-2</v>
+        <v>4.1666666666666741E-2</v>
       </c>
       <c r="L74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="O74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -6940,19 +6940,19 @@
       </c>
       <c r="Q74" s="12">
         <f t="shared" si="8"/>
-        <v>0.5</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="R74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="S74">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="T74" s="12">
         <f t="shared" si="9"/>
-        <v>2.1702838063438978E-2</v>
+        <v>1.4975041597337757E-2</v>
       </c>
       <c r="U74">
         <v>2</v>
@@ -6976,27 +6976,27 @@
       </c>
       <c r="F75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12943551.285408163</v>
+        <v>13708803.873142265</v>
       </c>
       <c r="G75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13584670.070504978</v>
+        <v>14530462.249641132</v>
       </c>
       <c r="H75" s="12">
         <f t="shared" si="5"/>
-        <v>4.9531907508225892E-2</v>
+        <v>5.9936547645022875E-2</v>
       </c>
       <c r="I75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>425</v>
+        <v>403</v>
       </c>
       <c r="J75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>463</v>
+        <v>405</v>
       </c>
       <c r="K75" s="12">
         <f t="shared" si="6"/>
-        <v>8.9411764705882302E-2</v>
+        <v>4.9627791563275903E-3</v>
       </c>
       <c r="L75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7028,11 +7028,11 @@
       </c>
       <c r="S75">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="T75" s="12">
         <f t="shared" si="9"/>
-        <v>6.8027210884353817E-3</v>
+        <v>1.133786848072571E-2</v>
       </c>
       <c r="U75">
         <v>1</v>
@@ -7056,27 +7056,27 @@
       </c>
       <c r="F76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>36997824.771402493</v>
+        <v>39546382.337860718</v>
       </c>
       <c r="G76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>36158999.173775911</v>
+        <v>38541613.188916355</v>
       </c>
       <c r="H76" s="12">
         <f t="shared" si="5"/>
-        <v>-2.2672295001379461E-2</v>
+        <v>-2.5407359397889184E-2</v>
       </c>
       <c r="I76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="J76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>562</v>
+        <v>502</v>
       </c>
       <c r="K76" s="12">
         <f t="shared" si="6"/>
-        <v>-0.28316326530612246</v>
+        <v>-0.35392535392535396</v>
       </c>
       <c r="L76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7092,7 +7092,7 @@
       </c>
       <c r="O76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -7100,19 +7100,19 @@
       </c>
       <c r="Q76" s="12">
         <f t="shared" si="8"/>
-        <v>-0.16666666666666663</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="R76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>972</v>
+        <v>965</v>
       </c>
       <c r="S76">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="T76" s="12">
         <f t="shared" si="9"/>
-        <v>-4.5267489711934172E-2</v>
+        <v>-3.6269430051813489E-2</v>
       </c>
       <c r="U76">
         <v>4</v>
@@ -7136,27 +7136,27 @@
       </c>
       <c r="F77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21724320.235075474</v>
+        <v>23025653.099902775</v>
       </c>
       <c r="G77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21556780.627003729</v>
+        <v>22939388.116681613</v>
       </c>
       <c r="H77" s="12">
         <f t="shared" si="5"/>
-        <v>-7.7120759710234132E-3</v>
+        <v>-3.7464728078234755E-3</v>
       </c>
       <c r="I77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>730</v>
+        <v>716</v>
       </c>
       <c r="J77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>715</v>
+        <v>681</v>
       </c>
       <c r="K77" s="12">
         <f t="shared" si="6"/>
-        <v>-2.0547945205479423E-2</v>
+        <v>-4.88826815642458E-2</v>
       </c>
       <c r="L77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7184,15 +7184,15 @@
       </c>
       <c r="R77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="S77">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="T77" s="12">
         <f t="shared" si="9"/>
-        <v>-2.0304568527918732E-2</v>
+        <v>-1.0217113665389577E-2</v>
       </c>
       <c r="U77">
         <v>3</v>
@@ -7216,27 +7216,27 @@
       </c>
       <c r="F78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18436711.83211863</v>
+        <v>19193236.094868459</v>
       </c>
       <c r="G78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17554926.06836798</v>
+        <v>18892615.754533097</v>
       </c>
       <c r="H78" s="12">
         <f t="shared" si="5"/>
-        <v>-4.7827713085718981E-2</v>
+        <v>-1.5662827198574147E-2</v>
       </c>
       <c r="I78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>918</v>
+        <v>418</v>
       </c>
       <c r="J78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>866</v>
+        <v>919</v>
       </c>
       <c r="K78" s="12">
         <f t="shared" si="6"/>
-        <v>-5.6644880174291923E-2</v>
+        <v>1.1985645933014353</v>
       </c>
       <c r="L78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="P78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q78" s="12">
         <f t="shared" si="8"/>
@@ -7264,15 +7264,15 @@
       </c>
       <c r="R78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="S78">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="T78" s="12">
         <f t="shared" si="9"/>
-        <v>1.8065887353878818E-2</v>
+        <v>2.5613660618996725E-2</v>
       </c>
       <c r="U78">
         <v>3</v>
@@ -7296,27 +7296,27 @@
       </c>
       <c r="F79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20675882.787564185</v>
+        <v>21820331.478659838</v>
       </c>
       <c r="G79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17375063.532339539</v>
+        <v>18937194.680255909</v>
       </c>
       <c r="H79" s="12">
         <f t="shared" si="5"/>
-        <v>-0.15964586804535241</v>
+        <v>-0.13213075159850896</v>
       </c>
       <c r="I79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>796</v>
+        <v>817</v>
       </c>
       <c r="J79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>790</v>
+        <v>859</v>
       </c>
       <c r="K79" s="12">
         <f t="shared" si="6"/>
-        <v>-7.5376884422110324E-3</v>
+        <v>5.1407588739290189E-2</v>
       </c>
       <c r="L79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7336,23 +7336,23 @@
       </c>
       <c r="P79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q79" s="12">
         <f t="shared" si="8"/>
-        <v>-0.8</v>
+        <v>-0.6</v>
       </c>
       <c r="R79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="S79">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="T79" s="12">
         <f t="shared" si="9"/>
-        <v>-2.3575638506876273E-2</v>
+        <v>-2.6470588235294135E-2</v>
       </c>
       <c r="U79">
         <v>3</v>
@@ -7376,27 +7376,27 @@
       </c>
       <c r="F80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21557213.686589696</v>
+        <v>22969864.224000525</v>
       </c>
       <c r="G80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23095754.28563593</v>
+        <v>24869476.140908346</v>
       </c>
       <c r="H80" s="12">
         <f t="shared" si="5"/>
-        <v>7.1370104755390074E-2</v>
+        <v>8.2700180479211349E-2</v>
       </c>
       <c r="I80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>715</v>
+        <v>652</v>
       </c>
       <c r="J80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="K80" s="12">
         <f t="shared" si="6"/>
-        <v>0.11328671328671325</v>
+        <v>0.21319018404907975</v>
       </c>
       <c r="L80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="O80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -7420,19 +7420,19 @@
       </c>
       <c r="Q80" s="12">
         <f t="shared" si="8"/>
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="R80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="S80">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="T80" s="12">
         <f t="shared" si="9"/>
-        <v>2.008032128514059E-2</v>
+        <v>1.0680907877169465E-2</v>
       </c>
       <c r="U80">
         <v>3</v>
@@ -7456,27 +7456,27 @@
       </c>
       <c r="F81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9879876.8658112064</v>
+        <v>10394587.674253045</v>
       </c>
       <c r="G81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10738264.072177881</v>
+        <v>11488416.949110754</v>
       </c>
       <c r="H81" s="12">
         <f t="shared" si="5"/>
-        <v>8.6882379003839549E-2</v>
+        <v>0.10523065552345834</v>
       </c>
       <c r="I81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>531</v>
+        <v>634</v>
       </c>
       <c r="J81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>510</v>
+        <v>587</v>
       </c>
       <c r="K81" s="12">
         <f t="shared" si="6"/>
-        <v>-3.9548022598870025E-2</v>
+        <v>-7.4132492113564652E-2</v>
       </c>
       <c r="L81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="O81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -7500,11 +7500,11 @@
       </c>
       <c r="Q81" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="R81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="S81">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -7512,7 +7512,7 @@
       </c>
       <c r="T81" s="12">
         <f t="shared" si="9"/>
-        <v>1.7699115044247371E-3</v>
+        <v>3.5460992907800915E-3</v>
       </c>
       <c r="U81">
         <v>1</v>
@@ -7536,27 +7536,27 @@
       </c>
       <c r="F82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>41733546.900617406</v>
+        <v>44349442.066209733</v>
       </c>
       <c r="G82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>45577456.506966852</v>
+        <v>48331718.355496056</v>
       </c>
       <c r="H82" s="12">
         <f t="shared" si="5"/>
-        <v>9.2105988870372801E-2</v>
+        <v>8.9793154180860757E-2</v>
       </c>
       <c r="I82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1295</v>
+        <v>1326</v>
       </c>
       <c r="J82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1232</v>
+        <v>1068</v>
       </c>
       <c r="K82" s="12">
         <f t="shared" si="6"/>
-        <v>-4.8648648648648596E-2</v>
+        <v>-0.19457013574660631</v>
       </c>
       <c r="L82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7572,27 +7572,27 @@
       </c>
       <c r="O82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q82" s="12">
         <f t="shared" si="8"/>
-        <v>-0.85714285714285721</v>
+        <v>-0.77777777777777779</v>
       </c>
       <c r="R82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="S82">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1765</v>
+        <v>1770</v>
       </c>
       <c r="T82" s="12">
         <f t="shared" si="9"/>
-        <v>2.9154518950437414E-2</v>
+        <v>3.1468531468531458E-2</v>
       </c>
       <c r="U82">
         <v>2</v>
@@ -7616,27 +7616,27 @@
       </c>
       <c r="F83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11696048.467407828</v>
+        <v>12502707.703434112</v>
       </c>
       <c r="G83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10779677.36682423</v>
+        <v>11400986.222267387</v>
       </c>
       <c r="H83" s="12">
         <f t="shared" si="5"/>
-        <v>-7.8348777635211975E-2</v>
+        <v>-8.8118630563850942E-2</v>
       </c>
       <c r="I83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>901</v>
+        <v>722</v>
       </c>
       <c r="J83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>636</v>
+        <v>606</v>
       </c>
       <c r="K83" s="12">
         <f t="shared" si="6"/>
-        <v>-0.29411764705882348</v>
+        <v>-0.16066481994459836</v>
       </c>
       <c r="L83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7664,15 +7664,15 @@
       </c>
       <c r="R83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>645</v>
+        <v>634</v>
       </c>
       <c r="S83">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="T83" s="12">
         <f t="shared" si="9"/>
-        <v>-0.13798449612403096</v>
+        <v>-0.10567823343848581</v>
       </c>
       <c r="U83">
         <v>2</v>
@@ -7696,19 +7696,19 @@
       </c>
       <c r="F84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19852232.268611159</v>
+        <v>21157037.639902744</v>
       </c>
       <c r="G84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19960572.610525478</v>
+        <v>21464086.625509623</v>
       </c>
       <c r="H84" s="12">
         <f t="shared" si="5"/>
-        <v>5.4573380186377918E-3</v>
+        <v>1.4512853398142012E-2</v>
       </c>
       <c r="I84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>551</v>
+        <v>652</v>
       </c>
       <c r="J84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="K84" s="12">
         <f t="shared" si="6"/>
-        <v>3.2667876588021727E-2</v>
+        <v>-0.12730061349693256</v>
       </c>
       <c r="L84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7732,7 +7732,7 @@
       </c>
       <c r="O84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -7740,11 +7740,11 @@
       </c>
       <c r="Q84" s="12">
         <f t="shared" si="8"/>
-        <v>-0.6</v>
+        <v>-0.63636363636363635</v>
       </c>
       <c r="R84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="S84">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -7752,7 +7752,7 @@
       </c>
       <c r="T84" s="12">
         <f t="shared" si="9"/>
-        <v>3.8585209003215493E-2</v>
+        <v>2.7027027027026973E-2</v>
       </c>
       <c r="U84">
         <v>7</v>
@@ -7776,27 +7776,27 @@
       </c>
       <c r="F85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5664274.1859372323</v>
+        <v>5927184.8282444756</v>
       </c>
       <c r="G85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4924927.4812102551</v>
+        <v>5259376.4748856099</v>
       </c>
       <c r="H85" s="12">
         <f t="shared" si="5"/>
-        <v>-0.13052805716265692</v>
+        <v>-0.11266872431185149</v>
       </c>
       <c r="I85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="J85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="K85" s="12">
         <f t="shared" si="6"/>
-        <v>-3.2154340836012874E-2</v>
+        <v>-5.7324840764331197E-2</v>
       </c>
       <c r="L85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7824,15 +7824,15 @@
       </c>
       <c r="R85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="S85">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="T85" s="12">
         <f t="shared" si="9"/>
-        <v>-2.8089887640448952E-3</v>
+        <v>-1.1204481792717047E-2</v>
       </c>
       <c r="U85">
         <v>2</v>
@@ -7865,43 +7865,43 @@
       <c r="A3" s="11"/>
       <c r="B3" s="11">
         <f t="shared" ref="B3:K3" si="0">SUBTOTAL(9,B6:B90)</f>
-        <v>83741</v>
+        <v>83700</v>
       </c>
       <c r="C3" s="11">
         <f t="shared" si="0"/>
-        <v>600</v>
+        <v>630</v>
       </c>
       <c r="D3" s="11">
         <f t="shared" si="0"/>
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E3" s="11">
         <f t="shared" si="0"/>
-        <v>72428</v>
+        <v>69775</v>
       </c>
       <c r="F3" s="11">
         <f t="shared" si="0"/>
-        <v>2094137380.8293059</v>
+        <v>2221039906.9815083</v>
       </c>
       <c r="G3" s="11">
         <f t="shared" si="0"/>
-        <v>84619</v>
+        <v>84549</v>
       </c>
       <c r="H3" s="11">
         <f t="shared" si="0"/>
-        <v>1046</v>
+        <v>1076</v>
       </c>
       <c r="I3" s="11">
         <f t="shared" si="0"/>
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J3" s="11">
         <f t="shared" si="0"/>
-        <v>70425</v>
+        <v>69895</v>
       </c>
       <c r="K3" s="11">
         <f t="shared" si="0"/>
-        <v>2082336634.7778966</v>
+        <v>2235483997.8356962</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -7961,7 +7961,7 @@
         <v>117</v>
       </c>
       <c r="B6" s="10">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C6" s="10">
         <v>3</v>
@@ -7970,13 +7970,13 @@
         <v>2</v>
       </c>
       <c r="E6" s="10">
-        <v>288</v>
+        <v>366</v>
       </c>
       <c r="F6" s="10">
-        <v>10081819.681227973</v>
+        <v>10600029.17885459</v>
       </c>
       <c r="G6" s="10">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="H6" s="10">
         <v>0</v>
@@ -7985,10 +7985,10 @@
         <v>2</v>
       </c>
       <c r="J6" s="10">
-        <v>386</v>
+        <v>430</v>
       </c>
       <c r="K6" s="10">
-        <v>9328903.5811648574</v>
+        <v>10028253.355198471</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
@@ -7996,22 +7996,22 @@
         <v>127</v>
       </c>
       <c r="B7" s="10">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="C7" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" s="10">
         <v>1</v>
       </c>
       <c r="E7" s="10">
-        <v>550</v>
+        <v>568</v>
       </c>
       <c r="F7" s="10">
-        <v>12646261.849610392</v>
+        <v>13325051.244588085</v>
       </c>
       <c r="G7" s="10">
-        <v>648</v>
+        <v>639</v>
       </c>
       <c r="H7" s="10">
         <v>4</v>
@@ -8020,10 +8020,10 @@
         <v>3</v>
       </c>
       <c r="J7" s="10">
-        <v>1204</v>
+        <v>544</v>
       </c>
       <c r="K7" s="10">
-        <v>10997989.293437231</v>
+        <v>11844501.537288273</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
@@ -8031,22 +8031,22 @@
         <v>119</v>
       </c>
       <c r="B8" s="10">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C8" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" s="10">
         <v>2</v>
       </c>
       <c r="E8" s="10">
-        <v>658</v>
+        <v>569</v>
       </c>
       <c r="F8" s="10">
-        <v>12713958.118884431</v>
+        <v>13568687.102148704</v>
       </c>
       <c r="G8" s="10">
-        <v>743</v>
+        <v>756</v>
       </c>
       <c r="H8" s="10">
         <v>6</v>
@@ -8055,10 +8055,10 @@
         <v>1</v>
       </c>
       <c r="J8" s="10">
-        <v>737</v>
+        <v>803</v>
       </c>
       <c r="K8" s="10">
-        <v>14219634.224562662</v>
+        <v>15687996.009139288</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
@@ -8066,7 +8066,7 @@
         <v>121</v>
       </c>
       <c r="B9" s="10">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="C9" s="10">
         <v>4</v>
@@ -8075,13 +8075,13 @@
         <v>3</v>
       </c>
       <c r="E9" s="10">
-        <v>1981</v>
+        <v>1188</v>
       </c>
       <c r="F9" s="10">
-        <v>23642031.302799549</v>
+        <v>24977688.513464183</v>
       </c>
       <c r="G9" s="10">
-        <v>1212</v>
+        <v>1206</v>
       </c>
       <c r="H9" s="10">
         <v>4</v>
@@ -8090,10 +8090,10 @@
         <v>4</v>
       </c>
       <c r="J9" s="10">
-        <v>1071</v>
+        <v>1123</v>
       </c>
       <c r="K9" s="10">
-        <v>23896411.194066271</v>
+        <v>25629330.071108133</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
@@ -8101,7 +8101,7 @@
         <v>123</v>
       </c>
       <c r="B10" s="10">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="C10" s="10">
         <v>1</v>
@@ -8110,13 +8110,13 @@
         <v>1</v>
       </c>
       <c r="E10" s="10">
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="F10" s="10">
-        <v>9596873.4474547114</v>
+        <v>10213403.496292388</v>
       </c>
       <c r="G10" s="10">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="H10" s="10">
         <v>1</v>
@@ -8125,10 +8125,10 @@
         <v>1</v>
       </c>
       <c r="J10" s="10">
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="K10" s="10">
-        <v>10735578.1970079</v>
+        <v>11564273.043757185</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
@@ -8136,7 +8136,7 @@
         <v>125</v>
       </c>
       <c r="B11" s="10">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C11" s="10">
         <v>2</v>
@@ -8145,10 +8145,10 @@
         <v>2</v>
       </c>
       <c r="E11" s="10">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="F11" s="10">
-        <v>8856040.2209448274</v>
+        <v>9311664.9737815727</v>
       </c>
       <c r="G11" s="10">
         <v>381</v>
@@ -8160,10 +8160,10 @@
         <v>2</v>
       </c>
       <c r="J11" s="10">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="K11" s="10">
-        <v>8947473.0958644543</v>
+        <v>9571632.1562437192</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -8171,25 +8171,25 @@
         <v>131</v>
       </c>
       <c r="B12" s="10">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C12" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="10">
         <v>1</v>
       </c>
       <c r="E12" s="10">
-        <v>481</v>
+        <v>464</v>
       </c>
       <c r="F12" s="10">
-        <v>10119494.23898562</v>
+        <v>10676512.083891636</v>
       </c>
       <c r="G12" s="10">
         <v>595</v>
       </c>
       <c r="H12" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="10">
         <v>3</v>
@@ -8198,7 +8198,7 @@
         <v>516</v>
       </c>
       <c r="K12" s="10">
-        <v>10567198.582857665</v>
+        <v>11355109.563810242</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
@@ -8206,7 +8206,7 @@
         <v>133</v>
       </c>
       <c r="B13" s="10">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C13" s="10">
         <v>0</v>
@@ -8215,10 +8215,10 @@
         <v>1</v>
       </c>
       <c r="E13" s="10">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="F13" s="10">
-        <v>4689917.3020850392</v>
+        <v>4961594.8237775872</v>
       </c>
       <c r="G13" s="10">
         <v>168</v>
@@ -8230,10 +8230,10 @@
         <v>1</v>
       </c>
       <c r="J13" s="10">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="K13" s="10">
-        <v>4719781.875237532</v>
+        <v>5041914.6980878524</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
@@ -8241,7 +8241,7 @@
         <v>141</v>
       </c>
       <c r="B14" s="10">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C14" s="10">
         <v>1</v>
@@ -8250,13 +8250,13 @@
         <v>0</v>
       </c>
       <c r="E14" s="10">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="F14" s="10">
-        <v>4570511.2464642841</v>
+        <v>4849624.7900021672</v>
       </c>
       <c r="G14" s="10">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H14" s="10">
         <v>1</v>
@@ -8265,10 +8265,10 @@
         <v>1</v>
       </c>
       <c r="J14" s="10">
-        <v>137</v>
+        <v>236</v>
       </c>
       <c r="K14" s="10">
-        <v>1301677.642551824</v>
+        <v>1744525.7676470859</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
@@ -8276,22 +8276,22 @@
         <v>135</v>
       </c>
       <c r="B15" s="10">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C15" s="10">
         <v>0</v>
       </c>
       <c r="D15" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="10">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="F15" s="10">
-        <v>7208654.6195380623</v>
+        <v>7595456.617649341</v>
       </c>
       <c r="G15" s="10">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="H15" s="10">
         <v>1</v>
@@ -8300,10 +8300,10 @@
         <v>1</v>
       </c>
       <c r="J15" s="10">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="K15" s="10">
-        <v>9475751.8262754045</v>
+        <v>10045007.129200447</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
@@ -8311,7 +8311,7 @@
         <v>143</v>
       </c>
       <c r="B16" s="10">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C16" s="10">
         <v>0</v>
@@ -8320,13 +8320,13 @@
         <v>2</v>
       </c>
       <c r="E16" s="10">
-        <v>227</v>
+        <v>191</v>
       </c>
       <c r="F16" s="10">
-        <v>3398341.1812919341</v>
+        <v>3597838.8388986508</v>
       </c>
       <c r="G16" s="10">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="H16" s="10">
         <v>0</v>
@@ -8335,10 +8335,10 @@
         <v>2</v>
       </c>
       <c r="J16" s="10">
-        <v>424</v>
+        <v>289</v>
       </c>
       <c r="K16" s="10">
-        <v>4599522.8086553616</v>
+        <v>4956645.1081354842</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -8346,7 +8346,7 @@
         <v>145</v>
       </c>
       <c r="B17" s="10">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C17" s="10">
         <v>7</v>
@@ -8355,13 +8355,13 @@
         <v>0</v>
       </c>
       <c r="E17" s="10">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="F17" s="10">
-        <v>4634949.7732747439</v>
+        <v>4842985.5262534879</v>
       </c>
       <c r="G17" s="10">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="H17" s="10">
         <v>1</v>
@@ -8370,10 +8370,10 @@
         <v>2</v>
       </c>
       <c r="J17" s="10">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="K17" s="10">
-        <v>4996010.6418833202</v>
+        <v>5379290.5404999712</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
@@ -8381,22 +8381,22 @@
         <v>20</v>
       </c>
       <c r="B18" s="10">
-        <v>1419</v>
+        <v>1430</v>
       </c>
       <c r="C18" s="10">
         <v>0</v>
       </c>
       <c r="D18" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="10">
-        <v>999</v>
+        <v>1150</v>
       </c>
       <c r="F18" s="10">
-        <v>8173457.9071941637</v>
+        <v>9663067.6915364582</v>
       </c>
       <c r="G18" s="10">
-        <v>1432</v>
+        <v>1435</v>
       </c>
       <c r="H18" s="10">
         <v>3</v>
@@ -8405,10 +8405,10 @@
         <v>3</v>
       </c>
       <c r="J18" s="10">
-        <v>1223</v>
+        <v>1023</v>
       </c>
       <c r="K18" s="10">
-        <v>19523999.849815324</v>
+        <v>21389073.525880821</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
@@ -8416,7 +8416,7 @@
         <v>45</v>
       </c>
       <c r="B19" s="10">
-        <v>1294</v>
+        <v>1284</v>
       </c>
       <c r="C19" s="10">
         <v>0</v>
@@ -8425,13 +8425,13 @@
         <v>2</v>
       </c>
       <c r="E19" s="10">
-        <v>922</v>
+        <v>880</v>
       </c>
       <c r="F19" s="10">
-        <v>33256265.103515387</v>
+        <v>35364801.206156261</v>
       </c>
       <c r="G19" s="10">
-        <v>1234</v>
+        <v>1241</v>
       </c>
       <c r="H19" s="10">
         <v>1</v>
@@ -8440,10 +8440,10 @@
         <v>3</v>
       </c>
       <c r="J19" s="10">
-        <v>1013</v>
+        <v>888</v>
       </c>
       <c r="K19" s="10">
-        <v>34614044.554706417</v>
+        <v>37576961.856111161</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
@@ -8451,7 +8451,7 @@
         <v>47</v>
       </c>
       <c r="B20" s="10">
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="C20" s="10">
         <v>2</v>
@@ -8460,13 +8460,13 @@
         <v>4</v>
       </c>
       <c r="E20" s="10">
-        <v>910</v>
+        <v>933</v>
       </c>
       <c r="F20" s="10">
-        <v>19360881.193097025</v>
+        <v>20529893.129484031</v>
       </c>
       <c r="G20" s="10">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="H20" s="10">
         <v>3</v>
@@ -8475,10 +8475,10 @@
         <v>5</v>
       </c>
       <c r="J20" s="10">
-        <v>918</v>
+        <v>1135</v>
       </c>
       <c r="K20" s="10">
-        <v>19707768.173094597</v>
+        <v>21206747.857916113</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
@@ -8486,7 +8486,7 @@
         <v>49</v>
       </c>
       <c r="B21" s="10">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="C21" s="10">
         <v>1</v>
@@ -8495,13 +8495,13 @@
         <v>3</v>
       </c>
       <c r="E21" s="10">
-        <v>633</v>
+        <v>854</v>
       </c>
       <c r="F21" s="10">
-        <v>19456613.387876816</v>
+        <v>20518785.163835421</v>
       </c>
       <c r="G21" s="10">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="H21" s="10">
         <v>4</v>
@@ -8510,10 +8510,10 @@
         <v>3</v>
       </c>
       <c r="J21" s="10">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="K21" s="10">
-        <v>14701576.182038048</v>
+        <v>16147770.054623244</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
@@ -8521,34 +8521,34 @@
         <v>51</v>
       </c>
       <c r="B22" s="10">
-        <v>2745</v>
+        <v>2741</v>
       </c>
       <c r="C22" s="10">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D22" s="10">
         <v>10</v>
       </c>
       <c r="E22" s="10">
-        <v>2123</v>
+        <v>2113</v>
       </c>
       <c r="F22" s="10">
-        <v>66752926.934528187</v>
+        <v>70768744.060212836</v>
       </c>
       <c r="G22" s="10">
-        <v>2837</v>
+        <v>2824</v>
       </c>
       <c r="H22" s="10">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I22" s="10">
         <v>10</v>
       </c>
       <c r="J22" s="10">
-        <v>2002</v>
+        <v>2030</v>
       </c>
       <c r="K22" s="10">
-        <v>72814817.405791759</v>
+        <v>77632214.60653232</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
@@ -8556,7 +8556,7 @@
         <v>53</v>
       </c>
       <c r="B23" s="10">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="C23" s="10">
         <v>0</v>
@@ -8565,13 +8565,13 @@
         <v>2</v>
       </c>
       <c r="E23" s="10">
-        <v>1169</v>
+        <v>1238</v>
       </c>
       <c r="F23" s="10">
-        <v>36794577.136621326</v>
+        <v>38832237.438178219</v>
       </c>
       <c r="G23" s="10">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="H23" s="10">
         <v>5</v>
@@ -8580,10 +8580,10 @@
         <v>1</v>
       </c>
       <c r="J23" s="10">
-        <v>1176</v>
+        <v>1147</v>
       </c>
       <c r="K23" s="10">
-        <v>18253988.933064144</v>
+        <v>20817166.925483521</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
@@ -8591,22 +8591,22 @@
         <v>55</v>
       </c>
       <c r="B24" s="10">
-        <v>3017</v>
+        <v>3018</v>
       </c>
       <c r="C24" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D24" s="10">
         <v>11</v>
       </c>
       <c r="E24" s="10">
-        <v>2398</v>
+        <v>2378</v>
       </c>
       <c r="F24" s="10">
-        <v>73829830.108036533</v>
+        <v>78073507.036272019</v>
       </c>
       <c r="G24" s="10">
-        <v>2967</v>
+        <v>2957</v>
       </c>
       <c r="H24" s="10">
         <v>16</v>
@@ -8615,10 +8615,10 @@
         <v>10</v>
       </c>
       <c r="J24" s="10">
-        <v>2168</v>
+        <v>2154</v>
       </c>
       <c r="K24" s="10">
-        <v>72601988.544970065</v>
+        <v>78167301.424380407</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
@@ -8626,7 +8626,7 @@
         <v>67</v>
       </c>
       <c r="B25" s="10">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C25" s="10">
         <v>5</v>
@@ -8635,13 +8635,13 @@
         <v>1</v>
       </c>
       <c r="E25" s="10">
-        <v>475</v>
+        <v>732</v>
       </c>
       <c r="F25" s="10">
-        <v>10266236.082020912</v>
+        <v>10898300.815067604</v>
       </c>
       <c r="G25" s="10">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="H25" s="10">
         <v>4</v>
@@ -8650,10 +8650,10 @@
         <v>1</v>
       </c>
       <c r="J25" s="10">
-        <v>475</v>
+        <v>453</v>
       </c>
       <c r="K25" s="10">
-        <v>10855173.82160108</v>
+        <v>11614733.231166488</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
@@ -8661,7 +8661,7 @@
         <v>74</v>
       </c>
       <c r="B26" s="10">
-        <v>1702</v>
+        <v>1708</v>
       </c>
       <c r="C26" s="10">
         <v>10</v>
@@ -8670,25 +8670,25 @@
         <v>1</v>
       </c>
       <c r="E26" s="10">
-        <v>1251</v>
+        <v>1289</v>
       </c>
       <c r="F26" s="10">
-        <v>28739105.010453988</v>
+        <v>30552762.607075132</v>
       </c>
       <c r="G26" s="10">
-        <v>1717</v>
+        <v>1714</v>
       </c>
       <c r="H26" s="10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I26" s="10">
         <v>1</v>
       </c>
       <c r="J26" s="10">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="K26" s="10">
-        <v>29878204.248217441</v>
+        <v>31893649.023847744</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
@@ -8696,34 +8696,34 @@
         <v>70</v>
       </c>
       <c r="B27" s="10">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="C27" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D27" s="10">
         <v>1</v>
       </c>
       <c r="E27" s="10">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="F27" s="10">
-        <v>12792800.080579426</v>
+        <v>13458741.548888275</v>
       </c>
       <c r="G27" s="10">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="H27" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I27" s="10">
         <v>1</v>
       </c>
       <c r="J27" s="10">
-        <v>833</v>
+        <v>894</v>
       </c>
       <c r="K27" s="10">
-        <v>12026624.385429287</v>
+        <v>12988114.50952672</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
@@ -8731,7 +8731,7 @@
         <v>72</v>
       </c>
       <c r="B28" s="10">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C28" s="10">
         <v>1</v>
@@ -8740,13 +8740,13 @@
         <v>1</v>
       </c>
       <c r="E28" s="10">
-        <v>716</v>
+        <v>732</v>
       </c>
       <c r="F28" s="10">
-        <v>14116105.390142018</v>
+        <v>15117116.893560741</v>
       </c>
       <c r="G28" s="10">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="H28" s="10">
         <v>5</v>
@@ -8755,10 +8755,10 @@
         <v>1</v>
       </c>
       <c r="J28" s="10">
-        <v>668</v>
+        <v>871</v>
       </c>
       <c r="K28" s="10">
-        <v>15041764.988150029</v>
+        <v>16143654.376540195</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
@@ -8766,23 +8766,23 @@
         <v>79</v>
       </c>
       <c r="B29" s="10">
+        <v>222</v>
+      </c>
+      <c r="C29" s="10">
+        <v>1</v>
+      </c>
+      <c r="D29" s="10">
+        <v>0</v>
+      </c>
+      <c r="E29" s="10">
+        <v>179</v>
+      </c>
+      <c r="F29" s="10">
+        <v>4374488.2756901234</v>
+      </c>
+      <c r="G29" s="10">
         <v>224</v>
       </c>
-      <c r="C29" s="10">
-        <v>1</v>
-      </c>
-      <c r="D29" s="10">
-        <v>0</v>
-      </c>
-      <c r="E29" s="10">
-        <v>193</v>
-      </c>
-      <c r="F29" s="10">
-        <v>4085296.183992228</v>
-      </c>
-      <c r="G29" s="10">
-        <v>226</v>
-      </c>
       <c r="H29" s="10">
         <v>1</v>
       </c>
@@ -8790,10 +8790,10 @@
         <v>2</v>
       </c>
       <c r="J29" s="10">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="K29" s="10">
-        <v>3252983.6141009722</v>
+        <v>3544161.3962469618</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
@@ -8801,7 +8801,7 @@
         <v>109</v>
       </c>
       <c r="B30" s="10">
-        <v>1664</v>
+        <v>1670</v>
       </c>
       <c r="C30" s="10">
         <v>2</v>
@@ -8810,13 +8810,13 @@
         <v>5</v>
       </c>
       <c r="E30" s="10">
-        <v>1346</v>
+        <v>1360</v>
       </c>
       <c r="F30" s="10">
-        <v>32881334.951630816</v>
+        <v>34543080.136784635</v>
       </c>
       <c r="G30" s="10">
-        <v>1644</v>
+        <v>1647</v>
       </c>
       <c r="H30" s="10">
         <v>10</v>
@@ -8825,10 +8825,10 @@
         <v>5</v>
       </c>
       <c r="J30" s="10">
-        <v>1478</v>
+        <v>1456</v>
       </c>
       <c r="K30" s="10">
-        <v>28162389.603792943</v>
+        <v>30361312.978099201</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
@@ -8836,34 +8836,34 @@
         <v>111</v>
       </c>
       <c r="B31" s="10">
-        <v>865</v>
+        <v>858</v>
       </c>
       <c r="C31" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" s="10">
         <v>1</v>
       </c>
       <c r="E31" s="10">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F31" s="10">
-        <v>22398496.405254211</v>
+        <v>23829126.881211925</v>
       </c>
       <c r="G31" s="10">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H31" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31" s="10">
         <v>1</v>
       </c>
       <c r="J31" s="10">
-        <v>646</v>
+        <v>683</v>
       </c>
       <c r="K31" s="10">
-        <v>23291306.937544983</v>
+        <v>25123400.694838129</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
@@ -8871,22 +8871,22 @@
         <v>113</v>
       </c>
       <c r="B32" s="10">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C32" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" s="10">
         <v>1</v>
       </c>
       <c r="E32" s="10">
-        <v>726</v>
+        <v>683</v>
       </c>
       <c r="F32" s="10">
-        <v>24190546.883645892</v>
+        <v>25615523.717296895</v>
       </c>
       <c r="G32" s="10">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="H32" s="10">
         <v>2</v>
@@ -8895,10 +8895,10 @@
         <v>2</v>
       </c>
       <c r="J32" s="10">
-        <v>787</v>
+        <v>813</v>
       </c>
       <c r="K32" s="10">
-        <v>22608286.960778888</v>
+        <v>24340756.119797848</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
@@ -8906,7 +8906,7 @@
         <v>115</v>
       </c>
       <c r="B33" s="10">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="C33" s="10">
         <v>1</v>
@@ -8915,25 +8915,25 @@
         <v>2</v>
       </c>
       <c r="E33" s="10">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="F33" s="10">
-        <v>31449964.011454657</v>
+        <v>33440236.344155505</v>
       </c>
       <c r="G33" s="10">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="H33" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I33" s="10">
         <v>2</v>
       </c>
       <c r="J33" s="10">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="K33" s="10">
-        <v>30719241.13553416</v>
+        <v>33277591.184311975</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
@@ -8941,7 +8941,7 @@
         <v>16</v>
       </c>
       <c r="B34" s="10">
-        <v>1508</v>
+        <v>1504</v>
       </c>
       <c r="C34" s="10">
         <v>1</v>
@@ -8950,13 +8950,13 @@
         <v>5</v>
       </c>
       <c r="E34" s="10">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="F34" s="10">
-        <v>46108166.034123458</v>
+        <v>48824205.713933267</v>
       </c>
       <c r="G34" s="10">
-        <v>1447</v>
+        <v>1453</v>
       </c>
       <c r="H34" s="10">
         <v>4</v>
@@ -8965,10 +8965,10 @@
         <v>4</v>
       </c>
       <c r="J34" s="10">
-        <v>1162</v>
+        <v>1108</v>
       </c>
       <c r="K34" s="10">
-        <v>43751923.266922899</v>
+        <v>46926675.133656777</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
@@ -8976,34 +8976,34 @@
         <v>18</v>
       </c>
       <c r="B35" s="10">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C35" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D35" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" s="10">
-        <v>542</v>
+        <v>408</v>
       </c>
       <c r="F35" s="10">
-        <v>17087525.954022851</v>
+        <v>18136491.705534205</v>
       </c>
       <c r="G35" s="10">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="H35" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="10">
         <v>5</v>
       </c>
       <c r="J35" s="10">
-        <v>537</v>
+        <v>566</v>
       </c>
       <c r="K35" s="10">
-        <v>17886223.967067465</v>
+        <v>19333862.377965305</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
@@ -9011,7 +9011,7 @@
         <v>43</v>
       </c>
       <c r="B36" s="10">
-        <v>1974</v>
+        <v>1971</v>
       </c>
       <c r="C36" s="10">
         <v>13</v>
@@ -9020,13 +9020,13 @@
         <v>10</v>
       </c>
       <c r="E36" s="10">
-        <v>1654</v>
+        <v>1905</v>
       </c>
       <c r="F36" s="10">
-        <v>54279827.871796161</v>
+        <v>57697960.692234173</v>
       </c>
       <c r="G36" s="10">
-        <v>1922</v>
+        <v>1906</v>
       </c>
       <c r="H36" s="10">
         <v>6</v>
@@ -9035,10 +9035,10 @@
         <v>9</v>
       </c>
       <c r="J36" s="10">
-        <v>52</v>
+        <v>985</v>
       </c>
       <c r="K36" s="10">
-        <v>46525766.431750014</v>
+        <v>46664841.921978779</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
@@ -9046,7 +9046,7 @@
         <v>152</v>
       </c>
       <c r="B37" s="10">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="C37" s="10">
         <v>2</v>
@@ -9055,13 +9055,13 @@
         <v>2</v>
       </c>
       <c r="E37" s="10">
-        <v>723</v>
+        <v>708</v>
       </c>
       <c r="F37" s="10">
-        <v>18746377.997059025</v>
+        <v>19871805.127006289</v>
       </c>
       <c r="G37" s="10">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="H37" s="10">
         <v>2</v>
@@ -9070,10 +9070,10 @@
         <v>2</v>
       </c>
       <c r="J37" s="10">
-        <v>695</v>
+        <v>673</v>
       </c>
       <c r="K37" s="10">
-        <v>18249413.325665232</v>
+        <v>19594455.916085906</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
@@ -9081,22 +9081,22 @@
         <v>149</v>
       </c>
       <c r="B38" s="10">
-        <v>690</v>
+        <v>699</v>
       </c>
       <c r="C38" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" s="10">
         <v>1</v>
       </c>
       <c r="E38" s="10">
-        <v>572</v>
+        <v>598</v>
       </c>
       <c r="F38" s="10">
-        <v>15180363.769693863</v>
+        <v>16205189.746109076</v>
       </c>
       <c r="G38" s="10">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="H38" s="10">
         <v>2</v>
@@ -9105,10 +9105,10 @@
         <v>1</v>
       </c>
       <c r="J38" s="10">
-        <v>534</v>
+        <v>458</v>
       </c>
       <c r="K38" s="10">
-        <v>17338354.810338959</v>
+        <v>18498161.104133904</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
@@ -9116,22 +9116,22 @@
         <v>154</v>
       </c>
       <c r="B39" s="10">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="C39" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D39" s="10">
         <v>2</v>
       </c>
       <c r="E39" s="10">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="F39" s="10">
-        <v>27075611.243230514</v>
+        <v>28717039.311782409</v>
       </c>
       <c r="G39" s="10">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="H39" s="10">
         <v>15</v>
@@ -9140,10 +9140,10 @@
         <v>1</v>
       </c>
       <c r="J39" s="10">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="K39" s="10">
-        <v>25902505.08937801</v>
+        <v>27878934.567649979</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
@@ -9151,7 +9151,7 @@
         <v>2</v>
       </c>
       <c r="B40" s="10">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="C40" s="10">
         <v>40</v>
@@ -9160,13 +9160,13 @@
         <v>1</v>
       </c>
       <c r="E40" s="10">
-        <v>789</v>
+        <v>755</v>
       </c>
       <c r="F40" s="10">
-        <v>26511431.303062446</v>
+        <v>28045446.933988571</v>
       </c>
       <c r="G40" s="10">
-        <v>1324</v>
+        <v>1315</v>
       </c>
       <c r="H40" s="10">
         <v>120</v>
@@ -9175,10 +9175,10 @@
         <v>1</v>
       </c>
       <c r="J40" s="10">
-        <v>791</v>
+        <v>806</v>
       </c>
       <c r="K40" s="10">
-        <v>24107934.363502286</v>
+        <v>25972836.316768873</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
@@ -9186,7 +9186,7 @@
         <v>156</v>
       </c>
       <c r="B41" s="10">
-        <v>1793</v>
+        <v>1791</v>
       </c>
       <c r="C41" s="10">
         <v>50</v>
@@ -9195,13 +9195,13 @@
         <v>4</v>
       </c>
       <c r="E41" s="10">
-        <v>1437</v>
+        <v>1334</v>
       </c>
       <c r="F41" s="10">
-        <v>41714812.457557224</v>
+        <v>44086773.432414651</v>
       </c>
       <c r="G41" s="10">
-        <v>2349</v>
+        <v>2319</v>
       </c>
       <c r="H41" s="10">
         <v>70</v>
@@ -9210,10 +9210,10 @@
         <v>5</v>
       </c>
       <c r="J41" s="10">
-        <v>1447</v>
+        <v>1627</v>
       </c>
       <c r="K41" s="10">
-        <v>44580467.56550619</v>
+        <v>47814301.153092101</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
@@ -9221,22 +9221,22 @@
         <v>14</v>
       </c>
       <c r="B42" s="10">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="C42" s="10">
         <v>2</v>
       </c>
       <c r="D42" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E42" s="10">
-        <v>482</v>
+        <v>38</v>
       </c>
       <c r="F42" s="10">
-        <v>17457645.379634544</v>
+        <v>17501171.752967127</v>
       </c>
       <c r="G42" s="10">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="H42" s="10">
         <v>1</v>
@@ -9245,10 +9245,10 @@
         <v>6</v>
       </c>
       <c r="J42" s="10">
-        <v>697</v>
+        <v>485</v>
       </c>
       <c r="K42" s="10">
-        <v>15995398.494616931</v>
+        <v>17234881.682922155</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
@@ -9256,34 +9256,34 @@
         <v>8</v>
       </c>
       <c r="B43" s="10">
-        <v>2017</v>
+        <v>2026</v>
       </c>
       <c r="C43" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D43" s="10">
         <v>5</v>
       </c>
       <c r="E43" s="10">
-        <v>1985</v>
+        <v>2207</v>
       </c>
       <c r="F43" s="10">
-        <v>48793911.539376937</v>
+        <v>51906929.79847452</v>
       </c>
       <c r="G43" s="10">
-        <v>2057</v>
+        <v>2060</v>
       </c>
       <c r="H43" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I43" s="10">
         <v>6</v>
       </c>
       <c r="J43" s="10">
-        <v>1780</v>
+        <v>1813</v>
       </c>
       <c r="K43" s="10">
-        <v>52343763.076205544</v>
+        <v>55848173.692558862</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.35">
@@ -9291,7 +9291,7 @@
         <v>39</v>
       </c>
       <c r="B44" s="10">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="C44" s="10">
         <v>4</v>
@@ -9300,13 +9300,13 @@
         <v>4</v>
       </c>
       <c r="E44" s="10">
-        <v>762</v>
+        <v>802</v>
       </c>
       <c r="F44" s="10">
-        <v>33739920.607283264</v>
+        <v>35818386.015351824</v>
       </c>
       <c r="G44" s="10">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H44" s="10">
         <v>3</v>
@@ -9315,10 +9315,10 @@
         <v>4</v>
       </c>
       <c r="J44" s="10">
-        <v>2065</v>
+        <v>1214</v>
       </c>
       <c r="K44" s="10">
-        <v>35711327.025523543</v>
+        <v>38783782.459595293</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.35">
@@ -9326,34 +9326,34 @@
         <v>6</v>
       </c>
       <c r="B45" s="10">
-        <v>1151</v>
+        <v>1145</v>
       </c>
       <c r="C45" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" s="10">
         <v>3</v>
       </c>
       <c r="E45" s="10">
-        <v>955</v>
+        <v>939</v>
       </c>
       <c r="F45" s="10">
-        <v>28381796.030693352</v>
+        <v>30056084.115850814</v>
       </c>
       <c r="G45" s="10">
-        <v>1093</v>
+        <v>1088</v>
       </c>
       <c r="H45" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I45" s="10">
         <v>3</v>
       </c>
       <c r="J45" s="10">
-        <v>854</v>
+        <v>936</v>
       </c>
       <c r="K45" s="10">
-        <v>19475103.312340401</v>
+        <v>21319527.778955884</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
@@ -9361,7 +9361,7 @@
         <v>41</v>
       </c>
       <c r="B46" s="10">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="C46" s="10">
         <v>0</v>
@@ -9370,25 +9370,25 @@
         <v>5</v>
       </c>
       <c r="E46" s="10">
-        <v>611</v>
+        <v>646</v>
       </c>
       <c r="F46" s="10">
-        <v>27882962.771981161</v>
+        <v>29545546.930951878</v>
       </c>
       <c r="G46" s="10">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H46" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I46" s="10">
         <v>4</v>
       </c>
       <c r="J46" s="10">
-        <v>982</v>
+        <v>564</v>
       </c>
       <c r="K46" s="10">
-        <v>27090027.561345614</v>
+        <v>28979341.557539623</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.35">
@@ -9396,7 +9396,7 @@
         <v>158</v>
       </c>
       <c r="B47" s="10">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C47" s="10">
         <v>3</v>
@@ -9405,13 +9405,13 @@
         <v>10</v>
       </c>
       <c r="E47" s="10">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="F47" s="10">
-        <v>17023761.506318234</v>
+        <v>18049660.276563376</v>
       </c>
       <c r="G47" s="10">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="H47" s="10">
         <v>2</v>
@@ -9420,10 +9420,10 @@
         <v>10</v>
       </c>
       <c r="J47" s="10">
-        <v>778</v>
+        <v>1046</v>
       </c>
       <c r="K47" s="10">
-        <v>17462894.453000762</v>
+        <v>18792405.690429319</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.35">
@@ -9431,7 +9431,7 @@
         <v>160</v>
       </c>
       <c r="B48" s="10">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="C48" s="10">
         <v>1</v>
@@ -9440,13 +9440,13 @@
         <v>1</v>
       </c>
       <c r="E48" s="10">
-        <v>2510</v>
+        <v>750</v>
       </c>
       <c r="F48" s="10">
-        <v>16200048.119271619</v>
+        <v>17220687.382163826</v>
       </c>
       <c r="G48" s="10">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="H48" s="10">
         <v>0</v>
@@ -9455,10 +9455,10 @@
         <v>2</v>
       </c>
       <c r="J48" s="10">
-        <v>697</v>
+        <v>475</v>
       </c>
       <c r="K48" s="10">
-        <v>15508561.952835817</v>
+        <v>16321357.881679956</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
@@ -9466,7 +9466,7 @@
         <v>83</v>
       </c>
       <c r="B49" s="10">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="C49" s="10">
         <v>8</v>
@@ -9475,13 +9475,13 @@
         <v>6</v>
       </c>
       <c r="E49" s="10">
-        <v>1159</v>
+        <v>1180</v>
       </c>
       <c r="F49" s="10">
-        <v>53212406.534532376</v>
+        <v>56121265.077946588</v>
       </c>
       <c r="G49" s="10">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="H49" s="10">
         <v>2</v>
@@ -9490,10 +9490,10 @@
         <v>5</v>
       </c>
       <c r="J49" s="10">
-        <v>1133</v>
+        <v>1074</v>
       </c>
       <c r="K49" s="10">
-        <v>47059692.469827741</v>
+        <v>50336716.63548696</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
@@ -9501,34 +9501,34 @@
         <v>202</v>
       </c>
       <c r="B50" s="10">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C50" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50" s="10">
         <v>2</v>
       </c>
       <c r="E50" s="10">
-        <v>466</v>
+        <v>450</v>
       </c>
       <c r="F50" s="10">
-        <v>9644974.3017519489</v>
+        <v>10182749.321593467</v>
       </c>
       <c r="G50" s="10">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H50" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" s="10">
         <v>1</v>
       </c>
       <c r="J50" s="10">
-        <v>473</v>
+        <v>429</v>
       </c>
       <c r="K50" s="10">
-        <v>7719861.9891268816</v>
+        <v>8258642.3442348354</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
@@ -9536,7 +9536,7 @@
         <v>31</v>
       </c>
       <c r="B51" s="10">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="C51" s="10">
         <v>1</v>
@@ -9545,13 +9545,13 @@
         <v>5</v>
       </c>
       <c r="E51" s="10">
-        <v>930</v>
+        <v>888</v>
       </c>
       <c r="F51" s="10">
-        <v>23670122.597009651</v>
+        <v>25070780.558970418</v>
       </c>
       <c r="G51" s="10">
-        <v>905</v>
+        <v>913</v>
       </c>
       <c r="H51" s="10">
         <v>2</v>
@@ -9560,10 +9560,10 @@
         <v>7</v>
       </c>
       <c r="J51" s="10">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="K51" s="10">
-        <v>22653838.112997834</v>
+        <v>24322654.950506765</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
@@ -9571,7 +9571,7 @@
         <v>33</v>
       </c>
       <c r="B52" s="10">
-        <v>1310</v>
+        <v>1307</v>
       </c>
       <c r="C52" s="10">
         <v>9</v>
@@ -9580,13 +9580,13 @@
         <v>12</v>
       </c>
       <c r="E52" s="10">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="F52" s="10">
-        <v>33891083.600854926</v>
+        <v>36249311.027373917</v>
       </c>
       <c r="G52" s="10">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="H52" s="10">
         <v>4</v>
@@ -9595,10 +9595,10 @@
         <v>12</v>
       </c>
       <c r="J52" s="10">
-        <v>1015</v>
+        <v>956</v>
       </c>
       <c r="K52" s="10">
-        <v>39599121.530364431</v>
+        <v>42593266.870044634</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.35">
@@ -9606,22 +9606,22 @@
         <v>85</v>
       </c>
       <c r="B53" s="10">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C53" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D53" s="10">
         <v>5</v>
       </c>
       <c r="E53" s="10">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F53" s="10">
-        <v>17681002.320624005</v>
+        <v>18877382.814397447</v>
       </c>
       <c r="G53" s="10">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="H53" s="10">
         <v>1</v>
@@ -9630,10 +9630,10 @@
         <v>6</v>
       </c>
       <c r="J53" s="10">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="K53" s="10">
-        <v>20476254.373544708</v>
+        <v>21999896.923067365</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.35">
@@ -9641,7 +9641,7 @@
         <v>81</v>
       </c>
       <c r="B54" s="10">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C54" s="10">
         <v>0</v>
@@ -9650,13 +9650,13 @@
         <v>6</v>
       </c>
       <c r="E54" s="10">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="F54" s="10">
-        <v>18461149.150816448</v>
+        <v>19430174.451933045</v>
       </c>
       <c r="G54" s="10">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H54" s="10">
         <v>0</v>
@@ -9665,10 +9665,10 @@
         <v>4</v>
       </c>
       <c r="J54" s="10">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="K54" s="10">
-        <v>14867632.890376093</v>
+        <v>16002679.555755092</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.35">
@@ -9685,13 +9685,13 @@
         <v>2</v>
       </c>
       <c r="E55" s="10">
-        <v>349</v>
+        <v>383</v>
       </c>
       <c r="F55" s="10">
-        <v>15175187.024739441</v>
+        <v>16077907.296333432</v>
       </c>
       <c r="G55" s="10">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H55" s="10">
         <v>1</v>
@@ -9700,10 +9700,10 @@
         <v>4</v>
       </c>
       <c r="J55" s="10">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="K55" s="10">
-        <v>12944386.16594301</v>
+        <v>13853359.611095656</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.35">
@@ -9711,22 +9711,22 @@
         <v>166</v>
       </c>
       <c r="B56" s="10">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="C56" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D56" s="10">
         <v>1</v>
       </c>
       <c r="E56" s="10">
-        <v>967</v>
+        <v>987</v>
       </c>
       <c r="F56" s="10">
-        <v>32732404.044502798</v>
+        <v>34631933.852164701</v>
       </c>
       <c r="G56" s="10">
-        <v>1108</v>
+        <v>1104</v>
       </c>
       <c r="H56" s="10">
         <v>5</v>
@@ -9735,10 +9735,10 @@
         <v>0</v>
       </c>
       <c r="J56" s="10">
-        <v>938</v>
+        <v>872</v>
       </c>
       <c r="K56" s="10">
-        <v>30650599.292324264</v>
+        <v>32913629.915348537</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
@@ -9746,7 +9746,7 @@
         <v>93</v>
       </c>
       <c r="B57" s="10">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="C57" s="10">
         <v>10</v>
@@ -9755,25 +9755,25 @@
         <v>3</v>
       </c>
       <c r="E57" s="10">
-        <v>1018</v>
+        <v>930</v>
       </c>
       <c r="F57" s="10">
-        <v>34854256.338008754</v>
+        <v>36634153.112307087</v>
       </c>
       <c r="G57" s="10">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="H57" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I57" s="10">
         <v>1</v>
       </c>
       <c r="J57" s="10">
-        <v>943</v>
+        <v>1002</v>
       </c>
       <c r="K57" s="10">
-        <v>29971764.592281073</v>
+        <v>32757032.238542307</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.35">
@@ -9781,7 +9781,7 @@
         <v>95</v>
       </c>
       <c r="B58" s="10">
-        <v>2212</v>
+        <v>2196</v>
       </c>
       <c r="C58" s="10">
         <v>35</v>
@@ -9790,13 +9790,13 @@
         <v>7</v>
       </c>
       <c r="E58" s="10">
-        <v>1410</v>
+        <v>1566</v>
       </c>
       <c r="F58" s="10">
-        <v>46006855.693857841</v>
+        <v>49012795.183127128</v>
       </c>
       <c r="G58" s="10">
-        <v>2065</v>
+        <v>2048</v>
       </c>
       <c r="H58" s="10">
         <v>8</v>
@@ -9805,10 +9805,10 @@
         <v>8</v>
       </c>
       <c r="J58" s="10">
-        <v>1660</v>
+        <v>1601</v>
       </c>
       <c r="K58" s="10">
-        <v>57135591.312040411</v>
+        <v>61098674.970430002</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.35">
@@ -9816,7 +9816,7 @@
         <v>174</v>
       </c>
       <c r="B59" s="10">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C59" s="10">
         <v>3</v>
@@ -9825,13 +9825,13 @@
         <v>0</v>
       </c>
       <c r="E59" s="10">
-        <v>570</v>
+        <v>556</v>
       </c>
       <c r="F59" s="10">
-        <v>15925948.807056723</v>
+        <v>16802002.123263378</v>
       </c>
       <c r="G59" s="10">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H59" s="10">
         <v>4</v>
@@ -9840,10 +9840,10 @@
         <v>0</v>
       </c>
       <c r="J59" s="10">
-        <v>528</v>
+        <v>447</v>
       </c>
       <c r="K59" s="10">
-        <v>14278357.522577465</v>
+        <v>15233052.180801317</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.35">
@@ -9851,22 +9851,22 @@
         <v>99</v>
       </c>
       <c r="B60" s="10">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="C60" s="10">
         <v>5</v>
       </c>
       <c r="D60" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E60" s="10">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="F60" s="10">
-        <v>23907515.938926905</v>
+        <v>25317769.097523954</v>
       </c>
       <c r="G60" s="10">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="H60" s="10">
         <v>6</v>
@@ -9875,10 +9875,10 @@
         <v>5</v>
       </c>
       <c r="J60" s="10">
-        <v>701</v>
+        <v>715</v>
       </c>
       <c r="K60" s="10">
-        <v>24722818.188481327</v>
+        <v>26561551.871163208</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.35">
@@ -9886,7 +9886,7 @@
         <v>172</v>
       </c>
       <c r="B61" s="10">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="C61" s="10">
         <v>2</v>
@@ -9895,13 +9895,13 @@
         <v>1</v>
       </c>
       <c r="E61" s="10">
-        <v>636</v>
+        <v>609</v>
       </c>
       <c r="F61" s="10">
-        <v>19219152.45467395</v>
+        <v>20332674.780575395</v>
       </c>
       <c r="G61" s="10">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="H61" s="10">
         <v>4</v>
@@ -9910,10 +9910,10 @@
         <v>1</v>
       </c>
       <c r="J61" s="10">
-        <v>631</v>
+        <v>740</v>
       </c>
       <c r="K61" s="10">
-        <v>15491777.19412148</v>
+        <v>16875594.073253468</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.35">
@@ -9921,22 +9921,22 @@
         <v>168</v>
       </c>
       <c r="B62" s="10">
-        <v>1082</v>
+        <v>1089</v>
       </c>
       <c r="C62" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D62" s="10">
         <v>1</v>
       </c>
       <c r="E62" s="10">
-        <v>1019</v>
+        <v>1043</v>
       </c>
       <c r="F62" s="10">
-        <v>32693040.576812342</v>
+        <v>34530254.150361381</v>
       </c>
       <c r="G62" s="10">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="H62" s="10">
         <v>6</v>
@@ -9945,10 +9945,10 @@
         <v>0</v>
       </c>
       <c r="J62" s="10">
-        <v>937</v>
+        <v>869</v>
       </c>
       <c r="K62" s="10">
-        <v>32144751.183899943</v>
+        <v>34330986.777931541</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.35">
@@ -9956,7 +9956,7 @@
         <v>101</v>
       </c>
       <c r="B63" s="10">
-        <v>1349</v>
+        <v>1362</v>
       </c>
       <c r="C63" s="10">
         <v>9</v>
@@ -9965,13 +9965,13 @@
         <v>4</v>
       </c>
       <c r="E63" s="10">
-        <v>1444</v>
+        <v>1437</v>
       </c>
       <c r="F63" s="10">
-        <v>41135039.004691504</v>
+        <v>43893016.899277039</v>
       </c>
       <c r="G63" s="10">
-        <v>1462</v>
+        <v>1478</v>
       </c>
       <c r="H63" s="10">
         <v>5</v>
@@ -9980,10 +9980,10 @@
         <v>4</v>
       </c>
       <c r="J63" s="10">
-        <v>1524</v>
+        <v>1339</v>
       </c>
       <c r="K63" s="10">
-        <v>40223865.983752102</v>
+        <v>43409662.357671969</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.35">
@@ -9991,7 +9991,7 @@
         <v>103</v>
       </c>
       <c r="B64" s="10">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="C64" s="10">
         <v>4</v>
@@ -10000,25 +10000,25 @@
         <v>5</v>
       </c>
       <c r="E64" s="10">
-        <v>717</v>
+        <v>702</v>
       </c>
       <c r="F64" s="10">
-        <v>21181066.675294984</v>
+        <v>22329910.806698915</v>
       </c>
       <c r="G64" s="10">
         <v>769</v>
       </c>
       <c r="H64" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I64" s="10">
         <v>4</v>
       </c>
       <c r="J64" s="10">
-        <v>726</v>
+        <v>693</v>
       </c>
       <c r="K64" s="10">
-        <v>21499850.705537871</v>
+        <v>23201281.738800615</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.35">
@@ -10035,13 +10035,13 @@
         <v>5</v>
       </c>
       <c r="E65" s="10">
-        <v>453</v>
+        <v>466</v>
       </c>
       <c r="F65" s="10">
-        <v>24380650.130268615</v>
+        <v>25864409.160511479</v>
       </c>
       <c r="G65" s="10">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="H65" s="10">
         <v>7</v>
@@ -10050,10 +10050,10 @@
         <v>5</v>
       </c>
       <c r="J65" s="10">
-        <v>485</v>
+        <v>468</v>
       </c>
       <c r="K65" s="10">
-        <v>24041232.874499574</v>
+        <v>25848326.485295001</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.35">
@@ -10061,34 +10061,34 @@
         <v>24</v>
       </c>
       <c r="B66" s="10">
-        <v>2023</v>
+        <v>2028</v>
       </c>
       <c r="C66" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D66" s="10">
         <v>9</v>
       </c>
       <c r="E66" s="10">
-        <v>1673</v>
+        <v>1642</v>
       </c>
       <c r="F66" s="10">
-        <v>61721106.397677347</v>
+        <v>66090588.086731672</v>
       </c>
       <c r="G66" s="10">
-        <v>1992</v>
+        <v>1983</v>
       </c>
       <c r="H66" s="10">
         <v>11</v>
       </c>
       <c r="I66" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J66" s="10">
-        <v>1781</v>
+        <v>1969</v>
       </c>
       <c r="K66" s="10">
-        <v>78146220.43496713</v>
+        <v>83965424.239891231</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.35">
@@ -10096,7 +10096,7 @@
         <v>27</v>
       </c>
       <c r="B67" s="10">
-        <v>1624</v>
+        <v>1614</v>
       </c>
       <c r="C67" s="10">
         <v>17</v>
@@ -10105,25 +10105,25 @@
         <v>8</v>
       </c>
       <c r="E67" s="10">
-        <v>1192</v>
+        <v>1197</v>
       </c>
       <c r="F67" s="10">
-        <v>58992955.728539579</v>
+        <v>62841028.586884134</v>
       </c>
       <c r="G67" s="10">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H67" s="10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I67" s="10">
         <v>6</v>
       </c>
       <c r="J67" s="10">
-        <v>1183</v>
+        <v>1096</v>
       </c>
       <c r="K67" s="10">
-        <v>57962386.104648069</v>
+        <v>62126278.515833758</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.35">
@@ -10131,7 +10131,7 @@
         <v>29</v>
       </c>
       <c r="B68" s="10">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="C68" s="10">
         <v>2</v>
@@ -10140,25 +10140,25 @@
         <v>1</v>
       </c>
       <c r="E68" s="10">
-        <v>777</v>
+        <v>740</v>
       </c>
       <c r="F68" s="10">
-        <v>37368994.644287363</v>
+        <v>39412261.823200494</v>
       </c>
       <c r="G68" s="10">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="H68" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I68" s="10">
         <v>1</v>
       </c>
       <c r="J68" s="10">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="K68" s="10">
-        <v>37583945.764142759</v>
+        <v>40280606.360153332</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.35">
@@ -10166,34 +10166,34 @@
         <v>57</v>
       </c>
       <c r="B69" s="10">
-        <v>1847</v>
+        <v>1831</v>
       </c>
       <c r="C69" s="10">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D69" s="10">
         <v>13</v>
       </c>
       <c r="E69" s="10">
-        <v>1261</v>
+        <v>1280</v>
       </c>
       <c r="F69" s="10">
-        <v>53896987.492598519</v>
+        <v>57167525.883572713</v>
       </c>
       <c r="G69" s="10">
-        <v>2294</v>
+        <v>2275</v>
       </c>
       <c r="H69" s="10">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I69" s="10">
         <v>12</v>
       </c>
       <c r="J69" s="10">
-        <v>1296</v>
+        <v>1405</v>
       </c>
       <c r="K69" s="10">
-        <v>56760340.422445491</v>
+        <v>60465669.223312296</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.35">
@@ -10201,7 +10201,7 @@
         <v>137</v>
       </c>
       <c r="B70" s="10">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C70" s="10">
         <v>1</v>
@@ -10210,13 +10210,13 @@
         <v>1</v>
       </c>
       <c r="E70" s="10">
-        <v>243</v>
+        <v>205</v>
       </c>
       <c r="F70" s="10">
-        <v>4177676.11918703</v>
+        <v>4378520.589103437</v>
       </c>
       <c r="G70" s="10">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H70" s="10">
         <v>0</v>
@@ -10225,10 +10225,10 @@
         <v>1</v>
       </c>
       <c r="J70" s="10">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="K70" s="10">
-        <v>1830061.480065604</v>
+        <v>2048502.629354598</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.35">
@@ -10236,7 +10236,7 @@
         <v>10</v>
       </c>
       <c r="B71" s="10">
-        <v>1737</v>
+        <v>1739</v>
       </c>
       <c r="C71" s="10">
         <v>5</v>
@@ -10245,25 +10245,25 @@
         <v>8</v>
       </c>
       <c r="E71" s="10">
-        <v>1639</v>
+        <v>1505</v>
       </c>
       <c r="F71" s="10">
-        <v>42837442.990329213</v>
+        <v>45352921.739393339</v>
       </c>
       <c r="G71" s="10">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="H71" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I71" s="10">
         <v>6</v>
       </c>
       <c r="J71" s="10">
-        <v>1413</v>
+        <v>1620</v>
       </c>
       <c r="K71" s="10">
-        <v>40358257.639780559</v>
+        <v>43209518.753187433</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.35">
@@ -10280,25 +10280,25 @@
         <v>2</v>
       </c>
       <c r="E72" s="10">
-        <v>590</v>
+        <v>714</v>
       </c>
       <c r="F72" s="10">
-        <v>17129997.41105824</v>
+        <v>18336011.237021081</v>
       </c>
       <c r="G72" s="10">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="H72" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I72" s="10">
         <v>3</v>
       </c>
       <c r="J72" s="10">
-        <v>578</v>
+        <v>591</v>
       </c>
       <c r="K72" s="10">
-        <v>19545247.766959641</v>
+        <v>20578373.523585159</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.35">
@@ -10306,7 +10306,7 @@
         <v>162</v>
       </c>
       <c r="B73" s="10">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="C73" s="10">
         <v>22</v>
@@ -10315,25 +10315,25 @@
         <v>5</v>
       </c>
       <c r="E73" s="10">
-        <v>885</v>
+        <v>1024</v>
       </c>
       <c r="F73" s="10">
-        <v>28510903.990744784</v>
+        <v>30336217.121641062</v>
       </c>
       <c r="G73" s="10">
-        <v>1369</v>
+        <v>1362</v>
       </c>
       <c r="H73" s="10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I73" s="10">
         <v>4</v>
       </c>
       <c r="J73" s="10">
-        <v>984</v>
+        <v>1057</v>
       </c>
       <c r="K73" s="10">
-        <v>27871659.032617167</v>
+        <v>30139103.683555558</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.35">
@@ -10341,7 +10341,7 @@
         <v>63</v>
       </c>
       <c r="B74" s="10">
-        <v>1386</v>
+        <v>1376</v>
       </c>
       <c r="C74" s="10">
         <v>7</v>
@@ -10350,25 +10350,25 @@
         <v>5</v>
       </c>
       <c r="E74" s="10">
-        <v>1312</v>
+        <v>1437</v>
       </c>
       <c r="F74" s="10">
-        <v>15593757.28553294</v>
+        <v>16618312.391290843</v>
       </c>
       <c r="G74" s="10">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="H74" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I74" s="10">
         <v>5</v>
       </c>
       <c r="J74" s="10">
-        <v>1190</v>
+        <v>1206</v>
       </c>
       <c r="K74" s="10">
-        <v>17271089.170965463</v>
+        <v>18957921.415138125</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.35">
@@ -10376,7 +10376,7 @@
         <v>59</v>
       </c>
       <c r="B75" s="10">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="C75" s="10">
         <v>5</v>
@@ -10385,13 +10385,13 @@
         <v>5</v>
       </c>
       <c r="E75" s="10">
-        <v>1364</v>
+        <v>1221</v>
       </c>
       <c r="F75" s="10">
-        <v>50258291.499809645</v>
+        <v>53443829.91769053</v>
       </c>
       <c r="G75" s="10">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="H75" s="10">
         <v>10</v>
@@ -10400,10 +10400,10 @@
         <v>4</v>
       </c>
       <c r="J75" s="10">
-        <v>1198</v>
+        <v>1165</v>
       </c>
       <c r="K75" s="10">
-        <v>50078251.351593465</v>
+        <v>53768628.46778176</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.35">
@@ -10411,7 +10411,7 @@
         <v>139</v>
       </c>
       <c r="B76" s="10">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C76" s="10">
         <v>2</v>
@@ -10420,13 +10420,13 @@
         <v>2</v>
       </c>
       <c r="E76" s="10">
-        <v>515</v>
+        <v>481</v>
       </c>
       <c r="F76" s="10">
-        <v>11124898.409664072</v>
+        <v>11826471.965840572</v>
       </c>
       <c r="G76" s="10">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="H76" s="10">
         <v>2</v>
@@ -10438,7 +10438,7 @@
         <v>432</v>
       </c>
       <c r="K76" s="10">
-        <v>10184693.362073636</v>
+        <v>10901511.46614914</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.35">
@@ -10446,7 +10446,7 @@
         <v>170</v>
       </c>
       <c r="B77" s="10">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="C77" s="10">
         <v>3</v>
@@ -10455,13 +10455,13 @@
         <v>1</v>
       </c>
       <c r="E77" s="10">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="F77" s="10">
-        <v>16955552.557962589</v>
+        <v>17876676.04137864</v>
       </c>
       <c r="G77" s="10">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="H77" s="10">
         <v>2</v>
@@ -10470,10 +10470,10 @@
         <v>1</v>
       </c>
       <c r="J77" s="10">
-        <v>1000</v>
+        <v>1324</v>
       </c>
       <c r="K77" s="10">
-        <v>15810033.870585823</v>
+        <v>17293360.891407505</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.35">
@@ -10481,7 +10481,7 @@
         <v>61</v>
       </c>
       <c r="B78" s="10">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="C78" s="10">
         <v>1</v>
@@ -10490,13 +10490,13 @@
         <v>4</v>
       </c>
       <c r="E78" s="10">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F78" s="10">
-        <v>12369088.577015188</v>
+        <v>13557893.517239362</v>
       </c>
       <c r="G78" s="10">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="H78" s="10">
         <v>0</v>
@@ -10505,10 +10505,10 @@
         <v>3</v>
       </c>
       <c r="J78" s="10">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="K78" s="10">
-        <v>15807488.14342864</v>
+        <v>17057156.633488394</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.35">
@@ -10516,22 +10516,22 @@
         <v>129</v>
       </c>
       <c r="B79" s="10">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C79" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D79" s="10">
         <v>1</v>
       </c>
       <c r="E79" s="10">
-        <v>736</v>
+        <v>672</v>
       </c>
       <c r="F79" s="10">
-        <v>11378936.90622247</v>
+        <v>12063598.275348464</v>
       </c>
       <c r="G79" s="10">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="H79" s="10">
         <v>6</v>
@@ -10540,10 +10540,10 @@
         <v>1</v>
       </c>
       <c r="J79" s="10">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="K79" s="10">
-        <v>12568715.058400322</v>
+        <v>13402969.79479092</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.35">
@@ -10560,13 +10560,13 @@
         <v>6</v>
       </c>
       <c r="E80" s="10">
-        <v>425</v>
+        <v>403</v>
       </c>
       <c r="F80" s="10">
-        <v>12943551.285408163</v>
+        <v>13708803.873142265</v>
       </c>
       <c r="G80" s="10">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H80" s="10">
         <v>1</v>
@@ -10575,10 +10575,10 @@
         <v>7</v>
       </c>
       <c r="J80" s="10">
-        <v>463</v>
+        <v>405</v>
       </c>
       <c r="K80" s="10">
-        <v>13584670.070504978</v>
+        <v>14530462.249641132</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.35">
@@ -10586,22 +10586,22 @@
         <v>107</v>
       </c>
       <c r="B81" s="10">
-        <v>972</v>
+        <v>965</v>
       </c>
       <c r="C81" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D81" s="10">
         <v>4</v>
       </c>
       <c r="E81" s="10">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="F81" s="10">
-        <v>36997824.771402493</v>
+        <v>39546382.337860718</v>
       </c>
       <c r="G81" s="10">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="H81" s="10">
         <v>5</v>
@@ -10610,10 +10610,10 @@
         <v>3</v>
       </c>
       <c r="J81" s="10">
-        <v>562</v>
+        <v>502</v>
       </c>
       <c r="K81" s="10">
-        <v>36158999.173775911</v>
+        <v>38541613.188916355</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.35">
@@ -10621,7 +10621,7 @@
         <v>37</v>
       </c>
       <c r="B82" s="10">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="C82" s="10">
         <v>2</v>
@@ -10630,13 +10630,13 @@
         <v>9</v>
       </c>
       <c r="E82" s="10">
-        <v>730</v>
+        <v>716</v>
       </c>
       <c r="F82" s="10">
-        <v>21724320.235075474</v>
+        <v>23025653.099902775</v>
       </c>
       <c r="G82" s="10">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="H82" s="10">
         <v>2</v>
@@ -10645,10 +10645,10 @@
         <v>10</v>
       </c>
       <c r="J82" s="10">
-        <v>715</v>
+        <v>681</v>
       </c>
       <c r="K82" s="10">
-        <v>21556780.627003729</v>
+        <v>22939388.116681613</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.35">
@@ -10656,7 +10656,7 @@
         <v>76</v>
       </c>
       <c r="B83" s="10">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="C83" s="10">
         <v>0</v>
@@ -10665,25 +10665,25 @@
         <v>2</v>
       </c>
       <c r="E83" s="10">
-        <v>918</v>
+        <v>418</v>
       </c>
       <c r="F83" s="10">
-        <v>18436711.83211863</v>
+        <v>19193236.094868459</v>
       </c>
       <c r="G83" s="10">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="H83" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I83" s="10">
         <v>2</v>
       </c>
       <c r="J83" s="10">
-        <v>866</v>
+        <v>919</v>
       </c>
       <c r="K83" s="10">
-        <v>17554926.06836798</v>
+        <v>18892615.754533097</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.35">
@@ -10691,7 +10691,7 @@
         <v>65</v>
       </c>
       <c r="B84" s="10">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="C84" s="10">
         <v>5</v>
@@ -10700,25 +10700,25 @@
         <v>4</v>
       </c>
       <c r="E84" s="10">
-        <v>796</v>
+        <v>817</v>
       </c>
       <c r="F84" s="10">
-        <v>20675882.787564185</v>
+        <v>21820331.478659838</v>
       </c>
       <c r="G84" s="10">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="H84" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I84" s="10">
         <v>5</v>
       </c>
       <c r="J84" s="10">
-        <v>790</v>
+        <v>859</v>
       </c>
       <c r="K84" s="10">
-        <v>17375063.532339539</v>
+        <v>18937194.680255909</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.35">
@@ -10726,22 +10726,22 @@
         <v>89</v>
       </c>
       <c r="B85" s="10">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="C85" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D85" s="10">
         <v>5</v>
       </c>
       <c r="E85" s="10">
-        <v>715</v>
+        <v>652</v>
       </c>
       <c r="F85" s="10">
-        <v>21557213.686589696</v>
+        <v>22969864.224000525</v>
       </c>
       <c r="G85" s="10">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="H85" s="10">
         <v>2</v>
@@ -10750,10 +10750,10 @@
         <v>6</v>
       </c>
       <c r="J85" s="10">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="K85" s="10">
-        <v>23095754.28563593</v>
+        <v>24869476.140908346</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.35">
@@ -10761,19 +10761,19 @@
         <v>147</v>
       </c>
       <c r="B86" s="10">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C86" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86" s="10">
         <v>1</v>
       </c>
       <c r="E86" s="10">
-        <v>531</v>
+        <v>634</v>
       </c>
       <c r="F86" s="10">
-        <v>9879876.8658112064</v>
+        <v>10394587.674253045</v>
       </c>
       <c r="G86" s="10">
         <v>566</v>
@@ -10785,10 +10785,10 @@
         <v>1</v>
       </c>
       <c r="J86" s="10">
-        <v>510</v>
+        <v>587</v>
       </c>
       <c r="K86" s="10">
-        <v>10738264.072177881</v>
+        <v>11488416.949110754</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.35">
@@ -10796,34 +10796,34 @@
         <v>164</v>
       </c>
       <c r="B87" s="10">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="C87" s="10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D87" s="10">
         <v>10</v>
       </c>
       <c r="E87" s="10">
-        <v>1295</v>
+        <v>1326</v>
       </c>
       <c r="F87" s="10">
-        <v>41733546.900617406</v>
+        <v>44349442.066209733</v>
       </c>
       <c r="G87" s="10">
-        <v>1765</v>
+        <v>1770</v>
       </c>
       <c r="H87" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I87" s="10">
         <v>10</v>
       </c>
       <c r="J87" s="10">
-        <v>1232</v>
+        <v>1068</v>
       </c>
       <c r="K87" s="10">
-        <v>45577456.506966852</v>
+        <v>48331718.355496056</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.35">
@@ -10831,7 +10831,7 @@
         <v>91</v>
       </c>
       <c r="B88" s="10">
-        <v>645</v>
+        <v>634</v>
       </c>
       <c r="C88" s="10">
         <v>5</v>
@@ -10840,13 +10840,13 @@
         <v>3</v>
       </c>
       <c r="E88" s="10">
-        <v>901</v>
+        <v>722</v>
       </c>
       <c r="F88" s="10">
-        <v>11696048.467407828</v>
+        <v>12502707.703434112</v>
       </c>
       <c r="G88" s="10">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="H88" s="10">
         <v>0</v>
@@ -10855,10 +10855,10 @@
         <v>3</v>
       </c>
       <c r="J88" s="10">
-        <v>636</v>
+        <v>606</v>
       </c>
       <c r="K88" s="10">
-        <v>10779677.36682423</v>
+        <v>11400986.222267387</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.35">
@@ -10866,19 +10866,19 @@
         <v>97</v>
       </c>
       <c r="B89" s="10">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="C89" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D89" s="10">
         <v>7</v>
       </c>
       <c r="E89" s="10">
-        <v>551</v>
+        <v>652</v>
       </c>
       <c r="F89" s="10">
-        <v>19852232.268611159</v>
+        <v>21157037.639902744</v>
       </c>
       <c r="G89" s="10">
         <v>646</v>
@@ -10893,7 +10893,7 @@
         <v>569</v>
       </c>
       <c r="K89" s="10">
-        <v>19960572.610525478</v>
+        <v>21464086.625509623</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.35">
@@ -10901,7 +10901,7 @@
         <v>78</v>
       </c>
       <c r="B90" s="10">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C90" s="10">
         <v>2</v>
@@ -10910,13 +10910,13 @@
         <v>1</v>
       </c>
       <c r="E90" s="10">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F90" s="10">
-        <v>5664274.1859372323</v>
+        <v>5927184.8282444756</v>
       </c>
       <c r="G90" s="10">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H90" s="10">
         <v>2</v>
@@ -10925,10 +10925,10 @@
         <v>1</v>
       </c>
       <c r="J90" s="10">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="K90" s="10">
-        <v>4924927.4812102551</v>
+        <v>5259376.4748856099</v>
       </c>
     </row>
   </sheetData>

--- a/SITE MONITORING.xlsx
+++ b/SITE MONITORING.xlsx
@@ -1136,27 +1136,27 @@
       </c>
       <c r="F2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10600029.17885459</v>
+        <v>11813210.545567276</v>
       </c>
       <c r="G2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10028253.355198471</v>
+        <v>11602296.38923113</v>
       </c>
       <c r="H2" s="12">
         <f>IFERROR(G2/F2-1,0)</f>
-        <v>-5.3940966954763025E-2</v>
+        <v>-1.7854092714472802E-2</v>
       </c>
       <c r="I2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>366</v>
+        <v>324</v>
       </c>
       <c r="J2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="K2" s="12">
         <f>IFERROR(J2/I2-1,0)</f>
-        <v>0.17486338797814205</v>
+        <v>0.32098765432098775</v>
       </c>
       <c r="L2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1184,15 +1184,15 @@
       </c>
       <c r="R2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="S2">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="T2" s="12">
         <f>IFERROR(S2/R2-1,0)</f>
-        <v>2.421307506053294E-3</v>
+        <v>-2.4038461538461453E-3</v>
       </c>
       <c r="U2">
         <v>3</v>
@@ -1216,27 +1216,27 @@
       </c>
       <c r="F3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13325051.244588085</v>
+        <v>14558309.604847057</v>
       </c>
       <c r="G3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11844501.537288273</v>
+        <v>13595181.152484637</v>
       </c>
       <c r="H3" s="12">
         <f t="shared" ref="H3:H66" si="0">IFERROR(G3/F3-1,0)</f>
-        <v>-0.11111024491565324</v>
+        <v>-6.6156612855777897E-2</v>
       </c>
       <c r="I3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>568</v>
+        <v>454</v>
       </c>
       <c r="J3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>544</v>
+        <v>519</v>
       </c>
       <c r="K3" s="12">
         <f t="shared" ref="K3:K66" si="1">IFERROR(J3/I3-1,0)</f>
-        <v>-4.2253521126760618E-2</v>
+        <v>0.14317180616740077</v>
       </c>
       <c r="L3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1256,15 +1256,15 @@
       </c>
       <c r="P3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q3" s="12">
         <f t="shared" ref="Q3:Q66" si="3">IFERROR(P3/O3-1,0)</f>
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="R3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="S3">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="T3" s="12">
         <f t="shared" ref="T3:T66" si="4">IFERROR(S3/R3-1,0)</f>
-        <v>-5.8910162002945521E-2</v>
+        <v>-5.7522123893805288E-2</v>
       </c>
       <c r="U3">
         <v>2</v>
@@ -1296,27 +1296,27 @@
       </c>
       <c r="F4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13568687.102148704</v>
+        <v>15765702.050982265</v>
       </c>
       <c r="G4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15687996.009139288</v>
+        <v>18573202.176985394</v>
       </c>
       <c r="H4" s="12">
         <f t="shared" si="0"/>
-        <v>0.15619115475475698</v>
+        <v>0.17807644194495054</v>
       </c>
       <c r="I4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>569</v>
+        <v>852</v>
       </c>
       <c r="J4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>803</v>
+        <v>790</v>
       </c>
       <c r="K4" s="12">
         <f t="shared" si="1"/>
-        <v>0.41124780316344456</v>
+        <v>-7.2769953051643244E-2</v>
       </c>
       <c r="L4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1332,27 +1332,27 @@
       </c>
       <c r="O4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q4" s="12">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="S4">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="T4" s="12">
         <f t="shared" si="4"/>
-        <v>0.10850439882697938</v>
+        <v>0.11695906432748537</v>
       </c>
       <c r="U4">
         <v>4</v>
@@ -1376,27 +1376,27 @@
       </c>
       <c r="F5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24977688.513464183</v>
+        <v>28310468.960497696</v>
       </c>
       <c r="G5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>25629330.071108133</v>
+        <v>29309668.523300178</v>
       </c>
       <c r="H5" s="12">
         <f t="shared" si="0"/>
-        <v>2.608894563212627E-2</v>
+        <v>3.5294348680577903E-2</v>
       </c>
       <c r="I5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1188</v>
+        <v>1378</v>
       </c>
       <c r="J5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1123</v>
+        <v>1107</v>
       </c>
       <c r="K5" s="12">
         <f t="shared" si="1"/>
-        <v>-5.4713804713804715E-2</v>
+        <v>-0.19666182873730043</v>
       </c>
       <c r="L5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1412,27 +1412,27 @@
       </c>
       <c r="O5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q5" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.16666666666666674</v>
       </c>
       <c r="R5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1192</v>
+        <v>1182</v>
       </c>
       <c r="S5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="T5" s="12">
         <f t="shared" si="4"/>
-        <v>1.1744966442952975E-2</v>
+        <v>1.8612521150592309E-2</v>
       </c>
       <c r="U5">
         <v>3</v>
@@ -1456,27 +1456,27 @@
       </c>
       <c r="F6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10213403.496292388</v>
+        <v>11757304.216271428</v>
       </c>
       <c r="G6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11564273.043757185</v>
+        <v>13279203.146268772</v>
       </c>
       <c r="H6" s="12">
         <f t="shared" si="0"/>
-        <v>0.1322643864951758</v>
+        <v>0.12944284693179275</v>
       </c>
       <c r="I6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>308</v>
+        <v>395</v>
       </c>
       <c r="J6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="K6" s="12">
         <f t="shared" si="1"/>
-        <v>0.22402597402597402</v>
+        <v>-7.5949367088607556E-2</v>
       </c>
       <c r="L6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1508,11 +1508,11 @@
       </c>
       <c r="S6">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="T6" s="12">
         <f t="shared" si="4"/>
-        <v>-4.8426150121065881E-3</v>
+        <v>-1.2106537530266359E-2</v>
       </c>
       <c r="U6">
         <v>3</v>
@@ -1536,27 +1536,27 @@
       </c>
       <c r="F7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9311664.9737815727</v>
+        <v>10339799.678089332</v>
       </c>
       <c r="G7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>9571632.1562437192</v>
+        <v>10850637.181308759</v>
       </c>
       <c r="H7" s="12">
         <f t="shared" si="0"/>
-        <v>2.7918442426152934E-2</v>
+        <v>4.9404970997835029E-2</v>
       </c>
       <c r="I7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>329</v>
+        <v>353</v>
       </c>
       <c r="J7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="K7" s="12">
         <f t="shared" si="1"/>
-        <v>-0.14893617021276595</v>
+        <v>-0.18413597733711051</v>
       </c>
       <c r="L7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="O7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -1580,19 +1580,19 @@
       </c>
       <c r="Q7" s="12">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="S7">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="T7" s="12">
         <f t="shared" si="4"/>
-        <v>3.2520325203251987E-2</v>
+        <v>3.2085561497326109E-2</v>
       </c>
       <c r="U7">
         <v>2</v>
@@ -1616,27 +1616,27 @@
       </c>
       <c r="F8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10676512.083891636</v>
+        <v>11840920.056150315</v>
       </c>
       <c r="G8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11355109.563810242</v>
+        <v>13055381.858272109</v>
       </c>
       <c r="H8" s="12">
         <f t="shared" si="0"/>
-        <v>6.3559847503235734E-2</v>
+        <v>0.10256481729145595</v>
       </c>
       <c r="I8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="J8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="K8" s="12">
         <f t="shared" si="1"/>
-        <v>0.11206896551724133</v>
+        <v>0.12179487179487181</v>
       </c>
       <c r="L8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1644,11 +1644,11 @@
       </c>
       <c r="M8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="R8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="S8">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="T8" s="12">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-3.3500837520937798E-3</v>
       </c>
       <c r="U8">
         <v>9</v>
@@ -1696,27 +1696,27 @@
       </c>
       <c r="F9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4961594.8237775872</v>
+        <v>5538273.8270198824</v>
       </c>
       <c r="G9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5041914.6980878524</v>
+        <v>5740248.3143004626</v>
       </c>
       <c r="H9" s="12">
         <f t="shared" si="0"/>
-        <v>1.6188317902410265E-2</v>
+        <v>3.6468851773849842E-2</v>
       </c>
       <c r="I9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="J9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="K9" s="12">
         <f t="shared" si="1"/>
-        <v>5.8823529411764719E-2</v>
+        <v>-6.8493150684931559E-2</v>
       </c>
       <c r="L9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1744,15 +1744,15 @@
       </c>
       <c r="R9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="S9">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="T9" s="12">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-5.8479532163743242E-3</v>
       </c>
       <c r="U9">
         <v>1</v>
@@ -1776,27 +1776,27 @@
       </c>
       <c r="F10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4849624.7900021672</v>
+        <v>5377723.235344599</v>
       </c>
       <c r="G10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>1744525.7676470859</v>
+        <v>2513527.1167136971</v>
       </c>
       <c r="H10" s="12">
         <f t="shared" si="0"/>
-        <v>-0.6402761361572662</v>
+        <v>-0.53260385357993734</v>
       </c>
       <c r="I10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="J10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>236</v>
+        <v>172</v>
       </c>
       <c r="K10" s="12">
         <f t="shared" si="1"/>
-        <v>0.54248366013071903</v>
+        <v>9.5541401273885329E-2</v>
       </c>
       <c r="L10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="R10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S10">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="T10" s="12">
         <f t="shared" si="4"/>
-        <v>-6.9999999999999951E-2</v>
+        <v>-6.0606060606060552E-2</v>
       </c>
       <c r="U10">
         <v>1</v>
@@ -1856,27 +1856,27 @@
       </c>
       <c r="F11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7595456.617649341</v>
+        <v>8449767.6351467129</v>
       </c>
       <c r="G11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10045007.129200447</v>
+        <v>11274051.916730504</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" si="0"/>
-        <v>0.32250207391865771</v>
+        <v>0.33424401753205779</v>
       </c>
       <c r="I11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>333</v>
+        <v>357</v>
       </c>
       <c r="J11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="K11" s="12">
         <f t="shared" si="1"/>
-        <v>0.12612612612612617</v>
+        <v>8.4033613445377853E-3</v>
       </c>
       <c r="L11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="P11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q11" s="12">
         <f t="shared" si="3"/>
@@ -1904,15 +1904,15 @@
       </c>
       <c r="R11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="S11">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="T11" s="12">
         <f t="shared" si="4"/>
-        <v>8.35734870317002E-2</v>
+        <v>0.11403508771929816</v>
       </c>
       <c r="U11">
         <v>4</v>
@@ -1936,31 +1936,31 @@
       </c>
       <c r="F12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>3597838.8388986508</v>
+        <v>4041060.1390938722</v>
       </c>
       <c r="G12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4956645.1081354842</v>
+        <v>5806029.4254871206</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="0"/>
-        <v>0.37767291145614035</v>
+        <v>0.43675897552690413</v>
       </c>
       <c r="I12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>191</v>
+        <v>228</v>
       </c>
       <c r="J12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="K12" s="12">
         <f t="shared" si="1"/>
-        <v>0.51308900523560208</v>
+        <v>0.17105263157894735</v>
       </c>
       <c r="L12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="N12" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -1984,15 +1984,15 @@
       </c>
       <c r="R12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="S12">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="T12" s="12">
         <f t="shared" si="4"/>
-        <v>1.8691588785046731E-2</v>
+        <v>4.7619047619047672E-2</v>
       </c>
       <c r="U12">
         <v>3</v>
@@ -2016,31 +2016,31 @@
       </c>
       <c r="F13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4842985.5262534879</v>
+        <v>5431815.5109380577</v>
       </c>
       <c r="G13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5379290.5404999712</v>
+        <v>6161717.6329658534</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="0"/>
-        <v>0.11073851270857848</v>
+        <v>0.13437535213741891</v>
       </c>
       <c r="I13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>173</v>
+        <v>219</v>
       </c>
       <c r="J13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>250</v>
+        <v>229</v>
       </c>
       <c r="K13" s="12">
         <f t="shared" si="1"/>
-        <v>0.44508670520231219</v>
+        <v>4.5662100456621113E-2</v>
       </c>
       <c r="L13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N13" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2064,15 +2064,15 @@
       </c>
       <c r="R13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="S13">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="T13" s="12">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-5.1181102362204745E-2</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -2096,27 +2096,27 @@
       </c>
       <c r="F14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9663067.6915364582</v>
+        <v>10793808.574127875</v>
       </c>
       <c r="G14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21389073.525880821</v>
+        <v>25119200.515578978</v>
       </c>
       <c r="H14" s="12">
         <f t="shared" si="0"/>
-        <v>1.2134868769070883</v>
+        <v>1.3271860292008721</v>
       </c>
       <c r="I14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1150</v>
+        <v>1258</v>
       </c>
       <c r="J14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1023</v>
+        <v>1101</v>
       </c>
       <c r="K14" s="12">
         <f t="shared" si="1"/>
-        <v>-0.11043478260869566</v>
+        <v>-0.12480127186009538</v>
       </c>
       <c r="L14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="P14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q14" s="12">
         <f t="shared" si="3"/>
@@ -2144,15 +2144,15 @@
       </c>
       <c r="R14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="S14">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1435</v>
+        <v>1428</v>
       </c>
       <c r="T14" s="12">
         <f t="shared" si="4"/>
-        <v>3.4965034965035446E-3</v>
+        <v>7.0077084793274125E-4</v>
       </c>
       <c r="U14">
         <v>3</v>
@@ -2176,27 +2176,27 @@
       </c>
       <c r="F15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>35364801.206156261</v>
+        <v>36194509.831490748</v>
       </c>
       <c r="G15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>37576961.856111161</v>
+        <v>43111493.808943726</v>
       </c>
       <c r="H15" s="12">
         <f t="shared" si="0"/>
-        <v>6.2552610915562301E-2</v>
+        <v>0.19110588897752967</v>
       </c>
       <c r="I15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>880</v>
+        <v>258</v>
       </c>
       <c r="J15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>888</v>
+        <v>895</v>
       </c>
       <c r="K15" s="12">
         <f t="shared" si="1"/>
-        <v>9.0909090909090384E-3</v>
+        <v>2.4689922480620154</v>
       </c>
       <c r="L15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="P15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="12">
         <f t="shared" si="3"/>
@@ -2224,15 +2224,15 @@
       </c>
       <c r="R15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1284</v>
+        <v>1278</v>
       </c>
       <c r="S15">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1241</v>
+        <v>1235</v>
       </c>
       <c r="T15" s="12">
         <f t="shared" si="4"/>
-        <v>-3.3489096573208754E-2</v>
+        <v>-3.3646322378716786E-2</v>
       </c>
       <c r="U15">
         <v>4</v>
@@ -2256,27 +2256,27 @@
       </c>
       <c r="F16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20529893.129484031</v>
+        <v>23300861.495705463</v>
       </c>
       <c r="G16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21206747.857916113</v>
+        <v>23318745.82605692</v>
       </c>
       <c r="H16" s="12">
         <f t="shared" si="0"/>
-        <v>3.2969228050194532E-2</v>
+        <v>7.6753944718976896E-4</v>
       </c>
       <c r="I16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>933</v>
+        <v>896</v>
       </c>
       <c r="J16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1135</v>
+        <v>894</v>
       </c>
       <c r="K16" s="12">
         <f t="shared" si="1"/>
-        <v>0.21650589496248651</v>
+        <v>-2.2321428571429047E-3</v>
       </c>
       <c r="L16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2292,19 +2292,19 @@
       </c>
       <c r="O16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q16" s="12">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="R16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1017</v>
+        <v>1022</v>
       </c>
       <c r="S16">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="T16" s="12">
         <f t="shared" si="4"/>
-        <v>1.0816125860373615E-2</v>
+        <v>5.8708414872798986E-3</v>
       </c>
       <c r="U16">
         <v>4</v>
@@ -2336,27 +2336,27 @@
       </c>
       <c r="F17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20518785.163835421</v>
+        <v>22855372.760754973</v>
       </c>
       <c r="G17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16147770.054623244</v>
+        <v>18884057.695519928</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="0"/>
-        <v>-0.21302504384694942</v>
+        <v>-0.17375849025985701</v>
       </c>
       <c r="I17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>854</v>
+        <v>665</v>
       </c>
       <c r="J17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>659</v>
+        <v>696</v>
       </c>
       <c r="K17" s="12">
         <f t="shared" si="1"/>
-        <v>-0.22833723653395788</v>
+        <v>4.6616541353383445E-2</v>
       </c>
       <c r="L17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2384,15 +2384,15 @@
       </c>
       <c r="R17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>953</v>
+        <v>964</v>
       </c>
       <c r="S17">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="T17" s="12">
         <f t="shared" si="4"/>
-        <v>-4.0923399790136372E-2</v>
+        <v>-4.9792531120331995E-2</v>
       </c>
       <c r="U17">
         <v>4</v>
@@ -2416,27 +2416,27 @@
       </c>
       <c r="F18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>70768744.060212836</v>
+        <v>79706464.844519541</v>
       </c>
       <c r="G18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>77632214.60653232</v>
+        <v>86512250.853451744</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="0"/>
-        <v>9.6984489939227592E-2</v>
+        <v>8.5385621131334855E-2</v>
       </c>
       <c r="I18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2113</v>
+        <v>2875</v>
       </c>
       <c r="J18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2030</v>
+        <v>2092</v>
       </c>
       <c r="K18" s="12">
         <f t="shared" si="1"/>
-        <v>-3.9280643634642676E-2</v>
+        <v>-0.27234782608695651</v>
       </c>
       <c r="L18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2452,27 +2452,27 @@
       </c>
       <c r="O18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>119</v>
+        <v>624</v>
       </c>
       <c r="P18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="Q18" s="12">
         <f t="shared" si="3"/>
-        <v>0.47899159663865554</v>
+        <v>-0.70993589743589736</v>
       </c>
       <c r="R18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2741</v>
+        <v>3231</v>
       </c>
       <c r="S18">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2824</v>
+        <v>2813</v>
       </c>
       <c r="T18" s="12">
         <f t="shared" si="4"/>
-        <v>3.0280919372491777E-2</v>
+        <v>-0.12937171154441351</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -2496,27 +2496,27 @@
       </c>
       <c r="F19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>38832237.438178219</v>
+        <v>43461261.025939107</v>
       </c>
       <c r="G19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20817166.925483521</v>
+        <v>25993637.843131464</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="0"/>
-        <v>-0.4639204872337086</v>
+        <v>-0.40191247953855713</v>
       </c>
       <c r="I19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1238</v>
+        <v>1188</v>
       </c>
       <c r="J19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1147</v>
+        <v>1167</v>
       </c>
       <c r="K19" s="12">
         <f t="shared" si="1"/>
-        <v>-7.3505654281098565E-2</v>
+        <v>-1.7676767676767624E-2</v>
       </c>
       <c r="L19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="P19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q19" s="12">
         <f t="shared" si="3"/>
@@ -2544,15 +2544,15 @@
       </c>
       <c r="R19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1449</v>
+        <v>1443</v>
       </c>
       <c r="S19">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1377</v>
+        <v>1381</v>
       </c>
       <c r="T19" s="12">
         <f t="shared" si="4"/>
-        <v>-4.9689440993788803E-2</v>
+        <v>-4.2966042966043005E-2</v>
       </c>
       <c r="U19">
         <v>1</v>
@@ -2576,27 +2576,27 @@
       </c>
       <c r="F20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>78073507.036272019</v>
+        <v>87326341.867069647</v>
       </c>
       <c r="G20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>78167301.424380407</v>
+        <v>87531836.582215488</v>
       </c>
       <c r="H20" s="12">
         <f t="shared" si="0"/>
-        <v>1.2013599960971622E-3</v>
+        <v>2.3531813053458972E-3</v>
       </c>
       <c r="I20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2378</v>
+        <v>2522</v>
       </c>
       <c r="J20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2154</v>
+        <v>2002</v>
       </c>
       <c r="K20" s="12">
         <f t="shared" si="1"/>
-        <v>-9.4196804037005921E-2</v>
+        <v>-0.20618556701030932</v>
       </c>
       <c r="L20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2612,27 +2612,27 @@
       </c>
       <c r="O20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q20" s="12">
         <f t="shared" si="3"/>
-        <v>0.23076923076923084</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="R20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>3018</v>
+        <v>3008</v>
       </c>
       <c r="S20">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2957</v>
+        <v>2936</v>
       </c>
       <c r="T20" s="12">
         <f t="shared" si="4"/>
-        <v>-2.0212060967528145E-2</v>
+        <v>-2.393617021276595E-2</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2656,27 +2656,27 @@
       </c>
       <c r="F21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10898300.815067604</v>
+        <v>12335831.009248348</v>
       </c>
       <c r="G21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11614733.231166488</v>
+        <v>13179743.144659448</v>
       </c>
       <c r="H21" s="12">
         <f t="shared" si="0"/>
-        <v>6.5737992394958367E-2</v>
+        <v>6.8411453981366055E-2</v>
       </c>
       <c r="I21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>732</v>
+        <v>459</v>
       </c>
       <c r="J21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>453</v>
+        <v>482</v>
       </c>
       <c r="K21" s="12">
         <f t="shared" si="1"/>
-        <v>-0.38114754098360659</v>
+        <v>5.0108932461873534E-2</v>
       </c>
       <c r="L21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2692,19 +2692,19 @@
       </c>
       <c r="O21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q21" s="12">
         <f t="shared" si="3"/>
-        <v>-0.19999999999999996</v>
+        <v>-0.16666666666666663</v>
       </c>
       <c r="R21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="S21">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="T21" s="12">
         <f t="shared" si="4"/>
-        <v>-3.0909090909090886E-2</v>
+        <v>-3.6166365280289381E-2</v>
       </c>
       <c r="U21">
         <v>1</v>
@@ -2736,31 +2736,31 @@
       </c>
       <c r="F22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>30552762.607075132</v>
+        <v>34331182.277683817</v>
       </c>
       <c r="G22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>31893649.023847744</v>
+        <v>36181572.167494185</v>
       </c>
       <c r="H22" s="12">
         <f t="shared" si="0"/>
-        <v>4.3887567026822616E-2</v>
+        <v>5.3898227997035031E-2</v>
       </c>
       <c r="I22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1289</v>
+        <v>1319</v>
       </c>
       <c r="J22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1279</v>
+        <v>1381</v>
       </c>
       <c r="K22" s="12">
         <f t="shared" si="1"/>
-        <v>-7.7579519006981679E-3</v>
+        <v>4.7005307050796086E-2</v>
       </c>
       <c r="L22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -2768,31 +2768,31 @@
       </c>
       <c r="N22" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="O22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q22" s="12">
         <f t="shared" si="3"/>
-        <v>0.60000000000000009</v>
+        <v>0.41666666666666674</v>
       </c>
       <c r="R22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="S22">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1714</v>
+        <v>1698</v>
       </c>
       <c r="T22" s="12">
         <f t="shared" si="4"/>
-        <v>3.5128805620607828E-3</v>
+        <v>-6.4365125804564105E-3</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2816,27 +2816,27 @@
       </c>
       <c r="F23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13458741.548888275</v>
+        <v>15055659.969758572</v>
       </c>
       <c r="G23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12988114.50952672</v>
+        <v>15017516.666063774</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="0"/>
-        <v>-3.4968131132619207E-2</v>
+        <v>-2.5334859960581824E-3</v>
       </c>
       <c r="I23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>753</v>
+        <v>800</v>
       </c>
       <c r="J23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>894</v>
+        <v>867</v>
       </c>
       <c r="K23" s="12">
         <f t="shared" si="1"/>
-        <v>0.18725099601593631</v>
+        <v>8.3749999999999991E-2</v>
       </c>
       <c r="L23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="O23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -2860,19 +2860,19 @@
       </c>
       <c r="Q23" s="12">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="R23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="S23">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="T23" s="12">
         <f t="shared" si="4"/>
-        <v>2.9239766081871288E-2</v>
+        <v>1.7421602787456525E-2</v>
       </c>
       <c r="U23">
         <v>1</v>
@@ -2896,27 +2896,27 @@
       </c>
       <c r="F24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15117116.893560741</v>
+        <v>16806306.479511511</v>
       </c>
       <c r="G24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16143654.376540195</v>
+        <v>18339133.799450003</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="0"/>
-        <v>6.7905639032050935E-2</v>
+        <v>9.1205484191732022E-2</v>
       </c>
       <c r="I24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>732</v>
+        <v>656</v>
       </c>
       <c r="J24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>871</v>
+        <v>759</v>
       </c>
       <c r="K24" s="12">
         <f t="shared" si="1"/>
-        <v>0.18989071038251359</v>
+        <v>0.15701219512195119</v>
       </c>
       <c r="L24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="O24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -2940,19 +2940,19 @@
       </c>
       <c r="Q24" s="12">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="R24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>902</v>
+        <v>893</v>
       </c>
       <c r="S24">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>884</v>
+        <v>875</v>
       </c>
       <c r="T24" s="12">
         <f t="shared" si="4"/>
-        <v>-1.9955654101995512E-2</v>
+        <v>-2.015677491601342E-2</v>
       </c>
       <c r="U24">
         <v>3</v>
@@ -2976,27 +2976,27 @@
       </c>
       <c r="F25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4374488.2756901234</v>
+        <v>4978274.1542370617</v>
       </c>
       <c r="G25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3544161.3962469618</v>
+        <v>4145553.8044927949</v>
       </c>
       <c r="H25" s="12">
         <f t="shared" si="0"/>
-        <v>-0.18981120238850535</v>
+        <v>-0.16727089026134279</v>
       </c>
       <c r="I25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="K25" s="12">
         <f t="shared" si="1"/>
-        <v>-5.5865921787709993E-3</v>
+        <v>3.2258064516129004E-2</v>
       </c>
       <c r="L25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3024,15 +3024,15 @@
       </c>
       <c r="R25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="S25">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="T25" s="12">
         <f t="shared" si="4"/>
-        <v>9.009009009008917E-3</v>
+        <v>-4.366812227074246E-3</v>
       </c>
       <c r="U25">
         <v>1</v>
@@ -3056,27 +3056,27 @@
       </c>
       <c r="F26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>34543080.136784635</v>
+        <v>38180141.640637457</v>
       </c>
       <c r="G26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>30361312.978099201</v>
+        <v>34673357.838432036</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="0"/>
-        <v>-0.12105947536022721</v>
+        <v>-9.184837068474716E-2</v>
       </c>
       <c r="I26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1360</v>
+        <v>1327</v>
       </c>
       <c r="J26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1456</v>
+        <v>1384</v>
       </c>
       <c r="K26" s="12">
         <f t="shared" si="1"/>
-        <v>7.0588235294117618E-2</v>
+        <v>4.2954031650339175E-2</v>
       </c>
       <c r="L26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3104,15 +3104,15 @@
       </c>
       <c r="R26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1670</v>
+        <v>1657</v>
       </c>
       <c r="S26">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1647</v>
+        <v>1653</v>
       </c>
       <c r="T26" s="12">
         <f t="shared" si="4"/>
-        <v>-1.377245508982039E-2</v>
+        <v>-2.4140012070006378E-3</v>
       </c>
       <c r="U26">
         <v>1</v>
@@ -3136,27 +3136,27 @@
       </c>
       <c r="F27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>23829126.881211925</v>
+        <v>26798065.721356105</v>
       </c>
       <c r="G27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>25123400.694838129</v>
+        <v>28932948.270447984</v>
       </c>
       <c r="H27" s="12">
         <f t="shared" si="0"/>
-        <v>5.4314781237187137E-2</v>
+        <v>7.9665546434962708E-2</v>
       </c>
       <c r="I27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>635</v>
+        <v>620</v>
       </c>
       <c r="J27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>683</v>
+        <v>695</v>
       </c>
       <c r="K27" s="12">
         <f t="shared" si="1"/>
-        <v>7.5590551181102361E-2</v>
+        <v>0.12096774193548376</v>
       </c>
       <c r="L27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3172,15 +3172,15 @@
       </c>
       <c r="O27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q27" s="12">
         <f t="shared" si="3"/>
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="R27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -3188,11 +3188,11 @@
       </c>
       <c r="S27">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="T27" s="12">
         <f t="shared" si="4"/>
-        <v>1.9813519813519864E-2</v>
+        <v>2.0979020979021046E-2</v>
       </c>
       <c r="U27">
         <v>1</v>
@@ -3216,27 +3216,27 @@
       </c>
       <c r="F28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>25615523.717296895</v>
+        <v>28967105.315619867</v>
       </c>
       <c r="G28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>24340756.119797848</v>
+        <v>27314154.578593209</v>
       </c>
       <c r="H28" s="12">
         <f t="shared" si="0"/>
-        <v>-4.9765431758018619E-2</v>
+        <v>-5.7063027838523461E-2</v>
       </c>
       <c r="I28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>683</v>
+        <v>757</v>
       </c>
       <c r="J28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>813</v>
+        <v>623</v>
       </c>
       <c r="K28" s="12">
         <f t="shared" si="1"/>
-        <v>0.19033674963396785</v>
+        <v>-0.1770145310435931</v>
       </c>
       <c r="L28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3244,11 +3244,11 @@
       </c>
       <c r="M28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N28" s="12">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -3264,15 +3264,15 @@
       </c>
       <c r="R28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1131</v>
+        <v>1127</v>
       </c>
       <c r="S28">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1052</v>
+        <v>1044</v>
       </c>
       <c r="T28" s="12">
         <f t="shared" si="4"/>
-        <v>-6.9849690539345755E-2</v>
+        <v>-7.3646850044365553E-2</v>
       </c>
       <c r="U28">
         <v>1</v>
@@ -3296,27 +3296,27 @@
       </c>
       <c r="F29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>33440236.344155505</v>
+        <v>37440462.056698211</v>
       </c>
       <c r="G29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>33277591.184311975</v>
+        <v>38738095.034786858</v>
       </c>
       <c r="H29" s="12">
         <f t="shared" si="0"/>
-        <v>-4.8637562895681441E-3</v>
+        <v>3.4658572752749972E-2</v>
       </c>
       <c r="I29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>979</v>
+        <v>891</v>
       </c>
       <c r="J29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>865</v>
+        <v>1017</v>
       </c>
       <c r="K29" s="12">
         <f t="shared" si="1"/>
-        <v>-0.11644535240040854</v>
+        <v>0.14141414141414144</v>
       </c>
       <c r="L29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3344,15 +3344,15 @@
       </c>
       <c r="R29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1113</v>
+        <v>1127</v>
       </c>
       <c r="S29">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1124</v>
+        <v>1120</v>
       </c>
       <c r="T29" s="12">
         <f t="shared" si="4"/>
-        <v>9.8831985624439067E-3</v>
+        <v>-6.2111801242236142E-3</v>
       </c>
       <c r="U29">
         <v>1</v>
@@ -3376,27 +3376,27 @@
       </c>
       <c r="F30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>48824205.713933267</v>
+        <v>54625541.40816319</v>
       </c>
       <c r="G30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>46926675.133656777</v>
+        <v>49689744.933685243</v>
       </c>
       <c r="H30" s="12">
         <f t="shared" si="0"/>
-        <v>-3.8864545823732222E-2</v>
+        <v>-9.0356934636081188E-2</v>
       </c>
       <c r="I30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1164</v>
+        <v>1170</v>
       </c>
       <c r="J30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1108</v>
+        <v>1153</v>
       </c>
       <c r="K30" s="12">
         <f t="shared" si="1"/>
-        <v>-4.8109965635738883E-2</v>
+        <v>-1.4529914529914478E-2</v>
       </c>
       <c r="L30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3424,15 +3424,15 @@
       </c>
       <c r="R30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1504</v>
+        <v>1500</v>
       </c>
       <c r="S30">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1453</v>
+        <v>1445</v>
       </c>
       <c r="T30" s="12">
         <f t="shared" si="4"/>
-        <v>-3.3909574468085069E-2</v>
+        <v>-3.6666666666666625E-2</v>
       </c>
       <c r="U30">
         <v>4</v>
@@ -3456,27 +3456,27 @@
       </c>
       <c r="F31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18136491.705534205</v>
+        <v>20563796.033259295</v>
       </c>
       <c r="G31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19333862.377965305</v>
+        <v>22475660.079455785</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="0"/>
-        <v>6.6019971881647432E-2</v>
+        <v>9.2972330745952458E-2</v>
       </c>
       <c r="I31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>408</v>
+        <v>546</v>
       </c>
       <c r="J31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>566</v>
+        <v>657</v>
       </c>
       <c r="K31" s="12">
         <f t="shared" si="1"/>
-        <v>0.38725490196078427</v>
+        <v>0.20329670329670324</v>
       </c>
       <c r="L31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3504,15 +3504,15 @@
       </c>
       <c r="R31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="S31">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>685</v>
+        <v>698</v>
       </c>
       <c r="T31" s="12">
         <f t="shared" si="4"/>
-        <v>-8.6830680173661801E-3</v>
+        <v>8.6705202312138407E-3</v>
       </c>
       <c r="U31">
         <v>3</v>
@@ -3536,31 +3536,31 @@
       </c>
       <c r="F32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>57697960.692234173</v>
+        <v>64619883.099481747</v>
       </c>
       <c r="G32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>46664841.921978779</v>
+        <v>54641880.595996283</v>
       </c>
       <c r="H32" s="12">
         <f t="shared" si="0"/>
-        <v>-0.19122198840106308</v>
+        <v>-0.15441071733485523</v>
       </c>
       <c r="I32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1905</v>
+        <v>1942</v>
       </c>
       <c r="J32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>985</v>
+        <v>1597</v>
       </c>
       <c r="K32" s="12">
         <f t="shared" si="1"/>
-        <v>-0.48293963254593175</v>
+        <v>-0.17765190525231722</v>
       </c>
       <c r="L32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -3568,31 +3568,31 @@
       </c>
       <c r="N32" s="12">
         <f t="shared" si="2"/>
-        <v>-9.9999999999999978E-2</v>
+        <v>-0.18181818181818177</v>
       </c>
       <c r="O32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q32" s="12">
         <f t="shared" si="3"/>
-        <v>-0.53846153846153844</v>
+        <v>-0.3571428571428571</v>
       </c>
       <c r="R32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="S32">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1906</v>
+        <v>1923</v>
       </c>
       <c r="T32" s="12">
         <f t="shared" si="4"/>
-        <v>-3.2978183663115224E-2</v>
+        <v>-2.385786802030454E-2</v>
       </c>
       <c r="U32">
         <v>5</v>
@@ -3616,27 +3616,27 @@
       </c>
       <c r="F33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19871805.127006289</v>
+        <v>22177650.670513704</v>
       </c>
       <c r="G33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19594455.916085906</v>
+        <v>22648991.031854369</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="0"/>
-        <v>-1.3956920830682784E-2</v>
+        <v>2.1252943710910577E-2</v>
       </c>
       <c r="I33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>708</v>
+        <v>676</v>
       </c>
       <c r="J33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>673</v>
+        <v>699</v>
       </c>
       <c r="K33" s="12">
         <f t="shared" si="1"/>
-        <v>-4.9435028248587587E-2</v>
+        <v>3.4023668639053151E-2</v>
       </c>
       <c r="L33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3656,23 +3656,23 @@
       </c>
       <c r="P33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q33" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="S33">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="4"/>
-        <v>1.7857142857142794E-2</v>
+        <v>1.3002364066193817E-2</v>
       </c>
       <c r="U33">
         <v>3</v>
@@ -3696,27 +3696,27 @@
       </c>
       <c r="F34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16205189.746109076</v>
+        <v>18494684.231714644</v>
       </c>
       <c r="G34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18498161.104133904</v>
+        <v>20507947.028976176</v>
       </c>
       <c r="H34" s="12">
         <f t="shared" si="0"/>
-        <v>0.14149611290885256</v>
+        <v>0.10885629470814062</v>
       </c>
       <c r="I34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>598</v>
+        <v>550</v>
       </c>
       <c r="J34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>458</v>
+        <v>560</v>
       </c>
       <c r="K34" s="12">
         <f t="shared" si="1"/>
-        <v>-0.23411371237458189</v>
+        <v>1.8181818181818077E-2</v>
       </c>
       <c r="L34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3732,27 +3732,27 @@
       </c>
       <c r="O34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q34" s="12">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="R34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="S34">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="T34" s="12">
         <f t="shared" si="4"/>
-        <v>6.7238912732475065E-2</v>
+        <v>7.6258992805755321E-2</v>
       </c>
       <c r="U34">
         <v>4</v>
@@ -3776,27 +3776,27 @@
       </c>
       <c r="F35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>28717039.311782409</v>
+        <v>32415149.402387757</v>
       </c>
       <c r="G35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>27878934.567649979</v>
+        <v>31697377.625365242</v>
       </c>
       <c r="H35" s="12">
         <f t="shared" si="0"/>
-        <v>-2.9184928677120303E-2</v>
+        <v>-2.2143096368688719E-2</v>
       </c>
       <c r="I35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="J35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>837</v>
+        <v>849</v>
       </c>
       <c r="K35" s="12">
         <f t="shared" si="1"/>
-        <v>-4.2334096109839847E-2</v>
+        <v>-3.4129692832764458E-2</v>
       </c>
       <c r="L35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3812,27 +3812,27 @@
       </c>
       <c r="O35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q35" s="12">
         <f t="shared" si="3"/>
-        <v>0.36363636363636354</v>
+        <v>0.41666666666666674</v>
       </c>
       <c r="R35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1098</v>
+        <v>1112</v>
       </c>
       <c r="S35">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="T35" s="12">
         <f t="shared" si="4"/>
-        <v>5.464480874316946E-2</v>
+        <v>4.496402877697836E-2</v>
       </c>
       <c r="U35">
         <v>13</v>
@@ -3856,27 +3856,27 @@
       </c>
       <c r="F36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>28045446.933988571</v>
+        <v>31422622.587050565</v>
       </c>
       <c r="G36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>25972836.316768873</v>
+        <v>29999625.405255064</v>
       </c>
       <c r="H36" s="12">
         <f t="shared" si="0"/>
-        <v>-7.3901857299620288E-2</v>
+        <v>-4.5285754804626821E-2</v>
       </c>
       <c r="I36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="J36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>806</v>
+        <v>880</v>
       </c>
       <c r="K36" s="12">
         <f t="shared" si="1"/>
-        <v>6.7549668874172131E-2</v>
+        <v>0.17489986648865163</v>
       </c>
       <c r="L36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3892,27 +3892,27 @@
       </c>
       <c r="O36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q36" s="12">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1.9512195121951219</v>
       </c>
       <c r="R36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1105</v>
+        <v>1098</v>
       </c>
       <c r="S36">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1315</v>
+        <v>1271</v>
       </c>
       <c r="T36" s="12">
         <f t="shared" si="4"/>
-        <v>0.19004524886877827</v>
+        <v>0.15755919854280509</v>
       </c>
       <c r="U36">
         <v>4</v>
@@ -3936,27 +3936,27 @@
       </c>
       <c r="F37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>44086773.432414651</v>
+        <v>49380423.194518387</v>
       </c>
       <c r="G37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>47814301.153092101</v>
+        <v>54072727.66768647</v>
       </c>
       <c r="H37" s="12">
         <f t="shared" si="0"/>
-        <v>8.4549796468815774E-2</v>
+        <v>9.5023577555912286E-2</v>
       </c>
       <c r="I37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1334</v>
+        <v>1328</v>
       </c>
       <c r="J37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1627</v>
+        <v>1420</v>
       </c>
       <c r="K37" s="12">
         <f t="shared" si="1"/>
-        <v>0.21964017991004492</v>
+        <v>6.9277108433734913E-2</v>
       </c>
       <c r="L37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="O37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="P37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3980,19 +3980,19 @@
       </c>
       <c r="Q37" s="12">
         <f t="shared" si="3"/>
-        <v>0.39999999999999991</v>
+        <v>0.27272727272727271</v>
       </c>
       <c r="R37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1791</v>
+        <v>1778</v>
       </c>
       <c r="S37">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2319</v>
+        <v>2274</v>
       </c>
       <c r="T37" s="12">
         <f t="shared" si="4"/>
-        <v>0.29480737018425462</v>
+        <v>0.27896512935883022</v>
       </c>
       <c r="U37">
         <v>16</v>
@@ -4016,27 +4016,27 @@
       </c>
       <c r="F38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17501171.752967127</v>
+        <v>17501175.169462778</v>
       </c>
       <c r="G38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17234881.682922155</v>
+        <v>19553902.07009979</v>
       </c>
       <c r="H38" s="12">
         <f t="shared" si="0"/>
-        <v>-1.5215556638361938E-2</v>
+        <v>0.11729080366093059</v>
       </c>
       <c r="I38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="J38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="K38" s="12">
         <f t="shared" si="1"/>
-        <v>11.763157894736842</v>
+        <v>35.92307692307692</v>
       </c>
       <c r="L38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4064,15 +4064,15 @@
       </c>
       <c r="R38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="S38">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="T38" s="12">
         <f t="shared" si="4"/>
-        <v>1.6051364365972098E-3</v>
+        <v>6.482982171799101E-3</v>
       </c>
       <c r="U38">
         <v>3</v>
@@ -4096,27 +4096,27 @@
       </c>
       <c r="F39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>51906929.79847452</v>
+        <v>58094258.463035837</v>
       </c>
       <c r="G39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>55848173.692558862</v>
+        <v>62788078.791813053</v>
       </c>
       <c r="H39" s="12">
         <f t="shared" si="0"/>
-        <v>7.5929050502234974E-2</v>
+        <v>8.07966303892802E-2</v>
       </c>
       <c r="I39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2207</v>
+        <v>1885</v>
       </c>
       <c r="J39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1813</v>
+        <v>1899</v>
       </c>
       <c r="K39" s="12">
         <f t="shared" si="1"/>
-        <v>-0.17852288173991848</v>
+        <v>7.4270557029176842E-3</v>
       </c>
       <c r="L39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4136,11 +4136,11 @@
       </c>
       <c r="P39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q39" s="12">
         <f t="shared" si="3"/>
-        <v>-0.4</v>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="R39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -4148,11 +4148,11 @@
       </c>
       <c r="S39">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2060</v>
+        <v>2052</v>
       </c>
       <c r="T39" s="12">
         <f t="shared" si="4"/>
-        <v>1.6781836130306038E-2</v>
+        <v>1.2833168805528095E-2</v>
       </c>
       <c r="U39">
         <v>4</v>
@@ -4176,27 +4176,27 @@
       </c>
       <c r="F40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>35818386.015351824</v>
+        <v>40259525.860920064</v>
       </c>
       <c r="G40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>38783782.459595293</v>
+        <v>43702130.166758053</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" si="0"/>
-        <v>8.2789784078280082E-2</v>
+        <v>8.5510304262667036E-2</v>
       </c>
       <c r="I40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>802</v>
+        <v>823</v>
       </c>
       <c r="J40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1214</v>
+        <v>849</v>
       </c>
       <c r="K40" s="12">
         <f t="shared" si="1"/>
-        <v>0.513715710723192</v>
+        <v>3.1591737545564991E-2</v>
       </c>
       <c r="L40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="O40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4220,19 +4220,19 @@
       </c>
       <c r="Q40" s="12">
         <f t="shared" si="3"/>
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="R40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="S40">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="T40" s="12">
         <f t="shared" si="4"/>
-        <v>3.436426116838498E-2</v>
+        <v>2.5114155251141579E-2</v>
       </c>
       <c r="U40">
         <v>3</v>
@@ -4256,27 +4256,27 @@
       </c>
       <c r="F41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>30056084.115850814</v>
+        <v>33706233.502371065</v>
       </c>
       <c r="G41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21319527.778955884</v>
+        <v>25153289.147385843</v>
       </c>
       <c r="H41" s="12">
         <f t="shared" si="0"/>
-        <v>-0.29067513596315397</v>
+        <v>-0.25374963222703495</v>
       </c>
       <c r="I41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>939</v>
+        <v>932</v>
       </c>
       <c r="J41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>936</v>
+        <v>1095</v>
       </c>
       <c r="K41" s="12">
         <f t="shared" si="1"/>
-        <v>-3.1948881789137795E-3</v>
+        <v>0.17489270386266087</v>
       </c>
       <c r="L41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4292,27 +4292,27 @@
       </c>
       <c r="O41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q41" s="12">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.66666666666666674</v>
       </c>
       <c r="R41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1145</v>
+        <v>1123</v>
       </c>
       <c r="S41">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1088</v>
+        <v>1097</v>
       </c>
       <c r="T41" s="12">
         <f t="shared" si="4"/>
-        <v>-4.9781659388646315E-2</v>
+        <v>-2.315227070347281E-2</v>
       </c>
       <c r="U41">
         <v>4</v>
@@ -4336,27 +4336,27 @@
       </c>
       <c r="F42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>29545546.930951878</v>
+        <v>32761795.611114733</v>
       </c>
       <c r="G42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>28979341.557539623</v>
+        <v>32727427.435014695</v>
       </c>
       <c r="H42" s="12">
         <f t="shared" si="0"/>
-        <v>-1.9163814253819078E-2</v>
+        <v>-1.049032125955196E-3</v>
       </c>
       <c r="I42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>646</v>
+        <v>623</v>
       </c>
       <c r="J42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="K42" s="12">
         <f t="shared" si="1"/>
-        <v>-0.12693498452012386</v>
+        <v>-8.0256821829855496E-2</v>
       </c>
       <c r="L42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4384,15 +4384,15 @@
       </c>
       <c r="R42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="S42">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="T42" s="12">
         <f t="shared" si="4"/>
-        <v>-3.1395348837209291E-2</v>
+        <v>-4.0462427745664775E-2</v>
       </c>
       <c r="U42">
         <v>2</v>
@@ -4416,27 +4416,27 @@
       </c>
       <c r="F43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18049660.276563376</v>
+        <v>20342697.235315848</v>
       </c>
       <c r="G43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18792405.690429319</v>
+        <v>21247499.714460559</v>
       </c>
       <c r="H43" s="12">
         <f t="shared" si="0"/>
-        <v>4.1150104904210449E-2</v>
+        <v>4.4477999582765992E-2</v>
       </c>
       <c r="I43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="J43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1046</v>
+        <v>671</v>
       </c>
       <c r="K43" s="12">
         <f t="shared" si="1"/>
-        <v>0.79416809605488847</v>
+        <v>0.10543657331136735</v>
       </c>
       <c r="L43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4444,11 +4444,11 @@
       </c>
       <c r="M43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N43" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="O43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4456,23 +4456,23 @@
       </c>
       <c r="P43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q43" s="12">
         <f t="shared" si="3"/>
-        <v>-0.33333333333333337</v>
+        <v>0</v>
       </c>
       <c r="R43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="S43">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="T43" s="12">
         <f t="shared" si="4"/>
-        <v>4.5248868778280604E-2</v>
+        <v>5.5722891566265087E-2</v>
       </c>
       <c r="U43">
         <v>2</v>
@@ -4496,27 +4496,27 @@
       </c>
       <c r="F44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17220687.382163826</v>
+        <v>19467108.785032246</v>
       </c>
       <c r="G44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16321357.881679956</v>
+        <v>18175582.361618567</v>
       </c>
       <c r="H44" s="12">
         <f t="shared" si="0"/>
-        <v>-5.222378645670922E-2</v>
+        <v>-6.6344028672953193E-2</v>
       </c>
       <c r="I44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>750</v>
+        <v>691</v>
       </c>
       <c r="J44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>475</v>
+        <v>732</v>
       </c>
       <c r="K44" s="12">
         <f t="shared" si="1"/>
-        <v>-0.3666666666666667</v>
+        <v>5.9334298118668638E-2</v>
       </c>
       <c r="L44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4524,11 +4524,11 @@
       </c>
       <c r="M44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N44" s="12">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4544,15 +4544,15 @@
       </c>
       <c r="R44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="S44">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="T44" s="12">
         <f t="shared" si="4"/>
-        <v>-1.5781922525107572E-2</v>
+        <v>-1.7094017094017144E-2</v>
       </c>
       <c r="U44">
         <v>3</v>
@@ -4576,27 +4576,27 @@
       </c>
       <c r="F45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>56121265.077946588</v>
+        <v>62477023.740561083</v>
       </c>
       <c r="G45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>50336716.63548696</v>
+        <v>58038275.749017172</v>
       </c>
       <c r="H45" s="12">
         <f t="shared" si="0"/>
-        <v>-0.10307231019160912</v>
+        <v>-7.1046085837507711E-2</v>
       </c>
       <c r="I45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1180</v>
+        <v>1103</v>
       </c>
       <c r="J45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1074</v>
+        <v>1454</v>
       </c>
       <c r="K45" s="12">
         <f t="shared" si="1"/>
-        <v>-8.9830508474576298E-2</v>
+        <v>0.31822302810516767</v>
       </c>
       <c r="L45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="O45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4620,19 +4620,19 @@
       </c>
       <c r="Q45" s="12">
         <f t="shared" si="3"/>
-        <v>-0.75</v>
+        <v>-0.8</v>
       </c>
       <c r="R45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1295</v>
+        <v>1283</v>
       </c>
       <c r="S45">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="T45" s="12">
         <f t="shared" si="4"/>
-        <v>-4.4787644787644743E-2</v>
+        <v>-3.5074045206547111E-2</v>
       </c>
       <c r="U45">
         <v>5</v>
@@ -4656,27 +4656,27 @@
       </c>
       <c r="F46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>25070780.558970418</v>
+        <v>28184934.114670154</v>
       </c>
       <c r="G46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>24322654.950506765</v>
+        <v>27492791.124575771</v>
       </c>
       <c r="H46" s="12">
         <f t="shared" si="0"/>
-        <v>-2.9840539136942401E-2</v>
+        <v>-2.4557197376385731E-2</v>
       </c>
       <c r="I46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>888</v>
+        <v>948</v>
       </c>
       <c r="J46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>921</v>
+        <v>939</v>
       </c>
       <c r="K46" s="12">
         <f t="shared" si="1"/>
-        <v>3.716216216216206E-2</v>
+        <v>-9.493670886076E-3</v>
       </c>
       <c r="L46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4692,27 +4692,27 @@
       </c>
       <c r="O46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q46" s="12">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="R46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>868</v>
+        <v>877</v>
       </c>
       <c r="S46">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="T46" s="12">
         <f t="shared" si="4"/>
-        <v>5.1843317972350311E-2</v>
+        <v>3.7628278221208733E-2</v>
       </c>
       <c r="U46">
         <v>4</v>
@@ -4736,27 +4736,27 @@
       </c>
       <c r="F47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>36249311.027373917</v>
+        <v>41289989.144723333</v>
       </c>
       <c r="G47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>42593266.870044634</v>
+        <v>47993219.130776621</v>
       </c>
       <c r="H47" s="12">
         <f t="shared" si="0"/>
-        <v>0.17500900466439306</v>
+        <v>0.16234516222705109</v>
       </c>
       <c r="I47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1015</v>
+        <v>1003</v>
       </c>
       <c r="J47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="K47" s="12">
         <f t="shared" si="1"/>
-        <v>-5.8128078817733964E-2</v>
+        <v>-5.1844466600199368E-2</v>
       </c>
       <c r="L47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4772,27 +4772,27 @@
       </c>
       <c r="O47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q47" s="12">
         <f t="shared" si="3"/>
-        <v>-0.55555555555555558</v>
+        <v>-0.61538461538461542</v>
       </c>
       <c r="R47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="S47">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1348</v>
+        <v>1345</v>
       </c>
       <c r="T47" s="12">
         <f t="shared" si="4"/>
-        <v>3.136954858454466E-2</v>
+        <v>2.9862174578866751E-2</v>
       </c>
       <c r="U47">
         <v>6</v>
@@ -4816,27 +4816,27 @@
       </c>
       <c r="F48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18877382.814397447</v>
+        <v>21359608.09983848</v>
       </c>
       <c r="G48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21999896.923067365</v>
+        <v>24793926.215664741</v>
       </c>
       <c r="H48" s="12">
         <f t="shared" si="0"/>
-        <v>0.16541032935394151</v>
+        <v>0.1607856333212514</v>
       </c>
       <c r="I48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="K48" s="12">
         <f t="shared" si="1"/>
-        <v>6.197183098591541E-2</v>
+        <v>3.9325842696629199E-2</v>
       </c>
       <c r="L48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="O48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4860,19 +4860,19 @@
       </c>
       <c r="Q48" s="12">
         <f t="shared" si="3"/>
-        <v>-0.8</v>
+        <v>-0.85714285714285721</v>
       </c>
       <c r="R48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="S48">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="T48" s="12">
         <f t="shared" si="4"/>
-        <v>1.4583333333333393E-2</v>
+        <v>1.2526096033402823E-2</v>
       </c>
       <c r="U48">
         <v>1</v>
@@ -4896,31 +4896,31 @@
       </c>
       <c r="F49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19430174.451933045</v>
+        <v>21478198.433565818</v>
       </c>
       <c r="G49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16002679.555755092</v>
+        <v>18005875.489039745</v>
       </c>
       <c r="H49" s="12">
         <f t="shared" si="0"/>
-        <v>-0.17640062391910039</v>
+        <v>-0.1616673276981917</v>
       </c>
       <c r="I49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>318</v>
+        <v>2191</v>
       </c>
       <c r="J49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="K49" s="12">
         <f t="shared" si="1"/>
-        <v>-5.031446540880502E-2</v>
+        <v>-0.85668644454586951</v>
       </c>
       <c r="L49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -4928,11 +4928,11 @@
       </c>
       <c r="N49" s="12">
         <f t="shared" si="2"/>
-        <v>-0.33333333333333337</v>
+        <v>-0.4285714285714286</v>
       </c>
       <c r="O49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4940,19 +4940,19 @@
       </c>
       <c r="Q49" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="S49">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="T49" s="12">
         <f t="shared" si="4"/>
-        <v>3.3860045146726803E-2</v>
+        <v>2.7027027027026973E-2</v>
       </c>
       <c r="U49">
         <v>5</v>
@@ -4976,27 +4976,27 @@
       </c>
       <c r="F50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16077907.296333432</v>
+        <v>17676503.12317507</v>
       </c>
       <c r="G50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13853359.611095656</v>
+        <v>15802232.271788953</v>
       </c>
       <c r="H50" s="12">
         <f t="shared" si="0"/>
-        <v>-0.13836052442876601</v>
+        <v>-0.10603176648263779</v>
       </c>
       <c r="I50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>383</v>
+        <v>351</v>
       </c>
       <c r="J50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>302</v>
+        <v>335</v>
       </c>
       <c r="K50" s="12">
         <f t="shared" si="1"/>
-        <v>-0.21148825065274146</v>
+        <v>-4.5584045584045607E-2</v>
       </c>
       <c r="L50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5012,15 +5012,15 @@
       </c>
       <c r="O50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q50" s="12">
         <f t="shared" si="3"/>
-        <v>-0.9</v>
+        <v>-0.81818181818181812</v>
       </c>
       <c r="R50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -5056,27 +5056,27 @@
       </c>
       <c r="F51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>34631933.852164701</v>
+        <v>38319010.734158374</v>
       </c>
       <c r="G51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>32913629.915348537</v>
+        <v>37135022.236871041</v>
       </c>
       <c r="H51" s="12">
         <f t="shared" si="0"/>
-        <v>-4.961617055955303E-2</v>
+        <v>-3.0898201039201156E-2</v>
       </c>
       <c r="I51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>987</v>
+        <v>997</v>
       </c>
       <c r="J51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>872</v>
+        <v>921</v>
       </c>
       <c r="K51" s="12">
         <f t="shared" si="1"/>
-        <v>-0.11651469098277611</v>
+        <v>-7.6228686058174566E-2</v>
       </c>
       <c r="L51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5084,15 +5084,15 @@
       </c>
       <c r="M51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51" s="12">
         <f t="shared" si="2"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5100,11 +5100,11 @@
       </c>
       <c r="Q51" s="12">
         <f t="shared" si="3"/>
-        <v>0.66666666666666674</v>
+        <v>0.25</v>
       </c>
       <c r="R51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="S51">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="T51" s="12">
         <f t="shared" si="4"/>
-        <v>-1.7793594306049876E-2</v>
+        <v>-1.9538188277087087E-2</v>
       </c>
       <c r="U51">
         <v>5</v>
@@ -5136,27 +5136,27 @@
       </c>
       <c r="F52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>36634153.112307087</v>
+        <v>40505878.641760208</v>
       </c>
       <c r="G52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>32757032.238542307</v>
+        <v>38633184.860168822</v>
       </c>
       <c r="H52" s="12">
         <f t="shared" si="0"/>
-        <v>-0.10583350628794197</v>
+        <v>-4.623264188770615E-2</v>
       </c>
       <c r="I52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>930</v>
+        <v>867</v>
       </c>
       <c r="J52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1002</v>
+        <v>926</v>
       </c>
       <c r="K52" s="12">
         <f t="shared" si="1"/>
-        <v>7.7419354838709653E-2</v>
+        <v>6.8050749711649372E-2</v>
       </c>
       <c r="L52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5184,15 +5184,15 @@
       </c>
       <c r="R52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>944</v>
+        <v>967</v>
       </c>
       <c r="S52">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1002</v>
+        <v>1009</v>
       </c>
       <c r="T52" s="12">
         <f t="shared" si="4"/>
-        <v>6.1440677966101642E-2</v>
+        <v>4.3433298862461278E-2</v>
       </c>
       <c r="U52">
         <v>4</v>
@@ -5216,27 +5216,27 @@
       </c>
       <c r="F53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>49012795.183127128</v>
+        <v>56342722.856981687</v>
       </c>
       <c r="G53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>61098674.970430002</v>
+        <v>69474698.048531413</v>
       </c>
       <c r="H53" s="12">
         <f t="shared" si="0"/>
-        <v>0.24658621778550383</v>
+        <v>0.23307313749964575</v>
       </c>
       <c r="I53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1566</v>
+        <v>1656</v>
       </c>
       <c r="J53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1601</v>
+        <v>1773</v>
       </c>
       <c r="K53" s="12">
         <f t="shared" si="1"/>
-        <v>2.2349936143039484E-2</v>
+        <v>7.0652173913043459E-2</v>
       </c>
       <c r="L53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5252,27 +5252,27 @@
       </c>
       <c r="O53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q53" s="12">
         <f t="shared" si="3"/>
-        <v>-0.77142857142857146</v>
+        <v>-0.75</v>
       </c>
       <c r="R53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2196</v>
+        <v>2161</v>
       </c>
       <c r="S53">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2048</v>
+        <v>2036</v>
       </c>
       <c r="T53" s="12">
         <f t="shared" si="4"/>
-        <v>-6.7395264116575593E-2</v>
+        <v>-5.7843590930124922E-2</v>
       </c>
       <c r="U53">
         <v>8</v>
@@ -5296,27 +5296,27 @@
       </c>
       <c r="F54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16802002.123263378</v>
+        <v>18581528.074724223</v>
       </c>
       <c r="G54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15233052.180801317</v>
+        <v>17379391.950311348</v>
       </c>
       <c r="H54" s="12">
         <f t="shared" si="0"/>
-        <v>-9.3378749208093192E-2</v>
+        <v>-6.4695224180625788E-2</v>
       </c>
       <c r="I54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>556</v>
+        <v>528</v>
       </c>
       <c r="J54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>447</v>
+        <v>498</v>
       </c>
       <c r="K54" s="12">
         <f t="shared" si="1"/>
-        <v>-0.1960431654676259</v>
+        <v>-5.6818181818181768E-2</v>
       </c>
       <c r="L54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5344,15 +5344,15 @@
       </c>
       <c r="R54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="S54">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="T54" s="12">
         <f t="shared" si="4"/>
-        <v>-1.3138686131386912E-2</v>
+        <v>8.7463556851312685E-3</v>
       </c>
       <c r="U54">
         <v>2</v>
@@ -5376,27 +5376,27 @@
       </c>
       <c r="F55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>25317769.097523954</v>
+        <v>28675817.814602911</v>
       </c>
       <c r="G55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>26561551.871163208</v>
+        <v>30317184.127649944</v>
       </c>
       <c r="H55" s="12">
         <f t="shared" si="0"/>
-        <v>4.912687088851353E-2</v>
+        <v>5.7238692324624196E-2</v>
       </c>
       <c r="I55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>650</v>
+        <v>794</v>
       </c>
       <c r="J55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>715</v>
+        <v>790</v>
       </c>
       <c r="K55" s="12">
         <f t="shared" si="1"/>
-        <v>0.10000000000000009</v>
+        <v>-5.0377833753149082E-3</v>
       </c>
       <c r="L55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="O55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="Q55" s="12">
         <f t="shared" si="3"/>
-        <v>0.19999999999999996</v>
+        <v>0</v>
       </c>
       <c r="R55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -5428,11 +5428,11 @@
       </c>
       <c r="S55">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="T55" s="12">
         <f t="shared" si="4"/>
-        <v>-1.9209039548022555E-2</v>
+        <v>-2.5988700564971712E-2</v>
       </c>
       <c r="U55">
         <v>7</v>
@@ -5456,27 +5456,27 @@
       </c>
       <c r="F56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20332674.780575395</v>
+        <v>22481594.447822541</v>
       </c>
       <c r="G56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16875594.073253468</v>
+        <v>19189044.107355248</v>
       </c>
       <c r="H56" s="12">
         <f t="shared" si="0"/>
-        <v>-0.17002586942592579</v>
+        <v>-0.14645537477819748</v>
       </c>
       <c r="I56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>609</v>
+        <v>624</v>
       </c>
       <c r="J56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>740</v>
+        <v>658</v>
       </c>
       <c r="K56" s="12">
         <f t="shared" si="1"/>
-        <v>0.21510673234811173</v>
+        <v>5.4487179487179516E-2</v>
       </c>
       <c r="L56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="O56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5500,19 +5500,19 @@
       </c>
       <c r="Q56" s="12">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="R56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="S56">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="T56" s="12">
         <f t="shared" si="4"/>
-        <v>-4.4416243654822329E-2</v>
+        <v>-5.4499366286438478E-2</v>
       </c>
       <c r="U56">
         <v>3</v>
@@ -5536,27 +5536,27 @@
       </c>
       <c r="F57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>34530254.150361381</v>
+        <v>38270861.122598462</v>
       </c>
       <c r="G57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>34330986.777931541</v>
+        <v>38656329.906607106</v>
       </c>
       <c r="H57" s="12">
         <f t="shared" si="0"/>
-        <v>-5.7708052643381524E-3</v>
+        <v>1.0072122045381215E-2</v>
       </c>
       <c r="I57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1043</v>
+        <v>1106</v>
       </c>
       <c r="J57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>869</v>
+        <v>938</v>
       </c>
       <c r="K57" s="12">
         <f t="shared" si="1"/>
-        <v>-0.16682646212847552</v>
+        <v>-0.15189873417721522</v>
       </c>
       <c r="L57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5572,27 +5572,27 @@
       </c>
       <c r="O57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q57" s="12">
         <f t="shared" si="3"/>
-        <v>-0.1428571428571429</v>
+        <v>-0.125</v>
       </c>
       <c r="R57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1089</v>
+        <v>1097</v>
       </c>
       <c r="S57">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="T57" s="12">
         <f t="shared" si="4"/>
-        <v>2.1120293847566529E-2</v>
+        <v>1.185050136736554E-2</v>
       </c>
       <c r="U57">
         <v>3</v>
@@ -5616,27 +5616,27 @@
       </c>
       <c r="F58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>43893016.899277039</v>
+        <v>49094951.780632906</v>
       </c>
       <c r="G58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>43409662.357671969</v>
+        <v>47134937.423156217</v>
       </c>
       <c r="H58" s="12">
         <f t="shared" si="0"/>
-        <v>-1.1012105700417996E-2</v>
+        <v>-3.9922930696305925E-2</v>
       </c>
       <c r="I58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1437</v>
+        <v>1410</v>
       </c>
       <c r="J58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1339</v>
+        <v>1041</v>
       </c>
       <c r="K58" s="12">
         <f t="shared" si="1"/>
-        <v>-6.8197633959638182E-2</v>
+        <v>-0.26170212765957446</v>
       </c>
       <c r="L58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5652,27 +5652,27 @@
       </c>
       <c r="O58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q58" s="12">
         <f t="shared" si="3"/>
-        <v>-0.44444444444444442</v>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="R58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="S58">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1478</v>
+        <v>1497</v>
       </c>
       <c r="T58" s="12">
         <f t="shared" si="4"/>
-        <v>8.5168869309838469E-2</v>
+        <v>9.992652461425422E-2</v>
       </c>
       <c r="U58">
         <v>4</v>
@@ -5696,27 +5696,27 @@
       </c>
       <c r="F59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>22329910.806698915</v>
+        <v>24841033.532271557</v>
       </c>
       <c r="G59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23201281.738800615</v>
+        <v>26286574.062764719</v>
       </c>
       <c r="H59" s="12">
         <f t="shared" si="0"/>
-        <v>3.9022589012773556E-2</v>
+        <v>5.819164201099869E-2</v>
       </c>
       <c r="I59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>702</v>
+        <v>678</v>
       </c>
       <c r="J59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>693</v>
+        <v>754</v>
       </c>
       <c r="K59" s="12">
         <f t="shared" si="1"/>
-        <v>-1.2820512820512775E-2</v>
+        <v>0.11209439528023601</v>
       </c>
       <c r="L59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5744,15 +5744,15 @@
       </c>
       <c r="R59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>779</v>
+        <v>768</v>
       </c>
       <c r="S59">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="T59" s="12">
         <f t="shared" si="4"/>
-        <v>-1.2836970474967901E-2</v>
+        <v>-5.2083333333333703E-3</v>
       </c>
       <c r="U59">
         <v>3</v>
@@ -5776,27 +5776,27 @@
       </c>
       <c r="F60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>25864409.160511479</v>
+        <v>29096685.519441087</v>
       </c>
       <c r="G60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>25848326.485295001</v>
+        <v>29372784.881242465</v>
       </c>
       <c r="H60" s="12">
         <f t="shared" si="0"/>
-        <v>-6.2180717590221146E-4</v>
+        <v>9.4890313749620425E-3</v>
       </c>
       <c r="I60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>466</v>
+        <v>448</v>
       </c>
       <c r="J60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="K60" s="12">
         <f t="shared" si="1"/>
-        <v>4.2918454935623185E-3</v>
+        <v>4.9107142857142794E-2</v>
       </c>
       <c r="L60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5812,27 +5812,27 @@
       </c>
       <c r="O60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q60" s="12">
         <f t="shared" si="3"/>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="R60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="S60">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="T60" s="12">
         <f t="shared" si="4"/>
-        <v>-7.9365079365079416E-2</v>
+        <v>-7.5581395348837233E-2</v>
       </c>
       <c r="U60">
         <v>10</v>
@@ -5856,27 +5856,27 @@
       </c>
       <c r="F61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>66090588.086731672</v>
+        <v>75334047.475907341</v>
       </c>
       <c r="G61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>83965424.239891231</v>
+        <v>94609229.45671463</v>
       </c>
       <c r="H61" s="12">
         <f t="shared" si="0"/>
-        <v>0.27045963231106596</v>
+        <v>0.25586282201247323</v>
       </c>
       <c r="I61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1642</v>
+        <v>1676</v>
       </c>
       <c r="J61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1969</v>
+        <v>1567</v>
       </c>
       <c r="K61" s="12">
         <f t="shared" si="1"/>
-        <v>0.1991473812423874</v>
+        <v>-6.5035799522673021E-2</v>
       </c>
       <c r="L61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5892,11 +5892,11 @@
       </c>
       <c r="O61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="P61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q61" s="12">
         <f t="shared" si="3"/>
@@ -5904,15 +5904,15 @@
       </c>
       <c r="R61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2028</v>
+        <v>2035</v>
       </c>
       <c r="S61">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1983</v>
+        <v>1990</v>
       </c>
       <c r="T61" s="12">
         <f t="shared" si="4"/>
-        <v>-2.2189349112425982E-2</v>
+        <v>-2.2113022113022129E-2</v>
       </c>
       <c r="U61">
         <v>10</v>
@@ -5936,27 +5936,27 @@
       </c>
       <c r="F62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>62841028.586884134</v>
+        <v>70479993.177585602</v>
       </c>
       <c r="G62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>62126278.515833758</v>
+        <v>70751538.977041662</v>
       </c>
       <c r="H62" s="12">
         <f t="shared" si="0"/>
-        <v>-1.1373939719369175E-2</v>
+        <v>3.8528068351519895E-3</v>
       </c>
       <c r="I62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1197</v>
+        <v>1193</v>
       </c>
       <c r="J62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1096</v>
+        <v>1356</v>
       </c>
       <c r="K62" s="12">
         <f t="shared" si="1"/>
-        <v>-8.4377610693400218E-2</v>
+        <v>0.13663034367141669</v>
       </c>
       <c r="L62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="O62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5980,19 +5980,19 @@
       </c>
       <c r="Q62" s="12">
         <f t="shared" si="3"/>
-        <v>-5.8823529411764719E-2</v>
+        <v>-0.15789473684210531</v>
       </c>
       <c r="R62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1614</v>
+        <v>1602</v>
       </c>
       <c r="S62">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1583</v>
+        <v>1599</v>
       </c>
       <c r="T62" s="12">
         <f t="shared" si="4"/>
-        <v>-1.9206939281288693E-2</v>
+        <v>-1.8726591760299671E-3</v>
       </c>
       <c r="U62">
         <v>8</v>
@@ -6016,27 +6016,27 @@
       </c>
       <c r="F63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>39412261.823200494</v>
+        <v>43706336.685455166</v>
       </c>
       <c r="G63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>40280606.360153332</v>
+        <v>45651879.400535792</v>
       </c>
       <c r="H63" s="12">
         <f t="shared" si="0"/>
-        <v>2.2032344676084392E-2</v>
+        <v>4.4513973547640528E-2</v>
       </c>
       <c r="I63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>740</v>
+        <v>656</v>
       </c>
       <c r="J63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>720</v>
+        <v>654</v>
       </c>
       <c r="K63" s="12">
         <f t="shared" si="1"/>
-        <v>-2.7027027027026973E-2</v>
+        <v>-3.0487804878048808E-3</v>
       </c>
       <c r="L63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6056,23 +6056,23 @@
       </c>
       <c r="P63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q63" s="12">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="R63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="S63">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="T63" s="12">
         <f t="shared" si="4"/>
-        <v>3.4762456546929332E-2</v>
+        <v>3.953488372093017E-2</v>
       </c>
       <c r="U63">
         <v>4</v>
@@ -6096,27 +6096,27 @@
       </c>
       <c r="F64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>57167525.883572713</v>
+        <v>64357523.01838614</v>
       </c>
       <c r="G64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>60465669.223312296</v>
+        <v>67636200.907637477</v>
       </c>
       <c r="H64" s="12">
         <f t="shared" si="0"/>
-        <v>5.7692602378080382E-2</v>
+        <v>5.0944749509931553E-2</v>
       </c>
       <c r="I64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1280</v>
+        <v>1463</v>
       </c>
       <c r="J64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1405</v>
+        <v>1245</v>
       </c>
       <c r="K64" s="12">
         <f t="shared" si="1"/>
-        <v>9.765625E-2</v>
+        <v>-0.14900888585099115</v>
       </c>
       <c r="L64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6132,27 +6132,27 @@
       </c>
       <c r="O64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>46</v>
+        <v>244</v>
       </c>
       <c r="P64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="Q64" s="12">
         <f t="shared" si="3"/>
-        <v>7.1086956521739122</v>
+        <v>0.54508196721311486</v>
       </c>
       <c r="R64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1831</v>
+        <v>2008</v>
       </c>
       <c r="S64">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2275</v>
+        <v>2204</v>
       </c>
       <c r="T64" s="12">
         <f t="shared" si="4"/>
-        <v>0.24249044238121242</v>
+        <v>9.7609561752987961E-2</v>
       </c>
       <c r="U64">
         <v>9</v>
@@ -6176,19 +6176,19 @@
       </c>
       <c r="F65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4378520.589103437</v>
+        <v>4831983.2646832503</v>
       </c>
       <c r="G65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>2048502.629354598</v>
+        <v>2632017.6643952979</v>
       </c>
       <c r="H65" s="12">
         <f t="shared" si="0"/>
-        <v>-0.53214731147945626</v>
+        <v>-0.45529247097509684</v>
       </c>
       <c r="I65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>205</v>
+        <v>255</v>
       </c>
       <c r="J65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="K65" s="12">
         <f t="shared" si="1"/>
-        <v>0.19999999999999996</v>
+        <v>-3.5294117647058809E-2</v>
       </c>
       <c r="L65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="O65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -6224,15 +6224,15 @@
       </c>
       <c r="R65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="S65">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="T65" s="12">
         <f t="shared" si="4"/>
-        <v>-5.4054054054054057E-2</v>
+        <v>-5.6179775280898903E-2</v>
       </c>
       <c r="U65">
         <v>3</v>
@@ -6256,31 +6256,31 @@
       </c>
       <c r="F66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>45352921.739393339</v>
+        <v>50773613.3984451</v>
       </c>
       <c r="G66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>43209518.753187433</v>
+        <v>48982194.351211667</v>
       </c>
       <c r="H66" s="12">
         <f t="shared" si="0"/>
-        <v>-4.7260527084061144E-2</v>
+        <v>-3.5282480944881733E-2</v>
       </c>
       <c r="I66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1505</v>
+        <v>1517</v>
       </c>
       <c r="J66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1620</v>
+        <v>1571</v>
       </c>
       <c r="K66" s="12">
         <f t="shared" si="1"/>
-        <v>7.6411960132890311E-2</v>
+        <v>3.5596572181938013E-2</v>
       </c>
       <c r="L66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -6288,11 +6288,11 @@
       </c>
       <c r="N66" s="12">
         <f t="shared" si="2"/>
-        <v>-0.25</v>
+        <v>-0.1428571428571429</v>
       </c>
       <c r="O66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -6300,19 +6300,19 @@
       </c>
       <c r="Q66" s="12">
         <f t="shared" si="3"/>
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="R66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1739</v>
+        <v>1781</v>
       </c>
       <c r="S66">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1659</v>
+        <v>1663</v>
       </c>
       <c r="T66" s="12">
         <f t="shared" si="4"/>
-        <v>-4.6003450258769396E-2</v>
+        <v>-6.6254912970241442E-2</v>
       </c>
       <c r="U66">
         <v>6</v>
@@ -6336,27 +6336,27 @@
       </c>
       <c r="F67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18336011.237021081</v>
+        <v>20933770.783716775</v>
       </c>
       <c r="G67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20578373.523585159</v>
+        <v>23094311.445282642</v>
       </c>
       <c r="H67" s="12">
         <f t="shared" ref="H67:H85" si="5">IFERROR(G67/F67-1,0)</f>
-        <v>0.12229280717480506</v>
+        <v>0.10320838437986679</v>
       </c>
       <c r="I67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>714</v>
+        <v>571</v>
       </c>
       <c r="J67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>591</v>
+        <v>614</v>
       </c>
       <c r="K67" s="12">
         <f t="shared" ref="K67:K85" si="6">IFERROR(J67/I67-1,0)</f>
-        <v>-0.17226890756302526</v>
+        <v>7.5306479859895026E-2</v>
       </c>
       <c r="L67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6384,15 +6384,15 @@
       </c>
       <c r="R67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="S67">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="T67" s="12">
         <f t="shared" ref="T67:T85" si="9">IFERROR(S67/R67-1,0)</f>
-        <v>0.11278195488721798</v>
+        <v>0.11295180722891573</v>
       </c>
       <c r="U67">
         <v>3</v>
@@ -6416,27 +6416,27 @@
       </c>
       <c r="F68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>30336217.121641062</v>
+        <v>34166560.655513391</v>
       </c>
       <c r="G68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>30139103.683555558</v>
+        <v>34962922.177493237</v>
       </c>
       <c r="H68" s="12">
         <f t="shared" si="5"/>
-        <v>-6.4976274825278013E-3</v>
+        <v>2.3308214426649876E-2</v>
       </c>
       <c r="I68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1024</v>
+        <v>1189</v>
       </c>
       <c r="J68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1057</v>
+        <v>982</v>
       </c>
       <c r="K68" s="12">
         <f t="shared" si="6"/>
-        <v>3.22265625E-2</v>
+        <v>-0.17409587888982336</v>
       </c>
       <c r="L68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6452,27 +6452,27 @@
       </c>
       <c r="O68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="P68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q68" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>-0.48888888888888893</v>
       </c>
       <c r="R68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1306</v>
+        <v>1325</v>
       </c>
       <c r="S68">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1362</v>
+        <v>1391</v>
       </c>
       <c r="T68" s="12">
         <f t="shared" si="9"/>
-        <v>4.2879019908116378E-2</v>
+        <v>4.9811320754717059E-2</v>
       </c>
       <c r="U68">
         <v>4</v>
@@ -6496,27 +6496,27 @@
       </c>
       <c r="F69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16618312.391290843</v>
+        <v>17151283.369032022</v>
       </c>
       <c r="G69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18957921.415138125</v>
+        <v>22198382.348371297</v>
       </c>
       <c r="H69" s="12">
         <f t="shared" si="5"/>
-        <v>0.14078499481532192</v>
+        <v>0.29426946489918104</v>
       </c>
       <c r="I69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1437</v>
+        <v>853</v>
       </c>
       <c r="J69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="K69" s="12">
         <f t="shared" si="6"/>
-        <v>-0.16075156576200422</v>
+        <v>0.41617819460726846</v>
       </c>
       <c r="L69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6536,23 +6536,23 @@
       </c>
       <c r="P69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q69" s="12">
         <f t="shared" si="8"/>
-        <v>-0.2857142857142857</v>
+        <v>-0.1428571428571429</v>
       </c>
       <c r="R69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1376</v>
+        <v>1356</v>
       </c>
       <c r="S69">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1262</v>
+        <v>1253</v>
       </c>
       <c r="T69" s="12">
         <f t="shared" si="9"/>
-        <v>-8.2848837209302362E-2</v>
+        <v>-7.5958702064896744E-2</v>
       </c>
       <c r="U69">
         <v>4</v>
@@ -6576,27 +6576,27 @@
       </c>
       <c r="F70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>53443829.91769053</v>
+        <v>60080748.523181163</v>
       </c>
       <c r="G70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>53768628.46778176</v>
+        <v>61224476.983174697</v>
       </c>
       <c r="H70" s="12">
         <f t="shared" si="5"/>
-        <v>6.0773816283647975E-3</v>
+        <v>1.9036521483287494E-2</v>
       </c>
       <c r="I70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1221</v>
+        <v>1210</v>
       </c>
       <c r="J70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1165</v>
+        <v>1241</v>
       </c>
       <c r="K70" s="12">
         <f t="shared" si="6"/>
-        <v>-4.586404586404591E-2</v>
+        <v>2.5619834710743694E-2</v>
       </c>
       <c r="L70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6604,35 +6604,35 @@
       </c>
       <c r="M70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N70" s="12">
         <f t="shared" si="7"/>
-        <v>-0.19999999999999996</v>
+        <v>0</v>
       </c>
       <c r="O70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q70" s="12">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0.85714285714285721</v>
       </c>
       <c r="R70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1742</v>
+        <v>1751</v>
       </c>
       <c r="S70">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1752</v>
+        <v>1758</v>
       </c>
       <c r="T70" s="12">
         <f t="shared" si="9"/>
-        <v>5.7405281285878296E-3</v>
+        <v>3.9977155910908557E-3</v>
       </c>
       <c r="U70">
         <v>4</v>
@@ -6656,27 +6656,27 @@
       </c>
       <c r="F71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11826471.965840572</v>
+        <v>13156020.104537236</v>
       </c>
       <c r="G71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10901511.46614914</v>
+        <v>12385983.388492895</v>
       </c>
       <c r="H71" s="12">
         <f t="shared" si="5"/>
-        <v>-7.8211025432020298E-2</v>
+        <v>-5.8531129469676868E-2</v>
       </c>
       <c r="I71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>481</v>
+        <v>494</v>
       </c>
       <c r="J71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="K71" s="12">
         <f t="shared" si="6"/>
-        <v>-0.10187110187110182</v>
+        <v>-0.10931174089068829</v>
       </c>
       <c r="L71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6704,15 +6704,15 @@
       </c>
       <c r="R71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="S71">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="T71" s="12">
         <f t="shared" si="9"/>
-        <v>3.0364372469635637E-2</v>
+        <v>2.2177419354838745E-2</v>
       </c>
       <c r="U71">
         <v>2</v>
@@ -6736,27 +6736,27 @@
       </c>
       <c r="F72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17876676.04137864</v>
+        <v>19982061.397274464</v>
       </c>
       <c r="G72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17293360.891407505</v>
+        <v>19938681.662497777</v>
       </c>
       <c r="H72" s="12">
         <f t="shared" si="5"/>
-        <v>-3.2629955849787229E-2</v>
+        <v>-2.1709339148864304E-3</v>
       </c>
       <c r="I72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>802</v>
+        <v>834</v>
       </c>
       <c r="J72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1324</v>
+        <v>791</v>
       </c>
       <c r="K72" s="12">
         <f t="shared" si="6"/>
-        <v>0.6508728179551122</v>
+        <v>-5.1558752997601931E-2</v>
       </c>
       <c r="L72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="O72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -6780,19 +6780,19 @@
       </c>
       <c r="Q72" s="12">
         <f t="shared" si="8"/>
-        <v>-0.33333333333333337</v>
+        <v>-0.5</v>
       </c>
       <c r="R72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>903</v>
+        <v>891</v>
       </c>
       <c r="S72">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="T72" s="12">
         <f t="shared" si="9"/>
-        <v>-2.4363233665559259E-2</v>
+        <v>-1.3468013468013518E-2</v>
       </c>
       <c r="U72">
         <v>3</v>
@@ -6816,27 +6816,27 @@
       </c>
       <c r="F73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13557893.517239362</v>
+        <v>14294811.694408428</v>
       </c>
       <c r="G73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17057156.633488394</v>
+        <v>19626666.190058872</v>
       </c>
       <c r="H73" s="12">
         <f t="shared" si="5"/>
-        <v>0.25809784623249854</v>
+        <v>0.37299228626677583</v>
       </c>
       <c r="I73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>529</v>
+        <v>633</v>
       </c>
       <c r="J73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="K73" s="12">
         <f t="shared" si="6"/>
-        <v>-4.7258979206049156E-2</v>
+        <v>-0.23064770932069512</v>
       </c>
       <c r="L73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6852,19 +6852,19 @@
       </c>
       <c r="O73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q73" s="12">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="R73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="S73">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -6872,7 +6872,7 @@
       </c>
       <c r="T73" s="12">
         <f t="shared" si="9"/>
-        <v>-4.7267355982274717E-2</v>
+        <v>-3.7313432835820892E-2</v>
       </c>
       <c r="U73">
         <v>7</v>
@@ -6896,27 +6896,27 @@
       </c>
       <c r="F74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12063598.275348464</v>
+        <v>13802610.510686357</v>
       </c>
       <c r="G74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13402969.79479092</v>
+        <v>14965299.75582342</v>
       </c>
       <c r="H74" s="12">
         <f t="shared" si="5"/>
-        <v>0.11102587212137305</v>
+        <v>8.4236908970000801E-2</v>
       </c>
       <c r="I74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>672</v>
+        <v>352</v>
       </c>
       <c r="J74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>700</v>
+        <v>596</v>
       </c>
       <c r="K74" s="12">
         <f t="shared" si="6"/>
-        <v>4.1666666666666741E-2</v>
+        <v>0.69318181818181812</v>
       </c>
       <c r="L74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6944,15 +6944,15 @@
       </c>
       <c r="R74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="S74">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="T74" s="12">
         <f t="shared" si="9"/>
-        <v>1.4975041597337757E-2</v>
+        <v>1.3157894736842035E-2</v>
       </c>
       <c r="U74">
         <v>2</v>
@@ -6976,27 +6976,27 @@
       </c>
       <c r="F75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13708803.873142265</v>
+        <v>15323299.284381747</v>
       </c>
       <c r="G75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14530462.249641132</v>
+        <v>16528959.138679625</v>
       </c>
       <c r="H75" s="12">
         <f t="shared" si="5"/>
-        <v>5.9936547645022875E-2</v>
+        <v>7.8681479224695705E-2</v>
       </c>
       <c r="I75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>403</v>
+        <v>427</v>
       </c>
       <c r="J75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>405</v>
+        <v>471</v>
       </c>
       <c r="K75" s="12">
         <f t="shared" si="6"/>
-        <v>4.9627791563275903E-3</v>
+        <v>0.10304449648711933</v>
       </c>
       <c r="L75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7024,15 +7024,15 @@
       </c>
       <c r="R75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="S75">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="T75" s="12">
         <f t="shared" si="9"/>
-        <v>1.133786848072571E-2</v>
+        <v>2.0785219399538146E-2</v>
       </c>
       <c r="U75">
         <v>1</v>
@@ -7056,31 +7056,31 @@
       </c>
       <c r="F76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>39546382.337860718</v>
+        <v>44142138.429326862</v>
       </c>
       <c r="G76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>38541613.188916355</v>
+        <v>43962551.141078793</v>
       </c>
       <c r="H76" s="12">
         <f t="shared" si="5"/>
-        <v>-2.5407359397889184E-2</v>
+        <v>-4.0683866853346018E-3</v>
       </c>
       <c r="I76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>777</v>
+        <v>736</v>
       </c>
       <c r="J76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>502</v>
+        <v>911</v>
       </c>
       <c r="K76" s="12">
         <f t="shared" si="6"/>
-        <v>-0.35392535392535396</v>
+        <v>0.23777173913043481</v>
       </c>
       <c r="L76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -7088,31 +7088,31 @@
       </c>
       <c r="N76" s="12">
         <f t="shared" si="7"/>
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="O76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q76" s="12">
         <f t="shared" si="8"/>
-        <v>-0.2857142857142857</v>
+        <v>-0.33333333333333337</v>
       </c>
       <c r="R76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="S76">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>930</v>
+        <v>919</v>
       </c>
       <c r="T76" s="12">
         <f t="shared" si="9"/>
-        <v>-3.6269430051813489E-2</v>
+        <v>-4.1710114702815382E-2</v>
       </c>
       <c r="U76">
         <v>4</v>
@@ -7136,27 +7136,27 @@
       </c>
       <c r="F77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>23025653.099902775</v>
+        <v>26320088.840679597</v>
       </c>
       <c r="G77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22939388.116681613</v>
+        <v>25795596.968580019</v>
       </c>
       <c r="H77" s="12">
         <f t="shared" si="5"/>
-        <v>-3.7464728078234755E-3</v>
+        <v>-1.9927435476165156E-2</v>
       </c>
       <c r="I77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>716</v>
+        <v>748</v>
       </c>
       <c r="J77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>681</v>
+        <v>694</v>
       </c>
       <c r="K77" s="12">
         <f t="shared" si="6"/>
-        <v>-4.88826815642458E-2</v>
+        <v>-7.2192513368983913E-2</v>
       </c>
       <c r="L77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="O77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -7180,19 +7180,19 @@
       </c>
       <c r="Q77" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>-0.33333333333333337</v>
       </c>
       <c r="R77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="S77">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="T77" s="12">
         <f t="shared" si="9"/>
-        <v>-1.0217113665389577E-2</v>
+        <v>-1.5306122448979553E-2</v>
       </c>
       <c r="U77">
         <v>3</v>
@@ -7216,27 +7216,27 @@
       </c>
       <c r="F78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19193236.094868459</v>
+        <v>21296375.880635846</v>
       </c>
       <c r="G78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18892615.754533097</v>
+        <v>21424759.907585599</v>
       </c>
       <c r="H78" s="12">
         <f t="shared" si="5"/>
-        <v>-1.5662827198574147E-2</v>
+        <v>6.0284448241021416E-3</v>
       </c>
       <c r="I78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>418</v>
+        <v>931</v>
       </c>
       <c r="J78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>919</v>
+        <v>969</v>
       </c>
       <c r="K78" s="12">
         <f t="shared" si="6"/>
-        <v>1.1985645933014353</v>
+        <v>4.081632653061229E-2</v>
       </c>
       <c r="L78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="R78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>937</v>
+        <v>949</v>
       </c>
       <c r="S78">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="T78" s="12">
         <f t="shared" si="9"/>
-        <v>2.5613660618996725E-2</v>
+        <v>1.2644889357218192E-2</v>
       </c>
       <c r="U78">
         <v>3</v>
@@ -7296,27 +7296,27 @@
       </c>
       <c r="F79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21820331.478659838</v>
+        <v>24350171.013393518</v>
       </c>
       <c r="G79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18937194.680255909</v>
+        <v>22204966.601389252</v>
       </c>
       <c r="H79" s="12">
         <f t="shared" si="5"/>
-        <v>-0.13213075159850896</v>
+        <v>-8.8098125094247637E-2</v>
       </c>
       <c r="I79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>817</v>
+        <v>802</v>
       </c>
       <c r="J79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="K79" s="12">
         <f t="shared" si="6"/>
-        <v>5.1407588739290189E-2</v>
+        <v>7.9800498753117122E-2</v>
       </c>
       <c r="L79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="O79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -7340,19 +7340,19 @@
       </c>
       <c r="Q79" s="12">
         <f t="shared" si="8"/>
-        <v>-0.6</v>
+        <v>-0.66666666666666674</v>
       </c>
       <c r="R79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="S79">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="T79" s="12">
         <f t="shared" si="9"/>
-        <v>-2.6470588235294135E-2</v>
+        <v>-2.16110019646365E-2</v>
       </c>
       <c r="U79">
         <v>3</v>
@@ -7376,27 +7376,27 @@
       </c>
       <c r="F80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>22969864.224000525</v>
+        <v>26106286.217771295</v>
       </c>
       <c r="G80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>24869476.140908346</v>
+        <v>28443447.509641979</v>
       </c>
       <c r="H80" s="12">
         <f t="shared" si="5"/>
-        <v>8.2700180479211349E-2</v>
+        <v>8.9524847478294811E-2</v>
       </c>
       <c r="I80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>652</v>
+        <v>720</v>
       </c>
       <c r="J80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>791</v>
+        <v>743</v>
       </c>
       <c r="K80" s="12">
         <f t="shared" si="6"/>
-        <v>0.21319018404907975</v>
+        <v>3.1944444444444553E-2</v>
       </c>
       <c r="L80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7424,15 +7424,15 @@
       </c>
       <c r="R80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="S80">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="T80" s="12">
         <f t="shared" si="9"/>
-        <v>1.0680907877169465E-2</v>
+        <v>9.3085106382979621E-3</v>
       </c>
       <c r="U80">
         <v>3</v>
@@ -7456,27 +7456,27 @@
       </c>
       <c r="F81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10394587.674253045</v>
+        <v>11647431.128983499</v>
       </c>
       <c r="G81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11488416.949110754</v>
+        <v>13047181.392881865</v>
       </c>
       <c r="H81" s="12">
         <f t="shared" si="5"/>
-        <v>0.10523065552345834</v>
+        <v>0.1201767366896227</v>
       </c>
       <c r="I81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>634</v>
+        <v>691</v>
       </c>
       <c r="J81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>587</v>
+        <v>522</v>
       </c>
       <c r="K81" s="12">
         <f t="shared" si="6"/>
-        <v>-7.4132492113564652E-2</v>
+        <v>-0.24457308248914611</v>
       </c>
       <c r="L81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7496,23 +7496,23 @@
       </c>
       <c r="P81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q81" s="12">
         <f t="shared" si="8"/>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="R81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="S81">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="T81" s="12">
         <f t="shared" si="9"/>
-        <v>3.5460992907800915E-3</v>
+        <v>-1.2237762237762184E-2</v>
       </c>
       <c r="U81">
         <v>1</v>
@@ -7536,27 +7536,27 @@
       </c>
       <c r="F82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>44349442.066209733</v>
+        <v>50025277.975978665</v>
       </c>
       <c r="G82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>48331718.355496056</v>
+        <v>54503798.017063886</v>
       </c>
       <c r="H82" s="12">
         <f t="shared" si="5"/>
-        <v>8.9793154180860757E-2</v>
+        <v>8.9525140534665981E-2</v>
       </c>
       <c r="I82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1326</v>
+        <v>1261</v>
       </c>
       <c r="J82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1068</v>
+        <v>1312</v>
       </c>
       <c r="K82" s="12">
         <f t="shared" si="6"/>
-        <v>-0.19457013574660631</v>
+        <v>4.0444091990483821E-2</v>
       </c>
       <c r="L82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7576,23 +7576,23 @@
       </c>
       <c r="P82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q82" s="12">
         <f t="shared" si="8"/>
-        <v>-0.77777777777777779</v>
+        <v>-0.33333333333333337</v>
       </c>
       <c r="R82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1716</v>
+        <v>1704</v>
       </c>
       <c r="S82">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1770</v>
+        <v>1764</v>
       </c>
       <c r="T82" s="12">
         <f t="shared" si="9"/>
-        <v>3.1468531468531458E-2</v>
+        <v>3.5211267605633756E-2</v>
       </c>
       <c r="U82">
         <v>2</v>
@@ -7616,27 +7616,27 @@
       </c>
       <c r="F83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12502707.703434112</v>
+        <v>13491062.530736148</v>
       </c>
       <c r="G83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11400986.222267387</v>
+        <v>12625436.34218335</v>
       </c>
       <c r="H83" s="12">
         <f t="shared" si="5"/>
-        <v>-8.8118630563850942E-2</v>
+        <v>-6.4162936505607115E-2</v>
       </c>
       <c r="I83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>722</v>
+        <v>641</v>
       </c>
       <c r="J83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>606</v>
+        <v>671</v>
       </c>
       <c r="K83" s="12">
         <f t="shared" si="6"/>
-        <v>-0.16066481994459836</v>
+        <v>4.6801872074883066E-2</v>
       </c>
       <c r="L83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7664,15 +7664,15 @@
       </c>
       <c r="R83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>634</v>
+        <v>620</v>
       </c>
       <c r="S83">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>567</v>
+        <v>578</v>
       </c>
       <c r="T83" s="12">
         <f t="shared" si="9"/>
-        <v>-0.10567823343848581</v>
+        <v>-6.7741935483870974E-2</v>
       </c>
       <c r="U83">
         <v>2</v>
@@ -7696,31 +7696,31 @@
       </c>
       <c r="F84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21157037.639902744</v>
+        <v>23429486.45540712</v>
       </c>
       <c r="G84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21464086.625509623</v>
+        <v>24509877.584273003</v>
       </c>
       <c r="H84" s="12">
         <f t="shared" si="5"/>
-        <v>1.4512853398142012E-2</v>
+        <v>4.6112454531266334E-2</v>
       </c>
       <c r="I84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>652</v>
+        <v>520</v>
       </c>
       <c r="J84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>569</v>
+        <v>641</v>
       </c>
       <c r="K84" s="12">
         <f t="shared" si="6"/>
-        <v>-0.12730061349693256</v>
+        <v>0.23269230769230775</v>
       </c>
       <c r="L84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -7728,11 +7728,11 @@
       </c>
       <c r="N84" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.16666666666666674</v>
       </c>
       <c r="O84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -7740,19 +7740,19 @@
       </c>
       <c r="Q84" s="12">
         <f t="shared" si="8"/>
-        <v>-0.63636363636363635</v>
+        <v>-0.66666666666666674</v>
       </c>
       <c r="R84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>629</v>
+        <v>604</v>
       </c>
       <c r="S84">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>646</v>
+        <v>631</v>
       </c>
       <c r="T84" s="12">
         <f t="shared" si="9"/>
-        <v>2.7027027027026973E-2</v>
+        <v>4.4701986754966949E-2</v>
       </c>
       <c r="U84">
         <v>7</v>
@@ -7776,27 +7776,27 @@
       </c>
       <c r="F85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5927184.8282444756</v>
+        <v>6461103.0332732033</v>
       </c>
       <c r="G85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5259376.4748856099</v>
+        <v>5909417.688019501</v>
       </c>
       <c r="H85" s="12">
         <f t="shared" si="5"/>
-        <v>-0.11266872431185149</v>
+        <v>-8.5385628802489122E-2</v>
       </c>
       <c r="I85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="J85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>296</v>
+        <v>380</v>
       </c>
       <c r="K85" s="12">
         <f t="shared" si="6"/>
-        <v>-5.7324840764331197E-2</v>
+        <v>0.24590163934426235</v>
       </c>
       <c r="L85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7824,15 +7824,15 @@
       </c>
       <c r="R85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="S85">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="T85" s="12">
         <f t="shared" si="9"/>
-        <v>-1.1204481792717047E-2</v>
+        <v>0</v>
       </c>
       <c r="U85">
         <v>2</v>
@@ -7865,11 +7865,11 @@
       <c r="A3" s="11"/>
       <c r="B3" s="11">
         <f t="shared" ref="B3:K3" si="0">SUBTOTAL(9,B6:B90)</f>
-        <v>83700</v>
+        <v>84319</v>
       </c>
       <c r="C3" s="11">
         <f t="shared" si="0"/>
-        <v>630</v>
+        <v>1419</v>
       </c>
       <c r="D3" s="11">
         <f t="shared" si="0"/>
@@ -7877,19 +7877,19 @@
       </c>
       <c r="E3" s="11">
         <f t="shared" si="0"/>
-        <v>69775</v>
+        <v>71611</v>
       </c>
       <c r="F3" s="11">
         <f t="shared" si="0"/>
-        <v>2221039906.9815083</v>
+        <v>2483285634.6846657</v>
       </c>
       <c r="G3" s="11">
         <f t="shared" si="0"/>
-        <v>84549</v>
+        <v>84407</v>
       </c>
       <c r="H3" s="11">
         <f t="shared" si="0"/>
-        <v>1076</v>
+        <v>1137</v>
       </c>
       <c r="I3" s="11">
         <f t="shared" si="0"/>
@@ -7897,11 +7897,11 @@
       </c>
       <c r="J3" s="11">
         <f t="shared" si="0"/>
-        <v>69895</v>
+        <v>70297</v>
       </c>
       <c r="K3" s="11">
         <f t="shared" si="0"/>
-        <v>2235483997.8356962</v>
+        <v>2540522841.3581352</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -7961,7 +7961,7 @@
         <v>117</v>
       </c>
       <c r="B6" s="10">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C6" s="10">
         <v>3</v>
@@ -7970,13 +7970,13 @@
         <v>2</v>
       </c>
       <c r="E6" s="10">
-        <v>366</v>
+        <v>324</v>
       </c>
       <c r="F6" s="10">
-        <v>10600029.17885459</v>
+        <v>11813210.545567276</v>
       </c>
       <c r="G6" s="10">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H6" s="10">
         <v>0</v>
@@ -7985,10 +7985,10 @@
         <v>2</v>
       </c>
       <c r="J6" s="10">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="K6" s="10">
-        <v>10028253.355198471</v>
+        <v>11602296.38923113</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
@@ -7996,7 +7996,7 @@
         <v>127</v>
       </c>
       <c r="B7" s="10">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C7" s="10">
         <v>2</v>
@@ -8005,25 +8005,25 @@
         <v>1</v>
       </c>
       <c r="E7" s="10">
-        <v>568</v>
+        <v>454</v>
       </c>
       <c r="F7" s="10">
-        <v>13325051.244588085</v>
+        <v>14558309.604847057</v>
       </c>
       <c r="G7" s="10">
         <v>639</v>
       </c>
       <c r="H7" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I7" s="10">
         <v>3</v>
       </c>
       <c r="J7" s="10">
-        <v>544</v>
+        <v>519</v>
       </c>
       <c r="K7" s="10">
-        <v>11844501.537288273</v>
+        <v>13595181.152484637</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
@@ -8031,34 +8031,34 @@
         <v>119</v>
       </c>
       <c r="B8" s="10">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C8" s="10">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D8" s="10">
         <v>2</v>
       </c>
       <c r="E8" s="10">
-        <v>569</v>
+        <v>852</v>
       </c>
       <c r="F8" s="10">
-        <v>13568687.102148704</v>
+        <v>15765702.050982265</v>
       </c>
       <c r="G8" s="10">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="H8" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I8" s="10">
         <v>1</v>
       </c>
       <c r="J8" s="10">
-        <v>803</v>
+        <v>790</v>
       </c>
       <c r="K8" s="10">
-        <v>15687996.009139288</v>
+        <v>18573202.176985394</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
@@ -8066,34 +8066,34 @@
         <v>121</v>
       </c>
       <c r="B9" s="10">
-        <v>1192</v>
+        <v>1182</v>
       </c>
       <c r="C9" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D9" s="10">
         <v>3</v>
       </c>
       <c r="E9" s="10">
-        <v>1188</v>
+        <v>1378</v>
       </c>
       <c r="F9" s="10">
-        <v>24977688.513464183</v>
+        <v>28310468.960497696</v>
       </c>
       <c r="G9" s="10">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="H9" s="10">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I9" s="10">
         <v>4</v>
       </c>
       <c r="J9" s="10">
-        <v>1123</v>
+        <v>1107</v>
       </c>
       <c r="K9" s="10">
-        <v>25629330.071108133</v>
+        <v>29309668.523300178</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
@@ -8110,13 +8110,13 @@
         <v>1</v>
       </c>
       <c r="E10" s="10">
-        <v>308</v>
+        <v>395</v>
       </c>
       <c r="F10" s="10">
-        <v>10213403.496292388</v>
+        <v>11757304.216271428</v>
       </c>
       <c r="G10" s="10">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="H10" s="10">
         <v>1</v>
@@ -8125,10 +8125,10 @@
         <v>1</v>
       </c>
       <c r="J10" s="10">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="K10" s="10">
-        <v>11564273.043757185</v>
+        <v>13279203.146268772</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
@@ -8136,22 +8136,22 @@
         <v>125</v>
       </c>
       <c r="B11" s="10">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C11" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="10">
         <v>2</v>
       </c>
       <c r="E11" s="10">
-        <v>329</v>
+        <v>353</v>
       </c>
       <c r="F11" s="10">
-        <v>9311664.9737815727</v>
+        <v>10339799.678089332</v>
       </c>
       <c r="G11" s="10">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="H11" s="10">
         <v>3</v>
@@ -8160,10 +8160,10 @@
         <v>2</v>
       </c>
       <c r="J11" s="10">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="K11" s="10">
-        <v>9571632.1562437192</v>
+        <v>10850637.181308759</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -8171,7 +8171,7 @@
         <v>131</v>
       </c>
       <c r="B12" s="10">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C12" s="10">
         <v>1</v>
@@ -8180,10 +8180,10 @@
         <v>1</v>
       </c>
       <c r="E12" s="10">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="F12" s="10">
-        <v>10676512.083891636</v>
+        <v>11840920.056150315</v>
       </c>
       <c r="G12" s="10">
         <v>595</v>
@@ -8192,13 +8192,13 @@
         <v>2</v>
       </c>
       <c r="I12" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J12" s="10">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="K12" s="10">
-        <v>11355109.563810242</v>
+        <v>13055381.858272109</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
@@ -8206,7 +8206,7 @@
         <v>133</v>
       </c>
       <c r="B13" s="10">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C13" s="10">
         <v>0</v>
@@ -8215,13 +8215,13 @@
         <v>1</v>
       </c>
       <c r="E13" s="10">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="F13" s="10">
-        <v>4961594.8237775872</v>
+        <v>5538273.8270198824</v>
       </c>
       <c r="G13" s="10">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H13" s="10">
         <v>0</v>
@@ -8230,10 +8230,10 @@
         <v>1</v>
       </c>
       <c r="J13" s="10">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="K13" s="10">
-        <v>5041914.6980878524</v>
+        <v>5740248.3143004626</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
@@ -8241,7 +8241,7 @@
         <v>141</v>
       </c>
       <c r="B14" s="10">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C14" s="10">
         <v>1</v>
@@ -8250,10 +8250,10 @@
         <v>0</v>
       </c>
       <c r="E14" s="10">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F14" s="10">
-        <v>4849624.7900021672</v>
+        <v>5377723.235344599</v>
       </c>
       <c r="G14" s="10">
         <v>186</v>
@@ -8265,10 +8265,10 @@
         <v>1</v>
       </c>
       <c r="J14" s="10">
-        <v>236</v>
+        <v>172</v>
       </c>
       <c r="K14" s="10">
-        <v>1744525.7676470859</v>
+        <v>2513527.1167136971</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
@@ -8276,7 +8276,7 @@
         <v>135</v>
       </c>
       <c r="B15" s="10">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C15" s="10">
         <v>0</v>
@@ -8285,25 +8285,25 @@
         <v>1</v>
       </c>
       <c r="E15" s="10">
-        <v>333</v>
+        <v>357</v>
       </c>
       <c r="F15" s="10">
-        <v>7595456.617649341</v>
+        <v>8449767.6351467129</v>
       </c>
       <c r="G15" s="10">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="H15" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" s="10">
         <v>1</v>
       </c>
       <c r="J15" s="10">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="K15" s="10">
-        <v>10045007.129200447</v>
+        <v>11274051.916730504</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
@@ -8311,22 +8311,22 @@
         <v>143</v>
       </c>
       <c r="B16" s="10">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C16" s="10">
         <v>0</v>
       </c>
       <c r="D16" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="10">
-        <v>191</v>
+        <v>228</v>
       </c>
       <c r="F16" s="10">
-        <v>3597838.8388986508</v>
+        <v>4041060.1390938722</v>
       </c>
       <c r="G16" s="10">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H16" s="10">
         <v>0</v>
@@ -8335,10 +8335,10 @@
         <v>2</v>
       </c>
       <c r="J16" s="10">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="K16" s="10">
-        <v>4956645.1081354842</v>
+        <v>5806029.4254871206</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -8346,22 +8346,22 @@
         <v>145</v>
       </c>
       <c r="B17" s="10">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C17" s="10">
         <v>7</v>
       </c>
       <c r="D17" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="10">
-        <v>173</v>
+        <v>219</v>
       </c>
       <c r="F17" s="10">
-        <v>4842985.5262534879</v>
+        <v>5431815.5109380577</v>
       </c>
       <c r="G17" s="10">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="H17" s="10">
         <v>1</v>
@@ -8370,10 +8370,10 @@
         <v>2</v>
       </c>
       <c r="J17" s="10">
-        <v>250</v>
+        <v>229</v>
       </c>
       <c r="K17" s="10">
-        <v>5379290.5404999712</v>
+        <v>6161717.6329658534</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
@@ -8381,7 +8381,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="10">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="C18" s="10">
         <v>0</v>
@@ -8390,25 +8390,25 @@
         <v>2</v>
       </c>
       <c r="E18" s="10">
-        <v>1150</v>
+        <v>1258</v>
       </c>
       <c r="F18" s="10">
-        <v>9663067.6915364582</v>
+        <v>10793808.574127875</v>
       </c>
       <c r="G18" s="10">
-        <v>1435</v>
+        <v>1428</v>
       </c>
       <c r="H18" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I18" s="10">
         <v>3</v>
       </c>
       <c r="J18" s="10">
-        <v>1023</v>
+        <v>1101</v>
       </c>
       <c r="K18" s="10">
-        <v>21389073.525880821</v>
+        <v>25119200.515578978</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
@@ -8416,7 +8416,7 @@
         <v>45</v>
       </c>
       <c r="B19" s="10">
-        <v>1284</v>
+        <v>1278</v>
       </c>
       <c r="C19" s="10">
         <v>0</v>
@@ -8425,25 +8425,25 @@
         <v>2</v>
       </c>
       <c r="E19" s="10">
-        <v>880</v>
+        <v>258</v>
       </c>
       <c r="F19" s="10">
-        <v>35364801.206156261</v>
+        <v>36194509.831490748</v>
       </c>
       <c r="G19" s="10">
-        <v>1241</v>
+        <v>1235</v>
       </c>
       <c r="H19" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" s="10">
         <v>3</v>
       </c>
       <c r="J19" s="10">
-        <v>888</v>
+        <v>895</v>
       </c>
       <c r="K19" s="10">
-        <v>37576961.856111161</v>
+        <v>43111493.808943726</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
@@ -8451,34 +8451,34 @@
         <v>47</v>
       </c>
       <c r="B20" s="10">
-        <v>1017</v>
+        <v>1022</v>
       </c>
       <c r="C20" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="10">
         <v>4</v>
       </c>
       <c r="E20" s="10">
-        <v>933</v>
+        <v>896</v>
       </c>
       <c r="F20" s="10">
-        <v>20529893.129484031</v>
+        <v>23300861.495705463</v>
       </c>
       <c r="G20" s="10">
         <v>1028</v>
       </c>
       <c r="H20" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I20" s="10">
         <v>5</v>
       </c>
       <c r="J20" s="10">
-        <v>1135</v>
+        <v>894</v>
       </c>
       <c r="K20" s="10">
-        <v>21206747.857916113</v>
+        <v>23318745.82605692</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
@@ -8486,7 +8486,7 @@
         <v>49</v>
       </c>
       <c r="B21" s="10">
-        <v>953</v>
+        <v>964</v>
       </c>
       <c r="C21" s="10">
         <v>1</v>
@@ -8495,13 +8495,13 @@
         <v>3</v>
       </c>
       <c r="E21" s="10">
-        <v>854</v>
+        <v>665</v>
       </c>
       <c r="F21" s="10">
-        <v>20518785.163835421</v>
+        <v>22855372.760754973</v>
       </c>
       <c r="G21" s="10">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="H21" s="10">
         <v>4</v>
@@ -8510,10 +8510,10 @@
         <v>3</v>
       </c>
       <c r="J21" s="10">
-        <v>659</v>
+        <v>696</v>
       </c>
       <c r="K21" s="10">
-        <v>16147770.054623244</v>
+        <v>18884057.695519928</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
@@ -8521,34 +8521,34 @@
         <v>51</v>
       </c>
       <c r="B22" s="10">
-        <v>2741</v>
+        <v>3231</v>
       </c>
       <c r="C22" s="10">
-        <v>119</v>
+        <v>624</v>
       </c>
       <c r="D22" s="10">
         <v>10</v>
       </c>
       <c r="E22" s="10">
-        <v>2113</v>
+        <v>2875</v>
       </c>
       <c r="F22" s="10">
-        <v>70768744.060212836</v>
+        <v>79706464.844519541</v>
       </c>
       <c r="G22" s="10">
-        <v>2824</v>
+        <v>2813</v>
       </c>
       <c r="H22" s="10">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="I22" s="10">
         <v>10</v>
       </c>
       <c r="J22" s="10">
-        <v>2030</v>
+        <v>2092</v>
       </c>
       <c r="K22" s="10">
-        <v>77632214.60653232</v>
+        <v>86512250.853451744</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
@@ -8556,7 +8556,7 @@
         <v>53</v>
       </c>
       <c r="B23" s="10">
-        <v>1449</v>
+        <v>1443</v>
       </c>
       <c r="C23" s="10">
         <v>0</v>
@@ -8565,25 +8565,25 @@
         <v>2</v>
       </c>
       <c r="E23" s="10">
-        <v>1238</v>
+        <v>1188</v>
       </c>
       <c r="F23" s="10">
-        <v>38832237.438178219</v>
+        <v>43461261.025939107</v>
       </c>
       <c r="G23" s="10">
-        <v>1377</v>
+        <v>1381</v>
       </c>
       <c r="H23" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I23" s="10">
         <v>1</v>
       </c>
       <c r="J23" s="10">
-        <v>1147</v>
+        <v>1167</v>
       </c>
       <c r="K23" s="10">
-        <v>20817166.925483521</v>
+        <v>25993637.843131464</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
@@ -8591,34 +8591,34 @@
         <v>55</v>
       </c>
       <c r="B24" s="10">
-        <v>3018</v>
+        <v>3008</v>
       </c>
       <c r="C24" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D24" s="10">
         <v>11</v>
       </c>
       <c r="E24" s="10">
-        <v>2378</v>
+        <v>2522</v>
       </c>
       <c r="F24" s="10">
-        <v>78073507.036272019</v>
+        <v>87326341.867069647</v>
       </c>
       <c r="G24" s="10">
-        <v>2957</v>
+        <v>2936</v>
       </c>
       <c r="H24" s="10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I24" s="10">
         <v>10</v>
       </c>
       <c r="J24" s="10">
-        <v>2154</v>
+        <v>2002</v>
       </c>
       <c r="K24" s="10">
-        <v>78167301.424380407</v>
+        <v>87531836.582215488</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
@@ -8626,34 +8626,34 @@
         <v>67</v>
       </c>
       <c r="B25" s="10">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C25" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" s="10">
         <v>1</v>
       </c>
       <c r="E25" s="10">
-        <v>732</v>
+        <v>459</v>
       </c>
       <c r="F25" s="10">
-        <v>10898300.815067604</v>
+        <v>12335831.009248348</v>
       </c>
       <c r="G25" s="10">
         <v>533</v>
       </c>
       <c r="H25" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I25" s="10">
         <v>1</v>
       </c>
       <c r="J25" s="10">
-        <v>453</v>
+        <v>482</v>
       </c>
       <c r="K25" s="10">
-        <v>11614733.231166488</v>
+        <v>13179743.144659448</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
@@ -8661,34 +8661,34 @@
         <v>74</v>
       </c>
       <c r="B26" s="10">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="C26" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D26" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="10">
-        <v>1289</v>
+        <v>1319</v>
       </c>
       <c r="F26" s="10">
-        <v>30552762.607075132</v>
+        <v>34331182.277683817</v>
       </c>
       <c r="G26" s="10">
-        <v>1714</v>
+        <v>1698</v>
       </c>
       <c r="H26" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I26" s="10">
         <v>1</v>
       </c>
       <c r="J26" s="10">
-        <v>1279</v>
+        <v>1381</v>
       </c>
       <c r="K26" s="10">
-        <v>31893649.023847744</v>
+        <v>36181572.167494185</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
@@ -8696,22 +8696,22 @@
         <v>70</v>
       </c>
       <c r="B27" s="10">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="C27" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D27" s="10">
         <v>1</v>
       </c>
       <c r="E27" s="10">
-        <v>753</v>
+        <v>800</v>
       </c>
       <c r="F27" s="10">
-        <v>13458741.548888275</v>
+        <v>15055659.969758572</v>
       </c>
       <c r="G27" s="10">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="H27" s="10">
         <v>10</v>
@@ -8720,10 +8720,10 @@
         <v>1</v>
       </c>
       <c r="J27" s="10">
-        <v>894</v>
+        <v>867</v>
       </c>
       <c r="K27" s="10">
-        <v>12988114.50952672</v>
+        <v>15017516.666063774</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
@@ -8731,22 +8731,22 @@
         <v>72</v>
       </c>
       <c r="B28" s="10">
-        <v>902</v>
+        <v>893</v>
       </c>
       <c r="C28" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="10">
         <v>1</v>
       </c>
       <c r="E28" s="10">
-        <v>732</v>
+        <v>656</v>
       </c>
       <c r="F28" s="10">
-        <v>15117116.893560741</v>
+        <v>16806306.479511511</v>
       </c>
       <c r="G28" s="10">
-        <v>884</v>
+        <v>875</v>
       </c>
       <c r="H28" s="10">
         <v>5</v>
@@ -8755,10 +8755,10 @@
         <v>1</v>
       </c>
       <c r="J28" s="10">
-        <v>871</v>
+        <v>759</v>
       </c>
       <c r="K28" s="10">
-        <v>16143654.376540195</v>
+        <v>18339133.799450003</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
@@ -8766,7 +8766,7 @@
         <v>79</v>
       </c>
       <c r="B29" s="10">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C29" s="10">
         <v>1</v>
@@ -8775,13 +8775,13 @@
         <v>0</v>
       </c>
       <c r="E29" s="10">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="F29" s="10">
-        <v>4374488.2756901234</v>
+        <v>4978274.1542370617</v>
       </c>
       <c r="G29" s="10">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H29" s="10">
         <v>1</v>
@@ -8790,10 +8790,10 @@
         <v>2</v>
       </c>
       <c r="J29" s="10">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="K29" s="10">
-        <v>3544161.3962469618</v>
+        <v>4145553.8044927949</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
@@ -8801,7 +8801,7 @@
         <v>109</v>
       </c>
       <c r="B30" s="10">
-        <v>1670</v>
+        <v>1657</v>
       </c>
       <c r="C30" s="10">
         <v>2</v>
@@ -8810,13 +8810,13 @@
         <v>5</v>
       </c>
       <c r="E30" s="10">
-        <v>1360</v>
+        <v>1327</v>
       </c>
       <c r="F30" s="10">
-        <v>34543080.136784635</v>
+        <v>38180141.640637457</v>
       </c>
       <c r="G30" s="10">
-        <v>1647</v>
+        <v>1653</v>
       </c>
       <c r="H30" s="10">
         <v>10</v>
@@ -8825,10 +8825,10 @@
         <v>5</v>
       </c>
       <c r="J30" s="10">
-        <v>1456</v>
+        <v>1384</v>
       </c>
       <c r="K30" s="10">
-        <v>30361312.978099201</v>
+        <v>34673357.838432036</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
@@ -8839,31 +8839,31 @@
         <v>858</v>
       </c>
       <c r="C31" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D31" s="10">
         <v>1</v>
       </c>
       <c r="E31" s="10">
-        <v>635</v>
+        <v>620</v>
       </c>
       <c r="F31" s="10">
-        <v>23829126.881211925</v>
+        <v>26798065.721356105</v>
       </c>
       <c r="G31" s="10">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H31" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I31" s="10">
         <v>1</v>
       </c>
       <c r="J31" s="10">
-        <v>683</v>
+        <v>695</v>
       </c>
       <c r="K31" s="10">
-        <v>25123400.694838129</v>
+        <v>28932948.270447984</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
@@ -8871,7 +8871,7 @@
         <v>113</v>
       </c>
       <c r="B32" s="10">
-        <v>1131</v>
+        <v>1127</v>
       </c>
       <c r="C32" s="10">
         <v>2</v>
@@ -8880,25 +8880,25 @@
         <v>1</v>
       </c>
       <c r="E32" s="10">
-        <v>683</v>
+        <v>757</v>
       </c>
       <c r="F32" s="10">
-        <v>25615523.717296895</v>
+        <v>28967105.315619867</v>
       </c>
       <c r="G32" s="10">
-        <v>1052</v>
+        <v>1044</v>
       </c>
       <c r="H32" s="10">
         <v>2</v>
       </c>
       <c r="I32" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J32" s="10">
-        <v>813</v>
+        <v>623</v>
       </c>
       <c r="K32" s="10">
-        <v>24340756.119797848</v>
+        <v>27314154.578593209</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
@@ -8906,7 +8906,7 @@
         <v>115</v>
       </c>
       <c r="B33" s="10">
-        <v>1113</v>
+        <v>1127</v>
       </c>
       <c r="C33" s="10">
         <v>1</v>
@@ -8915,13 +8915,13 @@
         <v>2</v>
       </c>
       <c r="E33" s="10">
-        <v>979</v>
+        <v>891</v>
       </c>
       <c r="F33" s="10">
-        <v>33440236.344155505</v>
+        <v>37440462.056698211</v>
       </c>
       <c r="G33" s="10">
-        <v>1124</v>
+        <v>1120</v>
       </c>
       <c r="H33" s="10">
         <v>3</v>
@@ -8930,10 +8930,10 @@
         <v>2</v>
       </c>
       <c r="J33" s="10">
-        <v>865</v>
+        <v>1017</v>
       </c>
       <c r="K33" s="10">
-        <v>33277591.184311975</v>
+        <v>38738095.034786858</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
@@ -8941,7 +8941,7 @@
         <v>16</v>
       </c>
       <c r="B34" s="10">
-        <v>1504</v>
+        <v>1500</v>
       </c>
       <c r="C34" s="10">
         <v>1</v>
@@ -8950,13 +8950,13 @@
         <v>5</v>
       </c>
       <c r="E34" s="10">
-        <v>1164</v>
+        <v>1170</v>
       </c>
       <c r="F34" s="10">
-        <v>48824205.713933267</v>
+        <v>54625541.40816319</v>
       </c>
       <c r="G34" s="10">
-        <v>1453</v>
+        <v>1445</v>
       </c>
       <c r="H34" s="10">
         <v>4</v>
@@ -8965,10 +8965,10 @@
         <v>4</v>
       </c>
       <c r="J34" s="10">
-        <v>1108</v>
+        <v>1153</v>
       </c>
       <c r="K34" s="10">
-        <v>46926675.133656777</v>
+        <v>49689744.933685243</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
@@ -8976,7 +8976,7 @@
         <v>18</v>
       </c>
       <c r="B35" s="10">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C35" s="10">
         <v>2</v>
@@ -8985,13 +8985,13 @@
         <v>3</v>
       </c>
       <c r="E35" s="10">
-        <v>408</v>
+        <v>546</v>
       </c>
       <c r="F35" s="10">
-        <v>18136491.705534205</v>
+        <v>20563796.033259295</v>
       </c>
       <c r="G35" s="10">
-        <v>685</v>
+        <v>698</v>
       </c>
       <c r="H35" s="10">
         <v>1</v>
@@ -9000,10 +9000,10 @@
         <v>5</v>
       </c>
       <c r="J35" s="10">
-        <v>566</v>
+        <v>657</v>
       </c>
       <c r="K35" s="10">
-        <v>19333862.377965305</v>
+        <v>22475660.079455785</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
@@ -9011,34 +9011,34 @@
         <v>43</v>
       </c>
       <c r="B36" s="10">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="C36" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D36" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E36" s="10">
-        <v>1905</v>
+        <v>1942</v>
       </c>
       <c r="F36" s="10">
-        <v>57697960.692234173</v>
+        <v>64619883.099481747</v>
       </c>
       <c r="G36" s="10">
-        <v>1906</v>
+        <v>1923</v>
       </c>
       <c r="H36" s="10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I36" s="10">
         <v>9</v>
       </c>
       <c r="J36" s="10">
-        <v>985</v>
+        <v>1597</v>
       </c>
       <c r="K36" s="10">
-        <v>46664841.921978779</v>
+        <v>54641880.595996283</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
@@ -9046,7 +9046,7 @@
         <v>152</v>
       </c>
       <c r="B37" s="10">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="C37" s="10">
         <v>2</v>
@@ -9055,25 +9055,25 @@
         <v>2</v>
       </c>
       <c r="E37" s="10">
-        <v>708</v>
+        <v>676</v>
       </c>
       <c r="F37" s="10">
-        <v>19871805.127006289</v>
+        <v>22177650.670513704</v>
       </c>
       <c r="G37" s="10">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="H37" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I37" s="10">
         <v>2</v>
       </c>
       <c r="J37" s="10">
-        <v>673</v>
+        <v>699</v>
       </c>
       <c r="K37" s="10">
-        <v>19594455.916085906</v>
+        <v>22648991.031854369</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
@@ -9081,34 +9081,34 @@
         <v>149</v>
       </c>
       <c r="B38" s="10">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="C38" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" s="10">
         <v>1</v>
       </c>
       <c r="E38" s="10">
-        <v>598</v>
+        <v>550</v>
       </c>
       <c r="F38" s="10">
-        <v>16205189.746109076</v>
+        <v>18494684.231714644</v>
       </c>
       <c r="G38" s="10">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="H38" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I38" s="10">
         <v>1</v>
       </c>
       <c r="J38" s="10">
-        <v>458</v>
+        <v>560</v>
       </c>
       <c r="K38" s="10">
-        <v>18498161.104133904</v>
+        <v>20507947.028976176</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
@@ -9116,34 +9116,34 @@
         <v>154</v>
       </c>
       <c r="B39" s="10">
-        <v>1098</v>
+        <v>1112</v>
       </c>
       <c r="C39" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D39" s="10">
         <v>2</v>
       </c>
       <c r="E39" s="10">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="F39" s="10">
-        <v>28717039.311782409</v>
+        <v>32415149.402387757</v>
       </c>
       <c r="G39" s="10">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="H39" s="10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I39" s="10">
         <v>1</v>
       </c>
       <c r="J39" s="10">
-        <v>837</v>
+        <v>849</v>
       </c>
       <c r="K39" s="10">
-        <v>27878934.567649979</v>
+        <v>31697377.625365242</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
@@ -9151,34 +9151,34 @@
         <v>2</v>
       </c>
       <c r="B40" s="10">
-        <v>1105</v>
+        <v>1098</v>
       </c>
       <c r="C40" s="10">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D40" s="10">
         <v>1</v>
       </c>
       <c r="E40" s="10">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="F40" s="10">
-        <v>28045446.933988571</v>
+        <v>31422622.587050565</v>
       </c>
       <c r="G40" s="10">
-        <v>1315</v>
+        <v>1271</v>
       </c>
       <c r="H40" s="10">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I40" s="10">
         <v>1</v>
       </c>
       <c r="J40" s="10">
-        <v>806</v>
+        <v>880</v>
       </c>
       <c r="K40" s="10">
-        <v>25972836.316768873</v>
+        <v>29999625.405255064</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
@@ -9186,22 +9186,22 @@
         <v>156</v>
       </c>
       <c r="B41" s="10">
-        <v>1791</v>
+        <v>1778</v>
       </c>
       <c r="C41" s="10">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D41" s="10">
         <v>4</v>
       </c>
       <c r="E41" s="10">
-        <v>1334</v>
+        <v>1328</v>
       </c>
       <c r="F41" s="10">
-        <v>44086773.432414651</v>
+        <v>49380423.194518387</v>
       </c>
       <c r="G41" s="10">
-        <v>2319</v>
+        <v>2274</v>
       </c>
       <c r="H41" s="10">
         <v>70</v>
@@ -9210,10 +9210,10 @@
         <v>5</v>
       </c>
       <c r="J41" s="10">
-        <v>1627</v>
+        <v>1420</v>
       </c>
       <c r="K41" s="10">
-        <v>47814301.153092101</v>
+        <v>54072727.66768647</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
@@ -9221,7 +9221,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="10">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="C42" s="10">
         <v>2</v>
@@ -9230,13 +9230,13 @@
         <v>5</v>
       </c>
       <c r="E42" s="10">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="F42" s="10">
-        <v>17501171.752967127</v>
+        <v>17501175.169462778</v>
       </c>
       <c r="G42" s="10">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="H42" s="10">
         <v>1</v>
@@ -9245,10 +9245,10 @@
         <v>6</v>
       </c>
       <c r="J42" s="10">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="K42" s="10">
-        <v>17234881.682922155</v>
+        <v>19553902.07009979</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
@@ -9265,25 +9265,25 @@
         <v>5</v>
       </c>
       <c r="E43" s="10">
-        <v>2207</v>
+        <v>1885</v>
       </c>
       <c r="F43" s="10">
-        <v>51906929.79847452</v>
+        <v>58094258.463035837</v>
       </c>
       <c r="G43" s="10">
-        <v>2060</v>
+        <v>2052</v>
       </c>
       <c r="H43" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I43" s="10">
         <v>6</v>
       </c>
       <c r="J43" s="10">
-        <v>1813</v>
+        <v>1899</v>
       </c>
       <c r="K43" s="10">
-        <v>55848173.692558862</v>
+        <v>62788078.791813053</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.35">
@@ -9291,22 +9291,22 @@
         <v>39</v>
       </c>
       <c r="B44" s="10">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="C44" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D44" s="10">
         <v>4</v>
       </c>
       <c r="E44" s="10">
-        <v>802</v>
+        <v>823</v>
       </c>
       <c r="F44" s="10">
-        <v>35818386.015351824</v>
+        <v>40259525.860920064</v>
       </c>
       <c r="G44" s="10">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="H44" s="10">
         <v>3</v>
@@ -9315,10 +9315,10 @@
         <v>4</v>
       </c>
       <c r="J44" s="10">
-        <v>1214</v>
+        <v>849</v>
       </c>
       <c r="K44" s="10">
-        <v>38783782.459595293</v>
+        <v>43702130.166758053</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.35">
@@ -9326,34 +9326,34 @@
         <v>6</v>
       </c>
       <c r="B45" s="10">
-        <v>1145</v>
+        <v>1123</v>
       </c>
       <c r="C45" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D45" s="10">
         <v>3</v>
       </c>
       <c r="E45" s="10">
-        <v>939</v>
+        <v>932</v>
       </c>
       <c r="F45" s="10">
-        <v>30056084.115850814</v>
+        <v>33706233.502371065</v>
       </c>
       <c r="G45" s="10">
-        <v>1088</v>
+        <v>1097</v>
       </c>
       <c r="H45" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I45" s="10">
         <v>3</v>
       </c>
       <c r="J45" s="10">
-        <v>936</v>
+        <v>1095</v>
       </c>
       <c r="K45" s="10">
-        <v>21319527.778955884</v>
+        <v>25153289.147385843</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
@@ -9361,7 +9361,7 @@
         <v>41</v>
       </c>
       <c r="B46" s="10">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="C46" s="10">
         <v>0</v>
@@ -9370,13 +9370,13 @@
         <v>5</v>
       </c>
       <c r="E46" s="10">
-        <v>646</v>
+        <v>623</v>
       </c>
       <c r="F46" s="10">
-        <v>29545546.930951878</v>
+        <v>32761795.611114733</v>
       </c>
       <c r="G46" s="10">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="H46" s="10">
         <v>5</v>
@@ -9385,10 +9385,10 @@
         <v>4</v>
       </c>
       <c r="J46" s="10">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="K46" s="10">
-        <v>28979341.557539623</v>
+        <v>32727427.435014695</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.35">
@@ -9396,7 +9396,7 @@
         <v>158</v>
       </c>
       <c r="B47" s="10">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C47" s="10">
         <v>3</v>
@@ -9405,25 +9405,25 @@
         <v>10</v>
       </c>
       <c r="E47" s="10">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="F47" s="10">
-        <v>18049660.276563376</v>
+        <v>20342697.235315848</v>
       </c>
       <c r="G47" s="10">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="H47" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I47" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J47" s="10">
-        <v>1046</v>
+        <v>671</v>
       </c>
       <c r="K47" s="10">
-        <v>18792405.690429319</v>
+        <v>21247499.714460559</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.35">
@@ -9431,7 +9431,7 @@
         <v>160</v>
       </c>
       <c r="B48" s="10">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="C48" s="10">
         <v>1</v>
@@ -9440,25 +9440,25 @@
         <v>1</v>
       </c>
       <c r="E48" s="10">
-        <v>750</v>
+        <v>691</v>
       </c>
       <c r="F48" s="10">
-        <v>17220687.382163826</v>
+        <v>19467108.785032246</v>
       </c>
       <c r="G48" s="10">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="H48" s="10">
         <v>0</v>
       </c>
       <c r="I48" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J48" s="10">
-        <v>475</v>
+        <v>732</v>
       </c>
       <c r="K48" s="10">
-        <v>16321357.881679956</v>
+        <v>18175582.361618567</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
@@ -9466,22 +9466,22 @@
         <v>83</v>
       </c>
       <c r="B49" s="10">
-        <v>1295</v>
+        <v>1283</v>
       </c>
       <c r="C49" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D49" s="10">
         <v>6</v>
       </c>
       <c r="E49" s="10">
-        <v>1180</v>
+        <v>1103</v>
       </c>
       <c r="F49" s="10">
-        <v>56121265.077946588</v>
+        <v>62477023.740561083</v>
       </c>
       <c r="G49" s="10">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="H49" s="10">
         <v>2</v>
@@ -9490,10 +9490,10 @@
         <v>5</v>
       </c>
       <c r="J49" s="10">
-        <v>1074</v>
+        <v>1454</v>
       </c>
       <c r="K49" s="10">
-        <v>50336716.63548696</v>
+        <v>58038275.749017172</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
@@ -9501,34 +9501,34 @@
         <v>202</v>
       </c>
       <c r="B50" s="10">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C50" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D50" s="10">
         <v>2</v>
       </c>
       <c r="E50" s="10">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F50" s="10">
-        <v>10182749.321593467</v>
+        <v>11376658.915109288</v>
       </c>
       <c r="G50" s="10">
+        <v>444</v>
+      </c>
+      <c r="H50" s="10">
+        <v>1</v>
+      </c>
+      <c r="I50" s="10">
+        <v>1</v>
+      </c>
+      <c r="J50" s="10">
         <v>440</v>
       </c>
-      <c r="H50" s="10">
-        <v>1</v>
-      </c>
-      <c r="I50" s="10">
-        <v>1</v>
-      </c>
-      <c r="J50" s="10">
-        <v>429</v>
-      </c>
       <c r="K50" s="10">
-        <v>8258642.3442348354</v>
+        <v>9365285.4537124839</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
@@ -9536,34 +9536,34 @@
         <v>31</v>
       </c>
       <c r="B51" s="10">
-        <v>868</v>
+        <v>877</v>
       </c>
       <c r="C51" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" s="10">
         <v>5</v>
       </c>
       <c r="E51" s="10">
-        <v>888</v>
+        <v>948</v>
       </c>
       <c r="F51" s="10">
-        <v>25070780.558970418</v>
+        <v>28184934.114670154</v>
       </c>
       <c r="G51" s="10">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="H51" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I51" s="10">
         <v>7</v>
       </c>
       <c r="J51" s="10">
-        <v>921</v>
+        <v>939</v>
       </c>
       <c r="K51" s="10">
-        <v>24322654.950506765</v>
+        <v>27492791.124575771</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
@@ -9571,34 +9571,34 @@
         <v>33</v>
       </c>
       <c r="B52" s="10">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="C52" s="10">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D52" s="10">
         <v>12</v>
       </c>
       <c r="E52" s="10">
-        <v>1015</v>
+        <v>1003</v>
       </c>
       <c r="F52" s="10">
-        <v>36249311.027373917</v>
+        <v>41289989.144723333</v>
       </c>
       <c r="G52" s="10">
-        <v>1348</v>
+        <v>1345</v>
       </c>
       <c r="H52" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I52" s="10">
         <v>12</v>
       </c>
       <c r="J52" s="10">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="K52" s="10">
-        <v>42593266.870044634</v>
+        <v>47993219.130776621</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.35">
@@ -9606,22 +9606,22 @@
         <v>85</v>
       </c>
       <c r="B53" s="10">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C53" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D53" s="10">
         <v>5</v>
       </c>
       <c r="E53" s="10">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F53" s="10">
-        <v>18877382.814397447</v>
+        <v>21359608.09983848</v>
       </c>
       <c r="G53" s="10">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="H53" s="10">
         <v>1</v>
@@ -9630,10 +9630,10 @@
         <v>6</v>
       </c>
       <c r="J53" s="10">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="K53" s="10">
-        <v>21999896.923067365</v>
+        <v>24793926.215664741</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.35">
@@ -9641,22 +9641,22 @@
         <v>81</v>
       </c>
       <c r="B54" s="10">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C54" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E54" s="10">
-        <v>318</v>
+        <v>2191</v>
       </c>
       <c r="F54" s="10">
-        <v>19430174.451933045</v>
+        <v>21478198.433565818</v>
       </c>
       <c r="G54" s="10">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="H54" s="10">
         <v>0</v>
@@ -9665,10 +9665,10 @@
         <v>4</v>
       </c>
       <c r="J54" s="10">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="K54" s="10">
-        <v>16002679.555755092</v>
+        <v>18005875.489039745</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.35">
@@ -9679,31 +9679,31 @@
         <v>428</v>
       </c>
       <c r="C55" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D55" s="10">
         <v>2</v>
       </c>
       <c r="E55" s="10">
-        <v>383</v>
+        <v>351</v>
       </c>
       <c r="F55" s="10">
-        <v>16077907.296333432</v>
+        <v>17676503.12317507</v>
       </c>
       <c r="G55" s="10">
         <v>422</v>
       </c>
       <c r="H55" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I55" s="10">
         <v>4</v>
       </c>
       <c r="J55" s="10">
-        <v>302</v>
+        <v>335</v>
       </c>
       <c r="K55" s="10">
-        <v>13853359.611095656</v>
+        <v>15802232.271788953</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.35">
@@ -9711,19 +9711,19 @@
         <v>166</v>
       </c>
       <c r="B56" s="10">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="C56" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D56" s="10">
         <v>1</v>
       </c>
       <c r="E56" s="10">
-        <v>987</v>
+        <v>997</v>
       </c>
       <c r="F56" s="10">
-        <v>34631933.852164701</v>
+        <v>38319010.734158374</v>
       </c>
       <c r="G56" s="10">
         <v>1104</v>
@@ -9732,13 +9732,13 @@
         <v>5</v>
       </c>
       <c r="I56" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" s="10">
-        <v>872</v>
+        <v>921</v>
       </c>
       <c r="K56" s="10">
-        <v>32913629.915348537</v>
+        <v>37135022.236871041</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
@@ -9746,7 +9746,7 @@
         <v>93</v>
       </c>
       <c r="B57" s="10">
-        <v>944</v>
+        <v>967</v>
       </c>
       <c r="C57" s="10">
         <v>10</v>
@@ -9755,13 +9755,13 @@
         <v>3</v>
       </c>
       <c r="E57" s="10">
-        <v>930</v>
+        <v>867</v>
       </c>
       <c r="F57" s="10">
-        <v>36634153.112307087</v>
+        <v>40505878.641760208</v>
       </c>
       <c r="G57" s="10">
-        <v>1002</v>
+        <v>1009</v>
       </c>
       <c r="H57" s="10">
         <v>7</v>
@@ -9770,10 +9770,10 @@
         <v>1</v>
       </c>
       <c r="J57" s="10">
-        <v>1002</v>
+        <v>926</v>
       </c>
       <c r="K57" s="10">
-        <v>32757032.238542307</v>
+        <v>38633184.860168822</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.35">
@@ -9781,34 +9781,34 @@
         <v>95</v>
       </c>
       <c r="B58" s="10">
-        <v>2196</v>
+        <v>2161</v>
       </c>
       <c r="C58" s="10">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D58" s="10">
         <v>7</v>
       </c>
       <c r="E58" s="10">
-        <v>1566</v>
+        <v>1656</v>
       </c>
       <c r="F58" s="10">
-        <v>49012795.183127128</v>
+        <v>56342722.856981687</v>
       </c>
       <c r="G58" s="10">
-        <v>2048</v>
+        <v>2036</v>
       </c>
       <c r="H58" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I58" s="10">
         <v>8</v>
       </c>
       <c r="J58" s="10">
-        <v>1601</v>
+        <v>1773</v>
       </c>
       <c r="K58" s="10">
-        <v>61098674.970430002</v>
+        <v>69474698.048531413</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.35">
@@ -9816,7 +9816,7 @@
         <v>174</v>
       </c>
       <c r="B59" s="10">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C59" s="10">
         <v>3</v>
@@ -9825,13 +9825,13 @@
         <v>0</v>
       </c>
       <c r="E59" s="10">
-        <v>556</v>
+        <v>528</v>
       </c>
       <c r="F59" s="10">
-        <v>16802002.123263378</v>
+        <v>18581528.074724223</v>
       </c>
       <c r="G59" s="10">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="H59" s="10">
         <v>4</v>
@@ -9840,10 +9840,10 @@
         <v>0</v>
       </c>
       <c r="J59" s="10">
-        <v>447</v>
+        <v>498</v>
       </c>
       <c r="K59" s="10">
-        <v>15233052.180801317</v>
+        <v>17379391.950311348</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.35">
@@ -9854,19 +9854,19 @@
         <v>885</v>
       </c>
       <c r="C60" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D60" s="10">
         <v>5</v>
       </c>
       <c r="E60" s="10">
-        <v>650</v>
+        <v>794</v>
       </c>
       <c r="F60" s="10">
-        <v>25317769.097523954</v>
+        <v>28675817.814602911</v>
       </c>
       <c r="G60" s="10">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="H60" s="10">
         <v>6</v>
@@ -9875,10 +9875,10 @@
         <v>5</v>
       </c>
       <c r="J60" s="10">
-        <v>715</v>
+        <v>790</v>
       </c>
       <c r="K60" s="10">
-        <v>26561551.871163208</v>
+        <v>30317184.127649944</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.35">
@@ -9886,22 +9886,22 @@
         <v>172</v>
       </c>
       <c r="B61" s="10">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C61" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D61" s="10">
         <v>1</v>
       </c>
       <c r="E61" s="10">
-        <v>609</v>
+        <v>624</v>
       </c>
       <c r="F61" s="10">
-        <v>20332674.780575395</v>
+        <v>22481594.447822541</v>
       </c>
       <c r="G61" s="10">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="H61" s="10">
         <v>4</v>
@@ -9910,10 +9910,10 @@
         <v>1</v>
       </c>
       <c r="J61" s="10">
-        <v>740</v>
+        <v>658</v>
       </c>
       <c r="K61" s="10">
-        <v>16875594.073253468</v>
+        <v>19189044.107355248</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.35">
@@ -9921,34 +9921,34 @@
         <v>168</v>
       </c>
       <c r="B62" s="10">
-        <v>1089</v>
+        <v>1097</v>
       </c>
       <c r="C62" s="10">
+        <v>8</v>
+      </c>
+      <c r="D62" s="10">
+        <v>1</v>
+      </c>
+      <c r="E62" s="10">
+        <v>1106</v>
+      </c>
+      <c r="F62" s="10">
+        <v>38270861.122598462</v>
+      </c>
+      <c r="G62" s="10">
+        <v>1110</v>
+      </c>
+      <c r="H62" s="10">
         <v>7</v>
-      </c>
-      <c r="D62" s="10">
-        <v>1</v>
-      </c>
-      <c r="E62" s="10">
-        <v>1043</v>
-      </c>
-      <c r="F62" s="10">
-        <v>34530254.150361381</v>
-      </c>
-      <c r="G62" s="10">
-        <v>1112</v>
-      </c>
-      <c r="H62" s="10">
-        <v>6</v>
       </c>
       <c r="I62" s="10">
         <v>0</v>
       </c>
       <c r="J62" s="10">
-        <v>869</v>
+        <v>938</v>
       </c>
       <c r="K62" s="10">
-        <v>34330986.777931541</v>
+        <v>38656329.906607106</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.35">
@@ -9956,34 +9956,34 @@
         <v>101</v>
       </c>
       <c r="B63" s="10">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="C63" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D63" s="10">
         <v>4</v>
       </c>
       <c r="E63" s="10">
-        <v>1437</v>
+        <v>1410</v>
       </c>
       <c r="F63" s="10">
-        <v>43893016.899277039</v>
+        <v>49094951.780632906</v>
       </c>
       <c r="G63" s="10">
-        <v>1478</v>
+        <v>1497</v>
       </c>
       <c r="H63" s="10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I63" s="10">
         <v>4</v>
       </c>
       <c r="J63" s="10">
-        <v>1339</v>
+        <v>1041</v>
       </c>
       <c r="K63" s="10">
-        <v>43409662.357671969</v>
+        <v>47134937.423156217</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.35">
@@ -9991,7 +9991,7 @@
         <v>103</v>
       </c>
       <c r="B64" s="10">
-        <v>779</v>
+        <v>768</v>
       </c>
       <c r="C64" s="10">
         <v>4</v>
@@ -10000,13 +10000,13 @@
         <v>5</v>
       </c>
       <c r="E64" s="10">
-        <v>702</v>
+        <v>678</v>
       </c>
       <c r="F64" s="10">
-        <v>22329910.806698915</v>
+        <v>24841033.532271557</v>
       </c>
       <c r="G64" s="10">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="H64" s="10">
         <v>2</v>
@@ -10015,10 +10015,10 @@
         <v>4</v>
       </c>
       <c r="J64" s="10">
-        <v>693</v>
+        <v>754</v>
       </c>
       <c r="K64" s="10">
-        <v>23201281.738800615</v>
+        <v>26286574.062764719</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.35">
@@ -10026,34 +10026,34 @@
         <v>105</v>
       </c>
       <c r="B65" s="10">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="C65" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D65" s="10">
         <v>5</v>
       </c>
       <c r="E65" s="10">
-        <v>466</v>
+        <v>448</v>
       </c>
       <c r="F65" s="10">
-        <v>25864409.160511479</v>
+        <v>29096685.519441087</v>
       </c>
       <c r="G65" s="10">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="H65" s="10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I65" s="10">
         <v>5</v>
       </c>
       <c r="J65" s="10">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="K65" s="10">
-        <v>25848326.485295001</v>
+        <v>29372784.881242465</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.35">
@@ -10061,34 +10061,34 @@
         <v>24</v>
       </c>
       <c r="B66" s="10">
-        <v>2028</v>
+        <v>2035</v>
       </c>
       <c r="C66" s="10">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D66" s="10">
         <v>9</v>
       </c>
       <c r="E66" s="10">
-        <v>1642</v>
+        <v>1676</v>
       </c>
       <c r="F66" s="10">
-        <v>66090588.086731672</v>
+        <v>75334047.475907341</v>
       </c>
       <c r="G66" s="10">
-        <v>1983</v>
+        <v>1990</v>
       </c>
       <c r="H66" s="10">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I66" s="10">
         <v>11</v>
       </c>
       <c r="J66" s="10">
-        <v>1969</v>
+        <v>1567</v>
       </c>
       <c r="K66" s="10">
-        <v>83965424.239891231</v>
+        <v>94609229.45671463</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.35">
@@ -10096,22 +10096,22 @@
         <v>27</v>
       </c>
       <c r="B67" s="10">
-        <v>1614</v>
+        <v>1602</v>
       </c>
       <c r="C67" s="10">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D67" s="10">
         <v>8</v>
       </c>
       <c r="E67" s="10">
-        <v>1197</v>
+        <v>1193</v>
       </c>
       <c r="F67" s="10">
-        <v>62841028.586884134</v>
+        <v>70479993.177585602</v>
       </c>
       <c r="G67" s="10">
-        <v>1583</v>
+        <v>1599</v>
       </c>
       <c r="H67" s="10">
         <v>16</v>
@@ -10120,10 +10120,10 @@
         <v>6</v>
       </c>
       <c r="J67" s="10">
-        <v>1096</v>
+        <v>1356</v>
       </c>
       <c r="K67" s="10">
-        <v>62126278.515833758</v>
+        <v>70751538.977041662</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.35">
@@ -10131,7 +10131,7 @@
         <v>29</v>
       </c>
       <c r="B68" s="10">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="C68" s="10">
         <v>2</v>
@@ -10140,25 +10140,25 @@
         <v>1</v>
       </c>
       <c r="E68" s="10">
-        <v>740</v>
+        <v>656</v>
       </c>
       <c r="F68" s="10">
-        <v>39412261.823200494</v>
+        <v>43706336.685455166</v>
       </c>
       <c r="G68" s="10">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H68" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I68" s="10">
         <v>1</v>
       </c>
       <c r="J68" s="10">
-        <v>720</v>
+        <v>654</v>
       </c>
       <c r="K68" s="10">
-        <v>40280606.360153332</v>
+        <v>45651879.400535792</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.35">
@@ -10166,34 +10166,34 @@
         <v>57</v>
       </c>
       <c r="B69" s="10">
-        <v>1831</v>
+        <v>2008</v>
       </c>
       <c r="C69" s="10">
-        <v>46</v>
+        <v>244</v>
       </c>
       <c r="D69" s="10">
         <v>13</v>
       </c>
       <c r="E69" s="10">
-        <v>1280</v>
+        <v>1463</v>
       </c>
       <c r="F69" s="10">
-        <v>57167525.883572713</v>
+        <v>64357523.01838614</v>
       </c>
       <c r="G69" s="10">
-        <v>2275</v>
+        <v>2204</v>
       </c>
       <c r="H69" s="10">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="I69" s="10">
         <v>12</v>
       </c>
       <c r="J69" s="10">
-        <v>1405</v>
+        <v>1245</v>
       </c>
       <c r="K69" s="10">
-        <v>60465669.223312296</v>
+        <v>67636200.907637477</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.35">
@@ -10201,22 +10201,22 @@
         <v>137</v>
       </c>
       <c r="B70" s="10">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="C70" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70" s="10">
         <v>1</v>
       </c>
       <c r="E70" s="10">
-        <v>205</v>
+        <v>255</v>
       </c>
       <c r="F70" s="10">
-        <v>4378520.589103437</v>
+        <v>4831983.2646832503</v>
       </c>
       <c r="G70" s="10">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="H70" s="10">
         <v>0</v>
@@ -10228,7 +10228,7 @@
         <v>246</v>
       </c>
       <c r="K70" s="10">
-        <v>2048502.629354598</v>
+        <v>2632017.6643952979</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.35">
@@ -10236,22 +10236,22 @@
         <v>10</v>
       </c>
       <c r="B71" s="10">
-        <v>1739</v>
+        <v>1781</v>
       </c>
       <c r="C71" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D71" s="10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E71" s="10">
-        <v>1505</v>
+        <v>1517</v>
       </c>
       <c r="F71" s="10">
-        <v>45352921.739393339</v>
+        <v>50773613.3984451</v>
       </c>
       <c r="G71" s="10">
-        <v>1659</v>
+        <v>1663</v>
       </c>
       <c r="H71" s="10">
         <v>9</v>
@@ -10260,10 +10260,10 @@
         <v>6</v>
       </c>
       <c r="J71" s="10">
-        <v>1620</v>
+        <v>1571</v>
       </c>
       <c r="K71" s="10">
-        <v>43209518.753187433</v>
+        <v>48982194.351211667</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.35">
@@ -10271,7 +10271,7 @@
         <v>12</v>
       </c>
       <c r="B72" s="10">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C72" s="10">
         <v>2</v>
@@ -10280,13 +10280,13 @@
         <v>2</v>
       </c>
       <c r="E72" s="10">
-        <v>714</v>
+        <v>571</v>
       </c>
       <c r="F72" s="10">
-        <v>18336011.237021081</v>
+        <v>20933770.783716775</v>
       </c>
       <c r="G72" s="10">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H72" s="10">
         <v>3</v>
@@ -10295,10 +10295,10 @@
         <v>3</v>
       </c>
       <c r="J72" s="10">
-        <v>591</v>
+        <v>614</v>
       </c>
       <c r="K72" s="10">
-        <v>20578373.523585159</v>
+        <v>23094311.445282642</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.35">
@@ -10306,34 +10306,34 @@
         <v>162</v>
       </c>
       <c r="B73" s="10">
-        <v>1306</v>
+        <v>1325</v>
       </c>
       <c r="C73" s="10">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="D73" s="10">
         <v>5</v>
       </c>
       <c r="E73" s="10">
-        <v>1024</v>
+        <v>1189</v>
       </c>
       <c r="F73" s="10">
-        <v>30336217.121641062</v>
+        <v>34166560.655513391</v>
       </c>
       <c r="G73" s="10">
-        <v>1362</v>
+        <v>1391</v>
       </c>
       <c r="H73" s="10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I73" s="10">
         <v>4</v>
       </c>
       <c r="J73" s="10">
-        <v>1057</v>
+        <v>982</v>
       </c>
       <c r="K73" s="10">
-        <v>30139103.683555558</v>
+        <v>34962922.177493237</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.35">
@@ -10341,7 +10341,7 @@
         <v>63</v>
       </c>
       <c r="B74" s="10">
-        <v>1376</v>
+        <v>1356</v>
       </c>
       <c r="C74" s="10">
         <v>7</v>
@@ -10350,25 +10350,25 @@
         <v>5</v>
       </c>
       <c r="E74" s="10">
-        <v>1437</v>
+        <v>853</v>
       </c>
       <c r="F74" s="10">
-        <v>16618312.391290843</v>
+        <v>17151283.369032022</v>
       </c>
       <c r="G74" s="10">
-        <v>1262</v>
+        <v>1253</v>
       </c>
       <c r="H74" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I74" s="10">
         <v>5</v>
       </c>
       <c r="J74" s="10">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="K74" s="10">
-        <v>18957921.415138125</v>
+        <v>22198382.348371297</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.35">
@@ -10376,34 +10376,34 @@
         <v>59</v>
       </c>
       <c r="B75" s="10">
-        <v>1742</v>
+        <v>1751</v>
       </c>
       <c r="C75" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D75" s="10">
         <v>5</v>
       </c>
       <c r="E75" s="10">
-        <v>1221</v>
+        <v>1210</v>
       </c>
       <c r="F75" s="10">
-        <v>53443829.91769053</v>
+        <v>60080748.523181163</v>
       </c>
       <c r="G75" s="10">
-        <v>1752</v>
+        <v>1758</v>
       </c>
       <c r="H75" s="10">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I75" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J75" s="10">
-        <v>1165</v>
+        <v>1241</v>
       </c>
       <c r="K75" s="10">
-        <v>53768628.46778176</v>
+        <v>61224476.983174697</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.35">
@@ -10411,22 +10411,22 @@
         <v>139</v>
       </c>
       <c r="B76" s="10">
+        <v>496</v>
+      </c>
+      <c r="C76" s="10">
+        <v>2</v>
+      </c>
+      <c r="D76" s="10">
+        <v>2</v>
+      </c>
+      <c r="E76" s="10">
         <v>494</v>
       </c>
-      <c r="C76" s="10">
-        <v>2</v>
-      </c>
-      <c r="D76" s="10">
-        <v>2</v>
-      </c>
-      <c r="E76" s="10">
-        <v>481</v>
-      </c>
       <c r="F76" s="10">
-        <v>11826471.965840572</v>
+        <v>13156020.104537236</v>
       </c>
       <c r="G76" s="10">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="H76" s="10">
         <v>2</v>
@@ -10435,10 +10435,10 @@
         <v>1</v>
       </c>
       <c r="J76" s="10">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="K76" s="10">
-        <v>10901511.46614914</v>
+        <v>12385983.388492895</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.35">
@@ -10446,22 +10446,22 @@
         <v>170</v>
       </c>
       <c r="B77" s="10">
-        <v>903</v>
+        <v>891</v>
       </c>
       <c r="C77" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D77" s="10">
         <v>1</v>
       </c>
       <c r="E77" s="10">
-        <v>802</v>
+        <v>834</v>
       </c>
       <c r="F77" s="10">
-        <v>17876676.04137864</v>
+        <v>19982061.397274464</v>
       </c>
       <c r="G77" s="10">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="H77" s="10">
         <v>2</v>
@@ -10470,10 +10470,10 @@
         <v>1</v>
       </c>
       <c r="J77" s="10">
-        <v>1324</v>
+        <v>791</v>
       </c>
       <c r="K77" s="10">
-        <v>17293360.891407505</v>
+        <v>19938681.662497777</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.35">
@@ -10481,34 +10481,34 @@
         <v>61</v>
       </c>
       <c r="B78" s="10">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="C78" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D78" s="10">
         <v>4</v>
       </c>
       <c r="E78" s="10">
-        <v>529</v>
+        <v>633</v>
       </c>
       <c r="F78" s="10">
-        <v>13557893.517239362</v>
+        <v>14294811.694408428</v>
       </c>
       <c r="G78" s="10">
         <v>645</v>
       </c>
       <c r="H78" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" s="10">
         <v>3</v>
       </c>
       <c r="J78" s="10">
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="K78" s="10">
-        <v>17057156.633488394</v>
+        <v>19626666.190058872</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.35">
@@ -10516,7 +10516,7 @@
         <v>129</v>
       </c>
       <c r="B79" s="10">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="C79" s="10">
         <v>5</v>
@@ -10525,13 +10525,13 @@
         <v>1</v>
       </c>
       <c r="E79" s="10">
-        <v>672</v>
+        <v>352</v>
       </c>
       <c r="F79" s="10">
-        <v>12063598.275348464</v>
+        <v>13802610.510686357</v>
       </c>
       <c r="G79" s="10">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="H79" s="10">
         <v>6</v>
@@ -10540,10 +10540,10 @@
         <v>1</v>
       </c>
       <c r="J79" s="10">
-        <v>700</v>
+        <v>596</v>
       </c>
       <c r="K79" s="10">
-        <v>13402969.79479092</v>
+        <v>14965299.75582342</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.35">
@@ -10551,7 +10551,7 @@
         <v>35</v>
       </c>
       <c r="B80" s="10">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="C80" s="10">
         <v>5</v>
@@ -10560,13 +10560,13 @@
         <v>6</v>
       </c>
       <c r="E80" s="10">
-        <v>403</v>
+        <v>427</v>
       </c>
       <c r="F80" s="10">
-        <v>13708803.873142265</v>
+        <v>15323299.284381747</v>
       </c>
       <c r="G80" s="10">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="H80" s="10">
         <v>1</v>
@@ -10575,10 +10575,10 @@
         <v>7</v>
       </c>
       <c r="J80" s="10">
-        <v>405</v>
+        <v>471</v>
       </c>
       <c r="K80" s="10">
-        <v>14530462.249641132</v>
+        <v>16528959.138679625</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.35">
@@ -10586,34 +10586,34 @@
         <v>107</v>
       </c>
       <c r="B81" s="10">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="C81" s="10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D81" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E81" s="10">
-        <v>777</v>
+        <v>736</v>
       </c>
       <c r="F81" s="10">
-        <v>39546382.337860718</v>
+        <v>44142138.429326862</v>
       </c>
       <c r="G81" s="10">
-        <v>930</v>
+        <v>919</v>
       </c>
       <c r="H81" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I81" s="10">
         <v>3</v>
       </c>
       <c r="J81" s="10">
-        <v>502</v>
+        <v>911</v>
       </c>
       <c r="K81" s="10">
-        <v>38541613.188916355</v>
+        <v>43962551.141078793</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.35">
@@ -10621,22 +10621,22 @@
         <v>37</v>
       </c>
       <c r="B82" s="10">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C82" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D82" s="10">
         <v>9</v>
       </c>
       <c r="E82" s="10">
-        <v>716</v>
+        <v>748</v>
       </c>
       <c r="F82" s="10">
-        <v>23025653.099902775</v>
+        <v>26320088.840679597</v>
       </c>
       <c r="G82" s="10">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="H82" s="10">
         <v>2</v>
@@ -10645,10 +10645,10 @@
         <v>10</v>
       </c>
       <c r="J82" s="10">
-        <v>681</v>
+        <v>694</v>
       </c>
       <c r="K82" s="10">
-        <v>22939388.116681613</v>
+        <v>25795596.968580019</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.35">
@@ -10656,7 +10656,7 @@
         <v>76</v>
       </c>
       <c r="B83" s="10">
-        <v>937</v>
+        <v>949</v>
       </c>
       <c r="C83" s="10">
         <v>0</v>
@@ -10665,10 +10665,10 @@
         <v>2</v>
       </c>
       <c r="E83" s="10">
-        <v>418</v>
+        <v>931</v>
       </c>
       <c r="F83" s="10">
-        <v>19193236.094868459</v>
+        <v>21296375.880635846</v>
       </c>
       <c r="G83" s="10">
         <v>961</v>
@@ -10680,10 +10680,10 @@
         <v>2</v>
       </c>
       <c r="J83" s="10">
-        <v>919</v>
+        <v>969</v>
       </c>
       <c r="K83" s="10">
-        <v>18892615.754533097</v>
+        <v>21424759.907585599</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.35">
@@ -10691,22 +10691,22 @@
         <v>65</v>
       </c>
       <c r="B84" s="10">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C84" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D84" s="10">
         <v>4</v>
       </c>
       <c r="E84" s="10">
-        <v>817</v>
+        <v>802</v>
       </c>
       <c r="F84" s="10">
-        <v>21820331.478659838</v>
+        <v>24350171.013393518</v>
       </c>
       <c r="G84" s="10">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="H84" s="10">
         <v>2</v>
@@ -10715,10 +10715,10 @@
         <v>5</v>
       </c>
       <c r="J84" s="10">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="K84" s="10">
-        <v>18937194.680255909</v>
+        <v>22204966.601389252</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.35">
@@ -10726,7 +10726,7 @@
         <v>89</v>
       </c>
       <c r="B85" s="10">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="C85" s="10">
         <v>5</v>
@@ -10735,13 +10735,13 @@
         <v>5</v>
       </c>
       <c r="E85" s="10">
-        <v>652</v>
+        <v>720</v>
       </c>
       <c r="F85" s="10">
-        <v>22969864.224000525</v>
+        <v>26106286.217771295</v>
       </c>
       <c r="G85" s="10">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="H85" s="10">
         <v>2</v>
@@ -10750,10 +10750,10 @@
         <v>6</v>
       </c>
       <c r="J85" s="10">
-        <v>791</v>
+        <v>743</v>
       </c>
       <c r="K85" s="10">
-        <v>24869476.140908346</v>
+        <v>28443447.509641979</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.35">
@@ -10761,7 +10761,7 @@
         <v>147</v>
       </c>
       <c r="B86" s="10">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="C86" s="10">
         <v>2</v>
@@ -10770,25 +10770,25 @@
         <v>1</v>
       </c>
       <c r="E86" s="10">
-        <v>634</v>
+        <v>691</v>
       </c>
       <c r="F86" s="10">
-        <v>10394587.674253045</v>
+        <v>11647431.128983499</v>
       </c>
       <c r="G86" s="10">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H86" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I86" s="10">
         <v>1</v>
       </c>
       <c r="J86" s="10">
-        <v>587</v>
+        <v>522</v>
       </c>
       <c r="K86" s="10">
-        <v>11488416.949110754</v>
+        <v>13047181.392881865</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.35">
@@ -10796,7 +10796,7 @@
         <v>164</v>
       </c>
       <c r="B87" s="10">
-        <v>1716</v>
+        <v>1704</v>
       </c>
       <c r="C87" s="10">
         <v>9</v>
@@ -10805,25 +10805,25 @@
         <v>10</v>
       </c>
       <c r="E87" s="10">
-        <v>1326</v>
+        <v>1261</v>
       </c>
       <c r="F87" s="10">
-        <v>44349442.066209733</v>
+        <v>50025277.975978665</v>
       </c>
       <c r="G87" s="10">
-        <v>1770</v>
+        <v>1764</v>
       </c>
       <c r="H87" s="10">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I87" s="10">
         <v>10</v>
       </c>
       <c r="J87" s="10">
-        <v>1068</v>
+        <v>1312</v>
       </c>
       <c r="K87" s="10">
-        <v>48331718.355496056</v>
+        <v>54503798.017063886</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.35">
@@ -10831,7 +10831,7 @@
         <v>91</v>
       </c>
       <c r="B88" s="10">
-        <v>634</v>
+        <v>620</v>
       </c>
       <c r="C88" s="10">
         <v>5</v>
@@ -10840,13 +10840,13 @@
         <v>3</v>
       </c>
       <c r="E88" s="10">
-        <v>722</v>
+        <v>641</v>
       </c>
       <c r="F88" s="10">
-        <v>12502707.703434112</v>
+        <v>13491062.530736148</v>
       </c>
       <c r="G88" s="10">
-        <v>567</v>
+        <v>578</v>
       </c>
       <c r="H88" s="10">
         <v>0</v>
@@ -10855,10 +10855,10 @@
         <v>3</v>
       </c>
       <c r="J88" s="10">
-        <v>606</v>
+        <v>671</v>
       </c>
       <c r="K88" s="10">
-        <v>11400986.222267387</v>
+        <v>12625436.34218335</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.35">
@@ -10866,22 +10866,22 @@
         <v>97</v>
       </c>
       <c r="B89" s="10">
-        <v>629</v>
+        <v>604</v>
       </c>
       <c r="C89" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D89" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E89" s="10">
-        <v>652</v>
+        <v>520</v>
       </c>
       <c r="F89" s="10">
-        <v>21157037.639902744</v>
+        <v>23429486.45540712</v>
       </c>
       <c r="G89" s="10">
-        <v>646</v>
+        <v>631</v>
       </c>
       <c r="H89" s="10">
         <v>4</v>
@@ -10890,10 +10890,10 @@
         <v>7</v>
       </c>
       <c r="J89" s="10">
-        <v>569</v>
+        <v>641</v>
       </c>
       <c r="K89" s="10">
-        <v>21464086.625509623</v>
+        <v>24509877.584273003</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.35">
@@ -10901,7 +10901,7 @@
         <v>78</v>
       </c>
       <c r="B90" s="10">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C90" s="10">
         <v>2</v>
@@ -10910,13 +10910,13 @@
         <v>1</v>
       </c>
       <c r="E90" s="10">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="F90" s="10">
-        <v>5927184.8282444756</v>
+        <v>6461103.0332732033</v>
       </c>
       <c r="G90" s="10">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="H90" s="10">
         <v>2</v>
@@ -10925,10 +10925,10 @@
         <v>1</v>
       </c>
       <c r="J90" s="10">
-        <v>296</v>
+        <v>380</v>
       </c>
       <c r="K90" s="10">
-        <v>5259376.4748856099</v>
+        <v>5909417.688019501</v>
       </c>
     </row>
   </sheetData>

--- a/SITE MONITORING.xlsx
+++ b/SITE MONITORING.xlsx
@@ -1136,27 +1136,27 @@
       </c>
       <c r="F2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11813210.545567276</v>
+        <v>12452036.798173808</v>
       </c>
       <c r="G2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11602296.38923113</v>
+        <v>12287955.952436997</v>
       </c>
       <c r="H2" s="12">
         <f>IFERROR(G2/F2-1,0)</f>
-        <v>-1.7854092714472802E-2</v>
+        <v>-1.3177028657743395E-2</v>
       </c>
       <c r="I2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="J2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>428</v>
+        <v>364</v>
       </c>
       <c r="K2" s="12">
         <f>IFERROR(J2/I2-1,0)</f>
-        <v>0.32098765432098775</v>
+        <v>7.3746312684365822E-2</v>
       </c>
       <c r="L2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1184,15 +1184,15 @@
       </c>
       <c r="R2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="S2">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="T2" s="12">
         <f>IFERROR(S2/R2-1,0)</f>
-        <v>-2.4038461538461453E-3</v>
+        <v>-1.6786570743405282E-2</v>
       </c>
       <c r="U2">
         <v>3</v>
@@ -1216,27 +1216,27 @@
       </c>
       <c r="F3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14558309.604847057</v>
+        <v>15270377.5820772</v>
       </c>
       <c r="G3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13595181.152484637</v>
+        <v>14339947.092993161</v>
       </c>
       <c r="H3" s="12">
         <f t="shared" ref="H3:H66" si="0">IFERROR(G3/F3-1,0)</f>
-        <v>-6.6156612855777897E-2</v>
+        <v>-6.0930417999361275E-2</v>
       </c>
       <c r="I3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>454</v>
+        <v>525</v>
       </c>
       <c r="J3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>519</v>
+        <v>487</v>
       </c>
       <c r="K3" s="12">
         <f t="shared" ref="K3:K66" si="1">IFERROR(J3/I3-1,0)</f>
-        <v>0.14317180616740077</v>
+        <v>-7.2380952380952435E-2</v>
       </c>
       <c r="L3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1244,11 +1244,11 @@
       </c>
       <c r="M3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N3" s="12">
         <f t="shared" ref="N3:N66" si="2">IFERROR(M3/L3-1,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -1256,23 +1256,23 @@
       </c>
       <c r="P3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q3" s="12">
         <f t="shared" ref="Q3:Q66" si="3">IFERROR(P3/O3-1,0)</f>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="S3">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="T3" s="12">
         <f t="shared" ref="T3:T66" si="4">IFERROR(S3/R3-1,0)</f>
-        <v>-5.7522123893805288E-2</v>
+        <v>-7.0484581497797349E-2</v>
       </c>
       <c r="U3">
         <v>2</v>
@@ -1296,27 +1296,27 @@
       </c>
       <c r="F4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15765702.050982265</v>
+        <v>17041117.995255239</v>
       </c>
       <c r="G4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18573202.176985394</v>
+        <v>19961475.905457538</v>
       </c>
       <c r="H4" s="12">
         <f t="shared" si="0"/>
-        <v>0.17807644194495054</v>
+        <v>0.17137126279011827</v>
       </c>
       <c r="I4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>852</v>
+        <v>909</v>
       </c>
       <c r="J4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>790</v>
+        <v>806</v>
       </c>
       <c r="K4" s="12">
         <f t="shared" si="1"/>
-        <v>-7.2769953051643244E-2</v>
+        <v>-0.11331133113311331</v>
       </c>
       <c r="L4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1336,23 +1336,23 @@
       </c>
       <c r="P4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q4" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.14285714285714279</v>
       </c>
       <c r="R4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="S4">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="T4" s="12">
         <f t="shared" si="4"/>
-        <v>0.11695906432748537</v>
+        <v>0.11353711790393017</v>
       </c>
       <c r="U4">
         <v>4</v>
@@ -1376,27 +1376,27 @@
       </c>
       <c r="F5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>28310468.960497696</v>
+        <v>30428581.790787671</v>
       </c>
       <c r="G5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>29309668.523300178</v>
+        <v>31260783.726436041</v>
       </c>
       <c r="H5" s="12">
         <f t="shared" si="0"/>
-        <v>3.5294348680577903E-2</v>
+        <v>2.7349350073894163E-2</v>
       </c>
       <c r="I5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1378</v>
+        <v>1468</v>
       </c>
       <c r="J5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1107</v>
+        <v>1088</v>
       </c>
       <c r="K5" s="12">
         <f t="shared" si="1"/>
-        <v>-0.19666182873730043</v>
+        <v>-0.25885558583106272</v>
       </c>
       <c r="L5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1404,35 +1404,35 @@
       </c>
       <c r="M5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="2"/>
-        <v>0.33333333333333326</v>
+        <v>0</v>
       </c>
       <c r="O5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q5" s="12">
         <f t="shared" si="3"/>
-        <v>0.16666666666666674</v>
+        <v>0.14285714285714279</v>
       </c>
       <c r="R5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="S5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1204</v>
+        <v>1213</v>
       </c>
       <c r="T5" s="12">
         <f t="shared" si="4"/>
-        <v>1.8612521150592309E-2</v>
+        <v>2.4493243243243201E-2</v>
       </c>
       <c r="U5">
         <v>3</v>
@@ -1456,27 +1456,27 @@
       </c>
       <c r="F6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11757304.216271428</v>
+        <v>12572009.692979235</v>
       </c>
       <c r="G6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13279203.146268772</v>
+        <v>14087321.867469653</v>
       </c>
       <c r="H6" s="12">
         <f t="shared" si="0"/>
-        <v>0.12944284693179275</v>
+        <v>0.12053062410034854</v>
       </c>
       <c r="I6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="J6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="K6" s="12">
         <f t="shared" si="1"/>
-        <v>-7.5949367088607556E-2</v>
+        <v>-2.6041666666666297E-3</v>
       </c>
       <c r="L6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1504,15 +1504,15 @@
       </c>
       <c r="R6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="S6">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="T6" s="12">
         <f t="shared" si="4"/>
-        <v>-1.2106537530266359E-2</v>
+        <v>-2.3980815347721673E-3</v>
       </c>
       <c r="U6">
         <v>3</v>
@@ -1536,27 +1536,27 @@
       </c>
       <c r="F7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10339799.678089332</v>
+        <v>10954941.459135331</v>
       </c>
       <c r="G7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>10850637.181308759</v>
+        <v>11489847.967613995</v>
       </c>
       <c r="H7" s="12">
         <f t="shared" si="0"/>
-        <v>4.9404970997835029E-2</v>
+        <v>4.8827874660398507E-2</v>
       </c>
       <c r="I7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="J7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="K7" s="12">
         <f t="shared" si="1"/>
-        <v>-0.18413597733711051</v>
+        <v>-0.17159763313609466</v>
       </c>
       <c r="L7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="R7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="S7">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="T7" s="12">
         <f t="shared" si="4"/>
-        <v>3.2085561497326109E-2</v>
+        <v>1.846965699208436E-2</v>
       </c>
       <c r="U7">
         <v>2</v>
@@ -1616,27 +1616,27 @@
       </c>
       <c r="F8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11840920.056150315</v>
+        <v>12590405.038448486</v>
       </c>
       <c r="G8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13055381.858272109</v>
+        <v>13775550.668594858</v>
       </c>
       <c r="H8" s="12">
         <f t="shared" si="0"/>
-        <v>0.10256481729145595</v>
+        <v>9.4130858104022996E-2</v>
       </c>
       <c r="I8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="J8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>525</v>
+        <v>488</v>
       </c>
       <c r="K8" s="12">
         <f t="shared" si="1"/>
-        <v>0.12179487179487181</v>
+        <v>5.3995680345572339E-2</v>
       </c>
       <c r="L8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1656,23 +1656,23 @@
       </c>
       <c r="P8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q8" s="12">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="S8">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="T8" s="12">
         <f t="shared" si="4"/>
-        <v>-3.3500837520937798E-3</v>
+        <v>0</v>
       </c>
       <c r="U8">
         <v>9</v>
@@ -1696,27 +1696,27 @@
       </c>
       <c r="F9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5538273.8270198824</v>
+        <v>5908394.1481695939</v>
       </c>
       <c r="G9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5740248.3143004626</v>
+        <v>6045648.5828848016</v>
       </c>
       <c r="H9" s="12">
         <f t="shared" si="0"/>
-        <v>3.6468851773849842E-2</v>
+        <v>2.3230412743829643E-2</v>
       </c>
       <c r="I9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>146</v>
+        <v>385</v>
       </c>
       <c r="J9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="K9" s="12">
         <f t="shared" si="1"/>
-        <v>-6.8493150684931559E-2</v>
+        <v>-0.65454545454545454</v>
       </c>
       <c r="L9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1748,11 +1748,11 @@
       </c>
       <c r="S9">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="T9" s="12">
         <f t="shared" si="4"/>
-        <v>-5.8479532163743242E-3</v>
+        <v>2.3391812865497075E-2</v>
       </c>
       <c r="U9">
         <v>1</v>
@@ -1776,27 +1776,27 @@
       </c>
       <c r="F10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5377723.235344599</v>
+        <v>5680298.6802293016</v>
       </c>
       <c r="G10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>2513527.1167136971</v>
+        <v>2860659.9967147</v>
       </c>
       <c r="H10" s="12">
         <f t="shared" si="0"/>
-        <v>-0.53260385357993734</v>
+        <v>-0.49638915878289325</v>
       </c>
       <c r="I10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>157</v>
+        <v>226</v>
       </c>
       <c r="J10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="K10" s="12">
         <f t="shared" si="1"/>
-        <v>9.5541401273885329E-2</v>
+        <v>-0.22123893805309736</v>
       </c>
       <c r="L10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1824,15 +1824,15 @@
       </c>
       <c r="R10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="S10">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="T10" s="12">
         <f t="shared" si="4"/>
-        <v>-6.0606060606060552E-2</v>
+        <v>-4.1025641025640991E-2</v>
       </c>
       <c r="U10">
         <v>1</v>
@@ -1856,27 +1856,27 @@
       </c>
       <c r="F11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8449767.6351467129</v>
+        <v>8944383.1211307161</v>
       </c>
       <c r="G11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11274051.916730504</v>
+        <v>11890504.003905904</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" si="0"/>
-        <v>0.33424401753205779</v>
+        <v>0.32938223272380918</v>
       </c>
       <c r="I11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="J11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="K11" s="12">
         <f t="shared" si="1"/>
-        <v>8.4033613445377853E-3</v>
+        <v>-7.7127659574468099E-2</v>
       </c>
       <c r="L11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="R11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="S11">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="T11" s="12">
         <f t="shared" si="4"/>
-        <v>0.11403508771929816</v>
+        <v>0.12058823529411766</v>
       </c>
       <c r="U11">
         <v>4</v>
@@ -1936,27 +1936,27 @@
       </c>
       <c r="F12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4041060.1390938722</v>
+        <v>4262490.9429104608</v>
       </c>
       <c r="G12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5806029.4254871206</v>
+        <v>6152814.3065978391</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="0"/>
-        <v>0.43675897552690413</v>
+        <v>0.44347856429617449</v>
       </c>
       <c r="I12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="J12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="K12" s="12">
         <f t="shared" si="1"/>
-        <v>0.17105263157894735</v>
+        <v>8.6776859504132275E-2</v>
       </c>
       <c r="L12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1984,15 +1984,15 @@
       </c>
       <c r="R12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="S12">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="T12" s="12">
         <f t="shared" si="4"/>
-        <v>4.7619047619047672E-2</v>
+        <v>5.1886792452830122E-2</v>
       </c>
       <c r="U12">
         <v>3</v>
@@ -2016,19 +2016,19 @@
       </c>
       <c r="F13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5431815.5109380577</v>
+        <v>5733341.8539821506</v>
       </c>
       <c r="G13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6161717.6329658534</v>
+        <v>6544098.7908061044</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="0"/>
-        <v>0.13437535213741891</v>
+        <v>0.14141088347293196</v>
       </c>
       <c r="I13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="J13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="K13" s="12">
         <f t="shared" si="1"/>
-        <v>4.5662100456621113E-2</v>
+        <v>2.6905829596412634E-2</v>
       </c>
       <c r="L13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2044,11 +2044,11 @@
       </c>
       <c r="M13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N13" s="12">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2056,23 +2056,23 @@
       </c>
       <c r="P13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q13" s="12">
         <f t="shared" si="3"/>
-        <v>-0.85714285714285721</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="R13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="S13">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="T13" s="12">
         <f t="shared" si="4"/>
-        <v>-5.1181102362204745E-2</v>
+        <v>-4.0000000000000036E-2</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -2096,27 +2096,27 @@
       </c>
       <c r="F14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10793808.574127875</v>
+        <v>12150068.330912439</v>
       </c>
       <c r="G14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>25119200.515578978</v>
+        <v>27129953.922294252</v>
       </c>
       <c r="H14" s="12">
         <f t="shared" si="0"/>
-        <v>1.3271860292008721</v>
+        <v>1.2329054605618719</v>
       </c>
       <c r="I14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1258</v>
+        <v>1062</v>
       </c>
       <c r="J14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1101</v>
+        <v>1064</v>
       </c>
       <c r="K14" s="12">
         <f t="shared" si="1"/>
-        <v>-0.12480127186009538</v>
+        <v>1.8832391713747842E-3</v>
       </c>
       <c r="L14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2144,15 +2144,15 @@
       </c>
       <c r="R14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="S14">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1428</v>
+        <v>1403</v>
       </c>
       <c r="T14" s="12">
         <f t="shared" si="4"/>
-        <v>7.0077084793274125E-4</v>
+        <v>-1.6129032258064502E-2</v>
       </c>
       <c r="U14">
         <v>3</v>
@@ -2176,27 +2176,27 @@
       </c>
       <c r="F15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>36194509.831490748</v>
+        <v>37115893.490185946</v>
       </c>
       <c r="G15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>43111493.808943726</v>
+        <v>46248297.021251909</v>
       </c>
       <c r="H15" s="12">
         <f t="shared" si="0"/>
-        <v>0.19110588897752967</v>
+        <v>0.2460510221444816</v>
       </c>
       <c r="I15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>258</v>
+        <v>1018</v>
       </c>
       <c r="J15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>895</v>
+        <v>913</v>
       </c>
       <c r="K15" s="12">
         <f t="shared" si="1"/>
-        <v>2.4689922480620154</v>
+        <v>-0.10314341846758346</v>
       </c>
       <c r="L15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -2220,19 +2220,19 @@
       </c>
       <c r="Q15" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1278</v>
+        <v>1271</v>
       </c>
       <c r="S15">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="T15" s="12">
         <f t="shared" si="4"/>
-        <v>-3.3646322378716786E-2</v>
+        <v>-3.3044846577498066E-2</v>
       </c>
       <c r="U15">
         <v>4</v>
@@ -2256,27 +2256,27 @@
       </c>
       <c r="F16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>23300861.495705463</v>
+        <v>24557779.647644848</v>
       </c>
       <c r="G16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23318745.82605692</v>
+        <v>24780324.33078628</v>
       </c>
       <c r="H16" s="12">
         <f t="shared" si="0"/>
-        <v>7.6753944718976896E-4</v>
+        <v>9.062084860052666E-3</v>
       </c>
       <c r="I16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="J16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>894</v>
+        <v>945</v>
       </c>
       <c r="K16" s="12">
         <f t="shared" si="1"/>
-        <v>-2.2321428571429047E-3</v>
+        <v>5.7046979865771785E-2</v>
       </c>
       <c r="L16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2304,15 +2304,15 @@
       </c>
       <c r="R16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="S16">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="T16" s="12">
         <f t="shared" si="4"/>
-        <v>5.8708414872798986E-3</v>
+        <v>3.9177277179236469E-3</v>
       </c>
       <c r="U16">
         <v>4</v>
@@ -2336,27 +2336,27 @@
       </c>
       <c r="F17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>22855372.760754973</v>
+        <v>24093521.100269504</v>
       </c>
       <c r="G17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18884057.695519928</v>
+        <v>20292128.333114807</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="0"/>
-        <v>-0.17375849025985701</v>
+        <v>-0.15777655542062619</v>
       </c>
       <c r="I17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>665</v>
+        <v>651</v>
       </c>
       <c r="J17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="K17" s="12">
         <f t="shared" si="1"/>
-        <v>4.6616541353383445E-2</v>
+        <v>7.3732718894009119E-2</v>
       </c>
       <c r="L17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2384,15 +2384,15 @@
       </c>
       <c r="R17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="S17">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="T17" s="12">
         <f t="shared" si="4"/>
-        <v>-4.9792531120331995E-2</v>
+        <v>-4.166666666666663E-2</v>
       </c>
       <c r="U17">
         <v>4</v>
@@ -2416,27 +2416,27 @@
       </c>
       <c r="F18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>79706464.844519541</v>
+        <v>84378043.245911941</v>
       </c>
       <c r="G18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>86512250.853451744</v>
+        <v>91431790.086039543</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="0"/>
-        <v>8.5385621131334855E-2</v>
+        <v>8.3596947366628482E-2</v>
       </c>
       <c r="I18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2875</v>
+        <v>2911</v>
       </c>
       <c r="J18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2092</v>
+        <v>2167</v>
       </c>
       <c r="K18" s="12">
         <f t="shared" si="1"/>
-        <v>-0.27234782608695651</v>
+        <v>-0.25558227413260048</v>
       </c>
       <c r="L18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2456,23 +2456,23 @@
       </c>
       <c r="P18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q18" s="12">
         <f t="shared" si="3"/>
-        <v>-0.70993589743589736</v>
+        <v>-0.70512820512820507</v>
       </c>
       <c r="R18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>3231</v>
+        <v>3219</v>
       </c>
       <c r="S18">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2813</v>
+        <v>2805</v>
       </c>
       <c r="T18" s="12">
         <f t="shared" si="4"/>
-        <v>-0.12937171154441351</v>
+        <v>-0.12861136999068035</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -2496,27 +2496,27 @@
       </c>
       <c r="F19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>43461261.025939107</v>
+        <v>45853440.719571456</v>
       </c>
       <c r="G19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>25993637.843131464</v>
+        <v>28580704.230768949</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="0"/>
-        <v>-0.40191247953855713</v>
+        <v>-0.3766944468668858</v>
       </c>
       <c r="I19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1188</v>
+        <v>1155</v>
       </c>
       <c r="J19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1167</v>
+        <v>1192</v>
       </c>
       <c r="K19" s="12">
         <f t="shared" si="1"/>
-        <v>-1.7676767676767624E-2</v>
+        <v>3.2034632034632082E-2</v>
       </c>
       <c r="L19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2524,11 +2524,11 @@
       </c>
       <c r="M19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N19" s="12">
         <f t="shared" si="2"/>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="O19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="P19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q19" s="12">
         <f t="shared" si="3"/>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="R19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1443</v>
+        <v>1440</v>
       </c>
       <c r="S19">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="T19" s="12">
         <f t="shared" si="4"/>
-        <v>-4.2966042966043005E-2</v>
+        <v>-4.0972222222222188E-2</v>
       </c>
       <c r="U19">
         <v>1</v>
@@ -2576,27 +2576,27 @@
       </c>
       <c r="F20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>87326341.867069647</v>
+        <v>91985409.680114254</v>
       </c>
       <c r="G20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>87531836.582215488</v>
+        <v>91798677.850888729</v>
       </c>
       <c r="H20" s="12">
         <f t="shared" si="0"/>
-        <v>2.3531813053458972E-3</v>
+        <v>-2.0300157370054528E-3</v>
       </c>
       <c r="I20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2522</v>
+        <v>2274</v>
       </c>
       <c r="J20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2002</v>
+        <v>1971</v>
       </c>
       <c r="K20" s="12">
         <f t="shared" si="1"/>
-        <v>-0.20618556701030932</v>
+        <v>-0.13324538258575203</v>
       </c>
       <c r="L20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2616,11 +2616,11 @@
       </c>
       <c r="P20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q20" s="12">
         <f t="shared" si="3"/>
-        <v>0.19999999999999996</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="R20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -2628,11 +2628,11 @@
       </c>
       <c r="S20">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2936</v>
+        <v>2933</v>
       </c>
       <c r="T20" s="12">
         <f t="shared" si="4"/>
-        <v>-2.393617021276595E-2</v>
+        <v>-2.4933510638297851E-2</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2656,27 +2656,27 @@
       </c>
       <c r="F21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12335831.009248348</v>
+        <v>13083985.836379612</v>
       </c>
       <c r="G21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13179743.144659448</v>
+        <v>13952390.293539824</v>
       </c>
       <c r="H21" s="12">
         <f t="shared" si="0"/>
-        <v>6.8411453981366055E-2</v>
+        <v>6.6371552829539215E-2</v>
       </c>
       <c r="I21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="K21" s="12">
         <f t="shared" si="1"/>
-        <v>5.0108932461873534E-2</v>
+        <v>5.8695652173913038E-2</v>
       </c>
       <c r="L21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2704,15 +2704,15 @@
       </c>
       <c r="R21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="S21">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="T21" s="12">
         <f t="shared" si="4"/>
-        <v>-3.6166365280289381E-2</v>
+        <v>-2.5408348457350294E-2</v>
       </c>
       <c r="U21">
         <v>1</v>
@@ -2736,27 +2736,27 @@
       </c>
       <c r="F22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>34331182.277683817</v>
+        <v>36202793.63631741</v>
       </c>
       <c r="G22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>36181572.167494185</v>
+        <v>38550165.164171152</v>
       </c>
       <c r="H22" s="12">
         <f t="shared" si="0"/>
-        <v>5.3898227997035031E-2</v>
+        <v>6.4839513531324222E-2</v>
       </c>
       <c r="I22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1319</v>
+        <v>1256</v>
       </c>
       <c r="J22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1381</v>
+        <v>1368</v>
       </c>
       <c r="K22" s="12">
         <f t="shared" si="1"/>
-        <v>4.7005307050796086E-2</v>
+        <v>8.9171974522292974E-2</v>
       </c>
       <c r="L22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="O22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -2780,19 +2780,19 @@
       </c>
       <c r="Q22" s="12">
         <f t="shared" si="3"/>
-        <v>0.41666666666666674</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="R22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="S22">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1698</v>
+        <v>1679</v>
       </c>
       <c r="T22" s="12">
         <f t="shared" si="4"/>
-        <v>-6.4365125804564105E-3</v>
+        <v>-1.6403046280023426E-2</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2816,27 +2816,27 @@
       </c>
       <c r="F23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15055659.969758572</v>
+        <v>15994034.782365471</v>
       </c>
       <c r="G23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15017516.666063774</v>
+        <v>16023991.278544333</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="0"/>
-        <v>-2.5334859960581824E-3</v>
+        <v>1.8729793067531197E-3</v>
       </c>
       <c r="I23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>800</v>
+        <v>1010</v>
       </c>
       <c r="J23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>867</v>
+        <v>820</v>
       </c>
       <c r="K23" s="12">
         <f t="shared" si="1"/>
-        <v>8.3749999999999991E-2</v>
+        <v>-0.18811881188118806</v>
       </c>
       <c r="L23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2864,15 +2864,15 @@
       </c>
       <c r="R23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="S23">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="T23" s="12">
         <f t="shared" si="4"/>
-        <v>1.7421602787456525E-2</v>
+        <v>1.9721577726218076E-2</v>
       </c>
       <c r="U23">
         <v>1</v>
@@ -2896,27 +2896,27 @@
       </c>
       <c r="F24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16806306.479511511</v>
+        <v>17730094.775826979</v>
       </c>
       <c r="G24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18339133.799450003</v>
+        <v>19429198.640231583</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="0"/>
-        <v>9.1205484191732022E-2</v>
+        <v>9.5831628983796824E-2</v>
       </c>
       <c r="I24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>656</v>
+        <v>803</v>
       </c>
       <c r="J24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>759</v>
+        <v>843</v>
       </c>
       <c r="K24" s="12">
         <f t="shared" si="1"/>
-        <v>0.15701219512195119</v>
+        <v>4.9813200498131982E-2</v>
       </c>
       <c r="L24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2936,23 +2936,23 @@
       </c>
       <c r="P24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q24" s="12">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="S24">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="T24" s="12">
         <f t="shared" si="4"/>
-        <v>-2.015677491601342E-2</v>
+        <v>-1.3544018058690765E-2</v>
       </c>
       <c r="U24">
         <v>3</v>
@@ -2976,27 +2976,27 @@
       </c>
       <c r="F25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4978274.1542370617</v>
+        <v>5277024.5563090751</v>
       </c>
       <c r="G25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4145553.8044927949</v>
+        <v>4433708.8725122856</v>
       </c>
       <c r="H25" s="12">
         <f t="shared" si="0"/>
-        <v>-0.16727089026134279</v>
+        <v>-0.15980893679726071</v>
       </c>
       <c r="I25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="K25" s="12">
         <f t="shared" si="1"/>
-        <v>3.2258064516129004E-2</v>
+        <v>1.1428571428571344E-2</v>
       </c>
       <c r="L25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="M25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N25" s="12">
         <f t="shared" si="2"/>
@@ -3056,27 +3056,27 @@
       </c>
       <c r="F26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>38180141.640637457</v>
+        <v>40235450.07087151</v>
       </c>
       <c r="G26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>34673357.838432036</v>
+        <v>36803930.469524823</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="0"/>
-        <v>-9.184837068474716E-2</v>
+        <v>-8.5285975310387729E-2</v>
       </c>
       <c r="I26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1327</v>
+        <v>1301</v>
       </c>
       <c r="J26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="K26" s="12">
         <f t="shared" si="1"/>
-        <v>4.2954031650339175E-2</v>
+        <v>6.3028439661798608E-2</v>
       </c>
       <c r="L26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3104,15 +3104,15 @@
       </c>
       <c r="R26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="S26">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1653</v>
+        <v>1646</v>
       </c>
       <c r="T26" s="12">
         <f t="shared" si="4"/>
-        <v>-2.4140012070006378E-3</v>
+        <v>-7.2376357056694873E-3</v>
       </c>
       <c r="U26">
         <v>1</v>
@@ -3136,27 +3136,27 @@
       </c>
       <c r="F27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>26798065.721356105</v>
+        <v>28301686.739777543</v>
       </c>
       <c r="G27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>28932948.270447984</v>
+        <v>30880741.730442863</v>
       </c>
       <c r="H27" s="12">
         <f t="shared" si="0"/>
-        <v>7.9665546434962708E-2</v>
+        <v>9.1127253805707076E-2</v>
       </c>
       <c r="I27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="J27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>695</v>
+        <v>617</v>
       </c>
       <c r="K27" s="12">
         <f t="shared" si="1"/>
-        <v>0.12096774193548376</v>
+        <v>-8.0385852090032461E-3</v>
       </c>
       <c r="L27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3176,23 +3176,23 @@
       </c>
       <c r="P27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q27" s="12">
         <f t="shared" si="3"/>
-        <v>-0.4</v>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="R27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="S27">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>876</v>
+        <v>884</v>
       </c>
       <c r="T27" s="12">
         <f t="shared" si="4"/>
-        <v>2.0979020979021046E-2</v>
+        <v>2.9103608847497187E-2</v>
       </c>
       <c r="U27">
         <v>1</v>
@@ -3216,27 +3216,27 @@
       </c>
       <c r="F28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>28967105.315619867</v>
+        <v>30771914.979088616</v>
       </c>
       <c r="G28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>27314154.578593209</v>
+        <v>29013524.004899658</v>
       </c>
       <c r="H28" s="12">
         <f t="shared" si="0"/>
-        <v>-5.7063027838523461E-2</v>
+        <v>-5.7142721711791133E-2</v>
       </c>
       <c r="I28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="J28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>623</v>
+        <v>789</v>
       </c>
       <c r="K28" s="12">
         <f t="shared" si="1"/>
-        <v>-0.1770145310435931</v>
+        <v>3.1372549019607954E-2</v>
       </c>
       <c r="L28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3264,15 +3264,15 @@
       </c>
       <c r="R28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="S28">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="T28" s="12">
         <f t="shared" si="4"/>
-        <v>-7.3646850044365553E-2</v>
+        <v>-7.4600355239786809E-2</v>
       </c>
       <c r="U28">
         <v>1</v>
@@ -3296,27 +3296,27 @@
       </c>
       <c r="F29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>37440462.056698211</v>
+        <v>39627788.142400511</v>
       </c>
       <c r="G29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>38738095.034786858</v>
+        <v>41174058.474659473</v>
       </c>
       <c r="H29" s="12">
         <f t="shared" si="0"/>
-        <v>3.4658572752749972E-2</v>
+        <v>3.901984957380189E-2</v>
       </c>
       <c r="I29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="J29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1017</v>
+        <v>874</v>
       </c>
       <c r="K29" s="12">
         <f t="shared" si="1"/>
-        <v>0.14141414141414144</v>
+        <v>-1.6872890888638969E-2</v>
       </c>
       <c r="L29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="O29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3340,19 +3340,19 @@
       </c>
       <c r="Q29" s="12">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="R29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="S29">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1120</v>
+        <v>1125</v>
       </c>
       <c r="T29" s="12">
         <f t="shared" si="4"/>
-        <v>-6.2111801242236142E-3</v>
+        <v>-4.4247787610619538E-3</v>
       </c>
       <c r="U29">
         <v>1</v>
@@ -3376,27 +3376,27 @@
       </c>
       <c r="F30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>54625541.40816319</v>
+        <v>57867671.527397662</v>
       </c>
       <c r="G30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>49689744.933685243</v>
+        <v>52940271.569831714</v>
       </c>
       <c r="H30" s="12">
         <f t="shared" si="0"/>
-        <v>-9.0356934636081188E-2</v>
+        <v>-8.5149442296689859E-2</v>
       </c>
       <c r="I30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1170</v>
+        <v>1103</v>
       </c>
       <c r="J30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1153</v>
+        <v>1132</v>
       </c>
       <c r="K30" s="12">
         <f t="shared" si="1"/>
-        <v>-1.4529914529914478E-2</v>
+        <v>2.6291931097008225E-2</v>
       </c>
       <c r="L30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="O30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3420,19 +3420,19 @@
       </c>
       <c r="Q30" s="12">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="R30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1500</v>
+        <v>1503</v>
       </c>
       <c r="S30">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="T30" s="12">
         <f t="shared" si="4"/>
-        <v>-3.6666666666666625E-2</v>
+        <v>-3.9920159680638667E-2</v>
       </c>
       <c r="U30">
         <v>4</v>
@@ -3456,27 +3456,27 @@
       </c>
       <c r="F31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20563796.033259295</v>
+        <v>21899406.198145673</v>
       </c>
       <c r="G31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22475660.079455785</v>
+        <v>23896792.324472841</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="0"/>
-        <v>9.2972330745952458E-2</v>
+        <v>9.1207318968141493E-2</v>
       </c>
       <c r="I31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>546</v>
+        <v>535</v>
       </c>
       <c r="J31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>657</v>
+        <v>554</v>
       </c>
       <c r="K31" s="12">
         <f t="shared" si="1"/>
-        <v>0.20329670329670324</v>
+        <v>3.5514018691588767E-2</v>
       </c>
       <c r="L31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="O31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3500,19 +3500,19 @@
       </c>
       <c r="Q31" s="12">
         <f t="shared" si="3"/>
-        <v>-0.5</v>
+        <v>-0.66666666666666674</v>
       </c>
       <c r="R31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="S31">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="T31" s="12">
         <f t="shared" si="4"/>
-        <v>8.6705202312138407E-3</v>
+        <v>1.4471780028943559E-2</v>
       </c>
       <c r="U31">
         <v>3</v>
@@ -3536,27 +3536,27 @@
       </c>
       <c r="F32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>64619883.099481747</v>
+        <v>68379291.574158043</v>
       </c>
       <c r="G32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>54641880.595996283</v>
+        <v>58685299.940138116</v>
       </c>
       <c r="H32" s="12">
         <f t="shared" si="0"/>
-        <v>-0.15441071733485523</v>
+        <v>-0.14176794480982147</v>
       </c>
       <c r="I32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1942</v>
+        <v>1890</v>
       </c>
       <c r="J32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1597</v>
+        <v>1575</v>
       </c>
       <c r="K32" s="12">
         <f t="shared" si="1"/>
-        <v>-0.17765190525231722</v>
+        <v>-0.16666666666666663</v>
       </c>
       <c r="L32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3572,27 +3572,27 @@
       </c>
       <c r="O32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q32" s="12">
         <f t="shared" si="3"/>
-        <v>-0.3571428571428571</v>
+        <v>-0.375</v>
       </c>
       <c r="R32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="S32">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1923</v>
+        <v>1926</v>
       </c>
       <c r="T32" s="12">
         <f t="shared" si="4"/>
-        <v>-2.385786802030454E-2</v>
+        <v>-2.1838496698831866E-2</v>
       </c>
       <c r="U32">
         <v>5</v>
@@ -3616,27 +3616,27 @@
       </c>
       <c r="F33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>22177650.670513704</v>
+        <v>23416239.072707906</v>
       </c>
       <c r="G33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22648991.031854369</v>
+        <v>23846332.143704496</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="0"/>
-        <v>2.1252943710910577E-2</v>
+        <v>1.8367299277272542E-2</v>
       </c>
       <c r="I33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>676</v>
+        <v>620</v>
       </c>
       <c r="J33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>699</v>
+        <v>712</v>
       </c>
       <c r="K33" s="12">
         <f t="shared" si="1"/>
-        <v>3.4023668639053151E-2</v>
+        <v>0.14838709677419359</v>
       </c>
       <c r="L33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3664,15 +3664,15 @@
       </c>
       <c r="R33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="S33">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="4"/>
-        <v>1.3002364066193817E-2</v>
+        <v>2.2538552787663146E-2</v>
       </c>
       <c r="U33">
         <v>3</v>
@@ -3696,27 +3696,27 @@
       </c>
       <c r="F34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18494684.231714644</v>
+        <v>19580984.263010703</v>
       </c>
       <c r="G34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20507947.028976176</v>
+        <v>21933834.462986201</v>
       </c>
       <c r="H34" s="12">
         <f t="shared" si="0"/>
-        <v>0.10885629470814062</v>
+        <v>0.12015995561674253</v>
       </c>
       <c r="I34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>550</v>
+        <v>534</v>
       </c>
       <c r="J34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>560</v>
+        <v>644</v>
       </c>
       <c r="K34" s="12">
         <f t="shared" si="1"/>
-        <v>1.8181818181818077E-2</v>
+        <v>0.20599250936329594</v>
       </c>
       <c r="L34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3744,15 +3744,15 @@
       </c>
       <c r="R34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="S34">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="T34" s="12">
         <f t="shared" si="4"/>
-        <v>7.6258992805755321E-2</v>
+        <v>8.0459770114942541E-2</v>
       </c>
       <c r="U34">
         <v>4</v>
@@ -3776,27 +3776,27 @@
       </c>
       <c r="F35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>32415149.402387757</v>
+        <v>34271546.343865938</v>
       </c>
       <c r="G35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>31697377.625365242</v>
+        <v>33947334.926795498</v>
       </c>
       <c r="H35" s="12">
         <f t="shared" si="0"/>
-        <v>-2.2143096368688719E-2</v>
+        <v>-9.4600755337224118E-3</v>
       </c>
       <c r="I35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>879</v>
+        <v>843</v>
       </c>
       <c r="J35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>849</v>
+        <v>950</v>
       </c>
       <c r="K35" s="12">
         <f t="shared" si="1"/>
-        <v>-3.4129692832764458E-2</v>
+        <v>0.12692763938315532</v>
       </c>
       <c r="L35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="O35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3820,19 +3820,19 @@
       </c>
       <c r="Q35" s="12">
         <f t="shared" si="3"/>
-        <v>0.41666666666666674</v>
+        <v>0.21428571428571419</v>
       </c>
       <c r="R35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="S35">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1162</v>
+        <v>1148</v>
       </c>
       <c r="T35" s="12">
         <f t="shared" si="4"/>
-        <v>4.496402877697836E-2</v>
+        <v>3.1446540880503138E-2</v>
       </c>
       <c r="U35">
         <v>13</v>
@@ -3856,27 +3856,27 @@
       </c>
       <c r="F36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>31422622.587050565</v>
+        <v>33052464.113899976</v>
       </c>
       <c r="G36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>29999625.405255064</v>
+        <v>32190582.015026674</v>
       </c>
       <c r="H36" s="12">
         <f t="shared" si="0"/>
-        <v>-4.5285754804626821E-2</v>
+        <v>-2.6076182880139465E-2</v>
       </c>
       <c r="I36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>749</v>
+        <v>769</v>
       </c>
       <c r="J36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>880</v>
+        <v>964</v>
       </c>
       <c r="K36" s="12">
         <f t="shared" si="1"/>
-        <v>0.17489986648865163</v>
+        <v>0.25357607282184658</v>
       </c>
       <c r="L36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3904,15 +3904,15 @@
       </c>
       <c r="R36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1098</v>
+        <v>1089</v>
       </c>
       <c r="S36">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1271</v>
+        <v>1252</v>
       </c>
       <c r="T36" s="12">
         <f t="shared" si="4"/>
-        <v>0.15755919854280509</v>
+        <v>0.14967860422405876</v>
       </c>
       <c r="U36">
         <v>4</v>
@@ -3936,27 +3936,27 @@
       </c>
       <c r="F37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>49380423.194518387</v>
+        <v>52158232.747112714</v>
       </c>
       <c r="G37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>54072727.66768647</v>
+        <v>57989157.172912218</v>
       </c>
       <c r="H37" s="12">
         <f t="shared" si="0"/>
-        <v>9.5023577555912286E-2</v>
+        <v>0.11179298298066431</v>
       </c>
       <c r="I37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1328</v>
+        <v>1371</v>
       </c>
       <c r="J37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1420</v>
+        <v>1578</v>
       </c>
       <c r="K37" s="12">
         <f t="shared" si="1"/>
-        <v>6.9277108433734913E-2</v>
+        <v>0.15098468271334786</v>
       </c>
       <c r="L37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3976,23 +3976,23 @@
       </c>
       <c r="P37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="Q37" s="12">
         <f t="shared" si="3"/>
-        <v>0.27272727272727271</v>
+        <v>0.32727272727272738</v>
       </c>
       <c r="R37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="S37">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2274</v>
+        <v>2269</v>
       </c>
       <c r="T37" s="12">
         <f t="shared" si="4"/>
-        <v>0.27896512935883022</v>
+        <v>0.27186098654708513</v>
       </c>
       <c r="U37">
         <v>16</v>
@@ -4016,31 +4016,31 @@
       </c>
       <c r="F38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17501175.169462778</v>
+        <v>17501175.59762124</v>
       </c>
       <c r="G38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19553902.07009979</v>
+        <v>20656820.414189544</v>
       </c>
       <c r="H38" s="12">
         <f t="shared" si="0"/>
-        <v>0.11729080366093059</v>
+        <v>0.18031044823053022</v>
       </c>
       <c r="I38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="K38" s="12">
         <f t="shared" si="1"/>
-        <v>35.92307692307692</v>
+        <v>58</v>
       </c>
       <c r="L38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="N38" s="12">
         <f t="shared" si="2"/>
-        <v>0.19999999999999996</v>
+        <v>0.5</v>
       </c>
       <c r="O38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4064,15 +4064,15 @@
       </c>
       <c r="R38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="S38">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="T38" s="12">
         <f t="shared" si="4"/>
-        <v>6.482982171799101E-3</v>
+        <v>8.1566068515497303E-3</v>
       </c>
       <c r="U38">
         <v>3</v>
@@ -4096,27 +4096,27 @@
       </c>
       <c r="F39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>58094258.463035837</v>
+        <v>61288523.598765254</v>
       </c>
       <c r="G39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>62788078.791813053</v>
+        <v>66763112.972614646</v>
       </c>
       <c r="H39" s="12">
         <f t="shared" si="0"/>
-        <v>8.07966303892802E-2</v>
+        <v>8.9324869525159833E-2</v>
       </c>
       <c r="I39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1885</v>
+        <v>1869</v>
       </c>
       <c r="J39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1899</v>
+        <v>1991</v>
       </c>
       <c r="K39" s="12">
         <f t="shared" si="1"/>
-        <v>7.4270557029176842E-3</v>
+        <v>6.527554842161587E-2</v>
       </c>
       <c r="L39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4132,27 +4132,27 @@
       </c>
       <c r="O39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="P39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q39" s="12">
         <f t="shared" si="3"/>
-        <v>-0.19999999999999996</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="R39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2026</v>
+        <v>2036</v>
       </c>
       <c r="S39">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2052</v>
+        <v>2059</v>
       </c>
       <c r="T39" s="12">
         <f t="shared" si="4"/>
-        <v>1.2833168805528095E-2</v>
+        <v>1.129666011787811E-2</v>
       </c>
       <c r="U39">
         <v>4</v>
@@ -4176,27 +4176,27 @@
       </c>
       <c r="F40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>40259525.860920064</v>
+        <v>42805016.573299475</v>
       </c>
       <c r="G40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>43702130.166758053</v>
+        <v>46227650.783002853</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" si="0"/>
-        <v>8.5510304262667036E-2</v>
+        <v>7.9958717077995844E-2</v>
       </c>
       <c r="I40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>823</v>
+        <v>760</v>
       </c>
       <c r="J40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>849</v>
+        <v>797</v>
       </c>
       <c r="K40" s="12">
         <f t="shared" si="1"/>
-        <v>3.1591737545564991E-2</v>
+        <v>4.8684210526315885E-2</v>
       </c>
       <c r="L40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4216,23 +4216,23 @@
       </c>
       <c r="P40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q40" s="12">
         <f t="shared" si="3"/>
-        <v>-0.5</v>
+        <v>-0.16666666666666663</v>
       </c>
       <c r="R40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="S40">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="T40" s="12">
         <f t="shared" si="4"/>
-        <v>2.5114155251141579E-2</v>
+        <v>2.0524515393386622E-2</v>
       </c>
       <c r="U40">
         <v>3</v>
@@ -4256,27 +4256,27 @@
       </c>
       <c r="F41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>33706233.502371065</v>
+        <v>35305267.70624648</v>
       </c>
       <c r="G41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>25153289.147385843</v>
+        <v>27034432.239690185</v>
       </c>
       <c r="H41" s="12">
         <f t="shared" si="0"/>
-        <v>-0.25374963222703495</v>
+        <v>-0.23426632918840484</v>
       </c>
       <c r="I41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>932</v>
+        <v>996</v>
       </c>
       <c r="J41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1095</v>
+        <v>1158</v>
       </c>
       <c r="K41" s="12">
         <f t="shared" si="1"/>
-        <v>0.17489270386266087</v>
+        <v>0.16265060240963858</v>
       </c>
       <c r="L41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4296,15 +4296,15 @@
       </c>
       <c r="P41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q41" s="12">
         <f t="shared" si="3"/>
-        <v>0.66666666666666674</v>
+        <v>1</v>
       </c>
       <c r="R41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1123</v>
+        <v>1116</v>
       </c>
       <c r="S41">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="T41" s="12">
         <f t="shared" si="4"/>
-        <v>-2.315227070347281E-2</v>
+        <v>-1.7025089605734789E-2</v>
       </c>
       <c r="U41">
         <v>4</v>
@@ -4336,27 +4336,27 @@
       </c>
       <c r="F42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>32761795.611114733</v>
+        <v>34656045.854344085</v>
       </c>
       <c r="G42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>32727427.435014695</v>
+        <v>34623144.718677483</v>
       </c>
       <c r="H42" s="12">
         <f t="shared" si="0"/>
-        <v>-1.049032125955196E-3</v>
+        <v>-9.4936207681861617E-4</v>
       </c>
       <c r="I42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>623</v>
+        <v>636</v>
       </c>
       <c r="J42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>573</v>
+        <v>612</v>
       </c>
       <c r="K42" s="12">
         <f t="shared" si="1"/>
-        <v>-8.0256821829855496E-2</v>
+        <v>-3.7735849056603765E-2</v>
       </c>
       <c r="L42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4384,15 +4384,15 @@
       </c>
       <c r="R42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="S42">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="T42" s="12">
         <f t="shared" si="4"/>
-        <v>-4.0462427745664775E-2</v>
+        <v>-2.5670945157526215E-2</v>
       </c>
       <c r="U42">
         <v>2</v>
@@ -4416,27 +4416,27 @@
       </c>
       <c r="F43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20342697.235315848</v>
+        <v>21610464.703248747</v>
       </c>
       <c r="G43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21247499.714460559</v>
+        <v>21742784.05233898</v>
       </c>
       <c r="H43" s="12">
         <f t="shared" si="0"/>
-        <v>4.4477999582765992E-2</v>
+        <v>6.1229293727469436E-3</v>
       </c>
       <c r="I43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>607</v>
+        <v>570</v>
       </c>
       <c r="J43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>671</v>
+        <v>123</v>
       </c>
       <c r="K43" s="12">
         <f t="shared" si="1"/>
-        <v>0.10543657331136735</v>
+        <v>-0.78421052631578947</v>
       </c>
       <c r="L43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4444,11 +4444,11 @@
       </c>
       <c r="M43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N43" s="12">
         <f t="shared" si="2"/>
-        <v>0.10000000000000009</v>
+        <v>0</v>
       </c>
       <c r="O43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4464,15 +4464,15 @@
       </c>
       <c r="R43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="S43">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="T43" s="12">
         <f t="shared" si="4"/>
-        <v>5.5722891566265087E-2</v>
+        <v>5.1282051282051322E-2</v>
       </c>
       <c r="U43">
         <v>2</v>
@@ -4496,27 +4496,27 @@
       </c>
       <c r="F44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19467108.785032246</v>
+        <v>20687868.148741201</v>
       </c>
       <c r="G44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18175582.361618567</v>
+        <v>18652888.434304617</v>
       </c>
       <c r="H44" s="12">
         <f t="shared" si="0"/>
-        <v>-6.6344028672953193E-2</v>
+        <v>-9.8365848999303784E-2</v>
       </c>
       <c r="I44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>691</v>
+        <v>721</v>
       </c>
       <c r="J44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>732</v>
+        <v>389</v>
       </c>
       <c r="K44" s="12">
         <f t="shared" si="1"/>
-        <v>5.9334298118668638E-2</v>
+        <v>-0.46047156726768379</v>
       </c>
       <c r="L44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4544,15 +4544,15 @@
       </c>
       <c r="R44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="S44">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="T44" s="12">
         <f t="shared" si="4"/>
-        <v>-1.7094017094017144E-2</v>
+        <v>-2.6874115983026914E-2</v>
       </c>
       <c r="U44">
         <v>3</v>
@@ -4576,31 +4576,31 @@
       </c>
       <c r="F45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>62477023.740561083</v>
+        <v>65941089.434293799</v>
       </c>
       <c r="G45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>58038275.749017172</v>
+        <v>62024410.34365315</v>
       </c>
       <c r="H45" s="12">
         <f t="shared" si="0"/>
-        <v>-7.1046085837507711E-2</v>
+        <v>-5.9396639094708603E-2</v>
       </c>
       <c r="I45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1103</v>
+        <v>1085</v>
       </c>
       <c r="J45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1454</v>
+        <v>1418</v>
       </c>
       <c r="K45" s="12">
         <f t="shared" si="1"/>
-        <v>0.31822302810516767</v>
+        <v>0.30691244239631343</v>
       </c>
       <c r="L45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -4608,31 +4608,31 @@
       </c>
       <c r="N45" s="12">
         <f t="shared" si="2"/>
-        <v>-0.16666666666666663</v>
+        <v>0</v>
       </c>
       <c r="O45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q45" s="12">
         <f t="shared" si="3"/>
-        <v>-0.8</v>
+        <v>-0.72727272727272729</v>
       </c>
       <c r="R45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="S45">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1238</v>
+        <v>1243</v>
       </c>
       <c r="T45" s="12">
         <f t="shared" si="4"/>
-        <v>-3.5074045206547111E-2</v>
+        <v>-2.8146989835809211E-2</v>
       </c>
       <c r="U45">
         <v>5</v>
@@ -4656,27 +4656,27 @@
       </c>
       <c r="F46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>28184934.114670154</v>
+        <v>29718671.064681828</v>
       </c>
       <c r="G46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>27492791.124575771</v>
+        <v>29054377.526877664</v>
       </c>
       <c r="H46" s="12">
         <f t="shared" si="0"/>
-        <v>-2.4557197376385731E-2</v>
+        <v>-2.2352733618483445E-2</v>
       </c>
       <c r="I46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="J46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>939</v>
+        <v>931</v>
       </c>
       <c r="K46" s="12">
         <f t="shared" si="1"/>
-        <v>-9.493670886076E-3</v>
+        <v>-2.0000000000000018E-2</v>
       </c>
       <c r="L46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4684,11 +4684,11 @@
       </c>
       <c r="M46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N46" s="12">
         <f t="shared" si="2"/>
-        <v>0.39999999999999991</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="O46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4704,15 +4704,15 @@
       </c>
       <c r="R46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="S46">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="T46" s="12">
         <f t="shared" si="4"/>
-        <v>3.7628278221208733E-2</v>
+        <v>4.2093287827076331E-2</v>
       </c>
       <c r="U46">
         <v>4</v>
@@ -4736,27 +4736,27 @@
       </c>
       <c r="F47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>41289989.144723333</v>
+        <v>43797964.177689955</v>
       </c>
       <c r="G47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>47993219.130776621</v>
+        <v>50825033.960358381</v>
       </c>
       <c r="H47" s="12">
         <f t="shared" si="0"/>
-        <v>0.16234516222705109</v>
+        <v>0.16044284054298386</v>
       </c>
       <c r="I47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1003</v>
+        <v>979</v>
       </c>
       <c r="J47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>951</v>
+        <v>1023</v>
       </c>
       <c r="K47" s="12">
         <f t="shared" si="1"/>
-        <v>-5.1844466600199368E-2</v>
+        <v>4.4943820224719211E-2</v>
       </c>
       <c r="L47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="O47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4780,19 +4780,19 @@
       </c>
       <c r="Q47" s="12">
         <f t="shared" si="3"/>
-        <v>-0.61538461538461542</v>
+        <v>-0.66666666666666674</v>
       </c>
       <c r="R47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1306</v>
+        <v>1303</v>
       </c>
       <c r="S47">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="T47" s="12">
         <f t="shared" si="4"/>
-        <v>2.9862174578866751E-2</v>
+        <v>3.1465848042977695E-2</v>
       </c>
       <c r="U47">
         <v>6</v>
@@ -4816,27 +4816,27 @@
       </c>
       <c r="F48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21359608.09983848</v>
+        <v>22770248.911103602</v>
       </c>
       <c r="G48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>24793926.215664741</v>
+        <v>26152148.725233007</v>
       </c>
       <c r="H48" s="12">
         <f t="shared" si="0"/>
-        <v>0.1607856333212514</v>
+        <v>0.14852274243169417</v>
       </c>
       <c r="I48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="J48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="K48" s="12">
         <f t="shared" si="1"/>
-        <v>3.9325842696629199E-2</v>
+        <v>1.1173184357541999E-2</v>
       </c>
       <c r="L48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4864,15 +4864,15 @@
       </c>
       <c r="R48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="S48">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="T48" s="12">
         <f t="shared" si="4"/>
-        <v>1.2526096033402823E-2</v>
+        <v>2.0746887966804906E-3</v>
       </c>
       <c r="U48">
         <v>1</v>
@@ -4896,31 +4896,31 @@
       </c>
       <c r="F49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21478198.433565818</v>
+        <v>22546305.818256099</v>
       </c>
       <c r="G49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18005875.489039745</v>
+        <v>19126089.304449983</v>
       </c>
       <c r="H49" s="12">
         <f t="shared" si="0"/>
-        <v>-0.1616673276981917</v>
+        <v>-0.15169742402042252</v>
       </c>
       <c r="I49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2191</v>
+        <v>298</v>
       </c>
       <c r="J49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="K49" s="12">
         <f t="shared" si="1"/>
-        <v>-0.85668644454586951</v>
+        <v>8.0536912751677958E-2</v>
       </c>
       <c r="L49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -4928,11 +4928,11 @@
       </c>
       <c r="N49" s="12">
         <f t="shared" si="2"/>
-        <v>-0.4285714285714286</v>
+        <v>-0.33333333333333337</v>
       </c>
       <c r="O49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4948,11 +4948,11 @@
       </c>
       <c r="S49">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="T49" s="12">
         <f t="shared" si="4"/>
-        <v>2.7027027027026973E-2</v>
+        <v>3.6036036036036112E-2</v>
       </c>
       <c r="U49">
         <v>5</v>
@@ -4976,27 +4976,27 @@
       </c>
       <c r="F50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17676503.12317507</v>
+        <v>18657852.426756896</v>
       </c>
       <c r="G50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15802232.271788953</v>
+        <v>16764643.498383747</v>
       </c>
       <c r="H50" s="12">
         <f t="shared" si="0"/>
-        <v>-0.10603176648263779</v>
+        <v>-0.10146982005593164</v>
       </c>
       <c r="I50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>351</v>
+        <v>378</v>
       </c>
       <c r="J50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>335</v>
+        <v>367</v>
       </c>
       <c r="K50" s="12">
         <f t="shared" si="1"/>
-        <v>-4.5584045584045607E-2</v>
+        <v>-2.9100529100529071E-2</v>
       </c>
       <c r="L50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5004,11 +5004,11 @@
       </c>
       <c r="M50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N50" s="12">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -5024,15 +5024,15 @@
       </c>
       <c r="R50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="S50">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="T50" s="12">
         <f t="shared" si="4"/>
-        <v>-1.4018691588784993E-2</v>
+        <v>-1.3986013986013957E-2</v>
       </c>
       <c r="U50">
         <v>4</v>
@@ -5056,27 +5056,27 @@
       </c>
       <c r="F51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>38319010.734158374</v>
+        <v>40544706.538535334</v>
       </c>
       <c r="G51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>37135022.236871041</v>
+        <v>39213836.923041739</v>
       </c>
       <c r="H51" s="12">
         <f t="shared" si="0"/>
-        <v>-3.0898201039201156E-2</v>
+        <v>-3.2824744069332001E-2</v>
       </c>
       <c r="I51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>997</v>
+        <v>927</v>
       </c>
       <c r="J51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>921</v>
+        <v>939</v>
       </c>
       <c r="K51" s="12">
         <f t="shared" si="1"/>
-        <v>-7.6228686058174566E-2</v>
+        <v>1.2944983818770295E-2</v>
       </c>
       <c r="L51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5108,11 +5108,11 @@
       </c>
       <c r="S51">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1104</v>
+        <v>1100</v>
       </c>
       <c r="T51" s="12">
         <f t="shared" si="4"/>
-        <v>-1.9538188277087087E-2</v>
+        <v>-2.3090586145648295E-2</v>
       </c>
       <c r="U51">
         <v>5</v>
@@ -5136,31 +5136,31 @@
       </c>
       <c r="F52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>40505878.641760208</v>
+        <v>42886891.103262864</v>
       </c>
       <c r="G52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>38633184.860168822</v>
+        <v>40939585.895147137</v>
       </c>
       <c r="H52" s="12">
         <f t="shared" si="0"/>
-        <v>-4.623264188770615E-2</v>
+        <v>-4.540560432387164E-2</v>
       </c>
       <c r="I52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>867</v>
+        <v>841</v>
       </c>
       <c r="J52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>926</v>
+        <v>862</v>
       </c>
       <c r="K52" s="12">
         <f t="shared" si="1"/>
-        <v>6.8050749711649372E-2</v>
+        <v>2.4970273483947647E-2</v>
       </c>
       <c r="L52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="N52" s="12">
         <f t="shared" si="2"/>
-        <v>-0.66666666666666674</v>
+        <v>-0.5</v>
       </c>
       <c r="O52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -5184,15 +5184,15 @@
       </c>
       <c r="R52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>967</v>
+        <v>980</v>
       </c>
       <c r="S52">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1009</v>
+        <v>1014</v>
       </c>
       <c r="T52" s="12">
         <f t="shared" si="4"/>
-        <v>4.3433298862461278E-2</v>
+        <v>3.469387755102038E-2</v>
       </c>
       <c r="U52">
         <v>4</v>
@@ -5216,27 +5216,27 @@
       </c>
       <c r="F53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>56342722.856981687</v>
+        <v>60223755.032434106</v>
       </c>
       <c r="G53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>69474698.048531413</v>
+        <v>73666459.599487707</v>
       </c>
       <c r="H53" s="12">
         <f t="shared" si="0"/>
-        <v>0.23307313749964575</v>
+        <v>0.22321266018390751</v>
       </c>
       <c r="I53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1656</v>
+        <v>1709</v>
       </c>
       <c r="J53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1773</v>
+        <v>1735</v>
       </c>
       <c r="K53" s="12">
         <f t="shared" si="1"/>
-        <v>7.0652173913043459E-2</v>
+        <v>1.5213575190169637E-2</v>
       </c>
       <c r="L53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5256,23 +5256,23 @@
       </c>
       <c r="P53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q53" s="12">
         <f t="shared" si="3"/>
-        <v>-0.75</v>
+        <v>-0.72222222222222221</v>
       </c>
       <c r="R53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2161</v>
+        <v>2163</v>
       </c>
       <c r="S53">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2036</v>
+        <v>2043</v>
       </c>
       <c r="T53" s="12">
         <f t="shared" si="4"/>
-        <v>-5.7843590930124922E-2</v>
+        <v>-5.5478502080443803E-2</v>
       </c>
       <c r="U53">
         <v>8</v>
@@ -5296,27 +5296,27 @@
       </c>
       <c r="F54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18581528.074724223</v>
+        <v>19628260.883901495</v>
       </c>
       <c r="G54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17379391.950311348</v>
+        <v>18415275.797894016</v>
       </c>
       <c r="H54" s="12">
         <f t="shared" si="0"/>
-        <v>-6.4695224180625788E-2</v>
+        <v>-6.1797888930767875E-2</v>
       </c>
       <c r="I54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>528</v>
+        <v>555</v>
       </c>
       <c r="J54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>498</v>
+        <v>550</v>
       </c>
       <c r="K54" s="12">
         <f t="shared" si="1"/>
-        <v>-5.6818181818181768E-2</v>
+        <v>-9.009009009009028E-3</v>
       </c>
       <c r="L54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5344,15 +5344,15 @@
       </c>
       <c r="R54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="S54">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="T54" s="12">
         <f t="shared" si="4"/>
-        <v>8.7463556851312685E-3</v>
+        <v>-1.4492753623188692E-3</v>
       </c>
       <c r="U54">
         <v>2</v>
@@ -5376,27 +5376,27 @@
       </c>
       <c r="F55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>28675817.814602911</v>
+        <v>30615413.367241357</v>
       </c>
       <c r="G55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>30317184.127649944</v>
+        <v>32094490.60502778</v>
       </c>
       <c r="H55" s="12">
         <f t="shared" si="0"/>
-        <v>5.7238692324624196E-2</v>
+        <v>4.8311522697552123E-2</v>
       </c>
       <c r="I55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>794</v>
+        <v>830</v>
       </c>
       <c r="J55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>790</v>
+        <v>740</v>
       </c>
       <c r="K55" s="12">
         <f t="shared" si="1"/>
-        <v>-5.0377833753149082E-3</v>
+        <v>-0.10843373493975905</v>
       </c>
       <c r="L55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5416,23 +5416,23 @@
       </c>
       <c r="P55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q55" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.16666666666666674</v>
       </c>
       <c r="R55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="S55">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="T55" s="12">
         <f t="shared" si="4"/>
-        <v>-2.5988700564971712E-2</v>
+        <v>-2.1517553793884536E-2</v>
       </c>
       <c r="U55">
         <v>7</v>
@@ -5456,27 +5456,27 @@
       </c>
       <c r="F56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>22481594.447822541</v>
+        <v>23662873.351727627</v>
       </c>
       <c r="G56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19189044.107355248</v>
+        <v>20317389.490997106</v>
       </c>
       <c r="H56" s="12">
         <f t="shared" si="0"/>
-        <v>-0.14645537477819748</v>
+        <v>-0.14138113368578997</v>
       </c>
       <c r="I56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="J56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>658</v>
+        <v>635</v>
       </c>
       <c r="K56" s="12">
         <f t="shared" si="1"/>
-        <v>5.4487179487179516E-2</v>
+        <v>1.2759170653907415E-2</v>
       </c>
       <c r="L56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5504,15 +5504,15 @@
       </c>
       <c r="R56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="S56">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>746</v>
+        <v>734</v>
       </c>
       <c r="T56" s="12">
         <f t="shared" si="4"/>
-        <v>-5.4499366286438478E-2</v>
+        <v>-6.4968152866242024E-2</v>
       </c>
       <c r="U56">
         <v>3</v>
@@ -5536,27 +5536,27 @@
       </c>
       <c r="F57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>38270861.122598462</v>
+        <v>40636216.140523255</v>
       </c>
       <c r="G57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>38656329.906607106</v>
+        <v>40981093.886455111</v>
       </c>
       <c r="H57" s="12">
         <f t="shared" si="0"/>
-        <v>1.0072122045381215E-2</v>
+        <v>8.486955201223445E-3</v>
       </c>
       <c r="I57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1106</v>
+        <v>1070</v>
       </c>
       <c r="J57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>938</v>
+        <v>977</v>
       </c>
       <c r="K57" s="12">
         <f t="shared" si="1"/>
-        <v>-0.15189873417721522</v>
+        <v>-8.6915887850467333E-2</v>
       </c>
       <c r="L57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5584,15 +5584,15 @@
       </c>
       <c r="R57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="S57">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="T57" s="12">
         <f t="shared" si="4"/>
-        <v>1.185050136736554E-2</v>
+        <v>1.0958904109588996E-2</v>
       </c>
       <c r="U57">
         <v>3</v>
@@ -5616,27 +5616,27 @@
       </c>
       <c r="F58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>49094951.780632906</v>
+        <v>51975399.294892192</v>
       </c>
       <c r="G58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>47134937.423156217</v>
+        <v>50074452.206668533</v>
       </c>
       <c r="H58" s="12">
         <f t="shared" si="0"/>
-        <v>-3.9922930696305925E-2</v>
+        <v>-3.6573977574241967E-2</v>
       </c>
       <c r="I58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1410</v>
+        <v>1343</v>
       </c>
       <c r="J58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1041</v>
+        <v>1408</v>
       </c>
       <c r="K58" s="12">
         <f t="shared" si="1"/>
-        <v>-0.26170212765957446</v>
+        <v>4.8399106478034248E-2</v>
       </c>
       <c r="L58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5652,27 +5652,27 @@
       </c>
       <c r="O58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q58" s="12">
         <f t="shared" si="3"/>
-        <v>-0.19999999999999996</v>
+        <v>-9.0909090909090939E-2</v>
       </c>
       <c r="R58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1361</v>
+        <v>1370</v>
       </c>
       <c r="S58">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1497</v>
+        <v>1503</v>
       </c>
       <c r="T58" s="12">
         <f t="shared" si="4"/>
-        <v>9.992652461425422E-2</v>
+        <v>9.7080291970802923E-2</v>
       </c>
       <c r="U58">
         <v>4</v>
@@ -5696,27 +5696,27 @@
       </c>
       <c r="F59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24841033.532271557</v>
+        <v>26207240.497092113</v>
       </c>
       <c r="G59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>26286574.062764719</v>
+        <v>27821994.716877595</v>
       </c>
       <c r="H59" s="12">
         <f t="shared" si="0"/>
-        <v>5.819164201099869E-2</v>
+        <v>6.1614812897399451E-2</v>
       </c>
       <c r="I59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>678</v>
+        <v>751</v>
       </c>
       <c r="J59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>754</v>
+        <v>682</v>
       </c>
       <c r="K59" s="12">
         <f t="shared" si="1"/>
-        <v>0.11209439528023601</v>
+        <v>-9.187749667110523E-2</v>
       </c>
       <c r="L59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="O59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5740,19 +5740,19 @@
       </c>
       <c r="Q59" s="12">
         <f t="shared" si="3"/>
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="R59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="S59">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="T59" s="12">
         <f t="shared" si="4"/>
-        <v>-5.2083333333333703E-3</v>
+        <v>1.2987012987013546E-3</v>
       </c>
       <c r="U59">
         <v>3</v>
@@ -5776,27 +5776,27 @@
       </c>
       <c r="F60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>29096685.519441087</v>
+        <v>30690396.011699993</v>
       </c>
       <c r="G60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>29372784.881242465</v>
+        <v>31019483.13461696</v>
       </c>
       <c r="H60" s="12">
         <f t="shared" si="0"/>
-        <v>9.4890313749620425E-3</v>
+        <v>1.0722804710356693E-2</v>
       </c>
       <c r="I60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>448</v>
+        <v>483</v>
       </c>
       <c r="J60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>470</v>
+        <v>453</v>
       </c>
       <c r="K60" s="12">
         <f t="shared" si="1"/>
-        <v>4.9107142857142794E-2</v>
+        <v>-6.2111801242236031E-2</v>
       </c>
       <c r="L60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5828,11 +5828,11 @@
       </c>
       <c r="S60">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="T60" s="12">
         <f t="shared" si="4"/>
-        <v>-7.5581395348837233E-2</v>
+        <v>-8.7209302325581439E-2</v>
       </c>
       <c r="U60">
         <v>10</v>
@@ -5856,27 +5856,27 @@
       </c>
       <c r="F61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>75334047.475907341</v>
+        <v>80494151.517660826</v>
       </c>
       <c r="G61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>94609229.45671463</v>
+        <v>99819639.769979075</v>
       </c>
       <c r="H61" s="12">
         <f t="shared" si="0"/>
-        <v>0.25586282201247323</v>
+        <v>0.24008561973695852</v>
       </c>
       <c r="I61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1676</v>
+        <v>1869</v>
       </c>
       <c r="J61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1567</v>
+        <v>1607</v>
       </c>
       <c r="K61" s="12">
         <f t="shared" si="1"/>
-        <v>-6.5035799522673021E-2</v>
+        <v>-0.14018191546281433</v>
       </c>
       <c r="L61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5892,27 +5892,27 @@
       </c>
       <c r="O61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="P61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q61" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-0.21052631578947367</v>
       </c>
       <c r="R61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2035</v>
+        <v>2047</v>
       </c>
       <c r="S61">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1990</v>
+        <v>1999</v>
       </c>
       <c r="T61" s="12">
         <f t="shared" si="4"/>
-        <v>-2.2113022113022129E-2</v>
+        <v>-2.3448949682462139E-2</v>
       </c>
       <c r="U61">
         <v>10</v>
@@ -5936,31 +5936,31 @@
       </c>
       <c r="F62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>70479993.177585602</v>
+        <v>74403597.224619329</v>
       </c>
       <c r="G62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>70751538.977041662</v>
+        <v>75202591.101204753</v>
       </c>
       <c r="H62" s="12">
         <f t="shared" si="0"/>
-        <v>3.8528068351519895E-3</v>
+        <v>1.0738645796564361E-2</v>
       </c>
       <c r="I62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1193</v>
+        <v>1177</v>
       </c>
       <c r="J62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1356</v>
+        <v>1376</v>
       </c>
       <c r="K62" s="12">
         <f t="shared" si="1"/>
-        <v>0.13663034367141669</v>
+        <v>0.16907391673746819</v>
       </c>
       <c r="L62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="N62" s="12">
         <f t="shared" si="2"/>
-        <v>-0.25</v>
+        <v>-0.1428571428571429</v>
       </c>
       <c r="O62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -5984,15 +5984,15 @@
       </c>
       <c r="R62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1602</v>
+        <v>1597</v>
       </c>
       <c r="S62">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1599</v>
+        <v>1602</v>
       </c>
       <c r="T62" s="12">
         <f t="shared" si="4"/>
-        <v>-1.8726591760299671E-3</v>
+        <v>3.1308703819661332E-3</v>
       </c>
       <c r="U62">
         <v>8</v>
@@ -6016,27 +6016,27 @@
       </c>
       <c r="F63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>43706336.685455166</v>
+        <v>46188082.820514478</v>
       </c>
       <c r="G63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>45651879.400535792</v>
+        <v>48323897.682485439</v>
       </c>
       <c r="H63" s="12">
         <f t="shared" si="0"/>
-        <v>4.4513973547640528E-2</v>
+        <v>4.6241686849628927E-2</v>
       </c>
       <c r="I63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="J63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="K63" s="12">
         <f t="shared" si="1"/>
-        <v>-3.0487804878048808E-3</v>
+        <v>1.388888888888884E-2</v>
       </c>
       <c r="L63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6064,15 +6064,15 @@
       </c>
       <c r="R63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>860</v>
+        <v>852</v>
       </c>
       <c r="S63">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="T63" s="12">
         <f t="shared" si="4"/>
-        <v>3.953488372093017E-2</v>
+        <v>4.6948356807511749E-2</v>
       </c>
       <c r="U63">
         <v>4</v>
@@ -6096,27 +6096,27 @@
       </c>
       <c r="F64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>64357523.01838614</v>
+        <v>67882627.172021404</v>
       </c>
       <c r="G64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>67636200.907637477</v>
+        <v>71504925.88939625</v>
       </c>
       <c r="H64" s="12">
         <f t="shared" si="0"/>
-        <v>5.0944749509931553E-2</v>
+        <v>5.3361204011677099E-2</v>
       </c>
       <c r="I64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1463</v>
+        <v>1445</v>
       </c>
       <c r="J64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1245</v>
+        <v>1277</v>
       </c>
       <c r="K64" s="12">
         <f t="shared" si="1"/>
-        <v>-0.14900888585099115</v>
+        <v>-0.11626297577854672</v>
       </c>
       <c r="L64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6136,23 +6136,23 @@
       </c>
       <c r="P64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>377</v>
+        <v>475</v>
       </c>
       <c r="Q64" s="12">
         <f t="shared" si="3"/>
-        <v>0.54508196721311486</v>
+        <v>0.94672131147540983</v>
       </c>
       <c r="R64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2008</v>
+        <v>1999</v>
       </c>
       <c r="S64">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2204</v>
+        <v>2271</v>
       </c>
       <c r="T64" s="12">
         <f t="shared" si="4"/>
-        <v>9.7609561752987961E-2</v>
+        <v>0.1360680340170084</v>
       </c>
       <c r="U64">
         <v>9</v>
@@ -6176,27 +6176,27 @@
       </c>
       <c r="F65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4831983.2646832503</v>
+        <v>5076964.1164683579</v>
       </c>
       <c r="G65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>2632017.6643952979</v>
+        <v>2920456.5121259899</v>
       </c>
       <c r="H65" s="12">
         <f t="shared" si="0"/>
-        <v>-0.45529247097509684</v>
+        <v>-0.42476321574683096</v>
       </c>
       <c r="I65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="J65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="K65" s="12">
         <f t="shared" si="1"/>
-        <v>-3.5294117647058809E-2</v>
+        <v>0</v>
       </c>
       <c r="L65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="R65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="S65">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="T65" s="12">
         <f t="shared" si="4"/>
-        <v>-5.6179775280898903E-2</v>
+        <v>-4.9056603773584895E-2</v>
       </c>
       <c r="U65">
         <v>3</v>
@@ -6256,27 +6256,27 @@
       </c>
       <c r="F66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>50773613.3984451</v>
+        <v>53626628.117396288</v>
       </c>
       <c r="G66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>48982194.351211667</v>
+        <v>51942957.043750465</v>
       </c>
       <c r="H66" s="12">
         <f t="shared" si="0"/>
-        <v>-3.5282480944881733E-2</v>
+        <v>-3.1396176354031247E-2</v>
       </c>
       <c r="I66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1517</v>
+        <v>1560</v>
       </c>
       <c r="J66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1571</v>
+        <v>1921</v>
       </c>
       <c r="K66" s="12">
         <f t="shared" si="1"/>
-        <v>3.5596572181938013E-2</v>
+        <v>0.23141025641025648</v>
       </c>
       <c r="L66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6304,15 +6304,15 @@
       </c>
       <c r="R66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1781</v>
+        <v>1805</v>
       </c>
       <c r="S66">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1663</v>
+        <v>1667</v>
       </c>
       <c r="T66" s="12">
         <f t="shared" si="4"/>
-        <v>-6.6254912970241442E-2</v>
+        <v>-7.6454293628808845E-2</v>
       </c>
       <c r="U66">
         <v>6</v>
@@ -6336,27 +6336,27 @@
       </c>
       <c r="F67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20933770.783716775</v>
+        <v>21968090.95705428</v>
       </c>
       <c r="G67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23094311.445282642</v>
+        <v>24581273.682099607</v>
       </c>
       <c r="H67" s="12">
         <f t="shared" ref="H67:H85" si="5">IFERROR(G67/F67-1,0)</f>
-        <v>0.10320838437986679</v>
+        <v>0.11895356452018846</v>
       </c>
       <c r="I67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>571</v>
+        <v>610</v>
       </c>
       <c r="J67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>614</v>
+        <v>763</v>
       </c>
       <c r="K67" s="12">
         <f t="shared" ref="K67:K85" si="6">IFERROR(J67/I67-1,0)</f>
-        <v>7.5306479859895026E-2</v>
+        <v>0.25081967213114753</v>
       </c>
       <c r="L67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6384,15 +6384,15 @@
       </c>
       <c r="R67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="S67">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="T67" s="12">
         <f t="shared" ref="T67:T85" si="9">IFERROR(S67/R67-1,0)</f>
-        <v>0.11295180722891573</v>
+        <v>0.10344827586206895</v>
       </c>
       <c r="U67">
         <v>3</v>
@@ -6416,27 +6416,27 @@
       </c>
       <c r="F68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>34166560.655513391</v>
+        <v>36202729.775051877</v>
       </c>
       <c r="G68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>34962922.177493237</v>
+        <v>37415644.270037763</v>
       </c>
       <c r="H68" s="12">
         <f t="shared" si="5"/>
-        <v>2.3308214426649876E-2</v>
+        <v>3.3503398846507215E-2</v>
       </c>
       <c r="I68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1189</v>
+        <v>1260</v>
       </c>
       <c r="J68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>982</v>
+        <v>1532</v>
       </c>
       <c r="K68" s="12">
         <f t="shared" si="6"/>
-        <v>-0.17409587888982336</v>
+        <v>0.21587301587301577</v>
       </c>
       <c r="L68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6444,11 +6444,11 @@
       </c>
       <c r="M68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N68" s="12">
         <f t="shared" si="7"/>
-        <v>-0.19999999999999996</v>
+        <v>0</v>
       </c>
       <c r="O68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -6464,15 +6464,15 @@
       </c>
       <c r="R68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="S68">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1391</v>
+        <v>1382</v>
       </c>
       <c r="T68" s="12">
         <f t="shared" si="9"/>
-        <v>4.9811320754717059E-2</v>
+        <v>4.2232277526395245E-2</v>
       </c>
       <c r="U68">
         <v>4</v>
@@ -6496,27 +6496,27 @@
       </c>
       <c r="F69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17151283.369032022</v>
+        <v>17783711.442227617</v>
       </c>
       <c r="G69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22198382.348371297</v>
+        <v>23929894.673063796</v>
       </c>
       <c r="H69" s="12">
         <f t="shared" si="5"/>
-        <v>0.29426946489918104</v>
+        <v>0.34560745380978242</v>
       </c>
       <c r="I69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>853</v>
+        <v>1260</v>
       </c>
       <c r="J69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1208</v>
+        <v>1215</v>
       </c>
       <c r="K69" s="12">
         <f t="shared" si="6"/>
-        <v>0.41617819460726846</v>
+        <v>-3.5714285714285698E-2</v>
       </c>
       <c r="L69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6536,23 +6536,23 @@
       </c>
       <c r="P69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q69" s="12">
         <f t="shared" si="8"/>
-        <v>-0.1428571428571429</v>
+        <v>0</v>
       </c>
       <c r="R69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="S69">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1253</v>
+        <v>1256</v>
       </c>
       <c r="T69" s="12">
         <f t="shared" si="9"/>
-        <v>-7.5958702064896744E-2</v>
+        <v>-7.5110456553755478E-2</v>
       </c>
       <c r="U69">
         <v>4</v>
@@ -6576,27 +6576,27 @@
       </c>
       <c r="F70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>60080748.523181163</v>
+        <v>63481150.813349932</v>
       </c>
       <c r="G70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>61224476.983174697</v>
+        <v>65060314.538961947</v>
       </c>
       <c r="H70" s="12">
         <f t="shared" si="5"/>
-        <v>1.9036521483287494E-2</v>
+        <v>2.4876104251089215E-2</v>
       </c>
       <c r="I70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1210</v>
+        <v>1180</v>
       </c>
       <c r="J70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1241</v>
+        <v>1259</v>
       </c>
       <c r="K70" s="12">
         <f t="shared" si="6"/>
-        <v>2.5619834710743694E-2</v>
+        <v>6.6949152542372881E-2</v>
       </c>
       <c r="L70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6612,7 +6612,7 @@
       </c>
       <c r="O70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -6620,19 +6620,19 @@
       </c>
       <c r="Q70" s="12">
         <f t="shared" si="8"/>
-        <v>0.85714285714285721</v>
+        <v>0.625</v>
       </c>
       <c r="R70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1751</v>
+        <v>1746</v>
       </c>
       <c r="S70">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1758</v>
+        <v>1732</v>
       </c>
       <c r="T70" s="12">
         <f t="shared" si="9"/>
-        <v>3.9977155910908557E-3</v>
+        <v>-8.0183276059564434E-3</v>
       </c>
       <c r="U70">
         <v>4</v>
@@ -6656,27 +6656,27 @@
       </c>
       <c r="F71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13156020.104537236</v>
+        <v>13786630.717428997</v>
       </c>
       <c r="G71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12385983.388492895</v>
+        <v>13044733.106628915</v>
       </c>
       <c r="H71" s="12">
         <f t="shared" si="5"/>
-        <v>-5.8531129469676868E-2</v>
+        <v>-5.3812829690301212E-2</v>
       </c>
       <c r="I71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>494</v>
+        <v>424</v>
       </c>
       <c r="J71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="K71" s="12">
         <f t="shared" si="6"/>
-        <v>-0.10931174089068829</v>
+        <v>4.7169811320754818E-2</v>
       </c>
       <c r="L71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="O71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -6700,19 +6700,19 @@
       </c>
       <c r="Q71" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>-0.33333333333333337</v>
       </c>
       <c r="R71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="S71">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="T71" s="12">
         <f t="shared" si="9"/>
-        <v>2.2177419354838745E-2</v>
+        <v>4.8780487804878092E-2</v>
       </c>
       <c r="U71">
         <v>2</v>
@@ -6736,27 +6736,27 @@
       </c>
       <c r="F72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19982061.397274464</v>
+        <v>21117188.467634171</v>
       </c>
       <c r="G72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19938681.662497777</v>
+        <v>21197941.625014752</v>
       </c>
       <c r="H72" s="12">
         <f t="shared" si="5"/>
-        <v>-2.1709339148864304E-3</v>
+        <v>3.8240487129406198E-3</v>
       </c>
       <c r="I72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>834</v>
+        <v>790</v>
       </c>
       <c r="J72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>791</v>
+        <v>808</v>
       </c>
       <c r="K72" s="12">
         <f t="shared" si="6"/>
-        <v>-5.1558752997601931E-2</v>
+        <v>2.2784810126582178E-2</v>
       </c>
       <c r="L72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6784,15 +6784,15 @@
       </c>
       <c r="R72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="S72">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="T72" s="12">
         <f t="shared" si="9"/>
-        <v>-1.3468013468013518E-2</v>
+        <v>-9.009009009009028E-3</v>
       </c>
       <c r="U72">
         <v>3</v>
@@ -6816,27 +6816,27 @@
       </c>
       <c r="F73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14294811.694408428</v>
+        <v>14736341.28762248</v>
       </c>
       <c r="G73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19626666.190058872</v>
+        <v>20935184.704319578</v>
       </c>
       <c r="H73" s="12">
         <f t="shared" si="5"/>
-        <v>0.37299228626677583</v>
+        <v>0.4206500986716224</v>
       </c>
       <c r="I73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>633</v>
+        <v>416</v>
       </c>
       <c r="J73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="K73" s="12">
         <f t="shared" si="6"/>
-        <v>-0.23064770932069512</v>
+        <v>0.18509615384615374</v>
       </c>
       <c r="L73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6856,23 +6856,23 @@
       </c>
       <c r="P73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q73" s="12">
         <f t="shared" si="8"/>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="R73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="S73">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="T73" s="12">
         <f t="shared" si="9"/>
-        <v>-3.7313432835820892E-2</v>
+        <v>-2.5525525525525561E-2</v>
       </c>
       <c r="U73">
         <v>7</v>
@@ -6896,27 +6896,27 @@
       </c>
       <c r="F74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13802610.510686357</v>
+        <v>13803241.814353952</v>
       </c>
       <c r="G74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14965299.75582342</v>
+        <v>15506233.992221871</v>
       </c>
       <c r="H74" s="12">
         <f t="shared" si="5"/>
-        <v>8.4236908970000801E-2</v>
+        <v>0.12337624746217091</v>
       </c>
       <c r="I74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>352</v>
+        <v>12</v>
       </c>
       <c r="J74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>596</v>
+        <v>551</v>
       </c>
       <c r="K74" s="12">
         <f t="shared" si="6"/>
-        <v>0.69318181818181812</v>
+        <v>44.916666666666664</v>
       </c>
       <c r="L74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="R74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="S74">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="T74" s="12">
         <f t="shared" si="9"/>
-        <v>1.3157894736842035E-2</v>
+        <v>1.9867549668874274E-2</v>
       </c>
       <c r="U74">
         <v>2</v>
@@ -6976,27 +6976,27 @@
       </c>
       <c r="F75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15323299.284381747</v>
+        <v>16238993.027723324</v>
       </c>
       <c r="G75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16528959.138679625</v>
+        <v>17523590.520165198</v>
       </c>
       <c r="H75" s="12">
         <f t="shared" si="5"/>
-        <v>7.8681479224695705E-2</v>
+        <v>7.9105735820490741E-2</v>
       </c>
       <c r="I75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="J75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="K75" s="12">
         <f t="shared" si="6"/>
-        <v>0.10304449648711933</v>
+        <v>0.13365155131264927</v>
       </c>
       <c r="L75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7012,27 +7012,27 @@
       </c>
       <c r="O75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q75" s="12">
         <f t="shared" si="8"/>
-        <v>-0.8</v>
+        <v>-0.66666666666666674</v>
       </c>
       <c r="R75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="S75">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="T75" s="12">
         <f t="shared" si="9"/>
-        <v>2.0785219399538146E-2</v>
+        <v>2.5345622119815614E-2</v>
       </c>
       <c r="U75">
         <v>1</v>
@@ -7056,31 +7056,31 @@
       </c>
       <c r="F76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>44142138.429326862</v>
+        <v>46538332.60440968</v>
       </c>
       <c r="G76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>43962551.141078793</v>
+        <v>46909192.026860319</v>
       </c>
       <c r="H76" s="12">
         <f t="shared" si="5"/>
-        <v>-4.0683866853346018E-3</v>
+        <v>7.9689022295461598E-3</v>
       </c>
       <c r="I76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>736</v>
+        <v>550</v>
       </c>
       <c r="J76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>911</v>
+        <v>757</v>
       </c>
       <c r="K76" s="12">
         <f t="shared" si="6"/>
-        <v>0.23777173913043481</v>
+        <v>0.37636363636363646</v>
       </c>
       <c r="L76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="N76" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="O76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -7096,11 +7096,11 @@
       </c>
       <c r="P76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q76" s="12">
         <f t="shared" si="8"/>
-        <v>-0.33333333333333337</v>
+        <v>-0.22222222222222221</v>
       </c>
       <c r="R76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -7108,11 +7108,11 @@
       </c>
       <c r="S76">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>919</v>
+        <v>908</v>
       </c>
       <c r="T76" s="12">
         <f t="shared" si="9"/>
-        <v>-4.1710114702815382E-2</v>
+        <v>-5.3180396246089723E-2</v>
       </c>
       <c r="U76">
         <v>4</v>
@@ -7136,27 +7136,27 @@
       </c>
       <c r="F77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>26320088.840679597</v>
+        <v>27857525.216046929</v>
       </c>
       <c r="G77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>25795596.968580019</v>
+        <v>27265674.916935232</v>
       </c>
       <c r="H77" s="12">
         <f t="shared" si="5"/>
-        <v>-1.9927435476165156E-2</v>
+        <v>-2.1245616562190928E-2</v>
       </c>
       <c r="I77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="J77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>694</v>
+        <v>734</v>
       </c>
       <c r="K77" s="12">
         <f t="shared" si="6"/>
-        <v>-7.2192513368983913E-2</v>
+        <v>-2.6525198938992078E-2</v>
       </c>
       <c r="L77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7176,23 +7176,23 @@
       </c>
       <c r="P77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q77" s="12">
         <f t="shared" si="8"/>
-        <v>-0.33333333333333337</v>
+        <v>0</v>
       </c>
       <c r="R77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="S77">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="T77" s="12">
         <f t="shared" si="9"/>
-        <v>-1.5306122448979553E-2</v>
+        <v>-1.6602809706257937E-2</v>
       </c>
       <c r="U77">
         <v>3</v>
@@ -7216,27 +7216,27 @@
       </c>
       <c r="F78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21296375.880635846</v>
+        <v>22505847.82083239</v>
       </c>
       <c r="G78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21424759.907585599</v>
+        <v>22856536.852877505</v>
       </c>
       <c r="H78" s="12">
         <f t="shared" si="5"/>
-        <v>6.0284448241021416E-3</v>
+        <v>1.5582129357530894E-2</v>
       </c>
       <c r="I78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>931</v>
+        <v>893</v>
       </c>
       <c r="J78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>969</v>
+        <v>1081</v>
       </c>
       <c r="K78" s="12">
         <f t="shared" si="6"/>
-        <v>4.081632653061229E-2</v>
+        <v>0.21052631578947367</v>
       </c>
       <c r="L78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7264,15 +7264,15 @@
       </c>
       <c r="R78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="S78">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="T78" s="12">
         <f t="shared" si="9"/>
-        <v>1.2644889357218192E-2</v>
+        <v>1.6967126193001114E-2</v>
       </c>
       <c r="U78">
         <v>3</v>
@@ -7296,27 +7296,27 @@
       </c>
       <c r="F79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24350171.013393518</v>
+        <v>25689391.598872714</v>
       </c>
       <c r="G79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22204966.601389252</v>
+        <v>23804512.005560592</v>
       </c>
       <c r="H79" s="12">
         <f t="shared" si="5"/>
-        <v>-8.8098125094247637E-2</v>
+        <v>-7.3371904743545269E-2</v>
       </c>
       <c r="I79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>802</v>
+        <v>792</v>
       </c>
       <c r="J79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>866</v>
+        <v>855</v>
       </c>
       <c r="K79" s="12">
         <f t="shared" si="6"/>
-        <v>7.9800498753117122E-2</v>
+        <v>7.9545454545454586E-2</v>
       </c>
       <c r="L79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7336,23 +7336,23 @@
       </c>
       <c r="P79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q79" s="12">
         <f t="shared" si="8"/>
-        <v>-0.66666666666666674</v>
+        <v>-0.5</v>
       </c>
       <c r="R79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="S79">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="T79" s="12">
         <f t="shared" si="9"/>
-        <v>-2.16110019646365E-2</v>
+        <v>-2.1674876847290636E-2</v>
       </c>
       <c r="U79">
         <v>3</v>
@@ -7376,27 +7376,27 @@
       </c>
       <c r="F80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>26106286.217771295</v>
+        <v>27707878.138874147</v>
       </c>
       <c r="G80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>28443447.509641979</v>
+        <v>30321505.756113347</v>
       </c>
       <c r="H80" s="12">
         <f t="shared" si="5"/>
-        <v>8.9524847478294811E-2</v>
+        <v>9.4327959872621214E-2</v>
       </c>
       <c r="I80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="J80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="K80" s="12">
         <f t="shared" si="6"/>
-        <v>3.1944444444444553E-2</v>
+        <v>2.0632737276478741E-2</v>
       </c>
       <c r="L80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7424,15 +7424,15 @@
       </c>
       <c r="R80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="S80">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="T80" s="12">
         <f t="shared" si="9"/>
-        <v>9.3085106382979621E-3</v>
+        <v>0</v>
       </c>
       <c r="U80">
         <v>3</v>
@@ -7456,27 +7456,27 @@
       </c>
       <c r="F81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11647431.128983499</v>
+        <v>12297623.509624189</v>
       </c>
       <c r="G81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13047181.392881865</v>
+        <v>13851013.837541368</v>
       </c>
       <c r="H81" s="12">
         <f t="shared" si="5"/>
-        <v>0.1201767366896227</v>
+        <v>0.12631630222713253</v>
       </c>
       <c r="I81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>691</v>
+        <v>632</v>
       </c>
       <c r="J81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>522</v>
+        <v>544</v>
       </c>
       <c r="K81" s="12">
         <f t="shared" si="6"/>
-        <v>-0.24457308248914611</v>
+        <v>-0.13924050632911389</v>
       </c>
       <c r="L81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7504,15 +7504,15 @@
       </c>
       <c r="R81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="S81">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="T81" s="12">
         <f t="shared" si="9"/>
-        <v>-1.2237762237762184E-2</v>
+        <v>0</v>
       </c>
       <c r="U81">
         <v>1</v>
@@ -7536,27 +7536,27 @@
       </c>
       <c r="F82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>50025277.975978665</v>
+        <v>52982781.551008649</v>
       </c>
       <c r="G82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>54503798.017063886</v>
+        <v>56341564.403701298</v>
       </c>
       <c r="H82" s="12">
         <f t="shared" si="5"/>
-        <v>8.9525140534665981E-2</v>
+        <v>6.3393856539204485E-2</v>
       </c>
       <c r="I82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1261</v>
+        <v>1317</v>
       </c>
       <c r="J82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1312</v>
+        <v>824</v>
       </c>
       <c r="K82" s="12">
         <f t="shared" si="6"/>
-        <v>4.0444091990483821E-2</v>
+        <v>-0.37433561123766135</v>
       </c>
       <c r="L82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7584,15 +7584,15 @@
       </c>
       <c r="R82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1704</v>
+        <v>1700</v>
       </c>
       <c r="S82">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="T82" s="12">
         <f t="shared" si="9"/>
-        <v>3.5211267605633756E-2</v>
+        <v>3.7058823529411811E-2</v>
       </c>
       <c r="U82">
         <v>2</v>
@@ -7616,27 +7616,27 @@
       </c>
       <c r="F83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13491062.530736148</v>
+        <v>14099053.264334928</v>
       </c>
       <c r="G83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12625436.34218335</v>
+        <v>13251615.22394882</v>
       </c>
       <c r="H83" s="12">
         <f t="shared" si="5"/>
-        <v>-6.4162936505607115E-2</v>
+        <v>-6.010602446121649E-2</v>
       </c>
       <c r="I83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>641</v>
+        <v>628</v>
       </c>
       <c r="J83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>671</v>
+        <v>625</v>
       </c>
       <c r="K83" s="12">
         <f t="shared" si="6"/>
-        <v>4.6801872074883066E-2</v>
+        <v>-4.777070063694322E-3</v>
       </c>
       <c r="L83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7664,15 +7664,15 @@
       </c>
       <c r="R83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>620</v>
+        <v>599</v>
       </c>
       <c r="S83">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="T83" s="12">
         <f t="shared" si="9"/>
-        <v>-6.7741935483870974E-2</v>
+        <v>-4.8414023372287174E-2</v>
       </c>
       <c r="U83">
         <v>2</v>
@@ -7696,27 +7696,27 @@
       </c>
       <c r="F84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>23429486.45540712</v>
+        <v>24761684.048804503</v>
       </c>
       <c r="G84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>24509877.584273003</v>
+        <v>25936117.318591543</v>
       </c>
       <c r="H84" s="12">
         <f t="shared" si="5"/>
-        <v>4.6112454531266334E-2</v>
+        <v>4.7429458653630574E-2</v>
       </c>
       <c r="I84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>520</v>
+        <v>574</v>
       </c>
       <c r="J84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>641</v>
+        <v>526</v>
       </c>
       <c r="K84" s="12">
         <f t="shared" si="6"/>
-        <v>0.23269230769230775</v>
+        <v>-8.362369337979092E-2</v>
       </c>
       <c r="L84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7776,27 +7776,27 @@
       </c>
       <c r="F85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6461103.0332732033</v>
+        <v>6820595.096124053</v>
       </c>
       <c r="G85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>5909417.688019501</v>
+        <v>6214020.6016599154</v>
       </c>
       <c r="H85" s="12">
         <f t="shared" si="5"/>
-        <v>-8.5385628802489122E-2</v>
+        <v>-8.8932781658426885E-2</v>
       </c>
       <c r="I85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="J85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="K85" s="12">
         <f t="shared" si="6"/>
-        <v>0.24590163934426235</v>
+        <v>0.12732919254658381</v>
       </c>
       <c r="L85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7824,15 +7824,15 @@
       </c>
       <c r="R85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="S85">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="T85" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-8.2872928176795924E-3</v>
       </c>
       <c r="U85">
         <v>2</v>
@@ -7865,43 +7865,43 @@
       <c r="A3" s="11"/>
       <c r="B3" s="11">
         <f t="shared" ref="B3:K3" si="0">SUBTOTAL(9,B6:B90)</f>
-        <v>84319</v>
+        <v>84274</v>
       </c>
       <c r="C3" s="11">
         <f t="shared" si="0"/>
-        <v>1419</v>
+        <v>1453</v>
       </c>
       <c r="D3" s="11">
         <f t="shared" si="0"/>
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="E3" s="11">
         <f t="shared" si="0"/>
-        <v>71611</v>
+        <v>70462</v>
       </c>
       <c r="F3" s="11">
         <f t="shared" si="0"/>
-        <v>2483285634.6846657</v>
+        <v>2624274086.5847387</v>
       </c>
       <c r="G3" s="11">
         <f t="shared" si="0"/>
-        <v>84407</v>
+        <v>84388</v>
       </c>
       <c r="H3" s="11">
         <f t="shared" si="0"/>
-        <v>1137</v>
+        <v>1269</v>
       </c>
       <c r="I3" s="11">
         <f t="shared" si="0"/>
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="J3" s="11">
         <f t="shared" si="0"/>
-        <v>70297</v>
+        <v>70547</v>
       </c>
       <c r="K3" s="11">
         <f t="shared" si="0"/>
-        <v>2540522841.3581352</v>
+        <v>2696476987.8468094</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -7961,7 +7961,7 @@
         <v>117</v>
       </c>
       <c r="B6" s="10">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C6" s="10">
         <v>3</v>
@@ -7970,13 +7970,13 @@
         <v>2</v>
       </c>
       <c r="E6" s="10">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="F6" s="10">
-        <v>11813210.545567276</v>
+        <v>12452036.798173808</v>
       </c>
       <c r="G6" s="10">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="H6" s="10">
         <v>0</v>
@@ -7985,10 +7985,10 @@
         <v>2</v>
       </c>
       <c r="J6" s="10">
-        <v>428</v>
+        <v>364</v>
       </c>
       <c r="K6" s="10">
-        <v>11602296.38923113</v>
+        <v>12287955.952436997</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
@@ -7996,7 +7996,7 @@
         <v>127</v>
       </c>
       <c r="B7" s="10">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="C7" s="10">
         <v>2</v>
@@ -8005,25 +8005,25 @@
         <v>1</v>
       </c>
       <c r="E7" s="10">
-        <v>454</v>
+        <v>525</v>
       </c>
       <c r="F7" s="10">
-        <v>14558309.604847057</v>
+        <v>15270377.5820772</v>
       </c>
       <c r="G7" s="10">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="H7" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J7" s="10">
-        <v>519</v>
+        <v>487</v>
       </c>
       <c r="K7" s="10">
-        <v>13595181.152484637</v>
+        <v>14339947.092993161</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
@@ -8031,7 +8031,7 @@
         <v>119</v>
       </c>
       <c r="B8" s="10">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C8" s="10">
         <v>7</v>
@@ -8040,25 +8040,25 @@
         <v>2</v>
       </c>
       <c r="E8" s="10">
-        <v>852</v>
+        <v>909</v>
       </c>
       <c r="F8" s="10">
-        <v>15765702.050982265</v>
+        <v>17041117.995255239</v>
       </c>
       <c r="G8" s="10">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H8" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I8" s="10">
         <v>1</v>
       </c>
       <c r="J8" s="10">
-        <v>790</v>
+        <v>806</v>
       </c>
       <c r="K8" s="10">
-        <v>18573202.176985394</v>
+        <v>19961475.905457538</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
@@ -8066,34 +8066,34 @@
         <v>121</v>
       </c>
       <c r="B9" s="10">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="C9" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" s="10">
         <v>3</v>
       </c>
       <c r="E9" s="10">
-        <v>1378</v>
+        <v>1468</v>
       </c>
       <c r="F9" s="10">
-        <v>28310468.960497696</v>
+        <v>30428581.790787671</v>
       </c>
       <c r="G9" s="10">
-        <v>1204</v>
+        <v>1213</v>
       </c>
       <c r="H9" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I9" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J9" s="10">
-        <v>1107</v>
+        <v>1088</v>
       </c>
       <c r="K9" s="10">
-        <v>29309668.523300178</v>
+        <v>31260783.726436041</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
@@ -8101,7 +8101,7 @@
         <v>123</v>
       </c>
       <c r="B10" s="10">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C10" s="10">
         <v>1</v>
@@ -8110,13 +8110,13 @@
         <v>1</v>
       </c>
       <c r="E10" s="10">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="F10" s="10">
-        <v>11757304.216271428</v>
+        <v>12572009.692979235</v>
       </c>
       <c r="G10" s="10">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="H10" s="10">
         <v>1</v>
@@ -8125,10 +8125,10 @@
         <v>1</v>
       </c>
       <c r="J10" s="10">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="K10" s="10">
-        <v>13279203.146268772</v>
+        <v>14087321.867469653</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
@@ -8136,7 +8136,7 @@
         <v>125</v>
       </c>
       <c r="B11" s="10">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="C11" s="10">
         <v>3</v>
@@ -8145,10 +8145,10 @@
         <v>2</v>
       </c>
       <c r="E11" s="10">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="F11" s="10">
-        <v>10339799.678089332</v>
+        <v>10954941.459135331</v>
       </c>
       <c r="G11" s="10">
         <v>386</v>
@@ -8160,10 +8160,10 @@
         <v>2</v>
       </c>
       <c r="J11" s="10">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="K11" s="10">
-        <v>10850637.181308759</v>
+        <v>11489847.967613995</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -8171,7 +8171,7 @@
         <v>131</v>
       </c>
       <c r="B12" s="10">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="C12" s="10">
         <v>1</v>
@@ -8180,25 +8180,25 @@
         <v>1</v>
       </c>
       <c r="E12" s="10">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="F12" s="10">
-        <v>11840920.056150315</v>
+        <v>12590405.038448486</v>
       </c>
       <c r="G12" s="10">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="H12" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I12" s="10">
         <v>2</v>
       </c>
       <c r="J12" s="10">
-        <v>525</v>
+        <v>488</v>
       </c>
       <c r="K12" s="10">
-        <v>13055381.858272109</v>
+        <v>13775550.668594858</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
@@ -8215,13 +8215,13 @@
         <v>1</v>
       </c>
       <c r="E13" s="10">
-        <v>146</v>
+        <v>385</v>
       </c>
       <c r="F13" s="10">
-        <v>5538273.8270198824</v>
+        <v>5908394.1481695939</v>
       </c>
       <c r="G13" s="10">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H13" s="10">
         <v>0</v>
@@ -8230,10 +8230,10 @@
         <v>1</v>
       </c>
       <c r="J13" s="10">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="K13" s="10">
-        <v>5740248.3143004626</v>
+        <v>6045648.5828848016</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
@@ -8241,7 +8241,7 @@
         <v>141</v>
       </c>
       <c r="B14" s="10">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C14" s="10">
         <v>1</v>
@@ -8250,13 +8250,13 @@
         <v>0</v>
       </c>
       <c r="E14" s="10">
-        <v>157</v>
+        <v>226</v>
       </c>
       <c r="F14" s="10">
-        <v>5377723.235344599</v>
+        <v>5680298.6802293016</v>
       </c>
       <c r="G14" s="10">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H14" s="10">
         <v>1</v>
@@ -8265,10 +8265,10 @@
         <v>1</v>
       </c>
       <c r="J14" s="10">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="K14" s="10">
-        <v>2513527.1167136971</v>
+        <v>2860659.9967147</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
@@ -8276,7 +8276,7 @@
         <v>135</v>
       </c>
       <c r="B15" s="10">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C15" s="10">
         <v>0</v>
@@ -8285,10 +8285,10 @@
         <v>1</v>
       </c>
       <c r="E15" s="10">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="F15" s="10">
-        <v>8449767.6351467129</v>
+        <v>8944383.1211307161</v>
       </c>
       <c r="G15" s="10">
         <v>381</v>
@@ -8300,10 +8300,10 @@
         <v>1</v>
       </c>
       <c r="J15" s="10">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="K15" s="10">
-        <v>11274051.916730504</v>
+        <v>11890504.003905904</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
@@ -8311,7 +8311,7 @@
         <v>143</v>
       </c>
       <c r="B16" s="10">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C16" s="10">
         <v>0</v>
@@ -8320,13 +8320,13 @@
         <v>1</v>
       </c>
       <c r="E16" s="10">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F16" s="10">
-        <v>4041060.1390938722</v>
+        <v>4262490.9429104608</v>
       </c>
       <c r="G16" s="10">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H16" s="10">
         <v>0</v>
@@ -8335,10 +8335,10 @@
         <v>2</v>
       </c>
       <c r="J16" s="10">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="K16" s="10">
-        <v>5806029.4254871206</v>
+        <v>6152814.3065978391</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -8346,7 +8346,7 @@
         <v>145</v>
       </c>
       <c r="B17" s="10">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C17" s="10">
         <v>7</v>
@@ -8355,25 +8355,25 @@
         <v>1</v>
       </c>
       <c r="E17" s="10">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F17" s="10">
-        <v>5431815.5109380577</v>
+        <v>5733341.8539821506</v>
       </c>
       <c r="G17" s="10">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H17" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17" s="10">
         <v>229</v>
       </c>
       <c r="K17" s="10">
-        <v>6161717.6329658534</v>
+        <v>6544098.7908061044</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
@@ -8381,7 +8381,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="10">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="C18" s="10">
         <v>0</v>
@@ -8390,13 +8390,13 @@
         <v>2</v>
       </c>
       <c r="E18" s="10">
-        <v>1258</v>
+        <v>1062</v>
       </c>
       <c r="F18" s="10">
-        <v>10793808.574127875</v>
+        <v>12150068.330912439</v>
       </c>
       <c r="G18" s="10">
-        <v>1428</v>
+        <v>1403</v>
       </c>
       <c r="H18" s="10">
         <v>4</v>
@@ -8405,10 +8405,10 @@
         <v>3</v>
       </c>
       <c r="J18" s="10">
-        <v>1101</v>
+        <v>1064</v>
       </c>
       <c r="K18" s="10">
-        <v>25119200.515578978</v>
+        <v>27129953.922294252</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
@@ -8416,22 +8416,22 @@
         <v>45</v>
       </c>
       <c r="B19" s="10">
-        <v>1278</v>
+        <v>1271</v>
       </c>
       <c r="C19" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="10">
         <v>2</v>
       </c>
       <c r="E19" s="10">
-        <v>258</v>
+        <v>1018</v>
       </c>
       <c r="F19" s="10">
-        <v>36194509.831490748</v>
+        <v>37115893.490185946</v>
       </c>
       <c r="G19" s="10">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="H19" s="10">
         <v>2</v>
@@ -8440,10 +8440,10 @@
         <v>3</v>
       </c>
       <c r="J19" s="10">
-        <v>895</v>
+        <v>913</v>
       </c>
       <c r="K19" s="10">
-        <v>43111493.808943726</v>
+        <v>46248297.021251909</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
@@ -8451,7 +8451,7 @@
         <v>47</v>
       </c>
       <c r="B20" s="10">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="C20" s="10">
         <v>3</v>
@@ -8460,13 +8460,13 @@
         <v>4</v>
       </c>
       <c r="E20" s="10">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="F20" s="10">
-        <v>23300861.495705463</v>
+        <v>24557779.647644848</v>
       </c>
       <c r="G20" s="10">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="H20" s="10">
         <v>4</v>
@@ -8475,10 +8475,10 @@
         <v>5</v>
       </c>
       <c r="J20" s="10">
-        <v>894</v>
+        <v>945</v>
       </c>
       <c r="K20" s="10">
-        <v>23318745.82605692</v>
+        <v>24780324.33078628</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
@@ -8486,7 +8486,7 @@
         <v>49</v>
       </c>
       <c r="B21" s="10">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="C21" s="10">
         <v>1</v>
@@ -8495,13 +8495,13 @@
         <v>3</v>
       </c>
       <c r="E21" s="10">
-        <v>665</v>
+        <v>651</v>
       </c>
       <c r="F21" s="10">
-        <v>22855372.760754973</v>
+        <v>24093521.100269504</v>
       </c>
       <c r="G21" s="10">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="H21" s="10">
         <v>4</v>
@@ -8510,10 +8510,10 @@
         <v>3</v>
       </c>
       <c r="J21" s="10">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="K21" s="10">
-        <v>18884057.695519928</v>
+        <v>20292128.333114807</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
@@ -8521,7 +8521,7 @@
         <v>51</v>
       </c>
       <c r="B22" s="10">
-        <v>3231</v>
+        <v>3219</v>
       </c>
       <c r="C22" s="10">
         <v>624</v>
@@ -8530,25 +8530,25 @@
         <v>10</v>
       </c>
       <c r="E22" s="10">
-        <v>2875</v>
+        <v>2911</v>
       </c>
       <c r="F22" s="10">
-        <v>79706464.844519541</v>
+        <v>84378043.245911941</v>
       </c>
       <c r="G22" s="10">
-        <v>2813</v>
+        <v>2805</v>
       </c>
       <c r="H22" s="10">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="I22" s="10">
         <v>10</v>
       </c>
       <c r="J22" s="10">
-        <v>2092</v>
+        <v>2167</v>
       </c>
       <c r="K22" s="10">
-        <v>86512250.853451744</v>
+        <v>91431790.086039543</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
@@ -8556,7 +8556,7 @@
         <v>53</v>
       </c>
       <c r="B23" s="10">
-        <v>1443</v>
+        <v>1440</v>
       </c>
       <c r="C23" s="10">
         <v>0</v>
@@ -8565,25 +8565,25 @@
         <v>2</v>
       </c>
       <c r="E23" s="10">
-        <v>1188</v>
+        <v>1155</v>
       </c>
       <c r="F23" s="10">
-        <v>43461261.025939107</v>
+        <v>45853440.719571456</v>
       </c>
       <c r="G23" s="10">
         <v>1381</v>
       </c>
       <c r="H23" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I23" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" s="10">
-        <v>1167</v>
+        <v>1192</v>
       </c>
       <c r="K23" s="10">
-        <v>25993637.843131464</v>
+        <v>28580704.230768949</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
@@ -8600,25 +8600,25 @@
         <v>11</v>
       </c>
       <c r="E24" s="10">
-        <v>2522</v>
+        <v>2274</v>
       </c>
       <c r="F24" s="10">
-        <v>87326341.867069647</v>
+        <v>91985409.680114254</v>
       </c>
       <c r="G24" s="10">
-        <v>2936</v>
+        <v>2933</v>
       </c>
       <c r="H24" s="10">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I24" s="10">
         <v>10</v>
       </c>
       <c r="J24" s="10">
-        <v>2002</v>
+        <v>1971</v>
       </c>
       <c r="K24" s="10">
-        <v>87531836.582215488</v>
+        <v>91798677.850888729</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
@@ -8626,7 +8626,7 @@
         <v>67</v>
       </c>
       <c r="B25" s="10">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C25" s="10">
         <v>6</v>
@@ -8635,13 +8635,13 @@
         <v>1</v>
       </c>
       <c r="E25" s="10">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F25" s="10">
-        <v>12335831.009248348</v>
+        <v>13083985.836379612</v>
       </c>
       <c r="G25" s="10">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="H25" s="10">
         <v>5</v>
@@ -8650,10 +8650,10 @@
         <v>1</v>
       </c>
       <c r="J25" s="10">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="K25" s="10">
-        <v>13179743.144659448</v>
+        <v>13952390.293539824</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
@@ -8661,22 +8661,22 @@
         <v>74</v>
       </c>
       <c r="B26" s="10">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="C26" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D26" s="10">
         <v>2</v>
       </c>
       <c r="E26" s="10">
-        <v>1319</v>
+        <v>1256</v>
       </c>
       <c r="F26" s="10">
-        <v>34331182.277683817</v>
+        <v>36202793.63631741</v>
       </c>
       <c r="G26" s="10">
-        <v>1698</v>
+        <v>1679</v>
       </c>
       <c r="H26" s="10">
         <v>17</v>
@@ -8685,10 +8685,10 @@
         <v>1</v>
       </c>
       <c r="J26" s="10">
-        <v>1381</v>
+        <v>1368</v>
       </c>
       <c r="K26" s="10">
-        <v>36181572.167494185</v>
+        <v>38550165.164171152</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
@@ -8696,7 +8696,7 @@
         <v>70</v>
       </c>
       <c r="B27" s="10">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C27" s="10">
         <v>10</v>
@@ -8705,13 +8705,13 @@
         <v>1</v>
       </c>
       <c r="E27" s="10">
-        <v>800</v>
+        <v>1010</v>
       </c>
       <c r="F27" s="10">
-        <v>15055659.969758572</v>
+        <v>15994034.782365471</v>
       </c>
       <c r="G27" s="10">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="H27" s="10">
         <v>10</v>
@@ -8720,10 +8720,10 @@
         <v>1</v>
       </c>
       <c r="J27" s="10">
-        <v>867</v>
+        <v>820</v>
       </c>
       <c r="K27" s="10">
-        <v>15017516.666063774</v>
+        <v>16023991.278544333</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
@@ -8731,7 +8731,7 @@
         <v>72</v>
       </c>
       <c r="B28" s="10">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="C28" s="10">
         <v>2</v>
@@ -8740,25 +8740,25 @@
         <v>1</v>
       </c>
       <c r="E28" s="10">
-        <v>656</v>
+        <v>803</v>
       </c>
       <c r="F28" s="10">
-        <v>16806306.479511511</v>
+        <v>17730094.775826979</v>
       </c>
       <c r="G28" s="10">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H28" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I28" s="10">
         <v>1</v>
       </c>
       <c r="J28" s="10">
-        <v>759</v>
+        <v>843</v>
       </c>
       <c r="K28" s="10">
-        <v>18339133.799450003</v>
+        <v>19429198.640231583</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
@@ -8775,10 +8775,10 @@
         <v>0</v>
       </c>
       <c r="E29" s="10">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="F29" s="10">
-        <v>4978274.1542370617</v>
+        <v>5277024.5563090751</v>
       </c>
       <c r="G29" s="10">
         <v>228</v>
@@ -8787,13 +8787,13 @@
         <v>1</v>
       </c>
       <c r="I29" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J29" s="10">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="K29" s="10">
-        <v>4145553.8044927949</v>
+        <v>4433708.8725122856</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
@@ -8801,7 +8801,7 @@
         <v>109</v>
       </c>
       <c r="B30" s="10">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="C30" s="10">
         <v>2</v>
@@ -8810,13 +8810,13 @@
         <v>5</v>
       </c>
       <c r="E30" s="10">
-        <v>1327</v>
+        <v>1301</v>
       </c>
       <c r="F30" s="10">
-        <v>38180141.640637457</v>
+        <v>40235450.07087151</v>
       </c>
       <c r="G30" s="10">
-        <v>1653</v>
+        <v>1646</v>
       </c>
       <c r="H30" s="10">
         <v>10</v>
@@ -8825,10 +8825,10 @@
         <v>5</v>
       </c>
       <c r="J30" s="10">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="K30" s="10">
-        <v>34673357.838432036</v>
+        <v>36803930.469524823</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
@@ -8836,7 +8836,7 @@
         <v>111</v>
       </c>
       <c r="B31" s="10">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C31" s="10">
         <v>5</v>
@@ -8845,25 +8845,25 @@
         <v>1</v>
       </c>
       <c r="E31" s="10">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="F31" s="10">
-        <v>26798065.721356105</v>
+        <v>28301686.739777543</v>
       </c>
       <c r="G31" s="10">
-        <v>876</v>
+        <v>884</v>
       </c>
       <c r="H31" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I31" s="10">
         <v>1</v>
       </c>
       <c r="J31" s="10">
-        <v>695</v>
+        <v>617</v>
       </c>
       <c r="K31" s="10">
-        <v>28932948.270447984</v>
+        <v>30880741.730442863</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
@@ -8871,7 +8871,7 @@
         <v>113</v>
       </c>
       <c r="B32" s="10">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="C32" s="10">
         <v>2</v>
@@ -8880,13 +8880,13 @@
         <v>1</v>
       </c>
       <c r="E32" s="10">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="F32" s="10">
-        <v>28967105.315619867</v>
+        <v>30771914.979088616</v>
       </c>
       <c r="G32" s="10">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="H32" s="10">
         <v>2</v>
@@ -8895,10 +8895,10 @@
         <v>1</v>
       </c>
       <c r="J32" s="10">
-        <v>623</v>
+        <v>789</v>
       </c>
       <c r="K32" s="10">
-        <v>27314154.578593209</v>
+        <v>29013524.004899658</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
@@ -8906,22 +8906,22 @@
         <v>115</v>
       </c>
       <c r="B33" s="10">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="C33" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" s="10">
         <v>2</v>
       </c>
       <c r="E33" s="10">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="F33" s="10">
-        <v>37440462.056698211</v>
+        <v>39627788.142400511</v>
       </c>
       <c r="G33" s="10">
-        <v>1120</v>
+        <v>1125</v>
       </c>
       <c r="H33" s="10">
         <v>3</v>
@@ -8930,10 +8930,10 @@
         <v>2</v>
       </c>
       <c r="J33" s="10">
-        <v>1017</v>
+        <v>874</v>
       </c>
       <c r="K33" s="10">
-        <v>38738095.034786858</v>
+        <v>41174058.474659473</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
@@ -8941,22 +8941,22 @@
         <v>16</v>
       </c>
       <c r="B34" s="10">
-        <v>1500</v>
+        <v>1503</v>
       </c>
       <c r="C34" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D34" s="10">
         <v>5</v>
       </c>
       <c r="E34" s="10">
-        <v>1170</v>
+        <v>1103</v>
       </c>
       <c r="F34" s="10">
-        <v>54625541.40816319</v>
+        <v>57867671.527397662</v>
       </c>
       <c r="G34" s="10">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="H34" s="10">
         <v>4</v>
@@ -8965,10 +8965,10 @@
         <v>4</v>
       </c>
       <c r="J34" s="10">
-        <v>1153</v>
+        <v>1132</v>
       </c>
       <c r="K34" s="10">
-        <v>49689744.933685243</v>
+        <v>52940271.569831714</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
@@ -8976,22 +8976,22 @@
         <v>18</v>
       </c>
       <c r="B35" s="10">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C35" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D35" s="10">
         <v>3</v>
       </c>
       <c r="E35" s="10">
-        <v>546</v>
+        <v>535</v>
       </c>
       <c r="F35" s="10">
-        <v>20563796.033259295</v>
+        <v>21899406.198145673</v>
       </c>
       <c r="G35" s="10">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="H35" s="10">
         <v>1</v>
@@ -9000,10 +9000,10 @@
         <v>5</v>
       </c>
       <c r="J35" s="10">
-        <v>657</v>
+        <v>554</v>
       </c>
       <c r="K35" s="10">
-        <v>22475660.079455785</v>
+        <v>23896792.324472841</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
@@ -9011,34 +9011,34 @@
         <v>43</v>
       </c>
       <c r="B36" s="10">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="C36" s="10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D36" s="10">
         <v>11</v>
       </c>
       <c r="E36" s="10">
-        <v>1942</v>
+        <v>1890</v>
       </c>
       <c r="F36" s="10">
-        <v>64619883.099481747</v>
+        <v>68379291.574158043</v>
       </c>
       <c r="G36" s="10">
-        <v>1923</v>
+        <v>1926</v>
       </c>
       <c r="H36" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I36" s="10">
         <v>9</v>
       </c>
       <c r="J36" s="10">
-        <v>1597</v>
+        <v>1575</v>
       </c>
       <c r="K36" s="10">
-        <v>54641880.595996283</v>
+        <v>58685299.940138116</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
@@ -9046,7 +9046,7 @@
         <v>152</v>
       </c>
       <c r="B37" s="10">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="C37" s="10">
         <v>2</v>
@@ -9055,13 +9055,13 @@
         <v>2</v>
       </c>
       <c r="E37" s="10">
-        <v>676</v>
+        <v>620</v>
       </c>
       <c r="F37" s="10">
-        <v>22177650.670513704</v>
+        <v>23416239.072707906</v>
       </c>
       <c r="G37" s="10">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="H37" s="10">
         <v>3</v>
@@ -9070,10 +9070,10 @@
         <v>2</v>
       </c>
       <c r="J37" s="10">
-        <v>699</v>
+        <v>712</v>
       </c>
       <c r="K37" s="10">
-        <v>22648991.031854369</v>
+        <v>23846332.143704496</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
@@ -9081,7 +9081,7 @@
         <v>149</v>
       </c>
       <c r="B38" s="10">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C38" s="10">
         <v>2</v>
@@ -9090,13 +9090,13 @@
         <v>1</v>
       </c>
       <c r="E38" s="10">
-        <v>550</v>
+        <v>534</v>
       </c>
       <c r="F38" s="10">
-        <v>18494684.231714644</v>
+        <v>19580984.263010703</v>
       </c>
       <c r="G38" s="10">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="H38" s="10">
         <v>3</v>
@@ -9105,10 +9105,10 @@
         <v>1</v>
       </c>
       <c r="J38" s="10">
-        <v>560</v>
+        <v>644</v>
       </c>
       <c r="K38" s="10">
-        <v>20507947.028976176</v>
+        <v>21933834.462986201</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
@@ -9116,22 +9116,22 @@
         <v>154</v>
       </c>
       <c r="B39" s="10">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="C39" s="10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D39" s="10">
         <v>2</v>
       </c>
       <c r="E39" s="10">
-        <v>879</v>
+        <v>843</v>
       </c>
       <c r="F39" s="10">
-        <v>32415149.402387757</v>
+        <v>34271546.343865938</v>
       </c>
       <c r="G39" s="10">
-        <v>1162</v>
+        <v>1148</v>
       </c>
       <c r="H39" s="10">
         <v>17</v>
@@ -9140,10 +9140,10 @@
         <v>1</v>
       </c>
       <c r="J39" s="10">
-        <v>849</v>
+        <v>950</v>
       </c>
       <c r="K39" s="10">
-        <v>31697377.625365242</v>
+        <v>33947334.926795498</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
@@ -9151,7 +9151,7 @@
         <v>2</v>
       </c>
       <c r="B40" s="10">
-        <v>1098</v>
+        <v>1089</v>
       </c>
       <c r="C40" s="10">
         <v>41</v>
@@ -9160,13 +9160,13 @@
         <v>1</v>
       </c>
       <c r="E40" s="10">
-        <v>749</v>
+        <v>769</v>
       </c>
       <c r="F40" s="10">
-        <v>31422622.587050565</v>
+        <v>33052464.113899976</v>
       </c>
       <c r="G40" s="10">
-        <v>1271</v>
+        <v>1252</v>
       </c>
       <c r="H40" s="10">
         <v>121</v>
@@ -9175,10 +9175,10 @@
         <v>1</v>
       </c>
       <c r="J40" s="10">
-        <v>880</v>
+        <v>964</v>
       </c>
       <c r="K40" s="10">
-        <v>29999625.405255064</v>
+        <v>32190582.015026674</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
@@ -9186,7 +9186,7 @@
         <v>156</v>
       </c>
       <c r="B41" s="10">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="C41" s="10">
         <v>55</v>
@@ -9195,25 +9195,25 @@
         <v>4</v>
       </c>
       <c r="E41" s="10">
-        <v>1328</v>
+        <v>1371</v>
       </c>
       <c r="F41" s="10">
-        <v>49380423.194518387</v>
+        <v>52158232.747112714</v>
       </c>
       <c r="G41" s="10">
-        <v>2274</v>
+        <v>2269</v>
       </c>
       <c r="H41" s="10">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I41" s="10">
         <v>5</v>
       </c>
       <c r="J41" s="10">
-        <v>1420</v>
+        <v>1578</v>
       </c>
       <c r="K41" s="10">
-        <v>54072727.66768647</v>
+        <v>57989157.172912218</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
@@ -9221,22 +9221,22 @@
         <v>14</v>
       </c>
       <c r="B42" s="10">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="C42" s="10">
         <v>2</v>
       </c>
       <c r="D42" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E42" s="10">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F42" s="10">
-        <v>17501175.169462778</v>
+        <v>17501175.59762124</v>
       </c>
       <c r="G42" s="10">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="H42" s="10">
         <v>1</v>
@@ -9245,10 +9245,10 @@
         <v>6</v>
       </c>
       <c r="J42" s="10">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="K42" s="10">
-        <v>19553902.07009979</v>
+        <v>20656820.414189544</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
@@ -9256,34 +9256,34 @@
         <v>8</v>
       </c>
       <c r="B43" s="10">
-        <v>2026</v>
+        <v>2036</v>
       </c>
       <c r="C43" s="10">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D43" s="10">
         <v>5</v>
       </c>
       <c r="E43" s="10">
-        <v>1885</v>
+        <v>1869</v>
       </c>
       <c r="F43" s="10">
-        <v>58094258.463035837</v>
+        <v>61288523.598765254</v>
       </c>
       <c r="G43" s="10">
-        <v>2052</v>
+        <v>2059</v>
       </c>
       <c r="H43" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I43" s="10">
         <v>6</v>
       </c>
       <c r="J43" s="10">
-        <v>1899</v>
+        <v>1991</v>
       </c>
       <c r="K43" s="10">
-        <v>62788078.791813053</v>
+        <v>66763112.972614646</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.35">
@@ -9291,7 +9291,7 @@
         <v>39</v>
       </c>
       <c r="B44" s="10">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C44" s="10">
         <v>6</v>
@@ -9300,25 +9300,25 @@
         <v>4</v>
       </c>
       <c r="E44" s="10">
-        <v>823</v>
+        <v>760</v>
       </c>
       <c r="F44" s="10">
-        <v>40259525.860920064</v>
+        <v>42805016.573299475</v>
       </c>
       <c r="G44" s="10">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="H44" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I44" s="10">
         <v>4</v>
       </c>
       <c r="J44" s="10">
-        <v>849</v>
+        <v>797</v>
       </c>
       <c r="K44" s="10">
-        <v>43702130.166758053</v>
+        <v>46227650.783002853</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.35">
@@ -9326,7 +9326,7 @@
         <v>6</v>
       </c>
       <c r="B45" s="10">
-        <v>1123</v>
+        <v>1116</v>
       </c>
       <c r="C45" s="10">
         <v>3</v>
@@ -9335,25 +9335,25 @@
         <v>3</v>
       </c>
       <c r="E45" s="10">
-        <v>932</v>
+        <v>996</v>
       </c>
       <c r="F45" s="10">
-        <v>33706233.502371065</v>
+        <v>35305267.70624648</v>
       </c>
       <c r="G45" s="10">
         <v>1097</v>
       </c>
       <c r="H45" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I45" s="10">
         <v>3</v>
       </c>
       <c r="J45" s="10">
-        <v>1095</v>
+        <v>1158</v>
       </c>
       <c r="K45" s="10">
-        <v>25153289.147385843</v>
+        <v>27034432.239690185</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
@@ -9361,7 +9361,7 @@
         <v>41</v>
       </c>
       <c r="B46" s="10">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="C46" s="10">
         <v>0</v>
@@ -9370,13 +9370,13 @@
         <v>5</v>
       </c>
       <c r="E46" s="10">
-        <v>623</v>
+        <v>636</v>
       </c>
       <c r="F46" s="10">
-        <v>32761795.611114733</v>
+        <v>34656045.854344085</v>
       </c>
       <c r="G46" s="10">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="H46" s="10">
         <v>5</v>
@@ -9385,10 +9385,10 @@
         <v>4</v>
       </c>
       <c r="J46" s="10">
-        <v>573</v>
+        <v>612</v>
       </c>
       <c r="K46" s="10">
-        <v>32727427.435014695</v>
+        <v>34623144.718677483</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.35">
@@ -9396,7 +9396,7 @@
         <v>158</v>
       </c>
       <c r="B47" s="10">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C47" s="10">
         <v>3</v>
@@ -9405,25 +9405,25 @@
         <v>10</v>
       </c>
       <c r="E47" s="10">
-        <v>607</v>
+        <v>570</v>
       </c>
       <c r="F47" s="10">
-        <v>20342697.235315848</v>
+        <v>21610464.703248747</v>
       </c>
       <c r="G47" s="10">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="H47" s="10">
         <v>3</v>
       </c>
       <c r="I47" s="10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J47" s="10">
-        <v>671</v>
+        <v>123</v>
       </c>
       <c r="K47" s="10">
-        <v>21247499.714460559</v>
+        <v>21742784.05233898</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.35">
@@ -9431,7 +9431,7 @@
         <v>160</v>
       </c>
       <c r="B48" s="10">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="C48" s="10">
         <v>1</v>
@@ -9440,13 +9440,13 @@
         <v>1</v>
       </c>
       <c r="E48" s="10">
-        <v>691</v>
+        <v>721</v>
       </c>
       <c r="F48" s="10">
-        <v>19467108.785032246</v>
+        <v>20687868.148741201</v>
       </c>
       <c r="G48" s="10">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="H48" s="10">
         <v>0</v>
@@ -9455,10 +9455,10 @@
         <v>1</v>
       </c>
       <c r="J48" s="10">
-        <v>732</v>
+        <v>389</v>
       </c>
       <c r="K48" s="10">
-        <v>18175582.361618567</v>
+        <v>18652888.434304617</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
@@ -9466,34 +9466,34 @@
         <v>83</v>
       </c>
       <c r="B49" s="10">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="C49" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D49" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E49" s="10">
-        <v>1103</v>
+        <v>1085</v>
       </c>
       <c r="F49" s="10">
-        <v>62477023.740561083</v>
+        <v>65941089.434293799</v>
       </c>
       <c r="G49" s="10">
-        <v>1238</v>
+        <v>1243</v>
       </c>
       <c r="H49" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I49" s="10">
         <v>5</v>
       </c>
       <c r="J49" s="10">
-        <v>1454</v>
+        <v>1418</v>
       </c>
       <c r="K49" s="10">
-        <v>58038275.749017172</v>
+        <v>62024410.34365315</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
@@ -9510,13 +9510,13 @@
         <v>2</v>
       </c>
       <c r="E50" s="10">
-        <v>451</v>
+        <v>434</v>
       </c>
       <c r="F50" s="10">
-        <v>11376658.915109288</v>
+        <v>12042453.550795225</v>
       </c>
       <c r="G50" s="10">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="H50" s="10">
         <v>1</v>
@@ -9525,10 +9525,10 @@
         <v>1</v>
       </c>
       <c r="J50" s="10">
-        <v>440</v>
+        <v>474</v>
       </c>
       <c r="K50" s="10">
-        <v>9365285.4537124839</v>
+        <v>9974558.4401260205</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
@@ -9536,7 +9536,7 @@
         <v>31</v>
       </c>
       <c r="B51" s="10">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C51" s="10">
         <v>2</v>
@@ -9545,25 +9545,25 @@
         <v>5</v>
       </c>
       <c r="E51" s="10">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="F51" s="10">
-        <v>28184934.114670154</v>
+        <v>29718671.064681828</v>
       </c>
       <c r="G51" s="10">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="H51" s="10">
         <v>3</v>
       </c>
       <c r="I51" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J51" s="10">
-        <v>939</v>
+        <v>931</v>
       </c>
       <c r="K51" s="10">
-        <v>27492791.124575771</v>
+        <v>29054377.526877664</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
@@ -9571,22 +9571,22 @@
         <v>33</v>
       </c>
       <c r="B52" s="10">
-        <v>1306</v>
+        <v>1303</v>
       </c>
       <c r="C52" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D52" s="10">
         <v>12</v>
       </c>
       <c r="E52" s="10">
-        <v>1003</v>
+        <v>979</v>
       </c>
       <c r="F52" s="10">
-        <v>41289989.144723333</v>
+        <v>43797964.177689955</v>
       </c>
       <c r="G52" s="10">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H52" s="10">
         <v>5</v>
@@ -9595,10 +9595,10 @@
         <v>12</v>
       </c>
       <c r="J52" s="10">
-        <v>951</v>
+        <v>1023</v>
       </c>
       <c r="K52" s="10">
-        <v>47993219.130776621</v>
+        <v>50825033.960358381</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.35">
@@ -9606,7 +9606,7 @@
         <v>85</v>
       </c>
       <c r="B53" s="10">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C53" s="10">
         <v>7</v>
@@ -9615,13 +9615,13 @@
         <v>5</v>
       </c>
       <c r="E53" s="10">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F53" s="10">
-        <v>21359608.09983848</v>
+        <v>22770248.911103602</v>
       </c>
       <c r="G53" s="10">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="H53" s="10">
         <v>1</v>
@@ -9630,10 +9630,10 @@
         <v>6</v>
       </c>
       <c r="J53" s="10">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="K53" s="10">
-        <v>24793926.215664741</v>
+        <v>26152148.725233007</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.35">
@@ -9644,19 +9644,19 @@
         <v>444</v>
       </c>
       <c r="C54" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E54" s="10">
-        <v>2191</v>
+        <v>298</v>
       </c>
       <c r="F54" s="10">
-        <v>21478198.433565818</v>
+        <v>22546305.818256099</v>
       </c>
       <c r="G54" s="10">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="H54" s="10">
         <v>0</v>
@@ -9665,10 +9665,10 @@
         <v>4</v>
       </c>
       <c r="J54" s="10">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="K54" s="10">
-        <v>18005875.489039745</v>
+        <v>19126089.304449983</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.35">
@@ -9676,7 +9676,7 @@
         <v>87</v>
       </c>
       <c r="B55" s="10">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C55" s="10">
         <v>11</v>
@@ -9685,25 +9685,25 @@
         <v>2</v>
       </c>
       <c r="E55" s="10">
-        <v>351</v>
+        <v>378</v>
       </c>
       <c r="F55" s="10">
-        <v>17676503.12317507</v>
+        <v>18657852.426756896</v>
       </c>
       <c r="G55" s="10">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H55" s="10">
         <v>2</v>
       </c>
       <c r="I55" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J55" s="10">
-        <v>335</v>
+        <v>367</v>
       </c>
       <c r="K55" s="10">
-        <v>15802232.271788953</v>
+        <v>16764643.498383747</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.35">
@@ -9720,13 +9720,13 @@
         <v>1</v>
       </c>
       <c r="E56" s="10">
-        <v>997</v>
+        <v>927</v>
       </c>
       <c r="F56" s="10">
-        <v>38319010.734158374</v>
+        <v>40544706.538535334</v>
       </c>
       <c r="G56" s="10">
-        <v>1104</v>
+        <v>1100</v>
       </c>
       <c r="H56" s="10">
         <v>5</v>
@@ -9735,10 +9735,10 @@
         <v>1</v>
       </c>
       <c r="J56" s="10">
-        <v>921</v>
+        <v>939</v>
       </c>
       <c r="K56" s="10">
-        <v>37135022.236871041</v>
+        <v>39213836.923041739</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
@@ -9746,22 +9746,22 @@
         <v>93</v>
       </c>
       <c r="B57" s="10">
-        <v>967</v>
+        <v>980</v>
       </c>
       <c r="C57" s="10">
         <v>10</v>
       </c>
       <c r="D57" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E57" s="10">
-        <v>867</v>
+        <v>841</v>
       </c>
       <c r="F57" s="10">
-        <v>40505878.641760208</v>
+        <v>42886891.103262864</v>
       </c>
       <c r="G57" s="10">
-        <v>1009</v>
+        <v>1014</v>
       </c>
       <c r="H57" s="10">
         <v>7</v>
@@ -9770,10 +9770,10 @@
         <v>1</v>
       </c>
       <c r="J57" s="10">
-        <v>926</v>
+        <v>862</v>
       </c>
       <c r="K57" s="10">
-        <v>38633184.860168822</v>
+        <v>40939585.895147137</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.35">
@@ -9781,7 +9781,7 @@
         <v>95</v>
       </c>
       <c r="B58" s="10">
-        <v>2161</v>
+        <v>2163</v>
       </c>
       <c r="C58" s="10">
         <v>36</v>
@@ -9790,25 +9790,25 @@
         <v>7</v>
       </c>
       <c r="E58" s="10">
-        <v>1656</v>
+        <v>1709</v>
       </c>
       <c r="F58" s="10">
-        <v>56342722.856981687</v>
+        <v>60223755.032434106</v>
       </c>
       <c r="G58" s="10">
-        <v>2036</v>
+        <v>2043</v>
       </c>
       <c r="H58" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I58" s="10">
         <v>8</v>
       </c>
       <c r="J58" s="10">
-        <v>1773</v>
+        <v>1735</v>
       </c>
       <c r="K58" s="10">
-        <v>69474698.048531413</v>
+        <v>73666459.599487707</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.35">
@@ -9816,7 +9816,7 @@
         <v>174</v>
       </c>
       <c r="B59" s="10">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="C59" s="10">
         <v>3</v>
@@ -9825,13 +9825,13 @@
         <v>0</v>
       </c>
       <c r="E59" s="10">
-        <v>528</v>
+        <v>555</v>
       </c>
       <c r="F59" s="10">
-        <v>18581528.074724223</v>
+        <v>19628260.883901495</v>
       </c>
       <c r="G59" s="10">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="H59" s="10">
         <v>4</v>
@@ -9840,10 +9840,10 @@
         <v>0</v>
       </c>
       <c r="J59" s="10">
-        <v>498</v>
+        <v>550</v>
       </c>
       <c r="K59" s="10">
-        <v>17379391.950311348</v>
+        <v>18415275.797894016</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.35">
@@ -9851,7 +9851,7 @@
         <v>99</v>
       </c>
       <c r="B60" s="10">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="C60" s="10">
         <v>6</v>
@@ -9860,25 +9860,25 @@
         <v>5</v>
       </c>
       <c r="E60" s="10">
-        <v>794</v>
+        <v>830</v>
       </c>
       <c r="F60" s="10">
-        <v>28675817.814602911</v>
+        <v>30615413.367241357</v>
       </c>
       <c r="G60" s="10">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="H60" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I60" s="10">
         <v>5</v>
       </c>
       <c r="J60" s="10">
-        <v>790</v>
+        <v>740</v>
       </c>
       <c r="K60" s="10">
-        <v>30317184.127649944</v>
+        <v>32094490.60502778</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.35">
@@ -9886,7 +9886,7 @@
         <v>172</v>
       </c>
       <c r="B61" s="10">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="C61" s="10">
         <v>3</v>
@@ -9895,13 +9895,13 @@
         <v>1</v>
       </c>
       <c r="E61" s="10">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="F61" s="10">
-        <v>22481594.447822541</v>
+        <v>23662873.351727627</v>
       </c>
       <c r="G61" s="10">
-        <v>746</v>
+        <v>734</v>
       </c>
       <c r="H61" s="10">
         <v>4</v>
@@ -9910,10 +9910,10 @@
         <v>1</v>
       </c>
       <c r="J61" s="10">
-        <v>658</v>
+        <v>635</v>
       </c>
       <c r="K61" s="10">
-        <v>19189044.107355248</v>
+        <v>20317389.490997106</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.35">
@@ -9921,7 +9921,7 @@
         <v>168</v>
       </c>
       <c r="B62" s="10">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="C62" s="10">
         <v>8</v>
@@ -9930,13 +9930,13 @@
         <v>1</v>
       </c>
       <c r="E62" s="10">
-        <v>1106</v>
+        <v>1070</v>
       </c>
       <c r="F62" s="10">
-        <v>38270861.122598462</v>
+        <v>40636216.140523255</v>
       </c>
       <c r="G62" s="10">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="H62" s="10">
         <v>7</v>
@@ -9945,10 +9945,10 @@
         <v>0</v>
       </c>
       <c r="J62" s="10">
-        <v>938</v>
+        <v>977</v>
       </c>
       <c r="K62" s="10">
-        <v>38656329.906607106</v>
+        <v>40981093.886455111</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.35">
@@ -9956,34 +9956,34 @@
         <v>101</v>
       </c>
       <c r="B63" s="10">
-        <v>1361</v>
+        <v>1370</v>
       </c>
       <c r="C63" s="10">
+        <v>11</v>
+      </c>
+      <c r="D63" s="10">
+        <v>4</v>
+      </c>
+      <c r="E63" s="10">
+        <v>1343</v>
+      </c>
+      <c r="F63" s="10">
+        <v>51975399.294892192</v>
+      </c>
+      <c r="G63" s="10">
+        <v>1503</v>
+      </c>
+      <c r="H63" s="10">
         <v>10</v>
       </c>
-      <c r="D63" s="10">
-        <v>4</v>
-      </c>
-      <c r="E63" s="10">
-        <v>1410</v>
-      </c>
-      <c r="F63" s="10">
-        <v>49094951.780632906</v>
-      </c>
-      <c r="G63" s="10">
-        <v>1497</v>
-      </c>
-      <c r="H63" s="10">
-        <v>8</v>
-      </c>
       <c r="I63" s="10">
         <v>4</v>
       </c>
       <c r="J63" s="10">
-        <v>1041</v>
+        <v>1408</v>
       </c>
       <c r="K63" s="10">
-        <v>47134937.423156217</v>
+        <v>50074452.206668533</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.35">
@@ -9991,22 +9991,22 @@
         <v>103</v>
       </c>
       <c r="B64" s="10">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C64" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D64" s="10">
         <v>5</v>
       </c>
       <c r="E64" s="10">
-        <v>678</v>
+        <v>751</v>
       </c>
       <c r="F64" s="10">
-        <v>24841033.532271557</v>
+        <v>26207240.497092113</v>
       </c>
       <c r="G64" s="10">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="H64" s="10">
         <v>2</v>
@@ -10015,10 +10015,10 @@
         <v>4</v>
       </c>
       <c r="J64" s="10">
-        <v>754</v>
+        <v>682</v>
       </c>
       <c r="K64" s="10">
-        <v>26286574.062764719</v>
+        <v>27821994.716877595</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.35">
@@ -10035,13 +10035,13 @@
         <v>5</v>
       </c>
       <c r="E65" s="10">
-        <v>448</v>
+        <v>483</v>
       </c>
       <c r="F65" s="10">
-        <v>29096685.519441087</v>
+        <v>30690396.011699993</v>
       </c>
       <c r="G65" s="10">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="H65" s="10">
         <v>9</v>
@@ -10050,10 +10050,10 @@
         <v>5</v>
       </c>
       <c r="J65" s="10">
-        <v>470</v>
+        <v>453</v>
       </c>
       <c r="K65" s="10">
-        <v>29372784.881242465</v>
+        <v>31019483.13461696</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.35">
@@ -10061,34 +10061,34 @@
         <v>24</v>
       </c>
       <c r="B66" s="10">
-        <v>2035</v>
+        <v>2047</v>
       </c>
       <c r="C66" s="10">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D66" s="10">
         <v>9</v>
       </c>
       <c r="E66" s="10">
-        <v>1676</v>
+        <v>1869</v>
       </c>
       <c r="F66" s="10">
-        <v>75334047.475907341</v>
+        <v>80494151.517660826</v>
       </c>
       <c r="G66" s="10">
-        <v>1990</v>
+        <v>1999</v>
       </c>
       <c r="H66" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I66" s="10">
         <v>11</v>
       </c>
       <c r="J66" s="10">
-        <v>1567</v>
+        <v>1607</v>
       </c>
       <c r="K66" s="10">
-        <v>94609229.45671463</v>
+        <v>99819639.769979075</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.35">
@@ -10096,22 +10096,22 @@
         <v>27</v>
       </c>
       <c r="B67" s="10">
-        <v>1602</v>
+        <v>1597</v>
       </c>
       <c r="C67" s="10">
         <v>19</v>
       </c>
       <c r="D67" s="10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E67" s="10">
-        <v>1193</v>
+        <v>1177</v>
       </c>
       <c r="F67" s="10">
-        <v>70479993.177585602</v>
+        <v>74403597.224619329</v>
       </c>
       <c r="G67" s="10">
-        <v>1599</v>
+        <v>1602</v>
       </c>
       <c r="H67" s="10">
         <v>16</v>
@@ -10120,10 +10120,10 @@
         <v>6</v>
       </c>
       <c r="J67" s="10">
-        <v>1356</v>
+        <v>1376</v>
       </c>
       <c r="K67" s="10">
-        <v>70751538.977041662</v>
+        <v>75202591.101204753</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.35">
@@ -10131,7 +10131,7 @@
         <v>29</v>
       </c>
       <c r="B68" s="10">
-        <v>860</v>
+        <v>852</v>
       </c>
       <c r="C68" s="10">
         <v>2</v>
@@ -10140,13 +10140,13 @@
         <v>1</v>
       </c>
       <c r="E68" s="10">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="F68" s="10">
-        <v>43706336.685455166</v>
+        <v>46188082.820514478</v>
       </c>
       <c r="G68" s="10">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="H68" s="10">
         <v>7</v>
@@ -10155,10 +10155,10 @@
         <v>1</v>
       </c>
       <c r="J68" s="10">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="K68" s="10">
-        <v>45651879.400535792</v>
+        <v>48323897.682485439</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.35">
@@ -10166,7 +10166,7 @@
         <v>57</v>
       </c>
       <c r="B69" s="10">
-        <v>2008</v>
+        <v>1999</v>
       </c>
       <c r="C69" s="10">
         <v>244</v>
@@ -10175,25 +10175,25 @@
         <v>13</v>
       </c>
       <c r="E69" s="10">
-        <v>1463</v>
+        <v>1445</v>
       </c>
       <c r="F69" s="10">
-        <v>64357523.01838614</v>
+        <v>67882627.172021404</v>
       </c>
       <c r="G69" s="10">
-        <v>2204</v>
+        <v>2271</v>
       </c>
       <c r="H69" s="10">
-        <v>377</v>
+        <v>475</v>
       </c>
       <c r="I69" s="10">
         <v>12</v>
       </c>
       <c r="J69" s="10">
-        <v>1245</v>
+        <v>1277</v>
       </c>
       <c r="K69" s="10">
-        <v>67636200.907637477</v>
+        <v>71504925.88939625</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.35">
@@ -10201,7 +10201,7 @@
         <v>137</v>
       </c>
       <c r="B70" s="10">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C70" s="10">
         <v>2</v>
@@ -10210,10 +10210,10 @@
         <v>1</v>
       </c>
       <c r="E70" s="10">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="F70" s="10">
-        <v>4831983.2646832503</v>
+        <v>5076964.1164683579</v>
       </c>
       <c r="G70" s="10">
         <v>252</v>
@@ -10225,10 +10225,10 @@
         <v>1</v>
       </c>
       <c r="J70" s="10">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="K70" s="10">
-        <v>2632017.6643952979</v>
+        <v>2920456.5121259899</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.35">
@@ -10236,7 +10236,7 @@
         <v>10</v>
       </c>
       <c r="B71" s="10">
-        <v>1781</v>
+        <v>1805</v>
       </c>
       <c r="C71" s="10">
         <v>6</v>
@@ -10245,13 +10245,13 @@
         <v>7</v>
       </c>
       <c r="E71" s="10">
-        <v>1517</v>
+        <v>1560</v>
       </c>
       <c r="F71" s="10">
-        <v>50773613.3984451</v>
+        <v>53626628.117396288</v>
       </c>
       <c r="G71" s="10">
-        <v>1663</v>
+        <v>1667</v>
       </c>
       <c r="H71" s="10">
         <v>9</v>
@@ -10260,10 +10260,10 @@
         <v>6</v>
       </c>
       <c r="J71" s="10">
-        <v>1571</v>
+        <v>1921</v>
       </c>
       <c r="K71" s="10">
-        <v>48982194.351211667</v>
+        <v>51942957.043750465</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.35">
@@ -10271,7 +10271,7 @@
         <v>12</v>
       </c>
       <c r="B72" s="10">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="C72" s="10">
         <v>2</v>
@@ -10280,13 +10280,13 @@
         <v>2</v>
       </c>
       <c r="E72" s="10">
-        <v>571</v>
+        <v>610</v>
       </c>
       <c r="F72" s="10">
-        <v>20933770.783716775</v>
+        <v>21968090.95705428</v>
       </c>
       <c r="G72" s="10">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="H72" s="10">
         <v>3</v>
@@ -10295,10 +10295,10 @@
         <v>3</v>
       </c>
       <c r="J72" s="10">
-        <v>614</v>
+        <v>763</v>
       </c>
       <c r="K72" s="10">
-        <v>23094311.445282642</v>
+        <v>24581273.682099607</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.35">
@@ -10306,7 +10306,7 @@
         <v>162</v>
       </c>
       <c r="B73" s="10">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="C73" s="10">
         <v>45</v>
@@ -10315,25 +10315,25 @@
         <v>5</v>
       </c>
       <c r="E73" s="10">
-        <v>1189</v>
+        <v>1260</v>
       </c>
       <c r="F73" s="10">
-        <v>34166560.655513391</v>
+        <v>36202729.775051877</v>
       </c>
       <c r="G73" s="10">
-        <v>1391</v>
+        <v>1382</v>
       </c>
       <c r="H73" s="10">
         <v>23</v>
       </c>
       <c r="I73" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J73" s="10">
-        <v>982</v>
+        <v>1532</v>
       </c>
       <c r="K73" s="10">
-        <v>34962922.177493237</v>
+        <v>37415644.270037763</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.35">
@@ -10341,7 +10341,7 @@
         <v>63</v>
       </c>
       <c r="B74" s="10">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="C74" s="10">
         <v>7</v>
@@ -10350,25 +10350,25 @@
         <v>5</v>
       </c>
       <c r="E74" s="10">
-        <v>853</v>
+        <v>1260</v>
       </c>
       <c r="F74" s="10">
-        <v>17151283.369032022</v>
+        <v>17783711.442227617</v>
       </c>
       <c r="G74" s="10">
-        <v>1253</v>
+        <v>1256</v>
       </c>
       <c r="H74" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I74" s="10">
         <v>5</v>
       </c>
       <c r="J74" s="10">
-        <v>1208</v>
+        <v>1215</v>
       </c>
       <c r="K74" s="10">
-        <v>22198382.348371297</v>
+        <v>23929894.673063796</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.35">
@@ -10376,22 +10376,22 @@
         <v>59</v>
       </c>
       <c r="B75" s="10">
-        <v>1751</v>
+        <v>1746</v>
       </c>
       <c r="C75" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D75" s="10">
         <v>5</v>
       </c>
       <c r="E75" s="10">
-        <v>1210</v>
+        <v>1180</v>
       </c>
       <c r="F75" s="10">
-        <v>60080748.523181163</v>
+        <v>63481150.813349932</v>
       </c>
       <c r="G75" s="10">
-        <v>1758</v>
+        <v>1732</v>
       </c>
       <c r="H75" s="10">
         <v>13</v>
@@ -10400,10 +10400,10 @@
         <v>5</v>
       </c>
       <c r="J75" s="10">
-        <v>1241</v>
+        <v>1259</v>
       </c>
       <c r="K75" s="10">
-        <v>61224476.983174697</v>
+        <v>65060314.538961947</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.35">
@@ -10411,22 +10411,22 @@
         <v>139</v>
       </c>
       <c r="B76" s="10">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="C76" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D76" s="10">
         <v>2</v>
       </c>
       <c r="E76" s="10">
-        <v>494</v>
+        <v>424</v>
       </c>
       <c r="F76" s="10">
-        <v>13156020.104537236</v>
+        <v>13786630.717428997</v>
       </c>
       <c r="G76" s="10">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="H76" s="10">
         <v>2</v>
@@ -10435,10 +10435,10 @@
         <v>1</v>
       </c>
       <c r="J76" s="10">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="K76" s="10">
-        <v>12385983.388492895</v>
+        <v>13044733.106628915</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.35">
@@ -10446,7 +10446,7 @@
         <v>170</v>
       </c>
       <c r="B77" s="10">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="C77" s="10">
         <v>4</v>
@@ -10455,13 +10455,13 @@
         <v>1</v>
       </c>
       <c r="E77" s="10">
-        <v>834</v>
+        <v>790</v>
       </c>
       <c r="F77" s="10">
-        <v>19982061.397274464</v>
+        <v>21117188.467634171</v>
       </c>
       <c r="G77" s="10">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H77" s="10">
         <v>2</v>
@@ -10470,10 +10470,10 @@
         <v>1</v>
       </c>
       <c r="J77" s="10">
-        <v>791</v>
+        <v>808</v>
       </c>
       <c r="K77" s="10">
-        <v>19938681.662497777</v>
+        <v>21197941.625014752</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.35">
@@ -10481,7 +10481,7 @@
         <v>61</v>
       </c>
       <c r="B78" s="10">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="C78" s="10">
         <v>2</v>
@@ -10490,25 +10490,25 @@
         <v>4</v>
       </c>
       <c r="E78" s="10">
-        <v>633</v>
+        <v>416</v>
       </c>
       <c r="F78" s="10">
-        <v>14294811.694408428</v>
+        <v>14736341.28762248</v>
       </c>
       <c r="G78" s="10">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="H78" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I78" s="10">
         <v>3</v>
       </c>
       <c r="J78" s="10">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="K78" s="10">
-        <v>19626666.190058872</v>
+        <v>20935184.704319578</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.35">
@@ -10516,7 +10516,7 @@
         <v>129</v>
       </c>
       <c r="B79" s="10">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="C79" s="10">
         <v>5</v>
@@ -10525,10 +10525,10 @@
         <v>1</v>
       </c>
       <c r="E79" s="10">
-        <v>352</v>
+        <v>12</v>
       </c>
       <c r="F79" s="10">
-        <v>13802610.510686357</v>
+        <v>13803241.814353952</v>
       </c>
       <c r="G79" s="10">
         <v>616</v>
@@ -10540,10 +10540,10 @@
         <v>1</v>
       </c>
       <c r="J79" s="10">
-        <v>596</v>
+        <v>551</v>
       </c>
       <c r="K79" s="10">
-        <v>14965299.75582342</v>
+        <v>15506233.992221871</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.35">
@@ -10551,34 +10551,34 @@
         <v>35</v>
       </c>
       <c r="B80" s="10">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C80" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D80" s="10">
         <v>6</v>
       </c>
       <c r="E80" s="10">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="F80" s="10">
-        <v>15323299.284381747</v>
+        <v>16238993.027723324</v>
       </c>
       <c r="G80" s="10">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="H80" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I80" s="10">
         <v>7</v>
       </c>
       <c r="J80" s="10">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="K80" s="10">
-        <v>16528959.138679625</v>
+        <v>17523590.520165198</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.35">
@@ -10592,28 +10592,28 @@
         <v>9</v>
       </c>
       <c r="D81" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E81" s="10">
-        <v>736</v>
+        <v>550</v>
       </c>
       <c r="F81" s="10">
-        <v>44142138.429326862</v>
+        <v>46538332.60440968</v>
       </c>
       <c r="G81" s="10">
-        <v>919</v>
+        <v>908</v>
       </c>
       <c r="H81" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I81" s="10">
         <v>3</v>
       </c>
       <c r="J81" s="10">
-        <v>911</v>
+        <v>757</v>
       </c>
       <c r="K81" s="10">
-        <v>43962551.141078793</v>
+        <v>46909192.026860319</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.35">
@@ -10621,7 +10621,7 @@
         <v>37</v>
       </c>
       <c r="B82" s="10">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C82" s="10">
         <v>3</v>
@@ -10630,25 +10630,25 @@
         <v>9</v>
       </c>
       <c r="E82" s="10">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="F82" s="10">
-        <v>26320088.840679597</v>
+        <v>27857525.216046929</v>
       </c>
       <c r="G82" s="10">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="H82" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I82" s="10">
         <v>10</v>
       </c>
       <c r="J82" s="10">
-        <v>694</v>
+        <v>734</v>
       </c>
       <c r="K82" s="10">
-        <v>25795596.968580019</v>
+        <v>27265674.916935232</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.35">
@@ -10656,7 +10656,7 @@
         <v>76</v>
       </c>
       <c r="B83" s="10">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="C83" s="10">
         <v>0</v>
@@ -10665,13 +10665,13 @@
         <v>2</v>
       </c>
       <c r="E83" s="10">
-        <v>931</v>
+        <v>893</v>
       </c>
       <c r="F83" s="10">
-        <v>21296375.880635846</v>
+        <v>22505847.82083239</v>
       </c>
       <c r="G83" s="10">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="H83" s="10">
         <v>3</v>
@@ -10680,10 +10680,10 @@
         <v>2</v>
       </c>
       <c r="J83" s="10">
-        <v>969</v>
+        <v>1081</v>
       </c>
       <c r="K83" s="10">
-        <v>21424759.907585599</v>
+        <v>22856536.852877505</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.35">
@@ -10691,7 +10691,7 @@
         <v>65</v>
       </c>
       <c r="B84" s="10">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="C84" s="10">
         <v>6</v>
@@ -10700,25 +10700,25 @@
         <v>4</v>
       </c>
       <c r="E84" s="10">
-        <v>802</v>
+        <v>792</v>
       </c>
       <c r="F84" s="10">
-        <v>24350171.013393518</v>
+        <v>25689391.598872714</v>
       </c>
       <c r="G84" s="10">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="H84" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I84" s="10">
         <v>5</v>
       </c>
       <c r="J84" s="10">
-        <v>866</v>
+        <v>855</v>
       </c>
       <c r="K84" s="10">
-        <v>22204966.601389252</v>
+        <v>23804512.005560592</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.35">
@@ -10726,7 +10726,7 @@
         <v>89</v>
       </c>
       <c r="B85" s="10">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="C85" s="10">
         <v>5</v>
@@ -10735,13 +10735,13 @@
         <v>5</v>
       </c>
       <c r="E85" s="10">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="F85" s="10">
-        <v>26106286.217771295</v>
+        <v>27707878.138874147</v>
       </c>
       <c r="G85" s="10">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="H85" s="10">
         <v>2</v>
@@ -10750,10 +10750,10 @@
         <v>6</v>
       </c>
       <c r="J85" s="10">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="K85" s="10">
-        <v>28443447.509641979</v>
+        <v>30321505.756113347</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.35">
@@ -10761,7 +10761,7 @@
         <v>147</v>
       </c>
       <c r="B86" s="10">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C86" s="10">
         <v>2</v>
@@ -10770,13 +10770,13 @@
         <v>1</v>
       </c>
       <c r="E86" s="10">
-        <v>691</v>
+        <v>632</v>
       </c>
       <c r="F86" s="10">
-        <v>11647431.128983499</v>
+        <v>12297623.509624189</v>
       </c>
       <c r="G86" s="10">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="H86" s="10">
         <v>2</v>
@@ -10785,10 +10785,10 @@
         <v>1</v>
       </c>
       <c r="J86" s="10">
-        <v>522</v>
+        <v>544</v>
       </c>
       <c r="K86" s="10">
-        <v>13047181.392881865</v>
+        <v>13851013.837541368</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.35">
@@ -10796,7 +10796,7 @@
         <v>164</v>
       </c>
       <c r="B87" s="10">
-        <v>1704</v>
+        <v>1700</v>
       </c>
       <c r="C87" s="10">
         <v>9</v>
@@ -10805,13 +10805,13 @@
         <v>10</v>
       </c>
       <c r="E87" s="10">
-        <v>1261</v>
+        <v>1317</v>
       </c>
       <c r="F87" s="10">
-        <v>50025277.975978665</v>
+        <v>52982781.551008649</v>
       </c>
       <c r="G87" s="10">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="H87" s="10">
         <v>6</v>
@@ -10820,10 +10820,10 @@
         <v>10</v>
       </c>
       <c r="J87" s="10">
-        <v>1312</v>
+        <v>824</v>
       </c>
       <c r="K87" s="10">
-        <v>54503798.017063886</v>
+        <v>56341564.403701298</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.35">
@@ -10831,7 +10831,7 @@
         <v>91</v>
       </c>
       <c r="B88" s="10">
-        <v>620</v>
+        <v>599</v>
       </c>
       <c r="C88" s="10">
         <v>5</v>
@@ -10840,13 +10840,13 @@
         <v>3</v>
       </c>
       <c r="E88" s="10">
-        <v>641</v>
+        <v>628</v>
       </c>
       <c r="F88" s="10">
-        <v>13491062.530736148</v>
+        <v>14099053.264334928</v>
       </c>
       <c r="G88" s="10">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="H88" s="10">
         <v>0</v>
@@ -10855,10 +10855,10 @@
         <v>3</v>
       </c>
       <c r="J88" s="10">
-        <v>671</v>
+        <v>625</v>
       </c>
       <c r="K88" s="10">
-        <v>12625436.34218335</v>
+        <v>13251615.22394882</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.35">
@@ -10875,10 +10875,10 @@
         <v>6</v>
       </c>
       <c r="E89" s="10">
-        <v>520</v>
+        <v>574</v>
       </c>
       <c r="F89" s="10">
-        <v>23429486.45540712</v>
+        <v>24761684.048804503</v>
       </c>
       <c r="G89" s="10">
         <v>631</v>
@@ -10890,10 +10890,10 @@
         <v>7</v>
       </c>
       <c r="J89" s="10">
-        <v>641</v>
+        <v>526</v>
       </c>
       <c r="K89" s="10">
-        <v>24509877.584273003</v>
+        <v>25936117.318591543</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.35">
@@ -10901,7 +10901,7 @@
         <v>78</v>
       </c>
       <c r="B90" s="10">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C90" s="10">
         <v>2</v>
@@ -10910,13 +10910,13 @@
         <v>1</v>
       </c>
       <c r="E90" s="10">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="F90" s="10">
-        <v>6461103.0332732033</v>
+        <v>6820595.096124053</v>
       </c>
       <c r="G90" s="10">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H90" s="10">
         <v>2</v>
@@ -10925,10 +10925,10 @@
         <v>1</v>
       </c>
       <c r="J90" s="10">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="K90" s="10">
-        <v>5909417.688019501</v>
+        <v>6214020.6016599154</v>
       </c>
     </row>
   </sheetData>

--- a/SITE MONITORING.xlsx
+++ b/SITE MONITORING.xlsx
@@ -701,7 +701,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -727,13 +727,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -749,6 +758,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1136,27 +1146,27 @@
       </c>
       <c r="F2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12452036.798173808</v>
+        <v>13087808.370799534</v>
       </c>
       <c r="G2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12287955.952436997</v>
+        <v>12916722.729567273</v>
       </c>
       <c r="H2" s="12">
         <f>IFERROR(G2/F2-1,0)</f>
-        <v>-1.3177028657743395E-2</v>
+        <v>-1.307213831262799E-2</v>
       </c>
       <c r="I2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="J2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="K2" s="12">
         <f>IFERROR(J2/I2-1,0)</f>
-        <v>7.3746312684365822E-2</v>
+        <v>7.9510703363914415E-2</v>
       </c>
       <c r="L2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1176,11 +1186,11 @@
       </c>
       <c r="P2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="12">
         <f>IFERROR(P2/O2-1,0)</f>
-        <v>-1</v>
+        <v>-0.66666666666666674</v>
       </c>
       <c r="R2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -1188,11 +1198,11 @@
       </c>
       <c r="S2">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="T2" s="12">
         <f>IFERROR(S2/R2-1,0)</f>
-        <v>-1.6786570743405282E-2</v>
+        <v>-7.194244604316502E-3</v>
       </c>
       <c r="U2">
         <v>3</v>
@@ -1216,27 +1226,27 @@
       </c>
       <c r="F3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15270377.5820772</v>
+        <v>15998166.242166299</v>
       </c>
       <c r="G3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14339947.092993161</v>
+        <v>15084594.410566358</v>
       </c>
       <c r="H3" s="12">
         <f t="shared" ref="H3:H66" si="0">IFERROR(G3/F3-1,0)</f>
-        <v>-6.0930417999361275E-2</v>
+        <v>-5.710478424658727E-2</v>
       </c>
       <c r="I3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>525</v>
+        <v>492</v>
       </c>
       <c r="J3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>487</v>
+        <v>500</v>
       </c>
       <c r="K3" s="12">
         <f t="shared" ref="K3:K66" si="1">IFERROR(J3/I3-1,0)</f>
-        <v>-7.2380952380952435E-2</v>
+        <v>1.6260162601626105E-2</v>
       </c>
       <c r="L3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1264,15 +1274,15 @@
       </c>
       <c r="R3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="S3">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="T3" s="12">
         <f t="shared" ref="T3:T66" si="4">IFERROR(S3/R3-1,0)</f>
-        <v>-7.0484581497797349E-2</v>
+        <v>-6.2130177514792884E-2</v>
       </c>
       <c r="U3">
         <v>2</v>
@@ -1296,27 +1306,27 @@
       </c>
       <c r="F4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17041117.995255239</v>
+        <v>18423447.133026849</v>
       </c>
       <c r="G4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19961475.905457538</v>
+        <v>21263351.156662799</v>
       </c>
       <c r="H4" s="12">
         <f t="shared" si="0"/>
-        <v>0.17137126279011827</v>
+        <v>0.1541461813921341</v>
       </c>
       <c r="I4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="J4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>806</v>
+        <v>788</v>
       </c>
       <c r="K4" s="12">
         <f t="shared" si="1"/>
-        <v>-0.11331133113311331</v>
+        <v>-0.13596491228070173</v>
       </c>
       <c r="L4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1336,23 +1346,23 @@
       </c>
       <c r="P4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q4" s="12">
         <f t="shared" si="3"/>
-        <v>0.14285714285714279</v>
+        <v>0.28571428571428581</v>
       </c>
       <c r="R4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="S4">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="T4" s="12">
         <f t="shared" si="4"/>
-        <v>0.11353711790393017</v>
+        <v>0.11594202898550732</v>
       </c>
       <c r="U4">
         <v>4</v>
@@ -1376,27 +1386,27 @@
       </c>
       <c r="F5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>30428581.790787671</v>
+        <v>32444786.249515016</v>
       </c>
       <c r="G5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>31260783.726436041</v>
+        <v>33059806.89004685</v>
       </c>
       <c r="H5" s="12">
         <f t="shared" si="0"/>
-        <v>2.7349350073894163E-2</v>
+        <v>1.8955915930592093E-2</v>
       </c>
       <c r="I5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1468</v>
+        <v>1484</v>
       </c>
       <c r="J5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1088</v>
+        <v>1130</v>
       </c>
       <c r="K5" s="12">
         <f t="shared" si="1"/>
-        <v>-0.25885558583106272</v>
+        <v>-0.23854447439353099</v>
       </c>
       <c r="L5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1424,15 +1434,15 @@
       </c>
       <c r="R5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="S5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="T5" s="12">
         <f t="shared" si="4"/>
-        <v>2.4493243243243201E-2</v>
+        <v>2.1885521885521841E-2</v>
       </c>
       <c r="U5">
         <v>3</v>
@@ -1456,27 +1466,27 @@
       </c>
       <c r="F6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12572009.692979235</v>
+        <v>13426816.547492765</v>
       </c>
       <c r="G6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14087321.867469653</v>
+        <v>14740995.052347932</v>
       </c>
       <c r="H6" s="12">
         <f t="shared" si="0"/>
-        <v>0.12053062410034854</v>
+        <v>9.7877147587941637E-2</v>
       </c>
       <c r="I6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="J6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="K6" s="12">
         <f t="shared" si="1"/>
-        <v>-2.6041666666666297E-3</v>
+        <v>-0.11294117647058821</v>
       </c>
       <c r="L6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1504,15 +1514,15 @@
       </c>
       <c r="R6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="S6">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="T6" s="12">
         <f t="shared" si="4"/>
-        <v>-2.3980815347721673E-3</v>
+        <v>-1.1961722488038284E-2</v>
       </c>
       <c r="U6">
         <v>3</v>
@@ -1536,27 +1546,27 @@
       </c>
       <c r="F7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10954941.459135331</v>
+        <v>11608508.537279077</v>
       </c>
       <c r="G7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11489847.967613995</v>
+        <v>12076791.011960519</v>
       </c>
       <c r="H7" s="12">
         <f t="shared" si="0"/>
-        <v>4.8827874660398507E-2</v>
+        <v>4.0339589980712853E-2</v>
       </c>
       <c r="I7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="J7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="K7" s="12">
         <f t="shared" si="1"/>
-        <v>-0.17159763313609466</v>
+        <v>-0.25348189415041777</v>
       </c>
       <c r="L7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1584,15 +1594,15 @@
       </c>
       <c r="R7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="S7">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="T7" s="12">
         <f t="shared" si="4"/>
-        <v>1.846965699208436E-2</v>
+        <v>1.8421052631578894E-2</v>
       </c>
       <c r="U7">
         <v>2</v>
@@ -1616,27 +1626,27 @@
       </c>
       <c r="F8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12590405.038448486</v>
+        <v>13234286.009974919</v>
       </c>
       <c r="G8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13775550.668594858</v>
+        <v>14483043.079303995</v>
       </c>
       <c r="H8" s="12">
         <f t="shared" si="0"/>
-        <v>9.4130858104022996E-2</v>
+        <v>9.4357721178752296E-2</v>
       </c>
       <c r="I8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="J8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="K8" s="12">
         <f t="shared" si="1"/>
-        <v>5.3995680345572339E-2</v>
+        <v>5.9602649006622599E-2</v>
       </c>
       <c r="L8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1664,15 +1674,15 @@
       </c>
       <c r="R8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="S8">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="T8" s="12">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.6835016835017313E-3</v>
       </c>
       <c r="U8">
         <v>9</v>
@@ -1696,27 +1706,27 @@
       </c>
       <c r="F9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5908394.1481695939</v>
+        <v>6272122.0239012884</v>
       </c>
       <c r="G9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6045648.5828848016</v>
+        <v>6320873.6215354437</v>
       </c>
       <c r="H9" s="12">
         <f t="shared" si="0"/>
-        <v>2.3230412743829643E-2</v>
+        <v>7.7727438095713808E-3</v>
       </c>
       <c r="I9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>385</v>
+        <v>168</v>
       </c>
       <c r="J9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="K9" s="12">
         <f t="shared" si="1"/>
-        <v>-0.65454545454545454</v>
+        <v>-0.10119047619047616</v>
       </c>
       <c r="L9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1744,15 +1754,15 @@
       </c>
       <c r="R9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="S9">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="T9" s="12">
         <f t="shared" si="4"/>
-        <v>2.3391812865497075E-2</v>
+        <v>5.8139534883721034E-3</v>
       </c>
       <c r="U9">
         <v>1</v>
@@ -1776,27 +1786,27 @@
       </c>
       <c r="F10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5680298.6802293016</v>
+        <v>5986210.4536223654</v>
       </c>
       <c r="G10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>2860659.9967147</v>
+        <v>3146674.465636583</v>
       </c>
       <c r="H10" s="12">
         <f t="shared" si="0"/>
-        <v>-0.49638915878289325</v>
+        <v>-0.47434616774415728</v>
       </c>
       <c r="I10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>226</v>
+        <v>184</v>
       </c>
       <c r="J10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="K10" s="12">
         <f t="shared" si="1"/>
-        <v>-0.22123893805309736</v>
+        <v>-0.11413043478260865</v>
       </c>
       <c r="L10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1856,27 +1866,27 @@
       </c>
       <c r="F11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8944383.1211307161</v>
+        <v>9371873.1319251489</v>
       </c>
       <c r="G11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11890504.003905904</v>
+        <v>12410426.942553291</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" si="0"/>
-        <v>0.32938223272380918</v>
+        <v>0.32422054458647676</v>
       </c>
       <c r="I11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>376</v>
+        <v>339</v>
       </c>
       <c r="J11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>347</v>
+        <v>382</v>
       </c>
       <c r="K11" s="12">
         <f t="shared" si="1"/>
-        <v>-7.7127659574468099E-2</v>
+        <v>0.12684365781710905</v>
       </c>
       <c r="L11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1896,7 +1906,7 @@
       </c>
       <c r="P11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q11" s="12">
         <f t="shared" si="3"/>
@@ -1904,15 +1914,15 @@
       </c>
       <c r="R11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="S11">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="T11" s="12">
         <f t="shared" si="4"/>
-        <v>0.12058823529411766</v>
+        <v>0.11337209302325579</v>
       </c>
       <c r="U11">
         <v>4</v>
@@ -1936,31 +1946,31 @@
       </c>
       <c r="F12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4262490.9429104608</v>
+        <v>4545722.9148001587</v>
       </c>
       <c r="G12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6152814.3065978391</v>
+        <v>6532815.7132673627</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="0"/>
-        <v>0.44347856429617449</v>
+        <v>0.4371346066865498</v>
       </c>
       <c r="I12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="J12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="K12" s="12">
         <f t="shared" si="1"/>
-        <v>8.6776859504132275E-2</v>
+        <v>4.8979591836734615E-2</v>
       </c>
       <c r="L12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -1968,7 +1978,7 @@
       </c>
       <c r="N12" s="12">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -1984,15 +1994,15 @@
       </c>
       <c r="R12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="S12">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="T12" s="12">
         <f t="shared" si="4"/>
-        <v>5.1886792452830122E-2</v>
+        <v>5.1162790697674376E-2</v>
       </c>
       <c r="U12">
         <v>3</v>
@@ -2016,27 +2026,27 @@
       </c>
       <c r="F13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5733341.8539821506</v>
+        <v>6093279.5223717354</v>
       </c>
       <c r="G13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6544098.7908061044</v>
+        <v>6845794.9533302337</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="0"/>
-        <v>0.14141088347293196</v>
+        <v>0.1234992467021423</v>
       </c>
       <c r="I13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="J13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K13" s="12">
         <f t="shared" si="1"/>
-        <v>2.6905829596412634E-2</v>
+        <v>7.9812206572769995E-2</v>
       </c>
       <c r="L13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2064,15 +2074,15 @@
       </c>
       <c r="R13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="S13">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="T13" s="12">
         <f t="shared" si="4"/>
-        <v>-4.0000000000000036E-2</v>
+        <v>-6.640625E-2</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -2096,27 +2106,27 @@
       </c>
       <c r="F14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12150068.330912439</v>
+        <v>13443706.666459411</v>
       </c>
       <c r="G14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>27129953.922294252</v>
+        <v>29022560.368282694</v>
       </c>
       <c r="H14" s="12">
         <f t="shared" si="0"/>
-        <v>1.2329054605618719</v>
+        <v>1.158821304892856</v>
       </c>
       <c r="I14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1062</v>
+        <v>1494</v>
       </c>
       <c r="J14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1064</v>
+        <v>1076</v>
       </c>
       <c r="K14" s="12">
         <f t="shared" si="1"/>
-        <v>1.8832391713747842E-3</v>
+        <v>-0.27978580990629187</v>
       </c>
       <c r="L14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2144,15 +2154,15 @@
       </c>
       <c r="R14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="S14">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1403</v>
+        <v>1384</v>
       </c>
       <c r="T14" s="12">
         <f t="shared" si="4"/>
-        <v>-1.6129032258064502E-2</v>
+        <v>-3.0133146461107208E-2</v>
       </c>
       <c r="U14">
         <v>3</v>
@@ -2176,27 +2186,27 @@
       </c>
       <c r="F15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>37115893.490185946</v>
+        <v>37942760.593333475</v>
       </c>
       <c r="G15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>46248297.021251909</v>
+        <v>49024095.31867002</v>
       </c>
       <c r="H15" s="12">
         <f t="shared" si="0"/>
-        <v>0.2460510221444816</v>
+        <v>0.29205399269982291</v>
       </c>
       <c r="I15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1018</v>
+        <v>181</v>
       </c>
       <c r="J15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>913</v>
+        <v>901</v>
       </c>
       <c r="K15" s="12">
         <f t="shared" si="1"/>
-        <v>-0.10314341846758346</v>
+        <v>3.9779005524861875</v>
       </c>
       <c r="L15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2224,15 +2234,15 @@
       </c>
       <c r="R15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="S15">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1229</v>
+        <v>1234</v>
       </c>
       <c r="T15" s="12">
         <f t="shared" si="4"/>
-        <v>-3.3044846577498066E-2</v>
+        <v>-2.7580772261623365E-2</v>
       </c>
       <c r="U15">
         <v>4</v>
@@ -2256,27 +2266,27 @@
       </c>
       <c r="F16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24557779.647644848</v>
+        <v>25808105.930136997</v>
       </c>
       <c r="G16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>24780324.33078628</v>
+        <v>26071080.14117502</v>
       </c>
       <c r="H16" s="12">
         <f t="shared" si="0"/>
-        <v>9.062084860052666E-3</v>
+        <v>1.0189597475688483E-2</v>
       </c>
       <c r="I16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>894</v>
+        <v>922</v>
       </c>
       <c r="J16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>945</v>
+        <v>859</v>
       </c>
       <c r="K16" s="12">
         <f t="shared" si="1"/>
-        <v>5.7046979865771785E-2</v>
+        <v>-6.8329718004338402E-2</v>
       </c>
       <c r="L16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2292,7 +2302,7 @@
       </c>
       <c r="O16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -2300,19 +2310,19 @@
       </c>
       <c r="Q16" s="12">
         <f t="shared" si="3"/>
-        <v>0.33333333333333326</v>
+        <v>0</v>
       </c>
       <c r="R16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="S16">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="T16" s="12">
         <f t="shared" si="4"/>
-        <v>3.9177277179236469E-3</v>
+        <v>2.9469548133596035E-3</v>
       </c>
       <c r="U16">
         <v>4</v>
@@ -2336,27 +2346,27 @@
       </c>
       <c r="F17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24093521.100269504</v>
+        <v>25100221.83684345</v>
       </c>
       <c r="G17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20292128.333114807</v>
+        <v>21493879.316390663</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="0"/>
-        <v>-0.15777655542062619</v>
+        <v>-0.14367771503753024</v>
       </c>
       <c r="I17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>651</v>
+        <v>583</v>
       </c>
       <c r="J17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>699</v>
+        <v>664</v>
       </c>
       <c r="K17" s="12">
         <f t="shared" si="1"/>
-        <v>7.3732718894009119E-2</v>
+        <v>0.13893653516295035</v>
       </c>
       <c r="L17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2384,15 +2394,15 @@
       </c>
       <c r="R17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>960</v>
+        <v>949</v>
       </c>
       <c r="S17">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="T17" s="12">
         <f t="shared" si="4"/>
-        <v>-4.166666666666663E-2</v>
+        <v>-3.3719704952581697E-2</v>
       </c>
       <c r="U17">
         <v>4</v>
@@ -2416,27 +2426,27 @@
       </c>
       <c r="F18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>84378043.245911941</v>
+        <v>89403755.644768402</v>
       </c>
       <c r="G18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>91431790.086039543</v>
+        <v>95903548.545516953</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="0"/>
-        <v>8.3596947366628482E-2</v>
+        <v>7.2701564423920173E-2</v>
       </c>
       <c r="I18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2911</v>
+        <v>2699</v>
       </c>
       <c r="J18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2167</v>
+        <v>2125</v>
       </c>
       <c r="K18" s="12">
         <f t="shared" si="1"/>
-        <v>-0.25558227413260048</v>
+        <v>-0.2126713597628751</v>
       </c>
       <c r="L18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2452,7 +2462,7 @@
       </c>
       <c r="O18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="P18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -2460,19 +2470,19 @@
       </c>
       <c r="Q18" s="12">
         <f t="shared" si="3"/>
-        <v>-0.70512820512820507</v>
+        <v>-0.7056</v>
       </c>
       <c r="R18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>3219</v>
+        <v>3188</v>
       </c>
       <c r="S18">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2805</v>
+        <v>2806</v>
       </c>
       <c r="T18" s="12">
         <f t="shared" si="4"/>
-        <v>-0.12861136999068035</v>
+        <v>-0.11982434127979924</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -2496,27 +2506,27 @@
       </c>
       <c r="F19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>45853440.719571456</v>
+        <v>48127649.671235926</v>
       </c>
       <c r="G19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>28580704.230768949</v>
+        <v>30944501.324133508</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="0"/>
-        <v>-0.3766944468668858</v>
+        <v>-0.35703277563899272</v>
       </c>
       <c r="I19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1155</v>
+        <v>1203</v>
       </c>
       <c r="J19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1192</v>
+        <v>1172</v>
       </c>
       <c r="K19" s="12">
         <f t="shared" si="1"/>
-        <v>3.2034632034632082E-2</v>
+        <v>-2.5768911055694121E-2</v>
       </c>
       <c r="L19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2544,15 +2554,15 @@
       </c>
       <c r="R19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="S19">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1381</v>
+        <v>1387</v>
       </c>
       <c r="T19" s="12">
         <f t="shared" si="4"/>
-        <v>-4.0972222222222188E-2</v>
+        <v>-3.7473976405274168E-2</v>
       </c>
       <c r="U19">
         <v>1</v>
@@ -2576,27 +2586,27 @@
       </c>
       <c r="F20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>91985409.680114254</v>
+        <v>96839659.029765069</v>
       </c>
       <c r="G20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>91798677.850888729</v>
+        <v>96555492.863442063</v>
       </c>
       <c r="H20" s="12">
         <f t="shared" si="0"/>
-        <v>-2.0300157370054528E-3</v>
+        <v>-2.9343986665180122E-3</v>
       </c>
       <c r="I20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2274</v>
+        <v>2319</v>
       </c>
       <c r="J20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1971</v>
+        <v>2118</v>
       </c>
       <c r="K20" s="12">
         <f t="shared" si="1"/>
-        <v>-0.13324538258575203</v>
+        <v>-8.6675291073738725E-2</v>
       </c>
       <c r="L20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2612,27 +2622,27 @@
       </c>
       <c r="O20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q20" s="12">
         <f t="shared" si="3"/>
-        <v>0.33333333333333326</v>
+        <v>0.3125</v>
       </c>
       <c r="R20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>3008</v>
+        <v>3014</v>
       </c>
       <c r="S20">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2933</v>
+        <v>2929</v>
       </c>
       <c r="T20" s="12">
         <f t="shared" si="4"/>
-        <v>-2.4933510638297851E-2</v>
+        <v>-2.8201725282017254E-2</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2656,27 +2666,27 @@
       </c>
       <c r="F21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13083985.836379612</v>
+        <v>13858968.280016633</v>
       </c>
       <c r="G21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13952390.293539824</v>
+        <v>14656128.885179391</v>
       </c>
       <c r="H21" s="12">
         <f t="shared" si="0"/>
-        <v>6.6371552829539215E-2</v>
+        <v>5.7519476851115359E-2</v>
       </c>
       <c r="I21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="J21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>487</v>
+        <v>451</v>
       </c>
       <c r="K21" s="12">
         <f t="shared" si="1"/>
-        <v>5.8695652173913038E-2</v>
+        <v>-3.426124197002145E-2</v>
       </c>
       <c r="L21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2704,15 +2714,15 @@
       </c>
       <c r="R21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="S21">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="T21" s="12">
         <f t="shared" si="4"/>
-        <v>-2.5408348457350294E-2</v>
+        <v>-2.5316455696202556E-2</v>
       </c>
       <c r="U21">
         <v>1</v>
@@ -2736,63 +2746,63 @@
       </c>
       <c r="F22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>36202793.63631741</v>
+        <v>38076981.426078215</v>
       </c>
       <c r="G22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>38550165.164171152</v>
+        <v>40696450.341174901</v>
       </c>
       <c r="H22" s="12">
         <f t="shared" si="0"/>
-        <v>6.4839513531324222E-2</v>
+        <v>6.8794027703642069E-2</v>
       </c>
       <c r="I22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1256</v>
+        <v>1285</v>
       </c>
       <c r="J22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1368</v>
+        <v>1351</v>
       </c>
       <c r="K22" s="12">
         <f t="shared" si="1"/>
-        <v>8.9171974522292974E-2</v>
+        <v>5.1361867704280195E-2</v>
       </c>
       <c r="L22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N22" s="12">
         <f t="shared" si="2"/>
-        <v>-0.5</v>
+        <v>1</v>
       </c>
       <c r="O22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q22" s="12">
         <f t="shared" si="3"/>
-        <v>0.30769230769230771</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="R22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1707</v>
+        <v>1712</v>
       </c>
       <c r="S22">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1679</v>
+        <v>1657</v>
       </c>
       <c r="T22" s="12">
         <f t="shared" si="4"/>
-        <v>-1.6403046280023426E-2</v>
+        <v>-3.2126168224299034E-2</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2816,27 +2826,27 @@
       </c>
       <c r="F23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15994034.782365471</v>
+        <v>16999705.014675111</v>
       </c>
       <c r="G23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16023991.278544333</v>
+        <v>16848952.521488499</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="0"/>
-        <v>1.8729793067531197E-3</v>
+        <v>-8.8679475941773056E-3</v>
       </c>
       <c r="I23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1010</v>
+        <v>919</v>
       </c>
       <c r="J23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>820</v>
+        <v>775</v>
       </c>
       <c r="K23" s="12">
         <f t="shared" si="1"/>
-        <v>-0.18811881188118806</v>
+        <v>-0.1566920565832427</v>
       </c>
       <c r="L23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2852,7 +2862,7 @@
       </c>
       <c r="O23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -2860,19 +2870,19 @@
       </c>
       <c r="Q23" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-9.0909090909090939E-2</v>
       </c>
       <c r="R23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>862</v>
+        <v>872</v>
       </c>
       <c r="S23">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>879</v>
+        <v>864</v>
       </c>
       <c r="T23" s="12">
         <f t="shared" si="4"/>
-        <v>1.9721577726218076E-2</v>
+        <v>-9.1743119266054496E-3</v>
       </c>
       <c r="U23">
         <v>1</v>
@@ -2896,27 +2906,27 @@
       </c>
       <c r="F24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17730094.775826979</v>
+        <v>18823380.21238241</v>
       </c>
       <c r="G24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19429198.640231583</v>
+        <v>20465850.794823397</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="0"/>
-        <v>9.5831628983796824E-2</v>
+        <v>8.725694130964512E-2</v>
       </c>
       <c r="I24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>803</v>
+        <v>870</v>
       </c>
       <c r="J24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>843</v>
+        <v>678</v>
       </c>
       <c r="K24" s="12">
         <f t="shared" si="1"/>
-        <v>4.9813200498131982E-2</v>
+        <v>-0.22068965517241379</v>
       </c>
       <c r="L24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2948,11 +2958,11 @@
       </c>
       <c r="S24">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="T24" s="12">
         <f t="shared" si="4"/>
-        <v>-1.3544018058690765E-2</v>
+        <v>-9.0293453724604733E-3</v>
       </c>
       <c r="U24">
         <v>3</v>
@@ -2976,27 +2986,27 @@
       </c>
       <c r="F25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5277024.5563090751</v>
+        <v>5565632.8976637917</v>
       </c>
       <c r="G25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4433708.8725122856</v>
+        <v>4723558.2871565996</v>
       </c>
       <c r="H25" s="12">
         <f t="shared" si="0"/>
-        <v>-0.15980893679726071</v>
+        <v>-0.15129898539672959</v>
       </c>
       <c r="I25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="J25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="K25" s="12">
         <f t="shared" si="1"/>
-        <v>1.1428571428571344E-2</v>
+        <v>-5.6122448979591844E-2</v>
       </c>
       <c r="L25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3056,27 +3066,27 @@
       </c>
       <c r="F26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>40235450.07087151</v>
+        <v>42168566.16250097</v>
       </c>
       <c r="G26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>36803930.469524823</v>
+        <v>38683079.315449901</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="0"/>
-        <v>-8.5285975310387729E-2</v>
+        <v>-8.265604368949564E-2</v>
       </c>
       <c r="I26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1301</v>
+        <v>1388</v>
       </c>
       <c r="J26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1383</v>
+        <v>1322</v>
       </c>
       <c r="K26" s="12">
         <f t="shared" si="1"/>
-        <v>6.3028439661798608E-2</v>
+        <v>-4.7550432276657006E-2</v>
       </c>
       <c r="L26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3092,27 +3102,27 @@
       </c>
       <c r="O26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q26" s="12">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1658</v>
+        <v>1649</v>
       </c>
       <c r="S26">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1646</v>
+        <v>1653</v>
       </c>
       <c r="T26" s="12">
         <f t="shared" si="4"/>
-        <v>-7.2376357056694873E-3</v>
+        <v>2.4257125530624535E-3</v>
       </c>
       <c r="U26">
         <v>1</v>
@@ -3136,27 +3146,27 @@
       </c>
       <c r="F27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>28301686.739777543</v>
+        <v>29823023.385615569</v>
       </c>
       <c r="G27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>30880741.730442863</v>
+        <v>32617935.380541101</v>
       </c>
       <c r="H27" s="12">
         <f t="shared" si="0"/>
-        <v>9.1127253805707076E-2</v>
+        <v>9.3716587979258748E-2</v>
       </c>
       <c r="I27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="J27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="K27" s="12">
         <f t="shared" si="1"/>
-        <v>-8.0385852090032461E-3</v>
+        <v>3.2467532467532756E-3</v>
       </c>
       <c r="L27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3176,15 +3186,15 @@
       </c>
       <c r="P27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q27" s="12">
         <f t="shared" si="3"/>
-        <v>-0.19999999999999996</v>
+        <v>0</v>
       </c>
       <c r="R27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="S27">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -3192,7 +3202,7 @@
       </c>
       <c r="T27" s="12">
         <f t="shared" si="4"/>
-        <v>2.9103608847497187E-2</v>
+        <v>2.5522041763341052E-2</v>
       </c>
       <c r="U27">
         <v>1</v>
@@ -3216,27 +3226,27 @@
       </c>
       <c r="F28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>30771914.979088616</v>
+        <v>32601221.645448308</v>
       </c>
       <c r="G28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>29013524.004899658</v>
+        <v>30351804.513628267</v>
       </c>
       <c r="H28" s="12">
         <f t="shared" si="0"/>
-        <v>-5.7142721711791133E-2</v>
+        <v>-6.8997939901865535E-2</v>
       </c>
       <c r="I28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>765</v>
+        <v>789</v>
       </c>
       <c r="J28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>789</v>
+        <v>764</v>
       </c>
       <c r="K28" s="12">
         <f t="shared" si="1"/>
-        <v>3.1372549019607954E-2</v>
+        <v>-3.1685678073510748E-2</v>
       </c>
       <c r="L28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3264,7 +3274,7 @@
       </c>
       <c r="R28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1126</v>
+        <v>1120</v>
       </c>
       <c r="S28">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -3272,7 +3282,7 @@
       </c>
       <c r="T28" s="12">
         <f t="shared" si="4"/>
-        <v>-7.4600355239786809E-2</v>
+        <v>-6.9642857142857117E-2</v>
       </c>
       <c r="U28">
         <v>1</v>
@@ -3296,27 +3306,27 @@
       </c>
       <c r="F29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>39627788.142400511</v>
+        <v>41893976.926671989</v>
       </c>
       <c r="G29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>41174058.474659473</v>
+        <v>43282975.098104343</v>
       </c>
       <c r="H29" s="12">
         <f t="shared" si="0"/>
-        <v>3.901984957380189E-2</v>
+        <v>3.3155080355907751E-2</v>
       </c>
       <c r="I29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>889</v>
+        <v>952</v>
       </c>
       <c r="J29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>874</v>
+        <v>900</v>
       </c>
       <c r="K29" s="12">
         <f t="shared" si="1"/>
-        <v>-1.6872890888638969E-2</v>
+        <v>-5.4621848739495826E-2</v>
       </c>
       <c r="L29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3332,27 +3342,27 @@
       </c>
       <c r="O29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q29" s="12">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="R29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="S29">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="T29" s="12">
         <f t="shared" si="4"/>
-        <v>-4.4247787610619538E-3</v>
+        <v>-7.0546737213403876E-3</v>
       </c>
       <c r="U29">
         <v>1</v>
@@ -3376,27 +3386,27 @@
       </c>
       <c r="F30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>57867671.527397662</v>
+        <v>60948510.020695314</v>
       </c>
       <c r="G30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>52940271.569831714</v>
+        <v>55959396.977800012</v>
       </c>
       <c r="H30" s="12">
         <f t="shared" si="0"/>
-        <v>-8.5149442296689859E-2</v>
+        <v>-8.1857834444209243E-2</v>
       </c>
       <c r="I30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1103</v>
+        <v>1167</v>
       </c>
       <c r="J30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1132</v>
+        <v>1151</v>
       </c>
       <c r="K30" s="12">
         <f t="shared" si="1"/>
-        <v>2.6291931097008225E-2</v>
+        <v>-1.3710368466152478E-2</v>
       </c>
       <c r="L30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3424,15 +3434,15 @@
       </c>
       <c r="R30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="S30">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1443</v>
+        <v>1456</v>
       </c>
       <c r="T30" s="12">
         <f t="shared" si="4"/>
-        <v>-3.9920159680638667E-2</v>
+        <v>-3.1914893617021267E-2</v>
       </c>
       <c r="U30">
         <v>4</v>
@@ -3456,27 +3466,27 @@
       </c>
       <c r="F31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21899406.198145673</v>
+        <v>23188488.13637552</v>
       </c>
       <c r="G31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23896792.324472841</v>
+        <v>25047854.91353824</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="0"/>
-        <v>9.1207318968141493E-2</v>
+        <v>8.0184907538062067E-2</v>
       </c>
       <c r="I31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>535</v>
+        <v>615</v>
       </c>
       <c r="J31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>554</v>
+        <v>508</v>
       </c>
       <c r="K31" s="12">
         <f t="shared" si="1"/>
-        <v>3.5514018691588767E-2</v>
+        <v>-0.17398373983739834</v>
       </c>
       <c r="L31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3504,15 +3514,15 @@
       </c>
       <c r="R31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="S31">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="T31" s="12">
         <f t="shared" si="4"/>
-        <v>1.4471780028943559E-2</v>
+        <v>2.8735632183907178E-3</v>
       </c>
       <c r="U31">
         <v>3</v>
@@ -3536,27 +3546,27 @@
       </c>
       <c r="F32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>68379291.574158043</v>
+        <v>72283101.544206813</v>
       </c>
       <c r="G32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>58685299.940138116</v>
+        <v>62386024.992774226</v>
       </c>
       <c r="H32" s="12">
         <f t="shared" si="0"/>
-        <v>-0.14176794480982147</v>
+        <v>-0.13692102773674897</v>
       </c>
       <c r="I32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1890</v>
+        <v>2045</v>
       </c>
       <c r="J32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="K32" s="12">
         <f t="shared" si="1"/>
-        <v>-0.16666666666666663</v>
+        <v>-0.23129584352078236</v>
       </c>
       <c r="L32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3572,7 +3582,7 @@
       </c>
       <c r="O32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3580,19 +3590,19 @@
       </c>
       <c r="Q32" s="12">
         <f t="shared" si="3"/>
-        <v>-0.375</v>
+        <v>-0.41176470588235292</v>
       </c>
       <c r="R32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="S32">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1926</v>
+        <v>1913</v>
       </c>
       <c r="T32" s="12">
         <f t="shared" si="4"/>
-        <v>-2.1838496698831866E-2</v>
+        <v>-2.7452974072191161E-2</v>
       </c>
       <c r="U32">
         <v>5</v>
@@ -3616,27 +3626,27 @@
       </c>
       <c r="F33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>23416239.072707906</v>
+        <v>24522885.913414594</v>
       </c>
       <c r="G33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23846332.143704496</v>
+        <v>24921846.100234803</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="0"/>
-        <v>1.8367299277272542E-2</v>
+        <v>1.6268892178060046E-2</v>
       </c>
       <c r="I33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>620</v>
+        <v>693</v>
       </c>
       <c r="J33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>712</v>
+        <v>741</v>
       </c>
       <c r="K33" s="12">
         <f t="shared" si="1"/>
-        <v>0.14838709677419359</v>
+        <v>6.9264069264069361E-2</v>
       </c>
       <c r="L33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3664,15 +3674,15 @@
       </c>
       <c r="R33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="S33">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="4"/>
-        <v>2.2538552787663146E-2</v>
+        <v>1.7751479289940919E-2</v>
       </c>
       <c r="U33">
         <v>3</v>
@@ -3696,27 +3706,27 @@
       </c>
       <c r="F34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19580984.263010703</v>
+        <v>20703555.59535294</v>
       </c>
       <c r="G34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21933834.462986201</v>
+        <v>23049754.684711441</v>
       </c>
       <c r="H34" s="12">
         <f t="shared" si="0"/>
-        <v>0.12015995561674253</v>
+        <v>0.11332348584052498</v>
       </c>
       <c r="I34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>534</v>
+        <v>582</v>
       </c>
       <c r="J34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>644</v>
+        <v>609</v>
       </c>
       <c r="K34" s="12">
         <f t="shared" si="1"/>
-        <v>0.20599250936329594</v>
+        <v>4.6391752577319645E-2</v>
       </c>
       <c r="L34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3732,7 +3742,7 @@
       </c>
       <c r="O34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3740,19 +3750,19 @@
       </c>
       <c r="Q34" s="12">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="R34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="S34">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="T34" s="12">
         <f t="shared" si="4"/>
-        <v>8.0459770114942541E-2</v>
+        <v>9.2219020172910726E-2</v>
       </c>
       <c r="U34">
         <v>4</v>
@@ -3776,27 +3786,27 @@
       </c>
       <c r="F35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>34271546.343865938</v>
+        <v>36053259.761528894</v>
       </c>
       <c r="G35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>33947334.926795498</v>
+        <v>35754529.012632072</v>
       </c>
       <c r="H35" s="12">
         <f t="shared" si="0"/>
-        <v>-9.4600755337224118E-3</v>
+        <v>-8.285818005715706E-3</v>
       </c>
       <c r="I35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>843</v>
+        <v>865</v>
       </c>
       <c r="J35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>950</v>
+        <v>893</v>
       </c>
       <c r="K35" s="12">
         <f t="shared" si="1"/>
-        <v>0.12692763938315532</v>
+        <v>3.2369942196531776E-2</v>
       </c>
       <c r="L35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3816,23 +3826,23 @@
       </c>
       <c r="P35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q35" s="12">
         <f t="shared" si="3"/>
-        <v>0.21428571428571419</v>
+        <v>0.28571428571428581</v>
       </c>
       <c r="R35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1113</v>
+        <v>1108</v>
       </c>
       <c r="S35">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="T35" s="12">
         <f t="shared" si="4"/>
-        <v>3.1446540880503138E-2</v>
+        <v>3.8808664259927905E-2</v>
       </c>
       <c r="U35">
         <v>13</v>
@@ -3856,27 +3866,27 @@
       </c>
       <c r="F36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>33052464.113899976</v>
+        <v>34761818.863370262</v>
       </c>
       <c r="G36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>32190582.015026674</v>
+        <v>33981946.736486293</v>
       </c>
       <c r="H36" s="12">
         <f t="shared" si="0"/>
-        <v>-2.6076182880139465E-2</v>
+        <v>-2.2434733060120338E-2</v>
       </c>
       <c r="I36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>769</v>
+        <v>861</v>
       </c>
       <c r="J36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>964</v>
+        <v>876</v>
       </c>
       <c r="K36" s="12">
         <f t="shared" si="1"/>
-        <v>0.25357607282184658</v>
+        <v>1.7421602787456525E-2</v>
       </c>
       <c r="L36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3896,23 +3906,23 @@
       </c>
       <c r="P36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>121</v>
+        <v>272</v>
       </c>
       <c r="Q36" s="12">
         <f t="shared" si="3"/>
-        <v>1.9512195121951219</v>
+        <v>5.6341463414634143</v>
       </c>
       <c r="R36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="S36">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1252</v>
+        <v>1381</v>
       </c>
       <c r="T36" s="12">
         <f t="shared" si="4"/>
-        <v>0.14967860422405876</v>
+        <v>0.27281105990783416</v>
       </c>
       <c r="U36">
         <v>4</v>
@@ -3936,27 +3946,27 @@
       </c>
       <c r="F37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>52158232.747112714</v>
+        <v>54910655.209512085</v>
       </c>
       <c r="G37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>57989157.172912218</v>
+        <v>60889043.762123182</v>
       </c>
       <c r="H37" s="12">
         <f t="shared" si="0"/>
-        <v>0.11179298298066431</v>
+        <v>0.10887483549049826</v>
       </c>
       <c r="I37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1371</v>
+        <v>1385</v>
       </c>
       <c r="J37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1578</v>
+        <v>1310</v>
       </c>
       <c r="K37" s="12">
         <f t="shared" si="1"/>
-        <v>0.15098468271334786</v>
+        <v>-5.4151624548736454E-2</v>
       </c>
       <c r="L37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3972,27 +3982,27 @@
       </c>
       <c r="O37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="P37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>73</v>
+        <v>123</v>
       </c>
       <c r="Q37" s="12">
         <f t="shared" si="3"/>
-        <v>0.32727272727272738</v>
+        <v>1.1578947368421053</v>
       </c>
       <c r="R37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1784</v>
+        <v>1795</v>
       </c>
       <c r="S37">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2269</v>
+        <v>2277</v>
       </c>
       <c r="T37" s="12">
         <f t="shared" si="4"/>
-        <v>0.27186098654708513</v>
+        <v>0.26852367688022283</v>
       </c>
       <c r="U37">
         <v>16</v>
@@ -4020,23 +4030,23 @@
       </c>
       <c r="G38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20656820.414189544</v>
+        <v>21690653.82312274</v>
       </c>
       <c r="H38" s="12">
         <f t="shared" si="0"/>
-        <v>0.18031044823053022</v>
+        <v>0.23938267473134389</v>
       </c>
       <c r="I38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="K38" s="12">
         <f t="shared" si="1"/>
-        <v>58</v>
+        <v>89.8</v>
       </c>
       <c r="L38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4064,15 +4074,15 @@
       </c>
       <c r="R38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="S38">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="T38" s="12">
         <f t="shared" si="4"/>
-        <v>8.1566068515497303E-3</v>
+        <v>1.8092105263157965E-2</v>
       </c>
       <c r="U38">
         <v>3</v>
@@ -4096,27 +4106,27 @@
       </c>
       <c r="F39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>61288523.598765254</v>
+        <v>63981776.356715463</v>
       </c>
       <c r="G39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>66763112.972614646</v>
+        <v>70387346.462206155</v>
       </c>
       <c r="H39" s="12">
         <f t="shared" si="0"/>
-        <v>8.9324869525159833E-2</v>
+        <v>0.10011554024036351</v>
       </c>
       <c r="I39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1869</v>
+        <v>1854</v>
       </c>
       <c r="J39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1991</v>
+        <v>1948</v>
       </c>
       <c r="K39" s="12">
         <f t="shared" si="1"/>
-        <v>6.527554842161587E-2</v>
+        <v>5.0701186623516747E-2</v>
       </c>
       <c r="L39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4136,23 +4146,23 @@
       </c>
       <c r="P39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q39" s="12">
         <f t="shared" si="3"/>
-        <v>-0.5714285714285714</v>
+        <v>-0.5</v>
       </c>
       <c r="R39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2036</v>
+        <v>2048</v>
       </c>
       <c r="S39">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2059</v>
+        <v>2066</v>
       </c>
       <c r="T39" s="12">
         <f t="shared" si="4"/>
-        <v>1.129666011787811E-2</v>
+        <v>8.7890625E-3</v>
       </c>
       <c r="U39">
         <v>4</v>
@@ -4176,27 +4186,27 @@
       </c>
       <c r="F40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>42805016.573299475</v>
+        <v>45081578.612316735</v>
       </c>
       <c r="G40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>46227650.783002853</v>
+        <v>48694697.570638672</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" si="0"/>
-        <v>7.9958717077995844E-2</v>
+        <v>8.0146238653115764E-2</v>
       </c>
       <c r="I40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>760</v>
+        <v>783</v>
       </c>
       <c r="J40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>797</v>
+        <v>838</v>
       </c>
       <c r="K40" s="12">
         <f t="shared" si="1"/>
-        <v>4.8684210526315885E-2</v>
+        <v>7.0242656449553076E-2</v>
       </c>
       <c r="L40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4224,15 +4234,15 @@
       </c>
       <c r="R40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="S40">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="T40" s="12">
         <f t="shared" si="4"/>
-        <v>2.0524515393386622E-2</v>
+        <v>1.3620885357548351E-2</v>
       </c>
       <c r="U40">
         <v>3</v>
@@ -4256,27 +4266,27 @@
       </c>
       <c r="F41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>35305267.70624648</v>
+        <v>36951327.241868146</v>
       </c>
       <c r="G41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>27034432.239690185</v>
+        <v>28817713.877122149</v>
       </c>
       <c r="H41" s="12">
         <f t="shared" si="0"/>
-        <v>-0.23426632918840484</v>
+        <v>-0.22011694766758227</v>
       </c>
       <c r="I41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>996</v>
+        <v>935</v>
       </c>
       <c r="J41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1158</v>
+        <v>1035</v>
       </c>
       <c r="K41" s="12">
         <f t="shared" si="1"/>
-        <v>0.16265060240963858</v>
+        <v>0.10695187165775399</v>
       </c>
       <c r="L41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4296,23 +4306,23 @@
       </c>
       <c r="P41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q41" s="12">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>1.3333333333333335</v>
       </c>
       <c r="R41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1116</v>
+        <v>1100</v>
       </c>
       <c r="S41">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="T41" s="12">
         <f t="shared" si="4"/>
-        <v>-1.7025089605734789E-2</v>
+        <v>-1.8181818181818299E-3</v>
       </c>
       <c r="U41">
         <v>4</v>
@@ -4336,27 +4346,27 @@
       </c>
       <c r="F42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>34656045.854344085</v>
+        <v>36616468.703792453</v>
       </c>
       <c r="G42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>34623144.718677483</v>
+        <v>36351905.914852493</v>
       </c>
       <c r="H42" s="12">
         <f t="shared" si="0"/>
-        <v>-9.4936207681861617E-4</v>
+        <v>-7.2252403987979053E-3</v>
       </c>
       <c r="I42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>636</v>
+        <v>646</v>
       </c>
       <c r="J42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="K42" s="12">
         <f t="shared" si="1"/>
-        <v>-3.7735849056603765E-2</v>
+        <v>-4.6439628482972117E-2</v>
       </c>
       <c r="L42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4376,7 +4386,7 @@
       </c>
       <c r="P42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q42" s="12">
         <f t="shared" si="3"/>
@@ -4384,7 +4394,7 @@
       </c>
       <c r="R42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="S42">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -4392,7 +4402,7 @@
       </c>
       <c r="T42" s="12">
         <f t="shared" si="4"/>
-        <v>-2.5670945157526215E-2</v>
+        <v>-2.6806526806526842E-2</v>
       </c>
       <c r="U42">
         <v>2</v>
@@ -4416,27 +4426,27 @@
       </c>
       <c r="F43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21610464.703248747</v>
+        <v>22704753.056662936</v>
       </c>
       <c r="G43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21742784.05233898</v>
+        <v>22763455.27254276</v>
       </c>
       <c r="H43" s="12">
         <f t="shared" si="0"/>
-        <v>6.1229293727469436E-3</v>
+        <v>2.5854593411926974E-3</v>
       </c>
       <c r="I43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="J43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>123</v>
+        <v>623</v>
       </c>
       <c r="K43" s="12">
         <f t="shared" si="1"/>
-        <v>-0.78421052631578947</v>
+        <v>8.1597222222222321E-2</v>
       </c>
       <c r="L43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4468,11 +4478,11 @@
       </c>
       <c r="S43">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="T43" s="12">
         <f t="shared" si="4"/>
-        <v>5.1282051282051322E-2</v>
+        <v>5.2790346907994001E-2</v>
       </c>
       <c r="U43">
         <v>2</v>
@@ -4496,27 +4506,27 @@
       </c>
       <c r="F44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20687868.148741201</v>
+        <v>21905672.652470183</v>
       </c>
       <c r="G44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18652888.434304617</v>
+        <v>19508855.302097976</v>
       </c>
       <c r="H44" s="12">
         <f t="shared" si="0"/>
-        <v>-9.8365848999303784E-2</v>
+        <v>-0.10941537328697049</v>
       </c>
       <c r="I44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="J44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>389</v>
+        <v>708</v>
       </c>
       <c r="K44" s="12">
         <f t="shared" si="1"/>
-        <v>-0.46047156726768379</v>
+        <v>-7.8125E-2</v>
       </c>
       <c r="L44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4532,7 +4542,7 @@
       </c>
       <c r="O44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4544,15 +4554,15 @@
       </c>
       <c r="R44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="S44">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="T44" s="12">
         <f t="shared" si="4"/>
-        <v>-2.6874115983026914E-2</v>
+        <v>-3.2394366197183055E-2</v>
       </c>
       <c r="U44">
         <v>3</v>
@@ -4576,27 +4586,27 @@
       </c>
       <c r="F45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>65941089.434293799</v>
+        <v>68951901.83255586</v>
       </c>
       <c r="G45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>62024410.34365315</v>
+        <v>65624769.39583008</v>
       </c>
       <c r="H45" s="12">
         <f t="shared" si="0"/>
-        <v>-5.9396639094708603E-2</v>
+        <v>-4.8252946594648738E-2</v>
       </c>
       <c r="I45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1085</v>
+        <v>1058</v>
       </c>
       <c r="J45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1418</v>
+        <v>1375</v>
       </c>
       <c r="K45" s="12">
         <f t="shared" si="1"/>
-        <v>0.30691244239631343</v>
+        <v>0.29962192816635169</v>
       </c>
       <c r="L45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4612,7 +4622,7 @@
       </c>
       <c r="O45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4620,19 +4630,19 @@
       </c>
       <c r="Q45" s="12">
         <f t="shared" si="3"/>
-        <v>-0.72727272727272729</v>
+        <v>-0.75</v>
       </c>
       <c r="R45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1279</v>
+        <v>1272</v>
       </c>
       <c r="S45">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1243</v>
+        <v>1250</v>
       </c>
       <c r="T45" s="12">
         <f t="shared" si="4"/>
-        <v>-2.8146989835809211E-2</v>
+        <v>-1.7295597484276781E-2</v>
       </c>
       <c r="U45">
         <v>5</v>
@@ -4656,27 +4666,27 @@
       </c>
       <c r="F46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>29718671.064681828</v>
+        <v>31224174.820838396</v>
       </c>
       <c r="G46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>29054377.526877664</v>
+        <v>30416321.719961289</v>
       </c>
       <c r="H46" s="12">
         <f t="shared" si="0"/>
-        <v>-2.2352733618483445E-2</v>
+        <v>-2.5872680559614336E-2</v>
       </c>
       <c r="I46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>950</v>
+        <v>922</v>
       </c>
       <c r="J46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>931</v>
+        <v>946</v>
       </c>
       <c r="K46" s="12">
         <f t="shared" si="1"/>
-        <v>-2.0000000000000018E-2</v>
+        <v>2.6030368763557465E-2</v>
       </c>
       <c r="L46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4704,15 +4714,15 @@
       </c>
       <c r="R46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="S46">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="T46" s="12">
         <f t="shared" si="4"/>
-        <v>4.2093287827076331E-2</v>
+        <v>3.167420814479649E-2</v>
       </c>
       <c r="U46">
         <v>4</v>
@@ -4736,27 +4746,27 @@
       </c>
       <c r="F47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>43797964.177689955</v>
+        <v>46284776.708795786</v>
       </c>
       <c r="G47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>50825033.960358381</v>
+        <v>53489987.771002561</v>
       </c>
       <c r="H47" s="12">
         <f t="shared" si="0"/>
-        <v>0.16044284054298386</v>
+        <v>0.15567129355595499</v>
       </c>
       <c r="I47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>979</v>
+        <v>996</v>
       </c>
       <c r="J47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="K47" s="12">
         <f t="shared" si="1"/>
-        <v>4.4943820224719211E-2</v>
+        <v>2.9116465863453733E-2</v>
       </c>
       <c r="L47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4772,27 +4782,27 @@
       </c>
       <c r="O47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q47" s="12">
         <f t="shared" si="3"/>
-        <v>-0.66666666666666674</v>
+        <v>-0.64705882352941169</v>
       </c>
       <c r="R47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="S47">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1344</v>
+        <v>1338</v>
       </c>
       <c r="T47" s="12">
         <f t="shared" si="4"/>
-        <v>3.1465848042977695E-2</v>
+        <v>2.8439661798616456E-2</v>
       </c>
       <c r="U47">
         <v>6</v>
@@ -4816,27 +4826,27 @@
       </c>
       <c r="F48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>22770248.911103602</v>
+        <v>24156172.660815898</v>
       </c>
       <c r="G48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>26152148.725233007</v>
+        <v>27405554.935270023</v>
       </c>
       <c r="H48" s="12">
         <f t="shared" si="0"/>
-        <v>0.14852274243169417</v>
+        <v>0.13451560891204406</v>
       </c>
       <c r="I48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="J48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="K48" s="12">
         <f t="shared" si="1"/>
-        <v>1.1173184357541999E-2</v>
+        <v>5.2631578947368363E-2</v>
       </c>
       <c r="L48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4856,23 +4866,23 @@
       </c>
       <c r="P48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q48" s="12">
         <f t="shared" si="3"/>
-        <v>-0.85714285714285721</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="R48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="S48">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="T48" s="12">
         <f t="shared" si="4"/>
-        <v>2.0746887966804906E-3</v>
+        <v>1.0330578512396604E-2</v>
       </c>
       <c r="U48">
         <v>1</v>
@@ -4896,27 +4906,27 @@
       </c>
       <c r="F49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>22546305.818256099</v>
+        <v>23676615.185974032</v>
       </c>
       <c r="G49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19126089.304449983</v>
+        <v>20136026.2156309</v>
       </c>
       <c r="H49" s="12">
         <f t="shared" si="0"/>
-        <v>-0.15169742402042252</v>
+        <v>-0.14953949044374248</v>
       </c>
       <c r="I49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>298</v>
+        <v>323</v>
       </c>
       <c r="J49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="K49" s="12">
         <f t="shared" si="1"/>
-        <v>8.0536912751677958E-2</v>
+        <v>-1.2383900928792602E-2</v>
       </c>
       <c r="L49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4948,11 +4958,11 @@
       </c>
       <c r="S49">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="T49" s="12">
         <f t="shared" si="4"/>
-        <v>3.6036036036036112E-2</v>
+        <v>3.1531531531531432E-2</v>
       </c>
       <c r="U49">
         <v>5</v>
@@ -4976,27 +4986,27 @@
       </c>
       <c r="F50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18657852.426756896</v>
+        <v>19565337.991295934</v>
       </c>
       <c r="G50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16764643.498383747</v>
+        <v>17633388.891193338</v>
       </c>
       <c r="H50" s="12">
         <f t="shared" si="0"/>
-        <v>-0.10146982005593164</v>
+        <v>-9.8743456461731771E-2</v>
       </c>
       <c r="I50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="J50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>367</v>
+        <v>341</v>
       </c>
       <c r="K50" s="12">
         <f t="shared" si="1"/>
-        <v>-2.9100529100529071E-2</v>
+        <v>-0.11197916666666663</v>
       </c>
       <c r="L50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5024,15 +5034,15 @@
       </c>
       <c r="R50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="S50">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="T50" s="12">
         <f t="shared" si="4"/>
-        <v>-1.3986013986013957E-2</v>
+        <v>-7.0257611241217877E-3</v>
       </c>
       <c r="U50">
         <v>4</v>
@@ -5056,27 +5066,27 @@
       </c>
       <c r="F51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>40544706.538535334</v>
+        <v>42465575.241866045</v>
       </c>
       <c r="G51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>39213836.923041739</v>
+        <v>41199724.440495275</v>
       </c>
       <c r="H51" s="12">
         <f t="shared" si="0"/>
-        <v>-3.2824744069332001E-2</v>
+        <v>-2.980886975299446E-2</v>
       </c>
       <c r="I51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>927</v>
+        <v>947</v>
       </c>
       <c r="J51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="K51" s="12">
         <f t="shared" si="1"/>
-        <v>1.2944983818770295E-2</v>
+        <v>-6.3357972544878516E-3</v>
       </c>
       <c r="L51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5104,15 +5114,15 @@
       </c>
       <c r="R51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="S51">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1100</v>
+        <v>1094</v>
       </c>
       <c r="T51" s="12">
         <f t="shared" si="4"/>
-        <v>-2.3090586145648295E-2</v>
+        <v>-2.9281277728482658E-2</v>
       </c>
       <c r="U51">
         <v>5</v>
@@ -5136,27 +5146,27 @@
       </c>
       <c r="F52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>42886891.103262864</v>
+        <v>45055941.481699936</v>
       </c>
       <c r="G52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>40939585.895147137</v>
+        <v>43110471.737202205</v>
       </c>
       <c r="H52" s="12">
         <f t="shared" si="0"/>
-        <v>-4.540560432387164E-2</v>
+        <v>-4.3178983293200246E-2</v>
       </c>
       <c r="I52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>841</v>
+        <v>810</v>
       </c>
       <c r="J52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>862</v>
+        <v>817</v>
       </c>
       <c r="K52" s="12">
         <f t="shared" si="1"/>
-        <v>2.4970273483947647E-2</v>
+        <v>8.6419753086419693E-3</v>
       </c>
       <c r="L52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5184,15 +5194,15 @@
       </c>
       <c r="R52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>980</v>
+        <v>971</v>
       </c>
       <c r="S52">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="T52" s="12">
         <f t="shared" si="4"/>
-        <v>3.469387755102038E-2</v>
+        <v>4.1194644696189497E-2</v>
       </c>
       <c r="U52">
         <v>4</v>
@@ -5216,27 +5226,27 @@
       </c>
       <c r="F53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>60223755.032434106</v>
+        <v>63893921.779931098</v>
       </c>
       <c r="G53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>73666459.599487707</v>
+        <v>77451228.109518692</v>
       </c>
       <c r="H53" s="12">
         <f t="shared" si="0"/>
-        <v>0.22321266018390751</v>
+        <v>0.21218460147559615</v>
       </c>
       <c r="I53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1709</v>
+        <v>1508</v>
       </c>
       <c r="J53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1735</v>
+        <v>1783</v>
       </c>
       <c r="K53" s="12">
         <f t="shared" si="1"/>
-        <v>1.5213575190169637E-2</v>
+        <v>0.18236074270557023</v>
       </c>
       <c r="L53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5252,7 +5262,7 @@
       </c>
       <c r="O53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5260,19 +5270,19 @@
       </c>
       <c r="Q53" s="12">
         <f t="shared" si="3"/>
-        <v>-0.72222222222222221</v>
+        <v>-0.72972972972972971</v>
       </c>
       <c r="R53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2163</v>
+        <v>2122</v>
       </c>
       <c r="S53">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2043</v>
+        <v>2048</v>
       </c>
       <c r="T53" s="12">
         <f t="shared" si="4"/>
-        <v>-5.5478502080443803E-2</v>
+        <v>-3.4872761545711617E-2</v>
       </c>
       <c r="U53">
         <v>8</v>
@@ -5296,27 +5306,27 @@
       </c>
       <c r="F54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19628260.883901495</v>
+        <v>20534534.922981523</v>
       </c>
       <c r="G54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18415275.797894016</v>
+        <v>19415132.028813072</v>
       </c>
       <c r="H54" s="12">
         <f t="shared" si="0"/>
-        <v>-6.1797888930767875E-2</v>
+        <v>-5.4513184660230918E-2</v>
       </c>
       <c r="I54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="J54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>550</v>
+        <v>582</v>
       </c>
       <c r="K54" s="12">
         <f t="shared" si="1"/>
-        <v>-9.009009009009028E-3</v>
+        <v>6.0109289617486406E-2</v>
       </c>
       <c r="L54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5344,15 +5354,15 @@
       </c>
       <c r="R54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="S54">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="T54" s="12">
         <f t="shared" si="4"/>
-        <v>-1.4492753623188692E-3</v>
+        <v>-1.4471780028944004E-3</v>
       </c>
       <c r="U54">
         <v>2</v>
@@ -5376,27 +5386,27 @@
       </c>
       <c r="F55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>30615413.367241357</v>
+        <v>32408420.627318345</v>
       </c>
       <c r="G55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>32094490.60502778</v>
+        <v>33783028.370750755</v>
       </c>
       <c r="H55" s="12">
         <f t="shared" si="0"/>
-        <v>4.8311522697552123E-2</v>
+        <v>4.2415141399198442E-2</v>
       </c>
       <c r="I55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>830</v>
+        <v>742</v>
       </c>
       <c r="J55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>740</v>
+        <v>763</v>
       </c>
       <c r="K55" s="12">
         <f t="shared" si="1"/>
-        <v>-0.10843373493975905</v>
+        <v>2.8301886792452935E-2</v>
       </c>
       <c r="L55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5424,15 +5434,15 @@
       </c>
       <c r="R55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="S55">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="T55" s="12">
         <f t="shared" si="4"/>
-        <v>-2.1517553793884536E-2</v>
+        <v>-2.924634420697414E-2</v>
       </c>
       <c r="U55">
         <v>7</v>
@@ -5456,27 +5466,27 @@
       </c>
       <c r="F56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>23662873.351727627</v>
+        <v>24757924.64762653</v>
       </c>
       <c r="G56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20317389.490997106</v>
+        <v>21302689.942315493</v>
       </c>
       <c r="H56" s="12">
         <f t="shared" si="0"/>
-        <v>-0.14138113368578997</v>
+        <v>-0.1395607569894709</v>
       </c>
       <c r="I56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>627</v>
+        <v>595</v>
       </c>
       <c r="J56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>635</v>
+        <v>603</v>
       </c>
       <c r="K56" s="12">
         <f t="shared" si="1"/>
-        <v>1.2759170653907415E-2</v>
+        <v>1.3445378151260456E-2</v>
       </c>
       <c r="L56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5504,15 +5514,15 @@
       </c>
       <c r="R56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="S56">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="T56" s="12">
         <f t="shared" si="4"/>
-        <v>-6.4968152866242024E-2</v>
+        <v>-6.7774936061381075E-2</v>
       </c>
       <c r="U56">
         <v>3</v>
@@ -5536,27 +5546,27 @@
       </c>
       <c r="F57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>40636216.140523255</v>
+        <v>42696543.090585358</v>
       </c>
       <c r="G57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>40981093.886455111</v>
+        <v>43034612.716141865</v>
       </c>
       <c r="H57" s="12">
         <f t="shared" si="0"/>
-        <v>8.486955201223445E-3</v>
+        <v>7.9179624645315805E-3</v>
       </c>
       <c r="I57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1070</v>
+        <v>1031</v>
       </c>
       <c r="J57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>977</v>
+        <v>1001</v>
       </c>
       <c r="K57" s="12">
         <f t="shared" si="1"/>
-        <v>-8.6915887850467333E-2</v>
+        <v>-2.9097963142580063E-2</v>
       </c>
       <c r="L57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5584,7 +5594,7 @@
       </c>
       <c r="R57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="S57">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -5592,7 +5602,7 @@
       </c>
       <c r="T57" s="12">
         <f t="shared" si="4"/>
-        <v>1.0958904109588996E-2</v>
+        <v>1.2808783165599191E-2</v>
       </c>
       <c r="U57">
         <v>3</v>
@@ -5616,27 +5626,27 @@
       </c>
       <c r="F58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>51975399.294892192</v>
+        <v>54590695.006662175</v>
       </c>
       <c r="G58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>50074452.206668533</v>
+        <v>53108125.971225314</v>
       </c>
       <c r="H58" s="12">
         <f t="shared" si="0"/>
-        <v>-3.6573977574241967E-2</v>
+        <v>-2.7157907318379637E-2</v>
       </c>
       <c r="I58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1343</v>
+        <v>1372</v>
       </c>
       <c r="J58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1408</v>
+        <v>1546</v>
       </c>
       <c r="K58" s="12">
         <f t="shared" si="1"/>
-        <v>4.8399106478034248E-2</v>
+        <v>0.12682215743440239</v>
       </c>
       <c r="L58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5652,7 +5662,7 @@
       </c>
       <c r="O58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5660,19 +5670,19 @@
       </c>
       <c r="Q58" s="12">
         <f t="shared" si="3"/>
-        <v>-9.0909090909090939E-2</v>
+        <v>-0.16666666666666663</v>
       </c>
       <c r="R58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1370</v>
+        <v>1363</v>
       </c>
       <c r="S58">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1503</v>
+        <v>1516</v>
       </c>
       <c r="T58" s="12">
         <f t="shared" si="4"/>
-        <v>9.7080291970802923E-2</v>
+        <v>0.11225238444607477</v>
       </c>
       <c r="U58">
         <v>4</v>
@@ -5696,27 +5706,27 @@
       </c>
       <c r="F59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>26207240.497092113</v>
+        <v>27563613.08958514</v>
       </c>
       <c r="G59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>27821994.716877595</v>
+        <v>29166523.35953356</v>
       </c>
       <c r="H59" s="12">
         <f t="shared" si="0"/>
-        <v>6.1614812897399451E-2</v>
+        <v>5.8153126179023129E-2</v>
       </c>
       <c r="I59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>751</v>
+        <v>693</v>
       </c>
       <c r="J59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>682</v>
+        <v>1398</v>
       </c>
       <c r="K59" s="12">
         <f t="shared" si="1"/>
-        <v>-9.187749667110523E-2</v>
+        <v>1.0173160173160172</v>
       </c>
       <c r="L59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5736,15 +5746,15 @@
       </c>
       <c r="P59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q59" s="12">
         <f t="shared" si="3"/>
-        <v>-0.6</v>
+        <v>-0.4</v>
       </c>
       <c r="R59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="S59">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -5752,7 +5762,7 @@
       </c>
       <c r="T59" s="12">
         <f t="shared" si="4"/>
-        <v>1.2987012987013546E-3</v>
+        <v>2.6007802340701769E-3</v>
       </c>
       <c r="U59">
         <v>3</v>
@@ -5776,27 +5786,27 @@
       </c>
       <c r="F60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>30690396.011699993</v>
+        <v>32225585.880645122</v>
       </c>
       <c r="G60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>31019483.13461696</v>
+        <v>32666251.142069764</v>
       </c>
       <c r="H60" s="12">
         <f t="shared" si="0"/>
-        <v>1.0722804710356693E-2</v>
+        <v>1.3674390996543773E-2</v>
       </c>
       <c r="I60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>483</v>
+        <v>451</v>
       </c>
       <c r="J60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="K60" s="12">
         <f t="shared" si="1"/>
-        <v>-6.2111801242236031E-2</v>
+        <v>4.434589800443467E-2</v>
       </c>
       <c r="L60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5812,7 +5822,7 @@
       </c>
       <c r="O60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5820,19 +5830,19 @@
       </c>
       <c r="Q60" s="12">
         <f t="shared" si="3"/>
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="R60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="S60">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="T60" s="12">
         <f t="shared" si="4"/>
-        <v>-8.7209302325581439E-2</v>
+        <v>-9.8265895953757232E-2</v>
       </c>
       <c r="U60">
         <v>10</v>
@@ -5856,27 +5866,27 @@
       </c>
       <c r="F61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>80494151.517660826</v>
+        <v>85317689.138641283</v>
       </c>
       <c r="G61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>99819639.769979075</v>
+        <v>104957958.57839498</v>
       </c>
       <c r="H61" s="12">
         <f t="shared" si="0"/>
-        <v>0.24008561973695852</v>
+        <v>0.23020161045194576</v>
       </c>
       <c r="I61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1869</v>
+        <v>1668</v>
       </c>
       <c r="J61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1607</v>
+        <v>1722</v>
       </c>
       <c r="K61" s="12">
         <f t="shared" si="1"/>
-        <v>-0.14018191546281433</v>
+        <v>3.2374100719424481E-2</v>
       </c>
       <c r="L61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5892,7 +5902,7 @@
       </c>
       <c r="O61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -5900,19 +5910,19 @@
       </c>
       <c r="Q61" s="12">
         <f t="shared" si="3"/>
-        <v>-0.21052631578947367</v>
+        <v>-0.25</v>
       </c>
       <c r="R61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="S61">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1999</v>
+        <v>2010</v>
       </c>
       <c r="T61" s="12">
         <f t="shared" si="4"/>
-        <v>-2.3448949682462139E-2</v>
+        <v>-1.85546875E-2</v>
       </c>
       <c r="U61">
         <v>10</v>
@@ -5936,27 +5946,27 @@
       </c>
       <c r="F62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>74403597.224619329</v>
+        <v>78408477.996826321</v>
       </c>
       <c r="G62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>75202591.101204753</v>
+        <v>79258311.448570415</v>
       </c>
       <c r="H62" s="12">
         <f t="shared" si="0"/>
-        <v>1.0738645796564361E-2</v>
+        <v>1.0838540339712877E-2</v>
       </c>
       <c r="I62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1177</v>
+        <v>1181</v>
       </c>
       <c r="J62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1376</v>
+        <v>1222</v>
       </c>
       <c r="K62" s="12">
         <f t="shared" si="1"/>
-        <v>0.16907391673746819</v>
+        <v>3.4716342082980578E-2</v>
       </c>
       <c r="L62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5984,15 +5994,15 @@
       </c>
       <c r="R62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1597</v>
+        <v>1587</v>
       </c>
       <c r="S62">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1602</v>
+        <v>1589</v>
       </c>
       <c r="T62" s="12">
         <f t="shared" si="4"/>
-        <v>3.1308703819661332E-3</v>
+        <v>1.260239445494582E-3</v>
       </c>
       <c r="U62">
         <v>8</v>
@@ -6016,27 +6026,27 @@
       </c>
       <c r="F63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>46188082.820514478</v>
+        <v>48727801.593974993</v>
       </c>
       <c r="G63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>48323897.682485439</v>
+        <v>50766777.004490346</v>
       </c>
       <c r="H63" s="12">
         <f t="shared" si="0"/>
-        <v>4.6241686849628927E-2</v>
+        <v>4.1844190458357744E-2</v>
       </c>
       <c r="I63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>648</v>
+        <v>655</v>
       </c>
       <c r="J63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>657</v>
+        <v>734</v>
       </c>
       <c r="K63" s="12">
         <f t="shared" si="1"/>
-        <v>1.388888888888884E-2</v>
+        <v>0.12061068702290068</v>
       </c>
       <c r="L63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6064,15 +6074,15 @@
       </c>
       <c r="R63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="S63">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="T63" s="12">
         <f t="shared" si="4"/>
-        <v>4.6948356807511749E-2</v>
+        <v>4.4444444444444509E-2</v>
       </c>
       <c r="U63">
         <v>4</v>
@@ -6096,27 +6106,27 @@
       </c>
       <c r="F64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>67882627.172021404</v>
+        <v>71373716.671775326</v>
       </c>
       <c r="G64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>71504925.88939625</v>
+        <v>75539145.629662246</v>
       </c>
       <c r="H64" s="12">
         <f t="shared" si="0"/>
-        <v>5.3361204011677099E-2</v>
+        <v>5.8360824574154924E-2</v>
       </c>
       <c r="I64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1445</v>
+        <v>1370</v>
       </c>
       <c r="J64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1277</v>
+        <v>1362</v>
       </c>
       <c r="K64" s="12">
         <f t="shared" si="1"/>
-        <v>-0.11626297577854672</v>
+        <v>-5.839416058394109E-3</v>
       </c>
       <c r="L64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6136,23 +6146,23 @@
       </c>
       <c r="P64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="Q64" s="12">
         <f t="shared" si="3"/>
-        <v>0.94672131147540983</v>
+        <v>0.95081967213114749</v>
       </c>
       <c r="R64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1999</v>
+        <v>1984</v>
       </c>
       <c r="S64">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2271</v>
+        <v>2259</v>
       </c>
       <c r="T64" s="12">
         <f t="shared" si="4"/>
-        <v>0.1360680340170084</v>
+        <v>0.13860887096774199</v>
       </c>
       <c r="U64">
         <v>9</v>
@@ -6176,27 +6186,27 @@
       </c>
       <c r="F65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5076964.1164683579</v>
+        <v>5369530.2958202437</v>
       </c>
       <c r="G65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>2920456.5121259899</v>
+        <v>3163370.7771156929</v>
       </c>
       <c r="H65" s="12">
         <f t="shared" si="0"/>
-        <v>-0.42476321574683096</v>
+        <v>-0.41086638814979259</v>
       </c>
       <c r="I65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>236</v>
+        <v>268</v>
       </c>
       <c r="J65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="K65" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-9.7014925373134275E-2</v>
       </c>
       <c r="L65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6224,15 +6234,15 @@
       </c>
       <c r="R65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="S65">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="T65" s="12">
         <f t="shared" si="4"/>
-        <v>-4.9056603773584895E-2</v>
+        <v>-2.6819923371647514E-2</v>
       </c>
       <c r="U65">
         <v>3</v>
@@ -6256,31 +6266,31 @@
       </c>
       <c r="F66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>53626628.117396288</v>
+        <v>56257298.48234468</v>
       </c>
       <c r="G66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>51942957.043750465</v>
+        <v>54652536.380899057</v>
       </c>
       <c r="H66" s="12">
         <f t="shared" si="0"/>
-        <v>-3.1396176354031247E-2</v>
+        <v>-2.8525402831940938E-2</v>
       </c>
       <c r="I66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1560</v>
+        <v>1598</v>
       </c>
       <c r="J66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1921</v>
+        <v>1580</v>
       </c>
       <c r="K66" s="12">
         <f t="shared" si="1"/>
-        <v>0.23141025641025648</v>
+        <v>-1.126408010012514E-2</v>
       </c>
       <c r="L66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -6288,7 +6298,7 @@
       </c>
       <c r="N66" s="12">
         <f t="shared" si="2"/>
-        <v>-0.1428571428571429</v>
+        <v>-0.25</v>
       </c>
       <c r="O66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -6296,23 +6306,23 @@
       </c>
       <c r="P66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q66" s="12">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0.66666666666666674</v>
       </c>
       <c r="R66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1805</v>
+        <v>1797</v>
       </c>
       <c r="S66">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1667</v>
+        <v>1672</v>
       </c>
       <c r="T66" s="12">
         <f t="shared" si="4"/>
-        <v>-7.6454293628808845E-2</v>
+        <v>-6.9560378408458523E-2</v>
       </c>
       <c r="U66">
         <v>6</v>
@@ -6336,27 +6346,27 @@
       </c>
       <c r="F67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21968090.95705428</v>
+        <v>22953791.33224605</v>
       </c>
       <c r="G67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>24581273.682099607</v>
+        <v>25985617.40753483</v>
       </c>
       <c r="H67" s="12">
         <f t="shared" ref="H67:H85" si="5">IFERROR(G67/F67-1,0)</f>
-        <v>0.11895356452018846</v>
+        <v>0.13208389112737096</v>
       </c>
       <c r="I67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>610</v>
+        <v>590</v>
       </c>
       <c r="J67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>763</v>
+        <v>646</v>
       </c>
       <c r="K67" s="12">
         <f t="shared" ref="K67:K85" si="6">IFERROR(J67/I67-1,0)</f>
-        <v>0.25081967213114753</v>
+        <v>9.4915254237288194E-2</v>
       </c>
       <c r="L67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6372,15 +6382,15 @@
       </c>
       <c r="O67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q67" s="12">
         <f t="shared" ref="Q67:Q85" si="8">IFERROR(P67/O67-1,0)</f>
-        <v>0.5</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="R67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -6388,11 +6398,11 @@
       </c>
       <c r="S67">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="T67" s="12">
         <f t="shared" ref="T67:T85" si="9">IFERROR(S67/R67-1,0)</f>
-        <v>0.10344827586206895</v>
+        <v>0.10944527736131926</v>
       </c>
       <c r="U67">
         <v>3</v>
@@ -6416,27 +6426,27 @@
       </c>
       <c r="F68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>36202729.775051877</v>
+        <v>38152542.670676976</v>
       </c>
       <c r="G68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>37415644.270037763</v>
+        <v>39573153.64074301</v>
       </c>
       <c r="H68" s="12">
         <f t="shared" si="5"/>
-        <v>3.3503398846507215E-2</v>
+        <v>3.7235027356587569E-2</v>
       </c>
       <c r="I68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1260</v>
+        <v>1027</v>
       </c>
       <c r="J68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1532</v>
+        <v>987</v>
       </c>
       <c r="K68" s="12">
         <f t="shared" si="6"/>
-        <v>0.21587301587301577</v>
+        <v>-3.8948393378773094E-2</v>
       </c>
       <c r="L68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6456,23 +6466,23 @@
       </c>
       <c r="P68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="Q68" s="12">
         <f t="shared" si="8"/>
-        <v>-0.48888888888888893</v>
+        <v>0.62222222222222223</v>
       </c>
       <c r="R68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1326</v>
+        <v>1321</v>
       </c>
       <c r="S68">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1382</v>
+        <v>1433</v>
       </c>
       <c r="T68" s="12">
         <f t="shared" si="9"/>
-        <v>4.2232277526395245E-2</v>
+        <v>8.4784254352763044E-2</v>
       </c>
       <c r="U68">
         <v>4</v>
@@ -6496,27 +6506,27 @@
       </c>
       <c r="F69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17783711.442227617</v>
+        <v>18265551.76599412</v>
       </c>
       <c r="G69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23929894.673063796</v>
+        <v>25656378.209861528</v>
       </c>
       <c r="H69" s="12">
         <f t="shared" si="5"/>
-        <v>0.34560745380978242</v>
+        <v>0.40463198366814601</v>
       </c>
       <c r="I69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1260</v>
+        <v>597</v>
       </c>
       <c r="J69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1215</v>
+        <v>1253</v>
       </c>
       <c r="K69" s="12">
         <f t="shared" si="6"/>
-        <v>-3.5714285714285698E-2</v>
+        <v>1.0988274706867673</v>
       </c>
       <c r="L69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6536,23 +6546,23 @@
       </c>
       <c r="P69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q69" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.28571428571428581</v>
       </c>
       <c r="R69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1358</v>
+        <v>1345</v>
       </c>
       <c r="S69">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="T69" s="12">
         <f t="shared" si="9"/>
-        <v>-7.5110456553755478E-2</v>
+        <v>-6.394052044609666E-2</v>
       </c>
       <c r="U69">
         <v>4</v>
@@ -6576,27 +6586,27 @@
       </c>
       <c r="F70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>63481150.813349932</v>
+        <v>67202251.554740682</v>
       </c>
       <c r="G70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>65060314.538961947</v>
+        <v>68457996.802198336</v>
       </c>
       <c r="H70" s="12">
         <f t="shared" si="5"/>
-        <v>2.4876104251089215E-2</v>
+        <v>1.8686059148401712E-2</v>
       </c>
       <c r="I70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1180</v>
+        <v>1236</v>
       </c>
       <c r="J70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1259</v>
+        <v>1225</v>
       </c>
       <c r="K70" s="12">
         <f t="shared" si="6"/>
-        <v>6.6949152542372881E-2</v>
+        <v>-8.8996763754045638E-3</v>
       </c>
       <c r="L70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6624,7 +6634,7 @@
       </c>
       <c r="R70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="S70">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -6632,7 +6642,7 @@
       </c>
       <c r="T70" s="12">
         <f t="shared" si="9"/>
-        <v>-8.0183276059564434E-3</v>
+        <v>-7.4498567335243848E-3</v>
       </c>
       <c r="U70">
         <v>4</v>
@@ -6656,27 +6666,27 @@
       </c>
       <c r="F71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13786630.717428997</v>
+        <v>14429554.57921656</v>
       </c>
       <c r="G71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13044733.106628915</v>
+        <v>13727240.991854239</v>
       </c>
       <c r="H71" s="12">
         <f t="shared" si="5"/>
-        <v>-5.3812829690301212E-2</v>
+        <v>-4.8671882663231303E-2</v>
       </c>
       <c r="I71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>424</v>
+        <v>628</v>
       </c>
       <c r="J71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="K71" s="12">
         <f t="shared" si="6"/>
-        <v>4.7169811320754818E-2</v>
+        <v>-0.30095541401273884</v>
       </c>
       <c r="L71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6704,15 +6714,15 @@
       </c>
       <c r="R71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="S71">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="T71" s="12">
         <f t="shared" si="9"/>
-        <v>4.8780487804878092E-2</v>
+        <v>4.0241448692152959E-2</v>
       </c>
       <c r="U71">
         <v>2</v>
@@ -6736,27 +6746,27 @@
       </c>
       <c r="F72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21117188.467634171</v>
+        <v>22171799.827533696</v>
       </c>
       <c r="G72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21197941.625014752</v>
+        <v>22253625.293895539</v>
       </c>
       <c r="H72" s="12">
         <f t="shared" si="5"/>
-        <v>3.8240487129406198E-3</v>
+        <v>3.690519804361081E-3</v>
       </c>
       <c r="I72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>790</v>
+        <v>852</v>
       </c>
       <c r="J72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>808</v>
+        <v>788</v>
       </c>
       <c r="K72" s="12">
         <f t="shared" si="6"/>
-        <v>2.2784810126582178E-2</v>
+        <v>-7.5117370892018753E-2</v>
       </c>
       <c r="L72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6772,27 +6782,27 @@
       </c>
       <c r="O72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q72" s="12">
         <f t="shared" si="8"/>
-        <v>-0.5</v>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="R72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="S72">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="T72" s="12">
         <f t="shared" si="9"/>
-        <v>-9.009009009009028E-3</v>
+        <v>-7.8740157480314821E-3</v>
       </c>
       <c r="U72">
         <v>3</v>
@@ -6816,27 +6826,27 @@
       </c>
       <c r="F73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14736341.28762248</v>
+        <v>15045724.399837304</v>
       </c>
       <c r="G73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20935184.704319578</v>
+        <v>22077326.343890451</v>
       </c>
       <c r="H73" s="12">
         <f t="shared" si="5"/>
-        <v>0.4206500986716224</v>
+        <v>0.46734884656860931</v>
       </c>
       <c r="I73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>416</v>
+        <v>633</v>
       </c>
       <c r="J73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="K73" s="12">
         <f t="shared" si="6"/>
-        <v>0.18509615384615374</v>
+        <v>-0.25750394944707744</v>
       </c>
       <c r="L73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6864,15 +6874,15 @@
       </c>
       <c r="R73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="S73">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="T73" s="12">
         <f t="shared" si="9"/>
-        <v>-2.5525525525525561E-2</v>
+        <v>-3.4379671150971625E-2</v>
       </c>
       <c r="U73">
         <v>7</v>
@@ -6896,27 +6906,27 @@
       </c>
       <c r="F74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13803241.814353952</v>
+        <v>13803246.696355209</v>
       </c>
       <c r="G74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15506233.992221871</v>
+        <v>16036060.553102637</v>
       </c>
       <c r="H74" s="12">
         <f t="shared" si="5"/>
-        <v>0.12337624746217091</v>
+        <v>0.16176004862225701</v>
       </c>
       <c r="I74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>551</v>
+        <v>513</v>
       </c>
       <c r="K74" s="12">
         <f t="shared" si="6"/>
-        <v>44.916666666666664</v>
+        <v>38.46153846153846</v>
       </c>
       <c r="L74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6944,15 +6954,15 @@
       </c>
       <c r="R74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="S74">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="T74" s="12">
         <f t="shared" si="9"/>
-        <v>1.9867549668874274E-2</v>
+        <v>4.8986486486486402E-2</v>
       </c>
       <c r="U74">
         <v>2</v>
@@ -6976,27 +6986,27 @@
       </c>
       <c r="F75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16238993.027723324</v>
+        <v>17050229.600482032</v>
       </c>
       <c r="G75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17523590.520165198</v>
+        <v>18475041.61702498</v>
       </c>
       <c r="H75" s="12">
         <f t="shared" si="5"/>
-        <v>7.9105735820490741E-2</v>
+        <v>8.3565561868015337E-2</v>
       </c>
       <c r="I75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="J75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>475</v>
+        <v>499</v>
       </c>
       <c r="K75" s="12">
         <f t="shared" si="6"/>
-        <v>0.13365155131264927</v>
+        <v>0.17136150234741776</v>
       </c>
       <c r="L75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7024,7 +7034,7 @@
       </c>
       <c r="R75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="S75">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -7032,7 +7042,7 @@
       </c>
       <c r="T75" s="12">
         <f t="shared" si="9"/>
-        <v>2.5345622119815614E-2</v>
+        <v>2.7713625866050862E-2</v>
       </c>
       <c r="U75">
         <v>1</v>
@@ -7056,31 +7066,31 @@
       </c>
       <c r="F76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>46538332.60440968</v>
+        <v>49208948.078755222</v>
       </c>
       <c r="G76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>46909192.026860319</v>
+        <v>49281799.342978746</v>
       </c>
       <c r="H76" s="12">
         <f t="shared" si="5"/>
-        <v>7.9689022295461598E-3</v>
+        <v>1.4804475012741847E-3</v>
       </c>
       <c r="I76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>550</v>
+        <v>788</v>
       </c>
       <c r="J76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>757</v>
+        <v>610</v>
       </c>
       <c r="K76" s="12">
         <f t="shared" si="6"/>
-        <v>0.37636363636363646</v>
+        <v>-0.2258883248730964</v>
       </c>
       <c r="L76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -7088,31 +7098,31 @@
       </c>
       <c r="N76" s="12">
         <f t="shared" si="7"/>
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="O76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q76" s="12">
         <f t="shared" si="8"/>
-        <v>-0.22222222222222221</v>
+        <v>-0.27272727272727271</v>
       </c>
       <c r="R76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>959</v>
+        <v>952</v>
       </c>
       <c r="S76">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>908</v>
+        <v>896</v>
       </c>
       <c r="T76" s="12">
         <f t="shared" si="9"/>
-        <v>-5.3180396246089723E-2</v>
+        <v>-5.8823529411764719E-2</v>
       </c>
       <c r="U76">
         <v>4</v>
@@ -7136,27 +7146,27 @@
       </c>
       <c r="F77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>27857525.216046929</v>
+        <v>29405507.483340576</v>
       </c>
       <c r="G77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>27265674.916935232</v>
+        <v>28529057.216889117</v>
       </c>
       <c r="H77" s="12">
         <f t="shared" si="5"/>
-        <v>-2.1245616562190928E-2</v>
+        <v>-2.9805650079258283E-2</v>
       </c>
       <c r="I77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>754</v>
+        <v>744</v>
       </c>
       <c r="J77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>734</v>
+        <v>724</v>
       </c>
       <c r="K77" s="12">
         <f t="shared" si="6"/>
-        <v>-2.6525198938992078E-2</v>
+        <v>-2.6881720430107503E-2</v>
       </c>
       <c r="L77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7172,11 +7182,11 @@
       </c>
       <c r="O77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q77" s="12">
         <f t="shared" si="8"/>
@@ -7184,15 +7194,15 @@
       </c>
       <c r="R77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="S77">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="T77" s="12">
         <f t="shared" si="9"/>
-        <v>-1.6602809706257937E-2</v>
+        <v>-1.5267175572519109E-2</v>
       </c>
       <c r="U77">
         <v>3</v>
@@ -7216,27 +7226,27 @@
       </c>
       <c r="F78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>22505847.82083239</v>
+        <v>23976905.020967472</v>
       </c>
       <c r="G78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22856536.852877505</v>
+        <v>24304206.202539802</v>
       </c>
       <c r="H78" s="12">
         <f t="shared" si="5"/>
-        <v>1.5582129357530894E-2</v>
+        <v>1.3650685160829124E-2</v>
       </c>
       <c r="I78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>893</v>
+        <v>1049</v>
       </c>
       <c r="J78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1081</v>
+        <v>1171</v>
       </c>
       <c r="K78" s="12">
         <f t="shared" si="6"/>
-        <v>0.21052631578947367</v>
+        <v>0.11630123927550051</v>
       </c>
       <c r="L78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7252,7 +7262,7 @@
       </c>
       <c r="O78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -7260,19 +7270,19 @@
       </c>
       <c r="Q78" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>943</v>
+        <v>951</v>
       </c>
       <c r="S78">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="T78" s="12">
         <f t="shared" si="9"/>
-        <v>1.6967126193001114E-2</v>
+        <v>9.4637223974762819E-3</v>
       </c>
       <c r="U78">
         <v>3</v>
@@ -7296,27 +7306,27 @@
       </c>
       <c r="F79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>25689391.598872714</v>
+        <v>27051046.84657656</v>
       </c>
       <c r="G79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23804512.005560592</v>
+        <v>25200040.858496305</v>
       </c>
       <c r="H79" s="12">
         <f t="shared" si="5"/>
-        <v>-7.3371904743545269E-2</v>
+        <v>-6.8426408729335697E-2</v>
       </c>
       <c r="I79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>792</v>
+        <v>818</v>
       </c>
       <c r="J79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>855</v>
+        <v>828</v>
       </c>
       <c r="K79" s="12">
         <f t="shared" si="6"/>
-        <v>7.9545454545454586E-2</v>
+        <v>1.2224938875305513E-2</v>
       </c>
       <c r="L79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7344,15 +7354,15 @@
       </c>
       <c r="R79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="S79">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="T79" s="12">
         <f t="shared" si="9"/>
-        <v>-2.1674876847290636E-2</v>
+        <v>-2.4606299212598381E-2</v>
       </c>
       <c r="U79">
         <v>3</v>
@@ -7376,27 +7386,27 @@
       </c>
       <c r="F80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>27707878.138874147</v>
+        <v>29446746.70471419</v>
       </c>
       <c r="G80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>30321505.756113347</v>
+        <v>32219102.200047638</v>
       </c>
       <c r="H80" s="12">
         <f t="shared" si="5"/>
-        <v>9.4327959872621214E-2</v>
+        <v>9.4148108214942905E-2</v>
       </c>
       <c r="I80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>727</v>
+        <v>756</v>
       </c>
       <c r="J80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>742</v>
+        <v>772</v>
       </c>
       <c r="K80" s="12">
         <f t="shared" si="6"/>
-        <v>2.0632737276478741E-2</v>
+        <v>2.1164021164021163E-2</v>
       </c>
       <c r="L80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7424,15 +7434,15 @@
       </c>
       <c r="R80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="S80">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="T80" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1.3245033112583293E-3</v>
       </c>
       <c r="U80">
         <v>3</v>
@@ -7456,27 +7466,27 @@
       </c>
       <c r="F81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12297623.509624189</v>
+        <v>12890849.296891289</v>
       </c>
       <c r="G81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13851013.837541368</v>
+        <v>14575510.609984348</v>
       </c>
       <c r="H81" s="12">
         <f t="shared" si="5"/>
-        <v>0.12631630222713253</v>
+        <v>0.13068660367469542</v>
       </c>
       <c r="I81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>632</v>
+        <v>679</v>
       </c>
       <c r="J81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>544</v>
+        <v>589</v>
       </c>
       <c r="K81" s="12">
         <f t="shared" si="6"/>
-        <v>-0.13924050632911389</v>
+        <v>-0.13254786450662737</v>
       </c>
       <c r="L81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7496,23 +7506,23 @@
       </c>
       <c r="P81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q81" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="S81">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="T81" s="12">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1.7636684303350414E-3</v>
       </c>
       <c r="U81">
         <v>1</v>
@@ -7536,27 +7546,27 @@
       </c>
       <c r="F82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>52982781.551008649</v>
+        <v>55870676.347908162</v>
       </c>
       <c r="G82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>56341564.403701298</v>
+        <v>60561873.35205964</v>
       </c>
       <c r="H82" s="12">
         <f t="shared" si="5"/>
-        <v>6.3393856539204485E-2</v>
+        <v>8.3965280372467088E-2</v>
       </c>
       <c r="I82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1317</v>
+        <v>1385</v>
       </c>
       <c r="J82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>824</v>
+        <v>1394</v>
       </c>
       <c r="K82" s="12">
         <f t="shared" si="6"/>
-        <v>-0.37433561123766135</v>
+        <v>6.4981949458484678E-3</v>
       </c>
       <c r="L82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7572,27 +7582,27 @@
       </c>
       <c r="O82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q82" s="12">
         <f t="shared" si="8"/>
-        <v>-0.33333333333333337</v>
+        <v>-0.30000000000000004</v>
       </c>
       <c r="R82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1700</v>
+        <v>1696</v>
       </c>
       <c r="S82">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1763</v>
+        <v>1768</v>
       </c>
       <c r="T82" s="12">
         <f t="shared" si="9"/>
-        <v>3.7058823529411811E-2</v>
+        <v>4.2452830188679291E-2</v>
       </c>
       <c r="U82">
         <v>2</v>
@@ -7616,27 +7626,27 @@
       </c>
       <c r="F83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14099053.264334928</v>
+        <v>15216982.418813448</v>
       </c>
       <c r="G83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13251615.22394882</v>
+        <v>13821141.409075508</v>
       </c>
       <c r="H83" s="12">
         <f t="shared" si="5"/>
-        <v>-6.010602446121649E-2</v>
+        <v>-9.1729159653375025E-2</v>
       </c>
       <c r="I83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>628</v>
+        <v>903</v>
       </c>
       <c r="J83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>625</v>
+        <v>648</v>
       </c>
       <c r="K83" s="12">
         <f t="shared" si="6"/>
-        <v>-4.777070063694322E-3</v>
+        <v>-0.28239202657807305</v>
       </c>
       <c r="L83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7664,15 +7674,15 @@
       </c>
       <c r="R83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="S83">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="T83" s="12">
         <f t="shared" si="9"/>
-        <v>-4.8414023372287174E-2</v>
+        <v>-5.6666666666666643E-2</v>
       </c>
       <c r="U83">
         <v>2</v>
@@ -7696,27 +7706,27 @@
       </c>
       <c r="F84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24761684.048804503</v>
+        <v>26078100.101177879</v>
       </c>
       <c r="G84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>25936117.318591543</v>
+        <v>27183832.475523256</v>
       </c>
       <c r="H84" s="12">
         <f t="shared" si="5"/>
-        <v>4.7429458653630574E-2</v>
+        <v>4.2400802591268327E-2</v>
       </c>
       <c r="I84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>574</v>
+        <v>521</v>
       </c>
       <c r="J84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="K84" s="12">
         <f t="shared" si="6"/>
-        <v>-8.362369337979092E-2</v>
+        <v>1.9193857965451588E-3</v>
       </c>
       <c r="L84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7732,7 +7742,7 @@
       </c>
       <c r="O84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -7740,19 +7750,19 @@
       </c>
       <c r="Q84" s="12">
         <f t="shared" si="8"/>
-        <v>-0.66666666666666674</v>
+        <v>-0.69230769230769229</v>
       </c>
       <c r="R84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="S84">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="T84" s="12">
         <f t="shared" si="9"/>
-        <v>4.4701986754966949E-2</v>
+        <v>5.3333333333333233E-2</v>
       </c>
       <c r="U84">
         <v>7</v>
@@ -7776,27 +7786,27 @@
       </c>
       <c r="F85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6820595.096124053</v>
+        <v>7162107.3929737266</v>
       </c>
       <c r="G85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6214020.6016599154</v>
+        <v>6488168.8620083621</v>
       </c>
       <c r="H85" s="12">
         <f t="shared" si="5"/>
-        <v>-8.8932781658426885E-2</v>
+        <v>-9.4097797475994449E-2</v>
       </c>
       <c r="I85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="J85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>363</v>
+        <v>304</v>
       </c>
       <c r="K85" s="12">
         <f t="shared" si="6"/>
-        <v>0.12732919254658381</v>
+        <v>-7.3170731707317027E-2</v>
       </c>
       <c r="L85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7812,7 +7822,7 @@
       </c>
       <c r="O85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -7820,19 +7830,19 @@
       </c>
       <c r="Q85" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>-0.33333333333333337</v>
       </c>
       <c r="R85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="S85">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="T85" s="12">
         <f t="shared" si="9"/>
-        <v>-8.2872928176795924E-3</v>
+        <v>-1.377410468319562E-2</v>
       </c>
       <c r="U85">
         <v>2</v>
@@ -7845,7 +7855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:K90"/>
+  <dimension ref="A3:K91"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -7865,11 +7875,11 @@
       <c r="A3" s="11"/>
       <c r="B3" s="11">
         <f t="shared" ref="B3:K3" si="0">SUBTOTAL(9,B6:B90)</f>
-        <v>84274</v>
+        <v>84155</v>
       </c>
       <c r="C3" s="11">
         <f t="shared" si="0"/>
-        <v>1453</v>
+        <v>1484</v>
       </c>
       <c r="D3" s="11">
         <f t="shared" si="0"/>
@@ -7877,31 +7887,31 @@
       </c>
       <c r="E3" s="11">
         <f t="shared" si="0"/>
-        <v>70462</v>
+        <v>70150</v>
       </c>
       <c r="F3" s="11">
         <f t="shared" si="0"/>
-        <v>2624274086.5847387</v>
+        <v>2762661133.2590084</v>
       </c>
       <c r="G3" s="11">
         <f t="shared" si="0"/>
-        <v>84388</v>
+        <v>84561</v>
       </c>
       <c r="H3" s="11">
         <f t="shared" si="0"/>
-        <v>1269</v>
+        <v>1547</v>
       </c>
       <c r="I3" s="11">
         <f t="shared" si="0"/>
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J3" s="11">
         <f t="shared" si="0"/>
-        <v>70547</v>
+        <v>70937</v>
       </c>
       <c r="K3" s="11">
         <f t="shared" si="0"/>
-        <v>2696476987.8468094</v>
+        <v>2842605836.7440019</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -7970,25 +7980,25 @@
         <v>2</v>
       </c>
       <c r="E6" s="10">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="F6" s="10">
-        <v>12452036.798173808</v>
+        <v>13087808.370799534</v>
       </c>
       <c r="G6" s="10">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="H6" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="10">
         <v>2</v>
       </c>
       <c r="J6" s="10">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="K6" s="10">
-        <v>12287955.952436997</v>
+        <v>12916722.729567273</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
@@ -7996,7 +8006,7 @@
         <v>127</v>
       </c>
       <c r="B7" s="10">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="C7" s="10">
         <v>2</v>
@@ -8005,13 +8015,13 @@
         <v>1</v>
       </c>
       <c r="E7" s="10">
-        <v>525</v>
+        <v>492</v>
       </c>
       <c r="F7" s="10">
-        <v>15270377.5820772</v>
+        <v>15998166.242166299</v>
       </c>
       <c r="G7" s="10">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H7" s="10">
         <v>6</v>
@@ -8020,10 +8030,10 @@
         <v>2</v>
       </c>
       <c r="J7" s="10">
-        <v>487</v>
+        <v>500</v>
       </c>
       <c r="K7" s="10">
-        <v>14339947.092993161</v>
+        <v>15084594.410566358</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
@@ -8031,7 +8041,7 @@
         <v>119</v>
       </c>
       <c r="B8" s="10">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="C8" s="10">
         <v>7</v>
@@ -8040,25 +8050,25 @@
         <v>2</v>
       </c>
       <c r="E8" s="10">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="F8" s="10">
-        <v>17041117.995255239</v>
+        <v>18423447.133026849</v>
       </c>
       <c r="G8" s="10">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="H8" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I8" s="10">
         <v>1</v>
       </c>
       <c r="J8" s="10">
-        <v>806</v>
+        <v>788</v>
       </c>
       <c r="K8" s="10">
-        <v>19961475.905457538</v>
+        <v>21263351.156662799</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
@@ -8066,7 +8076,7 @@
         <v>121</v>
       </c>
       <c r="B9" s="10">
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="C9" s="10">
         <v>7</v>
@@ -8075,13 +8085,13 @@
         <v>3</v>
       </c>
       <c r="E9" s="10">
-        <v>1468</v>
+        <v>1484</v>
       </c>
       <c r="F9" s="10">
-        <v>30428581.790787671</v>
+        <v>32444786.249515016</v>
       </c>
       <c r="G9" s="10">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="H9" s="10">
         <v>8</v>
@@ -8090,10 +8100,10 @@
         <v>3</v>
       </c>
       <c r="J9" s="10">
-        <v>1088</v>
+        <v>1130</v>
       </c>
       <c r="K9" s="10">
-        <v>31260783.726436041</v>
+        <v>33059806.89004685</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
@@ -8101,7 +8111,7 @@
         <v>123</v>
       </c>
       <c r="B10" s="10">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C10" s="10">
         <v>1</v>
@@ -8110,13 +8120,13 @@
         <v>1</v>
       </c>
       <c r="E10" s="10">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="F10" s="10">
-        <v>12572009.692979235</v>
+        <v>13426816.547492765</v>
       </c>
       <c r="G10" s="10">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="H10" s="10">
         <v>1</v>
@@ -8125,10 +8135,10 @@
         <v>1</v>
       </c>
       <c r="J10" s="10">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="K10" s="10">
-        <v>14087321.867469653</v>
+        <v>14740995.052347932</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
@@ -8136,7 +8146,7 @@
         <v>125</v>
       </c>
       <c r="B11" s="10">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C11" s="10">
         <v>3</v>
@@ -8145,13 +8155,13 @@
         <v>2</v>
       </c>
       <c r="E11" s="10">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="F11" s="10">
-        <v>10954941.459135331</v>
+        <v>11608508.537279077</v>
       </c>
       <c r="G11" s="10">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H11" s="10">
         <v>3</v>
@@ -8160,10 +8170,10 @@
         <v>2</v>
       </c>
       <c r="J11" s="10">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="K11" s="10">
-        <v>11489847.967613995</v>
+        <v>12076791.011960519</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -8171,7 +8181,7 @@
         <v>131</v>
       </c>
       <c r="B12" s="10">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C12" s="10">
         <v>1</v>
@@ -8180,13 +8190,13 @@
         <v>1</v>
       </c>
       <c r="E12" s="10">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="F12" s="10">
-        <v>12590405.038448486</v>
+        <v>13234286.009974919</v>
       </c>
       <c r="G12" s="10">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="H12" s="10">
         <v>3</v>
@@ -8195,10 +8205,10 @@
         <v>2</v>
       </c>
       <c r="J12" s="10">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="K12" s="10">
-        <v>13775550.668594858</v>
+        <v>14483043.079303995</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
@@ -8206,7 +8216,7 @@
         <v>133</v>
       </c>
       <c r="B13" s="10">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C13" s="10">
         <v>0</v>
@@ -8215,13 +8225,13 @@
         <v>1</v>
       </c>
       <c r="E13" s="10">
-        <v>385</v>
+        <v>168</v>
       </c>
       <c r="F13" s="10">
-        <v>5908394.1481695939</v>
+        <v>6272122.0239012884</v>
       </c>
       <c r="G13" s="10">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H13" s="10">
         <v>0</v>
@@ -8230,10 +8240,10 @@
         <v>1</v>
       </c>
       <c r="J13" s="10">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="K13" s="10">
-        <v>6045648.5828848016</v>
+        <v>6320873.6215354437</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
@@ -8250,10 +8260,10 @@
         <v>0</v>
       </c>
       <c r="E14" s="10">
-        <v>226</v>
+        <v>184</v>
       </c>
       <c r="F14" s="10">
-        <v>5680298.6802293016</v>
+        <v>5986210.4536223654</v>
       </c>
       <c r="G14" s="10">
         <v>187</v>
@@ -8265,10 +8275,10 @@
         <v>1</v>
       </c>
       <c r="J14" s="10">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="K14" s="10">
-        <v>2860659.9967147</v>
+        <v>3146674.465636583</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
@@ -8276,7 +8286,7 @@
         <v>135</v>
       </c>
       <c r="B15" s="10">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C15" s="10">
         <v>0</v>
@@ -8285,25 +8295,25 @@
         <v>1</v>
       </c>
       <c r="E15" s="10">
-        <v>376</v>
+        <v>339</v>
       </c>
       <c r="F15" s="10">
-        <v>8944383.1211307161</v>
+        <v>9371873.1319251489</v>
       </c>
       <c r="G15" s="10">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H15" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I15" s="10">
         <v>1</v>
       </c>
       <c r="J15" s="10">
-        <v>347</v>
+        <v>382</v>
       </c>
       <c r="K15" s="10">
-        <v>11890504.003905904</v>
+        <v>12410426.942553291</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
@@ -8311,22 +8321,22 @@
         <v>143</v>
       </c>
       <c r="B16" s="10">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C16" s="10">
         <v>0</v>
       </c>
       <c r="D16" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="10">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F16" s="10">
-        <v>4262490.9429104608</v>
+        <v>4545722.9148001587</v>
       </c>
       <c r="G16" s="10">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="H16" s="10">
         <v>0</v>
@@ -8335,10 +8345,10 @@
         <v>2</v>
       </c>
       <c r="J16" s="10">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="K16" s="10">
-        <v>6152814.3065978391</v>
+        <v>6532815.7132673627</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -8346,7 +8356,7 @@
         <v>145</v>
       </c>
       <c r="B17" s="10">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C17" s="10">
         <v>7</v>
@@ -8355,13 +8365,13 @@
         <v>1</v>
       </c>
       <c r="E17" s="10">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="F17" s="10">
-        <v>5733341.8539821506</v>
+        <v>6093279.5223717354</v>
       </c>
       <c r="G17" s="10">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H17" s="10">
         <v>2</v>
@@ -8370,10 +8380,10 @@
         <v>1</v>
       </c>
       <c r="J17" s="10">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K17" s="10">
-        <v>6544098.7908061044</v>
+        <v>6845794.9533302337</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
@@ -8381,7 +8391,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="10">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="C18" s="10">
         <v>0</v>
@@ -8390,13 +8400,13 @@
         <v>2</v>
       </c>
       <c r="E18" s="10">
-        <v>1062</v>
+        <v>1494</v>
       </c>
       <c r="F18" s="10">
-        <v>12150068.330912439</v>
+        <v>13443706.666459411</v>
       </c>
       <c r="G18" s="10">
-        <v>1403</v>
+        <v>1384</v>
       </c>
       <c r="H18" s="10">
         <v>4</v>
@@ -8405,10 +8415,10 @@
         <v>3</v>
       </c>
       <c r="J18" s="10">
-        <v>1064</v>
+        <v>1076</v>
       </c>
       <c r="K18" s="10">
-        <v>27129953.922294252</v>
+        <v>29022560.368282694</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
@@ -8416,7 +8426,7 @@
         <v>45</v>
       </c>
       <c r="B19" s="10">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="C19" s="10">
         <v>1</v>
@@ -8425,13 +8435,13 @@
         <v>2</v>
       </c>
       <c r="E19" s="10">
-        <v>1018</v>
+        <v>181</v>
       </c>
       <c r="F19" s="10">
-        <v>37115893.490185946</v>
+        <v>37942760.593333475</v>
       </c>
       <c r="G19" s="10">
-        <v>1229</v>
+        <v>1234</v>
       </c>
       <c r="H19" s="10">
         <v>2</v>
@@ -8440,10 +8450,10 @@
         <v>3</v>
       </c>
       <c r="J19" s="10">
-        <v>913</v>
+        <v>901</v>
       </c>
       <c r="K19" s="10">
-        <v>46248297.021251909</v>
+        <v>49024095.31867002</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
@@ -8451,22 +8461,22 @@
         <v>47</v>
       </c>
       <c r="B20" s="10">
+        <v>1018</v>
+      </c>
+      <c r="C20" s="10">
+        <v>4</v>
+      </c>
+      <c r="D20" s="10">
+        <v>4</v>
+      </c>
+      <c r="E20" s="10">
+        <v>922</v>
+      </c>
+      <c r="F20" s="10">
+        <v>25808105.930136997</v>
+      </c>
+      <c r="G20" s="10">
         <v>1021</v>
-      </c>
-      <c r="C20" s="10">
-        <v>3</v>
-      </c>
-      <c r="D20" s="10">
-        <v>4</v>
-      </c>
-      <c r="E20" s="10">
-        <v>894</v>
-      </c>
-      <c r="F20" s="10">
-        <v>24557779.647644848</v>
-      </c>
-      <c r="G20" s="10">
-        <v>1025</v>
       </c>
       <c r="H20" s="10">
         <v>4</v>
@@ -8475,10 +8485,10 @@
         <v>5</v>
       </c>
       <c r="J20" s="10">
-        <v>945</v>
+        <v>859</v>
       </c>
       <c r="K20" s="10">
-        <v>24780324.33078628</v>
+        <v>26071080.14117502</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
@@ -8486,7 +8496,7 @@
         <v>49</v>
       </c>
       <c r="B21" s="10">
-        <v>960</v>
+        <v>949</v>
       </c>
       <c r="C21" s="10">
         <v>1</v>
@@ -8495,13 +8505,13 @@
         <v>3</v>
       </c>
       <c r="E21" s="10">
-        <v>651</v>
+        <v>583</v>
       </c>
       <c r="F21" s="10">
-        <v>24093521.100269504</v>
+        <v>25100221.83684345</v>
       </c>
       <c r="G21" s="10">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="H21" s="10">
         <v>4</v>
@@ -8510,10 +8520,10 @@
         <v>3</v>
       </c>
       <c r="J21" s="10">
-        <v>699</v>
+        <v>664</v>
       </c>
       <c r="K21" s="10">
-        <v>20292128.333114807</v>
+        <v>21493879.316390663</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
@@ -8521,22 +8531,22 @@
         <v>51</v>
       </c>
       <c r="B22" s="10">
-        <v>3219</v>
+        <v>3188</v>
       </c>
       <c r="C22" s="10">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D22" s="10">
         <v>10</v>
       </c>
       <c r="E22" s="10">
-        <v>2911</v>
+        <v>2699</v>
       </c>
       <c r="F22" s="10">
-        <v>84378043.245911941</v>
+        <v>89403755.644768402</v>
       </c>
       <c r="G22" s="10">
-        <v>2805</v>
+        <v>2806</v>
       </c>
       <c r="H22" s="10">
         <v>184</v>
@@ -8545,10 +8555,10 @@
         <v>10</v>
       </c>
       <c r="J22" s="10">
-        <v>2167</v>
+        <v>2125</v>
       </c>
       <c r="K22" s="10">
-        <v>91431790.086039543</v>
+        <v>95903548.545516953</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
@@ -8556,7 +8566,7 @@
         <v>53</v>
       </c>
       <c r="B23" s="10">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="C23" s="10">
         <v>0</v>
@@ -8565,13 +8575,13 @@
         <v>2</v>
       </c>
       <c r="E23" s="10">
-        <v>1155</v>
+        <v>1203</v>
       </c>
       <c r="F23" s="10">
-        <v>45853440.719571456</v>
+        <v>48127649.671235926</v>
       </c>
       <c r="G23" s="10">
-        <v>1381</v>
+        <v>1387</v>
       </c>
       <c r="H23" s="10">
         <v>7</v>
@@ -8580,10 +8590,10 @@
         <v>2</v>
       </c>
       <c r="J23" s="10">
-        <v>1192</v>
+        <v>1172</v>
       </c>
       <c r="K23" s="10">
-        <v>28580704.230768949</v>
+        <v>30944501.324133508</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
@@ -8591,34 +8601,34 @@
         <v>55</v>
       </c>
       <c r="B24" s="10">
-        <v>3008</v>
+        <v>3014</v>
       </c>
       <c r="C24" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D24" s="10">
         <v>11</v>
       </c>
       <c r="E24" s="10">
-        <v>2274</v>
+        <v>2319</v>
       </c>
       <c r="F24" s="10">
-        <v>91985409.680114254</v>
+        <v>96839659.029765069</v>
       </c>
       <c r="G24" s="10">
-        <v>2933</v>
+        <v>2929</v>
       </c>
       <c r="H24" s="10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I24" s="10">
         <v>10</v>
       </c>
       <c r="J24" s="10">
-        <v>1971</v>
+        <v>2118</v>
       </c>
       <c r="K24" s="10">
-        <v>91798677.850888729</v>
+        <v>96555492.863442063</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
@@ -8626,7 +8636,7 @@
         <v>67</v>
       </c>
       <c r="B25" s="10">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C25" s="10">
         <v>6</v>
@@ -8635,13 +8645,13 @@
         <v>1</v>
       </c>
       <c r="E25" s="10">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="F25" s="10">
-        <v>13083985.836379612</v>
+        <v>13858968.280016633</v>
       </c>
       <c r="G25" s="10">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="H25" s="10">
         <v>5</v>
@@ -8650,10 +8660,10 @@
         <v>1</v>
       </c>
       <c r="J25" s="10">
-        <v>487</v>
+        <v>451</v>
       </c>
       <c r="K25" s="10">
-        <v>13952390.293539824</v>
+        <v>14656128.885179391</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
@@ -8661,34 +8671,34 @@
         <v>74</v>
       </c>
       <c r="B26" s="10">
-        <v>1707</v>
+        <v>1712</v>
       </c>
       <c r="C26" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D26" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" s="10">
-        <v>1256</v>
+        <v>1285</v>
       </c>
       <c r="F26" s="10">
-        <v>36202793.63631741</v>
+        <v>38076981.426078215</v>
       </c>
       <c r="G26" s="10">
-        <v>1679</v>
+        <v>1657</v>
       </c>
       <c r="H26" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I26" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26" s="10">
-        <v>1368</v>
+        <v>1351</v>
       </c>
       <c r="K26" s="10">
-        <v>38550165.164171152</v>
+        <v>40696450.341174901</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
@@ -8696,22 +8706,22 @@
         <v>70</v>
       </c>
       <c r="B27" s="10">
-        <v>862</v>
+        <v>872</v>
       </c>
       <c r="C27" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D27" s="10">
         <v>1</v>
       </c>
       <c r="E27" s="10">
-        <v>1010</v>
+        <v>919</v>
       </c>
       <c r="F27" s="10">
-        <v>15994034.782365471</v>
+        <v>16999705.014675111</v>
       </c>
       <c r="G27" s="10">
-        <v>879</v>
+        <v>864</v>
       </c>
       <c r="H27" s="10">
         <v>10</v>
@@ -8720,10 +8730,10 @@
         <v>1</v>
       </c>
       <c r="J27" s="10">
-        <v>820</v>
+        <v>775</v>
       </c>
       <c r="K27" s="10">
-        <v>16023991.278544333</v>
+        <v>16848952.521488499</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
@@ -8740,13 +8750,13 @@
         <v>1</v>
       </c>
       <c r="E28" s="10">
-        <v>803</v>
+        <v>870</v>
       </c>
       <c r="F28" s="10">
-        <v>17730094.775826979</v>
+        <v>18823380.21238241</v>
       </c>
       <c r="G28" s="10">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="H28" s="10">
         <v>6</v>
@@ -8755,10 +8765,10 @@
         <v>1</v>
       </c>
       <c r="J28" s="10">
-        <v>843</v>
+        <v>678</v>
       </c>
       <c r="K28" s="10">
-        <v>19429198.640231583</v>
+        <v>20465850.794823397</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
@@ -8775,10 +8785,10 @@
         <v>0</v>
       </c>
       <c r="E29" s="10">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="F29" s="10">
-        <v>5277024.5563090751</v>
+        <v>5565632.8976637917</v>
       </c>
       <c r="G29" s="10">
         <v>228</v>
@@ -8790,10 +8800,10 @@
         <v>1</v>
       </c>
       <c r="J29" s="10">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="K29" s="10">
-        <v>4433708.8725122856</v>
+        <v>4723558.2871565996</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
@@ -8801,34 +8811,34 @@
         <v>109</v>
       </c>
       <c r="B30" s="10">
-        <v>1658</v>
+        <v>1649</v>
       </c>
       <c r="C30" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D30" s="10">
         <v>5</v>
       </c>
       <c r="E30" s="10">
-        <v>1301</v>
+        <v>1388</v>
       </c>
       <c r="F30" s="10">
-        <v>40235450.07087151</v>
+        <v>42168566.16250097</v>
       </c>
       <c r="G30" s="10">
-        <v>1646</v>
+        <v>1653</v>
       </c>
       <c r="H30" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I30" s="10">
         <v>5</v>
       </c>
       <c r="J30" s="10">
-        <v>1383</v>
+        <v>1322</v>
       </c>
       <c r="K30" s="10">
-        <v>36803930.469524823</v>
+        <v>38683079.315449901</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
@@ -8836,7 +8846,7 @@
         <v>111</v>
       </c>
       <c r="B31" s="10">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="C31" s="10">
         <v>5</v>
@@ -8845,25 +8855,25 @@
         <v>1</v>
       </c>
       <c r="E31" s="10">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="F31" s="10">
-        <v>28301686.739777543</v>
+        <v>29823023.385615569</v>
       </c>
       <c r="G31" s="10">
         <v>884</v>
       </c>
       <c r="H31" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I31" s="10">
         <v>1</v>
       </c>
       <c r="J31" s="10">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="K31" s="10">
-        <v>30880741.730442863</v>
+        <v>32617935.380541101</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
@@ -8871,7 +8881,7 @@
         <v>113</v>
       </c>
       <c r="B32" s="10">
-        <v>1126</v>
+        <v>1120</v>
       </c>
       <c r="C32" s="10">
         <v>2</v>
@@ -8880,10 +8890,10 @@
         <v>1</v>
       </c>
       <c r="E32" s="10">
-        <v>765</v>
+        <v>789</v>
       </c>
       <c r="F32" s="10">
-        <v>30771914.979088616</v>
+        <v>32601221.645448308</v>
       </c>
       <c r="G32" s="10">
         <v>1042</v>
@@ -8895,10 +8905,10 @@
         <v>1</v>
       </c>
       <c r="J32" s="10">
-        <v>789</v>
+        <v>764</v>
       </c>
       <c r="K32" s="10">
-        <v>29013524.004899658</v>
+        <v>30351804.513628267</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
@@ -8906,34 +8916,34 @@
         <v>115</v>
       </c>
       <c r="B33" s="10">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="C33" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D33" s="10">
         <v>2</v>
       </c>
       <c r="E33" s="10">
-        <v>889</v>
+        <v>952</v>
       </c>
       <c r="F33" s="10">
-        <v>39627788.142400511</v>
+        <v>41893976.926671989</v>
       </c>
       <c r="G33" s="10">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H33" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I33" s="10">
         <v>2</v>
       </c>
       <c r="J33" s="10">
-        <v>874</v>
+        <v>900</v>
       </c>
       <c r="K33" s="10">
-        <v>41174058.474659473</v>
+        <v>43282975.098104343</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
@@ -8941,7 +8951,7 @@
         <v>16</v>
       </c>
       <c r="B34" s="10">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="C34" s="10">
         <v>3</v>
@@ -8950,13 +8960,13 @@
         <v>5</v>
       </c>
       <c r="E34" s="10">
-        <v>1103</v>
+        <v>1167</v>
       </c>
       <c r="F34" s="10">
-        <v>57867671.527397662</v>
+        <v>60948510.020695314</v>
       </c>
       <c r="G34" s="10">
-        <v>1443</v>
+        <v>1456</v>
       </c>
       <c r="H34" s="10">
         <v>4</v>
@@ -8965,10 +8975,10 @@
         <v>4</v>
       </c>
       <c r="J34" s="10">
-        <v>1132</v>
+        <v>1151</v>
       </c>
       <c r="K34" s="10">
-        <v>52940271.569831714</v>
+        <v>55959396.977800012</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
@@ -8976,7 +8986,7 @@
         <v>18</v>
       </c>
       <c r="B35" s="10">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="C35" s="10">
         <v>3</v>
@@ -8985,13 +8995,13 @@
         <v>3</v>
       </c>
       <c r="E35" s="10">
-        <v>535</v>
+        <v>615</v>
       </c>
       <c r="F35" s="10">
-        <v>21899406.198145673</v>
+        <v>23188488.13637552</v>
       </c>
       <c r="G35" s="10">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="H35" s="10">
         <v>1</v>
@@ -9000,10 +9010,10 @@
         <v>5</v>
       </c>
       <c r="J35" s="10">
-        <v>554</v>
+        <v>508</v>
       </c>
       <c r="K35" s="10">
-        <v>23896792.324472841</v>
+        <v>25047854.91353824</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
@@ -9011,22 +9021,22 @@
         <v>43</v>
       </c>
       <c r="B36" s="10">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="C36" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D36" s="10">
         <v>11</v>
       </c>
       <c r="E36" s="10">
-        <v>1890</v>
+        <v>2045</v>
       </c>
       <c r="F36" s="10">
-        <v>68379291.574158043</v>
+        <v>72283101.544206813</v>
       </c>
       <c r="G36" s="10">
-        <v>1926</v>
+        <v>1913</v>
       </c>
       <c r="H36" s="10">
         <v>10</v>
@@ -9035,10 +9045,10 @@
         <v>9</v>
       </c>
       <c r="J36" s="10">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="K36" s="10">
-        <v>58685299.940138116</v>
+        <v>62386024.992774226</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
@@ -9046,7 +9056,7 @@
         <v>152</v>
       </c>
       <c r="B37" s="10">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C37" s="10">
         <v>2</v>
@@ -9055,13 +9065,13 @@
         <v>2</v>
       </c>
       <c r="E37" s="10">
-        <v>620</v>
+        <v>693</v>
       </c>
       <c r="F37" s="10">
-        <v>23416239.072707906</v>
+        <v>24522885.913414594</v>
       </c>
       <c r="G37" s="10">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="H37" s="10">
         <v>3</v>
@@ -9070,10 +9080,10 @@
         <v>2</v>
       </c>
       <c r="J37" s="10">
-        <v>712</v>
+        <v>741</v>
       </c>
       <c r="K37" s="10">
-        <v>23846332.143704496</v>
+        <v>24921846.100234803</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
@@ -9081,22 +9091,22 @@
         <v>149</v>
       </c>
       <c r="B38" s="10">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C38" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D38" s="10">
         <v>1</v>
       </c>
       <c r="E38" s="10">
-        <v>534</v>
+        <v>582</v>
       </c>
       <c r="F38" s="10">
-        <v>19580984.263010703</v>
+        <v>20703555.59535294</v>
       </c>
       <c r="G38" s="10">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="H38" s="10">
         <v>3</v>
@@ -9105,10 +9115,10 @@
         <v>1</v>
       </c>
       <c r="J38" s="10">
-        <v>644</v>
+        <v>609</v>
       </c>
       <c r="K38" s="10">
-        <v>21933834.462986201</v>
+        <v>23049754.684711441</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
@@ -9116,7 +9126,7 @@
         <v>154</v>
       </c>
       <c r="B39" s="10">
-        <v>1113</v>
+        <v>1108</v>
       </c>
       <c r="C39" s="10">
         <v>14</v>
@@ -9125,25 +9135,25 @@
         <v>2</v>
       </c>
       <c r="E39" s="10">
-        <v>843</v>
+        <v>865</v>
       </c>
       <c r="F39" s="10">
-        <v>34271546.343865938</v>
+        <v>36053259.761528894</v>
       </c>
       <c r="G39" s="10">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="H39" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I39" s="10">
         <v>1</v>
       </c>
       <c r="J39" s="10">
-        <v>950</v>
+        <v>893</v>
       </c>
       <c r="K39" s="10">
-        <v>33947334.926795498</v>
+        <v>35754529.012632072</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
@@ -9151,7 +9161,7 @@
         <v>2</v>
       </c>
       <c r="B40" s="10">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="C40" s="10">
         <v>41</v>
@@ -9160,25 +9170,25 @@
         <v>1</v>
       </c>
       <c r="E40" s="10">
-        <v>769</v>
+        <v>861</v>
       </c>
       <c r="F40" s="10">
-        <v>33052464.113899976</v>
+        <v>34761818.863370262</v>
       </c>
       <c r="G40" s="10">
-        <v>1252</v>
+        <v>1381</v>
       </c>
       <c r="H40" s="10">
-        <v>121</v>
+        <v>272</v>
       </c>
       <c r="I40" s="10">
         <v>1</v>
       </c>
       <c r="J40" s="10">
-        <v>964</v>
+        <v>876</v>
       </c>
       <c r="K40" s="10">
-        <v>32190582.015026674</v>
+        <v>33981946.736486293</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
@@ -9186,34 +9196,34 @@
         <v>156</v>
       </c>
       <c r="B41" s="10">
-        <v>1784</v>
+        <v>1795</v>
       </c>
       <c r="C41" s="10">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D41" s="10">
         <v>4</v>
       </c>
       <c r="E41" s="10">
-        <v>1371</v>
+        <v>1385</v>
       </c>
       <c r="F41" s="10">
-        <v>52158232.747112714</v>
+        <v>54910655.209512085</v>
       </c>
       <c r="G41" s="10">
-        <v>2269</v>
+        <v>2277</v>
       </c>
       <c r="H41" s="10">
-        <v>73</v>
+        <v>123</v>
       </c>
       <c r="I41" s="10">
         <v>5</v>
       </c>
       <c r="J41" s="10">
-        <v>1578</v>
+        <v>1310</v>
       </c>
       <c r="K41" s="10">
-        <v>57989157.172912218</v>
+        <v>60889043.762123182</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
@@ -9221,7 +9231,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="10">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="C42" s="10">
         <v>2</v>
@@ -9230,13 +9240,13 @@
         <v>4</v>
       </c>
       <c r="E42" s="10">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F42" s="10">
         <v>17501175.59762124</v>
       </c>
       <c r="G42" s="10">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H42" s="10">
         <v>1</v>
@@ -9245,10 +9255,10 @@
         <v>6</v>
       </c>
       <c r="J42" s="10">
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="K42" s="10">
-        <v>20656820.414189544</v>
+        <v>21690653.82312274</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
@@ -9256,7 +9266,7 @@
         <v>8</v>
       </c>
       <c r="B43" s="10">
-        <v>2036</v>
+        <v>2048</v>
       </c>
       <c r="C43" s="10">
         <v>14</v>
@@ -9265,25 +9275,25 @@
         <v>5</v>
       </c>
       <c r="E43" s="10">
-        <v>1869</v>
+        <v>1854</v>
       </c>
       <c r="F43" s="10">
-        <v>61288523.598765254</v>
+        <v>63981776.356715463</v>
       </c>
       <c r="G43" s="10">
-        <v>2059</v>
+        <v>2066</v>
       </c>
       <c r="H43" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I43" s="10">
         <v>6</v>
       </c>
       <c r="J43" s="10">
-        <v>1991</v>
+        <v>1948</v>
       </c>
       <c r="K43" s="10">
-        <v>66763112.972614646</v>
+        <v>70387346.462206155</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.35">
@@ -9291,7 +9301,7 @@
         <v>39</v>
       </c>
       <c r="B44" s="10">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="C44" s="10">
         <v>6</v>
@@ -9300,13 +9310,13 @@
         <v>4</v>
       </c>
       <c r="E44" s="10">
-        <v>760</v>
+        <v>783</v>
       </c>
       <c r="F44" s="10">
-        <v>42805016.573299475</v>
+        <v>45081578.612316735</v>
       </c>
       <c r="G44" s="10">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="H44" s="10">
         <v>5</v>
@@ -9315,10 +9325,10 @@
         <v>4</v>
       </c>
       <c r="J44" s="10">
-        <v>797</v>
+        <v>838</v>
       </c>
       <c r="K44" s="10">
-        <v>46227650.783002853</v>
+        <v>48694697.570638672</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.35">
@@ -9326,7 +9336,7 @@
         <v>6</v>
       </c>
       <c r="B45" s="10">
-        <v>1116</v>
+        <v>1100</v>
       </c>
       <c r="C45" s="10">
         <v>3</v>
@@ -9335,25 +9345,25 @@
         <v>3</v>
       </c>
       <c r="E45" s="10">
-        <v>996</v>
+        <v>935</v>
       </c>
       <c r="F45" s="10">
-        <v>35305267.70624648</v>
+        <v>36951327.241868146</v>
       </c>
       <c r="G45" s="10">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H45" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I45" s="10">
         <v>3</v>
       </c>
       <c r="J45" s="10">
-        <v>1158</v>
+        <v>1035</v>
       </c>
       <c r="K45" s="10">
-        <v>27034432.239690185</v>
+        <v>28817713.877122149</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
@@ -9361,7 +9371,7 @@
         <v>41</v>
       </c>
       <c r="B46" s="10">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C46" s="10">
         <v>0</v>
@@ -9370,25 +9380,25 @@
         <v>5</v>
       </c>
       <c r="E46" s="10">
-        <v>636</v>
+        <v>646</v>
       </c>
       <c r="F46" s="10">
-        <v>34656045.854344085</v>
+        <v>36616468.703792453</v>
       </c>
       <c r="G46" s="10">
         <v>835</v>
       </c>
       <c r="H46" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I46" s="10">
         <v>4</v>
       </c>
       <c r="J46" s="10">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="K46" s="10">
-        <v>34623144.718677483</v>
+        <v>36351905.914852493</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.35">
@@ -9405,13 +9415,13 @@
         <v>10</v>
       </c>
       <c r="E47" s="10">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="F47" s="10">
-        <v>21610464.703248747</v>
+        <v>22704753.056662936</v>
       </c>
       <c r="G47" s="10">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H47" s="10">
         <v>3</v>
@@ -9420,10 +9430,10 @@
         <v>10</v>
       </c>
       <c r="J47" s="10">
-        <v>123</v>
+        <v>623</v>
       </c>
       <c r="K47" s="10">
-        <v>21742784.05233898</v>
+        <v>22763455.27254276</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.35">
@@ -9431,22 +9441,22 @@
         <v>160</v>
       </c>
       <c r="B48" s="10">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="C48" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" s="10">
         <v>1</v>
       </c>
       <c r="E48" s="10">
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="F48" s="10">
-        <v>20687868.148741201</v>
+        <v>21905672.652470183</v>
       </c>
       <c r="G48" s="10">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H48" s="10">
         <v>0</v>
@@ -9455,10 +9465,10 @@
         <v>1</v>
       </c>
       <c r="J48" s="10">
-        <v>389</v>
+        <v>708</v>
       </c>
       <c r="K48" s="10">
-        <v>18652888.434304617</v>
+        <v>19508855.302097976</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
@@ -9466,22 +9476,22 @@
         <v>83</v>
       </c>
       <c r="B49" s="10">
-        <v>1279</v>
+        <v>1272</v>
       </c>
       <c r="C49" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D49" s="10">
         <v>5</v>
       </c>
       <c r="E49" s="10">
-        <v>1085</v>
+        <v>1058</v>
       </c>
       <c r="F49" s="10">
-        <v>65941089.434293799</v>
+        <v>68951901.83255586</v>
       </c>
       <c r="G49" s="10">
-        <v>1243</v>
+        <v>1250</v>
       </c>
       <c r="H49" s="10">
         <v>3</v>
@@ -9490,10 +9500,10 @@
         <v>5</v>
       </c>
       <c r="J49" s="10">
-        <v>1418</v>
+        <v>1375</v>
       </c>
       <c r="K49" s="10">
-        <v>62024410.34365315</v>
+        <v>65624769.39583008</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
@@ -9501,7 +9511,7 @@
         <v>202</v>
       </c>
       <c r="B50" s="10">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C50" s="10">
         <v>3</v>
@@ -9510,13 +9520,13 @@
         <v>2</v>
       </c>
       <c r="E50" s="10">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="F50" s="10">
-        <v>12042453.550795225</v>
+        <v>12686952.26487137</v>
       </c>
       <c r="G50" s="10">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H50" s="10">
         <v>1</v>
@@ -9525,10 +9535,10 @@
         <v>1</v>
       </c>
       <c r="J50" s="10">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="K50" s="10">
-        <v>9974558.4401260205</v>
+        <v>10487918.343386697</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
@@ -9536,7 +9546,7 @@
         <v>31</v>
       </c>
       <c r="B51" s="10">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="C51" s="10">
         <v>2</v>
@@ -9545,13 +9555,13 @@
         <v>5</v>
       </c>
       <c r="E51" s="10">
-        <v>950</v>
+        <v>922</v>
       </c>
       <c r="F51" s="10">
-        <v>29718671.064681828</v>
+        <v>31224174.820838396</v>
       </c>
       <c r="G51" s="10">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="H51" s="10">
         <v>3</v>
@@ -9560,10 +9570,10 @@
         <v>6</v>
       </c>
       <c r="J51" s="10">
-        <v>931</v>
+        <v>946</v>
       </c>
       <c r="K51" s="10">
-        <v>29054377.526877664</v>
+        <v>30416321.719961289</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
@@ -9571,34 +9581,34 @@
         <v>33</v>
       </c>
       <c r="B52" s="10">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="C52" s="10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D52" s="10">
         <v>12</v>
       </c>
       <c r="E52" s="10">
-        <v>979</v>
+        <v>996</v>
       </c>
       <c r="F52" s="10">
-        <v>43797964.177689955</v>
+        <v>46284776.708795786</v>
       </c>
       <c r="G52" s="10">
-        <v>1344</v>
+        <v>1338</v>
       </c>
       <c r="H52" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I52" s="10">
         <v>12</v>
       </c>
       <c r="J52" s="10">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="K52" s="10">
-        <v>50825033.960358381</v>
+        <v>53489987.771002561</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.35">
@@ -9606,7 +9616,7 @@
         <v>85</v>
       </c>
       <c r="B53" s="10">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C53" s="10">
         <v>7</v>
@@ -9615,25 +9625,25 @@
         <v>5</v>
       </c>
       <c r="E53" s="10">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F53" s="10">
-        <v>22770248.911103602</v>
+        <v>24156172.660815898</v>
       </c>
       <c r="G53" s="10">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="H53" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I53" s="10">
         <v>6</v>
       </c>
       <c r="J53" s="10">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="K53" s="10">
-        <v>26152148.725233007</v>
+        <v>27405554.935270023</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.35">
@@ -9650,13 +9660,13 @@
         <v>6</v>
       </c>
       <c r="E54" s="10">
-        <v>298</v>
+        <v>323</v>
       </c>
       <c r="F54" s="10">
-        <v>22546305.818256099</v>
+        <v>23676615.185974032</v>
       </c>
       <c r="G54" s="10">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="H54" s="10">
         <v>0</v>
@@ -9665,10 +9675,10 @@
         <v>4</v>
       </c>
       <c r="J54" s="10">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="K54" s="10">
-        <v>19126089.304449983</v>
+        <v>20136026.2156309</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.35">
@@ -9676,7 +9686,7 @@
         <v>87</v>
       </c>
       <c r="B55" s="10">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C55" s="10">
         <v>11</v>
@@ -9685,13 +9695,13 @@
         <v>2</v>
       </c>
       <c r="E55" s="10">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="F55" s="10">
-        <v>18657852.426756896</v>
+        <v>19565337.991295934</v>
       </c>
       <c r="G55" s="10">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H55" s="10">
         <v>2</v>
@@ -9700,10 +9710,10 @@
         <v>3</v>
       </c>
       <c r="J55" s="10">
-        <v>367</v>
+        <v>341</v>
       </c>
       <c r="K55" s="10">
-        <v>16764643.498383747</v>
+        <v>17633388.891193338</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.35">
@@ -9711,7 +9721,7 @@
         <v>166</v>
       </c>
       <c r="B56" s="10">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="C56" s="10">
         <v>4</v>
@@ -9720,13 +9730,13 @@
         <v>1</v>
       </c>
       <c r="E56" s="10">
-        <v>927</v>
+        <v>947</v>
       </c>
       <c r="F56" s="10">
-        <v>40544706.538535334</v>
+        <v>42465575.241866045</v>
       </c>
       <c r="G56" s="10">
-        <v>1100</v>
+        <v>1094</v>
       </c>
       <c r="H56" s="10">
         <v>5</v>
@@ -9735,10 +9745,10 @@
         <v>1</v>
       </c>
       <c r="J56" s="10">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="K56" s="10">
-        <v>39213836.923041739</v>
+        <v>41199724.440495275</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
@@ -9746,7 +9756,7 @@
         <v>93</v>
       </c>
       <c r="B57" s="10">
-        <v>980</v>
+        <v>971</v>
       </c>
       <c r="C57" s="10">
         <v>10</v>
@@ -9755,13 +9765,13 @@
         <v>2</v>
       </c>
       <c r="E57" s="10">
-        <v>841</v>
+        <v>810</v>
       </c>
       <c r="F57" s="10">
-        <v>42886891.103262864</v>
+        <v>45055941.481699936</v>
       </c>
       <c r="G57" s="10">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="H57" s="10">
         <v>7</v>
@@ -9770,10 +9780,10 @@
         <v>1</v>
       </c>
       <c r="J57" s="10">
-        <v>862</v>
+        <v>817</v>
       </c>
       <c r="K57" s="10">
-        <v>40939585.895147137</v>
+        <v>43110471.737202205</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.35">
@@ -9781,22 +9791,22 @@
         <v>95</v>
       </c>
       <c r="B58" s="10">
-        <v>2163</v>
+        <v>2122</v>
       </c>
       <c r="C58" s="10">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D58" s="10">
         <v>7</v>
       </c>
       <c r="E58" s="10">
-        <v>1709</v>
+        <v>1508</v>
       </c>
       <c r="F58" s="10">
-        <v>60223755.032434106</v>
+        <v>63893921.779931098</v>
       </c>
       <c r="G58" s="10">
-        <v>2043</v>
+        <v>2048</v>
       </c>
       <c r="H58" s="10">
         <v>10</v>
@@ -9805,10 +9815,10 @@
         <v>8</v>
       </c>
       <c r="J58" s="10">
-        <v>1735</v>
+        <v>1783</v>
       </c>
       <c r="K58" s="10">
-        <v>73666459.599487707</v>
+        <v>77451228.109518692</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.35">
@@ -9816,7 +9826,7 @@
         <v>174</v>
       </c>
       <c r="B59" s="10">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C59" s="10">
         <v>3</v>
@@ -9825,13 +9835,13 @@
         <v>0</v>
       </c>
       <c r="E59" s="10">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="F59" s="10">
-        <v>19628260.883901495</v>
+        <v>20534534.922981523</v>
       </c>
       <c r="G59" s="10">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H59" s="10">
         <v>4</v>
@@ -9840,10 +9850,10 @@
         <v>0</v>
       </c>
       <c r="J59" s="10">
-        <v>550</v>
+        <v>582</v>
       </c>
       <c r="K59" s="10">
-        <v>18415275.797894016</v>
+        <v>19415132.028813072</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.35">
@@ -9851,7 +9861,7 @@
         <v>99</v>
       </c>
       <c r="B60" s="10">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="C60" s="10">
         <v>6</v>
@@ -9860,13 +9870,13 @@
         <v>5</v>
       </c>
       <c r="E60" s="10">
-        <v>830</v>
+        <v>742</v>
       </c>
       <c r="F60" s="10">
-        <v>30615413.367241357</v>
+        <v>32408420.627318345</v>
       </c>
       <c r="G60" s="10">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H60" s="10">
         <v>7</v>
@@ -9875,10 +9885,10 @@
         <v>5</v>
       </c>
       <c r="J60" s="10">
-        <v>740</v>
+        <v>763</v>
       </c>
       <c r="K60" s="10">
-        <v>32094490.60502778</v>
+        <v>33783028.370750755</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.35">
@@ -9886,7 +9896,7 @@
         <v>172</v>
       </c>
       <c r="B61" s="10">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="C61" s="10">
         <v>3</v>
@@ -9895,13 +9905,13 @@
         <v>1</v>
       </c>
       <c r="E61" s="10">
-        <v>627</v>
+        <v>595</v>
       </c>
       <c r="F61" s="10">
-        <v>23662873.351727627</v>
+        <v>24757924.64762653</v>
       </c>
       <c r="G61" s="10">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="H61" s="10">
         <v>4</v>
@@ -9910,10 +9920,10 @@
         <v>1</v>
       </c>
       <c r="J61" s="10">
-        <v>635</v>
+        <v>603</v>
       </c>
       <c r="K61" s="10">
-        <v>20317389.490997106</v>
+        <v>21302689.942315493</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.35">
@@ -9921,7 +9931,7 @@
         <v>168</v>
       </c>
       <c r="B62" s="10">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="C62" s="10">
         <v>8</v>
@@ -9930,10 +9940,10 @@
         <v>1</v>
       </c>
       <c r="E62" s="10">
-        <v>1070</v>
+        <v>1031</v>
       </c>
       <c r="F62" s="10">
-        <v>40636216.140523255</v>
+        <v>42696543.090585358</v>
       </c>
       <c r="G62" s="10">
         <v>1107</v>
@@ -9945,10 +9955,10 @@
         <v>0</v>
       </c>
       <c r="J62" s="10">
-        <v>977</v>
+        <v>1001</v>
       </c>
       <c r="K62" s="10">
-        <v>40981093.886455111</v>
+        <v>43034612.716141865</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.35">
@@ -9956,22 +9966,22 @@
         <v>101</v>
       </c>
       <c r="B63" s="10">
-        <v>1370</v>
+        <v>1363</v>
       </c>
       <c r="C63" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D63" s="10">
         <v>4</v>
       </c>
       <c r="E63" s="10">
-        <v>1343</v>
+        <v>1372</v>
       </c>
       <c r="F63" s="10">
-        <v>51975399.294892192</v>
+        <v>54590695.006662175</v>
       </c>
       <c r="G63" s="10">
-        <v>1503</v>
+        <v>1516</v>
       </c>
       <c r="H63" s="10">
         <v>10</v>
@@ -9980,10 +9990,10 @@
         <v>4</v>
       </c>
       <c r="J63" s="10">
-        <v>1408</v>
+        <v>1546</v>
       </c>
       <c r="K63" s="10">
-        <v>50074452.206668533</v>
+        <v>53108125.971225314</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.35">
@@ -9991,7 +10001,7 @@
         <v>103</v>
       </c>
       <c r="B64" s="10">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C64" s="10">
         <v>5</v>
@@ -10000,25 +10010,25 @@
         <v>5</v>
       </c>
       <c r="E64" s="10">
-        <v>751</v>
+        <v>693</v>
       </c>
       <c r="F64" s="10">
-        <v>26207240.497092113</v>
+        <v>27563613.08958514</v>
       </c>
       <c r="G64" s="10">
         <v>771</v>
       </c>
       <c r="H64" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I64" s="10">
         <v>4</v>
       </c>
       <c r="J64" s="10">
-        <v>682</v>
+        <v>1398</v>
       </c>
       <c r="K64" s="10">
-        <v>27821994.716877595</v>
+        <v>29166523.35953356</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.35">
@@ -10026,22 +10036,22 @@
         <v>105</v>
       </c>
       <c r="B65" s="10">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="C65" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D65" s="10">
         <v>5</v>
       </c>
       <c r="E65" s="10">
-        <v>483</v>
+        <v>451</v>
       </c>
       <c r="F65" s="10">
-        <v>30690396.011699993</v>
+        <v>32225585.880645122</v>
       </c>
       <c r="G65" s="10">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="H65" s="10">
         <v>9</v>
@@ -10050,10 +10060,10 @@
         <v>5</v>
       </c>
       <c r="J65" s="10">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="K65" s="10">
-        <v>31019483.13461696</v>
+        <v>32666251.142069764</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.35">
@@ -10061,22 +10071,22 @@
         <v>24</v>
       </c>
       <c r="B66" s="10">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="C66" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D66" s="10">
         <v>9</v>
       </c>
       <c r="E66" s="10">
-        <v>1869</v>
+        <v>1668</v>
       </c>
       <c r="F66" s="10">
-        <v>80494151.517660826</v>
+        <v>85317689.138641283</v>
       </c>
       <c r="G66" s="10">
-        <v>1999</v>
+        <v>2010</v>
       </c>
       <c r="H66" s="10">
         <v>15</v>
@@ -10085,10 +10095,10 @@
         <v>11</v>
       </c>
       <c r="J66" s="10">
-        <v>1607</v>
+        <v>1722</v>
       </c>
       <c r="K66" s="10">
-        <v>99819639.769979075</v>
+        <v>104957958.57839498</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.35">
@@ -10096,7 +10106,7 @@
         <v>27</v>
       </c>
       <c r="B67" s="10">
-        <v>1597</v>
+        <v>1587</v>
       </c>
       <c r="C67" s="10">
         <v>19</v>
@@ -10105,13 +10115,13 @@
         <v>7</v>
       </c>
       <c r="E67" s="10">
-        <v>1177</v>
+        <v>1181</v>
       </c>
       <c r="F67" s="10">
-        <v>74403597.224619329</v>
+        <v>78408477.996826321</v>
       </c>
       <c r="G67" s="10">
-        <v>1602</v>
+        <v>1589</v>
       </c>
       <c r="H67" s="10">
         <v>16</v>
@@ -10120,10 +10130,10 @@
         <v>6</v>
       </c>
       <c r="J67" s="10">
-        <v>1376</v>
+        <v>1222</v>
       </c>
       <c r="K67" s="10">
-        <v>75202591.101204753</v>
+        <v>79258311.448570415</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.35">
@@ -10131,7 +10141,7 @@
         <v>29</v>
       </c>
       <c r="B68" s="10">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="C68" s="10">
         <v>2</v>
@@ -10140,13 +10150,13 @@
         <v>1</v>
       </c>
       <c r="E68" s="10">
-        <v>648</v>
+        <v>655</v>
       </c>
       <c r="F68" s="10">
-        <v>46188082.820514478</v>
+        <v>48727801.593974993</v>
       </c>
       <c r="G68" s="10">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H68" s="10">
         <v>7</v>
@@ -10155,10 +10165,10 @@
         <v>1</v>
       </c>
       <c r="J68" s="10">
-        <v>657</v>
+        <v>734</v>
       </c>
       <c r="K68" s="10">
-        <v>48323897.682485439</v>
+        <v>50766777.004490346</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.35">
@@ -10166,7 +10176,7 @@
         <v>57</v>
       </c>
       <c r="B69" s="10">
-        <v>1999</v>
+        <v>1984</v>
       </c>
       <c r="C69" s="10">
         <v>244</v>
@@ -10175,25 +10185,25 @@
         <v>13</v>
       </c>
       <c r="E69" s="10">
-        <v>1445</v>
+        <v>1370</v>
       </c>
       <c r="F69" s="10">
-        <v>67882627.172021404</v>
+        <v>71373716.671775326</v>
       </c>
       <c r="G69" s="10">
-        <v>2271</v>
+        <v>2259</v>
       </c>
       <c r="H69" s="10">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I69" s="10">
         <v>12</v>
       </c>
       <c r="J69" s="10">
-        <v>1277</v>
+        <v>1362</v>
       </c>
       <c r="K69" s="10">
-        <v>71504925.88939625</v>
+        <v>75539145.629662246</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.35">
@@ -10201,7 +10211,7 @@
         <v>137</v>
       </c>
       <c r="B70" s="10">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C70" s="10">
         <v>2</v>
@@ -10210,13 +10220,13 @@
         <v>1</v>
       </c>
       <c r="E70" s="10">
-        <v>236</v>
+        <v>268</v>
       </c>
       <c r="F70" s="10">
-        <v>5076964.1164683579</v>
+        <v>5369530.2958202437</v>
       </c>
       <c r="G70" s="10">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="H70" s="10">
         <v>0</v>
@@ -10225,10 +10235,10 @@
         <v>1</v>
       </c>
       <c r="J70" s="10">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="K70" s="10">
-        <v>2920456.5121259899</v>
+        <v>3163370.7771156929</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.35">
@@ -10236,34 +10246,34 @@
         <v>10</v>
       </c>
       <c r="B71" s="10">
-        <v>1805</v>
+        <v>1797</v>
       </c>
       <c r="C71" s="10">
         <v>6</v>
       </c>
       <c r="D71" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E71" s="10">
-        <v>1560</v>
+        <v>1598</v>
       </c>
       <c r="F71" s="10">
-        <v>53626628.117396288</v>
+        <v>56257298.48234468</v>
       </c>
       <c r="G71" s="10">
-        <v>1667</v>
+        <v>1672</v>
       </c>
       <c r="H71" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I71" s="10">
         <v>6</v>
       </c>
       <c r="J71" s="10">
-        <v>1921</v>
+        <v>1580</v>
       </c>
       <c r="K71" s="10">
-        <v>51942957.043750465</v>
+        <v>54652536.380899057</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.35">
@@ -10274,31 +10284,31 @@
         <v>667</v>
       </c>
       <c r="C72" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D72" s="10">
         <v>2</v>
       </c>
       <c r="E72" s="10">
-        <v>610</v>
+        <v>590</v>
       </c>
       <c r="F72" s="10">
-        <v>21968090.95705428</v>
+        <v>22953791.33224605</v>
       </c>
       <c r="G72" s="10">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="H72" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I72" s="10">
         <v>3</v>
       </c>
       <c r="J72" s="10">
-        <v>763</v>
+        <v>646</v>
       </c>
       <c r="K72" s="10">
-        <v>24581273.682099607</v>
+        <v>25985617.40753483</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.35">
@@ -10306,7 +10316,7 @@
         <v>162</v>
       </c>
       <c r="B73" s="10">
-        <v>1326</v>
+        <v>1321</v>
       </c>
       <c r="C73" s="10">
         <v>45</v>
@@ -10315,25 +10325,25 @@
         <v>5</v>
       </c>
       <c r="E73" s="10">
-        <v>1260</v>
+        <v>1027</v>
       </c>
       <c r="F73" s="10">
-        <v>36202729.775051877</v>
+        <v>38152542.670676976</v>
       </c>
       <c r="G73" s="10">
-        <v>1382</v>
+        <v>1433</v>
       </c>
       <c r="H73" s="10">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="I73" s="10">
         <v>5</v>
       </c>
       <c r="J73" s="10">
-        <v>1532</v>
+        <v>987</v>
       </c>
       <c r="K73" s="10">
-        <v>37415644.270037763</v>
+        <v>39573153.64074301</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.35">
@@ -10341,7 +10351,7 @@
         <v>63</v>
       </c>
       <c r="B74" s="10">
-        <v>1358</v>
+        <v>1345</v>
       </c>
       <c r="C74" s="10">
         <v>7</v>
@@ -10350,25 +10360,25 @@
         <v>5</v>
       </c>
       <c r="E74" s="10">
-        <v>1260</v>
+        <v>597</v>
       </c>
       <c r="F74" s="10">
-        <v>17783711.442227617</v>
+        <v>18265551.76599412</v>
       </c>
       <c r="G74" s="10">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="H74" s="10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I74" s="10">
         <v>5</v>
       </c>
       <c r="J74" s="10">
-        <v>1215</v>
+        <v>1253</v>
       </c>
       <c r="K74" s="10">
-        <v>23929894.673063796</v>
+        <v>25656378.209861528</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.35">
@@ -10376,7 +10386,7 @@
         <v>59</v>
       </c>
       <c r="B75" s="10">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="C75" s="10">
         <v>8</v>
@@ -10385,10 +10395,10 @@
         <v>5</v>
       </c>
       <c r="E75" s="10">
-        <v>1180</v>
+        <v>1236</v>
       </c>
       <c r="F75" s="10">
-        <v>63481150.813349932</v>
+        <v>67202251.554740682</v>
       </c>
       <c r="G75" s="10">
         <v>1732</v>
@@ -10400,10 +10410,10 @@
         <v>5</v>
       </c>
       <c r="J75" s="10">
-        <v>1259</v>
+        <v>1225</v>
       </c>
       <c r="K75" s="10">
-        <v>65060314.538961947</v>
+        <v>68457996.802198336</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.35">
@@ -10411,7 +10421,7 @@
         <v>139</v>
       </c>
       <c r="B76" s="10">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C76" s="10">
         <v>3</v>
@@ -10420,13 +10430,13 @@
         <v>2</v>
       </c>
       <c r="E76" s="10">
-        <v>424</v>
+        <v>628</v>
       </c>
       <c r="F76" s="10">
-        <v>13786630.717428997</v>
+        <v>14429554.57921656</v>
       </c>
       <c r="G76" s="10">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H76" s="10">
         <v>2</v>
@@ -10435,10 +10445,10 @@
         <v>1</v>
       </c>
       <c r="J76" s="10">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="K76" s="10">
-        <v>13044733.106628915</v>
+        <v>13727240.991854239</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.35">
@@ -10446,34 +10456,34 @@
         <v>170</v>
       </c>
       <c r="B77" s="10">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C77" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D77" s="10">
         <v>1</v>
       </c>
       <c r="E77" s="10">
-        <v>790</v>
+        <v>852</v>
       </c>
       <c r="F77" s="10">
-        <v>21117188.467634171</v>
+        <v>22171799.827533696</v>
       </c>
       <c r="G77" s="10">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="H77" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I77" s="10">
         <v>1</v>
       </c>
       <c r="J77" s="10">
-        <v>808</v>
+        <v>788</v>
       </c>
       <c r="K77" s="10">
-        <v>21197941.625014752</v>
+        <v>22253625.293895539</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.35">
@@ -10481,7 +10491,7 @@
         <v>61</v>
       </c>
       <c r="B78" s="10">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="C78" s="10">
         <v>2</v>
@@ -10490,13 +10500,13 @@
         <v>4</v>
       </c>
       <c r="E78" s="10">
-        <v>416</v>
+        <v>633</v>
       </c>
       <c r="F78" s="10">
-        <v>14736341.28762248</v>
+        <v>15045724.399837304</v>
       </c>
       <c r="G78" s="10">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="H78" s="10">
         <v>2</v>
@@ -10505,10 +10515,10 @@
         <v>3</v>
       </c>
       <c r="J78" s="10">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="K78" s="10">
-        <v>20935184.704319578</v>
+        <v>22077326.343890451</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.35">
@@ -10516,7 +10526,7 @@
         <v>129</v>
       </c>
       <c r="B79" s="10">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="C79" s="10">
         <v>5</v>
@@ -10525,13 +10535,13 @@
         <v>1</v>
       </c>
       <c r="E79" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F79" s="10">
-        <v>13803241.814353952</v>
+        <v>13803246.696355209</v>
       </c>
       <c r="G79" s="10">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="H79" s="10">
         <v>6</v>
@@ -10540,10 +10550,10 @@
         <v>1</v>
       </c>
       <c r="J79" s="10">
-        <v>551</v>
+        <v>513</v>
       </c>
       <c r="K79" s="10">
-        <v>15506233.992221871</v>
+        <v>16036060.553102637</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.35">
@@ -10551,7 +10561,7 @@
         <v>35</v>
       </c>
       <c r="B80" s="10">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C80" s="10">
         <v>6</v>
@@ -10560,10 +10570,10 @@
         <v>6</v>
       </c>
       <c r="E80" s="10">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="F80" s="10">
-        <v>16238993.027723324</v>
+        <v>17050229.600482032</v>
       </c>
       <c r="G80" s="10">
         <v>445</v>
@@ -10575,10 +10585,10 @@
         <v>7</v>
       </c>
       <c r="J80" s="10">
-        <v>475</v>
+        <v>499</v>
       </c>
       <c r="K80" s="10">
-        <v>17523590.520165198</v>
+        <v>18475041.61702498</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.35">
@@ -10586,34 +10596,34 @@
         <v>107</v>
       </c>
       <c r="B81" s="10">
-        <v>959</v>
+        <v>952</v>
       </c>
       <c r="C81" s="10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D81" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E81" s="10">
-        <v>550</v>
+        <v>788</v>
       </c>
       <c r="F81" s="10">
-        <v>46538332.60440968</v>
+        <v>49208948.078755222</v>
       </c>
       <c r="G81" s="10">
-        <v>908</v>
+        <v>896</v>
       </c>
       <c r="H81" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I81" s="10">
         <v>3</v>
       </c>
       <c r="J81" s="10">
-        <v>757</v>
+        <v>610</v>
       </c>
       <c r="K81" s="10">
-        <v>46909192.026860319</v>
+        <v>49281799.342978746</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.35">
@@ -10621,34 +10631,34 @@
         <v>37</v>
       </c>
       <c r="B82" s="10">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C82" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D82" s="10">
         <v>9</v>
       </c>
       <c r="E82" s="10">
-        <v>754</v>
+        <v>744</v>
       </c>
       <c r="F82" s="10">
-        <v>27857525.216046929</v>
+        <v>29405507.483340576</v>
       </c>
       <c r="G82" s="10">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="H82" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I82" s="10">
         <v>10</v>
       </c>
       <c r="J82" s="10">
-        <v>734</v>
+        <v>724</v>
       </c>
       <c r="K82" s="10">
-        <v>27265674.916935232</v>
+        <v>28529057.216889117</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.35">
@@ -10656,22 +10666,22 @@
         <v>76</v>
       </c>
       <c r="B83" s="10">
-        <v>943</v>
+        <v>951</v>
       </c>
       <c r="C83" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D83" s="10">
         <v>2</v>
       </c>
       <c r="E83" s="10">
-        <v>893</v>
+        <v>1049</v>
       </c>
       <c r="F83" s="10">
-        <v>22505847.82083239</v>
+        <v>23976905.020967472</v>
       </c>
       <c r="G83" s="10">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H83" s="10">
         <v>3</v>
@@ -10680,10 +10690,10 @@
         <v>2</v>
       </c>
       <c r="J83" s="10">
-        <v>1081</v>
+        <v>1171</v>
       </c>
       <c r="K83" s="10">
-        <v>22856536.852877505</v>
+        <v>24304206.202539802</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.35">
@@ -10691,7 +10701,7 @@
         <v>65</v>
       </c>
       <c r="B84" s="10">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C84" s="10">
         <v>6</v>
@@ -10700,13 +10710,13 @@
         <v>4</v>
       </c>
       <c r="E84" s="10">
-        <v>792</v>
+        <v>818</v>
       </c>
       <c r="F84" s="10">
-        <v>25689391.598872714</v>
+        <v>27051046.84657656</v>
       </c>
       <c r="G84" s="10">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="H84" s="10">
         <v>3</v>
@@ -10715,10 +10725,10 @@
         <v>5</v>
       </c>
       <c r="J84" s="10">
-        <v>855</v>
+        <v>828</v>
       </c>
       <c r="K84" s="10">
-        <v>23804512.005560592</v>
+        <v>25200040.858496305</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.35">
@@ -10726,7 +10736,7 @@
         <v>89</v>
       </c>
       <c r="B85" s="10">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C85" s="10">
         <v>5</v>
@@ -10735,13 +10745,13 @@
         <v>5</v>
       </c>
       <c r="E85" s="10">
-        <v>727</v>
+        <v>756</v>
       </c>
       <c r="F85" s="10">
-        <v>27707878.138874147</v>
+        <v>29446746.70471419</v>
       </c>
       <c r="G85" s="10">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="H85" s="10">
         <v>2</v>
@@ -10750,10 +10760,10 @@
         <v>6</v>
       </c>
       <c r="J85" s="10">
-        <v>742</v>
+        <v>772</v>
       </c>
       <c r="K85" s="10">
-        <v>30321505.756113347</v>
+        <v>32219102.200047638</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.35">
@@ -10761,7 +10771,7 @@
         <v>147</v>
       </c>
       <c r="B86" s="10">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C86" s="10">
         <v>2</v>
@@ -10770,25 +10780,25 @@
         <v>1</v>
       </c>
       <c r="E86" s="10">
-        <v>632</v>
+        <v>679</v>
       </c>
       <c r="F86" s="10">
-        <v>12297623.509624189</v>
+        <v>12890849.296891289</v>
       </c>
       <c r="G86" s="10">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="H86" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I86" s="10">
         <v>1</v>
       </c>
       <c r="J86" s="10">
-        <v>544</v>
+        <v>589</v>
       </c>
       <c r="K86" s="10">
-        <v>13851013.837541368</v>
+        <v>14575510.609984348</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.35">
@@ -10796,34 +10806,34 @@
         <v>164</v>
       </c>
       <c r="B87" s="10">
-        <v>1700</v>
+        <v>1696</v>
       </c>
       <c r="C87" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D87" s="10">
         <v>10</v>
       </c>
       <c r="E87" s="10">
-        <v>1317</v>
+        <v>1385</v>
       </c>
       <c r="F87" s="10">
-        <v>52982781.551008649</v>
+        <v>55870676.347908162</v>
       </c>
       <c r="G87" s="10">
-        <v>1763</v>
+        <v>1768</v>
       </c>
       <c r="H87" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I87" s="10">
         <v>10</v>
       </c>
       <c r="J87" s="10">
-        <v>824</v>
+        <v>1394</v>
       </c>
       <c r="K87" s="10">
-        <v>56341564.403701298</v>
+        <v>60561873.35205964</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.35">
@@ -10831,7 +10841,7 @@
         <v>91</v>
       </c>
       <c r="B88" s="10">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C88" s="10">
         <v>5</v>
@@ -10840,13 +10850,13 @@
         <v>3</v>
       </c>
       <c r="E88" s="10">
-        <v>628</v>
+        <v>903</v>
       </c>
       <c r="F88" s="10">
-        <v>14099053.264334928</v>
+        <v>15216982.418813448</v>
       </c>
       <c r="G88" s="10">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="H88" s="10">
         <v>0</v>
@@ -10855,10 +10865,10 @@
         <v>3</v>
       </c>
       <c r="J88" s="10">
-        <v>625</v>
+        <v>648</v>
       </c>
       <c r="K88" s="10">
-        <v>13251615.22394882</v>
+        <v>13821141.409075508</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.35">
@@ -10866,22 +10876,22 @@
         <v>97</v>
       </c>
       <c r="B89" s="10">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C89" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D89" s="10">
         <v>6</v>
       </c>
       <c r="E89" s="10">
-        <v>574</v>
+        <v>521</v>
       </c>
       <c r="F89" s="10">
-        <v>24761684.048804503</v>
+        <v>26078100.101177879</v>
       </c>
       <c r="G89" s="10">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H89" s="10">
         <v>4</v>
@@ -10890,10 +10900,10 @@
         <v>7</v>
       </c>
       <c r="J89" s="10">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="K89" s="10">
-        <v>25936117.318591543</v>
+        <v>27183832.475523256</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.35">
@@ -10901,22 +10911,22 @@
         <v>78</v>
       </c>
       <c r="B90" s="10">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C90" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D90" s="10">
         <v>1</v>
       </c>
       <c r="E90" s="10">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="F90" s="10">
-        <v>6820595.096124053</v>
+        <v>7162107.3929737266</v>
       </c>
       <c r="G90" s="10">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H90" s="10">
         <v>2</v>
@@ -10925,10 +10935,42 @@
         <v>1</v>
       </c>
       <c r="J90" s="10">
-        <v>363</v>
+        <v>304</v>
       </c>
       <c r="K90" s="10">
-        <v>6214020.6016599154</v>
+        <v>6488168.8620083621</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B91" s="13">
+        <v>84155</v>
+      </c>
+      <c r="C91" s="13">
+        <v>1484</v>
+      </c>
+      <c r="D91" s="13">
+        <v>307</v>
+      </c>
+      <c r="E91" s="13">
+        <v>70150</v>
+      </c>
+      <c r="F91" s="13">
+        <v>2762661133.2590084</v>
+      </c>
+      <c r="G91" s="13">
+        <v>84561</v>
+      </c>
+      <c r="H91" s="13">
+        <v>1547</v>
+      </c>
+      <c r="I91" s="13">
+        <v>314</v>
+      </c>
+      <c r="J91" s="13">
+        <v>70937</v>
+      </c>
+      <c r="K91" s="13">
+        <v>2842605836.7440019</v>
       </c>
     </row>
   </sheetData>

--- a/SITE MONITORING.xlsx
+++ b/SITE MONITORING.xlsx
@@ -1146,19 +1146,19 @@
       </c>
       <c r="F2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13087808.370799534</v>
+        <v>12452036.798173808</v>
       </c>
       <c r="G2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12916722.729567273</v>
+        <v>12287955.952436997</v>
       </c>
       <c r="H2" s="12">
         <f>IFERROR(G2/F2-1,0)</f>
-        <v>-1.307213831262799E-2</v>
+        <v>-1.3177028657743395E-2</v>
       </c>
       <c r="I2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="J2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="K2" s="12">
         <f>IFERROR(J2/I2-1,0)</f>
-        <v>7.9510703363914415E-2</v>
+        <v>0.14610389610389607</v>
       </c>
       <c r="L2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="R2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="S2">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="T2" s="12">
         <f>IFERROR(S2/R2-1,0)</f>
-        <v>-7.194244604316502E-3</v>
+        <v>7.2992700729928028E-3</v>
       </c>
       <c r="U2">
         <v>3</v>
@@ -1226,19 +1226,19 @@
       </c>
       <c r="F3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15998166.242166299</v>
+        <v>15270377.5820772</v>
       </c>
       <c r="G3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>15084594.410566358</v>
+        <v>14339947.092993161</v>
       </c>
       <c r="H3" s="12">
         <f t="shared" ref="H3:H66" si="0">IFERROR(G3/F3-1,0)</f>
-        <v>-5.710478424658727E-2</v>
+        <v>-6.0930417999361275E-2</v>
       </c>
       <c r="I3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="J3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="K3" s="12">
         <f t="shared" ref="K3:K66" si="1">IFERROR(J3/I3-1,0)</f>
-        <v>1.6260162601626105E-2</v>
+        <v>5.0420168067226934E-2</v>
       </c>
       <c r="L3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="R3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="S3">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="T3" s="12">
         <f t="shared" ref="T3:T66" si="4">IFERROR(S3/R3-1,0)</f>
-        <v>-6.2130177514792884E-2</v>
+        <v>-5.6547619047619069E-2</v>
       </c>
       <c r="U3">
         <v>2</v>
@@ -1306,19 +1306,19 @@
       </c>
       <c r="F4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18423447.133026849</v>
+        <v>17041117.995255239</v>
       </c>
       <c r="G4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21263351.156662799</v>
+        <v>19961475.905457538</v>
       </c>
       <c r="H4" s="12">
         <f t="shared" si="0"/>
-        <v>0.1541461813921341</v>
+        <v>0.17137126279011827</v>
       </c>
       <c r="I4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>912</v>
+        <v>809</v>
       </c>
       <c r="J4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="K4" s="12">
         <f t="shared" si="1"/>
-        <v>-0.13596491228070173</v>
+        <v>-2.595797280593326E-2</v>
       </c>
       <c r="L4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="R4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="S4">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T4" s="12">
         <f t="shared" si="4"/>
-        <v>0.11594202898550732</v>
+        <v>0.1191860465116279</v>
       </c>
       <c r="U4">
         <v>4</v>
@@ -1386,19 +1386,19 @@
       </c>
       <c r="F5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>32444786.249515016</v>
+        <v>30428581.790787671</v>
       </c>
       <c r="G5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>33059806.89004685</v>
+        <v>31260783.726436041</v>
       </c>
       <c r="H5" s="12">
         <f t="shared" si="0"/>
-        <v>1.8955915930592093E-2</v>
+        <v>2.7349350073894163E-2</v>
       </c>
       <c r="I5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1484</v>
+        <v>1442</v>
       </c>
       <c r="J5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="K5" s="12">
         <f t="shared" si="1"/>
-        <v>-0.23854447439353099</v>
+        <v>-0.21636615811373094</v>
       </c>
       <c r="L5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="O5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -1430,11 +1430,11 @@
       </c>
       <c r="Q5" s="12">
         <f t="shared" si="3"/>
-        <v>0.14285714285714279</v>
+        <v>0</v>
       </c>
       <c r="R5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1188</v>
+        <v>1193</v>
       </c>
       <c r="S5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="T5" s="12">
         <f t="shared" si="4"/>
-        <v>2.1885521885521841E-2</v>
+        <v>1.7602682313495377E-2</v>
       </c>
       <c r="U5">
         <v>3</v>
@@ -1466,19 +1466,19 @@
       </c>
       <c r="F6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13426816.547492765</v>
+        <v>12572009.692979235</v>
       </c>
       <c r="G6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14740995.052347932</v>
+        <v>14087321.867469653</v>
       </c>
       <c r="H6" s="12">
         <f t="shared" si="0"/>
-        <v>9.7877147587941637E-2</v>
+        <v>0.12053062410034854</v>
       </c>
       <c r="I6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>425</v>
+        <v>333</v>
       </c>
       <c r="J6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="K6" s="12">
         <f t="shared" si="1"/>
-        <v>-0.11294117647058821</v>
+        <v>0.13213213213213204</v>
       </c>
       <c r="L6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -1510,11 +1510,11 @@
       </c>
       <c r="Q6" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="R6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="S6">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="T6" s="12">
         <f t="shared" si="4"/>
-        <v>-1.1961722488038284E-2</v>
+        <v>-2.5943396226415061E-2</v>
       </c>
       <c r="U6">
         <v>3</v>
@@ -1546,19 +1546,19 @@
       </c>
       <c r="F7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>11608508.537279077</v>
+        <v>10954941.459135331</v>
       </c>
       <c r="G7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12076791.011960519</v>
+        <v>11489847.967613995</v>
       </c>
       <c r="H7" s="12">
         <f t="shared" si="0"/>
-        <v>4.0339589980712853E-2</v>
+        <v>4.8827874660398507E-2</v>
       </c>
       <c r="I7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>359</v>
+        <v>328</v>
       </c>
       <c r="J7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="K7" s="12">
         <f t="shared" si="1"/>
-        <v>-0.25348189415041777</v>
+        <v>-0.18292682926829273</v>
       </c>
       <c r="L7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="R7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="S7">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="T7" s="12">
         <f t="shared" si="4"/>
-        <v>1.8421052631578894E-2</v>
+        <v>3.2000000000000028E-2</v>
       </c>
       <c r="U7">
         <v>2</v>
@@ -1626,27 +1626,27 @@
       </c>
       <c r="F8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13234286.009974919</v>
+        <v>12590405.038448486</v>
       </c>
       <c r="G8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14483043.079303995</v>
+        <v>13775550.668594858</v>
       </c>
       <c r="H8" s="12">
         <f t="shared" si="0"/>
-        <v>9.4357721178752296E-2</v>
+        <v>9.4130858104022996E-2</v>
       </c>
       <c r="I8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="J8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>480</v>
+        <v>374</v>
       </c>
       <c r="K8" s="12">
         <f t="shared" si="1"/>
-        <v>5.9602649006622599E-2</v>
+        <v>-0.18518518518518523</v>
       </c>
       <c r="L8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="O8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -1670,19 +1670,19 @@
       </c>
       <c r="Q8" s="12">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="R8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="S8">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>595</v>
+        <v>419</v>
       </c>
       <c r="T8" s="12">
         <f t="shared" si="4"/>
-        <v>1.6835016835017313E-3</v>
+        <v>-0.28862478777589129</v>
       </c>
       <c r="U8">
         <v>9</v>
@@ -1706,27 +1706,27 @@
       </c>
       <c r="F9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6272122.0239012884</v>
+        <v>5908394.1481695939</v>
       </c>
       <c r="G9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6320873.6215354437</v>
+        <v>6045648.5828848016</v>
       </c>
       <c r="H9" s="12">
         <f t="shared" si="0"/>
-        <v>7.7727438095713808E-3</v>
+        <v>2.3230412743829643E-2</v>
       </c>
       <c r="I9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="J9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>151</v>
+        <v>500</v>
       </c>
       <c r="K9" s="12">
         <f t="shared" si="1"/>
-        <v>-0.10119047619047616</v>
+        <v>2.2679738562091503</v>
       </c>
       <c r="L9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1734,23 +1734,23 @@
       </c>
       <c r="M9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N9" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q9" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -1758,11 +1758,11 @@
       </c>
       <c r="S9">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>173</v>
+        <v>629</v>
       </c>
       <c r="T9" s="12">
         <f t="shared" si="4"/>
-        <v>5.8139534883721034E-3</v>
+        <v>2.6569767441860463</v>
       </c>
       <c r="U9">
         <v>1</v>
@@ -1786,27 +1786,27 @@
       </c>
       <c r="F10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5986210.4536223654</v>
+        <v>5680298.6802293016</v>
       </c>
       <c r="G10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3146674.465636583</v>
+        <v>2860659.9967147</v>
       </c>
       <c r="H10" s="12">
         <f t="shared" si="0"/>
-        <v>-0.47434616774415728</v>
+        <v>-0.49638915878289325</v>
       </c>
       <c r="I10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="J10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>163</v>
+        <v>757</v>
       </c>
       <c r="K10" s="12">
         <f t="shared" si="1"/>
-        <v>-0.11413043478260865</v>
+        <v>3.6441717791411046</v>
       </c>
       <c r="L10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1826,23 +1826,23 @@
       </c>
       <c r="P10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q10" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="S10">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>187</v>
+        <v>774</v>
       </c>
       <c r="T10" s="12">
         <f t="shared" si="4"/>
-        <v>-4.1025641025640991E-2</v>
+        <v>2.9289340101522843</v>
       </c>
       <c r="U10">
         <v>1</v>
@@ -1866,27 +1866,27 @@
       </c>
       <c r="F11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>9371873.1319251489</v>
+        <v>8944383.1211307161</v>
       </c>
       <c r="G11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12410426.942553291</v>
+        <v>11890504.003905904</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" si="0"/>
-        <v>0.32422054458647676</v>
+        <v>0.32938223272380918</v>
       </c>
       <c r="I11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="J11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>382</v>
+        <v>1155</v>
       </c>
       <c r="K11" s="12">
         <f t="shared" si="1"/>
-        <v>0.12684365781710905</v>
+        <v>2.5</v>
       </c>
       <c r="L11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1894,35 +1894,35 @@
       </c>
       <c r="M11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q11" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="S11">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>383</v>
+        <v>1210</v>
       </c>
       <c r="T11" s="12">
         <f t="shared" si="4"/>
-        <v>0.11337209302325579</v>
+        <v>2.6119402985074629</v>
       </c>
       <c r="U11">
         <v>4</v>
@@ -1946,35 +1946,35 @@
       </c>
       <c r="F12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4545722.9148001587</v>
+        <v>4262490.9429104608</v>
       </c>
       <c r="G12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6532815.7132673627</v>
+        <v>6152814.3065978391</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="0"/>
-        <v>0.4371346066865498</v>
+        <v>0.44347856429617449</v>
       </c>
       <c r="I12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="J12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>257</v>
+        <v>374</v>
       </c>
       <c r="K12" s="12">
         <f t="shared" si="1"/>
-        <v>4.8979591836734615E-2</v>
+        <v>0.65486725663716805</v>
       </c>
       <c r="L12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="2"/>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="P12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="12">
         <f t="shared" si="3"/>
@@ -1994,15 +1994,15 @@
       </c>
       <c r="R12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="S12">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>226</v>
+        <v>410</v>
       </c>
       <c r="T12" s="12">
         <f t="shared" si="4"/>
-        <v>5.1162790697674376E-2</v>
+        <v>0.92488262910798125</v>
       </c>
       <c r="U12">
         <v>3</v>
@@ -2026,27 +2026,27 @@
       </c>
       <c r="F13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6093279.5223717354</v>
+        <v>5733341.8539821506</v>
       </c>
       <c r="G13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6845794.9533302337</v>
+        <v>6544098.7908061044</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="0"/>
-        <v>0.1234992467021423</v>
+        <v>0.14141088347293196</v>
       </c>
       <c r="I13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="J13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>230</v>
+        <v>322</v>
       </c>
       <c r="K13" s="12">
         <f t="shared" si="1"/>
-        <v>7.9812206572769995E-2</v>
+        <v>0.5862068965517242</v>
       </c>
       <c r="L13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2054,11 +2054,11 @@
       </c>
       <c r="M13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N13" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2066,11 +2066,11 @@
       </c>
       <c r="P13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q13" s="12">
         <f t="shared" si="3"/>
-        <v>-0.7142857142857143</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="R13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -2078,11 +2078,11 @@
       </c>
       <c r="S13">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>239</v>
+        <v>390</v>
       </c>
       <c r="T13" s="12">
         <f t="shared" si="4"/>
-        <v>-6.640625E-2</v>
+        <v>0.5234375</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -2106,27 +2106,27 @@
       </c>
       <c r="F14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13443706.666459411</v>
+        <v>12150068.330912439</v>
       </c>
       <c r="G14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>29022560.368282694</v>
+        <v>27129953.922294252</v>
       </c>
       <c r="H14" s="12">
         <f t="shared" si="0"/>
-        <v>1.158821304892856</v>
+        <v>1.2329054605618719</v>
       </c>
       <c r="I14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1494</v>
+        <v>1199</v>
       </c>
       <c r="J14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1076</v>
+        <v>529</v>
       </c>
       <c r="K14" s="12">
         <f t="shared" si="1"/>
-        <v>-0.27978580990629187</v>
+        <v>-0.55879899916597164</v>
       </c>
       <c r="L14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2134,11 +2134,11 @@
       </c>
       <c r="M14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N14" s="12">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="P14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q14" s="12">
         <f t="shared" si="3"/>
@@ -2154,15 +2154,15 @@
       </c>
       <c r="R14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="S14">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1384</v>
+        <v>615</v>
       </c>
       <c r="T14" s="12">
         <f t="shared" si="4"/>
-        <v>-3.0133146461107208E-2</v>
+        <v>-0.56872370266479666</v>
       </c>
       <c r="U14">
         <v>3</v>
@@ -2186,27 +2186,27 @@
       </c>
       <c r="F15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>37942760.593333475</v>
+        <v>37115893.490185946</v>
       </c>
       <c r="G15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>49024095.31867002</v>
+        <v>46248297.021251909</v>
       </c>
       <c r="H15" s="12">
         <f t="shared" si="0"/>
-        <v>0.29205399269982291</v>
+        <v>0.2460510221444816</v>
       </c>
       <c r="I15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>181</v>
+        <v>996</v>
       </c>
       <c r="J15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>901</v>
+        <v>150</v>
       </c>
       <c r="K15" s="12">
         <f t="shared" si="1"/>
-        <v>3.9779005524861875</v>
+        <v>-0.8493975903614458</v>
       </c>
       <c r="L15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2214,35 +2214,35 @@
       </c>
       <c r="M15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N15" s="12">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
       <c r="O15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="12">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1269</v>
+        <v>1259</v>
       </c>
       <c r="S15">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1234</v>
+        <v>176</v>
       </c>
       <c r="T15" s="12">
         <f t="shared" si="4"/>
-        <v>-2.7580772261623365E-2</v>
+        <v>-0.86020651310563934</v>
       </c>
       <c r="U15">
         <v>4</v>
@@ -2266,27 +2266,27 @@
       </c>
       <c r="F16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>25808105.930136997</v>
+        <v>24557779.647644848</v>
       </c>
       <c r="G16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>26071080.14117502</v>
+        <v>24780324.33078628</v>
       </c>
       <c r="H16" s="12">
         <f t="shared" si="0"/>
-        <v>1.0189597475688483E-2</v>
+        <v>9.062084860052666E-3</v>
       </c>
       <c r="I16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>922</v>
+        <v>1758</v>
       </c>
       <c r="J16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>859</v>
+        <v>186</v>
       </c>
       <c r="K16" s="12">
         <f t="shared" si="1"/>
-        <v>-6.8329718004338402E-2</v>
+        <v>-0.89419795221843001</v>
       </c>
       <c r="L16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2294,11 +2294,11 @@
       </c>
       <c r="M16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N16" s="12">
         <f t="shared" si="2"/>
-        <v>0.25</v>
+        <v>-0.75</v>
       </c>
       <c r="O16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2306,23 +2306,23 @@
       </c>
       <c r="P16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="R16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1018</v>
+        <v>1028</v>
       </c>
       <c r="S16">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1021</v>
+        <v>199</v>
       </c>
       <c r="T16" s="12">
         <f t="shared" si="4"/>
-        <v>2.9469548133596035E-3</v>
+        <v>-0.80642023346303504</v>
       </c>
       <c r="U16">
         <v>4</v>
@@ -2346,27 +2346,27 @@
       </c>
       <c r="F17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>25100221.83684345</v>
+        <v>24093521.100269504</v>
       </c>
       <c r="G17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21493879.316390663</v>
+        <v>20292128.333114807</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="0"/>
-        <v>-0.14367771503753024</v>
+        <v>-0.15777655542062619</v>
       </c>
       <c r="I17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="J17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>664</v>
+        <v>431</v>
       </c>
       <c r="K17" s="12">
         <f t="shared" si="1"/>
-        <v>0.13893653516295035</v>
+        <v>-0.26575809199318567</v>
       </c>
       <c r="L17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2374,11 +2374,11 @@
       </c>
       <c r="M17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N17" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-0.66666666666666674</v>
       </c>
       <c r="O17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2386,23 +2386,23 @@
       </c>
       <c r="P17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="12">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="S17">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>917</v>
+        <v>387</v>
       </c>
       <c r="T17" s="12">
         <f t="shared" si="4"/>
-        <v>-3.3719704952581697E-2</v>
+        <v>-0.59177215189873422</v>
       </c>
       <c r="U17">
         <v>4</v>
@@ -2426,63 +2426,63 @@
       </c>
       <c r="F18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>89403755.644768402</v>
+        <v>84378043.245911941</v>
       </c>
       <c r="G18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>95903548.545516953</v>
+        <v>91431790.086039543</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="0"/>
-        <v>7.2701564423920173E-2</v>
+        <v>8.3596947366628482E-2</v>
       </c>
       <c r="I18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2699</v>
+        <v>2465</v>
       </c>
       <c r="J18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2125</v>
+        <v>263</v>
       </c>
       <c r="K18" s="12">
         <f t="shared" si="1"/>
-        <v>-0.2126713597628751</v>
+        <v>-0.89330628803245438</v>
       </c>
       <c r="L18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N18" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-0.81818181818181812</v>
       </c>
       <c r="O18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>625</v>
+        <v>695</v>
       </c>
       <c r="P18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="12">
         <f t="shared" si="3"/>
-        <v>-0.7056</v>
+        <v>-1</v>
       </c>
       <c r="R18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>3188</v>
+        <v>3177</v>
       </c>
       <c r="S18">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2806</v>
+        <v>226</v>
       </c>
       <c r="T18" s="12">
         <f t="shared" si="4"/>
-        <v>-0.11982434127979924</v>
+        <v>-0.92886370790053507</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -2506,27 +2506,27 @@
       </c>
       <c r="F19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>48127649.671235926</v>
+        <v>45853440.719571456</v>
       </c>
       <c r="G19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>30944501.324133508</v>
+        <v>28580704.230768949</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="0"/>
-        <v>-0.35703277563899272</v>
+        <v>-0.3766944468668858</v>
       </c>
       <c r="I19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1203</v>
+        <v>1195</v>
       </c>
       <c r="J19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1172</v>
+        <v>231</v>
       </c>
       <c r="K19" s="12">
         <f t="shared" si="1"/>
-        <v>-2.5768911055694121E-2</v>
+        <v>-0.80669456066945611</v>
       </c>
       <c r="L19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2534,35 +2534,35 @@
       </c>
       <c r="M19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N19" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="O19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1441</v>
+        <v>1435</v>
       </c>
       <c r="S19">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1387</v>
+        <v>239</v>
       </c>
       <c r="T19" s="12">
         <f t="shared" si="4"/>
-        <v>-3.7473976405274168E-2</v>
+        <v>-0.83344947735191632</v>
       </c>
       <c r="U19">
         <v>1</v>
@@ -2586,27 +2586,27 @@
       </c>
       <c r="F20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>96839659.029765069</v>
+        <v>91985409.680114254</v>
       </c>
       <c r="G20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>96555492.863442063</v>
+        <v>91798677.850888729</v>
       </c>
       <c r="H20" s="12">
         <f t="shared" si="0"/>
-        <v>-2.9343986665180122E-3</v>
+        <v>-2.0300157370054528E-3</v>
       </c>
       <c r="I20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2319</v>
+        <v>2257</v>
       </c>
       <c r="J20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2118</v>
+        <v>1040</v>
       </c>
       <c r="K20" s="12">
         <f t="shared" si="1"/>
-        <v>-8.6675291073738725E-2</v>
+        <v>-0.539211342490031</v>
       </c>
       <c r="L20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2614,35 +2614,35 @@
       </c>
       <c r="M20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N20" s="12">
         <f t="shared" si="2"/>
-        <v>-9.0909090909090939E-2</v>
+        <v>-0.72727272727272729</v>
       </c>
       <c r="O20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="P20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="Q20" s="12">
         <f t="shared" si="3"/>
-        <v>0.3125</v>
+        <v>-0.78947368421052633</v>
       </c>
       <c r="R20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>3014</v>
+        <v>3011</v>
       </c>
       <c r="S20">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2929</v>
+        <v>1386</v>
       </c>
       <c r="T20" s="12">
         <f t="shared" si="4"/>
-        <v>-2.8201725282017254E-2</v>
+        <v>-0.53968781135835275</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2666,27 +2666,27 @@
       </c>
       <c r="F21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13858968.280016633</v>
+        <v>13083985.836379612</v>
       </c>
       <c r="G21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14656128.885179391</v>
+        <v>13952390.293539824</v>
       </c>
       <c r="H21" s="12">
         <f t="shared" si="0"/>
-        <v>5.7519476851115359E-2</v>
+        <v>6.6371552829539215E-2</v>
       </c>
       <c r="I21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="J21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>451</v>
+        <v>893</v>
       </c>
       <c r="K21" s="12">
         <f t="shared" si="1"/>
-        <v>-3.426124197002145E-2</v>
+        <v>0.9204301075268817</v>
       </c>
       <c r="L21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2694,11 +2694,11 @@
       </c>
       <c r="M21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N21" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2706,23 +2706,23 @@
       </c>
       <c r="P21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="12">
         <f t="shared" si="3"/>
-        <v>-0.16666666666666663</v>
+        <v>-0.66666666666666674</v>
       </c>
       <c r="R21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="S21">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>539</v>
+        <v>1233</v>
       </c>
       <c r="T21" s="12">
         <f t="shared" si="4"/>
-        <v>-2.5316455696202556E-2</v>
+        <v>1.2541133455210236</v>
       </c>
       <c r="U21">
         <v>1</v>
@@ -2746,27 +2746,27 @@
       </c>
       <c r="F22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>38076981.426078215</v>
+        <v>36202793.63631741</v>
       </c>
       <c r="G22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>40696450.341174901</v>
+        <v>38550165.164171152</v>
       </c>
       <c r="H22" s="12">
         <f t="shared" si="0"/>
-        <v>6.8794027703642069E-2</v>
+        <v>6.4839513531324222E-2</v>
       </c>
       <c r="I22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1285</v>
+        <v>1297</v>
       </c>
       <c r="J22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1351</v>
+        <v>904</v>
       </c>
       <c r="K22" s="12">
         <f t="shared" si="1"/>
-        <v>5.1361867704280195E-2</v>
+        <v>-0.30300693909020815</v>
       </c>
       <c r="L22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2774,35 +2774,35 @@
       </c>
       <c r="M22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N22" s="12">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="P22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="Q22" s="12">
         <f t="shared" si="3"/>
-        <v>0.19999999999999996</v>
+        <v>-0.77272727272727271</v>
       </c>
       <c r="R22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1712</v>
+        <v>1731</v>
       </c>
       <c r="S22">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1657</v>
+        <v>1017</v>
       </c>
       <c r="T22" s="12">
         <f t="shared" si="4"/>
-        <v>-3.2126168224299034E-2</v>
+        <v>-0.41247833622183705</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2826,27 +2826,27 @@
       </c>
       <c r="F23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>16999705.014675111</v>
+        <v>15994034.782365471</v>
       </c>
       <c r="G23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16848952.521488499</v>
+        <v>16023991.278544333</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="0"/>
-        <v>-8.8679475941773056E-3</v>
+        <v>1.8729793067531197E-3</v>
       </c>
       <c r="I23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>919</v>
+        <v>743</v>
       </c>
       <c r="J23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>775</v>
+        <v>673</v>
       </c>
       <c r="K23" s="12">
         <f t="shared" si="1"/>
-        <v>-0.1566920565832427</v>
+        <v>-9.4212651413189796E-2</v>
       </c>
       <c r="L23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2854,35 +2854,35 @@
       </c>
       <c r="M23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N23" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Q23" s="12">
         <f t="shared" si="3"/>
-        <v>-9.0909090909090939E-2</v>
+        <v>-0.66666666666666674</v>
       </c>
       <c r="R23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="S23">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>864</v>
+        <v>919</v>
       </c>
       <c r="T23" s="12">
         <f t="shared" si="4"/>
-        <v>-9.1743119266054496E-3</v>
+        <v>5.0285714285714267E-2</v>
       </c>
       <c r="U23">
         <v>1</v>
@@ -2906,27 +2906,27 @@
       </c>
       <c r="F24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18823380.21238241</v>
+        <v>17730094.775826979</v>
       </c>
       <c r="G24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20465850.794823397</v>
+        <v>19429198.640231583</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="0"/>
-        <v>8.725694130964512E-2</v>
+        <v>9.5831628983796824E-2</v>
       </c>
       <c r="I24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>870</v>
+        <v>920</v>
       </c>
       <c r="J24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>678</v>
+        <v>2089</v>
       </c>
       <c r="K24" s="12">
         <f t="shared" si="1"/>
-        <v>-0.22068965517241379</v>
+        <v>1.2706521739130436</v>
       </c>
       <c r="L24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2934,35 +2934,35 @@
       </c>
       <c r="M24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N24" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>6</v>
+        <v>186</v>
       </c>
       <c r="Q24" s="12">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="R24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>886</v>
+        <v>897</v>
       </c>
       <c r="S24">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>878</v>
+        <v>2788</v>
       </c>
       <c r="T24" s="12">
         <f t="shared" si="4"/>
-        <v>-9.0293453724604733E-3</v>
+        <v>2.1081382385730212</v>
       </c>
       <c r="U24">
         <v>3</v>
@@ -2986,27 +2986,27 @@
       </c>
       <c r="F25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5565632.8976637917</v>
+        <v>5277024.5563090751</v>
       </c>
       <c r="G25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4723558.2871565996</v>
+        <v>4433708.8725122856</v>
       </c>
       <c r="H25" s="12">
         <f t="shared" si="0"/>
-        <v>-0.15129898539672959</v>
+        <v>-0.15980893679726071</v>
       </c>
       <c r="I25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="J25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>185</v>
+        <v>1195</v>
       </c>
       <c r="K25" s="12">
         <f t="shared" si="1"/>
-        <v>-5.6122448979591844E-2</v>
+        <v>5.9476744186046515</v>
       </c>
       <c r="L25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N25" s="12">
         <f t="shared" si="2"/>
@@ -3026,23 +3026,23 @@
       </c>
       <c r="P25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q25" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S25">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>228</v>
+        <v>1379</v>
       </c>
       <c r="T25" s="12">
         <f t="shared" si="4"/>
-        <v>-4.366812227074246E-3</v>
+        <v>4.9956521739130437</v>
       </c>
       <c r="U25">
         <v>1</v>
@@ -3066,27 +3066,27 @@
       </c>
       <c r="F26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>42168566.16250097</v>
+        <v>40235450.07087151</v>
       </c>
       <c r="G26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>38683079.315449901</v>
+        <v>36803930.469524823</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="0"/>
-        <v>-8.265604368949564E-2</v>
+        <v>-8.5285975310387729E-2</v>
       </c>
       <c r="I26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1388</v>
+        <v>1323</v>
       </c>
       <c r="J26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1322</v>
+        <v>2088</v>
       </c>
       <c r="K26" s="12">
         <f t="shared" si="1"/>
-        <v>-4.7550432276657006E-2</v>
+        <v>0.57823129251700678</v>
       </c>
       <c r="L26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3094,11 +3094,11 @@
       </c>
       <c r="M26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N26" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -3106,23 +3106,23 @@
       </c>
       <c r="P26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="Q26" s="12">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4.25</v>
       </c>
       <c r="R26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1649</v>
+        <v>1653</v>
       </c>
       <c r="S26">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1653</v>
+        <v>2920</v>
       </c>
       <c r="T26" s="12">
         <f t="shared" si="4"/>
-        <v>2.4257125530624535E-3</v>
+        <v>0.76648517846339992</v>
       </c>
       <c r="U26">
         <v>1</v>
@@ -3146,27 +3146,27 @@
       </c>
       <c r="F27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>29823023.385615569</v>
+        <v>28301686.739777543</v>
       </c>
       <c r="G27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>32617935.380541101</v>
+        <v>30880741.730442863</v>
       </c>
       <c r="H27" s="12">
         <f t="shared" si="0"/>
-        <v>9.3716587979258748E-2</v>
+        <v>9.1127253805707076E-2</v>
       </c>
       <c r="I27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="J27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>618</v>
+        <v>485</v>
       </c>
       <c r="K27" s="12">
         <f t="shared" si="1"/>
-        <v>3.2467532467532756E-3</v>
+        <v>-0.20098846787479407</v>
       </c>
       <c r="L27" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3182,11 +3182,11 @@
       </c>
       <c r="O27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q27" s="12">
         <f t="shared" si="3"/>
@@ -3194,15 +3194,15 @@
       </c>
       <c r="R27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="S27">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>884</v>
+        <v>537</v>
       </c>
       <c r="T27" s="12">
         <f t="shared" si="4"/>
-        <v>2.5522041763341052E-2</v>
+        <v>-0.3777520278099652</v>
       </c>
       <c r="U27">
         <v>1</v>
@@ -3226,27 +3226,27 @@
       </c>
       <c r="F28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>32601221.645448308</v>
+        <v>30771914.979088616</v>
       </c>
       <c r="G28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>30351804.513628267</v>
+        <v>29013524.004899658</v>
       </c>
       <c r="H28" s="12">
         <f t="shared" si="0"/>
-        <v>-6.8997939901865535E-2</v>
+        <v>-5.7142721711791133E-2</v>
       </c>
       <c r="I28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="J28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>764</v>
+        <v>1300</v>
       </c>
       <c r="K28" s="12">
         <f t="shared" si="1"/>
-        <v>-3.1685678073510748E-2</v>
+        <v>0.68831168831168821</v>
       </c>
       <c r="L28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3254,11 +3254,11 @@
       </c>
       <c r="M28" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N28" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -3266,23 +3266,23 @@
       </c>
       <c r="P28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Q28" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="R28" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1120</v>
+        <v>1115</v>
       </c>
       <c r="S28">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1042</v>
+        <v>1671</v>
       </c>
       <c r="T28" s="12">
         <f t="shared" si="4"/>
-        <v>-6.9642857142857117E-2</v>
+        <v>0.49865470852017935</v>
       </c>
       <c r="U28">
         <v>1</v>
@@ -3306,27 +3306,27 @@
       </c>
       <c r="F29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>41893976.926671989</v>
+        <v>39627788.142400511</v>
       </c>
       <c r="G29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>43282975.098104343</v>
+        <v>41174058.474659473</v>
       </c>
       <c r="H29" s="12">
         <f t="shared" si="0"/>
-        <v>3.3155080355907751E-2</v>
+        <v>3.901984957380189E-2</v>
       </c>
       <c r="I29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>952</v>
+        <v>915</v>
       </c>
       <c r="J29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>900</v>
+        <v>954</v>
       </c>
       <c r="K29" s="12">
         <f t="shared" si="1"/>
-        <v>-5.4621848739495826E-2</v>
+        <v>4.2622950819672045E-2</v>
       </c>
       <c r="L29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3334,11 +3334,11 @@
       </c>
       <c r="M29" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N29" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="O29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -3346,11 +3346,11 @@
       </c>
       <c r="P29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Q29" s="12">
         <f t="shared" si="3"/>
-        <v>0.33333333333333326</v>
+        <v>3</v>
       </c>
       <c r="R29" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -3358,11 +3358,11 @@
       </c>
       <c r="S29">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1126</v>
+        <v>872</v>
       </c>
       <c r="T29" s="12">
         <f t="shared" si="4"/>
-        <v>-7.0546737213403876E-3</v>
+        <v>-0.23104056437389775</v>
       </c>
       <c r="U29">
         <v>1</v>
@@ -3386,27 +3386,27 @@
       </c>
       <c r="F30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>60948510.020695314</v>
+        <v>57867671.527397662</v>
       </c>
       <c r="G30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>55959396.977800012</v>
+        <v>52940271.569831714</v>
       </c>
       <c r="H30" s="12">
         <f t="shared" si="0"/>
-        <v>-8.1857834444209243E-2</v>
+        <v>-8.5149442296689859E-2</v>
       </c>
       <c r="I30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="J30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1151</v>
+        <v>684</v>
       </c>
       <c r="K30" s="12">
         <f t="shared" si="1"/>
-        <v>-1.3710368466152478E-2</v>
+        <v>-0.41186586414445403</v>
       </c>
       <c r="L30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3414,11 +3414,11 @@
       </c>
       <c r="M30" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N30" s="12">
         <f t="shared" si="2"/>
-        <v>-0.19999999999999996</v>
+        <v>-0.8</v>
       </c>
       <c r="O30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -3426,23 +3426,23 @@
       </c>
       <c r="P30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q30" s="12">
         <f t="shared" si="3"/>
-        <v>0.33333333333333326</v>
+        <v>1</v>
       </c>
       <c r="R30" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1504</v>
+        <v>1507</v>
       </c>
       <c r="S30">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1456</v>
+        <v>872</v>
       </c>
       <c r="T30" s="12">
         <f t="shared" si="4"/>
-        <v>-3.1914893617021267E-2</v>
+        <v>-0.42136695421366954</v>
       </c>
       <c r="U30">
         <v>4</v>
@@ -3466,27 +3466,27 @@
       </c>
       <c r="F31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>23188488.13637552</v>
+        <v>21899406.198145673</v>
       </c>
       <c r="G31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>25047854.91353824</v>
+        <v>23896792.324472841</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="0"/>
-        <v>8.0184907538062067E-2</v>
+        <v>9.1207318968141493E-2</v>
       </c>
       <c r="I31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>615</v>
+        <v>604</v>
       </c>
       <c r="J31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>508</v>
+        <v>177</v>
       </c>
       <c r="K31" s="12">
         <f t="shared" si="1"/>
-        <v>-0.17398373983739834</v>
+        <v>-0.70695364238410596</v>
       </c>
       <c r="L31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3494,11 +3494,11 @@
       </c>
       <c r="M31" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N31" s="12">
         <f t="shared" si="2"/>
-        <v>0.66666666666666674</v>
+        <v>-0.66666666666666674</v>
       </c>
       <c r="O31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -3514,15 +3514,15 @@
       </c>
       <c r="R31" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>696</v>
+        <v>705</v>
       </c>
       <c r="S31">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>698</v>
+        <v>229</v>
       </c>
       <c r="T31" s="12">
         <f t="shared" si="4"/>
-        <v>2.8735632183907178E-3</v>
+        <v>-0.67517730496453898</v>
       </c>
       <c r="U31">
         <v>3</v>
@@ -3546,27 +3546,27 @@
       </c>
       <c r="F32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>72283101.544206813</v>
+        <v>68379291.574158043</v>
       </c>
       <c r="G32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>62386024.992774226</v>
+        <v>58685299.940138116</v>
       </c>
       <c r="H32" s="12">
         <f t="shared" si="0"/>
-        <v>-0.13692102773674897</v>
+        <v>-0.14176794480982147</v>
       </c>
       <c r="I32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2045</v>
+        <v>1677</v>
       </c>
       <c r="J32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1572</v>
+        <v>1317</v>
       </c>
       <c r="K32" s="12">
         <f t="shared" si="1"/>
-        <v>-0.23129584352078236</v>
+        <v>-0.21466905187835417</v>
       </c>
       <c r="L32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3574,11 +3574,11 @@
       </c>
       <c r="M32" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N32" s="12">
         <f t="shared" si="2"/>
-        <v>-0.18181818181818177</v>
+        <v>-0.54545454545454541</v>
       </c>
       <c r="O32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -3586,23 +3586,23 @@
       </c>
       <c r="P32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q32" s="12">
         <f t="shared" si="3"/>
-        <v>-0.41176470588235292</v>
+        <v>-0.29411764705882348</v>
       </c>
       <c r="R32" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1967</v>
+        <v>1958</v>
       </c>
       <c r="S32">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1913</v>
+        <v>1638</v>
       </c>
       <c r="T32" s="12">
         <f t="shared" si="4"/>
-        <v>-2.7452974072191161E-2</v>
+        <v>-0.16343207354443312</v>
       </c>
       <c r="U32">
         <v>5</v>
@@ -3626,27 +3626,27 @@
       </c>
       <c r="F33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24522885.913414594</v>
+        <v>23416239.072707906</v>
       </c>
       <c r="G33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>24921846.100234803</v>
+        <v>23846332.143704496</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="0"/>
-        <v>1.6268892178060046E-2</v>
+        <v>1.8367299277272542E-2</v>
       </c>
       <c r="I33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>693</v>
+        <v>707</v>
       </c>
       <c r="J33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>741</v>
+        <v>631</v>
       </c>
       <c r="K33" s="12">
         <f t="shared" si="1"/>
-        <v>6.9264069264069361E-2</v>
+        <v>-0.10749646393210754</v>
       </c>
       <c r="L33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3654,11 +3654,11 @@
       </c>
       <c r="M33" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N33" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="O33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -3666,23 +3666,23 @@
       </c>
       <c r="P33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q33" s="12">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="R33" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="S33">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>860</v>
+        <v>884</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="4"/>
-        <v>1.7751479289940919E-2</v>
+        <v>5.3635280095351678E-2</v>
       </c>
       <c r="U33">
         <v>3</v>
@@ -3706,27 +3706,27 @@
       </c>
       <c r="F34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20703555.59535294</v>
+        <v>19580984.263010703</v>
       </c>
       <c r="G34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>23049754.684711441</v>
+        <v>21933834.462986201</v>
       </c>
       <c r="H34" s="12">
         <f t="shared" si="0"/>
-        <v>0.11332348584052498</v>
+        <v>0.12015995561674253</v>
       </c>
       <c r="I34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>582</v>
+        <v>592</v>
       </c>
       <c r="J34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>609</v>
+        <v>1418</v>
       </c>
       <c r="K34" s="12">
         <f t="shared" si="1"/>
-        <v>4.6391752577319645E-2</v>
+        <v>1.3952702702702702</v>
       </c>
       <c r="L34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3734,15 +3734,15 @@
       </c>
       <c r="M34" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N34" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -3750,19 +3750,19 @@
       </c>
       <c r="Q34" s="12">
         <f t="shared" si="3"/>
-        <v>-0.25</v>
+        <v>-0.4</v>
       </c>
       <c r="R34" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="S34">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>758</v>
+        <v>1039</v>
       </c>
       <c r="T34" s="12">
         <f t="shared" si="4"/>
-        <v>9.2219020172910726E-2</v>
+        <v>0.49067431850789101</v>
       </c>
       <c r="U34">
         <v>4</v>
@@ -3786,27 +3786,27 @@
       </c>
       <c r="F35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>36053259.761528894</v>
+        <v>34271546.343865938</v>
       </c>
       <c r="G35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>35754529.012632072</v>
+        <v>33947334.926795498</v>
       </c>
       <c r="H35" s="12">
         <f t="shared" si="0"/>
-        <v>-8.285818005715706E-3</v>
+        <v>-9.4600755337224118E-3</v>
       </c>
       <c r="I35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>865</v>
+        <v>993</v>
       </c>
       <c r="J35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="K35" s="12">
         <f t="shared" si="1"/>
-        <v>3.2369942196531776E-2</v>
+        <v>-0.10171198388721048</v>
       </c>
       <c r="L35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3814,35 +3814,35 @@
       </c>
       <c r="M35" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N35" s="12">
         <f t="shared" si="2"/>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="O35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="P35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Q35" s="12">
         <f t="shared" si="3"/>
-        <v>0.28571428571428581</v>
+        <v>-0.77777777777777779</v>
       </c>
       <c r="R35" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1108</v>
+        <v>1124</v>
       </c>
       <c r="S35">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1151</v>
+        <v>1130</v>
       </c>
       <c r="T35" s="12">
         <f t="shared" si="4"/>
-        <v>3.8808664259927905E-2</v>
+        <v>5.3380782918148739E-3</v>
       </c>
       <c r="U35">
         <v>13</v>
@@ -3866,27 +3866,27 @@
       </c>
       <c r="F36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>34761818.863370262</v>
+        <v>33052464.113899976</v>
       </c>
       <c r="G36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>33981946.736486293</v>
+        <v>32190582.015026674</v>
       </c>
       <c r="H36" s="12">
         <f t="shared" si="0"/>
-        <v>-2.2434733060120338E-2</v>
+        <v>-2.6076182880139465E-2</v>
       </c>
       <c r="I36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="J36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>876</v>
+        <v>1129</v>
       </c>
       <c r="K36" s="12">
         <f t="shared" si="1"/>
-        <v>1.7421602787456525E-2</v>
+        <v>0.3021914648212225</v>
       </c>
       <c r="L36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3894,11 +3894,11 @@
       </c>
       <c r="M36" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N36" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -3906,23 +3906,23 @@
       </c>
       <c r="P36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>272</v>
+        <v>5</v>
       </c>
       <c r="Q36" s="12">
         <f t="shared" si="3"/>
-        <v>5.6341463414634143</v>
+        <v>-0.87804878048780488</v>
       </c>
       <c r="R36" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1085</v>
+        <v>1093</v>
       </c>
       <c r="S36">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1381</v>
+        <v>1460</v>
       </c>
       <c r="T36" s="12">
         <f t="shared" si="4"/>
-        <v>0.27281105990783416</v>
+        <v>0.33577310155535223</v>
       </c>
       <c r="U36">
         <v>4</v>
@@ -3946,27 +3946,27 @@
       </c>
       <c r="F37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>54910655.209512085</v>
+        <v>52158232.747112714</v>
       </c>
       <c r="G37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>60889043.762123182</v>
+        <v>57989157.172912218</v>
       </c>
       <c r="H37" s="12">
         <f t="shared" si="0"/>
-        <v>0.10887483549049826</v>
+        <v>0.11179298298066431</v>
       </c>
       <c r="I37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1385</v>
+        <v>1425</v>
       </c>
       <c r="J37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1310</v>
+        <v>827</v>
       </c>
       <c r="K37" s="12">
         <f t="shared" si="1"/>
-        <v>-5.4151624548736454E-2</v>
+        <v>-0.41964912280701749</v>
       </c>
       <c r="L37" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3986,23 +3986,23 @@
       </c>
       <c r="P37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>123</v>
+        <v>1</v>
       </c>
       <c r="Q37" s="12">
         <f t="shared" si="3"/>
-        <v>1.1578947368421053</v>
+        <v>-0.98245614035087714</v>
       </c>
       <c r="R37" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1795</v>
+        <v>1791</v>
       </c>
       <c r="S37">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2277</v>
+        <v>696</v>
       </c>
       <c r="T37" s="12">
         <f t="shared" si="4"/>
-        <v>0.26852367688022283</v>
+        <v>-0.61139028475711887</v>
       </c>
       <c r="U37">
         <v>16</v>
@@ -4030,23 +4030,23 @@
       </c>
       <c r="G38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21690653.82312274</v>
+        <v>20656820.414189544</v>
       </c>
       <c r="H38" s="12">
         <f t="shared" si="0"/>
-        <v>0.23938267473134389</v>
+        <v>0.18031044823053022</v>
       </c>
       <c r="I38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>5</v>
+        <v>443</v>
       </c>
       <c r="J38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>454</v>
+        <v>1560</v>
       </c>
       <c r="K38" s="12">
         <f t="shared" si="1"/>
-        <v>89.8</v>
+        <v>2.5214446952595937</v>
       </c>
       <c r="L38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4054,11 +4054,11 @@
       </c>
       <c r="M38" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N38" s="12">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="O38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4066,23 +4066,23 @@
       </c>
       <c r="P38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q38" s="12">
         <f t="shared" si="3"/>
-        <v>-0.5</v>
+        <v>4.5</v>
       </c>
       <c r="R38" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="S38">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>619</v>
+        <v>1909</v>
       </c>
       <c r="T38" s="12">
         <f t="shared" si="4"/>
-        <v>1.8092105263157965E-2</v>
+        <v>2.1658374792703152</v>
       </c>
       <c r="U38">
         <v>3</v>
@@ -4106,27 +4106,27 @@
       </c>
       <c r="F39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>63981776.356715463</v>
+        <v>61288523.598765254</v>
       </c>
       <c r="G39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>70387346.462206155</v>
+        <v>66763112.972614646</v>
       </c>
       <c r="H39" s="12">
         <f t="shared" si="0"/>
-        <v>0.10011554024036351</v>
+        <v>8.9324869525159833E-2</v>
       </c>
       <c r="I39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1854</v>
+        <v>2056</v>
       </c>
       <c r="J39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1948</v>
+        <v>601</v>
       </c>
       <c r="K39" s="12">
         <f t="shared" si="1"/>
-        <v>5.0701186623516747E-2</v>
+        <v>-0.70768482490272366</v>
       </c>
       <c r="L39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4134,11 +4134,11 @@
       </c>
       <c r="M39" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N39" s="12">
         <f t="shared" si="2"/>
-        <v>0.19999999999999996</v>
+        <v>-0.6</v>
       </c>
       <c r="O39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4146,23 +4146,23 @@
       </c>
       <c r="P39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q39" s="12">
         <f t="shared" si="3"/>
-        <v>-0.5</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="R39" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2048</v>
+        <v>2055</v>
       </c>
       <c r="S39">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2066</v>
+        <v>866</v>
       </c>
       <c r="T39" s="12">
         <f t="shared" si="4"/>
-        <v>8.7890625E-3</v>
+        <v>-0.57858880778588806</v>
       </c>
       <c r="U39">
         <v>4</v>
@@ -4186,27 +4186,27 @@
       </c>
       <c r="F40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>45081578.612316735</v>
+        <v>42805016.573299475</v>
       </c>
       <c r="G40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>48694697.570638672</v>
+        <v>46227650.783002853</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" si="0"/>
-        <v>8.0146238653115764E-2</v>
+        <v>7.9958717077995844E-2</v>
       </c>
       <c r="I40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>783</v>
+        <v>793</v>
       </c>
       <c r="J40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>838</v>
+        <v>507</v>
       </c>
       <c r="K40" s="12">
         <f t="shared" si="1"/>
-        <v>7.0242656449553076E-2</v>
+        <v>-0.36065573770491799</v>
       </c>
       <c r="L40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4214,35 +4214,35 @@
       </c>
       <c r="M40" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N40" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="O40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q40" s="12">
         <f t="shared" si="3"/>
-        <v>-0.16666666666666663</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="R40" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="S40">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>893</v>
+        <v>754</v>
       </c>
       <c r="T40" s="12">
         <f t="shared" si="4"/>
-        <v>1.3620885357548351E-2</v>
+        <v>-0.14318181818181819</v>
       </c>
       <c r="U40">
         <v>3</v>
@@ -4266,27 +4266,27 @@
       </c>
       <c r="F41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>36951327.241868146</v>
+        <v>35305267.70624648</v>
       </c>
       <c r="G41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>28817713.877122149</v>
+        <v>27034432.239690185</v>
       </c>
       <c r="H41" s="12">
         <f t="shared" si="0"/>
-        <v>-0.22011694766758227</v>
+        <v>-0.23426632918840484</v>
       </c>
       <c r="I41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>935</v>
+        <v>954</v>
       </c>
       <c r="J41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1035</v>
+        <v>822</v>
       </c>
       <c r="K41" s="12">
         <f t="shared" si="1"/>
-        <v>0.10695187165775399</v>
+        <v>-0.13836477987421381</v>
       </c>
       <c r="L41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4294,11 +4294,11 @@
       </c>
       <c r="M41" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N41" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-0.66666666666666674</v>
       </c>
       <c r="O41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4306,23 +4306,23 @@
       </c>
       <c r="P41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="Q41" s="12">
         <f t="shared" si="3"/>
-        <v>1.3333333333333335</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="R41" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="S41">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1098</v>
+        <v>1146</v>
       </c>
       <c r="T41" s="12">
         <f t="shared" si="4"/>
-        <v>-1.8181818181818299E-3</v>
+        <v>4.2766151046405909E-2</v>
       </c>
       <c r="U41">
         <v>4</v>
@@ -4346,27 +4346,27 @@
       </c>
       <c r="F42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>36616468.703792453</v>
+        <v>34656045.854344085</v>
       </c>
       <c r="G42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>36351905.914852493</v>
+        <v>34623144.718677483</v>
       </c>
       <c r="H42" s="12">
         <f t="shared" si="0"/>
-        <v>-7.2252403987979053E-3</v>
+        <v>-9.4936207681861617E-4</v>
       </c>
       <c r="I42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>646</v>
+        <v>621</v>
       </c>
       <c r="J42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>616</v>
+        <v>932</v>
       </c>
       <c r="K42" s="12">
         <f t="shared" si="1"/>
-        <v>-4.6439628482972117E-2</v>
+        <v>0.50080515297906603</v>
       </c>
       <c r="L42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4374,11 +4374,11 @@
       </c>
       <c r="M42" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N42" s="12">
         <f t="shared" si="2"/>
-        <v>-0.19999999999999996</v>
+        <v>-0.8</v>
       </c>
       <c r="O42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="P42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>6</v>
+        <v>319</v>
       </c>
       <c r="Q42" s="12">
         <f t="shared" si="3"/>
@@ -4394,15 +4394,15 @@
       </c>
       <c r="R42" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="S42">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>835</v>
+        <v>1415</v>
       </c>
       <c r="T42" s="12">
         <f t="shared" si="4"/>
-        <v>-2.6806526806526842E-2</v>
+        <v>0.64534883720930236</v>
       </c>
       <c r="U42">
         <v>2</v>
@@ -4426,27 +4426,27 @@
       </c>
       <c r="F43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>22704753.056662936</v>
+        <v>21610464.703248747</v>
       </c>
       <c r="G43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22763455.27254276</v>
+        <v>21742784.05233898</v>
       </c>
       <c r="H43" s="12">
         <f t="shared" si="0"/>
-        <v>2.5854593411926974E-3</v>
+        <v>6.1229293727469436E-3</v>
       </c>
       <c r="I43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="J43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>623</v>
+        <v>1573</v>
       </c>
       <c r="K43" s="12">
         <f t="shared" si="1"/>
-        <v>8.1597222222222321E-2</v>
+        <v>1.7693661971830985</v>
       </c>
       <c r="L43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4454,11 +4454,11 @@
       </c>
       <c r="M43" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N43" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="O43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4466,23 +4466,23 @@
       </c>
       <c r="P43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>137</v>
       </c>
       <c r="Q43" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>44.666666666666664</v>
       </c>
       <c r="R43" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="S43">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>698</v>
+        <v>2252</v>
       </c>
       <c r="T43" s="12">
         <f t="shared" si="4"/>
-        <v>5.2790346907994001E-2</v>
+        <v>2.3813813813813813</v>
       </c>
       <c r="U43">
         <v>2</v>
@@ -4506,27 +4506,27 @@
       </c>
       <c r="F44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21905672.652470183</v>
+        <v>20687868.148741201</v>
       </c>
       <c r="G44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19508855.302097976</v>
+        <v>18652888.434304617</v>
       </c>
       <c r="H44" s="12">
         <f t="shared" si="0"/>
-        <v>-0.10941537328697049</v>
+        <v>-9.8365848999303784E-2</v>
       </c>
       <c r="I44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>768</v>
+        <v>720</v>
       </c>
       <c r="J44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>708</v>
+        <v>442</v>
       </c>
       <c r="K44" s="12">
         <f t="shared" si="1"/>
-        <v>-7.8125E-2</v>
+        <v>-0.38611111111111107</v>
       </c>
       <c r="L44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4534,11 +4534,11 @@
       </c>
       <c r="M44" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N44" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4546,23 +4546,23 @@
       </c>
       <c r="P44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q44" s="12">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="R44" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="S44">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>687</v>
+        <v>614</v>
       </c>
       <c r="T44" s="12">
         <f t="shared" si="4"/>
-        <v>-3.2394366197183055E-2</v>
+        <v>-0.13399153737658676</v>
       </c>
       <c r="U44">
         <v>3</v>
@@ -4586,27 +4586,27 @@
       </c>
       <c r="F45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>68951901.83255586</v>
+        <v>65941089.434293799</v>
       </c>
       <c r="G45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>65624769.39583008</v>
+        <v>62024410.34365315</v>
       </c>
       <c r="H45" s="12">
         <f t="shared" si="0"/>
-        <v>-4.8252946594648738E-2</v>
+        <v>-5.9396639094708603E-2</v>
       </c>
       <c r="I45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1058</v>
+        <v>1083</v>
       </c>
       <c r="J45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1375</v>
+        <v>1807</v>
       </c>
       <c r="K45" s="12">
         <f t="shared" si="1"/>
-        <v>0.29962192816635169</v>
+        <v>0.66851338873499544</v>
       </c>
       <c r="L45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4614,11 +4614,11 @@
       </c>
       <c r="M45" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N45" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="O45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4626,23 +4626,23 @@
       </c>
       <c r="P45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q45" s="12">
         <f t="shared" si="3"/>
-        <v>-0.75</v>
+        <v>-0.33333333333333337</v>
       </c>
       <c r="R45" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1272</v>
+        <v>1259</v>
       </c>
       <c r="S45">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1250</v>
+        <v>2070</v>
       </c>
       <c r="T45" s="12">
         <f t="shared" si="4"/>
-        <v>-1.7295597484276781E-2</v>
+        <v>0.64416203335980948</v>
       </c>
       <c r="U45">
         <v>5</v>
@@ -4666,27 +4666,27 @@
       </c>
       <c r="F46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>31224174.820838396</v>
+        <v>29718671.064681828</v>
       </c>
       <c r="G46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>30416321.719961289</v>
+        <v>29054377.526877664</v>
       </c>
       <c r="H46" s="12">
         <f t="shared" si="0"/>
-        <v>-2.5872680559614336E-2</v>
+        <v>-2.2352733618483445E-2</v>
       </c>
       <c r="I46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>922</v>
+        <v>908</v>
       </c>
       <c r="J46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>946</v>
+        <v>1098</v>
       </c>
       <c r="K46" s="12">
         <f t="shared" si="1"/>
-        <v>2.6030368763557465E-2</v>
+        <v>0.20925110132158586</v>
       </c>
       <c r="L46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4694,35 +4694,35 @@
       </c>
       <c r="M46" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N46" s="12">
         <f t="shared" si="2"/>
-        <v>0.19999999999999996</v>
+        <v>-0.4</v>
       </c>
       <c r="O46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q46" s="12">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>1.6666666666666665</v>
       </c>
       <c r="R46" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="S46">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>912</v>
+        <v>1097</v>
       </c>
       <c r="T46" s="12">
         <f t="shared" si="4"/>
-        <v>3.167420814479649E-2</v>
+        <v>0.22982062780269064</v>
       </c>
       <c r="U46">
         <v>4</v>
@@ -4746,27 +4746,27 @@
       </c>
       <c r="F47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>46284776.708795786</v>
+        <v>43797964.177689955</v>
       </c>
       <c r="G47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>53489987.771002561</v>
+        <v>50825033.960358381</v>
       </c>
       <c r="H47" s="12">
         <f t="shared" si="0"/>
-        <v>0.15567129355595499</v>
+        <v>0.16044284054298386</v>
       </c>
       <c r="I47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>996</v>
+        <v>1055</v>
       </c>
       <c r="J47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1025</v>
+        <v>621</v>
       </c>
       <c r="K47" s="12">
         <f t="shared" si="1"/>
-        <v>2.9116465863453733E-2</v>
+        <v>-0.41137440758293842</v>
       </c>
       <c r="L47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4774,15 +4774,15 @@
       </c>
       <c r="M47" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N47" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-0.66666666666666674</v>
       </c>
       <c r="O47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -4790,19 +4790,19 @@
       </c>
       <c r="Q47" s="12">
         <f t="shared" si="3"/>
-        <v>-0.64705882352941169</v>
+        <v>-0.66666666666666674</v>
       </c>
       <c r="R47" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1301</v>
+        <v>1308</v>
       </c>
       <c r="S47">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1338</v>
+        <v>833</v>
       </c>
       <c r="T47" s="12">
         <f t="shared" si="4"/>
-        <v>2.8439661798616456E-2</v>
+        <v>-0.36314984709480125</v>
       </c>
       <c r="U47">
         <v>6</v>
@@ -4826,27 +4826,27 @@
       </c>
       <c r="F48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24156172.660815898</v>
+        <v>22770248.911103602</v>
       </c>
       <c r="G48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>27405554.935270023</v>
+        <v>26152148.725233007</v>
       </c>
       <c r="H48" s="12">
         <f t="shared" si="0"/>
-        <v>0.13451560891204406</v>
+        <v>0.14852274243169417</v>
       </c>
       <c r="I48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="J48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>380</v>
+        <v>547</v>
       </c>
       <c r="K48" s="12">
         <f t="shared" si="1"/>
-        <v>5.2631578947368363E-2</v>
+        <v>0.42819843342036545</v>
       </c>
       <c r="L48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4854,35 +4854,35 @@
       </c>
       <c r="M48" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N48" s="12">
         <f t="shared" si="2"/>
-        <v>0.19999999999999996</v>
+        <v>1</v>
       </c>
       <c r="O48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q48" s="12">
         <f t="shared" si="3"/>
-        <v>-0.7142857142857143</v>
+        <v>-0.66666666666666674</v>
       </c>
       <c r="R48" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="S48">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>489</v>
+        <v>703</v>
       </c>
       <c r="T48" s="12">
         <f t="shared" si="4"/>
-        <v>1.0330578512396604E-2</v>
+        <v>0.44948453608247418</v>
       </c>
       <c r="U48">
         <v>1</v>
@@ -4906,27 +4906,27 @@
       </c>
       <c r="F49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>23676615.185974032</v>
+        <v>22546305.818256099</v>
       </c>
       <c r="G49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20136026.2156309</v>
+        <v>19126089.304449983</v>
       </c>
       <c r="H49" s="12">
         <f t="shared" si="0"/>
-        <v>-0.14953949044374248</v>
+        <v>-0.15169742402042252</v>
       </c>
       <c r="I49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>323</v>
+        <v>292</v>
       </c>
       <c r="J49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>319</v>
+        <v>756</v>
       </c>
       <c r="K49" s="12">
         <f t="shared" si="1"/>
-        <v>-1.2383900928792602E-2</v>
+        <v>1.5890410958904111</v>
       </c>
       <c r="L49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -4934,11 +4934,11 @@
       </c>
       <c r="M49" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N49" s="12">
         <f t="shared" si="2"/>
-        <v>-0.33333333333333337</v>
+        <v>-0.83333333333333337</v>
       </c>
       <c r="O49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -4946,23 +4946,23 @@
       </c>
       <c r="P49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q49" s="12">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R49" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="S49">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>458</v>
+        <v>694</v>
       </c>
       <c r="T49" s="12">
         <f t="shared" si="4"/>
-        <v>3.1531531531531432E-2</v>
+        <v>0.55955056179775275</v>
       </c>
       <c r="U49">
         <v>5</v>
@@ -4986,27 +4986,27 @@
       </c>
       <c r="F50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19565337.991295934</v>
+        <v>18657852.426756896</v>
       </c>
       <c r="G50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>17633388.891193338</v>
+        <v>16764643.498383747</v>
       </c>
       <c r="H50" s="12">
         <f t="shared" si="0"/>
-        <v>-9.8743456461731771E-2</v>
+        <v>-0.10146982005593164</v>
       </c>
       <c r="I50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>384</v>
+        <v>348</v>
       </c>
       <c r="J50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>341</v>
+        <v>1358</v>
       </c>
       <c r="K50" s="12">
         <f t="shared" si="1"/>
-        <v>-0.11197916666666663</v>
+        <v>2.9022988505747125</v>
       </c>
       <c r="L50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5014,11 +5014,11 @@
       </c>
       <c r="M50" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N50" s="12">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="O50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -5026,11 +5026,11 @@
       </c>
       <c r="P50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q50" s="12">
         <f t="shared" si="3"/>
-        <v>-0.81818181818181812</v>
+        <v>-0.45454545454545459</v>
       </c>
       <c r="R50" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -5038,11 +5038,11 @@
       </c>
       <c r="S50">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>424</v>
+        <v>1262</v>
       </c>
       <c r="T50" s="12">
         <f t="shared" si="4"/>
-        <v>-7.0257611241217877E-3</v>
+        <v>1.9555035128805622</v>
       </c>
       <c r="U50">
         <v>4</v>
@@ -5066,27 +5066,27 @@
       </c>
       <c r="F51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>42465575.241866045</v>
+        <v>40544706.538535334</v>
       </c>
       <c r="G51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>41199724.440495275</v>
+        <v>39213836.923041739</v>
       </c>
       <c r="H51" s="12">
         <f t="shared" si="0"/>
-        <v>-2.980886975299446E-2</v>
+        <v>-3.2824744069332001E-2</v>
       </c>
       <c r="I51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>947</v>
+        <v>995</v>
       </c>
       <c r="J51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>941</v>
+        <v>492</v>
       </c>
       <c r="K51" s="12">
         <f t="shared" si="1"/>
-        <v>-6.3357972544878516E-3</v>
+        <v>-0.50552763819095481</v>
       </c>
       <c r="L51" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5102,27 +5102,27 @@
       </c>
       <c r="O51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q51" s="12">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>-0.8</v>
       </c>
       <c r="R51" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1127</v>
+        <v>1134</v>
       </c>
       <c r="S51">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1094</v>
+        <v>441</v>
       </c>
       <c r="T51" s="12">
         <f t="shared" si="4"/>
-        <v>-2.9281277728482658E-2</v>
+        <v>-0.61111111111111116</v>
       </c>
       <c r="U51">
         <v>5</v>
@@ -5146,27 +5146,27 @@
       </c>
       <c r="F52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>45055941.481699936</v>
+        <v>42886891.103262864</v>
       </c>
       <c r="G52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>43110471.737202205</v>
+        <v>40939585.895147137</v>
       </c>
       <c r="H52" s="12">
         <f t="shared" si="0"/>
-        <v>-4.3178983293200246E-2</v>
+        <v>-4.540560432387164E-2</v>
       </c>
       <c r="I52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>810</v>
+        <v>912</v>
       </c>
       <c r="J52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>817</v>
+        <v>949</v>
       </c>
       <c r="K52" s="12">
         <f t="shared" si="1"/>
-        <v>8.6419753086419693E-3</v>
+        <v>4.0570175438596534E-2</v>
       </c>
       <c r="L52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5174,35 +5174,35 @@
       </c>
       <c r="M52" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N52" s="12">
         <f t="shared" si="2"/>
-        <v>-0.5</v>
+        <v>2</v>
       </c>
       <c r="O52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="P52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q52" s="12">
         <f t="shared" si="3"/>
-        <v>-0.30000000000000004</v>
+        <v>-0.7857142857142857</v>
       </c>
       <c r="R52" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>971</v>
+        <v>978</v>
       </c>
       <c r="S52">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1011</v>
+        <v>922</v>
       </c>
       <c r="T52" s="12">
         <f t="shared" si="4"/>
-        <v>4.1194644696189497E-2</v>
+        <v>-5.7259713701431458E-2</v>
       </c>
       <c r="U52">
         <v>4</v>
@@ -5226,27 +5226,27 @@
       </c>
       <c r="F53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>63893921.779931098</v>
+        <v>60223755.032434106</v>
       </c>
       <c r="G53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>77451228.109518692</v>
+        <v>73666459.599487707</v>
       </c>
       <c r="H53" s="12">
         <f t="shared" si="0"/>
-        <v>0.21218460147559615</v>
+        <v>0.22321266018390751</v>
       </c>
       <c r="I53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1508</v>
+        <v>1462</v>
       </c>
       <c r="J53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1783</v>
+        <v>1087</v>
       </c>
       <c r="K53" s="12">
         <f t="shared" si="1"/>
-        <v>0.18236074270557023</v>
+        <v>-0.2564979480164159</v>
       </c>
       <c r="L53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5254,35 +5254,35 @@
       </c>
       <c r="M53" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N53" s="12">
         <f t="shared" si="2"/>
-        <v>0.14285714285714279</v>
+        <v>0.71428571428571419</v>
       </c>
       <c r="O53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q53" s="12">
         <f t="shared" si="3"/>
-        <v>-0.72972972972972971</v>
+        <v>-0.84615384615384615</v>
       </c>
       <c r="R53" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2122</v>
+        <v>2083</v>
       </c>
       <c r="S53">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2048</v>
+        <v>1354</v>
       </c>
       <c r="T53" s="12">
         <f t="shared" si="4"/>
-        <v>-3.4872761545711617E-2</v>
+        <v>-0.34997599615938546</v>
       </c>
       <c r="U53">
         <v>8</v>
@@ -5306,27 +5306,27 @@
       </c>
       <c r="F54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20534534.922981523</v>
+        <v>19628260.883901495</v>
       </c>
       <c r="G54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19415132.028813072</v>
+        <v>18415275.797894016</v>
       </c>
       <c r="H54" s="12">
         <f t="shared" si="0"/>
-        <v>-5.4513184660230918E-2</v>
+        <v>-6.1797888930767875E-2</v>
       </c>
       <c r="I54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>549</v>
+        <v>529</v>
       </c>
       <c r="J54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>582</v>
+        <v>357</v>
       </c>
       <c r="K54" s="12">
         <f t="shared" si="1"/>
-        <v>6.0109289617486406E-2</v>
+        <v>-0.32514177693761814</v>
       </c>
       <c r="L54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M54" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N54" s="12">
         <f t="shared" si="2"/>
@@ -5354,15 +5354,15 @@
       </c>
       <c r="R54" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="S54">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>690</v>
+        <v>490</v>
       </c>
       <c r="T54" s="12">
         <f t="shared" si="4"/>
-        <v>-1.4471780028944004E-3</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="U54">
         <v>2</v>
@@ -5386,27 +5386,27 @@
       </c>
       <c r="F55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>32408420.627318345</v>
+        <v>30615413.367241357</v>
       </c>
       <c r="G55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>33783028.370750755</v>
+        <v>32094490.60502778</v>
       </c>
       <c r="H55" s="12">
         <f t="shared" si="0"/>
-        <v>4.2415141399198442E-2</v>
+        <v>4.8311522697552123E-2</v>
       </c>
       <c r="I55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>742</v>
+        <v>796</v>
       </c>
       <c r="J55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>763</v>
+        <v>310</v>
       </c>
       <c r="K55" s="12">
         <f t="shared" si="1"/>
-        <v>2.8301886792452935E-2</v>
+        <v>-0.61055276381909551</v>
       </c>
       <c r="L55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5414,23 +5414,23 @@
       </c>
       <c r="M55" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N55" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="O55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q55" s="12">
         <f t="shared" si="3"/>
-        <v>0.16666666666666674</v>
+        <v>-0.55555555555555558</v>
       </c>
       <c r="R55" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -5438,11 +5438,11 @@
       </c>
       <c r="S55">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>863</v>
+        <v>457</v>
       </c>
       <c r="T55" s="12">
         <f t="shared" si="4"/>
-        <v>-2.924634420697414E-2</v>
+        <v>-0.48593925759280088</v>
       </c>
       <c r="U55">
         <v>7</v>
@@ -5466,27 +5466,27 @@
       </c>
       <c r="F56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24757924.64762653</v>
+        <v>23662873.351727627</v>
       </c>
       <c r="G56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>21302689.942315493</v>
+        <v>20317389.490997106</v>
       </c>
       <c r="H56" s="12">
         <f t="shared" si="0"/>
-        <v>-0.1395607569894709</v>
+        <v>-0.14138113368578997</v>
       </c>
       <c r="I56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>595</v>
+        <v>679</v>
       </c>
       <c r="J56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>603</v>
+        <v>326</v>
       </c>
       <c r="K56" s="12">
         <f t="shared" si="1"/>
-        <v>1.3445378151260456E-2</v>
+        <v>-0.51988217967599404</v>
       </c>
       <c r="L56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5494,11 +5494,11 @@
       </c>
       <c r="M56" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N56" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -5506,23 +5506,23 @@
       </c>
       <c r="P56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q56" s="12">
         <f t="shared" si="3"/>
-        <v>0.33333333333333326</v>
+        <v>-0.33333333333333337</v>
       </c>
       <c r="R56" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="S56">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>729</v>
+        <v>418</v>
       </c>
       <c r="T56" s="12">
         <f t="shared" si="4"/>
-        <v>-6.7774936061381075E-2</v>
+        <v>-0.46203346203346207</v>
       </c>
       <c r="U56">
         <v>3</v>
@@ -5546,27 +5546,27 @@
       </c>
       <c r="F57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>42696543.090585358</v>
+        <v>40636216.140523255</v>
       </c>
       <c r="G57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>43034612.716141865</v>
+        <v>40981093.886455111</v>
       </c>
       <c r="H57" s="12">
         <f t="shared" si="0"/>
-        <v>7.9179624645315805E-3</v>
+        <v>8.486955201223445E-3</v>
       </c>
       <c r="I57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1031</v>
+        <v>978</v>
       </c>
       <c r="J57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1001</v>
+        <v>949</v>
       </c>
       <c r="K57" s="12">
         <f t="shared" si="1"/>
-        <v>-2.9097963142580063E-2</v>
+        <v>-2.9652351738241323E-2</v>
       </c>
       <c r="L57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5574,11 +5574,11 @@
       </c>
       <c r="M57" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N57" s="12">
         <f t="shared" si="2"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -5594,15 +5594,15 @@
       </c>
       <c r="R57" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="S57">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1107</v>
+        <v>1096</v>
       </c>
       <c r="T57" s="12">
         <f t="shared" si="4"/>
-        <v>1.2808783165599191E-2</v>
+        <v>1.8281535648994041E-3</v>
       </c>
       <c r="U57">
         <v>3</v>
@@ -5626,27 +5626,27 @@
       </c>
       <c r="F58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>54590695.006662175</v>
+        <v>51975399.294892192</v>
       </c>
       <c r="G58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>53108125.971225314</v>
+        <v>50074452.206668533</v>
       </c>
       <c r="H58" s="12">
         <f t="shared" si="0"/>
-        <v>-2.7157907318379637E-2</v>
+        <v>-3.6573977574241967E-2</v>
       </c>
       <c r="I58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1372</v>
+        <v>1304</v>
       </c>
       <c r="J58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1546</v>
+        <v>803</v>
       </c>
       <c r="K58" s="12">
         <f t="shared" si="1"/>
-        <v>0.12682215743440239</v>
+        <v>-0.38420245398773001</v>
       </c>
       <c r="L58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5654,35 +5654,35 @@
       </c>
       <c r="M58" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N58" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="O58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q58" s="12">
         <f t="shared" si="3"/>
-        <v>-0.16666666666666663</v>
+        <v>-0.5</v>
       </c>
       <c r="R58" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1363</v>
+        <v>1374</v>
       </c>
       <c r="S58">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1516</v>
+        <v>1011</v>
       </c>
       <c r="T58" s="12">
         <f t="shared" si="4"/>
-        <v>0.11225238444607477</v>
+        <v>-0.26419213973799127</v>
       </c>
       <c r="U58">
         <v>4</v>
@@ -5706,27 +5706,27 @@
       </c>
       <c r="F59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>27563613.08958514</v>
+        <v>26207240.497092113</v>
       </c>
       <c r="G59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>29166523.35953356</v>
+        <v>27821994.716877595</v>
       </c>
       <c r="H59" s="12">
         <f t="shared" si="0"/>
-        <v>5.8153126179023129E-2</v>
+        <v>6.1614812897399451E-2</v>
       </c>
       <c r="I59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>693</v>
+        <v>741</v>
       </c>
       <c r="J59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1398</v>
+        <v>1700</v>
       </c>
       <c r="K59" s="12">
         <f t="shared" si="1"/>
-        <v>1.0173160173160172</v>
+        <v>1.2941970310391362</v>
       </c>
       <c r="L59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5734,35 +5734,35 @@
       </c>
       <c r="M59" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N59" s="12">
         <f t="shared" si="2"/>
-        <v>-0.19999999999999996</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="O59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q59" s="12">
         <f t="shared" si="3"/>
-        <v>-0.4</v>
+        <v>1</v>
       </c>
       <c r="R59" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>769</v>
+        <v>778</v>
       </c>
       <c r="S59">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>771</v>
+        <v>2052</v>
       </c>
       <c r="T59" s="12">
         <f t="shared" si="4"/>
-        <v>2.6007802340701769E-3</v>
+        <v>1.6375321336760926</v>
       </c>
       <c r="U59">
         <v>3</v>
@@ -5786,27 +5786,27 @@
       </c>
       <c r="F60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>32225585.880645122</v>
+        <v>30690396.011699993</v>
       </c>
       <c r="G60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>32666251.142069764</v>
+        <v>31019483.13461696</v>
       </c>
       <c r="H60" s="12">
         <f t="shared" si="0"/>
-        <v>1.3674390996543773E-2</v>
+        <v>1.0722804710356693E-2</v>
       </c>
       <c r="I60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>451</v>
+        <v>495</v>
       </c>
       <c r="J60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>471</v>
+        <v>650</v>
       </c>
       <c r="K60" s="12">
         <f t="shared" si="1"/>
-        <v>4.434589800443467E-2</v>
+        <v>0.31313131313131315</v>
       </c>
       <c r="L60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5814,35 +5814,35 @@
       </c>
       <c r="M60" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N60" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Q60" s="12">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>-0.4285714285714286</v>
       </c>
       <c r="R60" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>692</v>
+        <v>681</v>
       </c>
       <c r="S60">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>624</v>
+        <v>683</v>
       </c>
       <c r="T60" s="12">
         <f t="shared" si="4"/>
-        <v>-9.8265895953757232E-2</v>
+        <v>2.936857562408246E-3</v>
       </c>
       <c r="U60">
         <v>10</v>
@@ -5866,27 +5866,27 @@
       </c>
       <c r="F61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>85317689.138641283</v>
+        <v>80494151.517660826</v>
       </c>
       <c r="G61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>104957958.57839498</v>
+        <v>99819639.769979075</v>
       </c>
       <c r="H61" s="12">
         <f t="shared" si="0"/>
-        <v>0.23020161045194576</v>
+        <v>0.24008561973695852</v>
       </c>
       <c r="I61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1668</v>
+        <v>1780</v>
       </c>
       <c r="J61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1722</v>
+        <v>733</v>
       </c>
       <c r="K61" s="12">
         <f t="shared" si="1"/>
-        <v>3.2374100719424481E-2</v>
+        <v>-0.58820224719101122</v>
       </c>
       <c r="L61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5894,35 +5894,35 @@
       </c>
       <c r="M61" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N61" s="12">
         <f t="shared" si="2"/>
-        <v>0.22222222222222232</v>
+        <v>-0.44444444444444442</v>
       </c>
       <c r="O61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q61" s="12">
         <f t="shared" si="3"/>
-        <v>-0.25</v>
+        <v>-0.59090909090909083</v>
       </c>
       <c r="R61" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>2048</v>
+        <v>2034</v>
       </c>
       <c r="S61">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2010</v>
+        <v>864</v>
       </c>
       <c r="T61" s="12">
         <f t="shared" si="4"/>
-        <v>-1.85546875E-2</v>
+        <v>-0.5752212389380531</v>
       </c>
       <c r="U61">
         <v>10</v>
@@ -5946,27 +5946,27 @@
       </c>
       <c r="F62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>78408477.996826321</v>
+        <v>74403597.224619329</v>
       </c>
       <c r="G62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>79258311.448570415</v>
+        <v>75202591.101204753</v>
       </c>
       <c r="H62" s="12">
         <f t="shared" si="0"/>
-        <v>1.0838540339712877E-2</v>
+        <v>1.0738645796564361E-2</v>
       </c>
       <c r="I62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1181</v>
+        <v>1208</v>
       </c>
       <c r="J62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1222</v>
+        <v>622</v>
       </c>
       <c r="K62" s="12">
         <f t="shared" si="1"/>
-        <v>3.4716342082980578E-2</v>
+        <v>-0.48509933774834435</v>
       </c>
       <c r="L62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -5974,35 +5974,35 @@
       </c>
       <c r="M62" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N62" s="12">
         <f t="shared" si="2"/>
-        <v>-0.1428571428571429</v>
+        <v>-0.85714285714285721</v>
       </c>
       <c r="O62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Q62" s="12">
         <f t="shared" si="3"/>
-        <v>-0.15789473684210531</v>
+        <v>-0.81818181818181812</v>
       </c>
       <c r="R62" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1587</v>
+        <v>1582</v>
       </c>
       <c r="S62">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1589</v>
+        <v>714</v>
       </c>
       <c r="T62" s="12">
         <f t="shared" si="4"/>
-        <v>1.260239445494582E-3</v>
+        <v>-0.54867256637168138</v>
       </c>
       <c r="U62">
         <v>8</v>
@@ -6026,27 +6026,27 @@
       </c>
       <c r="F63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>48727801.593974993</v>
+        <v>46188082.820514478</v>
       </c>
       <c r="G63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>50766777.004490346</v>
+        <v>48323897.682485439</v>
       </c>
       <c r="H63" s="12">
         <f t="shared" si="0"/>
-        <v>4.1844190458357744E-2</v>
+        <v>4.6241686849628927E-2</v>
       </c>
       <c r="I63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>655</v>
+        <v>737</v>
       </c>
       <c r="J63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>734</v>
+        <v>990</v>
       </c>
       <c r="K63" s="12">
         <f t="shared" si="1"/>
-        <v>0.12061068702290068</v>
+        <v>0.34328358208955234</v>
       </c>
       <c r="L63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6054,11 +6054,11 @@
       </c>
       <c r="M63" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N63" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -6074,15 +6074,15 @@
       </c>
       <c r="R63" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="S63">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>893</v>
+        <v>1094</v>
       </c>
       <c r="T63" s="12">
         <f t="shared" si="4"/>
-        <v>4.4444444444444509E-2</v>
+        <v>0.27654609101516914</v>
       </c>
       <c r="U63">
         <v>4</v>
@@ -6106,27 +6106,27 @@
       </c>
       <c r="F64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>71373716.671775326</v>
+        <v>67882627.172021404</v>
       </c>
       <c r="G64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>75539145.629662246</v>
+        <v>71504925.88939625</v>
       </c>
       <c r="H64" s="12">
         <f t="shared" si="0"/>
-        <v>5.8360824574154924E-2</v>
+        <v>5.3361204011677099E-2</v>
       </c>
       <c r="I64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1370</v>
+        <v>1282</v>
       </c>
       <c r="J64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1362</v>
+        <v>1548</v>
       </c>
       <c r="K64" s="12">
         <f t="shared" si="1"/>
-        <v>-5.839416058394109E-3</v>
+        <v>0.20748829953198134</v>
       </c>
       <c r="L64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6134,35 +6134,35 @@
       </c>
       <c r="M64" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N64" s="12">
         <f t="shared" si="2"/>
-        <v>-7.6923076923076872E-2</v>
+        <v>-0.69230769230769229</v>
       </c>
       <c r="O64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>244</v>
+        <v>280</v>
       </c>
       <c r="P64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>476</v>
+        <v>11</v>
       </c>
       <c r="Q64" s="12">
         <f t="shared" si="3"/>
-        <v>0.95081967213114749</v>
+        <v>-0.96071428571428574</v>
       </c>
       <c r="R64" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1984</v>
+        <v>2017</v>
       </c>
       <c r="S64">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2259</v>
+        <v>1522</v>
       </c>
       <c r="T64" s="12">
         <f t="shared" si="4"/>
-        <v>0.13860887096774199</v>
+        <v>-0.24541398116013879</v>
       </c>
       <c r="U64">
         <v>9</v>
@@ -6186,27 +6186,27 @@
       </c>
       <c r="F65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5369530.2958202437</v>
+        <v>5076964.1164683579</v>
       </c>
       <c r="G65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>3163370.7771156929</v>
+        <v>2920456.5121259899</v>
       </c>
       <c r="H65" s="12">
         <f t="shared" si="0"/>
-        <v>-0.41086638814979259</v>
+        <v>-0.42476321574683096</v>
       </c>
       <c r="I65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="J65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>242</v>
+        <v>702</v>
       </c>
       <c r="K65" s="12">
         <f t="shared" si="1"/>
-        <v>-9.7014925373134275E-2</v>
+        <v>1.8192771084337349</v>
       </c>
       <c r="L65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6214,11 +6214,11 @@
       </c>
       <c r="M65" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N65" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -6226,23 +6226,23 @@
       </c>
       <c r="P65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q65" s="12">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="R65" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="S65">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>254</v>
+        <v>762</v>
       </c>
       <c r="T65" s="12">
         <f t="shared" si="4"/>
-        <v>-2.6819923371647514E-2</v>
+        <v>1.9083969465648853</v>
       </c>
       <c r="U65">
         <v>3</v>
@@ -6266,39 +6266,39 @@
       </c>
       <c r="F66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>56257298.48234468</v>
+        <v>53626628.117396288</v>
       </c>
       <c r="G66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>54652536.380899057</v>
+        <v>51942957.043750465</v>
       </c>
       <c r="H66" s="12">
         <f t="shared" si="0"/>
-        <v>-2.8525402831940938E-2</v>
+        <v>-3.1396176354031247E-2</v>
       </c>
       <c r="I66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1598</v>
+        <v>1532</v>
       </c>
       <c r="J66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1580</v>
+        <v>481</v>
       </c>
       <c r="K66" s="12">
         <f t="shared" si="1"/>
-        <v>-1.126408010012514E-2</v>
+        <v>-0.68603133159268936</v>
       </c>
       <c r="L66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M66" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N66" s="12">
         <f t="shared" si="2"/>
-        <v>-0.25</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="O66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -6306,23 +6306,23 @@
       </c>
       <c r="P66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q66" s="12">
         <f t="shared" si="3"/>
-        <v>0.66666666666666674</v>
+        <v>0.5</v>
       </c>
       <c r="R66" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1797</v>
+        <v>1767</v>
       </c>
       <c r="S66">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1672</v>
+        <v>623</v>
       </c>
       <c r="T66" s="12">
         <f t="shared" si="4"/>
-        <v>-6.9560378408458523E-2</v>
+        <v>-0.64742501414827391</v>
       </c>
       <c r="U66">
         <v>6</v>
@@ -6346,27 +6346,27 @@
       </c>
       <c r="F67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>22953791.33224605</v>
+        <v>21968090.95705428</v>
       </c>
       <c r="G67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>25985617.40753483</v>
+        <v>24581273.682099607</v>
       </c>
       <c r="H67" s="12">
         <f t="shared" ref="H67:H85" si="5">IFERROR(G67/F67-1,0)</f>
-        <v>0.13208389112737096</v>
+        <v>0.11895356452018846</v>
       </c>
       <c r="I67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="J67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>646</v>
+        <v>1820</v>
       </c>
       <c r="K67" s="12">
         <f t="shared" ref="K67:K85" si="6">IFERROR(J67/I67-1,0)</f>
-        <v>9.4915254237288194E-2</v>
+        <v>2.0795262267343486</v>
       </c>
       <c r="L67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6374,11 +6374,11 @@
       </c>
       <c r="M67" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="N67" s="12">
         <f t="shared" ref="N67:N85" si="7">IFERROR(M67/L67-1,0)</f>
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="O67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -6386,23 +6386,23 @@
       </c>
       <c r="P67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="Q67" s="12">
         <f t="shared" ref="Q67:Q85" si="8">IFERROR(P67/O67-1,0)</f>
-        <v>0.33333333333333326</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="R67" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="S67">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>740</v>
+        <v>2012</v>
       </c>
       <c r="T67" s="12">
         <f t="shared" ref="T67:T85" si="9">IFERROR(S67/R67-1,0)</f>
-        <v>0.10944527736131926</v>
+        <v>2.0029850746268658</v>
       </c>
       <c r="U67">
         <v>3</v>
@@ -6426,27 +6426,27 @@
       </c>
       <c r="F68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>38152542.670676976</v>
+        <v>36202729.775051877</v>
       </c>
       <c r="G68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>39573153.64074301</v>
+        <v>37415644.270037763</v>
       </c>
       <c r="H68" s="12">
         <f t="shared" si="5"/>
-        <v>3.7235027356587569E-2</v>
+        <v>3.3503398846507215E-2</v>
       </c>
       <c r="I68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1027</v>
+        <v>899</v>
       </c>
       <c r="J68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>987</v>
+        <v>1199</v>
       </c>
       <c r="K68" s="12">
         <f t="shared" si="6"/>
-        <v>-3.8948393378773094E-2</v>
+        <v>0.33370411568409342</v>
       </c>
       <c r="L68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6454,35 +6454,35 @@
       </c>
       <c r="M68" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N68" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="O68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="Q68" s="12">
         <f t="shared" si="8"/>
-        <v>0.62222222222222223</v>
+        <v>-0.48936170212765961</v>
       </c>
       <c r="R68" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="S68">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1433</v>
+        <v>1580</v>
       </c>
       <c r="T68" s="12">
         <f t="shared" si="9"/>
-        <v>8.4784254352763044E-2</v>
+        <v>0.19787717968157703</v>
       </c>
       <c r="U68">
         <v>4</v>
@@ -6506,27 +6506,27 @@
       </c>
       <c r="F69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18265551.76599412</v>
+        <v>17783711.442227617</v>
       </c>
       <c r="G69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>25656378.209861528</v>
+        <v>23929894.673063796</v>
       </c>
       <c r="H69" s="12">
         <f t="shared" si="5"/>
-        <v>0.40463198366814601</v>
+        <v>0.34560745380978242</v>
       </c>
       <c r="I69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>597</v>
+        <v>1397</v>
       </c>
       <c r="J69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1253</v>
+        <v>716</v>
       </c>
       <c r="K69" s="12">
         <f t="shared" si="6"/>
-        <v>1.0988274706867673</v>
+        <v>-0.48747315676449532</v>
       </c>
       <c r="L69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6534,11 +6534,11 @@
       </c>
       <c r="M69" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N69" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="O69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -6554,15 +6554,15 @@
       </c>
       <c r="R69" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1345</v>
+        <v>1327</v>
       </c>
       <c r="S69">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1259</v>
+        <v>898</v>
       </c>
       <c r="T69" s="12">
         <f t="shared" si="9"/>
-        <v>-6.394052044609666E-2</v>
+        <v>-0.32328560663149963</v>
       </c>
       <c r="U69">
         <v>4</v>
@@ -6586,27 +6586,27 @@
       </c>
       <c r="F70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>67202251.554740682</v>
+        <v>63481150.813349932</v>
       </c>
       <c r="G70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>68457996.802198336</v>
+        <v>65060314.538961947</v>
       </c>
       <c r="H70" s="12">
         <f t="shared" si="5"/>
-        <v>1.8686059148401712E-2</v>
+        <v>2.4876104251089215E-2</v>
       </c>
       <c r="I70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1236</v>
+        <v>1189</v>
       </c>
       <c r="J70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1225</v>
+        <v>1301</v>
       </c>
       <c r="K70" s="12">
         <f t="shared" si="6"/>
-        <v>-8.8996763754045638E-3</v>
+        <v>9.419680403700581E-2</v>
       </c>
       <c r="L70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6614,35 +6614,35 @@
       </c>
       <c r="M70" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="N70" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>13</v>
+        <v>527</v>
       </c>
       <c r="Q70" s="12">
         <f t="shared" si="8"/>
-        <v>0.625</v>
+        <v>51.7</v>
       </c>
       <c r="R70" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1745</v>
+        <v>1750</v>
       </c>
       <c r="S70">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1732</v>
+        <v>2257</v>
       </c>
       <c r="T70" s="12">
         <f t="shared" si="9"/>
-        <v>-7.4498567335243848E-3</v>
+        <v>0.28971428571428581</v>
       </c>
       <c r="U70">
         <v>4</v>
@@ -6666,27 +6666,27 @@
       </c>
       <c r="F71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>14429554.57921656</v>
+        <v>13786630.717428997</v>
       </c>
       <c r="G71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13727240.991854239</v>
+        <v>13044733.106628915</v>
       </c>
       <c r="H71" s="12">
         <f t="shared" si="5"/>
-        <v>-4.8671882663231303E-2</v>
+        <v>-5.3812829690301212E-2</v>
       </c>
       <c r="I71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>628</v>
+        <v>424</v>
       </c>
       <c r="J71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>439</v>
+        <v>269</v>
       </c>
       <c r="K71" s="12">
         <f t="shared" si="6"/>
-        <v>-0.30095541401273884</v>
+        <v>-0.36556603773584906</v>
       </c>
       <c r="L71" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6702,15 +6702,15 @@
       </c>
       <c r="O71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q71" s="12">
         <f t="shared" si="8"/>
-        <v>-0.33333333333333337</v>
+        <v>-1</v>
       </c>
       <c r="R71" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -6718,11 +6718,11 @@
       </c>
       <c r="S71">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>517</v>
+        <v>250</v>
       </c>
       <c r="T71" s="12">
         <f t="shared" si="9"/>
-        <v>4.0241448692152959E-2</v>
+        <v>-0.49698189134808857</v>
       </c>
       <c r="U71">
         <v>2</v>
@@ -6746,27 +6746,27 @@
       </c>
       <c r="F72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>22171799.827533696</v>
+        <v>21117188.467634171</v>
       </c>
       <c r="G72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22253625.293895539</v>
+        <v>21197941.625014752</v>
       </c>
       <c r="H72" s="12">
         <f t="shared" si="5"/>
-        <v>3.690519804361081E-3</v>
+        <v>3.8240487129406198E-3</v>
       </c>
       <c r="I72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>852</v>
+        <v>761</v>
       </c>
       <c r="J72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>788</v>
+        <v>1722</v>
       </c>
       <c r="K72" s="12">
         <f t="shared" si="6"/>
-        <v>-7.5117370892018753E-2</v>
+        <v>1.2628120893561103</v>
       </c>
       <c r="L72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6774,11 +6774,11 @@
       </c>
       <c r="M72" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N72" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -6786,23 +6786,23 @@
       </c>
       <c r="P72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Q72" s="12">
         <f t="shared" si="8"/>
-        <v>-0.19999999999999996</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="R72" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="S72">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>882</v>
+        <v>1669</v>
       </c>
       <c r="T72" s="12">
         <f t="shared" si="9"/>
-        <v>-7.8740157480314821E-3</v>
+        <v>0.87528089887640448</v>
       </c>
       <c r="U72">
         <v>3</v>
@@ -6826,27 +6826,27 @@
       </c>
       <c r="F73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15045724.399837304</v>
+        <v>14736341.28762248</v>
       </c>
       <c r="G73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>22077326.343890451</v>
+        <v>20935184.704319578</v>
       </c>
       <c r="H73" s="12">
         <f t="shared" si="5"/>
-        <v>0.46734884656860931</v>
+        <v>0.4206500986716224</v>
       </c>
       <c r="I73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>633</v>
+        <v>173</v>
       </c>
       <c r="J73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>470</v>
+        <v>578</v>
       </c>
       <c r="K73" s="12">
         <f t="shared" si="6"/>
-        <v>-0.25750394944707744</v>
+        <v>2.3410404624277459</v>
       </c>
       <c r="L73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6854,11 +6854,11 @@
       </c>
       <c r="M73" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N73" s="12">
         <f t="shared" si="7"/>
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="O73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -6866,23 +6866,23 @@
       </c>
       <c r="P73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q73" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R73" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="S73">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>646</v>
+        <v>762</v>
       </c>
       <c r="T73" s="12">
         <f t="shared" si="9"/>
-        <v>-3.4379671150971625E-2</v>
+        <v>0.14414414414414423</v>
       </c>
       <c r="U73">
         <v>7</v>
@@ -6906,27 +6906,27 @@
       </c>
       <c r="F74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13803246.696355209</v>
+        <v>13803241.814353952</v>
       </c>
       <c r="G74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16036060.553102637</v>
+        <v>15506233.992221871</v>
       </c>
       <c r="H74" s="12">
         <f t="shared" si="5"/>
-        <v>0.16176004862225701</v>
+        <v>0.12337624746217091</v>
       </c>
       <c r="I74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>513</v>
+        <v>815</v>
       </c>
       <c r="K74" s="12">
         <f t="shared" si="6"/>
-        <v>38.46153846153846</v>
+        <v>162</v>
       </c>
       <c r="L74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -6934,11 +6934,11 @@
       </c>
       <c r="M74" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N74" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -6946,23 +6946,23 @@
       </c>
       <c r="P74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="Q74" s="12">
         <f t="shared" si="8"/>
-        <v>0.19999999999999996</v>
+        <v>14.4</v>
       </c>
       <c r="R74" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="S74">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>621</v>
+        <v>1377</v>
       </c>
       <c r="T74" s="12">
         <f t="shared" si="9"/>
-        <v>4.8986486486486402E-2</v>
+        <v>1.3338983050847459</v>
       </c>
       <c r="U74">
         <v>2</v>
@@ -6986,27 +6986,27 @@
       </c>
       <c r="F75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17050229.600482032</v>
+        <v>16238993.027723324</v>
       </c>
       <c r="G75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>18475041.61702498</v>
+        <v>17523590.520165198</v>
       </c>
       <c r="H75" s="12">
         <f t="shared" si="5"/>
-        <v>8.3565561868015337E-2</v>
+        <v>7.9105735820490741E-2</v>
       </c>
       <c r="I75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>426</v>
+        <v>494</v>
       </c>
       <c r="J75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>499</v>
+        <v>1288</v>
       </c>
       <c r="K75" s="12">
         <f t="shared" si="6"/>
-        <v>0.17136150234741776</v>
+        <v>1.6072874493927127</v>
       </c>
       <c r="L75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7014,11 +7014,11 @@
       </c>
       <c r="M75" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N75" s="12">
         <f t="shared" si="7"/>
-        <v>0.16666666666666674</v>
+        <v>-0.16666666666666663</v>
       </c>
       <c r="O75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -7026,23 +7026,23 @@
       </c>
       <c r="P75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q75" s="12">
         <f t="shared" si="8"/>
-        <v>-0.66666666666666674</v>
+        <v>0.66666666666666674</v>
       </c>
       <c r="R75" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="S75">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>445</v>
+        <v>1260</v>
       </c>
       <c r="T75" s="12">
         <f t="shared" si="9"/>
-        <v>2.7713625866050862E-2</v>
+        <v>1.9508196721311477</v>
       </c>
       <c r="U75">
         <v>1</v>
@@ -7066,27 +7066,27 @@
       </c>
       <c r="F76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>49208948.078755222</v>
+        <v>46538332.60440968</v>
       </c>
       <c r="G76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>49281799.342978746</v>
+        <v>46909192.026860319</v>
       </c>
       <c r="H76" s="12">
         <f t="shared" si="5"/>
-        <v>1.4804475012741847E-3</v>
+        <v>7.9689022295461598E-3</v>
       </c>
       <c r="I76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>788</v>
+        <v>644</v>
       </c>
       <c r="J76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>610</v>
+        <v>1222</v>
       </c>
       <c r="K76" s="12">
         <f t="shared" si="6"/>
-        <v>-0.2258883248730964</v>
+        <v>0.89751552795031064</v>
       </c>
       <c r="L76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7094,11 +7094,11 @@
       </c>
       <c r="M76" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N76" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.66666666666666674</v>
       </c>
       <c r="O76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -7106,23 +7106,23 @@
       </c>
       <c r="P76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q76" s="12">
         <f t="shared" si="8"/>
-        <v>-0.27272727272727271</v>
+        <v>0.18181818181818188</v>
       </c>
       <c r="R76" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>952</v>
+        <v>939</v>
       </c>
       <c r="S76">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>896</v>
+        <v>1723</v>
       </c>
       <c r="T76" s="12">
         <f t="shared" si="9"/>
-        <v>-5.8823529411764719E-2</v>
+        <v>0.83493077742279009</v>
       </c>
       <c r="U76">
         <v>4</v>
@@ -7146,39 +7146,39 @@
       </c>
       <c r="F77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>29405507.483340576</v>
+        <v>27857525.216046929</v>
       </c>
       <c r="G77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>28529057.216889117</v>
+        <v>27265674.916935232</v>
       </c>
       <c r="H77" s="12">
         <f t="shared" si="5"/>
-        <v>-2.9805650079258283E-2</v>
+        <v>-2.1245616562190928E-2</v>
       </c>
       <c r="I77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>744</v>
+        <v>787</v>
       </c>
       <c r="J77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>724</v>
+        <v>458</v>
       </c>
       <c r="K77" s="12">
         <f t="shared" si="6"/>
-        <v>-2.6881720430107503E-2</v>
+        <v>-0.4180432020330368</v>
       </c>
       <c r="L77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M77" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N77" s="12">
         <f t="shared" si="7"/>
-        <v>0.11111111111111116</v>
+        <v>-0.9</v>
       </c>
       <c r="O77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -7186,23 +7186,23 @@
       </c>
       <c r="P77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q77" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="R77" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>786</v>
+        <v>802</v>
       </c>
       <c r="S77">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>774</v>
+        <v>512</v>
       </c>
       <c r="T77" s="12">
         <f t="shared" si="9"/>
-        <v>-1.5267175572519109E-2</v>
+        <v>-0.36159600997506236</v>
       </c>
       <c r="U77">
         <v>3</v>
@@ -7226,27 +7226,27 @@
       </c>
       <c r="F78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>23976905.020967472</v>
+        <v>22505847.82083239</v>
       </c>
       <c r="G78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>24304206.202539802</v>
+        <v>22856536.852877505</v>
       </c>
       <c r="H78" s="12">
         <f t="shared" si="5"/>
-        <v>1.3650685160829124E-2</v>
+        <v>1.5582129357530894E-2</v>
       </c>
       <c r="I78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1049</v>
+        <v>978</v>
       </c>
       <c r="J78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1171</v>
+        <v>774</v>
       </c>
       <c r="K78" s="12">
         <f t="shared" si="6"/>
-        <v>0.11630123927550051</v>
+        <v>-0.20858895705521474</v>
       </c>
       <c r="L78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7254,11 +7254,11 @@
       </c>
       <c r="M78" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N78" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="O78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -7266,23 +7266,23 @@
       </c>
       <c r="P78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q78" s="12">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R78" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="S78">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>960</v>
+        <v>876</v>
       </c>
       <c r="T78" s="12">
         <f t="shared" si="9"/>
-        <v>9.4637223974762819E-3</v>
+        <v>-7.9831932773109293E-2</v>
       </c>
       <c r="U78">
         <v>3</v>
@@ -7306,27 +7306,27 @@
       </c>
       <c r="F79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>27051046.84657656</v>
+        <v>25689391.598872714</v>
       </c>
       <c r="G79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>25200040.858496305</v>
+        <v>23804512.005560592</v>
       </c>
       <c r="H79" s="12">
         <f t="shared" si="5"/>
-        <v>-6.8426408729335697E-2</v>
+        <v>-7.3371904743545269E-2</v>
       </c>
       <c r="I79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>818</v>
+        <v>836</v>
       </c>
       <c r="J79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>828</v>
+        <v>480</v>
       </c>
       <c r="K79" s="12">
         <f t="shared" si="6"/>
-        <v>1.2224938875305513E-2</v>
+        <v>-0.42583732057416268</v>
       </c>
       <c r="L79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7334,35 +7334,35 @@
       </c>
       <c r="M79" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N79" s="12">
         <f t="shared" si="7"/>
-        <v>0.25</v>
+        <v>-0.25</v>
       </c>
       <c r="O79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q79" s="12">
         <f t="shared" si="8"/>
-        <v>-0.5</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="R79" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="S79">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>991</v>
+        <v>652</v>
       </c>
       <c r="T79" s="12">
         <f t="shared" si="9"/>
-        <v>-2.4606299212598381E-2</v>
+        <v>-0.35445544554455444</v>
       </c>
       <c r="U79">
         <v>3</v>
@@ -7386,27 +7386,27 @@
       </c>
       <c r="F80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>29446746.70471419</v>
+        <v>27707878.138874147</v>
       </c>
       <c r="G80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>32219102.200047638</v>
+        <v>30321505.756113347</v>
       </c>
       <c r="H80" s="12">
         <f t="shared" si="5"/>
-        <v>9.4148108214942905E-2</v>
+        <v>9.4327959872621214E-2</v>
       </c>
       <c r="I80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>756</v>
+        <v>683</v>
       </c>
       <c r="J80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>772</v>
+        <v>542</v>
       </c>
       <c r="K80" s="12">
         <f t="shared" si="6"/>
-        <v>2.1164021164021163E-2</v>
+        <v>-0.20644216691068817</v>
       </c>
       <c r="L80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7414,35 +7414,35 @@
       </c>
       <c r="M80" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N80" s="12">
         <f t="shared" si="7"/>
-        <v>0.19999999999999996</v>
+        <v>-0.8</v>
       </c>
       <c r="O80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q80" s="12">
         <f t="shared" si="8"/>
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="R80" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>755</v>
+        <v>743</v>
       </c>
       <c r="S80">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>756</v>
+        <v>620</v>
       </c>
       <c r="T80" s="12">
         <f t="shared" si="9"/>
-        <v>1.3245033112583293E-3</v>
+        <v>-0.16554508748317631</v>
       </c>
       <c r="U80">
         <v>3</v>
@@ -7466,27 +7466,27 @@
       </c>
       <c r="F81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12890849.296891289</v>
+        <v>12297623.509624189</v>
       </c>
       <c r="G81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14575510.609984348</v>
+        <v>13851013.837541368</v>
       </c>
       <c r="H81" s="12">
         <f t="shared" si="5"/>
-        <v>0.13068660367469542</v>
+        <v>0.12631630222713253</v>
       </c>
       <c r="I81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>679</v>
+        <v>566</v>
       </c>
       <c r="J81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>589</v>
+        <v>464</v>
       </c>
       <c r="K81" s="12">
         <f t="shared" si="6"/>
-        <v>-0.13254786450662737</v>
+        <v>-0.18021201413427557</v>
       </c>
       <c r="L81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7494,11 +7494,11 @@
       </c>
       <c r="M81" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N81" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -7506,23 +7506,23 @@
       </c>
       <c r="P81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q81" s="12">
         <f t="shared" si="8"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R81" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="S81">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>568</v>
+        <v>447</v>
       </c>
       <c r="T81" s="12">
         <f t="shared" si="9"/>
-        <v>1.7636684303350414E-3</v>
+        <v>-0.2130281690140845</v>
       </c>
       <c r="U81">
         <v>1</v>
@@ -7546,27 +7546,27 @@
       </c>
       <c r="F82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>55870676.347908162</v>
+        <v>52982781.551008649</v>
       </c>
       <c r="G82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>60561873.35205964</v>
+        <v>56341564.403701298</v>
       </c>
       <c r="H82" s="12">
         <f t="shared" si="5"/>
-        <v>8.3965280372467088E-2</v>
+        <v>6.3393856539204485E-2</v>
       </c>
       <c r="I82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1385</v>
+        <v>1265</v>
       </c>
       <c r="J82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1394</v>
+        <v>550</v>
       </c>
       <c r="K82" s="12">
         <f t="shared" si="6"/>
-        <v>6.4981949458484678E-3</v>
+        <v>-0.56521739130434789</v>
       </c>
       <c r="L82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7574,11 +7574,11 @@
       </c>
       <c r="M82" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N82" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="O82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -7586,23 +7586,23 @@
       </c>
       <c r="P82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q82" s="12">
         <f t="shared" si="8"/>
-        <v>-0.30000000000000004</v>
+        <v>-9.9999999999999978E-2</v>
       </c>
       <c r="R82" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1696</v>
+        <v>1702</v>
       </c>
       <c r="S82">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1768</v>
+        <v>900</v>
       </c>
       <c r="T82" s="12">
         <f t="shared" si="9"/>
-        <v>4.2452830188679291E-2</v>
+        <v>-0.47121034077555812</v>
       </c>
       <c r="U82">
         <v>2</v>
@@ -7626,27 +7626,27 @@
       </c>
       <c r="F83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15216982.418813448</v>
+        <v>14099053.264334928</v>
       </c>
       <c r="G83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13821141.409075508</v>
+        <v>13251615.22394882</v>
       </c>
       <c r="H83" s="12">
         <f t="shared" si="5"/>
-        <v>-9.1729159653375025E-2</v>
+        <v>-6.010602446121649E-2</v>
       </c>
       <c r="I83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="J83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>648</v>
+        <v>709</v>
       </c>
       <c r="K83" s="12">
         <f t="shared" si="6"/>
-        <v>-0.28239202657807305</v>
+        <v>-0.21309655937846839</v>
       </c>
       <c r="L83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7654,35 +7654,35 @@
       </c>
       <c r="M83" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N83" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="O83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q83" s="12">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.33333333333333337</v>
       </c>
       <c r="R83" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>600</v>
+        <v>624</v>
       </c>
       <c r="S83">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>566</v>
+        <v>769</v>
       </c>
       <c r="T83" s="12">
         <f t="shared" si="9"/>
-        <v>-5.6666666666666643E-2</v>
+        <v>0.23237179487179493</v>
       </c>
       <c r="U83">
         <v>2</v>
@@ -7706,27 +7706,27 @@
       </c>
       <c r="F84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>26078100.101177879</v>
+        <v>24761684.048804503</v>
       </c>
       <c r="G84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>27183832.475523256</v>
+        <v>25936117.318591543</v>
       </c>
       <c r="H84" s="12">
         <f t="shared" si="5"/>
-        <v>4.2400802591268327E-2</v>
+        <v>4.7429458653630574E-2</v>
       </c>
       <c r="I84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>521</v>
+        <v>501</v>
       </c>
       <c r="J84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>522</v>
+        <v>1026</v>
       </c>
       <c r="K84" s="12">
         <f t="shared" si="6"/>
-        <v>1.9193857965451588E-3</v>
+        <v>1.0479041916167664</v>
       </c>
       <c r="L84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7734,11 +7734,11 @@
       </c>
       <c r="M84" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N84" s="12">
         <f t="shared" si="7"/>
-        <v>0.16666666666666674</v>
+        <v>-0.66666666666666674</v>
       </c>
       <c r="O84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -7746,23 +7746,23 @@
       </c>
       <c r="P84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q84" s="12">
         <f t="shared" si="8"/>
-        <v>-0.69230769230769229</v>
+        <v>-0.76923076923076916</v>
       </c>
       <c r="R84" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="S84">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>632</v>
+        <v>954</v>
       </c>
       <c r="T84" s="12">
         <f t="shared" si="9"/>
-        <v>5.3333333333333233E-2</v>
+        <v>0.61694915254237293</v>
       </c>
       <c r="U84">
         <v>7</v>
@@ -7786,27 +7786,27 @@
       </c>
       <c r="F85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7162107.3929737266</v>
+        <v>6820595.096124053</v>
       </c>
       <c r="G85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6488168.8620083621</v>
+        <v>6214020.6016599154</v>
       </c>
       <c r="H85" s="12">
         <f t="shared" si="5"/>
-        <v>-9.4097797475994449E-2</v>
+        <v>-8.8932781658426885E-2</v>
       </c>
       <c r="I85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="J85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>304</v>
+        <v>892</v>
       </c>
       <c r="K85" s="12">
         <f t="shared" si="6"/>
-        <v>-7.3170731707317027E-2</v>
+        <v>1.8961038961038961</v>
       </c>
       <c r="L85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -7814,11 +7814,11 @@
       </c>
       <c r="M85" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N85" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -7826,23 +7826,23 @@
       </c>
       <c r="P85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q85" s="12">
         <f t="shared" si="8"/>
-        <v>-0.33333333333333337</v>
+        <v>0</v>
       </c>
       <c r="R85" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="S85">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>358</v>
+        <v>988</v>
       </c>
       <c r="T85" s="12">
         <f t="shared" si="9"/>
-        <v>-1.377410468319562E-2</v>
+        <v>1.7444444444444445</v>
       </c>
       <c r="U85">
         <v>2</v>
@@ -7875,11 +7875,11 @@
       <c r="A3" s="11"/>
       <c r="B3" s="11">
         <f t="shared" ref="B3:K3" si="0">SUBTOTAL(9,B6:B90)</f>
-        <v>84155</v>
+        <v>84119</v>
       </c>
       <c r="C3" s="11">
         <f t="shared" si="0"/>
-        <v>1484</v>
+        <v>1649</v>
       </c>
       <c r="D3" s="11">
         <f t="shared" si="0"/>
@@ -7887,31 +7887,31 @@
       </c>
       <c r="E3" s="11">
         <f t="shared" si="0"/>
-        <v>70150</v>
+        <v>70689</v>
       </c>
       <c r="F3" s="11">
         <f t="shared" si="0"/>
-        <v>2762661133.2590084</v>
+        <v>2612231633.0339432</v>
       </c>
       <c r="G3" s="11">
         <f t="shared" si="0"/>
-        <v>84561</v>
+        <v>83692</v>
       </c>
       <c r="H3" s="11">
         <f t="shared" si="0"/>
-        <v>1547</v>
+        <v>1733</v>
       </c>
       <c r="I3" s="11">
         <f t="shared" si="0"/>
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="J3" s="11">
         <f t="shared" si="0"/>
-        <v>70937</v>
+        <v>70354</v>
       </c>
       <c r="K3" s="11">
         <f t="shared" si="0"/>
-        <v>2842605836.7440019</v>
+        <v>2686502429.4066834</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -7971,7 +7971,7 @@
         <v>117</v>
       </c>
       <c r="B6" s="10">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="C6" s="10">
         <v>3</v>
@@ -7980,10 +7980,10 @@
         <v>2</v>
       </c>
       <c r="E6" s="10">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="F6" s="10">
-        <v>13087808.370799534</v>
+        <v>12452036.798173808</v>
       </c>
       <c r="G6" s="10">
         <v>414</v>
@@ -7998,7 +7998,7 @@
         <v>353</v>
       </c>
       <c r="K6" s="10">
-        <v>12916722.729567273</v>
+        <v>12287955.952436997</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
@@ -8006,7 +8006,7 @@
         <v>127</v>
       </c>
       <c r="B7" s="10">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="C7" s="10">
         <v>2</v>
@@ -8015,10 +8015,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="10">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="F7" s="10">
-        <v>15998166.242166299</v>
+        <v>15270377.5820772</v>
       </c>
       <c r="G7" s="10">
         <v>634</v>
@@ -8033,7 +8033,7 @@
         <v>500</v>
       </c>
       <c r="K7" s="10">
-        <v>15084594.410566358</v>
+        <v>14339947.092993161</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
@@ -8041,7 +8041,7 @@
         <v>119</v>
       </c>
       <c r="B8" s="10">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C8" s="10">
         <v>7</v>
@@ -8050,10 +8050,10 @@
         <v>2</v>
       </c>
       <c r="E8" s="10">
-        <v>912</v>
+        <v>809</v>
       </c>
       <c r="F8" s="10">
-        <v>18423447.133026849</v>
+        <v>17041117.995255239</v>
       </c>
       <c r="G8" s="10">
         <v>770</v>
@@ -8068,7 +8068,7 @@
         <v>788</v>
       </c>
       <c r="K8" s="10">
-        <v>21263351.156662799</v>
+        <v>19961475.905457538</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
@@ -8076,19 +8076,19 @@
         <v>121</v>
       </c>
       <c r="B9" s="10">
-        <v>1188</v>
+        <v>1193</v>
       </c>
       <c r="C9" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" s="10">
         <v>3</v>
       </c>
       <c r="E9" s="10">
-        <v>1484</v>
+        <v>1442</v>
       </c>
       <c r="F9" s="10">
-        <v>32444786.249515016</v>
+        <v>30428581.790787671</v>
       </c>
       <c r="G9" s="10">
         <v>1214</v>
@@ -8103,7 +8103,7 @@
         <v>1130</v>
       </c>
       <c r="K9" s="10">
-        <v>33059806.89004685</v>
+        <v>31260783.726436041</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
@@ -8111,19 +8111,19 @@
         <v>123</v>
       </c>
       <c r="B10" s="10">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C10" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="10">
         <v>1</v>
       </c>
       <c r="E10" s="10">
-        <v>425</v>
+        <v>333</v>
       </c>
       <c r="F10" s="10">
-        <v>13426816.547492765</v>
+        <v>12572009.692979235</v>
       </c>
       <c r="G10" s="10">
         <v>413</v>
@@ -8138,7 +8138,7 @@
         <v>377</v>
       </c>
       <c r="K10" s="10">
-        <v>14740995.052347932</v>
+        <v>14087321.867469653</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
@@ -8146,7 +8146,7 @@
         <v>125</v>
       </c>
       <c r="B11" s="10">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C11" s="10">
         <v>3</v>
@@ -8155,10 +8155,10 @@
         <v>2</v>
       </c>
       <c r="E11" s="10">
-        <v>359</v>
+        <v>328</v>
       </c>
       <c r="F11" s="10">
-        <v>11608508.537279077</v>
+        <v>10954941.459135331</v>
       </c>
       <c r="G11" s="10">
         <v>387</v>
@@ -8173,7 +8173,7 @@
         <v>268</v>
       </c>
       <c r="K11" s="10">
-        <v>12076791.011960519</v>
+        <v>11489847.967613995</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -8181,22 +8181,22 @@
         <v>131</v>
       </c>
       <c r="B12" s="10">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="C12" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="10">
         <v>1</v>
       </c>
       <c r="E12" s="10">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="F12" s="10">
-        <v>13234286.009974919</v>
+        <v>12590405.038448486</v>
       </c>
       <c r="G12" s="10">
-        <v>595</v>
+        <v>419</v>
       </c>
       <c r="H12" s="10">
         <v>3</v>
@@ -8205,10 +8205,10 @@
         <v>2</v>
       </c>
       <c r="J12" s="10">
-        <v>480</v>
+        <v>374</v>
       </c>
       <c r="K12" s="10">
-        <v>14483043.079303995</v>
+        <v>13775550.668594858</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
@@ -8219,31 +8219,31 @@
         <v>172</v>
       </c>
       <c r="C13" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="10">
         <v>1</v>
       </c>
       <c r="E13" s="10">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="F13" s="10">
-        <v>6272122.0239012884</v>
+        <v>5908394.1481695939</v>
       </c>
       <c r="G13" s="10">
-        <v>173</v>
+        <v>629</v>
       </c>
       <c r="H13" s="10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I13" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" s="10">
-        <v>151</v>
+        <v>500</v>
       </c>
       <c r="K13" s="10">
-        <v>6320873.6215354437</v>
+        <v>6045648.5828848016</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
@@ -8251,7 +8251,7 @@
         <v>141</v>
       </c>
       <c r="B14" s="10">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C14" s="10">
         <v>1</v>
@@ -8260,25 +8260,25 @@
         <v>0</v>
       </c>
       <c r="E14" s="10">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="F14" s="10">
-        <v>5986210.4536223654</v>
+        <v>5680298.6802293016</v>
       </c>
       <c r="G14" s="10">
-        <v>187</v>
+        <v>774</v>
       </c>
       <c r="H14" s="10">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I14" s="10">
         <v>1</v>
       </c>
       <c r="J14" s="10">
-        <v>163</v>
+        <v>757</v>
       </c>
       <c r="K14" s="10">
-        <v>3146674.465636583</v>
+        <v>2860659.9967147</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
@@ -8286,34 +8286,34 @@
         <v>135</v>
       </c>
       <c r="B15" s="10">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="C15" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="10">
         <v>1</v>
       </c>
       <c r="E15" s="10">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="F15" s="10">
-        <v>9371873.1319251489</v>
+        <v>8944383.1211307161</v>
       </c>
       <c r="G15" s="10">
-        <v>383</v>
+        <v>1210</v>
       </c>
       <c r="H15" s="10">
+        <v>9</v>
+      </c>
+      <c r="I15" s="10">
         <v>3</v>
       </c>
-      <c r="I15" s="10">
-        <v>1</v>
-      </c>
       <c r="J15" s="10">
-        <v>382</v>
+        <v>1155</v>
       </c>
       <c r="K15" s="10">
-        <v>12410426.942553291</v>
+        <v>11890504.003905904</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
@@ -8321,34 +8321,34 @@
         <v>143</v>
       </c>
       <c r="B16" s="10">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C16" s="10">
         <v>0</v>
       </c>
       <c r="D16" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="10">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="F16" s="10">
-        <v>4545722.9148001587</v>
+        <v>4262490.9429104608</v>
       </c>
       <c r="G16" s="10">
-        <v>226</v>
+        <v>410</v>
       </c>
       <c r="H16" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" s="10">
-        <v>257</v>
+        <v>374</v>
       </c>
       <c r="K16" s="10">
-        <v>6532815.7132673627</v>
+        <v>6152814.3065978391</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -8365,25 +8365,25 @@
         <v>1</v>
       </c>
       <c r="E17" s="10">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="F17" s="10">
-        <v>6093279.5223717354</v>
+        <v>5733341.8539821506</v>
       </c>
       <c r="G17" s="10">
-        <v>239</v>
+        <v>390</v>
       </c>
       <c r="H17" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" s="10">
-        <v>230</v>
+        <v>322</v>
       </c>
       <c r="K17" s="10">
-        <v>6845794.9533302337</v>
+        <v>6544098.7908061044</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
@@ -8391,7 +8391,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="10">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="C18" s="10">
         <v>0</v>
@@ -8400,25 +8400,25 @@
         <v>2</v>
       </c>
       <c r="E18" s="10">
-        <v>1494</v>
+        <v>1199</v>
       </c>
       <c r="F18" s="10">
-        <v>13443706.666459411</v>
+        <v>12150068.330912439</v>
       </c>
       <c r="G18" s="10">
-        <v>1384</v>
+        <v>615</v>
       </c>
       <c r="H18" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I18" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J18" s="10">
-        <v>1076</v>
+        <v>529</v>
       </c>
       <c r="K18" s="10">
-        <v>29022560.368282694</v>
+        <v>27129953.922294252</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
@@ -8426,34 +8426,34 @@
         <v>45</v>
       </c>
       <c r="B19" s="10">
-        <v>1269</v>
+        <v>1259</v>
       </c>
       <c r="C19" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="10">
         <v>2</v>
       </c>
       <c r="E19" s="10">
-        <v>181</v>
+        <v>996</v>
       </c>
       <c r="F19" s="10">
-        <v>37942760.593333475</v>
+        <v>37115893.490185946</v>
       </c>
       <c r="G19" s="10">
-        <v>1234</v>
+        <v>176</v>
       </c>
       <c r="H19" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I19" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J19" s="10">
-        <v>901</v>
+        <v>150</v>
       </c>
       <c r="K19" s="10">
-        <v>49024095.31867002</v>
+        <v>46248297.021251909</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
@@ -8461,7 +8461,7 @@
         <v>47</v>
       </c>
       <c r="B20" s="10">
-        <v>1018</v>
+        <v>1028</v>
       </c>
       <c r="C20" s="10">
         <v>4</v>
@@ -8470,25 +8470,25 @@
         <v>4</v>
       </c>
       <c r="E20" s="10">
-        <v>922</v>
+        <v>1758</v>
       </c>
       <c r="F20" s="10">
-        <v>25808105.930136997</v>
+        <v>24557779.647644848</v>
       </c>
       <c r="G20" s="10">
-        <v>1021</v>
+        <v>199</v>
       </c>
       <c r="H20" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I20" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J20" s="10">
-        <v>859</v>
+        <v>186</v>
       </c>
       <c r="K20" s="10">
-        <v>26071080.14117502</v>
+        <v>24780324.33078628</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
@@ -8496,7 +8496,7 @@
         <v>49</v>
       </c>
       <c r="B21" s="10">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="C21" s="10">
         <v>1</v>
@@ -8505,25 +8505,25 @@
         <v>3</v>
       </c>
       <c r="E21" s="10">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="F21" s="10">
-        <v>25100221.83684345</v>
+        <v>24093521.100269504</v>
       </c>
       <c r="G21" s="10">
-        <v>917</v>
+        <v>387</v>
       </c>
       <c r="H21" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I21" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J21" s="10">
-        <v>664</v>
+        <v>431</v>
       </c>
       <c r="K21" s="10">
-        <v>21493879.316390663</v>
+        <v>20292128.333114807</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
@@ -8531,34 +8531,34 @@
         <v>51</v>
       </c>
       <c r="B22" s="10">
-        <v>3188</v>
+        <v>3177</v>
       </c>
       <c r="C22" s="10">
-        <v>625</v>
+        <v>695</v>
       </c>
       <c r="D22" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E22" s="10">
-        <v>2699</v>
+        <v>2465</v>
       </c>
       <c r="F22" s="10">
-        <v>89403755.644768402</v>
+        <v>84378043.245911941</v>
       </c>
       <c r="G22" s="10">
-        <v>2806</v>
+        <v>226</v>
       </c>
       <c r="H22" s="10">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="I22" s="10">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J22" s="10">
-        <v>2125</v>
+        <v>263</v>
       </c>
       <c r="K22" s="10">
-        <v>95903548.545516953</v>
+        <v>91431790.086039543</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
@@ -8566,34 +8566,34 @@
         <v>53</v>
       </c>
       <c r="B23" s="10">
-        <v>1441</v>
+        <v>1435</v>
       </c>
       <c r="C23" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" s="10">
         <v>2</v>
       </c>
       <c r="E23" s="10">
-        <v>1203</v>
+        <v>1195</v>
       </c>
       <c r="F23" s="10">
-        <v>48127649.671235926</v>
+        <v>45853440.719571456</v>
       </c>
       <c r="G23" s="10">
-        <v>1387</v>
+        <v>239</v>
       </c>
       <c r="H23" s="10">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I23" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J23" s="10">
-        <v>1172</v>
+        <v>231</v>
       </c>
       <c r="K23" s="10">
-        <v>30944501.324133508</v>
+        <v>28580704.230768949</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
@@ -8601,34 +8601,34 @@
         <v>55</v>
       </c>
       <c r="B24" s="10">
-        <v>3014</v>
+        <v>3011</v>
       </c>
       <c r="C24" s="10">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D24" s="10">
         <v>11</v>
       </c>
       <c r="E24" s="10">
-        <v>2319</v>
+        <v>2257</v>
       </c>
       <c r="F24" s="10">
-        <v>96839659.029765069</v>
+        <v>91985409.680114254</v>
       </c>
       <c r="G24" s="10">
-        <v>2929</v>
+        <v>1386</v>
       </c>
       <c r="H24" s="10">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="I24" s="10">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J24" s="10">
-        <v>2118</v>
+        <v>1040</v>
       </c>
       <c r="K24" s="10">
-        <v>96555492.863442063</v>
+        <v>91798677.850888729</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
@@ -8636,7 +8636,7 @@
         <v>67</v>
       </c>
       <c r="B25" s="10">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="C25" s="10">
         <v>6</v>
@@ -8645,25 +8645,25 @@
         <v>1</v>
       </c>
       <c r="E25" s="10">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F25" s="10">
-        <v>13858968.280016633</v>
+        <v>13083985.836379612</v>
       </c>
       <c r="G25" s="10">
-        <v>539</v>
+        <v>1233</v>
       </c>
       <c r="H25" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I25" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J25" s="10">
-        <v>451</v>
+        <v>893</v>
       </c>
       <c r="K25" s="10">
-        <v>14656128.885179391</v>
+        <v>13952390.293539824</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
@@ -8671,34 +8671,34 @@
         <v>74</v>
       </c>
       <c r="B26" s="10">
-        <v>1712</v>
+        <v>1731</v>
       </c>
       <c r="C26" s="10">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D26" s="10">
         <v>1</v>
       </c>
       <c r="E26" s="10">
-        <v>1285</v>
+        <v>1297</v>
       </c>
       <c r="F26" s="10">
-        <v>38076981.426078215</v>
+        <v>36202793.63631741</v>
       </c>
       <c r="G26" s="10">
-        <v>1657</v>
+        <v>1017</v>
       </c>
       <c r="H26" s="10">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I26" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J26" s="10">
-        <v>1351</v>
+        <v>904</v>
       </c>
       <c r="K26" s="10">
-        <v>40696450.341174901</v>
+        <v>38550165.164171152</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
@@ -8706,34 +8706,34 @@
         <v>70</v>
       </c>
       <c r="B27" s="10">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="C27" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D27" s="10">
         <v>1</v>
       </c>
       <c r="E27" s="10">
+        <v>743</v>
+      </c>
+      <c r="F27" s="10">
+        <v>15994034.782365471</v>
+      </c>
+      <c r="G27" s="10">
         <v>919</v>
       </c>
-      <c r="F27" s="10">
-        <v>16999705.014675111</v>
-      </c>
-      <c r="G27" s="10">
-        <v>864</v>
-      </c>
       <c r="H27" s="10">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I27" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J27" s="10">
-        <v>775</v>
+        <v>673</v>
       </c>
       <c r="K27" s="10">
-        <v>16848952.521488499</v>
+        <v>16023991.278544333</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
@@ -8741,34 +8741,34 @@
         <v>72</v>
       </c>
       <c r="B28" s="10">
-        <v>886</v>
+        <v>897</v>
       </c>
       <c r="C28" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D28" s="10">
         <v>1</v>
       </c>
       <c r="E28" s="10">
-        <v>870</v>
+        <v>920</v>
       </c>
       <c r="F28" s="10">
-        <v>18823380.21238241</v>
+        <v>17730094.775826979</v>
       </c>
       <c r="G28" s="10">
-        <v>878</v>
+        <v>2788</v>
       </c>
       <c r="H28" s="10">
-        <v>6</v>
+        <v>186</v>
       </c>
       <c r="I28" s="10">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J28" s="10">
-        <v>678</v>
+        <v>2089</v>
       </c>
       <c r="K28" s="10">
-        <v>20465850.794823397</v>
+        <v>19429198.640231583</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
@@ -8776,7 +8776,7 @@
         <v>79</v>
       </c>
       <c r="B29" s="10">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C29" s="10">
         <v>1</v>
@@ -8785,25 +8785,25 @@
         <v>0</v>
       </c>
       <c r="E29" s="10">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="F29" s="10">
-        <v>5565632.8976637917</v>
+        <v>5277024.5563090751</v>
       </c>
       <c r="G29" s="10">
-        <v>228</v>
+        <v>1379</v>
       </c>
       <c r="H29" s="10">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I29" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="10">
-        <v>185</v>
+        <v>1195</v>
       </c>
       <c r="K29" s="10">
-        <v>4723558.2871565996</v>
+        <v>4433708.8725122856</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
@@ -8811,7 +8811,7 @@
         <v>109</v>
       </c>
       <c r="B30" s="10">
-        <v>1649</v>
+        <v>1653</v>
       </c>
       <c r="C30" s="10">
         <v>4</v>
@@ -8820,25 +8820,25 @@
         <v>5</v>
       </c>
       <c r="E30" s="10">
-        <v>1388</v>
+        <v>1323</v>
       </c>
       <c r="F30" s="10">
-        <v>42168566.16250097</v>
+        <v>40235450.07087151</v>
       </c>
       <c r="G30" s="10">
-        <v>1653</v>
+        <v>2920</v>
       </c>
       <c r="H30" s="10">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="I30" s="10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J30" s="10">
-        <v>1322</v>
+        <v>2088</v>
       </c>
       <c r="K30" s="10">
-        <v>38683079.315449901</v>
+        <v>36803930.469524823</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
@@ -8846,34 +8846,34 @@
         <v>111</v>
       </c>
       <c r="B31" s="10">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C31" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D31" s="10">
         <v>1</v>
       </c>
       <c r="E31" s="10">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="F31" s="10">
-        <v>29823023.385615569</v>
+        <v>28301686.739777543</v>
       </c>
       <c r="G31" s="10">
-        <v>884</v>
+        <v>537</v>
       </c>
       <c r="H31" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I31" s="10">
         <v>1</v>
       </c>
       <c r="J31" s="10">
-        <v>618</v>
+        <v>485</v>
       </c>
       <c r="K31" s="10">
-        <v>32617935.380541101</v>
+        <v>30880741.730442863</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
@@ -8881,7 +8881,7 @@
         <v>113</v>
       </c>
       <c r="B32" s="10">
-        <v>1120</v>
+        <v>1115</v>
       </c>
       <c r="C32" s="10">
         <v>2</v>
@@ -8890,25 +8890,25 @@
         <v>1</v>
       </c>
       <c r="E32" s="10">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="F32" s="10">
-        <v>32601221.645448308</v>
+        <v>30771914.979088616</v>
       </c>
       <c r="G32" s="10">
-        <v>1042</v>
+        <v>1671</v>
       </c>
       <c r="H32" s="10">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="I32" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J32" s="10">
-        <v>764</v>
+        <v>1300</v>
       </c>
       <c r="K32" s="10">
-        <v>30351804.513628267</v>
+        <v>29013524.004899658</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
@@ -8925,25 +8925,25 @@
         <v>2</v>
       </c>
       <c r="E33" s="10">
-        <v>952</v>
+        <v>915</v>
       </c>
       <c r="F33" s="10">
-        <v>41893976.926671989</v>
+        <v>39627788.142400511</v>
       </c>
       <c r="G33" s="10">
-        <v>1126</v>
+        <v>872</v>
       </c>
       <c r="H33" s="10">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I33" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J33" s="10">
-        <v>900</v>
+        <v>954</v>
       </c>
       <c r="K33" s="10">
-        <v>43282975.098104343</v>
+        <v>41174058.474659473</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
@@ -8951,7 +8951,7 @@
         <v>16</v>
       </c>
       <c r="B34" s="10">
-        <v>1504</v>
+        <v>1507</v>
       </c>
       <c r="C34" s="10">
         <v>3</v>
@@ -8960,25 +8960,25 @@
         <v>5</v>
       </c>
       <c r="E34" s="10">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="F34" s="10">
-        <v>60948510.020695314</v>
+        <v>57867671.527397662</v>
       </c>
       <c r="G34" s="10">
-        <v>1456</v>
+        <v>872</v>
       </c>
       <c r="H34" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I34" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J34" s="10">
-        <v>1151</v>
+        <v>684</v>
       </c>
       <c r="K34" s="10">
-        <v>55959396.977800012</v>
+        <v>52940271.569831714</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
@@ -8986,7 +8986,7 @@
         <v>18</v>
       </c>
       <c r="B35" s="10">
-        <v>696</v>
+        <v>705</v>
       </c>
       <c r="C35" s="10">
         <v>3</v>
@@ -8995,25 +8995,25 @@
         <v>3</v>
       </c>
       <c r="E35" s="10">
-        <v>615</v>
+        <v>604</v>
       </c>
       <c r="F35" s="10">
-        <v>23188488.13637552</v>
+        <v>21899406.198145673</v>
       </c>
       <c r="G35" s="10">
-        <v>698</v>
+        <v>229</v>
       </c>
       <c r="H35" s="10">
         <v>1</v>
       </c>
       <c r="I35" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J35" s="10">
-        <v>508</v>
+        <v>177</v>
       </c>
       <c r="K35" s="10">
-        <v>25047854.91353824</v>
+        <v>23896792.324472841</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
@@ -9021,7 +9021,7 @@
         <v>43</v>
       </c>
       <c r="B36" s="10">
-        <v>1967</v>
+        <v>1958</v>
       </c>
       <c r="C36" s="10">
         <v>17</v>
@@ -9030,25 +9030,25 @@
         <v>11</v>
       </c>
       <c r="E36" s="10">
-        <v>2045</v>
+        <v>1677</v>
       </c>
       <c r="F36" s="10">
-        <v>72283101.544206813</v>
+        <v>68379291.574158043</v>
       </c>
       <c r="G36" s="10">
-        <v>1913</v>
+        <v>1638</v>
       </c>
       <c r="H36" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I36" s="10">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J36" s="10">
-        <v>1572</v>
+        <v>1317</v>
       </c>
       <c r="K36" s="10">
-        <v>62386024.992774226</v>
+        <v>58685299.940138116</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
@@ -9056,7 +9056,7 @@
         <v>152</v>
       </c>
       <c r="B37" s="10">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="C37" s="10">
         <v>2</v>
@@ -9065,25 +9065,25 @@
         <v>2</v>
       </c>
       <c r="E37" s="10">
-        <v>693</v>
+        <v>707</v>
       </c>
       <c r="F37" s="10">
-        <v>24522885.913414594</v>
+        <v>23416239.072707906</v>
       </c>
       <c r="G37" s="10">
-        <v>860</v>
+        <v>884</v>
       </c>
       <c r="H37" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I37" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J37" s="10">
-        <v>741</v>
+        <v>631</v>
       </c>
       <c r="K37" s="10">
-        <v>24921846.100234803</v>
+        <v>23846332.143704496</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
@@ -9091,34 +9091,34 @@
         <v>149</v>
       </c>
       <c r="B38" s="10">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="C38" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D38" s="10">
         <v>1</v>
       </c>
       <c r="E38" s="10">
-        <v>582</v>
+        <v>592</v>
       </c>
       <c r="F38" s="10">
-        <v>20703555.59535294</v>
+        <v>19580984.263010703</v>
       </c>
       <c r="G38" s="10">
-        <v>758</v>
+        <v>1039</v>
       </c>
       <c r="H38" s="10">
         <v>3</v>
       </c>
       <c r="I38" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J38" s="10">
-        <v>609</v>
+        <v>1418</v>
       </c>
       <c r="K38" s="10">
-        <v>23049754.684711441</v>
+        <v>21933834.462986201</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
@@ -9126,34 +9126,34 @@
         <v>154</v>
       </c>
       <c r="B39" s="10">
-        <v>1108</v>
+        <v>1124</v>
       </c>
       <c r="C39" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D39" s="10">
         <v>2</v>
       </c>
       <c r="E39" s="10">
-        <v>865</v>
+        <v>993</v>
       </c>
       <c r="F39" s="10">
-        <v>36053259.761528894</v>
+        <v>34271546.343865938</v>
       </c>
       <c r="G39" s="10">
-        <v>1151</v>
+        <v>1130</v>
       </c>
       <c r="H39" s="10">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="I39" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J39" s="10">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="K39" s="10">
-        <v>35754529.012632072</v>
+        <v>33947334.926795498</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
@@ -9161,7 +9161,7 @@
         <v>2</v>
       </c>
       <c r="B40" s="10">
-        <v>1085</v>
+        <v>1093</v>
       </c>
       <c r="C40" s="10">
         <v>41</v>
@@ -9170,25 +9170,25 @@
         <v>1</v>
       </c>
       <c r="E40" s="10">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="F40" s="10">
-        <v>34761818.863370262</v>
+        <v>33052464.113899976</v>
       </c>
       <c r="G40" s="10">
-        <v>1381</v>
+        <v>1460</v>
       </c>
       <c r="H40" s="10">
-        <v>272</v>
+        <v>5</v>
       </c>
       <c r="I40" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J40" s="10">
-        <v>876</v>
+        <v>1129</v>
       </c>
       <c r="K40" s="10">
-        <v>33981946.736486293</v>
+        <v>32190582.015026674</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
@@ -9196,7 +9196,7 @@
         <v>156</v>
       </c>
       <c r="B41" s="10">
-        <v>1795</v>
+        <v>1791</v>
       </c>
       <c r="C41" s="10">
         <v>57</v>
@@ -9205,25 +9205,25 @@
         <v>4</v>
       </c>
       <c r="E41" s="10">
-        <v>1385</v>
+        <v>1425</v>
       </c>
       <c r="F41" s="10">
-        <v>54910655.209512085</v>
+        <v>52158232.747112714</v>
       </c>
       <c r="G41" s="10">
-        <v>2277</v>
+        <v>696</v>
       </c>
       <c r="H41" s="10">
-        <v>123</v>
+        <v>1</v>
       </c>
       <c r="I41" s="10">
         <v>5</v>
       </c>
       <c r="J41" s="10">
-        <v>1310</v>
+        <v>827</v>
       </c>
       <c r="K41" s="10">
-        <v>60889043.762123182</v>
+        <v>57989157.172912218</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
@@ -9231,7 +9231,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="10">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="C42" s="10">
         <v>2</v>
@@ -9240,25 +9240,25 @@
         <v>4</v>
       </c>
       <c r="E42" s="10">
-        <v>5</v>
+        <v>443</v>
       </c>
       <c r="F42" s="10">
         <v>17501175.59762124</v>
       </c>
       <c r="G42" s="10">
-        <v>619</v>
+        <v>1909</v>
       </c>
       <c r="H42" s="10">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I42" s="10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J42" s="10">
-        <v>454</v>
+        <v>1560</v>
       </c>
       <c r="K42" s="10">
-        <v>21690653.82312274</v>
+        <v>20656820.414189544</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
@@ -9266,7 +9266,7 @@
         <v>8</v>
       </c>
       <c r="B43" s="10">
-        <v>2048</v>
+        <v>2055</v>
       </c>
       <c r="C43" s="10">
         <v>14</v>
@@ -9275,25 +9275,25 @@
         <v>5</v>
       </c>
       <c r="E43" s="10">
-        <v>1854</v>
+        <v>2056</v>
       </c>
       <c r="F43" s="10">
-        <v>63981776.356715463</v>
+        <v>61288523.598765254</v>
       </c>
       <c r="G43" s="10">
-        <v>2066</v>
+        <v>866</v>
       </c>
       <c r="H43" s="10">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I43" s="10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J43" s="10">
-        <v>1948</v>
+        <v>601</v>
       </c>
       <c r="K43" s="10">
-        <v>70387346.462206155</v>
+        <v>66763112.972614646</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.35">
@@ -9301,34 +9301,34 @@
         <v>39</v>
       </c>
       <c r="B44" s="10">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="C44" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D44" s="10">
         <v>4</v>
       </c>
       <c r="E44" s="10">
-        <v>783</v>
+        <v>793</v>
       </c>
       <c r="F44" s="10">
-        <v>45081578.612316735</v>
+        <v>42805016.573299475</v>
       </c>
       <c r="G44" s="10">
-        <v>893</v>
+        <v>754</v>
       </c>
       <c r="H44" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I44" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J44" s="10">
-        <v>838</v>
+        <v>507</v>
       </c>
       <c r="K44" s="10">
-        <v>48694697.570638672</v>
+        <v>46227650.783002853</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.35">
@@ -9336,7 +9336,7 @@
         <v>6</v>
       </c>
       <c r="B45" s="10">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="C45" s="10">
         <v>3</v>
@@ -9345,25 +9345,25 @@
         <v>3</v>
       </c>
       <c r="E45" s="10">
-        <v>935</v>
+        <v>954</v>
       </c>
       <c r="F45" s="10">
-        <v>36951327.241868146</v>
+        <v>35305267.70624648</v>
       </c>
       <c r="G45" s="10">
-        <v>1098</v>
+        <v>1146</v>
       </c>
       <c r="H45" s="10">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="I45" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J45" s="10">
-        <v>1035</v>
+        <v>822</v>
       </c>
       <c r="K45" s="10">
-        <v>28817713.877122149</v>
+        <v>27034432.239690185</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
@@ -9371,7 +9371,7 @@
         <v>41</v>
       </c>
       <c r="B46" s="10">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C46" s="10">
         <v>0</v>
@@ -9380,25 +9380,25 @@
         <v>5</v>
       </c>
       <c r="E46" s="10">
-        <v>646</v>
+        <v>621</v>
       </c>
       <c r="F46" s="10">
-        <v>36616468.703792453</v>
+        <v>34656045.854344085</v>
       </c>
       <c r="G46" s="10">
-        <v>835</v>
+        <v>1415</v>
       </c>
       <c r="H46" s="10">
-        <v>6</v>
+        <v>319</v>
       </c>
       <c r="I46" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J46" s="10">
-        <v>616</v>
+        <v>932</v>
       </c>
       <c r="K46" s="10">
-        <v>36351905.914852493</v>
+        <v>34623144.718677483</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.35">
@@ -9406,7 +9406,7 @@
         <v>158</v>
       </c>
       <c r="B47" s="10">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C47" s="10">
         <v>3</v>
@@ -9415,25 +9415,25 @@
         <v>10</v>
       </c>
       <c r="E47" s="10">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F47" s="10">
-        <v>22704753.056662936</v>
+        <v>21610464.703248747</v>
       </c>
       <c r="G47" s="10">
-        <v>698</v>
+        <v>2252</v>
       </c>
       <c r="H47" s="10">
-        <v>3</v>
+        <v>137</v>
       </c>
       <c r="I47" s="10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J47" s="10">
-        <v>623</v>
+        <v>1573</v>
       </c>
       <c r="K47" s="10">
-        <v>22763455.27254276</v>
+        <v>21742784.05233898</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.35">
@@ -9441,7 +9441,7 @@
         <v>160</v>
       </c>
       <c r="B48" s="10">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C48" s="10">
         <v>2</v>
@@ -9450,25 +9450,25 @@
         <v>1</v>
       </c>
       <c r="E48" s="10">
-        <v>768</v>
+        <v>720</v>
       </c>
       <c r="F48" s="10">
-        <v>21905672.652470183</v>
+        <v>20687868.148741201</v>
       </c>
       <c r="G48" s="10">
-        <v>687</v>
+        <v>614</v>
       </c>
       <c r="H48" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J48" s="10">
-        <v>708</v>
+        <v>442</v>
       </c>
       <c r="K48" s="10">
-        <v>19508855.302097976</v>
+        <v>18652888.434304617</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
@@ -9476,7 +9476,7 @@
         <v>83</v>
       </c>
       <c r="B49" s="10">
-        <v>1272</v>
+        <v>1259</v>
       </c>
       <c r="C49" s="10">
         <v>12</v>
@@ -9485,25 +9485,25 @@
         <v>5</v>
       </c>
       <c r="E49" s="10">
-        <v>1058</v>
+        <v>1083</v>
       </c>
       <c r="F49" s="10">
-        <v>68951901.83255586</v>
+        <v>65941089.434293799</v>
       </c>
       <c r="G49" s="10">
-        <v>1250</v>
+        <v>2070</v>
       </c>
       <c r="H49" s="10">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I49" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J49" s="10">
-        <v>1375</v>
+        <v>1807</v>
       </c>
       <c r="K49" s="10">
-        <v>65624769.39583008</v>
+        <v>62024410.34365315</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
@@ -9511,7 +9511,7 @@
         <v>202</v>
       </c>
       <c r="B50" s="10">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="C50" s="10">
         <v>3</v>
@@ -9520,25 +9520,25 @@
         <v>2</v>
       </c>
       <c r="E50" s="10">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="F50" s="10">
-        <v>12686952.26487137</v>
+        <v>0</v>
       </c>
       <c r="G50" s="10">
-        <v>442</v>
+        <v>892</v>
       </c>
       <c r="H50" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I50" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J50" s="10">
-        <v>482</v>
+        <v>822</v>
       </c>
       <c r="K50" s="10">
-        <v>10487918.343386697</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
@@ -9546,34 +9546,34 @@
         <v>31</v>
       </c>
       <c r="B51" s="10">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="C51" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D51" s="10">
         <v>5</v>
       </c>
       <c r="E51" s="10">
-        <v>922</v>
+        <v>908</v>
       </c>
       <c r="F51" s="10">
-        <v>31224174.820838396</v>
+        <v>29718671.064681828</v>
       </c>
       <c r="G51" s="10">
-        <v>912</v>
+        <v>1097</v>
       </c>
       <c r="H51" s="10">
+        <v>8</v>
+      </c>
+      <c r="I51" s="10">
         <v>3</v>
       </c>
-      <c r="I51" s="10">
-        <v>6</v>
-      </c>
       <c r="J51" s="10">
-        <v>946</v>
+        <v>1098</v>
       </c>
       <c r="K51" s="10">
-        <v>30416321.719961289</v>
+        <v>29054377.526877664</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
@@ -9581,34 +9581,34 @@
         <v>33</v>
       </c>
       <c r="B52" s="10">
-        <v>1301</v>
+        <v>1308</v>
       </c>
       <c r="C52" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D52" s="10">
         <v>12</v>
       </c>
       <c r="E52" s="10">
-        <v>996</v>
+        <v>1055</v>
       </c>
       <c r="F52" s="10">
-        <v>46284776.708795786</v>
+        <v>43797964.177689955</v>
       </c>
       <c r="G52" s="10">
-        <v>1338</v>
+        <v>833</v>
       </c>
       <c r="H52" s="10">
         <v>6</v>
       </c>
       <c r="I52" s="10">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J52" s="10">
-        <v>1025</v>
+        <v>621</v>
       </c>
       <c r="K52" s="10">
-        <v>53489987.771002561</v>
+        <v>50825033.960358381</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.35">
@@ -9616,34 +9616,34 @@
         <v>85</v>
       </c>
       <c r="B53" s="10">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C53" s="10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D53" s="10">
         <v>5</v>
       </c>
       <c r="E53" s="10">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="F53" s="10">
-        <v>24156172.660815898</v>
+        <v>22770248.911103602</v>
       </c>
       <c r="G53" s="10">
-        <v>489</v>
+        <v>703</v>
       </c>
       <c r="H53" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I53" s="10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J53" s="10">
-        <v>380</v>
+        <v>547</v>
       </c>
       <c r="K53" s="10">
-        <v>27405554.935270023</v>
+        <v>26152148.725233007</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.35">
@@ -9651,7 +9651,7 @@
         <v>81</v>
       </c>
       <c r="B54" s="10">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C54" s="10">
         <v>2</v>
@@ -9660,25 +9660,25 @@
         <v>6</v>
       </c>
       <c r="E54" s="10">
-        <v>323</v>
+        <v>292</v>
       </c>
       <c r="F54" s="10">
-        <v>23676615.185974032</v>
+        <v>22546305.818256099</v>
       </c>
       <c r="G54" s="10">
-        <v>458</v>
+        <v>694</v>
       </c>
       <c r="H54" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I54" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J54" s="10">
-        <v>319</v>
+        <v>756</v>
       </c>
       <c r="K54" s="10">
-        <v>20136026.2156309</v>
+        <v>19126089.304449983</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.35">
@@ -9695,25 +9695,25 @@
         <v>2</v>
       </c>
       <c r="E55" s="10">
-        <v>384</v>
+        <v>348</v>
       </c>
       <c r="F55" s="10">
-        <v>19565337.991295934</v>
+        <v>18657852.426756896</v>
       </c>
       <c r="G55" s="10">
-        <v>424</v>
+        <v>1262</v>
       </c>
       <c r="H55" s="10">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I55" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J55" s="10">
-        <v>341</v>
+        <v>1358</v>
       </c>
       <c r="K55" s="10">
-        <v>17633388.891193338</v>
+        <v>16764643.498383747</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.35">
@@ -9721,34 +9721,34 @@
         <v>166</v>
       </c>
       <c r="B56" s="10">
-        <v>1127</v>
+        <v>1134</v>
       </c>
       <c r="C56" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D56" s="10">
         <v>1</v>
       </c>
       <c r="E56" s="10">
-        <v>947</v>
+        <v>995</v>
       </c>
       <c r="F56" s="10">
-        <v>42465575.241866045</v>
+        <v>40544706.538535334</v>
       </c>
       <c r="G56" s="10">
-        <v>1094</v>
+        <v>441</v>
       </c>
       <c r="H56" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I56" s="10">
         <v>1</v>
       </c>
       <c r="J56" s="10">
-        <v>941</v>
+        <v>492</v>
       </c>
       <c r="K56" s="10">
-        <v>41199724.440495275</v>
+        <v>39213836.923041739</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
@@ -9756,34 +9756,34 @@
         <v>93</v>
       </c>
       <c r="B57" s="10">
-        <v>971</v>
+        <v>978</v>
       </c>
       <c r="C57" s="10">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D57" s="10">
         <v>2</v>
       </c>
       <c r="E57" s="10">
-        <v>810</v>
+        <v>912</v>
       </c>
       <c r="F57" s="10">
-        <v>45055941.481699936</v>
+        <v>42886891.103262864</v>
       </c>
       <c r="G57" s="10">
-        <v>1011</v>
+        <v>922</v>
       </c>
       <c r="H57" s="10">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I57" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J57" s="10">
-        <v>817</v>
+        <v>949</v>
       </c>
       <c r="K57" s="10">
-        <v>43110471.737202205</v>
+        <v>40939585.895147137</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.35">
@@ -9791,34 +9791,34 @@
         <v>95</v>
       </c>
       <c r="B58" s="10">
-        <v>2122</v>
+        <v>2083</v>
       </c>
       <c r="C58" s="10">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D58" s="10">
         <v>7</v>
       </c>
       <c r="E58" s="10">
-        <v>1508</v>
+        <v>1462</v>
       </c>
       <c r="F58" s="10">
-        <v>63893921.779931098</v>
+        <v>60223755.032434106</v>
       </c>
       <c r="G58" s="10">
-        <v>2048</v>
+        <v>1354</v>
       </c>
       <c r="H58" s="10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I58" s="10">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J58" s="10">
-        <v>1783</v>
+        <v>1087</v>
       </c>
       <c r="K58" s="10">
-        <v>77451228.109518692</v>
+        <v>73666459.599487707</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.35">
@@ -9826,7 +9826,7 @@
         <v>174</v>
       </c>
       <c r="B59" s="10">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="C59" s="10">
         <v>3</v>
@@ -9835,25 +9835,25 @@
         <v>0</v>
       </c>
       <c r="E59" s="10">
-        <v>549</v>
+        <v>529</v>
       </c>
       <c r="F59" s="10">
-        <v>20534534.922981523</v>
+        <v>19628260.883901495</v>
       </c>
       <c r="G59" s="10">
-        <v>690</v>
+        <v>490</v>
       </c>
       <c r="H59" s="10">
         <v>4</v>
       </c>
       <c r="I59" s="10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J59" s="10">
-        <v>582</v>
+        <v>357</v>
       </c>
       <c r="K59" s="10">
-        <v>19415132.028813072</v>
+        <v>18415275.797894016</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.35">
@@ -9864,31 +9864,31 @@
         <v>889</v>
       </c>
       <c r="C60" s="10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D60" s="10">
         <v>5</v>
       </c>
       <c r="E60" s="10">
-        <v>742</v>
+        <v>796</v>
       </c>
       <c r="F60" s="10">
-        <v>32408420.627318345</v>
+        <v>30615413.367241357</v>
       </c>
       <c r="G60" s="10">
-        <v>863</v>
+        <v>457</v>
       </c>
       <c r="H60" s="10">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I60" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J60" s="10">
-        <v>763</v>
+        <v>310</v>
       </c>
       <c r="K60" s="10">
-        <v>33783028.370750755</v>
+        <v>32094490.60502778</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.35">
@@ -9896,7 +9896,7 @@
         <v>172</v>
       </c>
       <c r="B61" s="10">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="C61" s="10">
         <v>3</v>
@@ -9905,25 +9905,25 @@
         <v>1</v>
       </c>
       <c r="E61" s="10">
-        <v>595</v>
+        <v>679</v>
       </c>
       <c r="F61" s="10">
-        <v>24757924.64762653</v>
+        <v>23662873.351727627</v>
       </c>
       <c r="G61" s="10">
-        <v>729</v>
+        <v>418</v>
       </c>
       <c r="H61" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I61" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J61" s="10">
-        <v>603</v>
+        <v>326</v>
       </c>
       <c r="K61" s="10">
-        <v>21302689.942315493</v>
+        <v>20317389.490997106</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.35">
@@ -9931,7 +9931,7 @@
         <v>168</v>
       </c>
       <c r="B62" s="10">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="C62" s="10">
         <v>8</v>
@@ -9940,25 +9940,25 @@
         <v>1</v>
       </c>
       <c r="E62" s="10">
-        <v>1031</v>
+        <v>978</v>
       </c>
       <c r="F62" s="10">
-        <v>42696543.090585358</v>
+        <v>40636216.140523255</v>
       </c>
       <c r="G62" s="10">
-        <v>1107</v>
+        <v>1096</v>
       </c>
       <c r="H62" s="10">
         <v>7</v>
       </c>
       <c r="I62" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" s="10">
-        <v>1001</v>
+        <v>949</v>
       </c>
       <c r="K62" s="10">
-        <v>43034612.716141865</v>
+        <v>40981093.886455111</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.35">
@@ -9966,34 +9966,34 @@
         <v>101</v>
       </c>
       <c r="B63" s="10">
-        <v>1363</v>
+        <v>1374</v>
       </c>
       <c r="C63" s="10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D63" s="10">
         <v>4</v>
       </c>
       <c r="E63" s="10">
-        <v>1372</v>
+        <v>1304</v>
       </c>
       <c r="F63" s="10">
-        <v>54590695.006662175</v>
+        <v>51975399.294892192</v>
       </c>
       <c r="G63" s="10">
-        <v>1516</v>
+        <v>1011</v>
       </c>
       <c r="H63" s="10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I63" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J63" s="10">
-        <v>1546</v>
+        <v>803</v>
       </c>
       <c r="K63" s="10">
-        <v>53108125.971225314</v>
+        <v>50074452.206668533</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.35">
@@ -10001,34 +10001,34 @@
         <v>103</v>
       </c>
       <c r="B64" s="10">
-        <v>769</v>
+        <v>778</v>
       </c>
       <c r="C64" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D64" s="10">
         <v>5</v>
       </c>
       <c r="E64" s="10">
-        <v>693</v>
+        <v>741</v>
       </c>
       <c r="F64" s="10">
-        <v>27563613.08958514</v>
+        <v>26207240.497092113</v>
       </c>
       <c r="G64" s="10">
-        <v>771</v>
+        <v>2052</v>
       </c>
       <c r="H64" s="10">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I64" s="10">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J64" s="10">
-        <v>1398</v>
+        <v>1700</v>
       </c>
       <c r="K64" s="10">
-        <v>29166523.35953356</v>
+        <v>27821994.716877595</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.35">
@@ -10036,34 +10036,34 @@
         <v>105</v>
       </c>
       <c r="B65" s="10">
-        <v>692</v>
+        <v>681</v>
       </c>
       <c r="C65" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D65" s="10">
         <v>5</v>
       </c>
       <c r="E65" s="10">
-        <v>451</v>
+        <v>495</v>
       </c>
       <c r="F65" s="10">
-        <v>32225585.880645122</v>
+        <v>30690396.011699993</v>
       </c>
       <c r="G65" s="10">
-        <v>624</v>
+        <v>683</v>
       </c>
       <c r="H65" s="10">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I65" s="10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J65" s="10">
-        <v>471</v>
+        <v>650</v>
       </c>
       <c r="K65" s="10">
-        <v>32666251.142069764</v>
+        <v>31019483.13461696</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.35">
@@ -10071,34 +10071,34 @@
         <v>24</v>
       </c>
       <c r="B66" s="10">
-        <v>2048</v>
+        <v>2034</v>
       </c>
       <c r="C66" s="10">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D66" s="10">
         <v>9</v>
       </c>
       <c r="E66" s="10">
-        <v>1668</v>
+        <v>1780</v>
       </c>
       <c r="F66" s="10">
-        <v>85317689.138641283</v>
+        <v>80494151.517660826</v>
       </c>
       <c r="G66" s="10">
-        <v>2010</v>
+        <v>864</v>
       </c>
       <c r="H66" s="10">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I66" s="10">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J66" s="10">
-        <v>1722</v>
+        <v>733</v>
       </c>
       <c r="K66" s="10">
-        <v>104957958.57839498</v>
+        <v>99819639.769979075</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.35">
@@ -10106,34 +10106,34 @@
         <v>27</v>
       </c>
       <c r="B67" s="10">
-        <v>1587</v>
+        <v>1582</v>
       </c>
       <c r="C67" s="10">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D67" s="10">
         <v>7</v>
       </c>
       <c r="E67" s="10">
-        <v>1181</v>
+        <v>1208</v>
       </c>
       <c r="F67" s="10">
-        <v>78408477.996826321</v>
+        <v>74403597.224619329</v>
       </c>
       <c r="G67" s="10">
-        <v>1589</v>
+        <v>714</v>
       </c>
       <c r="H67" s="10">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I67" s="10">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J67" s="10">
-        <v>1222</v>
+        <v>622</v>
       </c>
       <c r="K67" s="10">
-        <v>79258311.448570415</v>
+        <v>75202591.101204753</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.35">
@@ -10141,7 +10141,7 @@
         <v>29</v>
       </c>
       <c r="B68" s="10">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="C68" s="10">
         <v>2</v>
@@ -10150,25 +10150,25 @@
         <v>1</v>
       </c>
       <c r="E68" s="10">
-        <v>655</v>
+        <v>737</v>
       </c>
       <c r="F68" s="10">
-        <v>48727801.593974993</v>
+        <v>46188082.820514478</v>
       </c>
       <c r="G68" s="10">
-        <v>893</v>
+        <v>1094</v>
       </c>
       <c r="H68" s="10">
         <v>7</v>
       </c>
       <c r="I68" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" s="10">
-        <v>734</v>
+        <v>990</v>
       </c>
       <c r="K68" s="10">
-        <v>50766777.004490346</v>
+        <v>48323897.682485439</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.35">
@@ -10176,34 +10176,34 @@
         <v>57</v>
       </c>
       <c r="B69" s="10">
-        <v>1984</v>
+        <v>2017</v>
       </c>
       <c r="C69" s="10">
-        <v>244</v>
+        <v>280</v>
       </c>
       <c r="D69" s="10">
         <v>13</v>
       </c>
       <c r="E69" s="10">
-        <v>1370</v>
+        <v>1282</v>
       </c>
       <c r="F69" s="10">
-        <v>71373716.671775326</v>
+        <v>67882627.172021404</v>
       </c>
       <c r="G69" s="10">
-        <v>2259</v>
+        <v>1522</v>
       </c>
       <c r="H69" s="10">
-        <v>476</v>
+        <v>11</v>
       </c>
       <c r="I69" s="10">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J69" s="10">
-        <v>1362</v>
+        <v>1548</v>
       </c>
       <c r="K69" s="10">
-        <v>75539145.629662246</v>
+        <v>71504925.88939625</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.35">
@@ -10211,7 +10211,7 @@
         <v>137</v>
       </c>
       <c r="B70" s="10">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C70" s="10">
         <v>2</v>
@@ -10220,25 +10220,25 @@
         <v>1</v>
       </c>
       <c r="E70" s="10">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="F70" s="10">
-        <v>5369530.2958202437</v>
+        <v>5076964.1164683579</v>
       </c>
       <c r="G70" s="10">
-        <v>254</v>
+        <v>762</v>
       </c>
       <c r="H70" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I70" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J70" s="10">
-        <v>242</v>
+        <v>702</v>
       </c>
       <c r="K70" s="10">
-        <v>3163370.7771156929</v>
+        <v>2920456.5121259899</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.35">
@@ -10246,34 +10246,34 @@
         <v>10</v>
       </c>
       <c r="B71" s="10">
-        <v>1797</v>
+        <v>1767</v>
       </c>
       <c r="C71" s="10">
         <v>6</v>
       </c>
       <c r="D71" s="10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E71" s="10">
-        <v>1598</v>
+        <v>1532</v>
       </c>
       <c r="F71" s="10">
-        <v>56257298.48234468</v>
+        <v>53626628.117396288</v>
       </c>
       <c r="G71" s="10">
-        <v>1672</v>
+        <v>623</v>
       </c>
       <c r="H71" s="10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I71" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J71" s="10">
-        <v>1580</v>
+        <v>481</v>
       </c>
       <c r="K71" s="10">
-        <v>54652536.380899057</v>
+        <v>51942957.043750465</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.35">
@@ -10281,7 +10281,7 @@
         <v>12</v>
       </c>
       <c r="B72" s="10">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C72" s="10">
         <v>3</v>
@@ -10290,25 +10290,25 @@
         <v>2</v>
       </c>
       <c r="E72" s="10">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F72" s="10">
-        <v>22953791.33224605</v>
+        <v>21968090.95705428</v>
       </c>
       <c r="G72" s="10">
-        <v>740</v>
+        <v>2012</v>
       </c>
       <c r="H72" s="10">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I72" s="10">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J72" s="10">
-        <v>646</v>
+        <v>1820</v>
       </c>
       <c r="K72" s="10">
-        <v>25985617.40753483</v>
+        <v>24581273.682099607</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.35">
@@ -10316,34 +10316,34 @@
         <v>162</v>
       </c>
       <c r="B73" s="10">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="C73" s="10">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D73" s="10">
         <v>5</v>
       </c>
       <c r="E73" s="10">
-        <v>1027</v>
+        <v>899</v>
       </c>
       <c r="F73" s="10">
-        <v>38152542.670676976</v>
+        <v>36202729.775051877</v>
       </c>
       <c r="G73" s="10">
-        <v>1433</v>
+        <v>1580</v>
       </c>
       <c r="H73" s="10">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="I73" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J73" s="10">
-        <v>987</v>
+        <v>1199</v>
       </c>
       <c r="K73" s="10">
-        <v>39573153.64074301</v>
+        <v>37415644.270037763</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.35">
@@ -10351,7 +10351,7 @@
         <v>63</v>
       </c>
       <c r="B74" s="10">
-        <v>1345</v>
+        <v>1327</v>
       </c>
       <c r="C74" s="10">
         <v>7</v>
@@ -10360,25 +10360,25 @@
         <v>5</v>
       </c>
       <c r="E74" s="10">
-        <v>597</v>
+        <v>1397</v>
       </c>
       <c r="F74" s="10">
-        <v>18265551.76599412</v>
+        <v>17783711.442227617</v>
       </c>
       <c r="G74" s="10">
-        <v>1259</v>
+        <v>898</v>
       </c>
       <c r="H74" s="10">
         <v>9</v>
       </c>
       <c r="I74" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J74" s="10">
-        <v>1253</v>
+        <v>716</v>
       </c>
       <c r="K74" s="10">
-        <v>25656378.209861528</v>
+        <v>23929894.673063796</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.35">
@@ -10386,34 +10386,34 @@
         <v>59</v>
       </c>
       <c r="B75" s="10">
-        <v>1745</v>
+        <v>1750</v>
       </c>
       <c r="C75" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D75" s="10">
         <v>5</v>
       </c>
       <c r="E75" s="10">
-        <v>1236</v>
+        <v>1189</v>
       </c>
       <c r="F75" s="10">
-        <v>67202251.554740682</v>
+        <v>63481150.813349932</v>
       </c>
       <c r="G75" s="10">
-        <v>1732</v>
+        <v>2257</v>
       </c>
       <c r="H75" s="10">
-        <v>13</v>
+        <v>527</v>
       </c>
       <c r="I75" s="10">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J75" s="10">
-        <v>1225</v>
+        <v>1301</v>
       </c>
       <c r="K75" s="10">
-        <v>68457996.802198336</v>
+        <v>65060314.538961947</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.35">
@@ -10424,31 +10424,31 @@
         <v>497</v>
       </c>
       <c r="C76" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D76" s="10">
         <v>2</v>
       </c>
       <c r="E76" s="10">
-        <v>628</v>
+        <v>424</v>
       </c>
       <c r="F76" s="10">
-        <v>14429554.57921656</v>
+        <v>13786630.717428997</v>
       </c>
       <c r="G76" s="10">
-        <v>517</v>
+        <v>250</v>
       </c>
       <c r="H76" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I76" s="10">
         <v>1</v>
       </c>
       <c r="J76" s="10">
-        <v>439</v>
+        <v>269</v>
       </c>
       <c r="K76" s="10">
-        <v>13727240.991854239</v>
+        <v>13044733.106628915</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.35">
@@ -10456,7 +10456,7 @@
         <v>170</v>
       </c>
       <c r="B77" s="10">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C77" s="10">
         <v>5</v>
@@ -10465,25 +10465,25 @@
         <v>1</v>
       </c>
       <c r="E77" s="10">
-        <v>852</v>
+        <v>761</v>
       </c>
       <c r="F77" s="10">
-        <v>22171799.827533696</v>
+        <v>21117188.467634171</v>
       </c>
       <c r="G77" s="10">
-        <v>882</v>
+        <v>1669</v>
       </c>
       <c r="H77" s="10">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I77" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J77" s="10">
-        <v>788</v>
+        <v>1722</v>
       </c>
       <c r="K77" s="10">
-        <v>22253625.293895539</v>
+        <v>21197941.625014752</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.35">
@@ -10491,7 +10491,7 @@
         <v>61</v>
       </c>
       <c r="B78" s="10">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="C78" s="10">
         <v>2</v>
@@ -10500,25 +10500,25 @@
         <v>4</v>
       </c>
       <c r="E78" s="10">
-        <v>633</v>
+        <v>173</v>
       </c>
       <c r="F78" s="10">
-        <v>15045724.399837304</v>
+        <v>14736341.28762248</v>
       </c>
       <c r="G78" s="10">
-        <v>646</v>
+        <v>762</v>
       </c>
       <c r="H78" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I78" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J78" s="10">
-        <v>470</v>
+        <v>578</v>
       </c>
       <c r="K78" s="10">
-        <v>22077326.343890451</v>
+        <v>20935184.704319578</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.35">
@@ -10526,7 +10526,7 @@
         <v>129</v>
       </c>
       <c r="B79" s="10">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C79" s="10">
         <v>5</v>
@@ -10535,25 +10535,25 @@
         <v>1</v>
       </c>
       <c r="E79" s="10">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F79" s="10">
-        <v>13803246.696355209</v>
+        <v>13803241.814353952</v>
       </c>
       <c r="G79" s="10">
-        <v>621</v>
+        <v>1377</v>
       </c>
       <c r="H79" s="10">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="I79" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J79" s="10">
-        <v>513</v>
+        <v>815</v>
       </c>
       <c r="K79" s="10">
-        <v>16036060.553102637</v>
+        <v>15506233.992221871</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.35">
@@ -10561,7 +10561,7 @@
         <v>35</v>
       </c>
       <c r="B80" s="10">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="C80" s="10">
         <v>6</v>
@@ -10570,25 +10570,25 @@
         <v>6</v>
       </c>
       <c r="E80" s="10">
-        <v>426</v>
+        <v>494</v>
       </c>
       <c r="F80" s="10">
-        <v>17050229.600482032</v>
+        <v>16238993.027723324</v>
       </c>
       <c r="G80" s="10">
-        <v>445</v>
+        <v>1260</v>
       </c>
       <c r="H80" s="10">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I80" s="10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J80" s="10">
-        <v>499</v>
+        <v>1288</v>
       </c>
       <c r="K80" s="10">
-        <v>18475041.61702498</v>
+        <v>17523590.520165198</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.35">
@@ -10596,7 +10596,7 @@
         <v>107</v>
       </c>
       <c r="B81" s="10">
-        <v>952</v>
+        <v>939</v>
       </c>
       <c r="C81" s="10">
         <v>11</v>
@@ -10605,25 +10605,25 @@
         <v>3</v>
       </c>
       <c r="E81" s="10">
-        <v>788</v>
+        <v>644</v>
       </c>
       <c r="F81" s="10">
-        <v>49208948.078755222</v>
+        <v>46538332.60440968</v>
       </c>
       <c r="G81" s="10">
-        <v>896</v>
+        <v>1723</v>
       </c>
       <c r="H81" s="10">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I81" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J81" s="10">
-        <v>610</v>
+        <v>1222</v>
       </c>
       <c r="K81" s="10">
-        <v>49281799.342978746</v>
+        <v>46909192.026860319</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.35">
@@ -10631,34 +10631,34 @@
         <v>37</v>
       </c>
       <c r="B82" s="10">
-        <v>786</v>
+        <v>802</v>
       </c>
       <c r="C82" s="10">
         <v>4</v>
       </c>
       <c r="D82" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E82" s="10">
-        <v>744</v>
+        <v>787</v>
       </c>
       <c r="F82" s="10">
-        <v>29405507.483340576</v>
+        <v>27857525.216046929</v>
       </c>
       <c r="G82" s="10">
-        <v>774</v>
+        <v>512</v>
       </c>
       <c r="H82" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I82" s="10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J82" s="10">
-        <v>724</v>
+        <v>458</v>
       </c>
       <c r="K82" s="10">
-        <v>28529057.216889117</v>
+        <v>27265674.916935232</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.35">
@@ -10666,7 +10666,7 @@
         <v>76</v>
       </c>
       <c r="B83" s="10">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C83" s="10">
         <v>1</v>
@@ -10675,25 +10675,25 @@
         <v>2</v>
       </c>
       <c r="E83" s="10">
-        <v>1049</v>
+        <v>978</v>
       </c>
       <c r="F83" s="10">
-        <v>23976905.020967472</v>
+        <v>22505847.82083239</v>
       </c>
       <c r="G83" s="10">
-        <v>960</v>
+        <v>876</v>
       </c>
       <c r="H83" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I83" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J83" s="10">
-        <v>1171</v>
+        <v>774</v>
       </c>
       <c r="K83" s="10">
-        <v>24304206.202539802</v>
+        <v>22856536.852877505</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.35">
@@ -10701,34 +10701,34 @@
         <v>65</v>
       </c>
       <c r="B84" s="10">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="C84" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D84" s="10">
         <v>4</v>
       </c>
       <c r="E84" s="10">
-        <v>818</v>
+        <v>836</v>
       </c>
       <c r="F84" s="10">
-        <v>27051046.84657656</v>
+        <v>25689391.598872714</v>
       </c>
       <c r="G84" s="10">
-        <v>991</v>
+        <v>652</v>
       </c>
       <c r="H84" s="10">
+        <v>2</v>
+      </c>
+      <c r="I84" s="10">
         <v>3</v>
       </c>
-      <c r="I84" s="10">
-        <v>5</v>
-      </c>
       <c r="J84" s="10">
-        <v>828</v>
+        <v>480</v>
       </c>
       <c r="K84" s="10">
-        <v>25200040.858496305</v>
+        <v>23804512.005560592</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.35">
@@ -10736,34 +10736,34 @@
         <v>89</v>
       </c>
       <c r="B85" s="10">
-        <v>755</v>
+        <v>743</v>
       </c>
       <c r="C85" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D85" s="10">
         <v>5</v>
       </c>
       <c r="E85" s="10">
-        <v>756</v>
+        <v>683</v>
       </c>
       <c r="F85" s="10">
-        <v>29446746.70471419</v>
+        <v>27707878.138874147</v>
       </c>
       <c r="G85" s="10">
-        <v>756</v>
+        <v>620</v>
       </c>
       <c r="H85" s="10">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I85" s="10">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J85" s="10">
-        <v>772</v>
+        <v>542</v>
       </c>
       <c r="K85" s="10">
-        <v>32219102.200047638</v>
+        <v>30321505.756113347</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.35">
@@ -10771,7 +10771,7 @@
         <v>147</v>
       </c>
       <c r="B86" s="10">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C86" s="10">
         <v>2</v>
@@ -10780,25 +10780,25 @@
         <v>1</v>
       </c>
       <c r="E86" s="10">
-        <v>679</v>
+        <v>566</v>
       </c>
       <c r="F86" s="10">
-        <v>12890849.296891289</v>
+        <v>12297623.509624189</v>
       </c>
       <c r="G86" s="10">
-        <v>568</v>
+        <v>447</v>
       </c>
       <c r="H86" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I86" s="10">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J86" s="10">
-        <v>589</v>
+        <v>464</v>
       </c>
       <c r="K86" s="10">
-        <v>14575510.609984348</v>
+        <v>13851013.837541368</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.35">
@@ -10806,7 +10806,7 @@
         <v>164</v>
       </c>
       <c r="B87" s="10">
-        <v>1696</v>
+        <v>1702</v>
       </c>
       <c r="C87" s="10">
         <v>10</v>
@@ -10815,25 +10815,25 @@
         <v>10</v>
       </c>
       <c r="E87" s="10">
-        <v>1385</v>
+        <v>1265</v>
       </c>
       <c r="F87" s="10">
-        <v>55870676.347908162</v>
+        <v>52982781.551008649</v>
       </c>
       <c r="G87" s="10">
-        <v>1768</v>
+        <v>900</v>
       </c>
       <c r="H87" s="10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I87" s="10">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J87" s="10">
-        <v>1394</v>
+        <v>550</v>
       </c>
       <c r="K87" s="10">
-        <v>60561873.35205964</v>
+        <v>56341564.403701298</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.35">
@@ -10841,34 +10841,34 @@
         <v>91</v>
       </c>
       <c r="B88" s="10">
-        <v>600</v>
+        <v>624</v>
       </c>
       <c r="C88" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D88" s="10">
         <v>3</v>
       </c>
       <c r="E88" s="10">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="F88" s="10">
-        <v>15216982.418813448</v>
+        <v>14099053.264334928</v>
       </c>
       <c r="G88" s="10">
-        <v>566</v>
+        <v>769</v>
       </c>
       <c r="H88" s="10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I88" s="10">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J88" s="10">
-        <v>648</v>
+        <v>709</v>
       </c>
       <c r="K88" s="10">
-        <v>13821141.409075508</v>
+        <v>13251615.22394882</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.35">
@@ -10876,7 +10876,7 @@
         <v>97</v>
       </c>
       <c r="B89" s="10">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="C89" s="10">
         <v>13</v>
@@ -10885,25 +10885,25 @@
         <v>6</v>
       </c>
       <c r="E89" s="10">
-        <v>521</v>
+        <v>501</v>
       </c>
       <c r="F89" s="10">
-        <v>26078100.101177879</v>
+        <v>24761684.048804503</v>
       </c>
       <c r="G89" s="10">
-        <v>632</v>
+        <v>954</v>
       </c>
       <c r="H89" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I89" s="10">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J89" s="10">
-        <v>522</v>
+        <v>1026</v>
       </c>
       <c r="K89" s="10">
-        <v>27183832.475523256</v>
+        <v>25936117.318591543</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.35">
@@ -10911,7 +10911,7 @@
         <v>78</v>
       </c>
       <c r="B90" s="10">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C90" s="10">
         <v>3</v>
@@ -10920,25 +10920,25 @@
         <v>1</v>
       </c>
       <c r="E90" s="10">
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="F90" s="10">
-        <v>7162107.3929737266</v>
+        <v>6820595.096124053</v>
       </c>
       <c r="G90" s="10">
-        <v>358</v>
+        <v>988</v>
       </c>
       <c r="H90" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I90" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J90" s="10">
-        <v>304</v>
+        <v>892</v>
       </c>
       <c r="K90" s="10">
-        <v>6488168.8620083621</v>
+        <v>6214020.6016599154</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.35">
@@ -10954,23 +10954,23 @@
       <c r="E91" s="13">
         <v>70150</v>
       </c>
-      <c r="F91" s="13">
-        <v>2762661133.2590084</v>
-      </c>
-      <c r="G91" s="13">
-        <v>84561</v>
-      </c>
-      <c r="H91" s="13">
-        <v>1547</v>
-      </c>
-      <c r="I91" s="13">
-        <v>314</v>
-      </c>
-      <c r="J91" s="13">
-        <v>70937</v>
-      </c>
-      <c r="K91" s="13">
-        <v>2842605836.7440019</v>
+      <c r="F91" s="10">
+        <v>0</v>
+      </c>
+      <c r="G91" s="10">
+        <v>760</v>
+      </c>
+      <c r="H91" s="10">
+        <v>2</v>
+      </c>
+      <c r="I91" s="10">
+        <v>6</v>
+      </c>
+      <c r="J91" s="10">
+        <v>771</v>
+      </c>
+      <c r="K91" s="10">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/SITE MONITORING.xlsx
+++ b/SITE MONITORING.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="205">
   <si>
     <t>SITE ID</t>
   </si>
@@ -641,6 +641,9 @@
   </si>
   <si>
     <t>GROWTH</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
   </si>
 </sst>
 </file>
@@ -742,7 +745,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -759,6 +762,9 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1146,27 +1152,27 @@
       </c>
       <c r="F2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12452036.798173808</v>
+        <v>14951903.352457</v>
       </c>
       <c r="G2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>12287955.952436997</v>
+        <v>14917900.520187205</v>
       </c>
       <c r="H2" s="12">
         <f>IFERROR(G2/F2-1,0)</f>
-        <v>-1.3177028657743395E-2</v>
+        <v>-2.2741474090793856E-3</v>
       </c>
       <c r="I2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="J2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>353</v>
+        <v>403</v>
       </c>
       <c r="K2" s="12">
         <f>IFERROR(J2/I2-1,0)</f>
-        <v>0.14610389610389607</v>
+        <v>0.29166666666666674</v>
       </c>
       <c r="L2" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1186,23 +1192,23 @@
       </c>
       <c r="P2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q2" s="12">
         <f>IFERROR(P2/O2-1,0)</f>
-        <v>-0.66666666666666674</v>
+        <v>0</v>
       </c>
       <c r="R2" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="S2">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="T2" s="12">
         <f>IFERROR(S2/R2-1,0)</f>
-        <v>7.2992700729928028E-3</v>
+        <v>7.2463768115942351E-3</v>
       </c>
       <c r="U2">
         <v>3</v>
@@ -1226,31 +1232,31 @@
       </c>
       <c r="F3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15270377.5820772</v>
+        <v>18047109.036899108</v>
       </c>
       <c r="G3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14339947.092993161</v>
+        <v>17442795.012084626</v>
       </c>
       <c r="H3" s="12">
         <f t="shared" ref="H3:H66" si="0">IFERROR(G3/F3-1,0)</f>
-        <v>-6.0930417999361275E-2</v>
+        <v>-3.3485364530069783E-2</v>
       </c>
       <c r="I3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>476</v>
+        <v>1193</v>
       </c>
       <c r="J3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>500</v>
+        <v>565</v>
       </c>
       <c r="K3" s="12">
         <f t="shared" ref="K3:K66" si="1">IFERROR(J3/I3-1,0)</f>
-        <v>5.0420168067226934E-2</v>
+        <v>-0.52640402347024307</v>
       </c>
       <c r="L3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -1258,7 +1264,7 @@
       </c>
       <c r="N3" s="12">
         <f t="shared" ref="N3:N66" si="2">IFERROR(M3/L3-1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -1274,15 +1280,15 @@
       </c>
       <c r="R3" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="S3">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="T3" s="12">
         <f t="shared" ref="T3:T66" si="4">IFERROR(S3/R3-1,0)</f>
-        <v>-5.6547619047619069E-2</v>
+        <v>-7.8171091445427776E-2</v>
       </c>
       <c r="U3">
         <v>2</v>
@@ -1306,27 +1312,27 @@
       </c>
       <c r="F4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17041117.995255239</v>
+        <v>22267218.174751002</v>
       </c>
       <c r="G4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19961475.905457538</v>
+        <v>25238742.900891054</v>
       </c>
       <c r="H4" s="12">
         <f t="shared" si="0"/>
-        <v>0.17137126279011827</v>
+        <v>0.13344840396406088</v>
       </c>
       <c r="I4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>809</v>
+        <v>860</v>
       </c>
       <c r="J4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>788</v>
+        <v>763</v>
       </c>
       <c r="K4" s="12">
         <f t="shared" si="1"/>
-        <v>-2.595797280593326E-2</v>
+        <v>-0.11279069767441863</v>
       </c>
       <c r="L4" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1342,27 +1348,27 @@
       </c>
       <c r="O4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q4" s="12">
         <f t="shared" si="3"/>
-        <v>0.28571428571428581</v>
+        <v>0.25</v>
       </c>
       <c r="R4" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="S4">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="T4" s="12">
         <f t="shared" si="4"/>
-        <v>0.1191860465116279</v>
+        <v>0.12772133526850515</v>
       </c>
       <c r="U4">
         <v>4</v>
@@ -1386,27 +1392,27 @@
       </c>
       <c r="F5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>30428581.790787671</v>
+        <v>38037278.997783728</v>
       </c>
       <c r="G5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>31260783.726436041</v>
+        <v>39072462.499094419</v>
       </c>
       <c r="H5" s="12">
         <f t="shared" si="0"/>
-        <v>2.7349350073894163E-2</v>
+        <v>2.7214972484519873E-2</v>
       </c>
       <c r="I5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1442</v>
+        <v>1457</v>
       </c>
       <c r="J5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1130</v>
+        <v>1122</v>
       </c>
       <c r="K5" s="12">
         <f t="shared" si="1"/>
-        <v>-0.21636615811373094</v>
+        <v>-0.22992450240219631</v>
       </c>
       <c r="L5" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1426,23 +1432,23 @@
       </c>
       <c r="P5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q5" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="R5" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="S5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="T5" s="12">
         <f t="shared" si="4"/>
-        <v>1.7602682313495377E-2</v>
+        <v>2.099076406381184E-2</v>
       </c>
       <c r="U5">
         <v>3</v>
@@ -1466,27 +1472,27 @@
       </c>
       <c r="F6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12572009.692979235</v>
+        <v>15830680.155176772</v>
       </c>
       <c r="G6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>14087321.867469653</v>
+        <v>16929716.14046596</v>
       </c>
       <c r="H6" s="12">
         <f t="shared" si="0"/>
-        <v>0.12053062410034854</v>
+        <v>6.9424432463806252E-2</v>
       </c>
       <c r="I6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="J6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="K6" s="12">
         <f t="shared" si="1"/>
-        <v>0.13213213213213204</v>
+        <v>0.19937694704049846</v>
       </c>
       <c r="L6" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1502,7 +1508,7 @@
       </c>
       <c r="O6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -1510,19 +1516,19 @@
       </c>
       <c r="Q6" s="12">
         <f t="shared" si="3"/>
-        <v>-0.5</v>
+        <v>-0.66666666666666674</v>
       </c>
       <c r="R6" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="S6">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="T6" s="12">
         <f t="shared" si="4"/>
-        <v>-2.5943396226415061E-2</v>
+        <v>-2.8368794326241176E-2</v>
       </c>
       <c r="U6">
         <v>3</v>
@@ -1546,27 +1552,27 @@
       </c>
       <c r="F7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>10954941.459135331</v>
+        <v>13208824.130166763</v>
       </c>
       <c r="G7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11489847.967613995</v>
+        <v>14148259.528787032</v>
       </c>
       <c r="H7" s="12">
         <f t="shared" si="0"/>
-        <v>4.8827874660398507E-2</v>
+        <v>7.1121803830725083E-2</v>
       </c>
       <c r="I7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="J7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>268</v>
+        <v>329</v>
       </c>
       <c r="K7" s="12">
         <f t="shared" si="1"/>
-        <v>-0.18292682926829273</v>
+        <v>1.5432098765432167E-2</v>
       </c>
       <c r="L7" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1594,15 +1600,15 @@
       </c>
       <c r="R7" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="S7">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="T7" s="12">
         <f t="shared" si="4"/>
-        <v>3.2000000000000028E-2</v>
+        <v>5.9299191374662996E-2</v>
       </c>
       <c r="U7">
         <v>2</v>
@@ -1626,27 +1632,27 @@
       </c>
       <c r="F8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12590405.038448486</v>
+        <v>15049479.585371532</v>
       </c>
       <c r="G8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13775550.668594858</v>
+        <v>17921273.980282489</v>
       </c>
       <c r="H8" s="12">
         <f t="shared" si="0"/>
-        <v>9.4130858104022996E-2</v>
+        <v>0.19082350181081442</v>
       </c>
       <c r="I8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>374</v>
+        <v>515</v>
       </c>
       <c r="K8" s="12">
         <f t="shared" si="1"/>
-        <v>-0.18518518518518523</v>
+        <v>0.11956521739130443</v>
       </c>
       <c r="L8" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1674,15 +1680,15 @@
       </c>
       <c r="R8" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="S8">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>419</v>
+        <v>627</v>
       </c>
       <c r="T8" s="12">
         <f t="shared" si="4"/>
-        <v>-0.28862478777589129</v>
+        <v>6.0913705583756306E-2</v>
       </c>
       <c r="U8">
         <v>9</v>
@@ -1706,27 +1712,27 @@
       </c>
       <c r="F9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5908394.1481695939</v>
+        <v>7249710.91573497</v>
       </c>
       <c r="G9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6045648.5828848016</v>
+        <v>7369289.6027623713</v>
       </c>
       <c r="H9" s="12">
         <f t="shared" si="0"/>
-        <v>2.3230412743829643E-2</v>
+        <v>1.6494269691204488E-2</v>
       </c>
       <c r="I9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="K9" s="12">
         <f t="shared" si="1"/>
-        <v>2.2679738562091503</v>
+        <v>-1.4084507042253502E-2</v>
       </c>
       <c r="L9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1734,11 +1740,11 @@
       </c>
       <c r="M9" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N9" s="12">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -1746,23 +1752,23 @@
       </c>
       <c r="P9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="12">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="R9" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="S9">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>629</v>
+        <v>180</v>
       </c>
       <c r="T9" s="12">
         <f t="shared" si="4"/>
-        <v>2.6569767441860463</v>
+        <v>3.4482758620689724E-2</v>
       </c>
       <c r="U9">
         <v>1</v>
@@ -1786,27 +1792,27 @@
       </c>
       <c r="F10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5680298.6802293016</v>
+        <v>6728804.5398440929</v>
       </c>
       <c r="G10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>2860659.9967147</v>
+        <v>4526039.6878608</v>
       </c>
       <c r="H10" s="12">
         <f t="shared" si="0"/>
-        <v>-0.49638915878289325</v>
+        <v>-0.3273634772625349</v>
       </c>
       <c r="I10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="J10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>757</v>
+        <v>225</v>
       </c>
       <c r="K10" s="12">
         <f t="shared" si="1"/>
-        <v>3.6441717791411046</v>
+        <v>0.46103896103896114</v>
       </c>
       <c r="L10" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1826,23 +1832,23 @@
       </c>
       <c r="P10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="12">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R10" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="S10">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>774</v>
+        <v>202</v>
       </c>
       <c r="T10" s="12">
         <f t="shared" si="4"/>
-        <v>2.9289340101522843</v>
+        <v>4.663212435233155E-2</v>
       </c>
       <c r="U10">
         <v>1</v>
@@ -1866,27 +1872,27 @@
       </c>
       <c r="F11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8944383.1211307161</v>
+        <v>10735179.324833753</v>
       </c>
       <c r="G11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>11890504.003905904</v>
+        <v>14892000.491402712</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" si="0"/>
-        <v>0.32938223272380918</v>
+        <v>0.38721487930368892</v>
       </c>
       <c r="I11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="J11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1155</v>
+        <v>360</v>
       </c>
       <c r="K11" s="12">
         <f t="shared" si="1"/>
-        <v>2.5</v>
+        <v>0.12149532710280364</v>
       </c>
       <c r="L11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1894,11 +1900,11 @@
       </c>
       <c r="M11" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -1906,23 +1912,23 @@
       </c>
       <c r="P11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Q11" s="12">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="R11" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="S11">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1210</v>
+        <v>392</v>
       </c>
       <c r="T11" s="12">
         <f t="shared" si="4"/>
-        <v>2.6119402985074629</v>
+        <v>0.18429003021148027</v>
       </c>
       <c r="U11">
         <v>4</v>
@@ -1946,27 +1952,27 @@
       </c>
       <c r="F12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>4262490.9429104608</v>
+        <v>5191002.4608562756</v>
       </c>
       <c r="G12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6152814.3065978391</v>
+        <v>7741147.2939902628</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="0"/>
-        <v>0.44347856429617449</v>
+        <v>0.49126249743933492</v>
       </c>
       <c r="I12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="J12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>374</v>
+        <v>264</v>
       </c>
       <c r="K12" s="12">
         <f t="shared" si="1"/>
-        <v>0.65486725663716805</v>
+        <v>5.1792828685258918E-2</v>
       </c>
       <c r="L12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -1974,11 +1980,11 @@
       </c>
       <c r="M12" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -1986,7 +1992,7 @@
       </c>
       <c r="P12" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="12">
         <f t="shared" si="3"/>
@@ -1998,11 +2004,11 @@
       </c>
       <c r="S12">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>410</v>
+        <v>228</v>
       </c>
       <c r="T12" s="12">
         <f t="shared" si="4"/>
-        <v>0.92488262910798125</v>
+        <v>7.0422535211267512E-2</v>
       </c>
       <c r="U12">
         <v>3</v>
@@ -2026,27 +2032,27 @@
       </c>
       <c r="F13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5733341.8539821506</v>
+        <v>7100621.9748010579</v>
       </c>
       <c r="G13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>6544098.7908061044</v>
+        <v>8038990.1155283554</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="0"/>
-        <v>0.14141088347293196</v>
+        <v>0.13215294998908722</v>
       </c>
       <c r="I13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="J13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>322</v>
+        <v>234</v>
       </c>
       <c r="K13" s="12">
         <f t="shared" si="1"/>
-        <v>0.5862068965517242</v>
+        <v>0.1090047393364928</v>
       </c>
       <c r="L13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2054,11 +2060,11 @@
       </c>
       <c r="M13" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N13" s="12">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2074,15 +2080,15 @@
       </c>
       <c r="R13" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="S13">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>390</v>
+        <v>247</v>
       </c>
       <c r="T13" s="12">
         <f t="shared" si="4"/>
-        <v>0.5234375</v>
+        <v>-2.7559055118110187E-2</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -2106,27 +2112,27 @@
       </c>
       <c r="F14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12150068.330912439</v>
+        <v>18247182.819930792</v>
       </c>
       <c r="G14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>27129953.922294252</v>
+        <v>34829506.004046865</v>
       </c>
       <c r="H14" s="12">
         <f t="shared" si="0"/>
-        <v>1.2329054605618719</v>
+        <v>0.90876073023194315</v>
       </c>
       <c r="I14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1199</v>
+        <v>1194</v>
       </c>
       <c r="J14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>529</v>
+        <v>1032</v>
       </c>
       <c r="K14" s="12">
         <f t="shared" si="1"/>
-        <v>-0.55879899916597164</v>
+        <v>-0.13567839195979903</v>
       </c>
       <c r="L14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2134,11 +2140,11 @@
       </c>
       <c r="M14" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N14" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2146,7 +2152,7 @@
       </c>
       <c r="P14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q14" s="12">
         <f t="shared" si="3"/>
@@ -2154,15 +2160,15 @@
       </c>
       <c r="R14" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1426</v>
+        <v>1419</v>
       </c>
       <c r="S14">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>615</v>
+        <v>1378</v>
       </c>
       <c r="T14" s="12">
         <f t="shared" si="4"/>
-        <v>-0.56872370266479666</v>
+        <v>-2.8893587033121948E-2</v>
       </c>
       <c r="U14">
         <v>3</v>
@@ -2186,27 +2192,27 @@
       </c>
       <c r="F15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>37115893.490185946</v>
+        <v>42818536.417284623</v>
       </c>
       <c r="G15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>46248297.021251909</v>
+        <v>56867748.293998539</v>
       </c>
       <c r="H15" s="12">
         <f t="shared" si="0"/>
-        <v>0.2460510221444816</v>
+        <v>0.3281105112934839</v>
       </c>
       <c r="I15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>996</v>
+        <v>976</v>
       </c>
       <c r="J15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>150</v>
+        <v>841</v>
       </c>
       <c r="K15" s="12">
         <f t="shared" si="1"/>
-        <v>-0.8493975903614458</v>
+        <v>-0.13831967213114749</v>
       </c>
       <c r="L15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2214,11 +2220,11 @@
       </c>
       <c r="M15" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N15" s="12">
         <f t="shared" si="2"/>
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
       <c r="O15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2226,23 +2232,23 @@
       </c>
       <c r="P15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="12">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R15" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="S15">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>176</v>
+        <v>1235</v>
       </c>
       <c r="T15" s="12">
         <f t="shared" si="4"/>
-        <v>-0.86020651310563934</v>
+        <v>-2.1394611727416746E-2</v>
       </c>
       <c r="U15">
         <v>4</v>
@@ -2266,27 +2272,27 @@
       </c>
       <c r="F16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24557779.647644848</v>
+        <v>30006800.283337731</v>
       </c>
       <c r="G16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>24780324.33078628</v>
+        <v>30255910.378636178</v>
       </c>
       <c r="H16" s="12">
         <f t="shared" si="0"/>
-        <v>9.062084860052666E-3</v>
+        <v>8.3017880262552524E-3</v>
       </c>
       <c r="I16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1758</v>
+        <v>1040</v>
       </c>
       <c r="J16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>186</v>
+        <v>878</v>
       </c>
       <c r="K16" s="12">
         <f t="shared" si="1"/>
-        <v>-0.89419795221843001</v>
+        <v>-0.15576923076923077</v>
       </c>
       <c r="L16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2294,11 +2300,11 @@
       </c>
       <c r="M16" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N16" s="12">
         <f t="shared" si="2"/>
-        <v>-0.75</v>
+        <v>0.25</v>
       </c>
       <c r="O16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2306,23 +2312,23 @@
       </c>
       <c r="P16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q16" s="12">
         <f t="shared" si="3"/>
-        <v>-0.75</v>
+        <v>0.25</v>
       </c>
       <c r="R16" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="S16">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>199</v>
+        <v>1018</v>
       </c>
       <c r="T16" s="12">
         <f t="shared" si="4"/>
-        <v>-0.80642023346303504</v>
+        <v>-5.859375E-3</v>
       </c>
       <c r="U16">
         <v>4</v>
@@ -2346,27 +2352,27 @@
       </c>
       <c r="F17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>24093521.100269504</v>
+        <v>28268248.559507672</v>
       </c>
       <c r="G17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>20292128.333114807</v>
+        <v>25029632.531552076</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="0"/>
-        <v>-0.15777655542062619</v>
+        <v>-0.11456726868443812</v>
       </c>
       <c r="I17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>587</v>
+        <v>666</v>
       </c>
       <c r="J17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>431</v>
+        <v>659</v>
       </c>
       <c r="K17" s="12">
         <f t="shared" si="1"/>
-        <v>-0.26575809199318567</v>
+        <v>-1.0510510510510551E-2</v>
       </c>
       <c r="L17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2374,11 +2380,11 @@
       </c>
       <c r="M17" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N17" s="12">
         <f t="shared" si="2"/>
-        <v>-0.66666666666666674</v>
+        <v>0</v>
       </c>
       <c r="O17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2386,23 +2392,23 @@
       </c>
       <c r="P17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q17" s="12">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R17" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="S17">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>387</v>
+        <v>918</v>
       </c>
       <c r="T17" s="12">
         <f t="shared" si="4"/>
-        <v>-0.59177215189873422</v>
+        <v>-3.5714285714285698E-2</v>
       </c>
       <c r="U17">
         <v>4</v>
@@ -2426,27 +2432,27 @@
       </c>
       <c r="F18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>84378043.245911941</v>
+        <v>104117051.10477778</v>
       </c>
       <c r="G18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>91431790.086039543</v>
+        <v>109390065.15594928</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="0"/>
-        <v>8.3596947366628482E-2</v>
+        <v>5.0645057607951349E-2</v>
       </c>
       <c r="I18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2465</v>
+        <v>2480</v>
       </c>
       <c r="J18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>263</v>
+        <v>2242</v>
       </c>
       <c r="K18" s="12">
         <f t="shared" si="1"/>
-        <v>-0.89330628803245438</v>
+        <v>-9.5967741935483852E-2</v>
       </c>
       <c r="L18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2454,11 +2460,11 @@
       </c>
       <c r="M18" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N18" s="12">
         <f t="shared" si="2"/>
-        <v>-0.81818181818181812</v>
+        <v>-9.0909090909090939E-2</v>
       </c>
       <c r="O18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2466,23 +2472,23 @@
       </c>
       <c r="P18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="Q18" s="12">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>-0.73093525179856123</v>
       </c>
       <c r="R18" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>3177</v>
+        <v>3159</v>
       </c>
       <c r="S18">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>226</v>
+        <v>2782</v>
       </c>
       <c r="T18" s="12">
         <f t="shared" si="4"/>
-        <v>-0.92886370790053507</v>
+        <v>-0.11934156378600824</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -2506,27 +2512,27 @@
       </c>
       <c r="F19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>45853440.719571456</v>
+        <v>55037135.637395509</v>
       </c>
       <c r="G19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>28580704.230768949</v>
+        <v>37942537.595623389</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="0"/>
-        <v>-0.3766944468668858</v>
+        <v>-0.31060115763286622</v>
       </c>
       <c r="I19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1195</v>
+        <v>1171</v>
       </c>
       <c r="J19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>231</v>
+        <v>1203</v>
       </c>
       <c r="K19" s="12">
         <f t="shared" si="1"/>
-        <v>-0.80669456066945611</v>
+        <v>2.7327070879590076E-2</v>
       </c>
       <c r="L19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2534,35 +2540,35 @@
       </c>
       <c r="M19" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N19" s="12">
         <f t="shared" si="2"/>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="O19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q19" s="12">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R19" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="S19">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>239</v>
+        <v>1380</v>
       </c>
       <c r="T19" s="12">
         <f t="shared" si="4"/>
-        <v>-0.83344947735191632</v>
+        <v>-3.7656903765690419E-2</v>
       </c>
       <c r="U19">
         <v>1</v>
@@ -2586,27 +2592,27 @@
       </c>
       <c r="F20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>91985409.680114254</v>
+        <v>111145086.15534</v>
       </c>
       <c r="G20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>91798677.850888729</v>
+        <v>111493327.89559795</v>
       </c>
       <c r="H20" s="12">
         <f t="shared" si="0"/>
-        <v>-2.0300157370054528E-3</v>
+        <v>3.1332176014622348E-3</v>
       </c>
       <c r="I20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>2257</v>
+        <v>2220</v>
       </c>
       <c r="J20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1040</v>
+        <v>2018</v>
       </c>
       <c r="K20" s="12">
         <f t="shared" si="1"/>
-        <v>-0.539211342490031</v>
+        <v>-9.099099099099095E-2</v>
       </c>
       <c r="L20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2614,35 +2620,35 @@
       </c>
       <c r="M20" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N20" s="12">
         <f t="shared" si="2"/>
-        <v>-0.72727272727272729</v>
+        <v>-9.0909090909090939E-2</v>
       </c>
       <c r="O20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="Q20" s="12">
         <f t="shared" si="3"/>
-        <v>-0.78947368421052633</v>
+        <v>0</v>
       </c>
       <c r="R20" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>3011</v>
+        <v>3002</v>
       </c>
       <c r="S20">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1386</v>
+        <v>2930</v>
       </c>
       <c r="T20" s="12">
         <f t="shared" si="4"/>
-        <v>-0.53968781135835275</v>
+        <v>-2.398401065956024E-2</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2666,27 +2672,27 @@
       </c>
       <c r="F21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>13083985.836379612</v>
+        <v>15827558.639347089</v>
       </c>
       <c r="G21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>13952390.293539824</v>
+        <v>16723491.22569038</v>
       </c>
       <c r="H21" s="12">
         <f t="shared" si="0"/>
-        <v>6.6371552829539215E-2</v>
+        <v>5.6605861128576906E-2</v>
       </c>
       <c r="I21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="J21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>893</v>
+        <v>459</v>
       </c>
       <c r="K21" s="12">
         <f t="shared" si="1"/>
-        <v>0.9204301075268817</v>
+        <v>-1.5021459227467782E-2</v>
       </c>
       <c r="L21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2694,11 +2700,11 @@
       </c>
       <c r="M21" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N21" s="12">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2706,23 +2712,23 @@
       </c>
       <c r="P21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q21" s="12">
         <f t="shared" si="3"/>
-        <v>-0.66666666666666674</v>
+        <v>0</v>
       </c>
       <c r="R21" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="S21">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1233</v>
+        <v>539</v>
       </c>
       <c r="T21" s="12">
         <f t="shared" si="4"/>
-        <v>1.2541133455210236</v>
+        <v>-7.3664825046040328E-3</v>
       </c>
       <c r="U21">
         <v>1</v>
@@ -2746,27 +2752,27 @@
       </c>
       <c r="F22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>36202793.63631741</v>
+        <v>44384128.087760858</v>
       </c>
       <c r="G22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>38550165.164171152</v>
+        <v>46771900.003547184</v>
       </c>
       <c r="H22" s="12">
         <f t="shared" si="0"/>
-        <v>6.4839513531324222E-2</v>
+        <v>5.3797878175391389E-2</v>
       </c>
       <c r="I22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1297</v>
+        <v>1325</v>
       </c>
       <c r="J22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>904</v>
+        <v>1344</v>
       </c>
       <c r="K22" s="12">
         <f t="shared" si="1"/>
-        <v>-0.30300693909020815</v>
+        <v>1.4339622641509342E-2</v>
       </c>
       <c r="L22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2774,11 +2780,11 @@
       </c>
       <c r="M22" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N22" s="12">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2786,23 +2792,23 @@
       </c>
       <c r="P22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="Q22" s="12">
         <f t="shared" si="3"/>
-        <v>-0.77272727272727271</v>
+        <v>-4.5454545454545414E-2</v>
       </c>
       <c r="R22" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1731</v>
+        <v>1743</v>
       </c>
       <c r="S22">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1017</v>
+        <v>1684</v>
       </c>
       <c r="T22" s="12">
         <f t="shared" si="4"/>
-        <v>-0.41247833622183705</v>
+        <v>-3.3849684452094131E-2</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2826,27 +2832,27 @@
       </c>
       <c r="F23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15994034.782365471</v>
+        <v>19610000.749189828</v>
       </c>
       <c r="G23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>16023991.278544333</v>
+        <v>19839840.108317044</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="0"/>
-        <v>1.8729793067531197E-3</v>
+        <v>1.1720517610725345E-2</v>
       </c>
       <c r="I23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="J23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>673</v>
+        <v>837</v>
       </c>
       <c r="K23" s="12">
         <f t="shared" si="1"/>
-        <v>-9.4212651413189796E-2</v>
+        <v>0.11748998664886523</v>
       </c>
       <c r="L23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2854,11 +2860,11 @@
       </c>
       <c r="M23" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N23" s="12">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2866,23 +2872,23 @@
       </c>
       <c r="P23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="Q23" s="12">
         <f t="shared" si="3"/>
-        <v>-0.66666666666666674</v>
+        <v>8.3333333333333259E-2</v>
       </c>
       <c r="R23" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>875</v>
+        <v>868</v>
       </c>
       <c r="S23">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>919</v>
+        <v>871</v>
       </c>
       <c r="T23" s="12">
         <f t="shared" si="4"/>
-        <v>5.0285714285714267E-2</v>
+        <v>3.4562211981565838E-3</v>
       </c>
       <c r="U23">
         <v>1</v>
@@ -2906,27 +2912,27 @@
       </c>
       <c r="F24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17730094.775826979</v>
+        <v>22176101.292153176</v>
       </c>
       <c r="G24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>19429198.640231583</v>
+        <v>23440716.256520767</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="0"/>
-        <v>9.5831628983796824E-2</v>
+        <v>5.7026027600941109E-2</v>
       </c>
       <c r="I24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>920</v>
+        <v>866</v>
       </c>
       <c r="J24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2089</v>
+        <v>710</v>
       </c>
       <c r="K24" s="12">
         <f t="shared" si="1"/>
-        <v>1.2706521739130436</v>
+        <v>-0.18013856812933027</v>
       </c>
       <c r="L24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -2934,11 +2940,11 @@
       </c>
       <c r="M24" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N24" s="12">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
@@ -2946,23 +2952,23 @@
       </c>
       <c r="P24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>186</v>
+        <v>6</v>
       </c>
       <c r="Q24" s="12">
         <f t="shared" si="3"/>
-        <v>36.200000000000003</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="R24" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>897</v>
+        <v>889</v>
       </c>
       <c r="S24">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2788</v>
+        <v>873</v>
       </c>
       <c r="T24" s="12">
         <f t="shared" si="4"/>
-        <v>2.1081382385730212</v>
+        <v>-1.7997750281214864E-2</v>
       </c>
       <c r="U24">
         <v>3</v>
@@ -2986,27 +2992,27 @@
       </c>
       <c r="F25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5277024.5563090751</v>
+        <v>6619221.7997575877</v>
       </c>
       <c r="G25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>4433708.8725122856</v>
+        <v>5691865.8715327857</v>
       </c>
       <c r="H25" s="12">
         <f t="shared" si="0"/>
-        <v>-0.15980893679726071</v>
+        <v>-0.14010044628792528</v>
       </c>
       <c r="I25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="J25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>1195</v>
+        <v>181</v>
       </c>
       <c r="K25" s="12">
         <f t="shared" si="1"/>
-        <v>5.9476744186046515</v>
+        <v>-7.6530612244897989E-2</v>
       </c>
       <c r="L25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3014,7 +3020,7 @@
       </c>
       <c r="M25" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N25" s="12">
         <f t="shared" si="2"/>
@@ -3026,23 +3032,23 @@
       </c>
       <c r="P25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="12">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R25" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="S25">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>1379</v>
+        <v>231</v>
       </c>
       <c r="T25" s="12">
         <f t="shared" si="4"/>
-        <v>4.9956521739130437</v>
+        <v>-1.7021276595744705E-2</v>
       </c>
       <c r="U25">
         <v>1</v>
@@ -3066,27 +3072,27 @@
       </c>
       <c r="F26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>40235450.07087151</v>
+        <v>47805891.078372709</v>
       </c>
       <c r="G26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>36803930.469524823</v>
+        <v>44573085.392273486</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="0"/>
-        <v>-8.5285975310387729E-2</v>
+        <v>-6.7623583896791684E-2</v>
       </c>
       <c r="I26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>1323</v>
+        <v>1306</v>
       </c>
       <c r="J26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>2088</v>
+        <v>1311</v>
       </c>
       <c r="K26" s="12">
         <f t="shared" si="1"/>
-        <v>0.57823129251700678</v>
+        <v>3.8284839203674981E-3</v>
       </c>
       <c r="L26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
@@ -3094,35 +3100,35 @@
       </c>
       <c r="M26" s="2">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N26" s="12">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Q26" s="12">
         <f t="shared" si="3"/>
-        <v>4.25</v>
+        <v>1.4</v>
       </c>
       <c r="R26" s="1">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1653</v>
+        <v>1660</v>
       </c>
       <c r="S26">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>2920</v>
+        <v>1632</v>
       </c>
       <c r="T26" s="12">
         <f t="shared" si="4"/>
-        <v>0.76648517846339992</v>
+        <v>-1.6867469879518038E-2</v>
       </c>
       <c r="U26">
         <v>1</v>
@@ -3146,27 +3152,27 @@
       </c>
       <c r="F27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>28301686.739777543</v>
+        <v>34419089.876729511</v>
       </c>
       <c r="G27" s="1">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>30880741.730442863</v>
+        <v>37901298.32547728</v>
       </c>
       <c r="H27" s="12">
         <f t="